--- a/public/ultimahora.xlsx
+++ b/public/ultimahora.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Todas las noticias" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Todas las noticias'!$A$1:$E$278</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Todas las noticias'!$A$1:$E$279</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -515,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E278"/>
+  <dimension ref="A1:E279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 07:17 p. m.</t>
+          <t>21/05/2026 07:38 p. m.</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -565,24 +565,24 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Más de 9.200 testigos electorales en el exterior fueron acreditados por el CNE para las elecciones</t>
+          <t>Profesor en Bolívar se desplomó mientras cantaba ante sus alumnos: “Inesperada y sensible partida”</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/elecciones/mas-de-9-200-testigos-electorales-en-el-exterior-fueron-acreditados-por-el-cne-para-las-elecciones-rg10</t>
+          <t>https://www.noticiascaracol.com/colombia/profesor-en-bolivar-se-desplomo-mientras-cantaba-ante-sus-alumnos-inesperada-y-sensible-partida-rg10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 07:04 p. m.</t>
+          <t>21/05/2026 07:26 p. m.</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -592,24 +592,24 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Encuesta Invamer: Cepeda obtiene 44,6 %; De La Espriella, 31,6 % y Paloma Valencia, 14 %</t>
+          <t>Ofrecen hasta $100 millones por autores de homicidio y desaparición de turistas en Buenaventura</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/elecciones/encuesta-invamer-cepeda-obtiene-44-6-de-la-espriella-31-6-y-paloma-valencia-14-so35</t>
+          <t>https://www.noticiascaracol.com/colombia/ofrecen-hasta-100-millones-por-autores-de-homicidio-y-desaparicion-de-turistas-en-buenaventura-rg10</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:51 p. m.</t>
+          <t>21/05/2026 07:15 p. m.</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -619,24 +619,24 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Cristiano Ronaldo conquista la liga de Arabia a sus 40 años antes del Mundial</t>
+          <t>Los cinco mejores municipios para vivir pensionado cerca a Bogotá, según la IA</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/deportes/futbol/cristiano-ronaldo-conquista-la-liga-de-arabia-a-sus-40-anos-antes-del-mundial-cb20</t>
+          <t>https://www.noticiascaracol.com/estilo-de-vida/los-cinco-mejores-municipios-para-vivir-pensionado-cerca-a-bogota-segun-la-ia-so35</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:47 p. m.</t>
+          <t>21/05/2026 07:02 p. m.</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -646,24 +646,24 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>“Es deplorable que eso haya sucedido”, Benedetti tras ataque a sede de Paloma Valencia</t>
+          <t>Iván Cepeda 44,6%; Abelardo De La Espriella 31,6%; Paloma Valencia 14,0%: encuesta Invamer</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/es-deplorable-que-eso-haya-sucedido-benedetti-tras-ataque-a-sede-de-paloma-valencia-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/ivan-cepeda-44-6-abelardo-de-la-espriella-31-6-paloma-valencia-14-0-encuesta-invamer-rg10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:31 p. m.</t>
+          <t>21/05/2026 06:52 p. m.</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -673,24 +673,24 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Néstor Lorenzo tomó decisión con Durán en la convocatoria para el Mundial</t>
+          <t>Denuncian agresión a adulto mayor en medio de las protestas en Bogotá: todo quedó grabado en video</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/deportes/futbol/copa-mundial-de-la-fifa-2026/nestor-lorenzo-tomo-decision-con-duran-en-la-convocatoria-para-el-mundial-so35</t>
+          <t>https://www.noticiascaracol.com/colombia/bogota/denuncian-agresion-a-adulto-mayor-en-medio-de-las-protestas-en-bogota-todo-quedo-grabado-en-video-rg10</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:06 p. m.</t>
+          <t>21/05/2026 06:43 p. m.</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -700,24 +700,24 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>"Grupo armado y política electoral detrás": Benedetti sobre enfrentamientos entre indígenas en Cauca</t>
+          <t>Resultados Chontico Noche último sorteo hoy, jueves 21 de mayo de 2026: números ganadores</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/grupo-armado-y-politica-electoral-detras-benedetti-sobre-enfrentamientos-entre-indigenas-en-cauca-rg10</t>
+          <t>https://www.noticiascaracol.com/economia/resultados-chontico-noche-ultimo-sorteo-hoy-jueves-21-de-mayo-de-2026-numeros-ganadores-so35</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:51 p. m.</t>
+          <t>21/05/2026 06:38 p. m.</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -727,24 +727,24 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Alcaldía de Cali confirma levantamiento total de bloqueos y retoma diálogo con transportadores</t>
+          <t>Los videos en los que Valentina Mor, influencer capturada en Medellín, se burlaba de las autoridades</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/regiones/pacifico/alcaldia-de-cali-confirma-levantamiento-total-de-bloqueos-y-retoma-dialogo-con-transportadores-rg10</t>
+          <t>https://www.noticiascaracol.com/colombia/los-videos-en-los-que-valentina-mor-influencer-capturada-en-medellin-se-burlaba-de-las-autoridades-rs15</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:46 p. m.</t>
+          <t>21/05/2026 05:47 p. m.</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -754,24 +754,24 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>ExxonMobil está en negociaciones para extraer petróleo de Venezuela, según el New York Times</t>
+          <t>¿Cómo va la seguridad alimentaria en Colombia? Hay persistencia de la brecha entre lo rural y urbano</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/mundo/exxonmobil-esta-en-negociaciones-para-extraer-petroleo-de-venezuela-segun-el-new-york-times-cb20</t>
+          <t>https://www.noticiascaracol.com/colombia/como-va-la-seguridad-alimentaria-en-colombia-hay-persistencia-de-la-brecha-entre-lo-rural-y-urbano-rg10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:40 p. m.</t>
+          <t>21/05/2026 05:29 p. m.</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -781,24 +781,24 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Millonarias deudas dejan sin atención de salud mental a usuarios de Nueva EPS en Manizales</t>
+          <t>Movilidad en Bogotá EN VIVO hoy 21 de mayo: accidente de tránsito en Av. NQS y protestas en Cl 26</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/salud/millonarias-deudas-dejan-sin-atencion-de-salud-mental-a-usuarios-de-nueva-eps-en-manizales-rg10</t>
+          <t>https://www.noticiascaracol.com/colombia/bogota/movilidad-en-bogota-en-vivo-hoy-21-de-mayo-accidente-de-transito-en-av-nqs-y-protestas-en-cl-26-rg10</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:27 p. m.</t>
+          <t>21/05/2026 05:12 p. m.</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -808,24 +808,24 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Cuatro muertos y más de 44 heridos dejan enfrentamientos entre indígenas en Silvia, Cauca</t>
+          <t>Las propuestas económicas de la candidata Paloma Valencia de cara a las elecciones presidenciales</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/regiones/pacifico/cuatro-muertos-y-mas-de-44-heridos-dejan-enfrentamientos-entre-indigenas-en-silvia-cauca-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/las-propuestas-economicas-de-la-candidata-paloma-valencia-de-cara-a-las-elecciones-presidenciales-rg10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:24 p. m.</t>
+          <t>21/05/2026 05:09 p. m.</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -835,24 +835,24 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Chontico Noche, resultado del último sorteo hoy jueves 21 de mayo de 2026</t>
+          <t>Así puede saber si le revocaron un comparendo, según Mintransporte: hay casi 6 millones anulados</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/chontico-noche-resultado-del-ultimo-sorteo-hoy-jueves-21-de-mayo-de-2026-so35</t>
+          <t>https://www.noticiascaracol.com/economia/asi-puede-saber-si-le-revocaron-un-comparendo-segun-mintransporte-hay-casi-6-millones-anulados-so35</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:24 p. m.</t>
+          <t>21/05/2026 05:02 p. m.</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -862,24 +862,24 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Paisita Noche, resultado del último sorteo hoy jueves 21 de mayo de 2026</t>
+          <t>Piden oración por actor de Sin Senos Sí Hay Paraíso: "Dios pronto lo tendrá de vuelta"</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/paisita-noche-resultado-del-ultimo-sorteo-hoy-jueves-21-de-mayo-de-2026-so35</t>
+          <t>https://www.noticiascaracol.com/entretenimiento/piden-oracion-por-actor-de-sin-senos-si-hay-paraiso-dios-pronto-lo-tendra-de-vuelta-rs15</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 07:15 p. m.</t>
+          <t>21/05/2026 04:42 p. m.</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -894,19 +894,19 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Los cinco mejores municipios para vivir pensionado cerca a Bogotá, según la IA</t>
+          <t>Caso Yulixa Toloza: Venezuela revela detalles sobre los tres capturados por su presunta vinculación</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/estilo-de-vida/los-cinco-mejores-municipios-para-vivir-pensionado-cerca-a-bogota-segun-la-ia-so35</t>
+          <t>https://www.noticiascaracol.com/colombia/bogota/caso-yulixa-toloza-venezuela-revela-detalles-sobre-los-tres-capturados-por-su-presunta-vinculacion-rg10</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 07:02 p. m.</t>
+          <t>21/05/2026 04:31 p. m.</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -921,19 +921,19 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Iván Cepeda 44,6%; Abelardo De La Espriella 31,6%; Paloma Valencia 14,0%: encuesta Invamer</t>
+          <t>Esta es la fecha en la que el presidente Gustavo Petro se reunirá con el Papa León XIV</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/ivan-cepeda-44-6-abelardo-de-la-espriella-31-6-paloma-valencia-14-0-encuesta-invamer-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/el-presidente-gustavo-petro-se-reunira-con-el-papa-leon-xiv-en-el-vaticano-el-2-de-julio-rg10</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:52 p. m.</t>
+          <t>21/05/2026 04:20 p. m.</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -948,19 +948,19 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Denuncian agresión a adulto mayor en medio de las protestas en Bogotá: todo quedo grabado en video</t>
+          <t>Cine de terror en Bogotá: desde Medellín llega la 3ª Muestra Fantasmagoría a la Cinemateca</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/bogota/denuncian-agresion-a-adulto-mayor-en-medio-de-las-protestas-en-bogota-todo-quedo-grabado-en-video-rg10</t>
+          <t>https://www.noticiascaracol.com/entretenimiento/muestra-fantasmagoria-2026-cine-de-terror-en-la-cinemateca-de-bogota-programacion-completa-rg10</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:43 p. m.</t>
+          <t>21/05/2026 04:02 p. m.</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -975,19 +975,19 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Resultados Chontico Noche último sorteo hoy, jueves 21 de mayo de 2026: números ganadores</t>
+          <t>Marco Rubio dice que Raúl Castro es un fugitivo: "No voy a hablar de cómo lo traeríamos aquí"</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/resultados-chontico-noche-ultimo-sorteo-hoy-jueves-21-de-mayo-de-2026-numeros-ganadores-so35</t>
+          <t>https://www.noticiascaracol.com/mundo/marco-rubio-dice-que-raul-castro-es-un-fugitivo-de-la-justicia-estadounidense-no-voy-a-hablar-de-como-lo-traeriamos-aqui-cb20</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:38 p. m.</t>
+          <t>21/05/2026 03:55 p. m.</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1002,19 +1002,19 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Los videos en los que Valentina Mor, influencer capturada en Medellín, se burlaba de las autoridades</t>
+          <t>Resultados Super Astro Sol hoy, jueves 21 de mayo de 2026: números ganadores</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/los-videos-en-los-que-valentina-mor-influencer-capturada-en-medellin-se-burlaba-de-las-autoridades-rs15</t>
+          <t>https://www.noticiascaracol.com/economia/resultados-super-astro-sol-hoy-jueves-21-de-mayo-de-2026-numeros-ganadores-so35</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:47 p. m.</t>
+          <t>21/05/2026 03:36 p. m.</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -1029,19 +1029,19 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>¿Cómo va la seguridad alimentaria en Colombia? Hay persistencia de la brecha entre lo rural y urbano</t>
+          <t>La champeta fue declarada Patrimonio Cultural Inmaterial de Colombia</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/como-va-la-seguridad-alimentaria-en-colombia-hay-persistencia-de-la-brecha-entre-lo-rural-y-urbano-rg10</t>
+          <t>https://www.noticiascaracol.com/colombia/la-champeta-fue-declarada-patrimonio-cultural-inmaterial-de-colombia-rg10</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:29 p. m.</t>
+          <t>21/05/2026 03:32 p. m.</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1056,19 +1056,19 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Movilidad en Bogotá EN VIVO hoy 21 de mayo: accidente de tránsito en Av. NQS y protestas en Cl 26</t>
+          <t>Álbum Panini 2026: ¿cuándo sale el kit de actualización y cuánto costará?</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/bogota/movilidad-en-bogota-en-vivo-hoy-21-de-mayo-accidente-de-transito-en-av-nqs-y-protestas-en-cl-26-rg10</t>
+          <t>https://www.noticiascaracol.com/lomastrinado/album-panini-2026-cuando-sale-el-kit-de-actualizacion-y-cuanto-costara-so35</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:12 p. m.</t>
+          <t>21/05/2026 03:26 p. m.</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -1083,19 +1083,19 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Las propuestas económicas de la candidata Paloma Valencia de cara a las elecciones presidenciales</t>
+          <t>Resultados Dorado Tarde, último sorteo jueves 21 de mayo de 2026: números ganadores</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/las-propuestas-economicas-de-la-candidata-paloma-valencia-de-cara-a-las-elecciones-presidenciales-rg10</t>
+          <t>https://www.noticiascaracol.com/economia/dorado-tarde-21-de-mayo-de-2026-cuales-son-los-numeros-ganadores-so35</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:09 p. m.</t>
+          <t>21/05/2026 03:25 p. m.</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1110,19 +1110,19 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Así puede saber si le revocaron un comparendo, según Mintransporte: hay casi 6 millones anulados</t>
+          <t>Expectactiva por lista de 26 de la Selección Colombia para el Mundial 2026; atentos a este ejercicio</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/asi-puede-saber-si-le-revocaron-un-comparendo-segun-mintransporte-hay-casi-6-millones-anulados-so35</t>
+          <t>https://www.noticiascaracol.com/golcaracol/seleccion-colombia/expectactiva-por-lista-de-26-de-la-seleccion-colombia-para-el-mundial-2026-atentos-a-este-ejercicio-rg10</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:02 p. m.</t>
+          <t>21/05/2026 03:23 p. m.</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -1137,19 +1137,19 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Piden oración por actor de Sin Senos Sí Hay Paraíso: "Dios pronto lo tendrá de vuelta"</t>
+          <t>La intentó robar y la atacó con un machete en TransMilenio: grave caso de agresión en Bogotá</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/entretenimiento/piden-oracion-por-actor-de-sin-senos-si-hay-paraiso-dios-pronto-lo-tendra-de-vuelta-rs15</t>
+          <t>https://www.noticiascaracol.com/colombia/bogota/la-intento-robar-y-la-ataco-con-un-machete-en-transmilenio-grave-caso-de-agresion-en-bogota-rg10</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:42 p. m.</t>
+          <t>21/05/2026 03:16 p. m.</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1164,19 +1164,19 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Caso Yulixa Toloza: Venezuela revela detalles sobre los tres capturados por su presunta vinculación</t>
+          <t>Anuncio de última hora para el Mundial 2026; los hinchas de la Selección Colombia celebran</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/bogota/caso-yulixa-toloza-venezuela-revela-detalles-sobre-los-tres-capturados-por-su-presunta-vinculacion-rg10</t>
+          <t>https://www.noticiascaracol.com/golcaracol/seleccion-colombia/anuncio-de-ultima-hora-para-el-mundial-2026-los-hinchas-de-la-seleccion-colombia-celebran-cb20</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:31 p. m.</t>
+          <t>21/05/2026 03:12 p. m.</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1191,19 +1191,19 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Esta es la fecha en la que el presidente Gustavo Petro se reunirá con el Papa León XIV</t>
+          <t>Esta entidad ofrece crédito de vivienda con tasas desde el 10,7% en Colombia: no es el FNA</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/el-presidente-gustavo-petro-se-reunira-con-el-papa-leon-xiv-en-el-vaticano-el-2-de-julio-rg10</t>
+          <t>https://www.noticiascaracol.com/economia/esta-entidad-ofrece-credito-de-vivienda-con-tasas-desde-el-10-7-en-colombia-no-es-el-fna-so35</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:20 p. m.</t>
+          <t>21/05/2026 03:03 p. m.</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,19 +1218,19 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Cine de terror en Bogotá: desde Medellín llega la 3ª Muestra Fantasmagoría a la Cinemateca</t>
+          <t>Vea el doblete de Cristiano Ronaldo  en Al Nassr vs. Damac para ganar el título de la Liga Saudí</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/entretenimiento/muestra-fantasmagoria-2026-cine-de-terror-en-la-cinemateca-de-bogota-programacion-completa-rg10</t>
+          <t>https://www.noticiascaracol.com/golcaracol/vea-el-doblete-de-cristiano-ronaldo-contra-damac-para-ganar-el-titulo-de-la-liga-saudi-rg10</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:02 p. m.</t>
+          <t>21/05/2026 03:01 p. m.</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -1245,19 +1245,19 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Marco Rubio dice que Raúl Castro es un fugitivo: "No voy a hablar de cómo lo traeríamos aquí"</t>
+          <t>Cristiano Ronaldo es campeón de la Liga de Arabia con Al Nassr; anotó dos goles en 4-1 sobre Damac</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/mundo/marco-rubio-dice-que-raul-castro-es-un-fugitivo-de-la-justicia-estadounidense-no-voy-a-hablar-de-como-lo-traeriamos-aqui-cb20</t>
+          <t>https://www.noticiascaracol.com/golcaracol/cristiano-ronaldo-es-campeon-de-la-liga-de-arabia-con-al-nassr-anoto-dos-goles-en-4-1-sobre-damac-rg10</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 03:55 p. m.</t>
+          <t>21/05/2026 07:35 p. m.</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1267,24 +1267,24 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Resultados Super Astro Sol hoy, jueves 21 de mayo de 2026: números ganadores</t>
+          <t>Encuesta Invamer: escenarios segunda vuelta entre Cepeda, De La Espriella, Paloma Valencia y Fajardo</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/resultados-super-astro-sol-hoy-jueves-21-de-mayo-de-2026-numeros-ganadores-so35</t>
+          <t>https://www.bluradio.com/nacion/elecciones/promesas-y-propuestas/encuesta-invamer-escenarios-segunda-vuelta-entre-cepeda-de-la-espriella-paloma-valencia-y-fajardo-so35</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 03:36 p. m.</t>
+          <t>21/05/2026 07:23 p. m.</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -1294,24 +1294,24 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>La champeta fue declarada Patrimonio Cultural Inmaterial de Colombia</t>
+          <t>Yulixa se arrepintió: los testimonios y rastros clave que revelan qué pasó tras cirugía</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/la-champeta-fue-declarada-patrimonio-cultural-inmaterial-de-colombia-rg10</t>
+          <t>https://www.bluradio.com/judicial/yulixa-se-arrepintio-los-testimonios-y-rastros-clave-que-revelan-que-paso-tras-cirugia-rg10</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 03:32 p. m.</t>
+          <t>21/05/2026 07:17 p. m.</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1321,24 +1321,24 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Álbum Panini 2026: ¿cuándo sale el kit de actualización y cuánto costará?</t>
+          <t>Más de 9.200 testigos electorales en el exterior fueron acreditados por el CNE para las elecciones</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/lomastrinado/album-panini-2026-cuando-sale-el-kit-de-actualizacion-y-cuanto-costara-so35</t>
+          <t>https://www.bluradio.com/nacion/elecciones/mas-de-9-200-testigos-electorales-en-el-exterior-fueron-acreditados-por-el-cne-para-las-elecciones-rg10</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 03:26 p. m.</t>
+          <t>21/05/2026 07:04 p. m.</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -1348,24 +1348,24 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Resultados Dorado Tarde, último sorteo jueves 21 de mayo de 2026: números ganadores</t>
+          <t>Encuesta Invamer: Cepeda obtiene 44,6 %; De La Espriella, 31,6 % y Paloma Valencia, 14 %</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/dorado-tarde-21-de-mayo-de-2026-cuales-son-los-numeros-ganadores-so35</t>
+          <t>https://www.bluradio.com/nacion/elecciones/encuesta-invamer-cepeda-obtiene-44-6-de-la-espriella-31-6-y-paloma-valencia-14-so35</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 03:25 p. m.</t>
+          <t>21/05/2026 06:51 p. m.</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1375,24 +1375,24 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Expectactiva por lista de 26 de la Selección Colombia para el Mundial 2026; atentos a este ejercicio</t>
+          <t>Cristiano Ronaldo conquista la liga de Arabia a sus 40 años antes del Mundial</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/golcaracol/seleccion-colombia/expectactiva-por-lista-de-26-de-la-seleccion-colombia-para-el-mundial-2026-atentos-a-este-ejercicio-rg10</t>
+          <t>https://www.bluradio.com/deportes/futbol/cristiano-ronaldo-conquista-la-liga-de-arabia-a-sus-40-anos-antes-del-mundial-cb20</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 03:23 p. m.</t>
+          <t>21/05/2026 06:47 p. m.</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -1402,24 +1402,24 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>La intentó robar y la atacó con un machete en TransMilenio: grave caso de agresión en Bogotá</t>
+          <t>“Es deplorable que eso haya sucedido”, Benedetti tras ataque a sede de Paloma Valencia</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/bogota/la-intento-robar-y-la-ataco-con-un-machete-en-transmilenio-grave-caso-de-agresion-en-bogota-rg10</t>
+          <t>https://www.bluradio.com/nacion/es-deplorable-que-eso-haya-sucedido-benedetti-tras-ataque-a-sede-de-paloma-valencia-rg10</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 03:16 p. m.</t>
+          <t>21/05/2026 06:31 p. m.</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1429,24 +1429,24 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Anuncio de última hora para el Mundial 2026; los hinchas de la Selección Colombia celebran</t>
+          <t>Néstor Lorenzo tomó decisión con Durán en la convocatoria para el Mundial</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/golcaracol/seleccion-colombia/anuncio-de-ultima-hora-para-el-mundial-2026-los-hinchas-de-la-seleccion-colombia-celebran-cb20</t>
+          <t>https://www.bluradio.com/deportes/futbol/copa-mundial-de-la-fifa-2026/nestor-lorenzo-tomo-decision-con-duran-en-la-convocatoria-para-el-mundial-so35</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 03:12 p. m.</t>
+          <t>21/05/2026 06:06 p. m.</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -1456,24 +1456,24 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Esta entidad ofrece crédito de vivienda con tasas desde el 10,7% en Colombia: no es el FNA</t>
+          <t>"Grupo armado y política electoral detrás": Benedetti sobre enfrentamientos entre indígenas en Cauca</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/esta-entidad-ofrece-credito-de-vivienda-con-tasas-desde-el-10-7-en-colombia-no-es-el-fna-so35</t>
+          <t>https://www.bluradio.com/nacion/grupo-armado-y-politica-electoral-detras-benedetti-sobre-enfrentamientos-entre-indigenas-en-cauca-rg10</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 03:03 p. m.</t>
+          <t>21/05/2026 05:51 p. m.</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1483,24 +1483,24 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Vea el doblete de Cristiano Ronaldo  en Al Nassr vs. Damac para ganar el título de la Liga Saudí</t>
+          <t>Alcaldía de Cali confirma levantamiento total de bloqueos y retoma diálogo con transportadores</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/golcaracol/vea-el-doblete-de-cristiano-ronaldo-contra-damac-para-ganar-el-titulo-de-la-liga-saudi-rg10</t>
+          <t>https://www.bluradio.com/regiones/pacifico/alcaldia-de-cali-confirma-levantamiento-total-de-bloqueos-y-retoma-dialogo-con-transportadores-rg10</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 03:01 p. m.</t>
+          <t>21/05/2026 05:46 p. m.</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -1510,24 +1510,24 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Cristiano Ronaldo es campeón de la Liga de Arabia con Al Nassr; anotó dos goles en 4-1 sobre Damac</t>
+          <t>ExxonMobil está en negociaciones para extraer petróleo de Venezuela, según el New York Times</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/golcaracol/cristiano-ronaldo-es-campeon-de-la-liga-de-arabia-con-al-nassr-anoto-dos-goles-en-4-1-sobre-damac-rg10</t>
+          <t>https://www.bluradio.com/mundo/exxonmobil-esta-en-negociaciones-para-extraer-petroleo-de-venezuela-segun-el-new-york-times-cb20</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 02:50 p. m.</t>
+          <t>21/05/2026 05:40 p. m.</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1537,24 +1537,24 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Videos | Encapuchados vandalizaron sede de campaña de Paloma Valencia en Bogotá; hay bloqueos</t>
+          <t>Millonarias deudas dejan sin atención de salud mental a usuarios de Nueva EPS en Manizales</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/bogota/videos-encapuchados-vandalizaron-sede-de-campana-de-paloma-valencia-en-bogota-hay-bloqueos-rg10</t>
+          <t>https://www.bluradio.com/salud/millonarias-deudas-dejan-sin-atencion-de-salud-mental-a-usuarios-de-nueva-eps-en-manizales-rg10</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 02:18 p. m.</t>
+          <t>21/05/2026 05:27 p. m.</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -1564,24 +1564,24 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Las pruebas que condenaron a estadounidense a 30 años por delitos sexuales contra menor colombiana</t>
+          <t>Cuatro muertos y más de 44 heridos dejan enfrentamientos entre indígenas en Silvia, Cauca</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/mundo/las-pruebas-que-condenaron-a-estadounidense-a-30-anos-por-delitos-sexuales-contra-menor-colombiana-rg10</t>
+          <t>https://www.bluradio.com/regiones/pacifico/cuatro-muertos-y-mas-de-44-heridos-dejan-enfrentamientos-entre-indigenas-en-silvia-cauca-rg10</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 07:10 p. m.</t>
+          <t>21/05/2026 07:34 p. m.</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1591,24 +1591,24 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Duerma informado con las movidas de este 21 de mayo de 2026</t>
+          <t>Más de 16 años de cárcel a Sandra Mosquera por quitarle la vida a su marido</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/duerma-informado-con-las-movidas-de-este-21-de-mayo-de-2026/</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/mas-de-16-anos-de-carcel-a-sandra-mosquera-por-quitarle-la-vida-a-su-marido/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:53 p. m.</t>
+          <t>21/05/2026 07:31 p. m.</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -1618,24 +1618,24 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>CNE negó solicitud para tumbar la candidatura de De la Espriella</t>
+          <t>Siete años después, Tayron Guerrero recibe otra oportunidad en la MLB</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/cne-nego-solicitud-para-tumbar-la-candidatura-de-de-la-espriella/</t>
+          <t>https://www.eluniversal.com.co/deportes/2026/05/21/siete-anos-despues-tayron-guerrero-recibe-otra-oportunidad-en-la-mlb/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:14 p. m.</t>
+          <t>21/05/2026 07:05 p. m.</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1645,24 +1645,24 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Petro se reunirá con el Papa León XIV en El Vaticano</t>
+          <t>EE. UU. captura a mujer vinculada al régimen cubano: es hermana de ejecutivo militar</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/petro-se-reunira-con-el-papa-leon-xiv-en-el-vaticano/</t>
+          <t>https://www.eluniversal.com.co/mundo/2026/05/21/ee-uu-captura-a-mujer-vinculada-al-regimen-cubano-es-hermana-de-ejecutivo-militar/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:48 p. m.</t>
+          <t>21/05/2026 07:02 p. m.</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -1672,24 +1672,24 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Vandalizada sede de Paloma en Bogotá. Uribismo señala a Cepeda</t>
+          <t>Redes estallan por comentario de Yina Calderón sobre Alejandro Estrada</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/vandalizada-sede-de-paloma-en-bogota-uribismo-senala-a-cepeda/</t>
+          <t>https://www.eluniversal.com.co/farandula/2026/05/21/redes-estallan-por-comentario-de-yina-calderon-sobre-alejandro-estrada/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:44 p. m.</t>
+          <t>21/05/2026 06:50 p. m.</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1699,24 +1699,24 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Guarumo: Cepeda se mantiene en el 37%, Abelardo con 27% y Paloma 21%</t>
+          <t>Así jugará Real Cartagena, ya finalista, ante el Barranquilla FC</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/guarumo-cepeda-se-mantiene-en-el-37-abelardo-con-27-y-paloma-21/</t>
+          <t>https://www.eluniversal.com.co/deportes/2026/05/21/asi-jugara-real-cartagena-ya-finalista-ante-el-barranquilla-fc/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:40 p. m.</t>
+          <t>21/05/2026 06:30 p. m.</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
@@ -1726,24 +1726,24 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>MinDefensa instala PMU por enfrentamientos entre comunidades indígenas</t>
+          <t>Real Cartagena: el día en que la hinchada volvió a celebrar llegar a una final</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/mindefensa-instala-pmu-por-enfrentamientos-entre-comunidades-indigenas/</t>
+          <t>https://www.eluniversal.com.co/deportes/2026/05/21/real-cartagena-el-dia-en-que-la-hinchada-volvio-a-celebrar-llegar-a-una-final/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 03:22 p. m.</t>
+          <t>21/05/2026 06:03 p. m.</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1753,24 +1753,24 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Corte Constitucional aplazó discusión sobre el futuro de la ley de encuestas</t>
+          <t>Cayó ‘el Chivato’ en Bolívar: lo sorprendieron armado y con amplio prontuario</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/corte-constitucional-aplazo-discusion-sobre-el-futuro-de-la-ley-de-encuestas/</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/cayo-el-chivato-en-bolivar-lo-sorprendieron-armado-y-con-amplio-prontuario-judicial/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 02:08 p. m.</t>
+          <t>21/05/2026 05:54 p. m.</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -1780,24 +1780,24 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Aunque de vacaciones, Ricardo Roa aparece de gira por Ecopetrol</t>
+          <t>Real Cartagena ya es finalista del Torneo BetPlay, empató el Unión Magdalena</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/aunque-de-vacaciones-ricardo-roa-aparece-de-gira-por-ecopetrol/</t>
+          <t>https://www.eluniversal.com.co/deportes/2026/05/21/real-cartagena-ya-es-finalista-del-torneo-betplay-empato-el-union-magdalena/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 01:15 p. m.</t>
+          <t>21/05/2026 05:54 p. m.</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1807,24 +1807,24 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Diario de Campaña: agarrón en el CNE y campaña de Abelardo contrató a Atlas</t>
+          <t>Deportes</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/diario-de-campana-agarron-en-el-cne-y-campana-de-abelardo-contrato-a-atlas/</t>
+          <t>https://www.eluniversal.com.co/deportes/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 12:57 p. m.</t>
+          <t>21/05/2026 05:08 p. m.</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -1834,24 +1834,24 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Cepeda hablará con Consejo Gremial sobre aportes a programas sociales</t>
+          <t>¿Karol G en Cartagena? Esto dijo Dumek Turbay sobre una posible presentación</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/cepeda-hablara-con-consejo-gremial-sobre-aportes-a-programas-sociales/</t>
+          <t>https://www.eluniversal.com.co/farandula/2026/05/21/karol-g-en-cartagena-esto-dijo-dumek-turbay-sobre-una-posible-presentacion/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 07:05 p. m.</t>
+          <t>21/05/2026 05:08 p. m.</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Paloma Valencia y Abelardo de la Espriella vencerían a Iván Cepeda en segunda vuelta, según la encuesta de Guarumo</t>
+          <t>Farándula</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-22/paloma-valencia-y-abelardo-de-la-espriella-vencerian-a-ivan-cepeda-en-segunda-vuelta-segun-la-encuesta-de-guarumo.html</t>
+          <t>https://www.eluniversal.com.co/farandula/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 07:00 p. m.</t>
+          <t>21/05/2026 04:55 p. m.</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -1888,24 +1888,24 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Hora 20 y EL PAÍS en elecciones: ¿Cuál es el país con el que sueñan los jóvenes?</t>
+          <t>2 hombres enviados a la cárcel por agresiones contra sus familiares en Bolívar</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/hora-20/2026-05-22/hora-20-y-el-pais-en-elecciones-cual-es-el-pais-con-el-que-suenan-los-jovenes.html</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/2-hombres-enviados-a-la-carcel-por-agresiones-contra-sus-familiares-en-bolivar/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:51 p. m.</t>
+          <t>21/05/2026 04:43 p. m.</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -1915,24 +1915,24 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Sheinbaum intenta relanzar la relación con Estados Unidos recibiendo al jefe de Seguridad Interior de Trump</t>
+          <t>Cayó banda de expendedores que operaba cerca de colegios y canchas en Mompox</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/mexico/2026-05-21/sheinbaum-intenta-relanzar-la-relacion-con-estados-unidos-recibiendo-al-jefe-de-seguridad-interior-de-trump.html</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/cayo-banda-de-expendedores-que-operaba-cerca-de-colegios-y-canchas-en-mompox/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:46 p. m.</t>
+          <t>21/05/2026 04:39 p. m.</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -1942,24 +1942,24 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>El ICE detiene en Florida a la hermana de la jefa del conglomerado militar cubano Gaesa</t>
+          <t>Encuesta Guarumo y Ecoanalítica: así están Cepeda, Abelardo y Paloma a 10 días de la primera vuelta</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/us/2026-05-21/el-ice-detiene-en-florida-a-la-hermana-de-la-jefa-del-conglomerado-militar-cubano-gaesa.html</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/21/encuesta-guarumo-y-ecoanalitica-asi-estan-cepeda-de-la-espriella-y-paloma-valencia-a-10-dias-de-la-primera-vuelta/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:44 p. m.</t>
+          <t>21/05/2026 04:39 p. m.</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -1969,24 +1969,24 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Videoanálisis | La derecha tradicional también flaquea en Colombia</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-21/videoanalisis-la-derecha-tradicional-tambien-flaquea-en-colombia.html</t>
+          <t>https://www.eluniversal.com.co/colombia/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:37 p. m.</t>
+          <t>21/05/2026 04:38 p. m.</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -1996,24 +1996,24 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Sheinbaum aprovecha la reforma judicial para colar un paquete electoral por la vía rápida</t>
+          <t>Accidente de tránsito frente al Mercado de Bazurto genera monumental trancón</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/mexico/2026-05-21/sheinbaum-aprovecha-la-reforma-judicial-para-colar-un-paquete-electoral-por-la-via-rapida.html</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/accidente-de-transito-frente-al-mercado-de-bazurto-genera-monumental-trancon/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:30 p. m.</t>
+          <t>21/05/2026 04:23 p. m.</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2023,24 +2023,24 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Radiografía de la salud mental en el mundo: 1.200 millones de personas viven con trastornos psiquiátricos</t>
+          <t>Dadis suspendió centro de estética en Cartagena tras inspección</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/salud-y-bienestar/2026-05-22/radiografia-de-la-salud-mental-en-el-mundo-1200-millones-de-personas-viven-con-trastornos-psiquiatricos.html</t>
+          <t>https://www.eluniversal.com.co/cartagena/2026/05/21/dadis-suspendio-centro-de-estetica-en-cartagena-por-realizar-procedimientos-invasivos-sin-habilitacion/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:13 p. m.</t>
+          <t>21/05/2026 04:23 p. m.</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
@@ -2050,24 +2050,24 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>La CNTE prepara un paro nacional indefinido el 1 de junio, ¿qué exigen los maestros?</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/mexico/2026-05-21/la-cnte-prepara-un-paro-nacional-indefinido-el-1-de-junio-que-exigen-los-maestros.html</t>
+          <t>https://www.eluniversal.com.co/cartagena/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:01 p. m.</t>
+          <t>21/05/2026 04:20 p. m.</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2077,24 +2077,24 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Emanciparse, una misión cada vez más imposible para los jóvenes: necesitan el 99% de su sueldo para irse a vivir solos</t>
+          <t>Miguel Díaz-Canel desafía a Donald Trump con contundente mensaje sobre Cuba</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/sociedad/2026-05-21/emanciparse-una-mision-cada-vez-mas-imposible-para-los-jovenes-necesitan-el-99-de-su-sueldo-para-irse-a-vivir-solos.html</t>
+          <t>https://www.eluniversal.com.co/mundo/2026/05/21/miguel-diaz-canel-desafia-a-donald-trump-con-contundente-mensaje-sobre-cuba/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:50 p. m.</t>
+          <t>21/05/2026 04:07 p. m.</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -2104,24 +2104,24 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>El Gobierno de Milei amenaza con devorarse a sí mismo</t>
+          <t>Caso Yulixa Toloza: Fiscalía rastreó a implicados mediante plataforma</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/argentina/2026-05-22/el-gobierno-de-milei-amenaza-con-devorarse-a-si-mismo.html</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/21/caso-yulixa-toloza-fiscalia-rastreo-a-implicados-mediante-plataforma/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:28 p. m.</t>
+          <t>21/05/2026 04:04 p. m.</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2131,24 +2131,24 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Trump da marcha atrás y anuncia el envío de 5.000 soldados adicionales de Estados Unidos a Polonia</t>
+          <t>Por error, hombre arrolló con camión y le quitó la vida a su esposa Paulina Castro</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/internacional/2026-05-21/trump-da-marcha-atras-y-anuncia-el-envio-de-5000-soldados-adicionales-de-estados-unidos-a-polonia.html</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/por-error-hombre-arrollo-con-camion-y-le-quito-la-vida-a-su-esposa-paulina-castro/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:26 p. m.</t>
+          <t>21/05/2026 03:56 p. m.</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -2158,24 +2158,24 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>António Costa: “La Unión Europea necesita a México, el mundo necesita a México”</t>
+          <t>Vandalizan sede de campaña de Paloma Valencia durante manifestaciones en Bogotá</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/mexico/economia/2026-05-21/antonio-costa-la-union-europea-necesita-a-mexico-el-mundo-necesita-a-mexico.html</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/21/vandalizan-sede-de-campana-de-paloma-valencia-durante-manifestaciones-en-bogota/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:17 p. m.</t>
+          <t>21/05/2026 03:43 p. m.</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2185,24 +2185,24 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Óscar Puente llama a la “colaboración inteligente” entre la izquierda en las elecciones</t>
+          <t>Ejemplar condena contra un mototaxista que agredió y abusó de su pasajera en Turbaco</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/espana/2026-05-21/oscar-puente-llama-a-la-colaboracion-inteligente-entre-la-izquierda-en-las-elecciones.html</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/ejemplar-condena-contra-un-mototaxista-que-agredio-y-abuso-de-su-pasajera-en-turbaco/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 03:50 p. m.</t>
+          <t>21/05/2026 03:39 p. m.</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -2212,26 +2212,22 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Telefónica vende su sede histórica de Gran Vía al empresario Tomás Olivo por más de 200 millones</t>
+          <t>Así hallaron a pescador tras 24 horas desaparecido en el mar de Cartagena</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/economia/2026-05-21/telefonica-vende-su-sede-historica-de-gran-via-a-un-empresario-murciano-por-mas-de-200-millones.html</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/asi-hallaron-a-pescador-tras-24-horas-desaparecido-en-el-mar-de-cartagena/</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>21/05/2026 03:42 p. m.</t>
-        </is>
-      </c>
+      <c r="A64" s="3" t="inlineStr"/>
       <c r="B64" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -2239,24 +2235,24 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Luis Almagro, exsecretario de la OEA, anuncia su respaldo a Paloma Valencia y critica a Abelardo de la Espriella: “Se presenta como un fiestero en Miami”</t>
+          <t>Premios Excelencia El Universal 2026: categorías, calendario y cómo participar</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/2026-05-21/luis-almagro-exsecretario-de-la-oea-anuncia-su-respaldo-a-paloma-valencia-y-critica-a-abelardo-de-la-espriella-se-presenta-como-un-fiestero-en-miami.html</t>
+          <t>https://www.eluniversal.com.co/cartagena/2026/05/20/premios-excelencia-el-universal-2026-categorias-calendario-y-como-participar/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 03:24 p. m.</t>
+          <t>21/05/2026 07:31 p. m.</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
@@ -2266,24 +2262,24 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Puig anuncia la ruptura de las negociaciones para fusionarse con Estée Lauder</t>
+          <t>Nueva Encuesta presidencial: Iván Cepeda lidera, pero perdería en segunda vuelta</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/economia/2026-05-21/puig-rompe-las-negociaciones-para-fusionarse-con-estee-lauder.html</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/21/nueva-encuesta-presidencial-ivan-cepeda-lidera-pero-perderia-en-segunda-vuelta/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 03:09 p. m.</t>
+          <t>21/05/2026 07:31 p. m.</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2293,24 +2289,24 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Las figuras no justifican el sueldo en una corrida petardo</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/cultura/2026-05-21/las-figuras-no-justifican-el-sueldo-en-una-corrida-petardo.html</t>
+          <t>https://www.vanguardia.com/colombia/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 02:43 p. m.</t>
+          <t>21/05/2026 07:14 p. m.</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -2320,24 +2316,24 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Detenida en Brasil una abogada con 21 millones de seguidores en redes por lavar dinero para el crimen organizado</t>
+          <t>Así operaba la red señalada de estafar a 280 personas con paquetes turísticos falsos en Bucaramanga</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/america/2026-05-21/detenida-en-brasil-una-abogada-con-21-millones-de-seguidores-en-redes-por-lavar-dinero-para-el-crimen-organizado.html</t>
+          <t>https://www.vanguardia.com/judicial/2026/05/21/asi-operaba-la-red-senalada-de-estafar-a-280-personas-con-paquetes-turisticos-falsos-en-bucaramanga/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 02:31 p. m.</t>
+          <t>21/05/2026 07:14 p. m.</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2347,24 +2343,24 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>La Policía detiene a tres personas como cooperadoras del crimen del cantaor Matías de Paula</t>
+          <t>Judicial</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/espana/2026-05-21/la-policia-detiene-a-tres-personas-como-cooperadoras-del-crimen-del-cantaor-matias-de-paula.html</t>
+          <t>https://www.vanguardia.com/judicial/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 02:08 p. m.</t>
+          <t>21/05/2026 06:50 p. m.</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -2374,24 +2370,24 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Stellantis prevé elevar su facturación casi un 25% en cinco años hasta los 200.000 millones para revitalizar el negocio</t>
+          <t>Último resultado de Chontico Noche del jueves 21 de mayo de 2026</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/economia/2026-05-21/stellantis-preve-elevar-su-facturacion-casi-un-25-hasta-los-200000-millones-en-cinco-anos-para-revitalizar-el-negocio.html</t>
+          <t>https://www.vanguardia.com/loterias/2026/05/21/ultimo-resultado-de-chontico-noche-del-jueves-21-de-mayo-de-2026/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 02:08 p. m.</t>
+          <t>21/05/2026 06:50 p. m.</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2401,24 +2397,24 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Renuncia el ministro de Trabajo de Bolivia, el primer cambio en el Gobierno de Paz por las protestas</t>
+          <t>Loterias</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/america/2026-05-21/renuncia-el-ministro-de-trabajo-de-bolivia-el-primer-cambio-en-el-gobierno-de-paz-por-las-protestas.html</t>
+          <t>https://www.vanguardia.com/loterias/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 12:48 p. m.</t>
+          <t>21/05/2026 06:20 p. m.</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -2428,24 +2424,24 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Un juez de Madrid archiva la denuncia de Begoña Gómez contra Vito Quiles por acoso</t>
+          <t>Mujer reportada como desaparecida fue hallada muerta en el río Magdalena</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/espana/2026-05-21/un-juez-de-madrid-archiva-la-denuncia-de-begona-gomez-contra-vito-quiles-por-acoso.html</t>
+          <t>https://www.vanguardia.com/judicial/2026/05/21/mujer-reportada-como-desaparecida-fue-hallada-muerta-en-el-rio-magdalena/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 12:45 p. m.</t>
+          <t>21/05/2026 06:14 p. m.</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2455,24 +2451,24 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>El Supremo obliga a Antena 3 a dejar de emitir ‘El Rosco’ de ‘Pasapalabra’</t>
+          <t>Horóscopo del viernes 22 de mayo de 2026: Predicciones y el vuelo de las ideas</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/television/2026-05-21/el-supremo-obliga-a-atresmedia-a-dejar-de-emitir-el-rosco-de-pasapalabra.html</t>
+          <t>https://www.vanguardia.com/entretenimiento/tendencias/2026/05/21/horoscopo-del-viernes-22-de-mayo-de-2026-predicciones-y-el-vuelo-de-las-ideas/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 11:44 a. m.</t>
+          <t>21/05/2026 06:14 p. m.</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
@@ -2482,24 +2478,24 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Los Javis en Cannes: “Federico García Lorca no es una idea, sino una persona a la que asesinaron por maricón”</t>
+          <t>Tendencias</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/cultura/cine/2026-05-21/los-javis-en-cannes-federico-garcia-lorca-no-es-una-idea-sino-una-persona-a-la-que-asesinaron-por-maricon.html</t>
+          <t>https://www.vanguardia.com/entretenimiento/tendencias/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 10:26 a. m.</t>
+          <t>21/05/2026 05:20 p. m.</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2509,24 +2505,24 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>La Audiencia Nacional ordena el bloqueo de 490.780 euros de las cuentas bancarias de Zapatero</t>
+          <t>En fotos: así quedó la sede de Paloma Valencia tras ataque vandálico en Bogotá</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/espana/2026-05-21/la-audiencia-nacional-ordena-el-bloqueo-de-cuentas-bancarias-de-zapatero.html</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/21/en-fotos-asi-quedo-la-sede-de-paloma-valencia-tras-ataque-vandalico-en-bogota/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 10:00 a. m.</t>
+          <t>21/05/2026 04:50 p. m.</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
@@ -2536,24 +2532,24 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Las pirámides egipcias fueron construidas a prueba de terremotos</t>
+          <t>Enfermería en Colombia: ¿Por qué hay déficit crítico de profesionales y cómo enfrentarlo?</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/ciencia/2026-05-21/las-piramides-egipcias-fueron-construidas-a-prueba-de-terremotos.html</t>
+          <t>https://www.vanguardia.com/entretenimiento/salud/2026/05/21/enfermeria-en-colombia-por-que-hay-deficit-critico-de-profesionales-y-como-enfrentarlo/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 09:49 a. m.</t>
+          <t>21/05/2026 04:15 p. m.</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2563,24 +2559,24 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Estados Unidos despliega su portaviones ‘USS Nimitz’ en el Caribe en plena campaña contra Cuba</t>
+          <t>Brutal enfrentamiento entre indígenas terminó en tragedia: tres muertos y varios heridos</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/internacional/2026-05-21/estados-unidos-despliega-su-portaviones-uss-nimitz-en-el-caribe-en-plena-campana-contra-cuba.html</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/21/brutal-enfrentamiento-entre-indigenas-termino-en-tragedia-tres-muertos-y-varios-heridos/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 07:12 a. m.</t>
+          <t>21/05/2026 03:20 p. m.</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -2590,24 +2586,24 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>El Supremo anula el registro único de alquileres turísticos al considerar que el Estado carece de competencias para crearlo</t>
+          <t>Caso Yulixa Toloza: revelan qué provocó realmente su muerte tras cirugía en Beauty Láser</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/economia/2026-05-21/el-supremo-anula-el-registro-unico-de-alquileres-turisticos-al-considerar-que-el-estado-carece-de-competencias-para-crearlo.html</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/21/caso-yulixa-toloza-revelan-que-provoco-realmente-su-muerte-tras-cirugia-en-beauty-lase/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>20/05/2026 10:30 p. m.</t>
+          <t>21/05/2026 02:25 p. m.</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2617,24 +2613,24 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Siete carreras con un buen sueldo y una nota de acceso asequible</t>
+          <t>Corte Constitucional: no pagar alimentos puede ser violencia económica en Colombia</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/educacion/2026-05-21/siete-carreras-con-un-buen-sueldo-y-una-nota-de-acceso-asequible.html</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/21/corte-constitucional-no-pagar-alimentos-puede-ser-violencia-economica-en-colombia/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>20/05/2026 10:30 p. m.</t>
+          <t>21/05/2026 02:22 p. m.</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
@@ -2644,24 +2640,24 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>El sendero en el que murió Isak Andic: un camino “sin riesgo” con un solo punto donde caer al vacío</t>
+          <t>Anulación de fotomultas en Colombia: pasos para recuperar su dinero si ya pagó</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/espana/catalunya/2026-05-21/el-sendero-en-el-que-murio-isak-andic-un-camino-sin-riesgo-con-un-solo-punto-donde-caer-al-vacio.html</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/20/fotomultas-anuladas-paso-a-paso-para-saber-si-le-devuelven-su-dinero/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 07:05 p. m.</t>
+          <t>21/05/2026 12:57 p. m.</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2671,24 +2667,24 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>EE. UU. captura a mujer vinculada al régimen cubano: es hermana de ejecutivo militar</t>
+          <t>Antioquia cierra 64 centros estéticos por irregularidades tras controles sanitarios</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/mundo/2026/05/21/ee-uu-captura-a-mujer-vinculada-al-regimen-cubano-es-hermana-de-ejecutivo-militar/</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/21/antioquia-cierra-64-centros-esteticos-por-irregularidades-tras-controles-sanitarios/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 07:02 p. m.</t>
+          <t>21/05/2026 12:34 p. m.</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
@@ -2698,24 +2694,24 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Redes estallan por comentario de Yina Calderón sobre Alejandro Estrada</t>
+          <t>La champeta será Patrimonio Cultural Inmaterial de Colombia: reconocimiento a este ritmo del Caribe</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/farandula/2026/05/21/redes-estallan-por-comentario-de-yina-calderon-sobre-alejandro-estrada/</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/21/la-champeta-sera-patrimonio-cultural-inmaterial-de-colombia-reconocimiento-a-este-ritmo-del-caribe/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:50 p. m.</t>
+          <t>21/05/2026 11:57 a. m.</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -2725,24 +2721,24 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Así jugará Real Cartagena, ya finalista, ante el Barranquilla FC</t>
+          <t>Caso Yulixa Toloza: capturados en Venezuela no serían extraditados a Colombia</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/deportes/2026/05/21/asi-jugara-real-cartagena-ya-finalista-ante-el-barranquilla-fc/</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/21/caso-yulixa-toloza-capturados-en-venezuela-no-serian-extraditados-a-colombia/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:30 p. m.</t>
+          <t>21/05/2026 07:30 p. m.</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
@@ -2752,24 +2748,24 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Real Cartagena: el día en que la hinchada volvió a celebrar llegar a una final</t>
+          <t>Invamer: Cepeda al frente con 44 % y Abelardo dobla a Paloma</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/deportes/2026/05/21/real-cartagena-el-dia-en-que-la-hinchada-volvio-a-celebrar-llegar-a-una-final/</t>
+          <t>https://www.lasillavacia.com/en-vivo/invamer-cepeda-al-frente-con-44-y-abelardo-dobla-a-paloma/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:03 p. m.</t>
+          <t>21/05/2026 07:10 p. m.</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -2779,24 +2775,24 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Cayó ‘el Chivato’ en Bolívar: lo sorprendieron armado y con amplio prontuario</t>
+          <t>Duerma informado con las movidas de este 21 de mayo de 2026</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/cayo-el-chivato-en-bolivar-lo-sorprendieron-armado-y-con-amplio-prontuario-judicial/</t>
+          <t>https://www.lasillavacia.com/en-vivo/duerma-informado-con-las-movidas-de-este-21-de-mayo-de-2026/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:00 p. m.</t>
+          <t>21/05/2026 06:53 p. m.</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
@@ -2806,24 +2802,24 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Real Cartagena y Envigado, cara a cara por un cupo a la Primera A</t>
+          <t>CNE negó solicitud para tumbar la candidatura de De la Espriella</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/deportes/2026/05/21/real-cartagena-y-envigado-cara-a-cara-por-un-cupo-a-la-primera-a/</t>
+          <t>https://www.lasillavacia.com/en-vivo/cne-nego-solicitud-para-tumbar-la-candidatura-de-de-la-espriella/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:54 p. m.</t>
+          <t>21/05/2026 06:14 p. m.</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -2833,24 +2829,24 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Real Cartagena ya es finalista del Torneo BetPlay, empató el Unión Magdalena</t>
+          <t>Petro se reunirá con el Papa León XIV en El Vaticano</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/deportes/2026/05/21/real-cartagena-ya-es-finalista-del-torneo-betplay-empato-el-union-magdalena/</t>
+          <t>https://www.lasillavacia.com/en-vivo/petro-se-reunira-con-el-papa-leon-xiv-en-el-vaticano/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:54 p. m.</t>
+          <t>21/05/2026 05:48 p. m.</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
@@ -2860,24 +2856,24 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Deportes</t>
+          <t>Vandalizada sede de Paloma en Bogotá. Uribismo señala a Cepeda</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/deportes/</t>
+          <t>https://www.lasillavacia.com/en-vivo/vandalizada-sede-de-paloma-en-bogota-uribismo-senala-a-cepeda/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:08 p. m.</t>
+          <t>21/05/2026 04:44 p. m.</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -2887,24 +2883,24 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>¿Karol G en Cartagena? Esto dijo Dumek Turbay sobre una posible presentación</t>
+          <t>Guarumo: Cepeda se mantiene en el 37%, Abelardo con 27% y Paloma 21%</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/farandula/2026/05/21/karol-g-en-cartagena-esto-dijo-dumek-turbay-sobre-una-posible-presentacion/</t>
+          <t>https://www.lasillavacia.com/en-vivo/guarumo-cepeda-se-mantiene-en-el-37-abelardo-con-27-y-paloma-21/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:08 p. m.</t>
+          <t>21/05/2026 04:40 p. m.</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
@@ -2914,24 +2910,24 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Farándula</t>
+          <t>MinDefensa instala PMU por enfrentamientos entre comunidades indígenas</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/farandula/</t>
+          <t>https://www.lasillavacia.com/en-vivo/mindefensa-instala-pmu-por-enfrentamientos-entre-comunidades-indigenas/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:55 p. m.</t>
+          <t>21/05/2026 03:22 p. m.</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -2941,24 +2937,24 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>2 hombres enviados a la cárcel por agresiones contra sus familiares en Bolívar</t>
+          <t>Corte Constitucional aplazó discusión sobre el futuro de la ley de encuestas</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/2-hombres-enviados-a-la-carcel-por-agresiones-contra-sus-familiares-en-bolivar/</t>
+          <t>https://www.lasillavacia.com/en-vivo/corte-constitucional-aplazo-discusion-sobre-el-futuro-de-la-ley-de-encuestas/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:43 p. m.</t>
+          <t>21/05/2026 02:08 p. m.</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
@@ -2968,24 +2964,24 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Cayó banda de expendedores que operaba cerca de colegios y canchas en Mompox</t>
+          <t>Aunque de vacaciones, Ricardo Roa aparece de gira por Ecopetrol</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/cayo-banda-de-expendedores-que-operaba-cerca-de-colegios-y-canchas-en-mompox/</t>
+          <t>https://www.lasillavacia.com/en-vivo/aunque-de-vacaciones-ricardo-roa-aparece-de-gira-por-ecopetrol/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:39 p. m.</t>
+          <t>21/05/2026 01:15 p. m.</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -2995,24 +2991,24 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Encuesta Guarumo y Ecoanalítica: así están Cepeda, Abelardo y Paloma a 10 días de la primera vuelta</t>
+          <t>Diario de Campaña: agarrón en el CNE y campaña de Abelardo contrató a Atlas</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/2026/05/21/encuesta-guarumo-y-ecoanalitica-asi-estan-cepeda-de-la-espriella-y-paloma-valencia-a-10-dias-de-la-primera-vuelta/</t>
+          <t>https://www.lasillavacia.com/en-vivo/diario-de-campana-agarron-en-el-cne-y-campana-de-abelardo-contrato-a-atlas/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:39 p. m.</t>
+          <t>21/05/2026 07:27 p. m.</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
@@ -3022,24 +3018,24 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Madre era cruelmente extorsionada por su propio hijo en Pereira: así lo descubrió + VIDEO</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/</t>
+          <t>https://www.noticiasrcn.com/colombia/madre-era-cruelmente-extorsionada-por-su-propio-hijo-en-pereira-asi-lo-descubrio-video-1023512</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:38 p. m.</t>
+          <t>21/05/2026 06:32 p. m.</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3049,24 +3045,24 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Accidente de tránsito frente al Mercado de Bazurto genera monumental trancón</t>
+          <t>Yulixa Toloza iba muerta en el carro cuando la dueña de la estética usó su celular para engañar a la amiga</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/accidente-de-transito-frente-al-mercado-de-bazurto-genera-monumental-trancon/</t>
+          <t>https://www.noticiasrcn.com/colombia/yulixa-toloza-iba-muerta-en-el-carro-cuando-la-duena-de-la-estetica-uso-su-celular-para-enganar-a-la-amiga-1023496</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:23 p. m.</t>
+          <t>21/05/2026 06:29 p. m.</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
@@ -3076,24 +3072,24 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Dadis suspendió centro de estética en Cartagena tras inspección</t>
+          <t>Juez adelanta audiencia en caso del asesinato de Jaime Esteban Moreno ante alerta por vencimiento de términos</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/cartagena/2026/05/21/dadis-suspendio-centro-de-estetica-en-cartagena-por-realizar-procedimientos-invasivos-sin-habilitacion/</t>
+          <t>https://www.noticiasrcn.com/colombia/juez-adelanta-audiencia-en-caso-del-asesinato-de-jaime-esteban-moreno-1023493</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:23 p. m.</t>
+          <t>21/05/2026 06:22 p. m.</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3103,24 +3099,24 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>El conmovedor video de Yulixa Toloza que compartió su familia: así quieren recordarla</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/cartagena/</t>
+          <t>https://www.noticiasrcn.com/colombia/asi-era-yulixa-toloza-en-vida-familia-compartio-video-1023482</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:20 p. m.</t>
+          <t>21/05/2026 05:58 p. m.</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
@@ -3130,24 +3126,24 @@
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Miguel Díaz-Canel desafía a Donald Trump con contundente mensaje sobre Cuba</t>
+          <t>Presidente Gustavo Petro se reunirá con el papa León XIV en el Vaticano</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/mundo/2026/05/21/miguel-diaz-canel-desafia-a-donald-trump-con-contundente-mensaje-sobre-cuba/</t>
+          <t>https://www.noticiasrcn.com/colombia/presidente-gustavo-petro-se-reunira-con-el-papa-leon-xiv-en-el-vaticano-1023462</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:07 p. m.</t>
+          <t>21/05/2026 05:36 p. m.</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3157,24 +3153,24 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Caso Yulixa Toloza: Fiscalía rastreó a implicados mediante plataforma</t>
+          <t>Líder social Yanet Mosquera sufrió atentado en la vía Panamericana</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/2026/05/21/caso-yulixa-toloza-fiscalia-rastreo-a-implicados-mediante-plataforma/</t>
+          <t>https://www.noticiasrcn.com/colombia/lider-social-yanet-mosquera-sufrio-atentado-en-la-via-panamericana-1023476</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:04 p. m.</t>
+          <t>21/05/2026 05:12 p. m.</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
@@ -3184,24 +3180,24 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Por error, hombre arrolló con camión y le quitó la vida a su esposa Paulina Castro</t>
+          <t>Avanzan los cierres y sellamientos de centros estéticos en Bogotá tras el caso Yulixa Toloza</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/por-error-hombre-arrollo-con-camion-y-le-quito-la-vida-a-su-esposa-paulina-castro/</t>
+          <t>https://www.noticiasrcn.com/colombia/avanzan-los-cierres-y-sellamientos-de-centros-esteticos-en-bogota-tras-el-caso-yulixa-toloza-1023460</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 03:56 p. m.</t>
+          <t>21/05/2026 04:38 p. m.</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3211,24 +3207,24 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Vandalizan sede de campaña de Paloma Valencia durante manifestaciones en Bogotá</t>
+          <t>Cambian al procurador que pidió libertad para dos de los capturados por el caso de Yulixa Toloza</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/2026/05/21/vandalizan-sede-de-campana-de-paloma-valencia-durante-manifestaciones-en-bogota/</t>
+          <t>https://www.noticiasrcn.com/colombia/cambian-al-procurador-que-pidio-libertad-para-dos-de-los-capturados-por-el-caso-de-yulixa-toloza-1023468</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 03:43 p. m.</t>
+          <t>21/05/2026 04:09 p. m.</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
@@ -3238,24 +3234,24 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Ejemplar condena contra un mototaxista que agredió y abusó de su pasajera en Turbaco</t>
+          <t>El Dorado renovó su servicio gratuito de buses entre terminales con vehículos eléctricos</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/ejemplar-condena-contra-un-mototaxista-que-agredio-y-abuso-de-su-pasajera-en-turbaco/</t>
+          <t>https://www.noticiasrcn.com/colombia/el-dorado-estrena-buses-electricos-gratuitos-1023433</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 03:39 p. m.</t>
+          <t>21/05/2026 03:19 p. m.</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3265,24 +3261,24 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Así hallaron a pescador tras 24 horas desaparecido en el mar de Cartagena</t>
+          <t>VIDEO | Encapuchados vandalizaron sede de campaña de Paloma Valencia en la carrera Séptima, en Bogotá</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/asi-hallaron-a-pescador-tras-24-horas-desaparecido-en-el-mar-de-cartagena/</t>
+          <t>https://www.noticiasrcn.com/colombia/encapuchados-vandalizaron-sede-de-campana-de-paloma-valencia-en-la-carrera-septima-en-bogota-1023436</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 03:18 p. m.</t>
+          <t>21/05/2026 07:20 p. m.</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
@@ -3292,22 +3288,26 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Caen funcionarios de la Registraduría por fraude con cédulas para extranjeros</t>
+          <t>Abelardo de la Espriella se dispara, iría a segunda vuelta con Iván Cepeda y deja atrás a Paloma Valencia, según la encuesta de Invamer</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/caen-funcionarios-de-la-registraduria-por-fraude-con-cedulas-para-extranjeros/</t>
+          <t>https://www.semana.com/politica/articulo/abelardo-de-la-espriella-se-dispara-iria-a-segunda-vuelta-con-ivan-cepeda-y-deja-atras-a-paloma-valencia-segun-la-encuesta-de-invamer/202623/</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="inlineStr"/>
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>21/05/2026 07:18 p. m.</t>
+        </is>
+      </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -3315,17 +3315,17 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Premios Excelencia El Universal 2026: categorías, calendario y cómo participar</t>
+          <t>Definida la final del Torneo Betplay: sin jugar, Real Cartagena es finalista y se ilusiona con el ascenso</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/cartagena/2026/05/20/premios-excelencia-el-universal-2026-categorias-calendario-y-como-participar/</t>
+          <t>https://www.semana.com/deportes/articulo/definida-la-final-del-torneo-betplay-sin-jugar-real-cartagena-es-finalista-y-se-ilusiona-con-el-ascenso/202648/</t>
         </is>
       </c>
     </row>
@@ -3342,24 +3342,24 @@
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>¿Aumento de precios? Fenavi advierte que bloqueos en vía a Buenaventura impactarían abastecimiento de pollo y huevo</t>
+          <t>“Me arrodillo”: Gustavo Petro hizo un fuerte llamado de atención a la Corte Constitucional por retrasar su reforma pensional</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/pais/articulo/2026/5/aumento-de-precios-fenavi-advierte-que-bloqueos-en-via-a-buenaventura-impactarian-abastecimiento-de-pollo-y-huevo</t>
+          <t>https://www.semana.com/politica/articulo/me-arrodillo-gustavo-petro-dio-un-fuerte-discurso-contra-la-corte-constitucional-por-retrasar-su-reforma-pensional/202642/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:00 p. m.</t>
+          <t>21/05/2026 06:53 p. m.</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -3369,24 +3369,24 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Así es el USS Nimitz, el portaviones que Estados Unidos desplegó en el Caribe frente a Cuba</t>
+          <t>Esta fue la cronología para deshacerse del cuerpo de Yulixa Toloza: la Fiscalía reveló detalles</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/internacional/articulo/2026/5/asi-es-el-uss-nimitz-el-portaviones-que-estados-unidos-desplego-en-el-caribe-frente-a-cuba</t>
+          <t>https://www.semana.com/nacion/articulo/esta-fue-la-cronologia-para-deshacerse-del-cuerpo-de-yulixa-toloza-la-fiscalia-revelo-detalles/202642/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:00 p. m.</t>
+          <t>21/05/2026 06:47 p. m.</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
@@ -3396,24 +3396,24 @@
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>“Mis excompañeros me trataban de traidora”: alias Karina, explica por qué no fue a la JEP</t>
+          <t>Nueva ofensiva del gobierno Trump contra Cuba: ICE arresta a mujer vinculada a poderoso conglomerado económico y militar</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/conflicto-armado-en-colombia/articulo/2026/5/mis-excompaneros-me-trataban-de-traidora-alias-karina-explica-por-que-no-fue-a-la-jep</t>
+          <t>https://www.semana.com/mundo/articulo/nueva-ofensiva-del-gobierno-trump-contra-cuba-ice-arresta-a-mujer-vinculada-a-poderosa-estructura-economica-militar/202652/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:45 p. m.</t>
+          <t>21/05/2026 06:42 p. m.</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3423,24 +3423,24 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Disputa territorial entre comunidades indígenas deja tres muertos y varios heridos en Cauca</t>
+          <t>“Venderlo con urgencia”: la orden para desaparecer el carro en el que fue transportada Yulixa Toloza</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/pais/articulo/2026/5/disputa-territorial-entre-comunidades-indigenas-deja-tres-muertos-y-varios-heridos-en-cauca</t>
+          <t>https://www.semana.com/nacion/articulo/venderlo-con-urgencia-la-orden-para-desaparecer-el-carro-en-el-que-fue-transportada-yulixa-toloza/202632/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:30 p. m.</t>
+          <t>21/05/2026 06:41 p. m.</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
@@ -3450,24 +3450,24 @@
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>Defensoría alerta por crisis humanitaria en cárceles y centros de detención del país</t>
+          <t>La cuenta regresiva para el eclipse solar más largo del siglo: solo podrá verse en estos países del mundo</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/pais/articulo/2026/5/defensoria-alerta-por-crisis-humanitaria-en-carceles-y-centros-de-detencion-del-pais</t>
+          <t>https://www.semana.com/tecnologia/articulo/la-cuenta-regresiva-para-el-eclipse-solar-mas-largo-del-siglo-solo-podra-verse-en-estos-paises-del-mundo/202643/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:00 p. m.</t>
+          <t>21/05/2026 06:41 p. m.</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3477,24 +3477,24 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>¿Por qué los transportadores de servicio público están protestando en Cali?: alcalde Eder dice que no cederá a bloqueos</t>
+          <t>Marcelo Bielsa es noticia en Uruguay por decisión sobre su futuro: a nada del Mundial 2026</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/pais/articulo/2026/5/por-que-los-transportadores-de-servicio-publico-estan-protestando-en-cali-alcalde-eder-dice-que-no-cedera-a-bloqueos</t>
+          <t>https://www.semana.com/deportes/articulo/marcelo-bielsa-es-noticia-en-uruguay-por-decision-sobre-su-futuro-a-nada-del-mundial-2026/202609/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 03:20 p. m.</t>
+          <t>21/05/2026 06:41 p. m.</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
@@ -3504,24 +3504,24 @@
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>Alcaldía de Kennedy sella cinco centros estéticos por no cumplir con los requisitos</t>
+          <t>Ecuador mantiene los aranceles sobre Colombia: presentó dos recursos y dos acciones ante la Comunidad Andina</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/pais/articulo/2026/5/alcaldia-de-kennedy-sella-cinco-centros-esteticos-por-no-cumplir-con-los-requisitos</t>
+          <t>https://www.semana.com/economia/macroeconomia/articulo/ecuador-mantiene-los-aranceles-sobre-colombia-presento-dos-recursos-y-dos-acciones-ante-la-comunidad-andina/202649/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 03:20 p. m.</t>
+          <t>21/05/2026 06:41 p. m.</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -3531,24 +3531,24 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>¿Habrá racionamiento de agua en Bogotá por la llegada del Fenómeno del Niño?</t>
+          <t>Caos en la movilidad de Bogotá: UNDMO interviene en zonas aledañas a la Universidad Nacional</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/pais/articulo/2026/5/habra-racionamiento-de-agua-en-bogota-por-la-llegada-del-fenomeno-del-nino</t>
+          <t>https://www.semana.com/nacion/articulo/caos-en-la-movilidad-de-bogota-se-reportan-manifestaciones-en-la-septima-y-otros-puntos/202608/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 01:30 p. m.</t>
+          <t>21/05/2026 06:41 p. m.</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
@@ -3558,24 +3558,24 @@
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>Por título de Julián Bedoya, piden a la Corte confirmar condena contra exfuncionarios de la Universidad de Medellín</t>
+          <t>Fico Gutiérrez denunció ante autoridades en Estados Unidos al ruso que se volvió un dolor de cabeza para Medellín: “A mí no me intimidan”</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/poder/articulo/2026/5/por-titulo-de-julian-bedoya-piden-a-la-corte-confirmar-condena-contra-exfuncionarios-de-la-universidad-de-medellin</t>
+          <t>https://www.semana.com/nacion/medellin/articulo/fico-gutierrez-denuncio-ante-autoridades-en-estados-unidos-al-ruso-que-se-volvio-un-dolor-de-cabeza-para-medellin-a-mi-no-me-intimidan/202603/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 12:22 p. m.</t>
+          <t>21/05/2026 05:41 p. m.</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -3585,24 +3585,24 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>¿Atlas Intel podrá divulgar encuestas en la recta final de la campaña electoral?</t>
+          <t>“Que Dios proteja su humanidad”: el alarmante mensaje de Fabián Ríos sobre el estado actual de Francisco Bolívar</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/elecciones-colombia-2026/articulo/2026/5/atlas-intel-podra-divulgar-encuestas-en-la-recta-final-de-la-campana-electoral</t>
+          <t>https://www.semana.com/gente/articulo/que-dios-proteja-su-humanidad-el-alarmante-mensaje-de-fabian-rios-sobre-el-estado-actual-de-francisco-bolivar/202655/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 10:42 a. m.</t>
+          <t>21/05/2026 05:41 p. m.</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
@@ -3612,24 +3612,24 @@
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>Cae red que expedía documentos colombianos falsos a extranjeros para enviarlos a Estados Unidos</t>
+          <t>“Se acaban los peajes”: Gustavo Petro se pronunció tras anuncio de la ANI sobre medida que aplicará en una región del país</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/pais/articulo/2026/5/cae-red-que-expedia-documentos-colombianos-falsos-a-extranjeros-para-enviarlos-a-estados-unidos</t>
+          <t>https://www.semana.com/politica/articulo/se-acaban-los-peajes-gustavo-petro-se-pronuncio-tras-anuncio-de-la-ani-sobre-medida-que-aplicara-en-una-region-del-pais/202628/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:00 a. m.</t>
+          <t>21/05/2026 05:41 p. m.</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -3639,24 +3639,24 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Percepción positiva sobre la minería aumentó en el último año según estudio Brújula Minera</t>
+          <t>El canciller de Cuba, Bruno Rodríguez Parrilla, acusa a Marco Rubio de “instigar una agresión militar” contra la isla</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/economia/articulo/2026/5/percepcion-positiva-sobre-la-mineria-aumento-en-el-ultimo-ano-segun-estudio-brujula-minera</t>
+          <t>https://www.semana.com/mundo/articulo/el-canciller-de-cuba-bruno-rodriguez-parrilla-acusa-a-marco-rubio-de-instigar-una-agresion-militar-contra-la-isla/202650/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>20/05/2026 07:30 p. m.</t>
+          <t>21/05/2026 04:41 p. m.</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
@@ -3666,24 +3666,24 @@
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>Consejo de Estado frena beneficio a siete cabecillas de bandas de Medellín que negocian con el Gobierno</t>
+          <t>El presidente Gustavo Petro visitará al papa León XIV en el Vaticano: esta es la fecha del encuentro</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/justicia/articulo/2026/5/consejo-de-estado-frena-beneficio-a-siete-cabecillas-de-bandas-de-medellin-que-negocian-con-el-gobierno</t>
+          <t>https://www.semana.com/politica/articulo/el-presidente-gustavo-petro-visitara-al-papa-leon-xiv-en-el-vaticano-esta-es-la-fecha-del-encuentro/202651/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>20/05/2026 05:32 p. m.</t>
+          <t>21/05/2026 04:41 p. m.</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -3693,24 +3693,24 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>El obstáculo que enfrenta Colombia para juzgar a los capturados por el caso de Yulixa Toloza</t>
+          <t>CNE dejó en firme candidatura de Abelardo de la Espriella tras estudiar queja por supuestas irregularidades en la recolección de firmas</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/pais/articulo/2026/5/el-obstaculo-que-enfrenta-colombia-para-juzgar-a-los-capturados-por-el-caso-de-yulixa-toloza</t>
+          <t>https://www.semana.com/politica/articulo/cne-dejo-en-firme-candidatura-de-abelardo-de-la-espriella-tras-estudiar-queja-por-supuestas-irregularidades-en-la-recoleccion-de-firmas/202649/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>20/05/2026 05:30 p. m.</t>
+          <t>21/05/2026 04:41 p. m.</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
@@ -3720,24 +3720,24 @@
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>Olmedo López admite ante una jueza su responsabilidad en el robo a la UNGRD</t>
+          <t>Tres muertos y 44 heridos: saldo parcial del brutal choque entre comunidades indígenas en Cauca</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/pais/articulo/2026/5/olmedo-lopez-admite-ante-una-jueza-su-responsabilidad-en-el-robo-a-la-ungrd</t>
+          <t>https://www.semana.com/nacion/cali/articulo/tres-muertos-y-44-heridos-saldo-parcial-del-brutal-choque-entre-comunidades-indigenas-en-cauca/202626/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>20/05/2026 03:30 p. m.</t>
+          <t>21/05/2026 03:41 p. m.</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -3747,24 +3747,24 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Ataque con drones por parte de estructuras ilegales dejan un soldado muerto y otros cuatro uniformados heridos en el  sur de Bolívar</t>
+          <t>Vándalos atacaron la sede de Paloma Valencia y Juan Daniel Oviedo en Bogotá; dejaron mensajes alusivos a Iván Cepeda</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/ataque-drones-estructuras-ilegales-sur-bolivar</t>
+          <t>https://www.semana.com/politica/articulo/vandalos-atacaron-la-sede-de-paloma-valencia-y-juan-daniel-oviedo-en-bogota-dejaron-mensajes-alusivos-a-ivan-cepeda/202617/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:58 p. m.</t>
+          <t>21/05/2026 03:41 p. m.</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
@@ -3774,26 +3774,22 @@
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>Indignante: funcionario de la Secretaría de Movilidad fue agredido por un hombre en la Comuna 13; alcalde pide justicia</t>
+          <t>Gustavo Petro agitó las redes sociales por hablar de la constituyente: le pasaron factura por promesa que hizo en mármol</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/medellin/funcionario-publico-agredido-en-la-comuna-13-alcalde-rechaza-la-situacion-JM36819246</t>
+          <t>https://www.semana.com/politica/articulo/gustavo-petro-agito-las-redes-sociales-por-hablar-de-la-constituyente-le-pasaron-factura-por-promesa-que-hizo-en-marmol/202638/</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="inlineStr">
-        <is>
-          <t>21/05/2026 06:30 p. m.</t>
-        </is>
-      </c>
+      <c r="A122" s="3" t="inlineStr"/>
       <c r="B122" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -3801,26 +3797,22 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Encuesta Invamer: Cepeda lidera con 44,9 %, Abelardo sube a 31,6 % y Paloma baja a 14%</t>
+          <t>Lesión de Neymar alerta en Brasil con el Mundial 2026 a la vuelta: médico del Santos dio parte oficial</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/especiales/elecciones-2026/encuesta-invamer-abelardo-ivan-cepeda-paloma-valencia-elecciones-2026-JM36817835</t>
+          <t>https://www.semana.com/deportes/articulo/lesion-de-neymar-alerta-en-brasil-con-el-mundial-2026-a-la-vuelta-medico-del-santos-dio-parte-oficial/202648/</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>21/05/2026 06:20 p. m.</t>
-        </is>
-      </c>
+      <c r="A123" s="6" t="inlineStr"/>
       <c r="B123" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -3828,26 +3820,22 @@
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>Según encuesta CB Global, habría empate técnico entre Iván Cepeda y Abelardo de la Espriella en primera vuelta</t>
+          <t>Carlos Vives le hace honor a la Selección Colombia y hace importante anuncio</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/especiales/elecciones-2026/encuesta-cb-global-empate-tecnico-cepeda-abelardo-paloma-fajardo-HM36812306</t>
+          <t>https://www.semana.com/cultura/articulo/carlos-vives-le-hace-honor-a-la-seleccion-colombia-y-hace-importante-anuncio/202654/</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="inlineStr">
-        <is>
-          <t>21/05/2026 05:20 p. m.</t>
-        </is>
-      </c>
+      <c r="A124" s="3" t="inlineStr"/>
       <c r="B124" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -3855,26 +3843,22 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Neymar sufrió lesión y preocupa a Brasil de cara al Mundial</t>
+          <t>Si no pudo ir, así podrá vivir el Mundial 2026 en Colombia: ‘Fan Zone’, la llamativa apuesta de la FCF</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/deportes/futbol/neymar-lesion-pantorilla-santos-mundial-brasil-EM36815652</t>
+          <t>https://www.semana.com/deportes/articulo/si-no-pudo-ir-asi-podra-vivir-el-mundial-2026-en-colombia-fan-zone-la-llamativa-apuesta-de-la-fcf/202618/</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="6" t="inlineStr">
-        <is>
-          <t>21/05/2026 04:20 p. m.</t>
-        </is>
-      </c>
+      <c r="A125" s="6" t="inlineStr"/>
       <c r="B125" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -3882,26 +3866,22 @@
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>¿Y los niños? En estos temas sobre la infancia se rajan los programas de candidatos a la presidencia, segúnNiñezYa</t>
+          <t>Ola de críticas contra Jhon Jáder Durán por salir con botella en mano: video hunde sueño del Mundial</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/especiales/elecciones-2026/candidatos-presidencia-se-rajan-propuestas-ninez-ON36803094</t>
+          <t>https://www.semana.com/deportes/articulo/ola-de-criticas-contra-jhon-jader-duran-por-salir-con-botella-en-mano-video-hunde-sueno-del-mundial/202655/</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="inlineStr">
-        <is>
-          <t>21/05/2026 04:20 p. m.</t>
-        </is>
-      </c>
+      <c r="A126" s="3" t="inlineStr"/>
       <c r="B126" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -3909,26 +3889,22 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>¿Cómo calcular la prima de junio de 2026 y cuánto recibirán quienes ganan el salario mínimo? Estas son las fechas y condiciones para el pago</t>
+          <t>Paloma Valencia propone regalar neveras nuevas; recuerdan cuando Daniel Quintero ofrecía lavadoras</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/negocios/finanzas/prima-junio-2026-colombia-cuanto-recibiran-como-se-calcula-DM36811424</t>
+          <t>https://www.semana.com/politica/articulo/paloma-valencia-propone-regalar-neveras-nuevas-recuerdan-cuando-daniel-quintero-ofrecia-lavadoras/202631/</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="6" t="inlineStr">
-        <is>
-          <t>21/05/2026 04:20 p. m.</t>
-        </is>
-      </c>
+      <c r="A127" s="6" t="inlineStr"/>
       <c r="B127" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -3936,26 +3912,22 @@
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>Encuesta Guarumo: Cepeda lidera con 37,1 %; siguen Abelardo con 27,5 % y Paloma con 21,7 %, ¿y en segunda vuelta?</t>
+          <t>Iván Cepeda presentó en Bogotá un paquete de medidas sociales con las que busca ganar la Presidencia: habría salario mínimo vital para líderes sociales</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/especiales/elecciones-2026/encuesta-guarumo-mayo-2026-cepeda-lidera-GM36810017</t>
+          <t>https://www.semana.com/politica/articulo/ivan-cepeda-presento-en-bogota-un-paquete-de-medidas-sociales-con-las-que-busca-ganar-la-presidencia-habria-salario-minimo-vital-para-lideres-sociales/202642/</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="inlineStr">
-        <is>
-          <t>21/05/2026 03:20 p. m.</t>
-        </is>
-      </c>
+      <c r="A128" s="3" t="inlineStr"/>
       <c r="B128" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -3963,26 +3935,22 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Luis Almagro, exsecretario general de la OEA, apoyará a Paloma: estas son las razones</t>
+          <t>La Casa de la Constitución: el centro en el que se adelantará el proceso de referendo contra la constituyente de Petro</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/especiales/elecciones-2026/paloma-valencia-apoyo-luis-almagro-elecciones-2026-ON36802268</t>
+          <t>https://www.semana.com/politica/articulo/la-casa-de-la-constitucion-el-centro-en-el-que-se-adelantara-el-proceso-de-referendo-contra-la-constituyente-de-petro/202646/</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t>21/05/2026 03:20 p. m.</t>
-        </is>
-      </c>
+      <c r="A129" s="6" t="inlineStr"/>
       <c r="B129" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -3990,26 +3958,22 @@
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>¿Monta en metro y aún no ha renovado su Cívica Classic? Pilas que queda poco tiempo para hacerlo</t>
+          <t>“No acepto”: vinculados al crimen de Yulixa Toloza se declararon inocentes. Detalles de la imputación</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/medellin/renovar-civica-classic-metro-medellin-NN36802780</t>
+          <t>https://www.semana.com/nacion/articulo/no-acepto-vinculados-al-crimen-de-yulixa-toloza-se-declararon-inocentes-detalles-de-la-imputacion/202647/</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="inlineStr">
-        <is>
-          <t>21/05/2026 03:20 p. m.</t>
-        </is>
-      </c>
+      <c r="A130" s="3" t="inlineStr"/>
       <c r="B130" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -4017,26 +3981,22 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Irene Vélez sería investigada en escándalo por millonario saqueo de regalías</t>
+          <t>Colombia anuncia cierre de puente internacional con Ecuador: esta es la razón de la medida</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/ministra-ambiente-investigada-caso-corrupcion-regalias-GN36803757</t>
+          <t>https://www.semana.com/nacion/articulo/colombia-anuncia-cierre-de-puente-internacional-con-ecuador-esta-es-la-razon-de-la-medida/202607/</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="6" t="inlineStr">
-        <is>
-          <t>21/05/2026 03:20 p. m.</t>
-        </is>
-      </c>
+      <c r="A131" s="6" t="inlineStr"/>
       <c r="B131" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -4044,26 +4004,22 @@
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>Ricardo Arjona regresa a Medellín, ¿cuándo y dónde será el concierto del guatemalteco?</t>
+          <t>Pacífico 1: obras en punto clave de la vía avanzan en su estabilización y manejo controlado del tráfico</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/cultura/musica/ricardo-arjona-concierto-medellin-envigado-2026-AN36802626</t>
+          <t>https://www.semana.com/nacion/articulo/pacifico-1-obras-en-punto-clave-de-la-via-avanzan-en-su-estabilizacion-y-manejo-controlado-del-trafico/202623/</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="inlineStr">
-        <is>
-          <t>21/05/2026 03:20 p. m.</t>
-        </is>
-      </c>
+      <c r="A132" s="3" t="inlineStr"/>
       <c r="B132" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -4071,24 +4027,24 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Tres muertos y 44 heridos dejan enfrentamientos entre comunidades Misak y Nasa en Cauca</t>
+          <t>“Empecemos a trabajar como seres civilizados”: procurador Eljach tras enfrentamientos entre comunidades misak y nasa</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/tres-muertos-44-heridos-enfrentamientos-comunidades-misak-nasa-cauca-CN36804547</t>
+          <t>https://www.semana.com/nacion/articulo/empecemos-a-trabajar-como-seres-civilizados-procurador-eljach-tras-enfrentamientos-entre-comunidades-misak-y-nasa/202625/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 03:20 p. m.</t>
+          <t>21/05/2026 07:18 p. m.</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
@@ -4103,19 +4059,19 @@
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>UdeA y EAFIT, entre mejores universidades del país, según Nature</t>
+          <t>Cero y van tres: la ANI dejó plantados otra vez a alcaldes del Oriente antioqueño</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/tendencias/nature-index-2025-universidad-antioquia-eafit-colombia-ranking-cientifico-GN36806617</t>
+          <t>https://www.elcolombiano.com/antioquia/la-ani-deja-plantados-a-alcaldes-oriente-antioqueno-MP36820268</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 03:20 p. m.</t>
+          <t>21/05/2026 06:56 p. m.</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -4130,19 +4086,19 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Sede de Paloma Valencia y Juan D. Oviedo en Bogotá fue vandalizada; piden garantías de seguridad</t>
+          <t>Indignante: funcionario de la Secretaría de Movilidad fue agredido por un hombre en la Comuna 13; alcalde pide justicia</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/politica/campana-de-paloma-valencia-denuncia-ataques-a-sede-en-bogota-HN36803037</t>
+          <t>https://www.elcolombiano.com/medellin/funcionario-publico-agredido-en-la-comuna-13-alcalde-rechaza-la-situacion-JM36819246</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 03:20 p. m.</t>
+          <t>21/05/2026 06:47 p. m.</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
@@ -4157,19 +4113,19 @@
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>Oficial: Conmebol emitió dura sanción contra el DIM por desmanes en el partido contra Flamengo en el Atanasio</t>
+          <t>La historia de Dafne: se la robaron hace 44 años en una clínica de Medellín y su familia aún la busca</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/deportes/futbol/dim-vs-flamengo-copa-libertadores-2026-sanciones-conmebol-GN36806819</t>
+          <t>https://www.elcolombiano.com/medellin/robo-bebe-dafne-desaparecida-familia-busqueda-FM36818490</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 02:20 p. m.</t>
+          <t>21/05/2026 06:41 p. m.</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -4184,19 +4140,19 @@
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Michael Jackson es hoy el número uno en la lista Billboard Artist 100 y es el sexto en hacerlo póstumamente</t>
+          <t>Según encuesta CB Global, habría empate técnico entre Iván Cepeda y Abelardo de la Espriella en primera vuelta</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/cultura/musica/michael-jackson-lidera-billboard-artist-tras-exito-de-su-pelicula-EL36796211</t>
+          <t>https://www.elcolombiano.com/especiales/elecciones-2026/encuesta-cb-global-empate-tecnico-cepeda-abelardo-paloma-fajardo-HM36812306</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 02:20 p. m.</t>
+          <t>21/05/2026 06:41 p. m.</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
@@ -4211,19 +4167,19 @@
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>Colombia podría sufrir por energía en el Mundial 2026; consumo subiría hasta 5%</t>
+          <t>Encuesta Invamer: Cepeda lidera con 44,9 %, Abelardo sube a 31,6 % y Paloma baja a 14%</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/negocios/energia-colombia-mundial-2026-consumo-embalses-racionamiento-FL36799840</t>
+          <t>https://www.elcolombiano.com/especiales/elecciones-2026/encuesta-invamer-abelardo-ivan-cepeda-paloma-valencia-elecciones-2026-JM36817835</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 02:20 p. m.</t>
+          <t>21/05/2026 05:41 p. m.</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -4238,19 +4194,19 @@
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>El próximo gobierno deberá emitir más deuda sin importar quién gane en las elecciones: JP Morgan</t>
+          <t>Neymar sufrió lesión y preocupa a Brasil de cara al Mundial</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/negocios/deuda-colombia-2026-jpmorgan-proximo-gobierno-emision-deuda-CN36802044</t>
+          <t>https://www.elcolombiano.com/deportes/futbol/neymar-lesion-pantorilla-santos-mundial-brasil-EM36815652</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 02:20 p. m.</t>
+          <t>21/05/2026 04:41 p. m.</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
@@ -4265,19 +4221,19 @@
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>Se conoce la causa de muerte de Yulixa Toloza: Medicina Legal ya dio informe</t>
+          <t>¿Y los niños? En estos temas sobre la infancia se rajan los programas de candidatos a la presidencia, segúnNiñezYa</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/embolia-pulmonar-causa-muerte-yulixa-toloza-centro-estetico-bogota-LL36799543</t>
+          <t>https://www.elcolombiano.com/especiales/elecciones-2026/candidatos-presidencia-se-rajan-propuestas-ninez-ON36803094</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 02:20 p. m.</t>
+          <t>21/05/2026 04:41 p. m.</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -4292,19 +4248,19 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Colombia tiene menos de 4 meses para evitar una crisis energética: Andesco</t>
+          <t>¿Cómo calcular la prima de junio de 2026 y cuánto recibirán quienes ganan el salario mínimo? Estas son las fechas y condiciones para el pago</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/negocios/colombia-cuatro-meses-evitar-crisis-energetica-el-nino-2026-andesco-MN36800972</t>
+          <t>https://www.elcolombiano.com/negocios/finanzas/prima-junio-2026-colombia-cuanto-recibiran-como-se-calcula-DM36811424</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 01:20 p. m.</t>
+          <t>21/05/2026 04:41 p. m.</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
@@ -4319,19 +4275,19 @@
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>¿Quién operó a Yulixa Toloza? Medio venezolano controvierte versiones y aseguró que fue un cirujano certificado</t>
+          <t>Encuesta Guarumo: Cepeda lidera con 37,1 %; siguen Abelardo con 27,5 % y Paloma con 21,7 %, ¿y en segunda vuelta?</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/quien-opero-yulixa-toloza-medio-venezolano-asegura-cirujano-certificado-CL36797630</t>
+          <t>https://www.elcolombiano.com/especiales/elecciones-2026/encuesta-guarumo-mayo-2026-cepeda-lidera-GM36810017</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 12:20 p. m.</t>
+          <t>21/05/2026 03:41 p. m.</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -4346,19 +4302,19 @@
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Así suena la canción oficial de la Selección Colombia rumbo al Mundial de Norteamérica</t>
+          <t>¿Monta en metro y aún no ha renovado su Cívica Classic? Pilas que queda poco tiempo para hacerlo</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/deportes/futbol/cancion-barras-incondicionales-seleccion-colombia-carlos-vives-IL36796781</t>
+          <t>https://www.elcolombiano.com/medellin/renovar-civica-classic-metro-medellin-NN36802780</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 12:20 p. m.</t>
+          <t>21/05/2026 03:41 p. m.</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
@@ -4373,19 +4329,19 @@
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>Matronas de barrios populares y corregimientos de Medellín llevan su cocina a La Pascasia</t>
+          <t>Irene Vélez sería investigada en escándalo por millonario saqueo de regalías</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/cultura/gastronomia/feria-gastronomica-matronas-urbanas-medellin-pascasia-carmen-acosta-JL36795639</t>
+          <t>https://www.elcolombiano.com/colombia/ministra-ambiente-investigada-caso-corrupcion-regalias-GN36803757</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 12:20 p. m.</t>
+          <t>21/05/2026 03:41 p. m.</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -4400,19 +4356,19 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Erradicación manual cayó 92% con Petro y contratos siguen sin destrabarse</t>
+          <t>Ricardo Arjona regresa a Medellín, ¿cuándo y dónde será el concierto del guatemalteco?</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/erradicacion-manuel-redujo-gobierno-gustavo-petro-no-hay-contratos-ML36795494</t>
+          <t>https://www.elcolombiano.com/cultura/musica/ricardo-arjona-concierto-medellin-envigado-2026-AN36802626</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 10:20 a. m.</t>
+          <t>21/05/2026 03:41 p. m.</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
@@ -4427,19 +4383,19 @@
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>Hombre fue condenado en Estados Unidos a 30 años de cárcel por delitos sexuales contra menores en Medellín</t>
+          <t>Tres muertos y 44 heridos dejan enfrentamientos entre comunidades Misak y Nasa en Cauca</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/medellin/condena-carcel-ramon-arellano-delitos-sexuales-en-medellin-estados-unidos-CL36791425</t>
+          <t>https://www.elcolombiano.com/colombia/tres-muertos-44-heridos-enfrentamientos-comunidades-misak-nasa-cauca-CN36804547</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 10:20 a. m.</t>
+          <t>21/05/2026 03:41 p. m.</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -4454,19 +4410,19 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Así cayó Valentina Mor: lainfluencerseñalada de drogar y robar a extranjeros en Medellín</t>
+          <t>UdeA y EAFIT, entre mejores universidades del país, según Nature</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/medellin/capturan-valentina-mor-influenciadora-robar-extranjeros-medellin-EK36787425</t>
+          <t>https://www.elcolombiano.com/tendencias/nature-index-2025-universidad-antioquia-eafit-colombia-ranking-cientifico-GN36806617</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 09:20 a. m.</t>
+          <t>21/05/2026 03:41 p. m.</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
@@ -4481,19 +4437,19 @@
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>Estas son las leyendas del fútbol que aparecen en “Dai Dai”, la nueva canción de Shakira para el Mundial 2026</t>
+          <t>Sede de Paloma Valencia y Juan D. Oviedo en Bogotá fue vandalizada; piden garantías de seguridad</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/tendencias/leyendas-futbol-aparecen-dai-dai-cancion-shakira-mundial-KK36784086</t>
+          <t>https://www.elcolombiano.com/colombia/politica/campana-de-paloma-valencia-denuncia-ataques-a-sede-en-bogota-HN36803037</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 09:20 a. m.</t>
+          <t>21/05/2026 03:41 p. m.</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -4508,19 +4464,19 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Este es el prontuario de los siete cabecillas de la Paz Urbana a los que les reactivaron las órdenes de captura</t>
+          <t>Oficial: Conmebol emitió dura sanción contra el DIM por desmanes en el partido contra Flamengo en el Atanasio</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/medellin/delitos-cabecillas-paz-urbana-ordenes-captura-consejo-de-estado-AK36784848</t>
+          <t>https://www.elcolombiano.com/deportes/futbol/dim-vs-flamengo-copa-libertadores-2026-sanciones-conmebol-GN36806819</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:20 a. m.</t>
+          <t>21/05/2026 02:41 p. m.</t>
         </is>
       </c>
       <c r="B149" s="6" t="inlineStr">
@@ -4535,17 +4491,21 @@
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>Caso Yulixa Toloza: ¿qué pasa con los controles a ‘clínicas de garaje’?</t>
+          <t>Michael Jackson es hoy el número uno en la lista Billboard Artist 100 y es el sexto en hacerlo póstumamente</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/yulixa-toloza-que-pasa-controles-clinicas-garaje-EF36777605</t>
+          <t>https://www.elcolombiano.com/cultura/musica/michael-jackson-lidera-billboard-artist-tras-exito-de-su-pelicula-EL36796211</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="3" t="inlineStr"/>
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>21/05/2026 02:41 p. m.</t>
+        </is>
+      </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -4558,19 +4518,19 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Operativo destapa helicóptero con pasado oscuro y motor Rolls-Royce</t>
+          <t>Colombia podría sufrir por energía en el Mundial 2026; consumo subiría hasta 5%</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/ejercito-incauta-helicoptero-de-la-mafia-NG33717192</t>
+          <t>https://www.elcolombiano.com/negocios/energia-colombia-mundial-2026-consumo-embalses-racionamiento-FL36799840</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:54 p. m.</t>
+          <t>21/05/2026 02:41 p. m.</t>
         </is>
       </c>
       <c r="B151" s="6" t="inlineStr">
@@ -4580,24 +4540,24 @@
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>Estudio revela que residuos de alimentos y bebidas lideran la contaminación marina global</t>
+          <t>El próximo gobierno deberá emitir más deuda sin importar quién gane en las elecciones: JP Morgan</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/ambiente/blog-el-rio/estudio-revela-que-residuos-de-alimentos-y-bebidas-lideran-la-contaminacion-marina-global/</t>
+          <t>https://www.elcolombiano.com/negocios/deuda-colombia-2026-jpmorgan-proximo-gobierno-emision-deuda-CN36802044</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:45 p. m.</t>
+          <t>21/05/2026 02:41 p. m.</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -4607,24 +4567,24 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Cede el hambre en Colombia: ¿qué hay y qué falta para asegurar el derecho a la alimentación?</t>
+          <t>Se conoce la causa de muerte de Yulixa Toloza: Medicina Legal ya dio informe</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/economia/cede-el-hambre-en-colombia-que-hay-y-que-falta-para-asegurar-el-derecho-a-la-alimentacion/</t>
+          <t>https://www.elcolombiano.com/colombia/embolia-pulmonar-causa-muerte-yulixa-toloza-centro-estetico-bogota-LL36799543</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:43 p. m.</t>
+          <t>21/05/2026 02:41 p. m.</t>
         </is>
       </c>
       <c r="B153" s="6" t="inlineStr">
@@ -4634,24 +4594,24 @@
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>Familia de Jaime Moreno pide acelerar juicio para evitar libertad de sus posibles asesinos</t>
+          <t>Colombia tiene menos de 4 meses para evitar una crisis energética: Andesco</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/bogota/caso-jaime-moreno-familia-pide-acelerar-juicio-para-evitar-libertad-de-senalados-homicidas/</t>
+          <t>https://www.elcolombiano.com/negocios/colombia-cuatro-meses-evitar-crisis-energetica-el-nino-2026-andesco-MN36800972</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>20/05/2026 07:20 p. m.</t>
+          <t>21/05/2026 01:41 p. m.</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -4661,24 +4621,24 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Sebastián Villa, figura en Copa Libertadores: marcó y asistió en el triunfo de su equipo</t>
+          <t>¿Quién operó a Yulixa Toloza? Medio venezolano controvierte versiones y aseguró que fue un cirujano certificado</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/deportes/futbol-mundial/sebastian-villa-figura-en-copa-libertadores-marco-y-asistio-en-el-triunfo-de-su-equipo/</t>
+          <t>https://www.elcolombiano.com/colombia/quien-opero-yulixa-toloza-medio-venezolano-asegura-cirujano-certificado-CL36797630</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>20/05/2026 07:15 p. m.</t>
+          <t>21/05/2026 12:41 p. m.</t>
         </is>
       </c>
       <c r="B155" s="6" t="inlineStr">
@@ -4688,24 +4648,24 @@
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>Más apoyo para el ciclismo colombiano: así funcionará la alianza con LATAM</t>
+          <t>Así suena la canción oficial de la Selección Colombia rumbo al Mundial de Norteamérica</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/deportes/ciclismo/mas-apoyo-para-el-ciclismo-colombiano-asi-funcionara-la-alianza-con-latam/</t>
+          <t>https://www.elcolombiano.com/deportes/futbol/cancion-barras-incondicionales-seleccion-colombia-carlos-vives-IL36796781</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>20/05/2026 07:10 p. m.</t>
+          <t>21/05/2026 12:41 p. m.</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -4715,24 +4675,24 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>No aceptaron cargos: Sequera y Hernández, imputados por dos cargos en el caso Yulixa Toloza</t>
+          <t>Matronas de barrios populares y corregimientos de Medellín llevan su cocina a La Pascasia</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/bogota/audiencia-en-vivo-del-caso-yulixa-toloza-fiscalia-entrega-mas-detalles-de-la-investigacion/</t>
+          <t>https://www.elcolombiano.com/cultura/gastronomia/feria-gastronomica-matronas-urbanas-medellin-pascasia-carmen-acosta-JL36795639</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>20/05/2026 07:04 p. m.</t>
+          <t>21/05/2026 12:41 p. m.</t>
         </is>
       </c>
       <c r="B157" s="6" t="inlineStr">
@@ -4742,24 +4702,24 @@
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>Invamer: Cepeda (44,6 %), De la Espriella (31,6 %) y Valencia (14 %) lideran la contienda</t>
+          <t>Erradicación manual cayó 92% con Petro y contratos siguen sin destrabarse</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/politica/elecciones-colombia-2026/encuesta-invamer-ivan-cepeda-abelardo-de-la-espriella-y-paloma-valencia-lideran-la-contienda-asi-les-fue/</t>
+          <t>https://www.elcolombiano.com/colombia/erradicacion-manuel-redujo-gobierno-gustavo-petro-no-hay-contratos-ML36795494</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>20/05/2026 07:02 p. m.</t>
+          <t>21/05/2026 10:41 a. m.</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -4769,24 +4729,24 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Mauricio García Villegas aboga por volver a la razón “Antes de perder el juicio”</t>
+          <t>Hombre fue condenado en Estados Unidos a 30 años de cárcel por delitos sexuales contra menores en Medellín</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/el-magazin-cultural/mauricio-garcia-villegas-aboga-por-volver-a-la-razon-antes-de-perder-el-juicio/</t>
+          <t>https://www.elcolombiano.com/medellin/condena-carcel-ramon-arellano-delitos-sexuales-en-medellin-estados-unidos-CL36791425</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>20/05/2026 07:02 p. m.</t>
+          <t>21/05/2026 09:41 a. m.</t>
         </is>
       </c>
       <c r="B159" s="6" t="inlineStr">
@@ -4796,24 +4756,24 @@
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>Chancla de Call of Duty: ¿Cómo conseguir la nueva arma por el Día de la Madre?</t>
+          <t>Estas son las leyendas del fútbol que aparecen en “Dai Dai”, la nueva canción de Shakira para el Mundial 2026</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/tecnologia/videojuegos/chancla-de-call-of-duty-como-conseguir-la-nueva-arma-por-el-dia-de-la-madre/</t>
+          <t>https://www.elcolombiano.com/tendencias/leyendas-futbol-aparecen-dai-dai-cancion-shakira-mundial-KK36784086</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>20/05/2026 07:00 p. m.</t>
+          <t>21/05/2026 09:41 a. m.</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -4823,24 +4783,24 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Regresaron al bosque a monitorear al imponente águila crestada, pero encontraron un potrero</t>
+          <t>Este es el prontuario de los siete cabecillas de la Paz Urbana a los que les reactivaron las órdenes de captura</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/ambiente/regresaron-al-bosque-para-monitorear-al-imponente-aguila-crestada-pero-encontraron-un-potrero/</t>
+          <t>https://www.elcolombiano.com/medellin/delitos-cabecillas-paz-urbana-ordenes-captura-consejo-de-estado-AK36784848</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:46 p. m.</t>
+          <t>21/05/2026 05:41 a. m.</t>
         </is>
       </c>
       <c r="B161" s="6" t="inlineStr">
@@ -4850,26 +4810,22 @@
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>Nueva ofensiva del gobierno Trump contra Cuba: ICE arresta a mujer vinculada a poderoso conglomerado económico y militar</t>
+          <t>Caso Yulixa Toloza: ¿qué pasa con los controles a ‘clínicas de garaje’?</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/mundo/articulo/nueva-ofensiva-del-gobierno-trump-contra-cuba-ice-arresta-a-mujer-vinculada-a-poderosa-estructura-economica-militar/202652/</t>
+          <t>https://www.elcolombiano.com/colombia/yulixa-toloza-que-pasa-controles-clinicas-garaje-EF36777605</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="3" t="inlineStr">
-        <is>
-          <t>21/05/2026 06:41 p. m.</t>
-        </is>
-      </c>
+      <c r="A162" s="3" t="inlineStr"/>
       <c r="B162" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -4877,24 +4833,24 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>“Venderlo con urgencia”: la orden para desaparecer el carro en el que fue transportada Yulixa Toloza</t>
+          <t>Operativo destapa helicóptero con pasado oscuro y motor Rolls-Royce</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/articulo/venderlo-con-urgencia-la-orden-para-desaparecer-el-carro-en-el-que-fue-transportada-yulixa-toloza/202632/</t>
+          <t>https://www.elcolombiano.com/colombia/ejercito-incauta-helicoptero-de-la-mafia-NG33717192</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:37 p. m.</t>
+          <t>21/05/2026 07:05 p. m.</t>
         </is>
       </c>
       <c r="B163" s="6" t="inlineStr">
@@ -4904,24 +4860,24 @@
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>Ecuador mantiene los aranceles sobre Colombia: presentó dos recursos y dos acciones ante la Comunidad Andina</t>
+          <t>Paloma Valencia y Abelardo de la Espriella vencerían a Iván Cepeda en segunda vuelta, según la encuesta de Guarumo</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/economia/macroeconomia/articulo/ecuador-mantiene-los-aranceles-sobre-colombia-presento-dos-recursos-y-dos-acciones-ante-la-comunidad-andina/202649/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-22/paloma-valencia-y-abelardo-de-la-espriella-vencerian-a-ivan-cepeda-en-segunda-vuelta-segun-la-encuesta-de-guarumo.html</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:25 p. m.</t>
+          <t>21/05/2026 07:00 p. m.</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -4931,24 +4887,24 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>Caos en la movilidad de Bogotá: UNDMO interviene en zonas aledañas a la Universidad Nacional</t>
+          <t>Hora 20 y EL PAÍS en elecciones: ¿Cuál es el país con el que sueñan los jóvenes?</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/articulo/caos-en-la-movilidad-de-bogota-se-reportan-manifestaciones-en-la-septima-y-otros-puntos/202608/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/hora-20/2026-05-22/hora-20-y-el-pais-en-elecciones-cual-es-el-pais-con-el-que-suenan-los-jovenes.html</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:21 p. m.</t>
+          <t>21/05/2026 06:51 p. m.</t>
         </is>
       </c>
       <c r="B165" s="6" t="inlineStr">
@@ -4958,24 +4914,24 @@
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>Marcelo Bielsa es noticia en Uruguay por decisión sobre su futuro: a nada del Mundial 2026</t>
+          <t>Sheinbaum intenta relanzar la relación con Estados Unidos recibiendo al jefe de Seguridad Interior de Trump</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/marcelo-bielsa-es-noticia-en-uruguay-por-decision-sobre-su-futuro-a-nada-del-mundial-2026/202609/</t>
+          <t>https://elpais.com/mexico/2026-05-21/sheinbaum-intenta-relanzar-la-relacion-con-estados-unidos-recibiendo-al-jefe-de-seguridad-interior-de-trump.html</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:20 p. m.</t>
+          <t>21/05/2026 06:46 p. m.</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -4985,24 +4941,24 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>La cuenta regresiva para el eclipse solar más largo del siglo: solo podrá verse en estos países del mundo</t>
+          <t>El ICE detiene en Florida a la hermana de la jefa del conglomerado militar cubano Gaesa</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/tecnologia/articulo/la-cuenta-regresiva-para-el-eclipse-solar-mas-largo-del-siglo-solo-podra-verse-en-estos-paises-del-mundo/202643/</t>
+          <t>https://elpais.com/us/2026-05-21/el-ice-detiene-en-florida-a-la-hermana-de-la-jefa-del-conglomerado-militar-cubano-gaesa.html</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:20 p. m.</t>
+          <t>21/05/2026 05:44 p. m.</t>
         </is>
       </c>
       <c r="B167" s="6" t="inlineStr">
@@ -5012,24 +4968,24 @@
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>El canciller de Cuba, Bruno Rodríguez Parrilla, acusa a Marco Rubio de “instigar una agresión militar” contra la isla</t>
+          <t>Videoanálisis | La derecha tradicional también flaquea en Colombia</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/mundo/articulo/el-canciller-de-cuba-bruno-rodriguez-parrilla-acusa-a-marco-rubio-de-instigar-una-agresion-militar-contra-la-isla/202650/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-21/videoanalisis-la-derecha-tradicional-tambien-flaquea-en-colombia.html</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:20 p. m.</t>
+          <t>21/05/2026 05:37 p. m.</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -5039,24 +4995,24 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Fico Gutiérrez denunció ante autoridades en Estados Unidos al ruso que se volvió un dolor de cabeza para Medellín: “A mí no me intimidan”</t>
+          <t>Sheinbaum aprovecha la reforma judicial para colar un paquete electoral por la vía rápida</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/medellin/articulo/fico-gutierrez-denuncio-ante-autoridades-en-estados-unidos-al-ruso-que-se-volvio-un-dolor-de-cabeza-para-medellin-a-mi-no-me-intimidan/202603/</t>
+          <t>https://elpais.com/mexico/2026-05-21/sheinbaum-aprovecha-la-reforma-judicial-para-colar-un-paquete-electoral-por-la-via-rapida.html</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:20 p. m.</t>
+          <t>21/05/2026 05:30 p. m.</t>
         </is>
       </c>
       <c r="B169" s="6" t="inlineStr">
@@ -5066,24 +5022,24 @@
       </c>
       <c r="C169" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>Enfermedad deja a titular de Atlético Nacional fuera de la semifinal ante Tolima: baja muy sensible</t>
+          <t>Radiografía de la salud mental en el mundo: 1.200 millones de personas viven con trastornos psiquiátricos</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/enfermedad-deja-a-titular-de-atletico-nacional-fuera-de-la-semifinal-ante-tolima-baja-muy-sensible/202658/</t>
+          <t>https://elpais.com/salud-y-bienestar/2026-05-22/radiografia-de-la-salud-mental-en-el-mundo-1200-millones-de-personas-viven-con-trastornos-psiquiatricos.html</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:20 p. m.</t>
+          <t>21/05/2026 05:13 p. m.</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -5093,24 +5049,24 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>“Que Dios proteja su humanidad”: el alarmante mensaje de Fabián Ríos sobre el estado actual de Francisco Bolívar</t>
+          <t>La CNTE prepara un paro nacional indefinido el 1 de junio, ¿qué exigen los maestros?</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/gente/articulo/que-dios-proteja-su-humanidad-el-alarmante-mensaje-de-fabian-rios-sobre-el-estado-actual-de-francisco-bolivar/202655/</t>
+          <t>https://elpais.com/mexico/2026-05-21/la-cnte-prepara-un-paro-nacional-indefinido-el-1-de-junio-que-exigen-los-maestros.html</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:20 p. m.</t>
+          <t>21/05/2026 05:01 p. m.</t>
         </is>
       </c>
       <c r="B171" s="6" t="inlineStr">
@@ -5120,24 +5076,24 @@
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>El presidente Gustavo Petro visitará al papa León XIV en el Vaticano: esta es la fecha del encuentro</t>
+          <t>Emanciparse, una misión cada vez más imposible para los jóvenes: necesitan el 99% de su sueldo para irse a vivir solos</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/el-presidente-gustavo-petro-visitara-al-papa-leon-xiv-en-el-vaticano-esta-es-la-fecha-del-encuentro/202651/</t>
+          <t>https://elpais.com/sociedad/2026-05-21/emanciparse-una-mision-cada-vez-mas-imposible-para-los-jovenes-necesitan-el-99-de-su-sueldo-para-irse-a-vivir-solos.html</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:20 p. m.</t>
+          <t>21/05/2026 04:50 p. m.</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -5147,24 +5103,24 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>“Se acaban los peajes”: Gustavo Petro se pronunció tras anuncio de la ANI sobre medida que aplicará en una región del país</t>
+          <t>El Gobierno de Milei amenaza con devorarse a sí mismo</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/se-acaban-los-peajes-gustavo-petro-se-pronuncio-tras-anuncio-de-la-ani-sobre-medida-que-aplicara-en-una-region-del-pais/202628/</t>
+          <t>https://elpais.com/argentina/2026-05-22/el-gobierno-de-milei-amenaza-con-devorarse-a-si-mismo.html</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:20 p. m.</t>
+          <t>21/05/2026 04:28 p. m.</t>
         </is>
       </c>
       <c r="B173" s="6" t="inlineStr">
@@ -5174,24 +5130,24 @@
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D173" s="7" t="inlineStr">
         <is>
-          <t>Abelardo de la Espriella e Iván Cepeda se enfrentarían en segunda vuelta, según encuesta de Guarumo para ‘El Tiempo’</t>
+          <t>Trump da marcha atrás y anuncia el envío de 5.000 soldados adicionales de Estados Unidos a Polonia</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/abelardo-de-la-espriella-e-ivan-cepeda-se-enfrentarian-en-segunda-vuelta-segun-encuesta-de-guarumo-para-el-tiempo/202638/</t>
+          <t>https://elpais.com/internacional/2026-05-21/trump-da-marcha-atras-y-anuncia-el-envio-de-5000-soldados-adicionales-de-estados-unidos-a-polonia.html</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:20 p. m.</t>
+          <t>21/05/2026 04:26 p. m.</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -5201,24 +5157,24 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Decisión final de Conmebol con los puntos del DIM vs. Flamengo en Libertadores: tabla de posiciones</t>
+          <t>António Costa: “La Unión Europea necesita a México, el mundo necesita a México”</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/decision-final-de-conmebol-con-los-puntos-del-dim-vs-flamengo-en-libertadores-tabla-de-posiciones/202619/</t>
+          <t>https://elpais.com/mexico/economia/2026-05-21/antonio-costa-la-union-europea-necesita-a-mexico-el-mundo-necesita-a-mexico.html</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:20 p. m.</t>
+          <t>21/05/2026 04:17 p. m.</t>
         </is>
       </c>
       <c r="B175" s="6" t="inlineStr">
@@ -5228,24 +5184,24 @@
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>CNE dejó en firme candidatura de Abelardo de la Espriella tras estudiar queja por supuestas irregularidades en la recolección de firmas</t>
+          <t>Óscar Puente llama a la “colaboración inteligente” entre la izquierda en las elecciones</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/cne-dejo-en-firme-candidatura-de-abelardo-de-la-espriella-tras-estudiar-queja-por-supuestas-irregularidades-en-la-recoleccion-de-firmas/202649/</t>
+          <t>https://elpais.com/espana/2026-05-21/oscar-puente-llama-a-la-colaboracion-inteligente-entre-la-izquierda-en-las-elecciones.html</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:20 p. m.</t>
+          <t>21/05/2026 03:50 p. m.</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -5255,24 +5211,24 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Tres muertos y 44 heridos: saldo parcial del brutal choque entre comunidades indígenas en Cauca</t>
+          <t>Telefónica vende su sede histórica de Gran Vía al empresario Tomás Olivo por más de 200 millones</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/cali/articulo/tres-muertos-y-44-heridos-saldo-parcial-del-brutal-choque-entre-comunidades-indigenas-en-cauca/202626/</t>
+          <t>https://elpais.com/economia/2026-05-21/telefonica-vende-su-sede-historica-de-gran-via-a-un-empresario-murciano-por-mas-de-200-millones.html</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 03:20 p. m.</t>
+          <t>21/05/2026 03:42 p. m.</t>
         </is>
       </c>
       <c r="B177" s="6" t="inlineStr">
@@ -5282,24 +5238,24 @@
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>Vándalos atacaron la sede de Paloma Valencia y Juan Daniel Oviedo en Bogotá; dejaron mensajes alusivos a Iván Cepeda</t>
+          <t>Luis Almagro, exsecretario de la OEA, anuncia su respaldo a Paloma Valencia y critica a Abelardo de la Espriella: “Se presenta como un fiestero en Miami”</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/vandalos-atacaron-la-sede-de-paloma-valencia-y-juan-daniel-oviedo-en-bogota-dejaron-mensajes-alusivos-a-ivan-cepeda/202617/</t>
+          <t>https://elpais.com/america-colombia/2026-05-21/luis-almagro-exsecretario-de-la-oea-anuncia-su-respaldo-a-paloma-valencia-y-critica-a-abelardo-de-la-espriella-se-presenta-como-un-fiestero-en-miami.html</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 03:20 p. m.</t>
+          <t>21/05/2026 03:24 p. m.</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -5309,24 +5265,24 @@
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Gustavo Petro agitó las redes sociales por hablar de la constituyente: le pasaron factura por promesa que hizo en mármol</t>
+          <t>Puig anuncia la ruptura de las negociaciones para fusionarse con Estée Lauder</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/gustavo-petro-agito-las-redes-sociales-por-hablar-de-la-constituyente-le-pasaron-factura-por-promesa-que-hizo-en-marmol/202638/</t>
+          <t>https://elpais.com/economia/2026-05-21/puig-rompe-las-negociaciones-para-fusionarse-con-estee-lauder.html</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 12:20 p. m.</t>
+          <t>21/05/2026 03:09 p. m.</t>
         </is>
       </c>
       <c r="B179" s="6" t="inlineStr">
@@ -5336,22 +5292,26 @@
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>Lorna Cepeda habló sobre Diego Torres, su excuñado, y destapó cómo es su relación actual: “Lo recordamos”</t>
+          <t>Las figuras no justifican el sueldo en una corrida petardo</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/gente/articulo/lorna-cepeda-hablo-sobre-diego-torres-su-excunado-y-destapo-como-es-su-relacion-actual-lo-recordamos/202655/</t>
+          <t>https://elpais.com/cultura/2026-05-21/las-figuras-no-justifican-el-sueldo-en-una-corrida-petardo.html</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="3" t="inlineStr"/>
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>21/05/2026 02:43 p. m.</t>
+        </is>
+      </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5359,22 +5319,26 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Carlos Vives le hace honor a la Selección Colombia y hace importante anuncio</t>
+          <t>Detenida en Brasil una abogada con 21 millones de seguidores en redes por lavar dinero para el crimen organizado</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/cultura/articulo/carlos-vives-le-hace-honor-a-la-seleccion-colombia-y-hace-importante-anuncio/202654/</t>
+          <t>https://elpais.com/america/2026-05-21/detenida-en-brasil-una-abogada-con-21-millones-de-seguidores-en-redes-por-lavar-dinero-para-el-crimen-organizado.html</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="6" t="inlineStr"/>
+      <c r="A181" s="6" t="inlineStr">
+        <is>
+          <t>21/05/2026 02:31 p. m.</t>
+        </is>
+      </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5382,22 +5346,26 @@
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D181" s="7" t="inlineStr">
         <is>
-          <t>Si no pudo ir, así podrá vivir el Mundial 2026 en Colombia: ‘Fan Zone’, la llamativa apuesta de la FCF</t>
+          <t>La Policía detiene a tres personas como cooperadoras del crimen del cantaor Matías de Paula</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/si-no-pudo-ir-asi-podra-vivir-el-mundial-2026-en-colombia-fan-zone-la-llamativa-apuesta-de-la-fcf/202618/</t>
+          <t>https://elpais.com/espana/2026-05-21/la-policia-detiene-a-tres-personas-como-cooperadoras-del-crimen-del-cantaor-matias-de-paula.html</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="3" t="inlineStr"/>
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>21/05/2026 02:08 p. m.</t>
+        </is>
+      </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5405,22 +5373,26 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Ola de críticas contra Jhon Jáder Durán por salir con botella en mano: video hunde sueño del Mundial</t>
+          <t>Stellantis prevé elevar su facturación casi un 25% en cinco años hasta los 200.000 millones para revitalizar el negocio</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/ola-de-criticas-contra-jhon-jader-duran-por-salir-con-botella-en-mano-video-hunde-sueno-del-mundial/202655/</t>
+          <t>https://elpais.com/economia/2026-05-21/stellantis-preve-elevar-su-facturacion-casi-un-25-hasta-los-200000-millones-en-cinco-anos-para-revitalizar-el-negocio.html</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="6" t="inlineStr"/>
+      <c r="A183" s="6" t="inlineStr">
+        <is>
+          <t>21/05/2026 02:08 p. m.</t>
+        </is>
+      </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5428,22 +5400,26 @@
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D183" s="7" t="inlineStr">
         <is>
-          <t>Revolcón en Inglaterra: excluyen a capitán de los convocados al Mundial 2026 y no se calló</t>
+          <t>Renuncia el ministro de Trabajo de Bolivia, el primer cambio en el Gobierno de Paz por las protestas</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/revolcon-en-inglaterra-excluyen-a-capitan-de-los-convocados-al-mundial-y-no-se-callo/202616/</t>
+          <t>https://elpais.com/america/2026-05-21/renuncia-el-ministro-de-trabajo-de-bolivia-el-primer-cambio-en-el-gobierno-de-paz-por-las-protestas.html</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="3" t="inlineStr"/>
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>21/05/2026 12:48 p. m.</t>
+        </is>
+      </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5451,22 +5427,26 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Paloma Valencia propone regalar neveras nuevas; recuerdan cuando Daniel Quintero ofrecía lavadoras</t>
+          <t>Un juez de Madrid archiva la denuncia de Begoña Gómez contra Vito Quiles por acoso</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/paloma-valencia-propone-regalar-neveras-nuevas-recuerdan-cuando-daniel-quintero-ofrecia-lavadoras/202631/</t>
+          <t>https://elpais.com/espana/2026-05-21/un-juez-de-madrid-archiva-la-denuncia-de-begona-gomez-contra-vito-quiles-por-acoso.html</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="6" t="inlineStr"/>
+      <c r="A185" s="6" t="inlineStr">
+        <is>
+          <t>21/05/2026 12:45 p. m.</t>
+        </is>
+      </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5474,22 +5454,26 @@
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D185" s="7" t="inlineStr">
         <is>
-          <t>Iván Cepeda presentó en Bogotá un paquete de medidas sociales con las que busca ganar la Presidencia: habría salario mínimo vital para líderes sociales</t>
+          <t>El Supremo obliga a Antena 3 a dejar de emitir ‘El Rosco’ de ‘Pasapalabra’</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/ivan-cepeda-presento-en-bogota-un-paquete-de-medidas-sociales-con-las-que-busca-ganar-la-presidencia-habria-salario-minimo-vital-para-lideres-sociales/202642/</t>
+          <t>https://elpais.com/television/2026-05-21/el-supremo-obliga-a-atresmedia-a-dejar-de-emitir-el-rosco-de-pasapalabra.html</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="3" t="inlineStr"/>
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>21/05/2026 11:44 a. m.</t>
+        </is>
+      </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5497,22 +5481,26 @@
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>La Casa de la Constitución: el centro en el que se adelantará el proceso de referendo contra la constituyente de Petro</t>
+          <t>Los Javis en Cannes: “Federico García Lorca no es una idea, sino una persona a la que asesinaron por maricón”</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/la-casa-de-la-constitucion-el-centro-en-el-que-se-adelantara-el-proceso-de-referendo-contra-la-constituyente-de-petro/202646/</t>
+          <t>https://elpais.com/cultura/cine/2026-05-21/los-javis-en-cannes-federico-garcia-lorca-no-es-una-idea-sino-una-persona-a-la-que-asesinaron-por-maricon.html</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="6" t="inlineStr"/>
+      <c r="A187" s="6" t="inlineStr">
+        <is>
+          <t>21/05/2026 10:26 a. m.</t>
+        </is>
+      </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5520,22 +5508,26 @@
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D187" s="7" t="inlineStr">
         <is>
-          <t>Colombia anuncia cierre de puente internacional con Ecuador: esta es la razón de la medida</t>
+          <t>La Audiencia Nacional ordena el bloqueo de 490.780 euros de las cuentas bancarias de Zapatero</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/articulo/colombia-anuncia-cierre-de-puente-internacional-con-ecuador-esta-es-la-razon-de-la-medida/202607/</t>
+          <t>https://elpais.com/espana/2026-05-21/la-audiencia-nacional-ordena-el-bloqueo-de-cuentas-bancarias-de-zapatero.html</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="3" t="inlineStr"/>
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>21/05/2026 10:00 a. m.</t>
+        </is>
+      </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5543,22 +5535,26 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Pacífico 1: obras en punto clave de la vía avanzan en su estabilización y manejo controlado del tráfico</t>
+          <t>Las pirámides egipcias fueron construidas a prueba de terremotos</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/articulo/pacifico-1-obras-en-punto-clave-de-la-via-avanzan-en-su-estabilizacion-y-manejo-controlado-del-trafico/202623/</t>
+          <t>https://elpais.com/ciencia/2026-05-21/las-piramides-egipcias-fueron-construidas-a-prueba-de-terremotos.html</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="6" t="inlineStr"/>
+      <c r="A189" s="6" t="inlineStr">
+        <is>
+          <t>21/05/2026 09:49 a. m.</t>
+        </is>
+      </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5566,22 +5562,26 @@
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D189" s="7" t="inlineStr">
         <is>
-          <t>“Empecemos a trabajar como seres civilizados”: procurador Eljach tras enfrentamientos entre comunidades misak y nasa</t>
+          <t>Estados Unidos despliega su portaviones ‘USS Nimitz’ en el Caribe en plena campaña contra Cuba</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/articulo/empecemos-a-trabajar-como-seres-civilizados-procurador-eljach-tras-enfrentamientos-entre-comunidades-misak-y-nasa/202625/</t>
+          <t>https://elpais.com/internacional/2026-05-21/estados-unidos-despliega-su-portaviones-uss-nimitz-en-el-caribe-en-plena-campana-contra-cuba.html</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="3" t="inlineStr"/>
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>21/05/2026 07:12 a. m.</t>
+        </is>
+      </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5589,24 +5589,24 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>Cundinamarca gana premio internacional por su banco de leche humana. ¿Dónde se puede donar?</t>
+          <t>El Supremo anula el registro único de alquileres turísticos al considerar que el Estado carece de competencias para crearlo</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/articulo/cundinamarca-gana-premio-internacional-por-su-banco-de-leche-humana-donde-se-puede-donar/202649/</t>
+          <t>https://elpais.com/economia/2026-05-21/el-supremo-anula-el-registro-unico-de-alquileres-turisticos-al-considerar-que-el-estado-carece-de-competencias-para-crearlo.html</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:32 p. m.</t>
+          <t>20/05/2026 10:30 p. m.</t>
         </is>
       </c>
       <c r="B191" s="6" t="inlineStr">
@@ -5616,24 +5616,24 @@
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D191" s="7" t="inlineStr">
         <is>
-          <t>Yulixa Toloza iba muerta en el carro cuando la dueña de la estética usó su celular para engañar a la amiga</t>
+          <t>Siete carreras con un buen sueldo y una nota de acceso asequible</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/yulixa-toloza-iba-muerta-en-el-carro-cuando-la-duena-de-la-estetica-uso-su-celular-para-enganar-a-la-amiga-1023496</t>
+          <t>https://elpais.com/educacion/2026-05-21/siete-carreras-con-un-buen-sueldo-y-una-nota-de-acceso-asequible.html</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:29 p. m.</t>
+          <t>20/05/2026 10:30 p. m.</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -5643,24 +5643,24 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>Juez adelanta audiencia en caso del asesinato de Jaime Esteban Moreno ante alerta por vencimiento de términos</t>
+          <t>El sendero en el que murió Isak Andic: un camino “sin riesgo” con un solo punto donde caer al vacío</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/juez-adelanta-audiencia-en-caso-del-asesinato-de-jaime-esteban-moreno-1023493</t>
+          <t>https://elpais.com/espana/catalunya/2026-05-21/el-sendero-en-el-que-murio-isak-andic-un-camino-sin-riesgo-con-un-solo-punto-donde-caer-al-vacio.html</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:22 p. m.</t>
+          <t>21/05/2026 07:00 p. m.</t>
         </is>
       </c>
       <c r="B193" s="6" t="inlineStr">
@@ -5670,24 +5670,24 @@
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D193" s="7" t="inlineStr">
         <is>
-          <t>El conmovedor video de Yulixa Toloza que compartió su familia: así quieren recordarla</t>
+          <t>¿Aumento de precios? Fenavi advierte que bloqueos en vía a Buenaventura impactarían abastecimiento de pollo y huevo</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/asi-era-yulixa-toloza-en-vida-familia-compartio-video-1023482</t>
+          <t>https://cambiocolombia.com/pais/articulo/2026/5/aumento-de-precios-fenavi-advierte-que-bloqueos-en-via-a-buenaventura-impactarian-abastecimiento-de-pollo-y-huevo</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:58 p. m.</t>
+          <t>21/05/2026 06:00 p. m.</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -5697,24 +5697,24 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Presidente Gustavo Petro se reunirá con el papa León XIV en el Vaticano</t>
+          <t>Así es el USS Nimitz, el portaviones que Estados Unidos desplegó en el Caribe frente a Cuba</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/presidente-gustavo-petro-se-reunira-con-el-papa-leon-xiv-en-el-vaticano-1023462</t>
+          <t>https://cambiocolombia.com/internacional/articulo/2026/5/asi-es-el-uss-nimitz-el-portaviones-que-estados-unidos-desplego-en-el-caribe-frente-a-cuba</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:36 p. m.</t>
+          <t>21/05/2026 06:00 p. m.</t>
         </is>
       </c>
       <c r="B195" s="6" t="inlineStr">
@@ -5724,24 +5724,24 @@
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D195" s="7" t="inlineStr">
         <is>
-          <t>Líder social Yanet Mosquera sufrió atentado en la vía Panamericana</t>
+          <t>“Mis excompañeros me trataban de traidora”: alias Karina, explica por qué no fue a la JEP</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/lider-social-yanet-mosquera-sufrio-atentado-en-la-via-panamericana-1023476</t>
+          <t>https://cambiocolombia.com/conflicto-armado-en-colombia/articulo/2026/5/mis-excompaneros-me-trataban-de-traidora-alias-karina-explica-por-que-no-fue-a-la-jep</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:12 p. m.</t>
+          <t>21/05/2026 04:45 p. m.</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -5751,24 +5751,24 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>Avanzan los cierres y sellamientos de centros estéticos en Bogotá tras el caso Yulixa Toloza</t>
+          <t>Disputa territorial entre comunidades indígenas deja tres muertos y varios heridos en Cauca</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/avanzan-los-cierres-y-sellamientos-de-centros-esteticos-en-bogota-tras-el-caso-yulixa-toloza-1023460</t>
+          <t>https://cambiocolombia.com/pais/articulo/2026/5/disputa-territorial-entre-comunidades-indigenas-deja-tres-muertos-y-varios-heridos-en-cauca</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:38 p. m.</t>
+          <t>21/05/2026 04:30 p. m.</t>
         </is>
       </c>
       <c r="B197" s="6" t="inlineStr">
@@ -5778,24 +5778,24 @@
       </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D197" s="7" t="inlineStr">
         <is>
-          <t>Cambian al procurador que pidió libertad para dos de los capturados por el caso de Yulixa Toloza</t>
+          <t>Defensoría alerta por crisis humanitaria en cárceles y centros de detención del país</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/cambian-al-procurador-que-pidio-libertad-para-dos-de-los-capturados-por-el-caso-de-yulixa-toloza-1023468</t>
+          <t>https://cambiocolombia.com/pais/articulo/2026/5/defensoria-alerta-por-crisis-humanitaria-en-carceles-y-centros-de-detencion-del-pais</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:09 p. m.</t>
+          <t>21/05/2026 04:00 p. m.</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -5805,24 +5805,24 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>El Dorado renovó su servicio gratuito de buses entre terminales con vehículos eléctricos</t>
+          <t>¿Por qué los transportadores de servicio público están protestando en Cali?: alcalde Eder dice que no cederá a bloqueos</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/el-dorado-estrena-buses-electricos-gratuitos-1023433</t>
+          <t>https://cambiocolombia.com/pais/articulo/2026/5/por-que-los-transportadores-de-servicio-publico-estan-protestando-en-cali-alcalde-eder-dice-que-no-cedera-a-bloqueos</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 03:19 p. m.</t>
+          <t>21/05/2026 03:20 p. m.</t>
         </is>
       </c>
       <c r="B199" s="6" t="inlineStr">
@@ -5832,24 +5832,24 @@
       </c>
       <c r="C199" s="6" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D199" s="7" t="inlineStr">
         <is>
-          <t>VIDEO | Encapuchados vandalizaron sede de campaña de Paloma Valencia en la carrera Séptima, en Bogotá</t>
+          <t>Alcaldía de Kennedy sella cinco centros estéticos por no cumplir con los requisitos</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/encapuchados-vandalizaron-sede-de-campana-de-paloma-valencia-en-la-carrera-septima-en-bogota-1023436</t>
+          <t>https://cambiocolombia.com/pais/articulo/2026/5/alcaldia-de-kennedy-sella-cinco-centros-esteticos-por-no-cumplir-con-los-requisitos</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 03:16 p. m.</t>
+          <t>21/05/2026 03:20 p. m.</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -5859,24 +5859,24 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>Dictamen de Medicina Legal reveló la causa de muerte de Yulixa Toloza: la dejaron morir en la estética</t>
+          <t>¿Habrá racionamiento de agua en Bogotá por la llegada del Fenómeno del Niño?</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/de-que-murio-yulixa-toloza-en-la-estetica-dictamen-de-medicina-legal-1023435</t>
+          <t>https://cambiocolombia.com/pais/articulo/2026/5/habra-racionamiento-de-agua-en-bogota-por-la-llegada-del-fenomeno-del-nino</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:20 p. m.</t>
+          <t>21/05/2026 01:30 p. m.</t>
         </is>
       </c>
       <c r="B201" s="6" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="C201" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D201" s="7" t="inlineStr">
         <is>
-          <t>Mujer reportada como desaparecida fue hallada muerta en el río Magdalena</t>
+          <t>Por título de Julián Bedoya, piden a la Corte confirmar condena contra exfuncionarios de la Universidad de Medellín</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/judicial/2026/05/21/mujer-reportada-como-desaparecida-fue-hallada-muerta-en-el-rio-magdalena/</t>
+          <t>https://cambiocolombia.com/poder/articulo/2026/5/por-titulo-de-julian-bedoya-piden-a-la-corte-confirmar-condena-contra-exfuncionarios-de-la-universidad-de-medellin</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:20 p. m.</t>
+          <t>21/05/2026 12:22 p. m.</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -5913,24 +5913,24 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>Judicial</t>
+          <t>¿Atlas Intel podrá divulgar encuestas en la recta final de la campaña electoral?</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/judicial/</t>
+          <t>https://cambiocolombia.com/elecciones-colombia-2026/articulo/2026/5/atlas-intel-podra-divulgar-encuestas-en-la-recta-final-de-la-campana-electoral</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:14 p. m.</t>
+          <t>21/05/2026 10:42 a. m.</t>
         </is>
       </c>
       <c r="B203" s="6" t="inlineStr">
@@ -5940,24 +5940,24 @@
       </c>
       <c r="C203" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D203" s="7" t="inlineStr">
         <is>
-          <t>Horóscopo del viernes 22 de mayo de 2026: Predicciones y el vuelo de las ideas</t>
+          <t>Cae red que expedía documentos colombianos falsos a extranjeros para enviarlos a Estados Unidos</t>
         </is>
       </c>
       <c r="E203" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/entretenimiento/tendencias/2026/05/21/horoscopo-del-viernes-22-de-mayo-de-2026-predicciones-y-el-vuelo-de-las-ideas/</t>
+          <t>https://cambiocolombia.com/pais/articulo/2026/5/cae-red-que-expedia-documentos-colombianos-falsos-a-extranjeros-para-enviarlos-a-estados-unidos</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:14 p. m.</t>
+          <t>21/05/2026 06:00 a. m.</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -5967,24 +5967,24 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>Tendencias</t>
+          <t>Percepción positiva sobre la minería aumentó en el último año según estudio Brújula Minera</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/entretenimiento/tendencias/</t>
+          <t>https://cambiocolombia.com/economia/articulo/2026/5/percepcion-positiva-sobre-la-mineria-aumento-en-el-ultimo-ano-segun-estudio-brujula-minera</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:14 p. m.</t>
+          <t>20/05/2026 07:30 p. m.</t>
         </is>
       </c>
       <c r="B205" s="6" t="inlineStr">
@@ -5994,24 +5994,24 @@
       </c>
       <c r="C205" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D205" s="7" t="inlineStr">
         <is>
-          <t>Esta es la campaña de Vanguardia contra el abstencionismo en las elecciones a la presidencia 2026</t>
+          <t>Consejo de Estado frena beneficio a siete cabecillas de bandas de Medellín que negocian con el Gobierno</t>
         </is>
       </c>
       <c r="E205" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/politica/2026/05/21/esta-es-la-campana-de-vanguardia-contra-el-abstencionismo-en-las-elecciones-a-la-presidencia-2026/</t>
+          <t>https://cambiocolombia.com/justicia/articulo/2026/5/consejo-de-estado-frena-beneficio-a-siete-cabecillas-de-bandas-de-medellin-que-negocian-con-el-gobierno</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:14 p. m.</t>
+          <t>20/05/2026 05:32 p. m.</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -6021,24 +6021,24 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>Política</t>
+          <t>El obstáculo que enfrenta Colombia para juzgar a los capturados por el caso de Yulixa Toloza</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/politica/</t>
+          <t>https://cambiocolombia.com/pais/articulo/2026/5/el-obstaculo-que-enfrenta-colombia-para-juzgar-a-los-capturados-por-el-caso-de-yulixa-toloza</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:13 p. m.</t>
+          <t>20/05/2026 05:30 p. m.</t>
         </is>
       </c>
       <c r="B207" s="6" t="inlineStr">
@@ -6048,24 +6048,24 @@
       </c>
       <c r="C207" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D207" s="7" t="inlineStr">
         <is>
-          <t>Homicidio, herencia y un pacto roto: El escándalo que sacude al imperio Mango</t>
+          <t>Olmedo López admite ante una jueza su responsabilidad en el robo a la UNGRD</t>
         </is>
       </c>
       <c r="E207" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/mundo/2026/05/21/homicidio-herencia-y-un-pacto-roto-el-escandalo-que-sacude-al-imperio-mango/</t>
+          <t>https://cambiocolombia.com/pais/articulo/2026/5/olmedo-lopez-admite-ante-una-jueza-su-responsabilidad-en-el-robo-a-la-ungrd</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:20 p. m.</t>
+          <t>20/05/2026 03:30 p. m.</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -6075,24 +6075,24 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>En fotos: así quedó la sede de Paloma Valencia tras ataque vandálico en Bogotá</t>
+          <t>Ataque con drones por parte de estructuras ilegales dejan un soldado muerto y otros cuatro uniformados heridos en el  sur de Bolívar</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/21/en-fotos-asi-quedo-la-sede-de-paloma-valencia-tras-ataque-vandalico-en-bogota/</t>
+          <t>https://cambiocolombia.com/ataque-drones-estructuras-ilegales-sur-bolivar</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:20 p. m.</t>
+          <t>21/05/2026 05:24 p. m.</t>
         </is>
       </c>
       <c r="B209" s="6" t="inlineStr">
@@ -6102,24 +6102,24 @@
       </c>
       <c r="C209" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D209" s="7" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>La Barra Incondicional: El sello de Carlos Vives y la FCF crean los nuevos cánticos para alentar a la Selección Colombia</t>
         </is>
       </c>
       <c r="E209" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/</t>
+          <t>https://canaltrece.com.co/noticias/la-barra-incondicional-el-sello-de-carlos-vives-y-la-fcf-crean-los-nuevos-canticos-para-alentar-a-la-seleccion-colombia/</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:50 p. m.</t>
+          <t>21/05/2026 05:17 p. m.</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -6129,24 +6129,24 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>Enfermería en Colombia: ¿Por qué hay déficit crítico de profesionales y cómo enfrentarlo?</t>
+          <t>Sebastián González presenta “Cómo Pudiste”: La nueva voz de la música popular colombiana</t>
         </is>
       </c>
       <c r="E210" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/entretenimiento/salud/2026/05/21/enfermeria-en-colombia-por-que-hay-deficit-critico-de-profesionales-y-como-enfrentarlo/</t>
+          <t>https://canaltrece.com.co/noticias/sebastian-gonzalez-presenta-como-pudiste-la-nueva-voz-de-la-musica-popular-colombiana/</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:15 p. m.</t>
+          <t>21/05/2026 05:11 p. m.</t>
         </is>
       </c>
       <c r="B211" s="6" t="inlineStr">
@@ -6156,24 +6156,24 @@
       </c>
       <c r="C211" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D211" s="7" t="inlineStr">
         <is>
-          <t>Brutal enfrentamiento entre indígenas terminó en tragedia: tres muertos y varios heridos</t>
+          <t>Andariega: El documental que retrata la vida de las recolectoras de café itinerantes llega a salas de cine</t>
         </is>
       </c>
       <c r="E211" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/21/brutal-enfrentamiento-entre-indigenas-termino-en-tragedia-tres-muertos-y-varios-heridos/</t>
+          <t>https://canaltrece.com.co/noticias/andariega-el-documental-que-retrata-la-vida-de-las-recolectoras-de-cafe-itinerantes-llega-a-salas-de-cine/</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 03:20 p. m.</t>
+          <t>21/05/2026 05:07 p. m.</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -6183,24 +6183,24 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>Caso Yulixa Toloza: revelan qué provocó realmente su muerte tras cirugía en Beauty Láser</t>
+          <t>Bogotá se convierte en la capital parrillera de Latinoamérica con «El Papá de los Asados»</t>
         </is>
       </c>
       <c r="E212" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/21/caso-yulixa-toloza-revelan-que-provoco-realmente-su-muerte-tras-cirugia-en-beauty-lase/</t>
+          <t>https://canaltrece.com.co/noticias/bogota-se-convierte-en-la-capital-parrillera-de-latinoamerica-con-el-papa-de-los-asados/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 02:25 p. m.</t>
+          <t>21/05/2026 04:59 p. m.</t>
         </is>
       </c>
       <c r="B213" s="6" t="inlineStr">
@@ -6210,24 +6210,24 @@
       </c>
       <c r="C213" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D213" s="7" t="inlineStr">
         <is>
-          <t>Corte Constitucional: no pagar alimentos puede ser violencia económica en Colombia</t>
+          <t>Fumaratto celebra 10 años de carrera y anuncia su desembarco en Europa con ‘Énfasis Tour’</t>
         </is>
       </c>
       <c r="E213" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/21/corte-constitucional-no-pagar-alimentos-puede-ser-violencia-economica-en-colombia/</t>
+          <t>https://canaltrece.com.co/noticias/fumaratto-celebra-10-anos-de-carrera-y-anuncia-su-desembarco-en-europa-con-enfasis-tour/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 02:22 p. m.</t>
+          <t>21/05/2026 04:44 p. m.</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -6237,24 +6237,24 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>Anulación de fotomultas en Colombia: pasos para recuperar su dinero si ya pagó</t>
+          <t>Smart Fit Run 2026: La cadena de gimnasios más grande de Latinoamérica debuta en las calles de Bogotá</t>
         </is>
       </c>
       <c r="E214" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/20/fotomultas-anuladas-paso-a-paso-para-saber-si-le-devuelven-su-dinero/</t>
+          <t>https://canaltrece.com.co/noticias/smart-fit-run-2026-la-cadena-de-gimnasios-mas-grande-de-latinoamerica-debuta-en-las-calles-de-bogota/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 12:57 p. m.</t>
+          <t>21/05/2026 04:20 p. m.</t>
         </is>
       </c>
       <c r="B215" s="6" t="inlineStr">
@@ -6264,24 +6264,24 @@
       </c>
       <c r="C215" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D215" s="7" t="inlineStr">
         <is>
-          <t>Antioquia cierra 64 centros estéticos por irregularidades tras controles sanitarios</t>
+          <t>El arte de saber cuándo callar: La hiperpersonalización real que exigen los usuarios en 2026</t>
         </is>
       </c>
       <c r="E215" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/21/antioquia-cierra-64-centros-esteticos-por-irregularidades-tras-controles-sanitarios/</t>
+          <t>https://canaltrece.com.co/noticias/el-arte-de-saber-cuando-callar-la-hiperpersonalizacion-real-que-exigen-los-usuarios-en-2026/</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 12:34 p. m.</t>
+          <t>21/05/2026 04:10 p. m.</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -6291,24 +6291,24 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t>La champeta será Patrimonio Cultural Inmaterial de Colombia: reconocimiento a este ritmo del Caribe</t>
+          <t>Convocatoria abierta: Ofrecen 300 becas gratuitas de empleo para jóvenes en Bogotá y Cundinamarca</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/21/la-champeta-sera-patrimonio-cultural-inmaterial-de-colombia-reconocimiento-a-este-ritmo-del-caribe/</t>
+          <t>https://canaltrece.com.co/noticias/convocatoria-abierta-ofrecen-300-becas-gratuitas-de-empleo-para-jovenes-en-bogota-y-cundinamarca/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 11:57 a. m.</t>
+          <t>21/05/2026 01:43 p. m.</t>
         </is>
       </c>
       <c r="B217" s="6" t="inlineStr">
@@ -6318,24 +6318,24 @@
       </c>
       <c r="C217" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D217" s="7" t="inlineStr">
         <is>
-          <t>Caso Yulixa Toloza: capturados en Venezuela no serían extraditados a Colombia</t>
+          <t>VASSAR Festival de Creadores llega al Parque El Country en Bogotá</t>
         </is>
       </c>
       <c r="E217" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/21/caso-yulixa-toloza-capturados-en-venezuela-no-serian-extraditados-a-colombia/</t>
+          <t>https://canaltrece.com.co/noticias/vassar-festival-de-creadores-bogota-2026/</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 11:51 a. m.</t>
+          <t>21/05/2026 01:37 p. m.</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -6345,24 +6345,24 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>Caso Juan Esteban Moreno: capturados por crimen quedarían libres por vencimiento de términos</t>
+          <t>Danibet Colombia Mundial 2026 analizará a la Selección partido a partido</t>
         </is>
       </c>
       <c r="E218" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/21/caso-juan-esteban-moreno-capturados-por-crimen-quedarian-libres-por-vencimiento-de-terminos/</t>
+          <t>https://canaltrece.com.co/noticias/danibet-colombia-mundial-2026-analisis-seleccion/</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:24 p. m.</t>
+          <t>21/05/2026 01:32 p. m.</t>
         </is>
       </c>
       <c r="B219" s="6" t="inlineStr">
@@ -6377,19 +6377,19 @@
       </c>
       <c r="D219" s="7" t="inlineStr">
         <is>
-          <t>La Barra Incondicional: El sello de Carlos Vives y la FCF crean los nuevos cánticos para alentar a la Selección Colombia</t>
+          <t>Expopet 2026 llega a Corferias para las familias interespecie</t>
         </is>
       </c>
       <c r="E219" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/la-barra-incondicional-el-sello-de-carlos-vives-y-la-fcf-crean-los-nuevos-canticos-para-alentar-a-la-seleccion-colombia/</t>
+          <t>https://canaltrece.com.co/noticias/expopet-2026-llega-a-corferias-para-las-familias-interespecie/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:17 p. m.</t>
+          <t>21/05/2026 01:23 p. m.</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -6404,19 +6404,19 @@
       </c>
       <c r="D220" s="4" t="inlineStr">
         <is>
-          <t>Sebastián González presenta “Cómo Pudiste”: La nueva voz de la música popular colombiana</t>
+          <t>Mangle Sonoro Comadrita llega a Bogotá con agenda de conciertos</t>
         </is>
       </c>
       <c r="E220" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/sebastian-gonzalez-presenta-como-pudiste-la-nueva-voz-de-la-musica-popular-colombiana/</t>
+          <t>https://canaltrece.com.co/noticias/mangle-sonoro-comadrita-agenda-bogota/</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:11 p. m.</t>
+          <t>21/05/2026 01:05 p. m.</t>
         </is>
       </c>
       <c r="B221" s="6" t="inlineStr">
@@ -6431,19 +6431,19 @@
       </c>
       <c r="D221" s="7" t="inlineStr">
         <is>
-          <t>Andariega: El documental que retrata la vida de las recolectoras de café itinerantes llega a salas de cine</t>
+          <t>Conecta el País de la Belleza es la serie que Colombia necesitaba</t>
         </is>
       </c>
       <c r="E221" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/andariega-el-documental-que-retrata-la-vida-de-las-recolectoras-de-cafe-itinerantes-llega-a-salas-de-cine/</t>
+          <t>https://canaltrece.com.co/regiones/conecta-el-pais-de-la-belleza-serie-canal-trece/</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:07 p. m.</t>
+          <t>20/05/2026 10:47 p. m.</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -6458,19 +6458,19 @@
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t>Bogotá se convierte en la capital parrillera de Latinoamérica con «El Papá de los Asados»</t>
+          <t>Cuarteto de Nos Colombia 2026 confirma conciertos en Cali, Medellín y Bogotá</t>
         </is>
       </c>
       <c r="E222" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/bogota-se-convierte-en-la-capital-parrillera-de-latinoamerica-con-el-papa-de-los-asados/</t>
+          <t>https://canaltrece.com.co/noticias/cuarteto-de-nos-colombia-2026-tour-puertas/</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:59 p. m.</t>
+          <t>20/05/2026 10:42 p. m.</t>
         </is>
       </c>
       <c r="B223" s="6" t="inlineStr">
@@ -6485,19 +6485,19 @@
       </c>
       <c r="D223" s="7" t="inlineStr">
         <is>
-          <t>Fumaratto celebra 10 años de carrera y anuncia su desembarco en Europa con ‘Énfasis Tour’</t>
+          <t>Morat Ya Es Mañana World Tour 2027 anuncia fechas en Estados Unidos y Canadá</t>
         </is>
       </c>
       <c r="E223" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/fumaratto-celebra-10-anos-de-carrera-y-anuncia-su-desembarco-en-europa-con-enfasis-tour/</t>
+          <t>https://canaltrece.com.co/noticias/morat-ya-es-manana-world-tour-2027-anuncia-fechas-en-estados-unidos-y-canada/</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:44 p. m.</t>
+          <t>20/05/2026 10:36 p. m.</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -6512,19 +6512,19 @@
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>Smart Fit Run 2026: La cadena de gimnasios más grande de Latinoamérica debuta en las calles de Bogotá</t>
+          <t>Monsieur Periné Instrucciones Para Ser Feliz Tour llega a Bogotá</t>
         </is>
       </c>
       <c r="E224" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/smart-fit-run-2026-la-cadena-de-gimnasios-mas-grande-de-latinoamerica-debuta-en-las-calles-de-bogota/</t>
+          <t>https://canaltrece.com.co/noticias/monsieur-perine-instrucciones-para-ser-feliz-tour-bogota/</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:20 p. m.</t>
+          <t>20/05/2026 10:31 p. m.</t>
         </is>
       </c>
       <c r="B225" s="6" t="inlineStr">
@@ -6539,19 +6539,19 @@
       </c>
       <c r="D225" s="7" t="inlineStr">
         <is>
-          <t>El arte de saber cuándo callar: La hiperpersonalización real que exigen los usuarios en 2026</t>
+          <t>Mari La Carajita y Manira estrenan Pida la bendición</t>
         </is>
       </c>
       <c r="E225" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/el-arte-de-saber-cuando-callar-la-hiperpersonalizacion-real-que-exigen-los-usuarios-en-2026/</t>
+          <t>https://canaltrece.com.co/noticias/mari-la-carajita-y-manira-pida-la-bendicion/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:10 p. m.</t>
+          <t>20/05/2026 10:26 p. m.</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -6566,19 +6566,19 @@
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t>Convocatoria abierta: Ofrecen 300 becas gratuitas de empleo para jóvenes en Bogotá y Cundinamarca</t>
+          <t>Gran Tomatina Colombiana 2026 llega a Sutamarchán con ambiente mundialista</t>
         </is>
       </c>
       <c r="E226" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/convocatoria-abierta-ofrecen-300-becas-gratuitas-de-empleo-para-jovenes-en-bogota-y-cundinamarca/</t>
+          <t>https://canaltrece.com.co/regiones/gran-tomatina-colombiana-2026-sutamarchan/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 01:43 p. m.</t>
+          <t>20/05/2026 10:16 a. m.</t>
         </is>
       </c>
       <c r="B227" s="6" t="inlineStr">
@@ -6593,19 +6593,19 @@
       </c>
       <c r="D227" s="7" t="inlineStr">
         <is>
-          <t>VASSAR Festival de Creadores llega al Parque El Country en Bogotá</t>
+          <t>Día Mundial de las Abejas 2026: «Juntos por las personas y el planeta» para proteger a nuestros polinizadores</t>
         </is>
       </c>
       <c r="E227" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/vassar-festival-de-creadores-bogota-2026/</t>
+          <t>https://canaltrece.com.co/noticias/dia-mundial-de-las-abejas-2026-juntos-por-las-personas-y-el-planeta-para-proteger-a-nuestros-polinizadores/</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 01:37 p. m.</t>
+          <t>20/05/2026 10:10 a. m.</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -6620,19 +6620,19 @@
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t>Danibet Colombia Mundial 2026 analizará a la Selección partido a partido</t>
+          <t>Festivales y grandes conciertos en Colombia: La agenda imperdible para el segundo semestre de 2026</t>
         </is>
       </c>
       <c r="E228" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/danibet-colombia-mundial-2026-analisis-seleccion/</t>
+          <t>https://canaltrece.com.co/noticias/festivales-y-grandes-conciertos-en-colombia-la-agenda-imperdible-para-el-segundo-semestre-de-2026/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 01:32 p. m.</t>
+          <t>20/05/2026 09:59 a. m.</t>
         </is>
       </c>
       <c r="B229" s="6" t="inlineStr">
@@ -6647,19 +6647,19 @@
       </c>
       <c r="D229" s="7" t="inlineStr">
         <is>
-          <t>Expopet 2026 llega a Corferias para las familias interespecie</t>
+          <t>Elecciones Presidenciales 2026: Guía de votación para colombianos en América Latina</t>
         </is>
       </c>
       <c r="E229" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/expopet-2026-llega-a-corferias-para-las-familias-interespecie/</t>
+          <t>https://canaltrece.com.co/noticias/elecciones-presidenciales-2026-guia-de-votacion-para-colombianos-en-america-latina/</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 01:23 p. m.</t>
+          <t>20/05/2026 09:53 a. m.</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -6674,19 +6674,19 @@
       </c>
       <c r="D230" s="4" t="inlineStr">
         <is>
-          <t>Mangle Sonoro Comadrita llega a Bogotá con agenda de conciertos</t>
+          <t>Elecciones Presidenciales 2026: Así se votará desde España del 25 al 31 de mayo</t>
         </is>
       </c>
       <c r="E230" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/mangle-sonoro-comadrita-agenda-bogota/</t>
+          <t>https://canaltrece.com.co/noticias/elecciones-presidenciales-2026-asi-se-votara-desde-espana-del-25-al-31-de-mayo/</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 01:05 p. m.</t>
+          <t>20/05/2026 09:47 a. m.</t>
         </is>
       </c>
       <c r="B231" s="6" t="inlineStr">
@@ -6701,19 +6701,19 @@
       </c>
       <c r="D231" s="7" t="inlineStr">
         <is>
-          <t>Conecta el País de la Belleza es la serie que Colombia necesitaba</t>
+          <t>Colombianos en Estados Unidos: Así se votará en las elecciones presidenciales de 2026</t>
         </is>
       </c>
       <c r="E231" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/regiones/conecta-el-pais-de-la-belleza-serie-canal-trece/</t>
+          <t>https://canaltrece.com.co/noticias/colombianos-en-estados-unidos-asi-se-votara-en-las-elecciones-presidenciales-de-2026/</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>20/05/2026 10:47 p. m.</t>
+          <t>20/05/2026 09:39 a. m.</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -6728,19 +6728,19 @@
       </c>
       <c r="D232" s="4" t="inlineStr">
         <is>
-          <t>Cuarteto de Nos Colombia 2026 confirma conciertos en Cali, Medellín y Bogotá</t>
+          <t>Elecciones Presidenciales en Colombia: Paso a paso para consultar su puesto de votación este 31 de mayo</t>
         </is>
       </c>
       <c r="E232" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/cuarteto-de-nos-colombia-2026-tour-puertas/</t>
+          <t>https://canaltrece.com.co/noticias/elecciones-presidenciales-en-colombia-paso-a-paso-para-consultar-su-puesto-de-votacion-este-31-de-mayo/</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
         <is>
-          <t>20/05/2026 10:42 p. m.</t>
+          <t>20/05/2026 09:33 a. m.</t>
         </is>
       </c>
       <c r="B233" s="6" t="inlineStr">
@@ -6755,19 +6755,19 @@
       </c>
       <c r="D233" s="7" t="inlineStr">
         <is>
-          <t>Morat Ya Es Mañana World Tour 2027 anuncia fechas en Estados Unidos y Canadá</t>
+          <t>El dolor de una madre: La historia de Yulitza Toloza y el último adiós desde Arauca</t>
         </is>
       </c>
       <c r="E233" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/morat-ya-es-manana-world-tour-2027-anuncia-fechas-en-estados-unidos-y-canada/</t>
+          <t>https://canaltrece.com.co/noticias/el-dolor-de-una-madre-la-historia-de-yulitza-toloza-y-el-ultimo-adios-desde-arauca/</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>20/05/2026 10:36 p. m.</t>
+          <t>20/05/2026 09:13 a. m.</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -6782,19 +6782,19 @@
       </c>
       <c r="D234" s="4" t="inlineStr">
         <is>
-          <t>Monsieur Periné Instrucciones Para Ser Feliz Tour llega a Bogotá</t>
+          <t>Orgullo del Valle: Gerónimo Mayac, el niño prodigio de 12 años que busca apoyo para representar a Colombia en el mundial de matemáticas en Singapur</t>
         </is>
       </c>
       <c r="E234" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/monsieur-perine-instrucciones-para-ser-feliz-tour-bogota/</t>
+          <t>https://canaltrece.com.co/noticias/orgullo-del-valle-geronimo-mayac-el-nino-prodigio-de-12-anos-que-busca-apoyo-para-representar-a-colombia-en-el-mundial-de-matematicas-en-singapur/</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="6" t="inlineStr">
         <is>
-          <t>20/05/2026 10:31 p. m.</t>
+          <t>19/05/2026 07:02 p. m.</t>
         </is>
       </c>
       <c r="B235" s="6" t="inlineStr">
@@ -6809,19 +6809,19 @@
       </c>
       <c r="D235" s="7" t="inlineStr">
         <is>
-          <t>Mari La Carajita y Manira estrenan Pida la bendición</t>
+          <t>Portugal Colombia Mundial 2026 mueve redes por comentario de Roberto Martínez</t>
         </is>
       </c>
       <c r="E235" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/mari-la-carajita-y-manira-pida-la-bendicion/</t>
+          <t>https://canaltrece.com.co/noticias/portugal-colombia-mundial-2026-roberto-martinez/</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>20/05/2026 10:26 p. m.</t>
+          <t>19/05/2026 06:52 p. m.</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -6836,19 +6836,19 @@
       </c>
       <c r="D236" s="4" t="inlineStr">
         <is>
-          <t>Gran Tomatina Colombiana 2026 llega a Sutamarchán con ambiente mundialista</t>
+          <t>Romeo Santos Prince Royce Bogotá confirma concierto en 2026</t>
         </is>
       </c>
       <c r="E236" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/regiones/gran-tomatina-colombiana-2026-sutamarchan/</t>
+          <t>https://canaltrece.com.co/noticias/romeo-santos-prince-royce-bogota-2026/</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="6" t="inlineStr">
         <is>
-          <t>20/05/2026 10:16 a. m.</t>
+          <t>19/05/2026 06:47 p. m.</t>
         </is>
       </c>
       <c r="B237" s="6" t="inlineStr">
@@ -6863,19 +6863,19 @@
       </c>
       <c r="D237" s="7" t="inlineStr">
         <is>
-          <t>Día Mundial de las Abejas 2026: «Juntos por las personas y el planeta» para proteger a nuestros polinizadores</t>
+          <t>Shakira Dai Dai Mundial 2026 une música, fútbol y educación</t>
         </is>
       </c>
       <c r="E237" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/dia-mundial-de-las-abejas-2026-juntos-por-las-personas-y-el-planeta-para-proteger-a-nuestros-polinizadores/</t>
+          <t>https://canaltrece.com.co/noticias/shakira-dai-dai-mundial-2026-educacion/</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>20/05/2026 10:10 a. m.</t>
+          <t>19/05/2026 06:38 p. m.</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -6890,289 +6890,289 @@
       </c>
       <c r="D238" s="4" t="inlineStr">
         <is>
-          <t>Festivales y grandes conciertos en Colombia: La agenda imperdible para el segundo semestre de 2026</t>
+          <t>Baum Festival 2026 prende Bogotá con dos días de electrónica</t>
         </is>
       </c>
       <c r="E238" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/festivales-y-grandes-conciertos-en-colombia-la-agenda-imperdible-para-el-segundo-semestre-de-2026/</t>
+          <t>https://canaltrece.com.co/noticias/baum-festival-2026-bogota-corferias/</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="6" t="inlineStr">
-        <is>
-          <t>20/05/2026 09:59 a. m.</t>
-        </is>
-      </c>
-      <c r="B239" s="6" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C239" s="6" t="inlineStr">
-        <is>
-          <t>Canal Trece</t>
-        </is>
-      </c>
-      <c r="D239" s="7" t="inlineStr">
-        <is>
-          <t>Elecciones Presidenciales 2026: Guía de votación para colombianos en América Latina</t>
-        </is>
-      </c>
-      <c r="E239" s="8" t="inlineStr">
-        <is>
-          <t>https://canaltrece.com.co/noticias/elecciones-presidenciales-2026-guia-de-votacion-para-colombianos-en-america-latina/</t>
+      <c r="A239" s="9" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B239" s="9" t="inlineStr">
+        <is>
+          <t>Entidad Oficial</t>
+        </is>
+      </c>
+      <c r="C239" s="9" t="inlineStr">
+        <is>
+          <t>Ministerio de Minas y Energía</t>
+        </is>
+      </c>
+      <c r="D239" s="10" t="inlineStr">
+        <is>
+          <t>Gobierno expide nueva resolución que acelera la entrada de proyectos de energía limpia y fortalece la confiabilidad eléctrica del país</t>
+        </is>
+      </c>
+      <c r="E239" s="11" t="inlineStr">
+        <is>
+          <t>https://www.minenergia.gov.co/es/sala-de-prensa/noticias-index/gobierno-expide-nueva-resolucion-que-acelera-la-entrada-de-proyectos-de-energia-limpia-y-fortalece-la-confiabilidad-electrica-del-pais/</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="3" t="inlineStr">
-        <is>
-          <t>20/05/2026 09:53 a. m.</t>
-        </is>
-      </c>
-      <c r="B240" s="3" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C240" s="3" t="inlineStr">
-        <is>
-          <t>Canal Trece</t>
-        </is>
-      </c>
-      <c r="D240" s="4" t="inlineStr">
-        <is>
-          <t>Elecciones Presidenciales 2026: Así se votará desde España del 25 al 31 de mayo</t>
-        </is>
-      </c>
-      <c r="E240" s="5" t="inlineStr">
-        <is>
-          <t>https://canaltrece.com.co/noticias/elecciones-presidenciales-2026-asi-se-votara-desde-espana-del-25-al-31-de-mayo/</t>
+      <c r="A240" s="12" t="inlineStr">
+        <is>
+          <t>21/05/2026 12:00 p. m.</t>
+        </is>
+      </c>
+      <c r="B240" s="12" t="inlineStr">
+        <is>
+          <t>Entidad Oficial</t>
+        </is>
+      </c>
+      <c r="C240" s="12" t="inlineStr">
+        <is>
+          <t>Ministerio de Relaciones Exteriores (Cancillería)</t>
+        </is>
+      </c>
+      <c r="D240" s="13" t="inlineStr">
+        <is>
+          <t>La Academia Diplomática Augusto Ramírez Ocampo publica el listado definitivo de Admitidos a presentar Pruebas Escritas Fase I del Concurso de Ingreso a la Carrera Diplomática y Consular 2028</t>
+        </is>
+      </c>
+      <c r="E240" s="14" t="inlineStr">
+        <is>
+          <t>https://www.cancilleria.gov.co/newsroom/Noticias</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="6" t="inlineStr">
-        <is>
-          <t>20/05/2026 09:47 a. m.</t>
-        </is>
-      </c>
-      <c r="B241" s="6" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C241" s="6" t="inlineStr">
-        <is>
-          <t>Canal Trece</t>
-        </is>
-      </c>
-      <c r="D241" s="7" t="inlineStr">
-        <is>
-          <t>Colombianos en Estados Unidos: Así se votará en las elecciones presidenciales de 2026</t>
-        </is>
-      </c>
-      <c r="E241" s="8" t="inlineStr">
-        <is>
-          <t>https://canaltrece.com.co/noticias/colombianos-en-estados-unidos-asi-se-votara-en-las-elecciones-presidenciales-de-2026/</t>
+      <c r="A241" s="9" t="inlineStr">
+        <is>
+          <t>21/05/2026 02:45 p. m.</t>
+        </is>
+      </c>
+      <c r="B241" s="9" t="inlineStr">
+        <is>
+          <t>Entidad Oficial</t>
+        </is>
+      </c>
+      <c r="C241" s="9" t="inlineStr">
+        <is>
+          <t>Ministerio del Interior</t>
+        </is>
+      </c>
+      <c r="D241" s="10" t="inlineStr">
+        <is>
+          <t>Avanza seguimiento a acuerdos de Consulta Previa del Complejo Penitenciario de Jamundí</t>
+        </is>
+      </c>
+      <c r="E241" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mininterior.gov.co/micrositios/direccion-de-autoridad-nacional-y-consulta-previa/avanza-seguimiento-a-acuerdos-de-consulta-previa-del-complejo-penitenciario-de-jamundi/</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="3" t="inlineStr">
-        <is>
-          <t>20/05/2026 09:39 a. m.</t>
-        </is>
-      </c>
-      <c r="B242" s="3" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C242" s="3" t="inlineStr">
-        <is>
-          <t>Canal Trece</t>
-        </is>
-      </c>
-      <c r="D242" s="4" t="inlineStr">
-        <is>
-          <t>Elecciones Presidenciales en Colombia: Paso a paso para consultar su puesto de votación este 31 de mayo</t>
-        </is>
-      </c>
-      <c r="E242" s="5" t="inlineStr">
-        <is>
-          <t>https://canaltrece.com.co/noticias/elecciones-presidenciales-en-colombia-paso-a-paso-para-consultar-su-puesto-de-votacion-este-31-de-mayo/</t>
+      <c r="A242" s="12" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B242" s="12" t="inlineStr">
+        <is>
+          <t>Entidad Oficial</t>
+        </is>
+      </c>
+      <c r="C242" s="12" t="inlineStr">
+        <is>
+          <t>Ministerio de Educación Nacional</t>
+        </is>
+      </c>
+      <c r="D242" s="13" t="inlineStr">
+        <is>
+          <t>La universidad pública que esperó Suba durante años ahora se pensará con su gente</t>
+        </is>
+      </c>
+      <c r="E242" s="14" t="inlineStr">
+        <is>
+          <t>https://www.mineducacion.gov.co/portal/salaprensa/Comunicados/428987:La-universidad-publica-que-espero-Suba-durante-anos-ahora-se-pensara-con-su-gente</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="6" t="inlineStr">
-        <is>
-          <t>20/05/2026 09:33 a. m.</t>
-        </is>
-      </c>
-      <c r="B243" s="6" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C243" s="6" t="inlineStr">
-        <is>
-          <t>Canal Trece</t>
-        </is>
-      </c>
-      <c r="D243" s="7" t="inlineStr">
-        <is>
-          <t>El dolor de una madre: La historia de Yulitza Toloza y el último adiós desde Arauca</t>
-        </is>
-      </c>
-      <c r="E243" s="8" t="inlineStr">
-        <is>
-          <t>https://canaltrece.com.co/noticias/el-dolor-de-una-madre-la-historia-de-yulitza-toloza-y-el-ultimo-adios-desde-arauca/</t>
+      <c r="A243" s="9" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B243" s="9" t="inlineStr">
+        <is>
+          <t>Entidad Oficial</t>
+        </is>
+      </c>
+      <c r="C243" s="9" t="inlineStr">
+        <is>
+          <t>Ministerio de Educación Nacional</t>
+        </is>
+      </c>
+      <c r="D243" s="10" t="inlineStr">
+        <is>
+          <t>¡Atención!  Se abre la convocatoria del Concurso Nacional de Escritura ‘Historias de Paz’ 2026</t>
+        </is>
+      </c>
+      <c r="E243" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mineducacion.gov.co/portal/salaprensa/Comunicados/428979:Atencion-Se-abre-la-convocatoria-del-Concurso-Nacional-de-Escritura-Historias-de-Paz-2026</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="3" t="inlineStr">
-        <is>
-          <t>20/05/2026 09:13 a. m.</t>
-        </is>
-      </c>
-      <c r="B244" s="3" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C244" s="3" t="inlineStr">
-        <is>
-          <t>Canal Trece</t>
-        </is>
-      </c>
-      <c r="D244" s="4" t="inlineStr">
-        <is>
-          <t>Orgullo del Valle: Gerónimo Mayac, el niño prodigio de 12 años que busca apoyo para representar a Colombia en el mundial de matemáticas en Singapur</t>
-        </is>
-      </c>
-      <c r="E244" s="5" t="inlineStr">
-        <is>
-          <t>https://canaltrece.com.co/noticias/orgullo-del-valle-geronimo-mayac-el-nino-prodigio-de-12-anos-que-busca-apoyo-para-representar-a-colombia-en-el-mundial-de-matematicas-en-singapur/</t>
+      <c r="A244" s="12" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B244" s="12" t="inlineStr">
+        <is>
+          <t>Entidad Oficial</t>
+        </is>
+      </c>
+      <c r="C244" s="12" t="inlineStr">
+        <is>
+          <t>Ministerio de Educación Nacional</t>
+        </is>
+      </c>
+      <c r="D244" s="13" t="inlineStr">
+        <is>
+          <t>La universidad pública que esperó Suba durante años ahora se pensará con su gente</t>
+        </is>
+      </c>
+      <c r="E244" s="14" t="inlineStr">
+        <is>
+          <t>https://www.mineducacion.gov.co/portal/salaprensa/Comunicados/428987:La-universidad-publica-que-espero-Suba-durante-anos-ahora-se-pensara-con-su-gente</t>
         </is>
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="6" t="inlineStr">
-        <is>
-          <t>19/05/2026 07:02 p. m.</t>
-        </is>
-      </c>
-      <c r="B245" s="6" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C245" s="6" t="inlineStr">
-        <is>
-          <t>Canal Trece</t>
-        </is>
-      </c>
-      <c r="D245" s="7" t="inlineStr">
-        <is>
-          <t>Portugal Colombia Mundial 2026 mueve redes por comentario de Roberto Martínez</t>
-        </is>
-      </c>
-      <c r="E245" s="8" t="inlineStr">
-        <is>
-          <t>https://canaltrece.com.co/noticias/portugal-colombia-mundial-2026-roberto-martinez/</t>
+      <c r="A245" s="9" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B245" s="9" t="inlineStr">
+        <is>
+          <t>Entidad Oficial</t>
+        </is>
+      </c>
+      <c r="C245" s="9" t="inlineStr">
+        <is>
+          <t>Ministerio de Educación Nacional</t>
+        </is>
+      </c>
+      <c r="D245" s="10" t="inlineStr">
+        <is>
+          <t>¡Atención!  Se abre la convocatoria del Concurso Nacional de Escritura ‘Historias de Paz’ 2026</t>
+        </is>
+      </c>
+      <c r="E245" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mineducacion.gov.co/portal/salaprensa/Comunicados/428979:Atencion-Se-abre-la-convocatoria-del-Concurso-Nacional-de-Escritura-Historias-de-Paz-2026</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="3" t="inlineStr">
-        <is>
-          <t>19/05/2026 06:52 p. m.</t>
-        </is>
-      </c>
-      <c r="B246" s="3" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C246" s="3" t="inlineStr">
-        <is>
-          <t>Canal Trece</t>
-        </is>
-      </c>
-      <c r="D246" s="4" t="inlineStr">
-        <is>
-          <t>Romeo Santos Prince Royce Bogotá confirma concierto en 2026</t>
-        </is>
-      </c>
-      <c r="E246" s="5" t="inlineStr">
-        <is>
-          <t>https://canaltrece.com.co/noticias/romeo-santos-prince-royce-bogota-2026/</t>
+      <c r="A246" s="12" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B246" s="12" t="inlineStr">
+        <is>
+          <t>Entidad Oficial</t>
+        </is>
+      </c>
+      <c r="C246" s="12" t="inlineStr">
+        <is>
+          <t>Ministerio de Comercio, Industria y Turismo</t>
+        </is>
+      </c>
+      <c r="D246" s="13" t="inlineStr">
+        <is>
+          <t>MinCIT, junto con la Agencia Presidencial de Cooperación Internacional y TICA, realizará talleres internacionales sobre turismo médico</t>
+        </is>
+      </c>
+      <c r="E246" s="14" t="inlineStr">
+        <is>
+          <t>https://www.mincit.gov.co/prensa/noticias/turismo/mincit-talleres-internacionales-turismo-medico</t>
         </is>
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="6" t="inlineStr">
-        <is>
-          <t>19/05/2026 06:47 p. m.</t>
-        </is>
-      </c>
-      <c r="B247" s="6" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C247" s="6" t="inlineStr">
-        <is>
-          <t>Canal Trece</t>
-        </is>
-      </c>
-      <c r="D247" s="7" t="inlineStr">
-        <is>
-          <t>Shakira Dai Dai Mundial 2026 une música, fútbol y educación</t>
-        </is>
-      </c>
-      <c r="E247" s="8" t="inlineStr">
-        <is>
-          <t>https://canaltrece.com.co/noticias/shakira-dai-dai-mundial-2026-educacion/</t>
+      <c r="A247" s="9" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B247" s="9" t="inlineStr">
+        <is>
+          <t>Entidad Oficial</t>
+        </is>
+      </c>
+      <c r="C247" s="9" t="inlineStr">
+        <is>
+          <t>Ministerio de Comercio, Industria y Turismo</t>
+        </is>
+      </c>
+      <c r="D247" s="10" t="inlineStr">
+        <is>
+          <t>Colombia muestra oportunidades de inversión y Ventanilla Única de Inversión entre empresarios franceses</t>
+        </is>
+      </c>
+      <c r="E247" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mincit.gov.co/prensa/noticias/comercio/colombia-muestra-oportunidades-inversion-francia</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="3" t="inlineStr">
-        <is>
-          <t>19/05/2026 06:38 p. m.</t>
-        </is>
-      </c>
-      <c r="B248" s="3" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C248" s="3" t="inlineStr">
-        <is>
-          <t>Canal Trece</t>
-        </is>
-      </c>
-      <c r="D248" s="4" t="inlineStr">
-        <is>
-          <t>Baum Festival 2026 prende Bogotá con dos días de electrónica</t>
-        </is>
-      </c>
-      <c r="E248" s="5" t="inlineStr">
-        <is>
-          <t>https://canaltrece.com.co/noticias/baum-festival-2026-bogota-corferias/</t>
+      <c r="A248" s="12" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B248" s="12" t="inlineStr">
+        <is>
+          <t>Entidad Oficial</t>
+        </is>
+      </c>
+      <c r="C248" s="12" t="inlineStr">
+        <is>
+          <t>Ministerio de Tecnologías de la Información y las Comunicaciones</t>
+        </is>
+      </c>
+      <c r="D248" s="13" t="inlineStr">
+        <is>
+          <t>El campo del Valle del Cauca se conecta con el futuro: AGROTECH llega a Palmira para transformar la producción rural</t>
+        </is>
+      </c>
+      <c r="E248" s="14" t="inlineStr">
+        <is>
+          <t>https://www.mintic.gov.co/portal/inicio/Sala-de-prensa/Noticias/438123:El-campo-del-Valle-del-Cauca-se-conecta-con-el-futuro-AGROTECH-llega-a-Palmira-para-transformar-la-produccion-rural</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="9" t="inlineStr">
         <is>
-          <t>21/05/2026 12:00 p. m.</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B249" s="9" t="inlineStr">
@@ -7182,17 +7182,17 @@
       </c>
       <c r="C249" s="9" t="inlineStr">
         <is>
-          <t>Ministerio de Relaciones Exteriores (Cancillería)</t>
+          <t>Ministerio de Tecnologías de la Información y las Comunicaciones</t>
         </is>
       </c>
       <c r="D249" s="10" t="inlineStr">
         <is>
-          <t>La Academia Diplomática Augusto Ramírez Ocampo publica el listado definitivo de Admitidos a presentar Pruebas Escritas Fase I del Concurso de Ingreso a la Carrera Diplomática y Consular 2028</t>
+          <t>El Ministerio TIC recibió 35 solicitudes para el uso de la banda de 900 MHz. en 139 municipios del país</t>
         </is>
       </c>
       <c r="E249" s="11" t="inlineStr">
         <is>
-          <t>https://www.cancilleria.gov.co/newsroom/Noticias</t>
+          <t>https://www.mintic.gov.co/portal/inicio/Sala-de-prensa/Noticias/438121:El-Ministerio-TIC-recibio-35-solicitudes-para-el-uso-de-la-banda-de-900-MHz-en-139-municipios-del-pais</t>
         </is>
       </c>
     </row>
@@ -7209,17 +7209,17 @@
       </c>
       <c r="C250" s="12" t="inlineStr">
         <is>
-          <t>Ministerio de Minas y Energía</t>
+          <t>Ministerio de Tecnologías de la Información y las Comunicaciones</t>
         </is>
       </c>
       <c r="D250" s="13" t="inlineStr">
         <is>
-          <t>Gobierno expide nueva resolución que acelera la entrada de proyectos de energía limpia y fortalece la confiabilidad eléctrica del país</t>
+          <t>Chocó abre sus puertas a la innovación y la transformación digital de Colombia 5.0</t>
         </is>
       </c>
       <c r="E250" s="14" t="inlineStr">
         <is>
-          <t>https://www.minenergia.gov.co/es/sala-de-prensa/noticias-index/gobierno-expide-nueva-resolucion-que-acelera-la-entrada-de-proyectos-de-energia-limpia-y-fortalece-la-confiabilidad-electrica-del-pais/</t>
+          <t>https://www.mintic.gov.co/portal/inicio/Sala-de-prensa/Noticias/438103:Choco-abre-sus-puertas-a-la-innovacion-y-la-transformacion-digital-de-Colombia-5-0</t>
         </is>
       </c>
     </row>
@@ -7241,19 +7241,19 @@
       </c>
       <c r="D251" s="10" t="inlineStr">
         <is>
-          <t>El campo del Valle del Cauca se conecta con el futuro: AGROTECH llega a Palmira para transformar la producción rural</t>
+          <t>Avanza la conectividad en la Amazonía: Gobierno Nacional garantiza recursos para el Plan de Fibra Óptica</t>
         </is>
       </c>
       <c r="E251" s="11" t="inlineStr">
         <is>
-          <t>https://www.mintic.gov.co/portal/inicio/Sala-de-prensa/Noticias/438123:El-campo-del-Valle-del-Cauca-se-conecta-con-el-futuro-AGROTECH-llega-a-Palmira-para-transformar-la-produccion-rural</t>
+          <t>https://www.mintic.gov.co/portal/inicio/Sala-de-prensa/Noticias/438101:Avanza-la-conectividad-en-la-Amazonia-Gobierno-Nacional-garantiza-recursos-para-el-Plan-de-Fibra-Optica</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="12" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>21/05/2026 08:46 p. m.</t>
         </is>
       </c>
       <c r="B252" s="12" t="inlineStr">
@@ -7263,24 +7263,24 @@
       </c>
       <c r="C252" s="12" t="inlineStr">
         <is>
-          <t>Ministerio de Tecnologías de la Información y las Comunicaciones</t>
+          <t>Superintendencia Nacional de Salud</t>
         </is>
       </c>
       <c r="D252" s="13" t="inlineStr">
         <is>
-          <t>El Ministerio TIC recibió 35 solicitudes para el uso de la banda de 900 MHz. en 139 municipios del país</t>
+          <t>Supersalud lidera seminario sobre prevención del suicidio y salud mental juvenil en Nariño</t>
         </is>
       </c>
       <c r="E252" s="14" t="inlineStr">
         <is>
-          <t>https://www.mintic.gov.co/portal/inicio/Sala-de-prensa/Noticias/438121:El-Ministerio-TIC-recibio-35-solicitudes-para-el-uso-de-la-banda-de-900-MHz-en-139-municipios-del-pais</t>
+          <t>https://wcmportal.supersalud.gov.co/portalweb/Comunicaciones/Lists/Noticias/Noticia.aspx?ID=2574</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="9" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>21/05/2026 01:45 p. m.</t>
         </is>
       </c>
       <c r="B253" s="9" t="inlineStr">
@@ -7290,24 +7290,24 @@
       </c>
       <c r="C253" s="9" t="inlineStr">
         <is>
-          <t>Ministerio de Tecnologías de la Información y las Comunicaciones</t>
+          <t>Superintendencia Nacional de Salud</t>
         </is>
       </c>
       <c r="D253" s="10" t="inlineStr">
         <is>
-          <t>Chocó abre sus puertas a la innovación y la transformación digital de Colombia 5.0</t>
+          <t>Supersalud avanza en auditoría integral al modelo de salud del FOMAG y advierte incumplimientos de órdenes previas</t>
         </is>
       </c>
       <c r="E253" s="11" t="inlineStr">
         <is>
-          <t>https://www.mintic.gov.co/portal/inicio/Sala-de-prensa/Noticias/438103:Choco-abre-sus-puertas-a-la-innovacion-y-la-transformacion-digital-de-Colombia-5-0</t>
+          <t>https://wcmportal.supersalud.gov.co/portalweb/Comunicaciones/Lists/Noticias/Noticia.aspx?ID=2573</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="12" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>21/05/2026 03:50 p. m.</t>
         </is>
       </c>
       <c r="B254" s="12" t="inlineStr">
@@ -7317,24 +7317,24 @@
       </c>
       <c r="C254" s="12" t="inlineStr">
         <is>
-          <t>Ministerio de Tecnologías de la Información y las Comunicaciones</t>
+          <t>Ministerio de Ciencia, Tecnología e Innovación</t>
         </is>
       </c>
       <c r="D254" s="13" t="inlineStr">
         <is>
-          <t>Avanza la conectividad en la Amazonía: Gobierno Nacional garantiza recursos para el Plan de Fibra Óptica</t>
+          <t>Gobierno Nacional avanza en la democratización del conocimiento para las comunidades afrocolombianas del país</t>
         </is>
       </c>
       <c r="E254" s="14" t="inlineStr">
         <is>
-          <t>https://www.mintic.gov.co/portal/inicio/Sala-de-prensa/Noticias/438101:Avanza-la-conectividad-en-la-Amazonia-Gobierno-Nacional-garantiza-recursos-para-el-Plan-de-Fibra-Optica</t>
+          <t>https://minciencias.gov.co/sala_de_prensa/gobierno-nacional-avanza-en-la-democratizacion-del-conocimiento-para-las-0</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="9" t="inlineStr">
         <is>
-          <t>21/05/2026 02:45 p. m.</t>
+          <t>21/05/2026 07:00 a. m.</t>
         </is>
       </c>
       <c r="B255" s="9" t="inlineStr">
@@ -7344,24 +7344,24 @@
       </c>
       <c r="C255" s="9" t="inlineStr">
         <is>
-          <t>Ministerio del Interior</t>
+          <t>Procuraduría General de la Nación</t>
         </is>
       </c>
       <c r="D255" s="10" t="inlineStr">
         <is>
-          <t>Avanza seguimiento a acuerdos de Consulta Previa del Complejo Penitenciario de Jamundí</t>
+          <t>Procuraduría suspendió provisionalmente al Notario Único de la Hormiga, Putumayo, por presunta indebida participación en política</t>
         </is>
       </c>
       <c r="E255" s="11" t="inlineStr">
         <is>
-          <t>https://www.mininterior.gov.co/micrositios/direccion-de-autoridad-nacional-y-consulta-previa/avanza-seguimiento-a-acuerdos-de-consulta-previa-del-complejo-penitenciario-de-jamundi/</t>
+          <t>https://www.procuraduria.gov.co/Pages/procuraduria-suspendio-provisionalmente-notario-unico-hormiga-putumayo-presunta-indebida-participacion.aspx</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="12" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>21/05/2026 02:00 a. m.</t>
         </is>
       </c>
       <c r="B256" s="12" t="inlineStr">
@@ -7371,24 +7371,24 @@
       </c>
       <c r="C256" s="12" t="inlineStr">
         <is>
-          <t>Ministerio de Educación Nacional</t>
+          <t>Procuraduría General de la Nación</t>
         </is>
       </c>
       <c r="D256" s="13" t="inlineStr">
         <is>
-          <t>La universidad pública que esperó Suba durante años ahora se pensará con su gente</t>
+          <t>Procurador General, Gregorio Eljach, rindió homenaje a la raza negra</t>
         </is>
       </c>
       <c r="E256" s="14" t="inlineStr">
         <is>
-          <t>https://www.mineducacion.gov.co/portal/salaprensa/Comunicados/428987:La-universidad-publica-que-espero-Suba-durante-anos-ahora-se-pensara-con-su-gente</t>
+          <t>https://www.procuraduria.gov.co/Pages/procurador-general-gregorio-eljach-rindio-homenaje-raza-negra.aspx</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="9" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>21/05/2026 12:00 p. m.</t>
         </is>
       </c>
       <c r="B257" s="9" t="inlineStr">
@@ -7398,24 +7398,24 @@
       </c>
       <c r="C257" s="9" t="inlineStr">
         <is>
-          <t>Ministerio de Educación Nacional</t>
+          <t>Procuraduría General de la Nación</t>
         </is>
       </c>
       <c r="D257" s="10" t="inlineStr">
         <is>
-          <t>¡Atención!  Se abre la convocatoria del Concurso Nacional de Escritura ‘Historias de Paz’ 2026</t>
+          <t>“Reafirmamos nuestro compromiso con la garantía de los derechos de la población negra, afrocolombiana, raizal y palenquera”: Procurador General, Gregorio Eljach</t>
         </is>
       </c>
       <c r="E257" s="11" t="inlineStr">
         <is>
-          <t>https://www.mineducacion.gov.co/portal/salaprensa/Comunicados/428979:Atencion-Se-abre-la-convocatoria-del-Concurso-Nacional-de-Escritura-Historias-de-Paz-2026</t>
+          <t>https://www.procuraduria.gov.co/Pages/reafirmamos-nuestro-compromiso-garantia-derechos-poblacion-negra-afrocolombiana-raizal-palenquera.aspx</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="12" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>21/05/2026 06:30 a. m.</t>
         </is>
       </c>
       <c r="B258" s="12" t="inlineStr">
@@ -7425,24 +7425,24 @@
       </c>
       <c r="C258" s="12" t="inlineStr">
         <is>
-          <t>Ministerio de Educación Nacional</t>
+          <t>Procuraduría General de la Nación</t>
         </is>
       </c>
       <c r="D258" s="13" t="inlineStr">
         <is>
-          <t>La universidad pública que esperó Suba durante años ahora se pensará con su gente</t>
+          <t>Acciones de la Procuraduría llevaron a INVÍAS a anunciar trabajos en vía Panamericana por más de 14 mil millones de pesos</t>
         </is>
       </c>
       <c r="E258" s="14" t="inlineStr">
         <is>
-          <t>https://www.mineducacion.gov.co/portal/salaprensa/Comunicados/428987:La-universidad-publica-que-espero-Suba-durante-anos-ahora-se-pensara-con-su-gente</t>
+          <t>https://www.procuraduria.gov.co/Pages/acciones-procuraduria-llevaron-invias-anunciar-trabajos-via-panamericana-mas-14-mil-millones.aspx</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="9" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>21/05/2026 02:45 p. m.</t>
         </is>
       </c>
       <c r="B259" s="9" t="inlineStr">
@@ -7452,17 +7452,17 @@
       </c>
       <c r="C259" s="9" t="inlineStr">
         <is>
-          <t>Ministerio de Educación Nacional</t>
+          <t>Ministerio de Vivienda, Ciudad y Territorio</t>
         </is>
       </c>
       <c r="D259" s="10" t="inlineStr">
         <is>
-          <t>¡Atención!  Se abre la convocatoria del Concurso Nacional de Escritura ‘Historias de Paz’ 2026</t>
+          <t>Gobierno abre convocatoria para obras e interventoría del Programa Barrios y Veredas de Paz en Ipiales, Nariño</t>
         </is>
       </c>
       <c r="E259" s="11" t="inlineStr">
         <is>
-          <t>https://www.mineducacion.gov.co/portal/salaprensa/Comunicados/428979:Atencion-Se-abre-la-convocatoria-del-Concurso-Nacional-de-Escritura-Historias-de-Paz-2026</t>
+          <t>https://minvivienda.gov.co/sala-de-prensa/gobierno-abre-convocatoria-para-obras-e-interventoria-del-programa-barrios-y-veredas-de-paz-en-ipiales-narino</t>
         </is>
       </c>
     </row>
@@ -7479,24 +7479,24 @@
       </c>
       <c r="C260" s="12" t="inlineStr">
         <is>
-          <t>Ministerio de Comercio, Industria y Turismo</t>
+          <t>Ministerio de Transporte</t>
         </is>
       </c>
       <c r="D260" s="13" t="inlineStr">
         <is>
-          <t>MinCIT, junto con la Agencia Presidencial de Cooperación Internacional y TICA, realizará talleres internacionales sobre turismo médico</t>
+          <t>Plataforma RNDC restablece su operación tras superar intermitencia tecnológica</t>
         </is>
       </c>
       <c r="E260" s="14" t="inlineStr">
         <is>
-          <t>https://www.mincit.gov.co/prensa/noticias/turismo/mincit-talleres-internacionales-turismo-medico</t>
+          <t>https://mintransporte.gov.co/publicaciones/12351/plataforma-rndc-restablece-su-operacion-tras-superar-intermitencia-tecnologica/</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="9" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>21/05/2026 05:11 p. m.</t>
         </is>
       </c>
       <c r="B261" s="9" t="inlineStr">
@@ -7506,24 +7506,24 @@
       </c>
       <c r="C261" s="9" t="inlineStr">
         <is>
-          <t>Ministerio de Comercio, Industria y Turismo</t>
+          <t>Fiscalía General de la Nación</t>
         </is>
       </c>
       <c r="D261" s="10" t="inlineStr">
         <is>
-          <t>Colombia muestra oportunidades de inversión y Ventanilla Única de Inversión entre empresarios franceses</t>
+          <t>Condenan a más de 16 años de prisión a responsable del crimen de un hombre en Anserma (Caldas)</t>
         </is>
       </c>
       <c r="E261" s="11" t="inlineStr">
         <is>
-          <t>https://www.mincit.gov.co/prensa/noticias/comercio/colombia-muestra-oportunidades-inversion-francia</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/condenan-a-mas-de-16-anos-de-prision-a-responsable-del-crimen-de-un-hombre-en-anserma-caldas/</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="12" t="inlineStr">
         <is>
-          <t>21/05/2026 03:50 p. m.</t>
+          <t>21/05/2026 05:01 p. m.</t>
         </is>
       </c>
       <c r="B262" s="12" t="inlineStr">
@@ -7533,24 +7533,24 @@
       </c>
       <c r="C262" s="12" t="inlineStr">
         <is>
-          <t>Ministerio de Ciencia, Tecnología e Innovación</t>
+          <t>Fiscalía General de la Nación</t>
         </is>
       </c>
       <c r="D262" s="13" t="inlineStr">
         <is>
-          <t>Gobierno Nacional avanza en la democratización del conocimiento para las comunidades afrocolombianas del país</t>
+          <t>Presunto responsable del crimen de un hombre en La Dorada (Caldas) fue asegurado</t>
         </is>
       </c>
       <c r="E262" s="14" t="inlineStr">
         <is>
-          <t>https://minciencias.gov.co/sala_de_prensa/gobierno-nacional-avanza-en-la-democratizacion-del-conocimiento-para-las-0</t>
+          <t>https://www.fiscalia.gov.co/colombia/seguridad-territorial/presunto-responsable-del-crimen-de-un-hombre-en-la-dorada-caldas-fue-asegurado/</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="9" t="inlineStr">
         <is>
-          <t>21/05/2026 08:46 p. m.</t>
+          <t>21/05/2026 04:51 p. m.</t>
         </is>
       </c>
       <c r="B263" s="9" t="inlineStr">
@@ -7560,24 +7560,24 @@
       </c>
       <c r="C263" s="9" t="inlineStr">
         <is>
-          <t>Superintendencia Nacional de Salud</t>
+          <t>Fiscalía General de la Nación</t>
         </is>
       </c>
       <c r="D263" s="10" t="inlineStr">
         <is>
-          <t>Supersalud lidera seminario sobre prevención del suicidio y salud mental juvenil en Nariño</t>
+          <t>Afectación a grupo delincuencial dedicado al tráfico local de estupefacientes en Viterbo (Caldas)</t>
         </is>
       </c>
       <c r="E263" s="11" t="inlineStr">
         <is>
-          <t>https://wcmportal.supersalud.gov.co/portalweb/Comunicaciones/Lists/Noticias/Noticia.aspx?ID=2574</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/afectacion-a-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-viterbo-caldas/</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="12" t="inlineStr">
         <is>
-          <t>21/05/2026 01:45 p. m.</t>
+          <t>21/05/2026 04:44 p. m.</t>
         </is>
       </c>
       <c r="B264" s="12" t="inlineStr">
@@ -7587,24 +7587,24 @@
       </c>
       <c r="C264" s="12" t="inlineStr">
         <is>
-          <t>Superintendencia Nacional de Salud</t>
+          <t>Fiscalía General de la Nación</t>
         </is>
       </c>
       <c r="D264" s="13" t="inlineStr">
         <is>
-          <t>Supersalud avanza en auditoría integral al modelo de salud del FOMAG y advierte incumplimientos de órdenes previas</t>
+          <t>Procesado señalado abusador sexual de una menor de edad en Palmira (Valle del Cauca)</t>
         </is>
       </c>
       <c r="E264" s="14" t="inlineStr">
         <is>
-          <t>https://wcmportal.supersalud.gov.co/portalweb/Comunicaciones/Lists/Noticias/Noticia.aspx?ID=2573</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/procesado-senalado-abusador-sexual-de-una-menor-de-edad-en-palmira-valle-del-cauca/</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="9" t="inlineStr">
         <is>
-          <t>21/05/2026 02:45 p. m.</t>
+          <t>21/05/2026 04:38 p. m.</t>
         </is>
       </c>
       <c r="B265" s="9" t="inlineStr">
@@ -7614,24 +7614,24 @@
       </c>
       <c r="C265" s="9" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda, Ciudad y Territorio</t>
+          <t>Fiscalía General de la Nación</t>
         </is>
       </c>
       <c r="D265" s="10" t="inlineStr">
         <is>
-          <t>Gobierno abre convocatoria para obras e interventoría del Programa Barrios y Veredas de Paz en Ipiales, Nariño</t>
+          <t>Asegurado presunto integrante del Clan del Golfo presuntamente involucrado en varios delitos en Zarzal (Valle del Cauca)</t>
         </is>
       </c>
       <c r="E265" s="11" t="inlineStr">
         <is>
-          <t>https://minvivienda.gov.co/sala-de-prensa/gobierno-abre-convocatoria-para-obras-e-interventoria-del-programa-barrios-y-veredas-de-paz-en-ipiales-narino</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-integrante-del-clan-del-golfo-presuntamente-involucrado-en-varios-delitos-en-zarzal-valle-del-cauca/</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="12" t="inlineStr">
         <is>
-          <t>21/05/2026 05:11 p. m.</t>
+          <t>21/05/2026 04:35 p. m.</t>
         </is>
       </c>
       <c r="B266" s="12" t="inlineStr">
@@ -7646,19 +7646,19 @@
       </c>
       <c r="D266" s="13" t="inlineStr">
         <is>
-          <t>Condenan a más de 16 años de prisión a responsable del crimen de un hombre en Anserma (Caldas)</t>
+          <t>Condenan a más de 16 años a responsables del crimen de un hombre en Dosquebradas</t>
         </is>
       </c>
       <c r="E266" s="14" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/condenan-a-mas-de-16-anos-de-prision-a-responsable-del-crimen-de-un-hombre-en-anserma-caldas/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/condenan-a-mas-de-16-anos-a-responsables-del-crimen-de-un-hombre-en-dosquebradas/</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="9" t="inlineStr">
         <is>
-          <t>21/05/2026 05:01 p. m.</t>
+          <t>21/05/2026 04:31 p. m.</t>
         </is>
       </c>
       <c r="B267" s="9" t="inlineStr">
@@ -7673,19 +7673,19 @@
       </c>
       <c r="D267" s="10" t="inlineStr">
         <is>
-          <t>Presunto responsable del crimen de un hombre en La Dorada (Caldas) fue asegurado</t>
+          <t>Capturado con fines de extradición presunto cabecilla del ‘Clan Cotes’ que estaría involucrado en tráfico de estupefacientes</t>
         </is>
       </c>
       <c r="E267" s="11" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/seguridad-territorial/presunto-responsable-del-crimen-de-un-hombre-en-la-dorada-caldas-fue-asegurado/</t>
+          <t>https://www.fiscalia.gov.co/colombia/crimen-organizado/capturado-con-fines-de-extradicion-presunto-cabecilla-del-clan-cotes-que-estaria-involucrado-en-trafico-de-estupefacientes/</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="12" t="inlineStr">
         <is>
-          <t>21/05/2026 04:51 p. m.</t>
+          <t>21/05/2026 04:24 p. m.</t>
         </is>
       </c>
       <c r="B268" s="12" t="inlineStr">
@@ -7700,19 +7700,19 @@
       </c>
       <c r="D268" s="13" t="inlineStr">
         <is>
-          <t>Afectación a grupo delincuencial dedicado al tráfico local de estupefacientes en Viterbo (Caldas)</t>
+          <t>Asegurados presuntos responsable de asesinar a un menor de edad en San Andrés</t>
         </is>
       </c>
       <c r="E268" s="14" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/afectacion-a-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-viterbo-caldas/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-responsable-de-asesinar-a-un-menor-de-edad-en-san-andres/</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="9" t="inlineStr">
         <is>
-          <t>21/05/2026 04:44 p. m.</t>
+          <t>21/05/2026 03:38 p. m.</t>
         </is>
       </c>
       <c r="B269" s="9" t="inlineStr">
@@ -7727,260 +7727,287 @@
       </c>
       <c r="D269" s="10" t="inlineStr">
         <is>
-          <t>Procesado señalado abusador sexual de una menor de edad en Palmira (Valle del Cauca)</t>
+          <t>Confirman condena contra exalcalde de Anzoátegui por irregularidades en contratos para el mantenimiento de maquinaria pesada</t>
         </is>
       </c>
       <c r="E269" s="11" t="inlineStr">
         <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/procesado-senalado-abusador-sexual-de-una-menor-de-edad-en-palmira-valle-del-cauca/</t>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/confirman-condena-contra-exalcalde-de-anzoategui-por-irregularidades-en-contratos-para-el-mantenimiento-de-maquinaria-pesada/</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="12" t="inlineStr">
-        <is>
-          <t>21/05/2026 04:38 p. m.</t>
-        </is>
-      </c>
-      <c r="B270" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C270" s="12" t="inlineStr">
-        <is>
-          <t>Fiscalía General de la Nación</t>
-        </is>
-      </c>
-      <c r="D270" s="13" t="inlineStr">
-        <is>
-          <t>Asegurado presunto integrante del Clan del Golfo presuntamente involucrado en varios delitos en Zarzal (Valle del Cauca)</t>
-        </is>
-      </c>
-      <c r="E270" s="14" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-integrante-del-clan-del-golfo-presuntamente-involucrado-en-varios-delitos-en-zarzal-valle-del-cauca/</t>
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t>20/05/2026 07:38 p. m.</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>Medio de Comunicación</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>El Espectador</t>
+        </is>
+      </c>
+      <c r="D270" s="4" t="inlineStr">
+        <is>
+          <t>¿Abelardo de la Espriella es la salvación de Colombia?| La Pulla</t>
+        </is>
+      </c>
+      <c r="E270" s="5" t="inlineStr">
+        <is>
+          <t>https://www.elespectador.com/opinion/columnistas/la-pulla/la-pulla-abelardo-de-la-espriella-es-la-salvacion-de-colombia/</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="9" t="inlineStr">
-        <is>
-          <t>21/05/2026 04:35 p. m.</t>
-        </is>
-      </c>
-      <c r="B271" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C271" s="9" t="inlineStr">
-        <is>
-          <t>Fiscalía General de la Nación</t>
-        </is>
-      </c>
-      <c r="D271" s="10" t="inlineStr">
-        <is>
-          <t>Condenan a más de 16 años a responsables del crimen de un hombre en Dosquebradas</t>
-        </is>
-      </c>
-      <c r="E271" s="11" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/condenan-a-mas-de-16-anos-a-responsables-del-crimen-de-un-hombre-en-dosquebradas/</t>
+      <c r="A271" s="6" t="inlineStr">
+        <is>
+          <t>20/05/2026 07:35 p. m.</t>
+        </is>
+      </c>
+      <c r="B271" s="6" t="inlineStr">
+        <is>
+          <t>Medio de Comunicación</t>
+        </is>
+      </c>
+      <c r="C271" s="6" t="inlineStr">
+        <is>
+          <t>El Espectador</t>
+        </is>
+      </c>
+      <c r="D271" s="7" t="inlineStr">
+        <is>
+          <t>Encuesta Invamer: Iván Cepeda ganaría en todos los escenarios de la segunda vuelta</t>
+        </is>
+      </c>
+      <c r="E271" s="8" t="inlineStr">
+        <is>
+          <t>https://www.elespectador.com/politica/elecciones-colombia-2026/encuesta-invamer-cepeda-le-ganaria-a-de-la-espriella-y-valencia-en-todos-los-escenarios-de-la-segunda-vuelta-noticias-hoy/</t>
         </is>
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="12" t="inlineStr">
-        <is>
-          <t>21/05/2026 04:31 p. m.</t>
-        </is>
-      </c>
-      <c r="B272" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C272" s="12" t="inlineStr">
-        <is>
-          <t>Fiscalía General de la Nación</t>
-        </is>
-      </c>
-      <c r="D272" s="13" t="inlineStr">
-        <is>
-          <t>Capturado con fines de extradición presunto cabecilla del ‘Clan Cotes’ que estaría involucrado en tráfico de estupefacientes</t>
-        </is>
-      </c>
-      <c r="E272" s="14" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/crimen-organizado/capturado-con-fines-de-extradicion-presunto-cabecilla-del-clan-cotes-que-estaria-involucrado-en-trafico-de-estupefacientes/</t>
+      <c r="A272" s="3" t="inlineStr">
+        <is>
+          <t>20/05/2026 07:26 p. m.</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t>Medio de Comunicación</t>
+        </is>
+      </c>
+      <c r="C272" s="3" t="inlineStr">
+        <is>
+          <t>El Espectador</t>
+        </is>
+      </c>
+      <c r="D272" s="4" t="inlineStr">
+        <is>
+          <t>EE. UU. busca multar a migrantes con USD 18.000 para recuperar los costos de la deportación</t>
+        </is>
+      </c>
+      <c r="E272" s="5" t="inlineStr">
+        <is>
+          <t>https://www.elespectador.com/mundo/america/estados-unidos-busca-multar-a-migrantes-con-usd-18000-para-recuperar-los-costos-de-la-deportacion/</t>
         </is>
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="9" t="inlineStr">
-        <is>
-          <t>21/05/2026 04:24 p. m.</t>
-        </is>
-      </c>
-      <c r="B273" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C273" s="9" t="inlineStr">
-        <is>
-          <t>Fiscalía General de la Nación</t>
-        </is>
-      </c>
-      <c r="D273" s="10" t="inlineStr">
-        <is>
-          <t>Asegurados presuntos responsable de asesinar a un menor de edad en San Andrés</t>
-        </is>
-      </c>
-      <c r="E273" s="11" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-responsable-de-asesinar-a-un-menor-de-edad-en-san-andres/</t>
+      <c r="A273" s="6" t="inlineStr">
+        <is>
+          <t>20/05/2026 07:23 p. m.</t>
+        </is>
+      </c>
+      <c r="B273" s="6" t="inlineStr">
+        <is>
+          <t>Medio de Comunicación</t>
+        </is>
+      </c>
+      <c r="C273" s="6" t="inlineStr">
+        <is>
+          <t>El Espectador</t>
+        </is>
+      </c>
+      <c r="D273" s="7" t="inlineStr">
+        <is>
+          <t>Ejército despliega más de 120 soldados por enfrentamientos entre comunidad nasa y misak</t>
+        </is>
+      </c>
+      <c r="E273" s="8" t="inlineStr">
+        <is>
+          <t>https://www.elespectador.com/judicial/ejercito-despliega-mas-de-120-soldados-por-enfrentamientos-entre-comunidad-nasa-y-misak/</t>
         </is>
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="12" t="inlineStr">
-        <is>
-          <t>21/05/2026 03:38 p. m.</t>
-        </is>
-      </c>
-      <c r="B274" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C274" s="12" t="inlineStr">
-        <is>
-          <t>Fiscalía General de la Nación</t>
-        </is>
-      </c>
-      <c r="D274" s="13" t="inlineStr">
-        <is>
-          <t>Confirman condena contra exalcalde de Anzoátegui por irregularidades en contratos para el mantenimiento de maquinaria pesada</t>
-        </is>
-      </c>
-      <c r="E274" s="14" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/confirman-condena-contra-exalcalde-de-anzoategui-por-irregularidades-en-contratos-para-el-mantenimiento-de-maquinaria-pesada/</t>
+      <c r="A274" s="3" t="inlineStr">
+        <is>
+          <t>20/05/2026 07:20 p. m.</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>Medio de Comunicación</t>
+        </is>
+      </c>
+      <c r="C274" s="3" t="inlineStr">
+        <is>
+          <t>El Espectador</t>
+        </is>
+      </c>
+      <c r="D274" s="4" t="inlineStr">
+        <is>
+          <t>Sebastián Villa, figura en Copa Libertadores: marcó y asistió en el triunfo de su equipo</t>
+        </is>
+      </c>
+      <c r="E274" s="5" t="inlineStr">
+        <is>
+          <t>https://www.elespectador.com/deportes/futbol-mundial/sebastian-villa-figura-en-copa-libertadores-marco-y-asistio-en-el-triunfo-de-su-equipo/</t>
         </is>
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="9" t="inlineStr">
-        <is>
-          <t>21/05/2026 07:00 a. m.</t>
-        </is>
-      </c>
-      <c r="B275" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C275" s="9" t="inlineStr">
-        <is>
-          <t>Procuraduría General de la Nación</t>
-        </is>
-      </c>
-      <c r="D275" s="10" t="inlineStr">
-        <is>
-          <t>Procuraduría suspendió provisionalmente al Notario Único de la Hormiga, Putumayo, por presunta indebida participación en política</t>
-        </is>
-      </c>
-      <c r="E275" s="11" t="inlineStr">
-        <is>
-          <t>https://www.procuraduria.gov.co/Pages/procuraduria-suspendio-provisionalmente-notario-unico-hormiga-putumayo-presunta-indebida-participacion.aspx</t>
+      <c r="A275" s="6" t="inlineStr">
+        <is>
+          <t>20/05/2026 07:15 p. m.</t>
+        </is>
+      </c>
+      <c r="B275" s="6" t="inlineStr">
+        <is>
+          <t>Medio de Comunicación</t>
+        </is>
+      </c>
+      <c r="C275" s="6" t="inlineStr">
+        <is>
+          <t>El Espectador</t>
+        </is>
+      </c>
+      <c r="D275" s="7" t="inlineStr">
+        <is>
+          <t>Más apoyo para el ciclismo colombiano: así funcionará la alianza con LATAM</t>
+        </is>
+      </c>
+      <c r="E275" s="8" t="inlineStr">
+        <is>
+          <t>https://www.elespectador.com/deportes/ciclismo/mas-apoyo-para-el-ciclismo-colombiano-asi-funcionara-la-alianza-con-latam/</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="12" t="inlineStr">
-        <is>
-          <t>21/05/2026 02:00 a. m.</t>
-        </is>
-      </c>
-      <c r="B276" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C276" s="12" t="inlineStr">
-        <is>
-          <t>Procuraduría General de la Nación</t>
-        </is>
-      </c>
-      <c r="D276" s="13" t="inlineStr">
-        <is>
-          <t>Procurador General, Gregorio Eljach, rindió homenaje a la raza negra</t>
-        </is>
-      </c>
-      <c r="E276" s="14" t="inlineStr">
-        <is>
-          <t>https://www.procuraduria.gov.co/Pages/procurador-general-gregorio-eljach-rindio-homenaje-raza-negra.aspx</t>
+      <c r="A276" s="3" t="inlineStr">
+        <is>
+          <t>20/05/2026 07:10 p. m.</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="inlineStr">
+        <is>
+          <t>Medio de Comunicación</t>
+        </is>
+      </c>
+      <c r="C276" s="3" t="inlineStr">
+        <is>
+          <t>El Espectador</t>
+        </is>
+      </c>
+      <c r="D276" s="4" t="inlineStr">
+        <is>
+          <t>No aceptaron cargos: Sequera y Hernández, imputados por dos cargos en el caso Yulixa Toloza</t>
+        </is>
+      </c>
+      <c r="E276" s="5" t="inlineStr">
+        <is>
+          <t>https://www.elespectador.com/bogota/audiencia-en-vivo-del-caso-yulixa-toloza-fiscalia-entrega-mas-detalles-de-la-investigacion/</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="9" t="inlineStr">
-        <is>
-          <t>21/05/2026 12:00 p. m.</t>
-        </is>
-      </c>
-      <c r="B277" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C277" s="9" t="inlineStr">
-        <is>
-          <t>Procuraduría General de la Nación</t>
-        </is>
-      </c>
-      <c r="D277" s="10" t="inlineStr">
-        <is>
-          <t>“Reafirmamos nuestro compromiso con la garantía de los derechos de la población negra, afrocolombiana, raizal y palenquera”: Procurador General, Gregorio Eljach</t>
-        </is>
-      </c>
-      <c r="E277" s="11" t="inlineStr">
-        <is>
-          <t>https://www.procuraduria.gov.co/Pages/reafirmamos-nuestro-compromiso-garantia-derechos-poblacion-negra-afrocolombiana-raizal-palenquera.aspx</t>
+      <c r="A277" s="6" t="inlineStr">
+        <is>
+          <t>20/05/2026 07:04 p. m.</t>
+        </is>
+      </c>
+      <c r="B277" s="6" t="inlineStr">
+        <is>
+          <t>Medio de Comunicación</t>
+        </is>
+      </c>
+      <c r="C277" s="6" t="inlineStr">
+        <is>
+          <t>El Espectador</t>
+        </is>
+      </c>
+      <c r="D277" s="7" t="inlineStr">
+        <is>
+          <t>Invamer: Cepeda (44,6 %), De la Espriella (31,6 %) y Valencia (14 %) lideran la contienda</t>
+        </is>
+      </c>
+      <c r="E277" s="8" t="inlineStr">
+        <is>
+          <t>https://www.elespectador.com/politica/elecciones-colombia-2026/encuesta-invamer-ivan-cepeda-abelardo-de-la-espriella-y-paloma-valencia-lideran-la-contienda-asi-les-fue/</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="12" t="inlineStr">
-        <is>
-          <t>21/05/2026 06:30 a. m.</t>
-        </is>
-      </c>
-      <c r="B278" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C278" s="12" t="inlineStr">
-        <is>
-          <t>Procuraduría General de la Nación</t>
-        </is>
-      </c>
-      <c r="D278" s="13" t="inlineStr">
-        <is>
-          <t>Acciones de la Procuraduría llevaron a INVÍAS a anunciar trabajos en vía Panamericana por más de 14 mil millones de pesos</t>
-        </is>
-      </c>
-      <c r="E278" s="14" t="inlineStr">
-        <is>
-          <t>https://www.procuraduria.gov.co/Pages/acciones-procuraduria-llevaron-invias-anunciar-trabajos-via-panamericana-mas-14-mil-millones.aspx</t>
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t>20/05/2026 07:02 p. m.</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>Medio de Comunicación</t>
+        </is>
+      </c>
+      <c r="C278" s="3" t="inlineStr">
+        <is>
+          <t>El Espectador</t>
+        </is>
+      </c>
+      <c r="D278" s="4" t="inlineStr">
+        <is>
+          <t>Mauricio García Villegas aboga por volver a la razón “Antes de perder el juicio”</t>
+        </is>
+      </c>
+      <c r="E278" s="5" t="inlineStr">
+        <is>
+          <t>https://www.elespectador.com/el-magazin-cultural/mauricio-garcia-villegas-aboga-por-volver-a-la-razon-antes-de-perder-el-juicio/</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="6" t="inlineStr">
+        <is>
+          <t>20/05/2026 07:02 p. m.</t>
+        </is>
+      </c>
+      <c r="B279" s="6" t="inlineStr">
+        <is>
+          <t>Medio de Comunicación</t>
+        </is>
+      </c>
+      <c r="C279" s="6" t="inlineStr">
+        <is>
+          <t>El Espectador</t>
+        </is>
+      </c>
+      <c r="D279" s="7" t="inlineStr">
+        <is>
+          <t>Chancla de Call of Duty: ¿Cómo conseguir la nueva arma por el Día de la Madre?</t>
+        </is>
+      </c>
+      <c r="E279" s="8" t="inlineStr">
+        <is>
+          <t>https://www.elespectador.com/tecnologia/videojuegos/chancla-de-call-of-duty-como-conseguir-la-nueva-arma-por-el-dia-de-la-madre/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E278"/>
+  <autoFilter ref="A1:E279"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -8259,6 +8286,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E276" r:id="rId275"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E277" r:id="rId276"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E279" r:id="rId278"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/ultimahora.xlsx
+++ b/public/ultimahora.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Todas las noticias" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Todas las noticias'!$A$1:$E$279</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Todas las noticias'!$A$1:$E$234</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -65,12 +65,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5FBFF"/>
+        <fgColor rgb="00EAF2FB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAF2FB"/>
+        <fgColor rgb="00F5FBFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -515,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E279"/>
+  <dimension ref="A1:E234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 07:38 p. m.</t>
+          <t>22/05/2026 09:05 a. m.</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -565,24 +565,24 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Profesor en Bolívar se desplomó mientras cantaba ante sus alumnos: “Inesperada y sensible partida”</t>
+          <t>Las confesiones más polémicas de James Rodríguez en su documental: Zidane, Bolillo Gómez y más</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/profesor-en-bolivar-se-desplomo-mientras-cantaba-ante-sus-alumnos-inesperada-y-sensible-partida-rg10</t>
+          <t>https://www.semana.com/deportes/articulo/las-confesiones-mas-polemicas-de-james-rodriguez-en-su-documental-zidane-bolillo-gomez-y-mas/202659/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 07:26 p. m.</t>
+          <t>22/05/2026 08:21 a. m.</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -592,24 +592,24 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Ofrecen hasta $100 millones por autores de homicidio y desaparición de turistas en Buenaventura</t>
+          <t>Abelardo de la Espriella se dispara y le saca 20 puntos de ventaja a Iván Cepeda en la plataforma Kalshi</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/ofrecen-hasta-100-millones-por-autores-de-homicidio-y-desaparicion-de-turistas-en-buenaventura-rg10</t>
+          <t>https://www.semana.com/confidenciales/articulo/abelardo-de-la-espriella-se-dispara-y-le-saca-20-puntos-de-ventaja-a-ivan-cepeda-en-la-plataforma-kalshi/202600/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 07:15 p. m.</t>
+          <t>22/05/2026 08:07 a. m.</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -619,24 +619,24 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Los cinco mejores municipios para vivir pensionado cerca a Bogotá, según la IA</t>
+          <t>“Finjan sorpresa”: Santiago Alarcón habló sin filtros sobre su voto presidencial a pocos días de las elecciones</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/estilo-de-vida/los-cinco-mejores-municipios-para-vivir-pensionado-cerca-a-bogota-segun-la-ia-so35</t>
+          <t>https://www.semana.com/gente/articulo/finjan-sorpresa-santiago-alarcon-hablo-sin-filtros-sobre-su-voto-presidencial-a-pocos-dias-de-las-elecciones/202647/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 07:02 p. m.</t>
+          <t>22/05/2026 08:07 a. m.</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -646,24 +646,24 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Iván Cepeda 44,6%; Abelardo De La Espriella 31,6%; Paloma Valencia 14,0%: encuesta Invamer</t>
+          <t>Joven estaba extorsionando a su mamá y le pedía millonaria suma: Así fue como se descubrió todo en Pereira</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/ivan-cepeda-44-6-abelardo-de-la-espriella-31-6-paloma-valencia-14-0-encuesta-invamer-rg10</t>
+          <t>https://www.semana.com/nacion/bucaramanga/articulo/joven-estaba-extorsionando-a-su-mama-y-le-pedia-millonaria-suma-asi-fue-como-se-descubrio-todo-en-pereira/202611/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:52 p. m.</t>
+          <t>22/05/2026 08:07 a. m.</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -673,24 +673,24 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Denuncian agresión a adulto mayor en medio de las protestas en Bogotá: todo quedó grabado en video</t>
+          <t>Aida Quilcué hizo un llamado urgente por enfrentamientos entre indígenas del Cauca: “Busquemos todos los mecanismos”</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/bogota/denuncian-agresion-a-adulto-mayor-en-medio-de-las-protestas-en-bogota-todo-quedo-grabado-en-video-rg10</t>
+          <t>https://www.semana.com/politica/articulo/aida-quilcue-hizo-un-llamado-urgente-por-enfrentamientos-entre-indigenas-del-cauca-busquemos-todos-los-mecanismos/202625/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:43 p. m.</t>
+          <t>22/05/2026 08:07 a. m.</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -700,24 +700,24 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Resultados Chontico Noche último sorteo hoy, jueves 21 de mayo de 2026: números ganadores</t>
+          <t>La JEP acompañó a las víctimas de la Masacre del 16 de mayo de 1998 en Barrancabermeja</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/resultados-chontico-noche-ultimo-sorteo-hoy-jueves-21-de-mayo-de-2026-numeros-ganadores-so35</t>
+          <t>https://www.semana.com/nacion/bucaramanga/articulo/la-jep-acompano-a-las-victimas-de-la-masacre-del-16-de-mayo-de-1998-en-barrancabermeja/202637/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:38 p. m.</t>
+          <t>22/05/2026 08:07 a. m.</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -727,24 +727,24 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Los videos en los que Valentina Mor, influencer capturada en Medellín, se burlaba de las autoridades</t>
+          <t>MinDefensa alerta por guerra entre indígenas en Cauca que deja al menos seis muertos</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/los-videos-en-los-que-valentina-mor-influencer-capturada-en-medellin-se-burlaba-de-las-autoridades-rs15</t>
+          <t>https://www.semana.com/nacion/cali/articulo/mindefensa-alerta-por-guerra-entre-indigenas-en-cauca-que-deja-al-menos-seis-muertos/202622/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:47 p. m.</t>
+          <t>22/05/2026 07:07 a. m.</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -754,24 +754,24 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>¿Cómo va la seguridad alimentaria en Colombia? Hay persistencia de la brecha entre lo rural y urbano</t>
+          <t>Comunicado oficial del Manchester City sobre Pep Guardiola: decisión final con su futuro</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/como-va-la-seguridad-alimentaria-en-colombia-hay-persistencia-de-la-brecha-entre-lo-rural-y-urbano-rg10</t>
+          <t>https://www.semana.com/deportes/articulo/comunicado-oficial-del-manchester-city-sobre-pep-guardiola-decision-final-con-su-futuro/202654/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:29 p. m.</t>
+          <t>22/05/2026 07:07 a. m.</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -781,24 +781,24 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Movilidad en Bogotá EN VIVO hoy 21 de mayo: accidente de tránsito en Av. NQS y protestas en Cl 26</t>
+          <t>Donald Trump anuncia el envío de 5.000 soldados de EE. UU. a un país europeo, tras ejercicios nucleares de Rusia</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/bogota/movilidad-en-bogota-en-vivo-hoy-21-de-mayo-accidente-de-transito-en-av-nqs-y-protestas-en-cl-26-rg10</t>
+          <t>https://www.semana.com/mundo/articulo/donald-trump-anuncia-el-envio-de-5000-soldados-de-ee-uu-a-un-pais-europeo-tras-ejercicios-nucleares-de-rusia/202608/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:12 p. m.</t>
+          <t>22/05/2026 07:07 a. m.</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -808,24 +808,24 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Las propuestas económicas de la candidata Paloma Valencia de cara a las elecciones presidenciales</t>
+          <t>Yulixa Toloza: envían a la cárcel a los dos hombres que intentaron borrar la evidencia del vehículo</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/las-propuestas-economicas-de-la-candidata-paloma-valencia-de-cara-a-las-elecciones-presidenciales-rg10</t>
+          <t>https://www.semana.com/nacion/articulo/yulixa-toloza-envian-a-la-carcel-a-los-dos-hombres-que-intentaron-borrar-la-evidencia-del-vehiculo/202616/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:09 p. m.</t>
+          <t>22/05/2026 07:07 a. m.</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -835,24 +835,24 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Así puede saber si le revocaron un comparendo, según Mintransporte: hay casi 6 millones anulados</t>
+          <t>La sorprendente cifra en que se vendió el cuadro que Fernando Botero cambió por dos paquetes de cigarrillos</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/asi-puede-saber-si-le-revocaron-un-comparendo-segun-mintransporte-hay-casi-6-millones-anulados-so35</t>
+          <t>https://www.semana.com/cultura/arte/articulo/la-sorprendente-cifra-en-que-se-vendio-el-cuadro-que-fernando-botero-cambio-por-dos-paquetes-de-cigarrillos/202657/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:02 p. m.</t>
+          <t>22/05/2026 07:07 a. m.</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -862,24 +862,24 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Piden oración por actor de Sin Senos Sí Hay Paraíso: "Dios pronto lo tendrá de vuelta"</t>
+          <t>“Sería muy negativo pasar de la paz total a la guerra total”: la advertencia de Eduardo Pizarro, el hermano de Carlos Pizarro</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/entretenimiento/piden-oracion-por-actor-de-sin-senos-si-hay-paraiso-dios-pronto-lo-tendra-de-vuelta-rs15</t>
+          <t>https://www.semana.com/videos/articulo/seria-muy-negativo-pasar-de-la-paz-total-a-la-guerra-total-la-advertencia-de-eduardo-pizarro-el-hermano-de-carlos-pizarro/202638/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:42 p. m.</t>
+          <t>22/05/2026 07:07 a. m.</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -889,24 +889,24 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Caso Yulixa Toloza: Venezuela revela detalles sobre los tres capturados por su presunta vinculación</t>
+          <t>Francia Márquez reaccionó a pelea entre indígenas misak y nasa en el Cauca que deja cuatro muertos: “Me duele en el alma”</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/bogota/caso-yulixa-toloza-venezuela-revela-detalles-sobre-los-tres-capturados-por-su-presunta-vinculacion-rg10</t>
+          <t>https://www.semana.com/politica/articulo/francia-marquez-reacciono-a-pelea-entre-indigenas-misak-y-nasa-en-el-cauca-que-deja-cuatro-muertos-me-duele-en-el-alma/202619/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:31 p. m.</t>
+          <t>22/05/2026 06:07 a. m.</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Esta es la fecha en la que el presidente Gustavo Petro se reunirá con el Papa León XIV</t>
+          <t>Anuncian sorpresivo simulacro aéreo de evacuación de la embajada de EE. UU. en Caracas, tras 5 meses de la captura de Maduro</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/el-presidente-gustavo-petro-se-reunira-con-el-papa-leon-xiv-en-el-vaticano-el-2-de-julio-rg10</t>
+          <t>https://www.semana.com/mundo/articulo/anuncian-sorpresivo-simulacro-aereo-de-evacuacion-de-la-embajada-de-ee-uu-en-caracas-tras-5-meses-de-la-captura-de-maduro/202629/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:20 p. m.</t>
+          <t>22/05/2026 06:07 a. m.</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -943,24 +943,24 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Cine de terror en Bogotá: desde Medellín llega la 3ª Muestra Fantasmagoría a la Cinemateca</t>
+          <t>Escandalosos audios sexuales que tienen a Javier Milei en el ojo del huracán en Argentina</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/entretenimiento/muestra-fantasmagoria-2026-cine-de-terror-en-la-cinemateca-de-bogota-programacion-completa-rg10</t>
+          <t>https://www.semana.com/mundo/articulo/escandalosos-audios-sexuales-que-tienen-a-javier-milei-en-el-ojo-del-huracan-en-argentina/202618/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:02 p. m.</t>
+          <t>22/05/2026 06:07 a. m.</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -970,24 +970,24 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Marco Rubio dice que Raúl Castro es un fugitivo: "No voy a hablar de cómo lo traeríamos aquí"</t>
+          <t>Ahorrar en tiempos de redes: la batalla financiera de los jóvenes colombianos</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/mundo/marco-rubio-dice-que-raul-castro-es-un-fugitivo-de-la-justicia-estadounidense-no-voy-a-hablar-de-como-lo-traeriamos-aqui-cb20</t>
+          <t>https://www.semana.com/economia/macroeconomia/articulo/ahorrar-en-tiempos-de-redes-la-batalla-financiera-de-los-jovenes-colombianos/202633/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 03:55 p. m.</t>
+          <t>22/05/2026 06:07 a. m.</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -997,24 +997,24 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Resultados Super Astro Sol hoy, jueves 21 de mayo de 2026: números ganadores</t>
+          <t>Así va la recta final por la Presidencia: candidatos llaman a las plazas y atraen electorado a último momento</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/resultados-super-astro-sol-hoy-jueves-21-de-mayo-de-2026-numeros-ganadores-so35</t>
+          <t>https://www.semana.com/politica/articulo/asi-va-la-recta-final-por-la-presidencia-candidatos-llaman-a-las-plazas-y-atraen-electorado-a-ultimo-momento/202656/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 03:36 p. m.</t>
+          <t>22/05/2026 06:07 a. m.</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -1024,26 +1024,22 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>La champeta fue declarada Patrimonio Cultural Inmaterial de Colombia</t>
+          <t>“Una masacre auspiciada por el Cric”: líder indígena misak revela escalofriantes detalles de batalla campal que dejó cuatro muertos</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/la-champeta-fue-declarada-patrimonio-cultural-inmaterial-de-colombia-rg10</t>
+          <t>https://www.semana.com/nacion/cali/articulo/una-masacre-auspiciada-por-el-cric-lider-indigena-misak-revela-escalofriantes-detalles-de-batalla-campal-que-dejo-cuatro-muertos/202606/</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>21/05/2026 03:32 p. m.</t>
-        </is>
-      </c>
+      <c r="A20" s="3" t="inlineStr"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -1051,26 +1047,22 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Álbum Panini 2026: ¿cuándo sale el kit de actualización y cuánto costará?</t>
+          <t>La “cosa perdida”: la denigrante forma en que se referían los dueños del centro estético a Yulixa Toloza</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/lomastrinado/album-panini-2026-cuando-sale-el-kit-de-actualizacion-y-cuanto-costara-so35</t>
+          <t>https://www.semana.com/nacion/articulo/la-cosa-perdida-la-denigrante-forma-en-como-se-referian-los-duenos-del-centro-estetico-a-yulixa-toloza/202648/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>21/05/2026 03:26 p. m.</t>
-        </is>
-      </c>
+      <c r="A21" s="6" t="inlineStr"/>
       <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -1078,26 +1070,22 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Resultados Dorado Tarde, último sorteo jueves 21 de mayo de 2026: números ganadores</t>
+          <t>Convocatoria oficial de Inglaterra para el Mundial 2026: afuera Cole Palmer y Alexander-Arnold</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/dorado-tarde-21-de-mayo-de-2026-cuales-son-los-numeros-ganadores-so35</t>
+          <t>https://www.semana.com/deportes/articulo/convocatoria-oficial-de-inglaterra-para-el-mundial-2026-afuera-cole-palmer-y-alexander-arnold/202622/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>21/05/2026 03:25 p. m.</t>
-        </is>
-      </c>
+      <c r="A22" s="3" t="inlineStr"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -1105,26 +1093,22 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Expectactiva por lista de 26 de la Selección Colombia para el Mundial 2026; atentos a este ejercicio</t>
+          <t>Inteligencia artificial predijo la lista final de Colombia al Mundial 2026: borró a un histórico</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/golcaracol/seleccion-colombia/expectactiva-por-lista-de-26-de-la-seleccion-colombia-para-el-mundial-2026-atentos-a-este-ejercicio-rg10</t>
+          <t>https://www.semana.com/deportes/articulo/inteligencia-artificial-predijo-la-lista-final-de-colombia-al-mundial-2026-borro-a-un-historico/202614/</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>21/05/2026 03:23 p. m.</t>
-        </is>
-      </c>
+      <c r="A23" s="6" t="inlineStr"/>
       <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -1132,26 +1116,22 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>La intentó robar y la atacó con un machete en TransMilenio: grave caso de agresión en Bogotá</t>
+          <t>Sebastián Villa: golazo y asistencia en Libertadores que resuenan en Selección Colombia</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/bogota/la-intento-robar-y-la-ataco-con-un-machete-en-transmilenio-grave-caso-de-agresion-en-bogota-rg10</t>
+          <t>https://www.semana.com/deportes/articulo/sebastian-villa-golazo-y-asistencia-en-libertadores-que-resuenan-en-seleccion-colombia/202655/</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>21/05/2026 03:16 p. m.</t>
-        </is>
-      </c>
+      <c r="A24" s="3" t="inlineStr"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -1159,26 +1139,22 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Anuncio de última hora para el Mundial 2026; los hinchas de la Selección Colombia celebran</t>
+          <t>Selección Colombia: Néstor Lorenzo borraría de la lista al Mundial a un recién campeón en Europa</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/golcaracol/seleccion-colombia/anuncio-de-ultima-hora-para-el-mundial-2026-los-hinchas-de-la-seleccion-colombia-celebran-cb20</t>
+          <t>https://www.semana.com/deportes/articulo/seleccion-colombia-nestor-lorenzo-borraria-de-la-lista-al-mundial-a-un-recien-campeon-en-europa/202606/</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>21/05/2026 03:12 p. m.</t>
-        </is>
-      </c>
+      <c r="A25" s="6" t="inlineStr"/>
       <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -1186,26 +1162,22 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Esta entidad ofrece crédito de vivienda con tasas desde el 10,7% en Colombia: no es el FNA</t>
+          <t>Estos son los escuderos de Erling Haaland en Noruega para el Mundial 2026: convocatoria oficial con varias figuras</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/esta-entidad-ofrece-credito-de-vivienda-con-tasas-desde-el-10-7-en-colombia-no-es-el-fna-so35</t>
+          <t>https://www.semana.com/deportes/articulo/estos-son-los-escuderos-de-erling-haaland-en-noruega-para-el-mundial-2026-convocatoria-oficial-con-varias-figuras/202648/</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>21/05/2026 03:03 p. m.</t>
-        </is>
-      </c>
+      <c r="A26" s="3" t="inlineStr"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -1213,26 +1185,22 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Vea el doblete de Cristiano Ronaldo  en Al Nassr vs. Damac para ganar el título de la Liga Saudí</t>
+          <t>Carlos Fernando Motoa radicó proyecto para tumbar la ley de encuestas “por el bien del país”</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/golcaracol/vea-el-doblete-de-cristiano-ronaldo-contra-damac-para-ganar-el-titulo-de-la-liga-saudi-rg10</t>
+          <t>https://www.semana.com/politica/articulo/carlos-fernando-motoa-radico-proyecto-para-tumbar-la-ley-de-encuestas-por-el-bien-del-pais/202611/</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>21/05/2026 03:01 p. m.</t>
-        </is>
-      </c>
+      <c r="A27" s="6" t="inlineStr"/>
       <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -1240,26 +1208,22 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Cristiano Ronaldo es campeón de la Liga de Arabia con Al Nassr; anotó dos goles en 4-1 sobre Damac</t>
+          <t>Tras su desplome en las encuestas, Paloma Valencia decide pelear con Invamer y califica como “falso” el resultado de ese estudio</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/golcaracol/cristiano-ronaldo-es-campeon-de-la-liga-de-arabia-con-al-nassr-anoto-dos-goles-en-4-1-sobre-damac-rg10</t>
+          <t>https://www.semana.com/politica/articulo/tras-su-desplome-en-las-encuestas-paloma-valencia-decide-pelear-con-invamer-y-califica-como-falso-el-resultado-de-ese-estudio/202632/</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>21/05/2026 07:35 p. m.</t>
-        </is>
-      </c>
+      <c r="A28" s="3" t="inlineStr"/>
       <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -1267,26 +1231,22 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Encuesta Invamer: escenarios segunda vuelta entre Cepeda, De La Espriella, Paloma Valencia y Fajardo</t>
+          <t>Escándalo: funcionario del Dane denunció presunta red de certificaciones irregulares y conflictos de interés bajo la dirección de Juan Daniel Oviedo</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/elecciones/promesas-y-propuestas/encuesta-invamer-escenarios-segunda-vuelta-entre-cepeda-de-la-espriella-paloma-valencia-y-fajardo-so35</t>
+          <t>https://www.semana.com/politica/articulo/escandalo-funcionario-del-dane-denuncio-presunta-red-de-certificaciones-irregulares-y-conflictos-de-interes-bajo-la-direccion-de-juan-daniel-oviedo/202602/</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>21/05/2026 07:23 p. m.</t>
-        </is>
-      </c>
+      <c r="A29" s="6" t="inlineStr"/>
       <c r="B29" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -1294,26 +1254,22 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Yulixa se arrepintió: los testimonios y rastros clave que revelan qué pasó tras cirugía</t>
+          <t>“Me arrodillo”: Gustavo Petro hizo un fuerte llamado de atención a la Corte Constitucional por retrasar su reforma pensional</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/judicial/yulixa-se-arrepintio-los-testimonios-y-rastros-clave-que-revelan-que-paso-tras-cirugia-rg10</t>
+          <t>https://www.semana.com/politica/articulo/me-arrodillo-gustavo-petro-dio-un-fuerte-discurso-contra-la-corte-constitucional-por-retrasar-su-reforma-pensional/202642/</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>21/05/2026 07:17 p. m.</t>
-        </is>
-      </c>
+      <c r="A30" s="3" t="inlineStr"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -1321,26 +1277,22 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Más de 9.200 testigos electorales en el exterior fueron acreditados por el CNE para las elecciones</t>
+          <t>Tenían casi una tonelada de marihuana escondida en una casa de Bogotá: así cayó la red</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/elecciones/mas-de-9-200-testigos-electorales-en-el-exterior-fueron-acreditados-por-el-cne-para-las-elecciones-rg10</t>
+          <t>https://www.semana.com/nacion/bogota/articulo/tenian-casi-una-tonelada-de-marihuana-escondida-en-una-casa-de-bogota-asi-cayo-la-red/202626/</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>21/05/2026 07:04 p. m.</t>
-        </is>
-      </c>
+      <c r="A31" s="6" t="inlineStr"/>
       <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -1348,24 +1300,24 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Encuesta Invamer: Cepeda obtiene 44,6 %; De La Espriella, 31,6 % y Paloma Valencia, 14 %</t>
+          <t>¿Se mueve el Día del Padre en Colombia? Fenalco quiere cambiar la fecha por esta razón</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/elecciones/encuesta-invamer-cepeda-obtiene-44-6-de-la-espriella-31-6-y-paloma-valencia-14-so35</t>
+          <t>https://www.semana.com/nacion/articulo/se-mueve-el-dia-del-padre-en-colombia-fenalco-quiere-cambiar-la-fecha-por-esta-razon/202622/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:51 p. m.</t>
+          <t>22/05/2026 09:05 a. m.</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1375,24 +1327,24 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Cristiano Ronaldo conquista la liga de Arabia a sus 40 años antes del Mundial</t>
+          <t>Mayo Junco: la voz cartagenera que mantiene vivo el bullerengue</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/deportes/futbol/cristiano-ronaldo-conquista-la-liga-de-arabia-a-sus-40-anos-antes-del-mundial-cb20</t>
+          <t>https://www.eluniversal.com.co/farandula/2026/05/22/mayo-junco-la-voz-cartagenera-que-mantiene-vivo-el-bullerengue/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:47 p. m.</t>
+          <t>22/05/2026 09:05 a. m.</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -1402,24 +1354,24 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>“Es deplorable que eso haya sucedido”, Benedetti tras ataque a sede de Paloma Valencia</t>
+          <t>Farándula</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/es-deplorable-que-eso-haya-sucedido-benedetti-tras-ataque-a-sede-de-paloma-valencia-rg10</t>
+          <t>https://www.eluniversal.com.co/farandula/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:31 p. m.</t>
+          <t>22/05/2026 08:55 a. m.</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1429,24 +1381,24 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Néstor Lorenzo tomó decisión con Durán en la convocatoria para el Mundial</t>
+          <t>La historia de ‘Pluma Blanca’, el jefe del Clan del Golfo que se infiltró en la Fuerza Pública</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/deportes/futbol/copa-mundial-de-la-fifa-2026/nestor-lorenzo-tomo-decision-con-duran-en-la-convocatoria-para-el-mundial-so35</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/22/la-historia-de-pluma-blanca-el-jefe-del-clan-del-golfo-que-se-infiltro-en-la-fuerza-publica/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:06 p. m.</t>
+          <t>22/05/2026 08:50 a. m.</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -1456,24 +1408,24 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>"Grupo armado y política electoral detrás": Benedetti sobre enfrentamientos entre indígenas en Cauca</t>
+          <t>¿Qué dijo? Pep Guardiola tomó drástica decisión en el Manchester City</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/grupo-armado-y-politica-electoral-detras-benedetti-sobre-enfrentamientos-entre-indigenas-en-cauca-rg10</t>
+          <t>https://www.eluniversal.com.co/deportes/2026/05/22/que-dijo-pep-guardiola-tomo-drastica-decision-en-el-manchester-city/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:51 p. m.</t>
+          <t>22/05/2026 08:50 a. m.</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1483,24 +1435,24 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Alcaldía de Cali confirma levantamiento total de bloqueos y retoma diálogo con transportadores</t>
+          <t>Deportes</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/regiones/pacifico/alcaldia-de-cali-confirma-levantamiento-total-de-bloqueos-y-retoma-dialogo-con-transportadores-rg10</t>
+          <t>https://www.eluniversal.com.co/deportes/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:46 p. m.</t>
+          <t>22/05/2026 08:31 a. m.</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -1510,24 +1462,24 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>ExxonMobil está en negociaciones para extraer petróleo de Venezuela, según el New York Times</t>
+          <t>Las estrellas de Inglaterra que no fueron convocadas para el Mundial 2026</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/mundo/exxonmobil-esta-en-negociaciones-para-extraer-petroleo-de-venezuela-segun-el-new-york-times-cb20</t>
+          <t>https://www.eluniversal.com.co/deportes/2026/05/22/las-estrellas-de-inglaterra-que-no-fueron-convocadas-para-el-mundial-2026/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:40 p. m.</t>
+          <t>22/05/2026 08:06 a. m.</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1537,24 +1489,24 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Millonarias deudas dejan sin atención de salud mental a usuarios de Nueva EPS en Manizales</t>
+          <t>“Será mi último partido esta temporada como entrenador del Real Madrid”: Álvaro Arbeloa</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/salud/millonarias-deudas-dejan-sin-atencion-de-salud-mental-a-usuarios-de-nueva-eps-en-manizales-rg10</t>
+          <t>https://www.eluniversal.com.co/deportes/2026/05/22/sera-mi-ultimo-partido-esta-temporada-como-entrenador-del-real-madrid-alvaro-arbeloa/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:27 p. m.</t>
+          <t>22/05/2026 07:36 a. m.</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -1564,24 +1516,24 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Cuatro muertos y más de 44 heridos dejan enfrentamientos entre indígenas en Silvia, Cauca</t>
+          <t>Yulixa Toloza: a la cárcel 2 hombres por desaparecer carro donde transportaron a la mujer</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/regiones/pacifico/cuatro-muertos-y-mas-de-44-heridos-dejan-enfrentamientos-entre-indigenas-en-silvia-cauca-rg10</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/22/yulixa-toloza-a-la-carcel-2-hombres-por-desaparecer-carro-donde-transportaron-a-la-mujer/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 07:34 p. m.</t>
+          <t>22/05/2026 07:36 a. m.</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1596,19 +1548,19 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Más de 16 años de cárcel a Sandra Mosquera por quitarle la vida a su marido</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/mas-de-16-anos-de-carcel-a-sandra-mosquera-por-quitarle-la-vida-a-su-marido/</t>
+          <t>https://www.eluniversal.com.co/colombia/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 07:31 p. m.</t>
+          <t>22/05/2026 07:31 a. m.</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -1623,19 +1575,19 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Siete años después, Tayron Guerrero recibe otra oportunidad en la MLB</t>
+          <t>Municipios de Bolívar que no tendrán luz el sábado 23 de mayo de 2026</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/deportes/2026/05/21/siete-anos-despues-tayron-guerrero-recibe-otra-oportunidad-en-la-mlb/</t>
+          <t>https://www.eluniversal.com.co/regional/bolivar/2026/05/22/municipios-de-bolivar-que-no-tendran-luz-el-sabado-23-de-mayo-de-2026/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 07:05 p. m.</t>
+          <t>22/05/2026 07:31 a. m.</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1650,19 +1602,19 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>EE. UU. captura a mujer vinculada al régimen cubano: es hermana de ejecutivo militar</t>
+          <t>Nascar: ¿De qué murió Kyle Busch? esto es lo que se sabe</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/mundo/2026/05/21/ee-uu-captura-a-mujer-vinculada-al-regimen-cubano-es-hermana-de-ejecutivo-militar/</t>
+          <t>https://www.eluniversal.com.co/deportes/2026/05/22/nascar-de-que-murio-kyle-busch-esto-es-lo-que-se-sabe/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 07:02 p. m.</t>
+          <t>22/05/2026 07:18 a. m.</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -1677,19 +1629,19 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Redes estallan por comentario de Yina Calderón sobre Alejandro Estrada</t>
+          <t>Cartagena tendrá cortes de luz este sábado 23 de mayo: barrios afectados</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/farandula/2026/05/21/redes-estallan-por-comentario-de-yina-calderon-sobre-alejandro-estrada/</t>
+          <t>https://www.eluniversal.com.co/cartagena/2026/05/22/cartagena-tendra-cortes-de-luz-este-sabado-23-de-mayo-barrios-afectados/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:50 p. m.</t>
+          <t>22/05/2026 07:10 a. m.</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1704,19 +1656,19 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Así jugará Real Cartagena, ya finalista, ante el Barranquilla FC</t>
+          <t>Ella era Yudis María Velásquez, la mujer que sicarios mataron en San Jacinto</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/deportes/2026/05/21/asi-jugara-real-cartagena-ya-finalista-ante-el-barranquilla-fc/</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/22/ella-era-yudis-maria-velasquez-sicarios-le-quitaron-la-vida-a-la-mujer-en-san-jacinto/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:30 p. m.</t>
+          <t>22/05/2026 12:40 a. m.</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
@@ -1731,19 +1683,19 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Real Cartagena: el día en que la hinchada volvió a celebrar llegar a una final</t>
+          <t>Prevén lloviznas en la mañana y altas temperaturas en Cartagena este 22 de mayo</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/deportes/2026/05/21/real-cartagena-el-dia-en-que-la-hinchada-volvio-a-celebrar-llegar-a-una-final/</t>
+          <t>https://www.eluniversal.com.co/cartagena/2026/05/22/preven-lloviznas-en-la-manana-y-altas-temperaturas-en-cartagena-este-22-de-mayo/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:03 p. m.</t>
+          <t>22/05/2026 12:05 a. m.</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1758,19 +1710,19 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Cayó ‘el Chivato’ en Bolívar: lo sorprendieron armado y con amplio prontuario</t>
+          <t>Gustavo Petro se reunirá nuevamente con el papa León XIV: esta es la fecha</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/cayo-el-chivato-en-bolivar-lo-sorprendieron-armado-y-con-amplio-prontuario-judicial/</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/22/gustavo-petro-se-reunira-nuevamente-con-el-papa-leon-xiv-esta-es-la-fecha/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:54 p. m.</t>
+          <t>22/05/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -1785,19 +1737,19 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Real Cartagena ya es finalista del Torneo BetPlay, empató el Unión Magdalena</t>
+          <t>Continúan los cortes de agua programados en Cartagena: Acuacar explica por qué</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/deportes/2026/05/21/real-cartagena-ya-es-finalista-del-torneo-betplay-empato-el-union-magdalena/</t>
+          <t>https://www.eluniversal.com.co/cartagena/2026/05/22/continuan-los-corte-de-agua-programados-en-cartagena-acuacar-explica-por-que/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:54 p. m.</t>
+          <t>22/05/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1812,19 +1764,19 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Deportes</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/deportes/</t>
+          <t>https://www.eluniversal.com.co/cartagena/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:08 p. m.</t>
+          <t>21/05/2026 11:26 p. m.</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -1839,19 +1791,19 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>¿Karol G en Cartagena? Esto dijo Dumek Turbay sobre una posible presentación</t>
+          <t>“Me arrodillo”: Petro pide al Consejo de Estado proteger las pensiones de los colombianos</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/farandula/2026/05/21/karol-g-en-cartagena-esto-dijo-dumek-turbay-sobre-una-posible-presentacion/</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/21/me-arrodillo-petro-pide-al-consejo-de-estado-proteger-las-pensiones-de-los-colombianos/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:08 p. m.</t>
+          <t>21/05/2026 09:20 p. m.</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -1866,19 +1818,19 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Farándula</t>
+          <t>Caen ‘Los Rompecadenas’ tras hurtar a turistas en el Centro Histórico de Cartagena</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/farandula/</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/caen-los-rompecadenas-tras-hurtar-a-turistas-en-el-centro-historico/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:55 p. m.</t>
+          <t>21/05/2026 08:24 p. m.</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -1893,19 +1845,19 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>2 hombres enviados a la cárcel por agresiones contra sus familiares en Bolívar</t>
+          <t>Video: cayó alias ‘Joselito’ con un revólver y con municiones en La Esperanza</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/2-hombres-enviados-a-la-carcel-por-agresiones-contra-sus-familiares-en-bolivar/</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/video-capturan-a-alias-joselito-con-municiones-en-la-esperanza/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:43 p. m.</t>
+          <t>21/05/2026 07:34 p. m.</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -1920,19 +1872,19 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Cayó banda de expendedores que operaba cerca de colegios y canchas en Mompox</t>
+          <t>Más de 16 años de cárcel a Sandra Mosquera por quitarle la vida de un hombre</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/cayo-banda-de-expendedores-que-operaba-cerca-de-colegios-y-canchas-en-mompox/</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/mas-de-16-anos-de-carcel-a-sandra-mosquera-por-quitarle-la-vida-a-su-marido/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:39 p. m.</t>
+          <t>21/05/2026 06:03 p. m.</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -1947,19 +1899,19 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Encuesta Guarumo y Ecoanalítica: así están Cepeda, Abelardo y Paloma a 10 días de la primera vuelta</t>
+          <t>Cayó ‘el Chivato’ en Bolívar: lo sorprendieron armado y con amplio prontuario</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/2026/05/21/encuesta-guarumo-y-ecoanalitica-asi-estan-cepeda-de-la-espriella-y-paloma-valencia-a-10-dias-de-la-primera-vuelta/</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/cayo-el-chivato-en-bolivar-lo-sorprendieron-armado-y-con-amplio-prontuario-judicial/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:39 p. m.</t>
+          <t>21/05/2026 04:55 p. m.</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -1974,19 +1926,19 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>2 hombres enviados a la cárcel por agresiones contra sus familiares en Bolívar</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/2-hombres-enviados-a-la-carcel-por-agresiones-contra-sus-familiares-en-bolivar/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:38 p. m.</t>
+          <t>21/05/2026 04:43 p. m.</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -2001,21 +1953,17 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Accidente de tránsito frente al Mercado de Bazurto genera monumental trancón</t>
+          <t>Cayó banda de expendedores que operaba cerca de colegios y canchas en Mompox</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/accidente-de-transito-frente-al-mercado-de-bazurto-genera-monumental-trancon/</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/cayo-banda-de-expendedores-que-operaba-cerca-de-colegios-y-canchas-en-mompox/</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>21/05/2026 04:23 p. m.</t>
-        </is>
-      </c>
+      <c r="A56" s="3" t="inlineStr"/>
       <c r="B56" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -2028,19 +1976,19 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Dadis suspendió centro de estética en Cartagena tras inspección</t>
+          <t>Premios Excelencia El Universal 2026: categorías, calendario y cómo participar</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/cartagena/2026/05/21/dadis-suspendio-centro-de-estetica-en-cartagena-por-realizar-procedimientos-invasivos-sin-habilitacion/</t>
+          <t>https://www.eluniversal.com.co/cartagena/2026/05/20/premios-excelencia-el-universal-2026-categorias-calendario-y-como-participar/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:23 p. m.</t>
+          <t>22/05/2026 09:04 a. m.</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
@@ -2050,24 +1998,24 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Hansi Flick dio noticias sobre el mercado de pases del Barcelona; empezó a mover fichas</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/cartagena/</t>
+          <t>https://www.noticiascaracol.com/golcaracol/hansi-flick-dio-noticias-sobre-el-mercado-de-pases-del-barcelona-empezo-a-mover-fichas-cb20</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:20 p. m.</t>
+          <t>22/05/2026 09:02 a. m.</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2077,24 +2025,24 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Miguel Díaz-Canel desafía a Donald Trump con contundente mensaje sobre Cuba</t>
+          <t>Manchester United eligió a su entrenador para la próxima temporada; "lucharemos por todo"</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/mundo/2026/05/21/miguel-diaz-canel-desafia-a-donald-trump-con-contundente-mensaje-sobre-cuba/</t>
+          <t>https://www.noticiascaracol.com/golcaracol/manchester-united-eligio-a-su-entrenador-para-la-proxima-temporada-lucharemos-por-todo-cb20</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:07 p. m.</t>
+          <t>22/05/2026 08:43 a. m.</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -2104,24 +2052,24 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Caso Yulixa Toloza: Fiscalía rastreó a implicados mediante plataforma</t>
+          <t>Precio del dólar en Colombia hoy, 22 de mayo de 2026: Tasa Representativa del Mercado este viernes</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/2026/05/21/caso-yulixa-toloza-fiscalia-rastreo-a-implicados-mediante-plataforma/</t>
+          <t>https://www.noticiascaracol.com/economia/precio-del-dolar-en-colombia-hoy-22-de-mayo-de-2026-tasa-representativa-del-mercado-este-viernes-so35</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:04 p. m.</t>
+          <t>22/05/2026 08:39 a. m.</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2131,24 +2079,24 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Por error, hombre arrolló con camión y le quitó la vida a su esposa Paulina Castro</t>
+          <t>Pep Guardiola ya tiene nuevo trabajo, tras confirmarse su salida del Manchester City</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/por-error-hombre-arrollo-con-camion-y-le-quito-la-vida-a-su-esposa-paulina-castro/</t>
+          <t>https://www.noticiascaracol.com/golcaracol/pep-guardiola-ya-tiene-nuevo-trabajo-tras-confirmarse-su-salida-del-manchester-city-cb20</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 03:56 p. m.</t>
+          <t>22/05/2026 08:34 a. m.</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -2158,24 +2106,24 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Vandalizan sede de campaña de Paloma Valencia durante manifestaciones en Bogotá</t>
+          <t>Chats revelan cómo se referían a Yulixa Toloza los sospechosos capturados por su muerte</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/2026/05/21/vandalizan-sede-de-campana-de-paloma-valencia-durante-manifestaciones-en-bogota/</t>
+          <t>https://www.noticiascaracol.com/colombia/bogota/chats-revelan-como-se-referian-a-yulixa-toloza-los-sospechosos-capturados-por-su-muerte-rg10</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 03:43 p. m.</t>
+          <t>22/05/2026 08:29 a. m.</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2185,24 +2133,24 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Ejemplar condena contra un mototaxista que agredió y abusó de su pasajera en Turbaco</t>
+          <t>Thomas Tuchel explicó por qué no convocó a Alexander-Arnold, Palmer, Foden y Maguire</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/ejemplar-condena-contra-un-mototaxista-que-agredio-y-abuso-de-su-pasajera-en-turbaco/</t>
+          <t>https://www.noticiascaracol.com/golcaracol/thomas-tuchel-explico-por-que-no-convoco-a-alexander-arnold-palmer-foden-y-maguire-cb20</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 03:39 p. m.</t>
+          <t>22/05/2026 08:22 a. m.</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -2212,22 +2160,26 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Así hallaron a pescador tras 24 horas desaparecido en el mar de Cartagena</t>
+          <t>Hombre arremetió contra grúa en medio de operativo en Medellín y dejó gravemente herido al conductor</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/21/asi-hallaron-a-pescador-tras-24-horas-desaparecido-en-el-mar-de-cartagena/</t>
+          <t>https://www.noticiascaracol.com/colombia/hombre-arremetio-contra-grua-en-medio-de-operativo-en-medellin-y-dejo-gravemente-herido-al-conductor-so35</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr"/>
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>22/05/2026 07:39 a. m.</t>
+        </is>
+      </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -2235,24 +2187,24 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Premios Excelencia El Universal 2026: categorías, calendario y cómo participar</t>
+          <t>Seis fallecidos y más de 100 heridos: ¿qué desató pelea entre indígenas Misak y Nasa en el Cauca?</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/cartagena/2026/05/20/premios-excelencia-el-universal-2026-categorias-calendario-y-como-participar/</t>
+          <t>https://www.noticiascaracol.com/colombia/grave-enfrentamiento-entre-indigenas-deja-seis-fallecidos-y-mas-de-100-heridos-que-desato-la-pelea-en-silvia-cauca-rg10</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 07:31 p. m.</t>
+          <t>22/05/2026 07:17 a. m.</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
@@ -2262,24 +2214,24 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Nueva Encuesta presidencial: Iván Cepeda lidera, pero perdería en segunda vuelta</t>
+          <t>ICE detiene a hermana de ejecutiva de empresa militar cubana Gaesa y le revoca la residencia</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/21/nueva-encuesta-presidencial-ivan-cepeda-lidera-pero-perderia-en-segunda-vuelta/</t>
+          <t>https://www.noticiascaracol.com/mundo/ice-detiene-a-hermana-de-ejecutiva-de-empresa-militar-cubana-gaesa-y-le-revoca-la-residencia-cb20</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 07:31 p. m.</t>
+          <t>22/05/2026 07:05 a. m.</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2289,24 +2241,24 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Se hundió la Ley Borrón y Cuenta Nueva 2.0, proyecto que buscaba eliminar reportes en Datacrédito</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/</t>
+          <t>https://www.noticiascaracol.com/economia/se-hundio-la-ley-borron-y-cuenta-nueva-2-0-proyecto-que-buscaba-eliminar-reportes-en-datacredito-so35</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 07:14 p. m.</t>
+          <t>22/05/2026 07:04 a. m.</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -2316,24 +2268,24 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Así operaba la red señalada de estafar a 280 personas con paquetes turísticos falsos en Bucaramanga</t>
+          <t>Manchester City ya tendría el reemplazo de Pep Guardiola; el técnico que suena con fuerza</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/judicial/2026/05/21/asi-operaba-la-red-senalada-de-estafar-a-280-personas-con-paquetes-turisticos-falsos-en-bucaramanga/</t>
+          <t>https://www.noticiascaracol.com/golcaracol/manchester-city-ya-tendria-el-reemplazo-de-pep-guardiola-el-tecnico-que-suena-con-fuerza-cb20</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 07:14 p. m.</t>
+          <t>22/05/2026 05:49 a. m.</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2343,24 +2295,24 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Judicial</t>
+          <t>James Rodríguez y las lecciones de Cristiano Ronaldo; "talento sin trabajo, no sirve"</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/judicial/</t>
+          <t>https://www.noticiascaracol.com/golcaracol/colombianos-en-el-exterior/james-rodriguez-y-las-lecciones-de-cristiano-ronaldo-talento-sin-trabajo-no-sirve-rg10</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:50 p. m.</t>
+          <t>22/05/2026 05:35 a. m.</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -2370,24 +2322,24 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Último resultado de Chontico Noche del jueves 21 de mayo de 2026</t>
+          <t>Los conflictos de James Rodríguez con técnico de Bayern Múnich; "¿voy a ir al Tour de Francia?"</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/loterias/2026/05/21/ultimo-resultado-de-chontico-noche-del-jueves-21-de-mayo-de-2026/</t>
+          <t>https://www.noticiascaracol.com/golcaracol/colombianos-en-el-exterior/los-conflictos-de-james-rodriguez-con-tecnico-de-bayern-munich-voy-a-ir-al-tour-de-francia-rg10</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:50 p. m.</t>
+          <t>22/05/2026 09:02 a. m.</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2397,24 +2349,24 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Loterias</t>
+          <t>OMS confirma otro caso de hantavirus en crucero MV Hondius: contagios suben a 12</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/loterias/</t>
+          <t>https://www.bluradio.com/salud/oms-confirma-otro-caso-de-hantavirus-en-crucero-mv-hondius-contagios-suben-a-12-cb20</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:20 p. m.</t>
+          <t>22/05/2026 08:55 a. m.</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -2424,24 +2376,24 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Mujer reportada como desaparecida fue hallada muerta en el río Magdalena</t>
+          <t>Salud mental infantil gana terreno en Colombia: inauguran en Bogotá centro de regulación emocional</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/judicial/2026/05/21/mujer-reportada-como-desaparecida-fue-hallada-muerta-en-el-rio-magdalena/</t>
+          <t>https://www.bluradio.com/salud/salud-mental-infantil-gana-terreno-en-colombia-inauguran-en-bogota-centro-de-regulacion-emocional-rg10</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:14 p. m.</t>
+          <t>22/05/2026 08:38 a. m.</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2451,24 +2403,24 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Horóscopo del viernes 22 de mayo de 2026: Predicciones y el vuelo de las ideas</t>
+          <t>Invamer revela una segunda vuelta marcada por el voto Petro vs. antiPetro</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/entretenimiento/tendencias/2026/05/21/horoscopo-del-viernes-22-de-mayo-de-2026-predicciones-y-el-vuelo-de-las-ideas/</t>
+          <t>https://www.bluradio.com/nacion/elecciones/invamer-revela-una-segunda-vuelta-marcada-por-el-voto-petro-vs-antipetro-pr30</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:14 p. m.</t>
+          <t>22/05/2026 08:37 a. m.</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
@@ -2478,24 +2430,24 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Tendencias</t>
+          <t>Ejército busca retirados de fuerzas especiales para reentrenar soldados</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/entretenimiento/tendencias/</t>
+          <t>https://www.bluradio.com/nacion/ejercito-busca-retirados-de-fuerzas-especiales-para-reentrenar-soldados-rg10</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:20 p. m.</t>
+          <t>22/05/2026 08:25 a. m.</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2505,24 +2457,24 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>En fotos: así quedó la sede de Paloma Valencia tras ataque vandálico en Bogotá</t>
+          <t>Procuraduría pide reforzar gestión del riesgo para garantizar elecciones seguras</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/21/en-fotos-asi-quedo-la-sede-de-paloma-valencia-tras-ataque-vandalico-en-bogota/</t>
+          <t>https://www.bluradio.com/nacion/elecciones/procuraduria-pide-reforzar-gestion-del-riesgo-para-garantizar-elecciones-seguras-rg10</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:50 p. m.</t>
+          <t>22/05/2026 08:19 a. m.</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
@@ -2532,24 +2484,24 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Enfermería en Colombia: ¿Por qué hay déficit crítico de profesionales y cómo enfrentarlo?</t>
+          <t>Falta de resultados del Icfes afecta ingreso de estudiantes de Santander a universidades</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/entretenimiento/salud/2026/05/21/enfermeria-en-colombia-por-que-hay-deficit-critico-de-profesionales-y-como-enfrentarlo/</t>
+          <t>https://www.bluradio.com/regiones/santanderes/estudiantes-en-santander-denuncian-retrasos-en-entrega-de-resultados-del-icfes-rg10</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:15 p. m.</t>
+          <t>22/05/2026 08:15 a. m.</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2559,24 +2511,24 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Brutal enfrentamiento entre indígenas terminó en tragedia: tres muertos y varios heridos</t>
+          <t>Aprobación de Gustavo Petro hoy: esto revela la última encuesta de Invamer</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/21/brutal-enfrentamiento-entre-indigenas-termino-en-tragedia-tres-muertos-y-varios-heridos/</t>
+          <t>https://www.bluradio.com/nacion/aprobacion-de-gustavo-petro-hoy-esto-revela-la-ultima-encuesta-de-invamer-pr30</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 03:20 p. m.</t>
+          <t>22/05/2026 08:15 a. m.</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -2586,24 +2538,24 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Caso Yulixa Toloza: revelan qué provocó realmente su muerte tras cirugía en Beauty Láser</t>
+          <t>Hallan sin vida a otra mujer que desapareció tras acudir a centro estético: inquietantes detalles</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/21/caso-yulixa-toloza-revelan-que-provoco-realmente-su-muerte-tras-cirugia-en-beauty-lase/</t>
+          <t>https://www.bluradio.com/mundo/hallan-sin-vida-a-otra-mujer-que-desaparecio-tras-acudir-a-centro-estetico-inquietantes-detalles-rs15</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 02:25 p. m.</t>
+          <t>22/05/2026 08:04 a. m.</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2613,24 +2565,24 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Corte Constitucional: no pagar alimentos puede ser violencia económica en Colombia</t>
+          <t>¿Iván Cepeda llegó a su techo? Esto dijeron en el análisis de la encuesta Invamer</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/21/corte-constitucional-no-pagar-alimentos-puede-ser-violencia-economica-en-colombia/</t>
+          <t>https://www.bluradio.com/nacion/elecciones/ivan-cepeda-llego-a-su-techo-esto-dijeron-en-el-analisis-de-la-encuesta-invamer-so35</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 02:22 p. m.</t>
+          <t>22/05/2026 08:00 a. m.</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
@@ -2640,24 +2592,24 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Anulación de fotomultas en Colombia: pasos para recuperar su dinero si ya pagó</t>
+          <t>Es una guerra entre hermanos por territorio: alcalde de Silvia por choque de indígenas Misak y Nasa</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/20/fotomultas-anuladas-paso-a-paso-para-saber-si-le-devuelven-su-dinero/</t>
+          <t>https://www.bluradio.com/nacion/es-una-guerra-entre-hermanos-por-territorio-alcalde-de-silvia-por-choque-de-indigenas-misak-y-nasa-rg10</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 12:57 p. m.</t>
+          <t>22/05/2026 07:45 a. m.</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2667,24 +2619,24 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Antioquia cierra 64 centros estéticos por irregularidades tras controles sanitarios</t>
+          <t>Paloma Valencia baja en la encuesta Invamer: los motivos de su desplome electoral</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/21/antioquia-cierra-64-centros-esteticos-por-irregularidades-tras-controles-sanitarios/</t>
+          <t>https://www.bluradio.com/nacion/elecciones/paloma-valencia-baja-en-la-encuesta-invamer-los-motivos-de-su-desplome-electoral-pr30</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 12:34 p. m.</t>
+          <t>22/05/2026 07:35 a. m.</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
@@ -2694,24 +2646,24 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>La champeta será Patrimonio Cultural Inmaterial de Colombia: reconocimiento a este ritmo del Caribe</t>
+          <t>Análisis encuesta Invamer, ¿por qué crece Abelardo de la Espriella?</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/21/la-champeta-sera-patrimonio-cultural-inmaterial-de-colombia-reconocimiento-a-este-ritmo-del-caribe/</t>
+          <t>https://www.bluradio.com/nacion/elecciones/analisis-encuesta-invamer-por-que-crece-abelardo-de-la-espriella-pr30</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 11:57 a. m.</t>
+          <t>22/05/2026 09:00 a. m.</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -2721,24 +2673,24 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Caso Yulixa Toloza: capturados en Venezuela no serían extraditados a Colombia</t>
+          <t>Spurs vs Thunder: hora y dónde ver en vivo el juego 3 de las finales del oeste en la NBA</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/21/caso-yulixa-toloza-capturados-en-venezuela-no-serian-extraditados-a-colombia/</t>
+          <t>https://www.elespectador.com/deportes/mas-deportes/spurs-vs-thunder-hora-y-donde-ver-en-vivo-el-juego-3-de-las-finales-del-oeste-en-la-nba/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 07:30 p. m.</t>
+          <t>22/05/2026 09:00 a. m.</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
@@ -2748,24 +2700,24 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Invamer: Cepeda al frente con 44 % y Abelardo dobla a Paloma</t>
+          <t>Impulsan proyecto para que conductores del SITP sepan cómo actuar ante animales atropellados</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/invamer-cepeda-al-frente-con-44-y-abelardo-dobla-a-paloma/</t>
+          <t>https://www.elespectador.com/la-red-zoocial/impulsan-proyecto-para-que-conductores-del-sitp-sepan-como-actuar-ante-animales-atropellados/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 07:10 p. m.</t>
+          <t>22/05/2026 08:25 a. m.</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -2775,24 +2727,24 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Duerma informado con las movidas de este 21 de mayo de 2026</t>
+          <t>Precio del dólar hoy en Colombia: así abrió la moneda el 22 de mayo</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/duerma-informado-con-las-movidas-de-este-21-de-mayo-de-2026/</t>
+          <t>https://www.elespectador.com/economia/finanzas-personales/precio-del-dolar-hoy-22-de-mayo-de-2026-en-colombia-noticias-hoy/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:53 p. m.</t>
+          <t>22/05/2026 08:25 a. m.</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
@@ -2802,24 +2754,24 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>CNE negó solicitud para tumbar la candidatura de De la Espriella</t>
+          <t>China instaló la turbina eólica flotante más grande del mundo: estas son sus características</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/cne-nego-solicitud-para-tumbar-la-candidatura-de-de-la-espriella/</t>
+          <t>https://www.elespectador.com/ambiente/blog-el-rio/china-instalo-la-turbina-eolica-flotante-mas-grande-del-mundo-estas-son-sus-caracteristicas/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:14 p. m.</t>
+          <t>22/05/2026 08:21 a. m.</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -2829,24 +2781,24 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Petro se reunirá con el Papa León XIV en El Vaticano</t>
+          <t>Arbeloa confirmó su salida de Real Madrid y dejó pistas sobre el nuevo técnico</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/petro-se-reunira-con-el-papa-leon-xiv-en-el-vaticano/</t>
+          <t>https://www.elespectador.com/deportes/futbol-mundial/arbeloa-confirmo-su-salida-de-real-madrid-y-dejo-pistas-sobre-el-nuevo-tecnico/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:48 p. m.</t>
+          <t>22/05/2026 08:15 a. m.</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
@@ -2856,24 +2808,24 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Vandalizada sede de Paloma en Bogotá. Uribismo señala a Cepeda</t>
+          <t>¿Colombia es un país de izquierda, derecha o centro?, esto dice la última encuesta Invamer</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/vandalizada-sede-de-paloma-en-bogota-uribismo-senala-a-cepeda/</t>
+          <t>https://www.elespectador.com/politica/elecciones-colombia-2026/colombia-es-un-pais-de-izquierda-derecha-o-centro-esto-dice-la-ultima-encuesta-invamer-noticias-hoy/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:44 p. m.</t>
+          <t>22/05/2026 08:08 a. m.</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -2883,24 +2835,24 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Guarumo: Cepeda se mantiene en el 37%, Abelardo con 27% y Paloma 21%</t>
+          <t>S&amp;P 500 suma ocho semanas de alzas: paz en Medio Oriente y auge de la IA sostienen rally</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/guarumo-cepeda-se-mantiene-en-el-37-abelardo-con-27-y-paloma-21/</t>
+          <t>https://www.elespectador.com/economia/sp-500-apunta-a-su-mejor-racha-desde-2023-por-ia-y-esperanzas-de-paz/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:40 p. m.</t>
+          <t>22/05/2026 08:00 a. m.</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
@@ -2910,24 +2862,24 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>MinDefensa instala PMU por enfrentamientos entre comunidades indígenas</t>
+          <t>México y EE. UU. celebraron que la migración irregular esté en el menor nivel en 50 años</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/mindefensa-instala-pmu-por-enfrentamientos-entre-comunidades-indigenas/</t>
+          <t>https://www.elespectador.com/mundo/america/mexico-y-estados-unidos-celebraron-que-la-migracion-irregular-este-en-el-menor-nivel-en-50-anos/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 03:22 p. m.</t>
+          <t>22/05/2026 08:00 a. m.</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -2937,24 +2889,24 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Corte Constitucional aplazó discusión sobre el futuro de la ley de encuestas</t>
+          <t>En Stonehenge se reconstruyó una estructura de hace 4.500 años usando técnicas de la época</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/corte-constitucional-aplazo-discusion-sobre-el-futuro-de-la-ley-de-encuestas/</t>
+          <t>https://www.elespectador.com/el-magazin-cultural/en-stonehenge-se-reconstruyo-una-estructura-de-hace-4500-anos-usando-tecnicas-de-la-epoca/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 02:08 p. m.</t>
+          <t>22/05/2026 07:51 a. m.</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
@@ -2964,24 +2916,24 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Aunque de vacaciones, Ricardo Roa aparece de gira por Ecopetrol</t>
+          <t>Emergencia en Colina Campestre por el incendio de un vehículo de alta gama en la calle 134</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/aunque-de-vacaciones-ricardo-roa-aparece-de-gira-por-ecopetrol/</t>
+          <t>https://www.elespectador.com/bogota/emergencia-en-colina-campestre-por-el-incendio-de-un-vehiculo-de-alta-gama-en-la-calle-134/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 01:15 p. m.</t>
+          <t>22/05/2026 08:55 a. m.</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -2991,24 +2943,24 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Diario de Campaña: agarrón en el CNE y campaña de Abelardo contrató a Atlas</t>
+          <t>Los anestesiólogos del 12 de octubre suspenderán su actividad extraordinaria en protesta por las condiciones laborales: “De la vocación no se vive”</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/diario-de-campana-agarron-en-el-cne-y-campana-de-abelardo-contrato-a-atlas/</t>
+          <t>https://elpais.com/espana/madrid/2026-05-22/los-anestesiologos-del-12-de-octubre-suspenderan-su-actividad-extraordinaria-en-protesta-por-las-condiciones-laborales-de-la-vocacion-no-se-vive.html</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 07:27 p. m.</t>
+          <t>22/05/2026 08:28 a. m.</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
@@ -3018,24 +2970,24 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Madre era cruelmente extorsionada por su propio hijo en Pereira: así lo descubrió + VIDEO</t>
+          <t>El preocupante brote de ébola revela el “impacto tremendo” del tijeretazo de Trump a las ayudas</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/madre-era-cruelmente-extorsionada-por-su-propio-hijo-en-pereira-asi-lo-descubrio-video-1023512</t>
+          <t>https://elpais.com/sociedad/2026-05-22/el-preocupante-brote-de-ebola-revela-el-impacto-tremendo-del-tijeretazo-de-trump-a-las-ayudas.html</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:32 p. m.</t>
+          <t>22/05/2026 08:00 a. m.</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3045,24 +2997,24 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Yulixa Toloza iba muerta en el carro cuando la dueña de la estética usó su celular para engañar a la amiga</t>
+          <t>El excomisionado del Gobierno para la dana niega en el juzgado que falsificara su título</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/yulixa-toloza-iba-muerta-en-el-carro-cuando-la-duena-de-la-estetica-uso-su-celular-para-enganar-a-la-amiga-1023496</t>
+          <t>https://elpais.com/espana/comunidad-valenciana/2026-05-22/el-excomisionado-del-gobierno-para-la-dana-niega-en-el-juzgado-que-falsificara-su-titulo.html</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:29 p. m.</t>
+          <t>22/05/2026 07:56 a. m.</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
@@ -3072,24 +3024,24 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Juez adelanta audiencia en caso del asesinato de Jaime Esteban Moreno ante alerta por vencimiento de términos</t>
+          <t>Santander y BBVA deniegan el aval a Riquelme para presentarse a las elecciones del Real Madrid contra Florentino Pérez</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/juez-adelanta-audiencia-en-caso-del-asesinato-de-jaime-esteban-moreno-1023493</t>
+          <t>https://elpais.com/economia/2026-05-22/santander-y-bbva-deniegan-el-aval-a-riquelme-para-presentarse-a-las-elecciones-del-real-madrid-contra-florentino-perez.html</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:22 p. m.</t>
+          <t>22/05/2026 07:53 a. m.</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3099,24 +3051,24 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>El conmovedor video de Yulixa Toloza que compartió su familia: así quieren recordarla</t>
+          <t>Una marea verde de profesores en huelga, a la Generalitat: “Tienen que convocarnos a negociar”</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/asi-era-yulixa-toloza-en-vida-familia-compartio-video-1023482</t>
+          <t>https://elpais.com/espana/comunidad-valenciana/2026-05-22/una-marea-verde-de-profesores-en-huelga-a-la-generalitat-tienen-que-convocarnos-a-negociar.html</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:58 p. m.</t>
+          <t>22/05/2026 07:50 a. m.</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
@@ -3126,24 +3078,24 @@
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Presidente Gustavo Petro se reunirá con el papa León XIV en el Vaticano</t>
+          <t>El Hospital Vall d’Hebron detecta nueve casos humanos de una infección cutánea asociada a animales</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/presidente-gustavo-petro-se-reunira-con-el-papa-leon-xiv-en-el-vaticano-1023462</t>
+          <t>https://elpais.com/espana/catalunya/2026-05-22/el-hospital-vall-dhebron-detecta-nueve-casos-humanos-de-una-infeccion-cutanea-asociada-a-animales.html</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:36 p. m.</t>
+          <t>22/05/2026 07:49 a. m.</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3153,24 +3105,24 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Líder social Yanet Mosquera sufrió atentado en la vía Panamericana</t>
+          <t>El pavor de los narcos del puerto de Valencia tras adulterar la coca: “¡A ver si se empieza la peña a morir!”</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/lider-social-yanet-mosquera-sufrio-atentado-en-la-via-panamericana-1023476</t>
+          <t>https://elpais.com/espana/comunidad-valenciana/2026-05-22/el-pavor-de-los-narcos-del-puerto-de-valencia-tras-adulterar-la-coca-a-ver-si-se-empieza-la-pena-a-morir.html</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:12 p. m.</t>
+          <t>22/05/2026 07:44 a. m.</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
@@ -3180,24 +3132,24 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Avanzan los cierres y sellamientos de centros estéticos en Bogotá tras el caso Yulixa Toloza</t>
+          <t>Imputación de Zapatero por el ‘caso Plus Ultra’, en directo | Ábalos se desvincula del rescate de Plus Ultra y acusa al expresidente de puentearle</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/avanzan-los-cierres-y-sellamientos-de-centros-esteticos-en-bogota-tras-el-caso-yulixa-toloza-1023460</t>
+          <t>https://elpais.com/espana/2026-05-22/ultima-hora-de-la-actualidad-politica-y-reacciones-tras-la-imputacion-de-zapatero-por-el-caso-plus-ultra-en-directo.html</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:38 p. m.</t>
+          <t>22/05/2026 07:40 a. m.</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3207,24 +3159,24 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Cambian al procurador que pidió libertad para dos de los capturados por el caso de Yulixa Toloza</t>
+          <t>La Hormiga, Jamaicón o Chicharito: el encanto y obsesión de México por los apodos</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/cambian-al-procurador-que-pidio-libertad-para-dos-de-los-capturados-por-el-caso-de-yulixa-toloza-1023468</t>
+          <t>https://elpais.com/mexico/2026-05-22/la-hormiga-jamaicon-o-chicharito-el-encanto-y-obsesion-de-mexico-por-los-apodos.html</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:09 p. m.</t>
+          <t>22/05/2026 07:39 a. m.</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
@@ -3234,24 +3186,24 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>El Dorado renovó su servicio gratuito de buses entre terminales con vehículos eléctricos</t>
+          <t>El Centro Botín recuerda a Marisol, la reina del arte pop antes de que Warhol se quedara con el puesto</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/el-dorado-estrena-buses-electricos-gratuitos-1023433</t>
+          <t>https://elpais.com/cultura/2026-05-22/el-centro-botin-recuerda-a-marisol-la-reina-del-arte-pop-antes-de-que-warhol-se-quedara-con-el-puesto.html</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 03:19 p. m.</t>
+          <t>22/05/2026 07:37 a. m.</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3261,24 +3213,24 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>VIDEO | Encapuchados vandalizaron sede de campaña de Paloma Valencia en la carrera Séptima, en Bogotá</t>
+          <t>Casi 550.000 inmigrantes han solicitado acogerse a la regularización extraordinaria</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/encapuchados-vandalizaron-sede-de-campana-de-paloma-valencia-en-la-carrera-septima-en-bogota-1023436</t>
+          <t>https://elpais.com/espana/2026-05-22/casi-550000-inmigrantes-han-solicitado-acogerse-a-la-regularizacion-extraordinaria.html</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 07:20 p. m.</t>
+          <t>22/05/2026 07:34 a. m.</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
@@ -3288,24 +3240,24 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Abelardo de la Espriella se dispara, iría a segunda vuelta con Iván Cepeda y deja atrás a Paloma Valencia, según la encuesta de Invamer</t>
+          <t>El juez Calama pide a Estados Unidos información sobre los investigados del ‘caso Plus Ultra’</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/abelardo-de-la-espriella-se-dispara-iria-a-segunda-vuelta-con-ivan-cepeda-y-deja-atras-a-paloma-valencia-segun-la-encuesta-de-invamer/202623/</t>
+          <t>https://elpais.com/espana/2026-05-22/el-juez-pide-a-estados-unidos-informacion-sobre-los-investigados-de-plus-ultra.html</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 07:18 p. m.</t>
+          <t>22/05/2026 07:15 a. m.</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -3315,24 +3267,24 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Definida la final del Torneo Betplay: sin jugar, Real Cartagena es finalista y se ilusiona con el ascenso</t>
+          <t>Antonio Filosa (Stellantis) avanza que Leapmotor producirá dos modelos grandes en la fábrica de Madrid</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/definida-la-final-del-torneo-betplay-sin-jugar-real-cartagena-es-finalista-y-se-ilusiona-con-el-ascenso/202648/</t>
+          <t>https://elpais.com/economia/2026-05-22/antonio-filosa-stellantis-espana-para-nosotros-es-tanto-un-gran-mercado-como-un-gran-centro-industrial.html</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 07:00 p. m.</t>
+          <t>22/05/2026 07:15 a. m.</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
@@ -3342,24 +3294,24 @@
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>“Me arrodillo”: Gustavo Petro hizo un fuerte llamado de atención a la Corte Constitucional por retrasar su reforma pensional</t>
+          <t>La patronal de pisos turísticos amenaza con reclamar 160 millones al Estado por denegar licencias tras la anulación del registro único</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/me-arrodillo-gustavo-petro-dio-un-fuerte-discurso-contra-la-corte-constitucional-por-retrasar-su-reforma-pensional/202642/</t>
+          <t>https://elpais.com/economia/2026-05-22/la-patronal-de-pisos-turisticos-amenaza-con-reclamar-160-millones-al-estado-por-denegar-licencias-tras-la-anulacion-del-registro-unico.html</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:53 p. m.</t>
+          <t>22/05/2026 07:15 a. m.</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -3369,24 +3321,24 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Esta fue la cronología para deshacerse del cuerpo de Yulixa Toloza: la Fiscalía reveló detalles</t>
+          <t>La actitud de escucha de Guido Guidi: una exposición reúne más de seis décadas de trabajo del fotógrafo italiano</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/articulo/esta-fue-la-cronologia-para-deshacerse-del-cuerpo-de-yulixa-toloza-la-fiscalia-revelo-detalles/202642/</t>
+          <t>https://elpais.com/eps/2026-05-22/la-actitud-de-escucha-de-guido-guidi-una-exposicion-reune-mas-de-seis-decadas-de-trabajo-del-fotografo-italiano.html</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:47 p. m.</t>
+          <t>22/05/2026 06:55 a. m.</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
@@ -3396,24 +3348,24 @@
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>Nueva ofensiva del gobierno Trump contra Cuba: ICE arresta a mujer vinculada a poderoso conglomerado económico y militar</t>
+          <t>Por qué descarriló la fusión de Puig y Estée Lauder: falta de encaje, ‘momentums’ diferentes y una cláusula de Charlotte Tilbury</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/mundo/articulo/nueva-ofensiva-del-gobierno-trump-contra-cuba-ice-arresta-a-mujer-vinculada-a-poderosa-estructura-economica-militar/202652/</t>
+          <t>https://elpais.com/economia/2026-05-22/por-que-descarrilo-la-fusion-de-puig-y-estee-lauder-falta-de-encaje-momentums-diferentes-y-una-clausula-de-charlotte-tilbury.html</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:42 p. m.</t>
+          <t>22/05/2026 06:28 a. m.</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3423,24 +3375,24 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>“Venderlo con urgencia”: la orden para desaparecer el carro en el que fue transportada Yulixa Toloza</t>
+          <t>Cataluña aumentará mil plazas y 500 profesores en los estudios de FP</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/articulo/venderlo-con-urgencia-la-orden-para-desaparecer-el-carro-en-el-que-fue-transportada-yulixa-toloza/202632/</t>
+          <t>https://elpais.com/espana/catalunya/2026-05-22/cataluna-aumentara-mil-plazas-y-500-profesores-en-los-estudios-de-fp.html</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:41 p. m.</t>
+          <t>22/05/2026 06:27 a. m.</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
@@ -3450,24 +3402,24 @@
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>La cuenta regresiva para el eclipse solar más largo del siglo: solo podrá verse en estos países del mundo</t>
+          <t>Junts y PP cargan contra los nuevos Presupuestos catalanes: “Son lo mismo que hace tres meses”</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/tecnologia/articulo/la-cuenta-regresiva-para-el-eclipse-solar-mas-largo-del-siglo-solo-podra-verse-en-estos-paises-del-mundo/202643/</t>
+          <t>https://elpais.com/espana/catalunya/2026-05-22/junts-y-pp-cargan-contra-los-nuevos-presupuestos-catalanes-son-lo-mismo-que-hace-tres-meses.html</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:41 p. m.</t>
+          <t>22/05/2026 06:25 a. m.</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3477,24 +3429,24 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Marcelo Bielsa es noticia en Uruguay por decisión sobre su futuro: a nada del Mundial 2026</t>
+          <t>Rubio advierte a los aliados de la OTAN que Trump está muy “decepcionado” por su falta de apoyo en Oriente Próximo</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/marcelo-bielsa-es-noticia-en-uruguay-por-decision-sobre-su-futuro-a-nada-del-mundial-2026/202609/</t>
+          <t>https://elpais.com/internacional/2026-05-22/rubio-advierte-a-los-aliados-de-la-otan-que-trump-esta-muy-decepcionado-por-su-falta-de-apoyo-en-oriente-proximo.html</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:41 p. m.</t>
+          <t>22/05/2026 06:22 a. m.</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
@@ -3504,24 +3456,24 @@
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>Ecuador mantiene los aranceles sobre Colombia: presentó dos recursos y dos acciones ante la Comunidad Andina</t>
+          <t>Rebeca Pérez (PP) asume la alcaldía de Murcia y apela a “una forma de hacer política diferente, sensata y cercana”</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/economia/macroeconomia/articulo/ecuador-mantiene-los-aranceles-sobre-colombia-presento-dos-recursos-y-dos-acciones-ante-la-comunidad-andina/202649/</t>
+          <t>https://elpais.com/espana/2026-05-22/la-popular-rebeca-perez-asume-la-alcaldia-de-murcia-y-apela-a-una-forma-de-hacer-politica-diferente-sensata-y-cercana.html</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:41 p. m.</t>
+          <t>22/05/2026 06:13 a. m.</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -3531,24 +3483,24 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Caos en la movilidad de Bogotá: UNDMO interviene en zonas aledañas a la Universidad Nacional</t>
+          <t>Los estrenos de teatro de la semana</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/articulo/caos-en-la-movilidad-de-bogota-se-reportan-manifestaciones-en-la-septima-y-otros-puntos/202608/</t>
+          <t>https://elpais.com/babelia/2026-05-22/los-estrenos-de-teatro-de-la-semana.html</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:41 p. m.</t>
+          <t>22/05/2026 06:08 a. m.</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
@@ -3558,24 +3510,24 @@
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>Fico Gutiérrez denunció ante autoridades en Estados Unidos al ruso que se volvió un dolor de cabeza para Medellín: “A mí no me intimidan”</t>
+          <t>‘Saeta’: la caverna fantástica de Javier Aranda</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/medellin/articulo/fico-gutierrez-denuncio-ante-autoridades-en-estados-unidos-al-ruso-que-se-volvio-un-dolor-de-cabeza-para-medellin-a-mi-no-me-intimidan/202603/</t>
+          <t>https://elpais.com/babelia/2026-05-22/saeta-la-caverna-fantastica-de-javier-aranda.html</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:41 p. m.</t>
+          <t>22/05/2026 06:07 a. m.</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -3585,24 +3537,24 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>“Que Dios proteja su humanidad”: el alarmante mensaje de Fabián Ríos sobre el estado actual de Francisco Bolívar</t>
+          <t>‘El Firmament’: doce mujeres con un poco de piedad</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/gente/articulo/que-dios-proteja-su-humanidad-el-alarmante-mensaje-de-fabian-rios-sobre-el-estado-actual-de-francisco-bolivar/202655/</t>
+          <t>https://elpais.com/babelia/2026-05-22/el-firmament-doce-mujeres-con-un-poco-de-piedad.html</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:41 p. m.</t>
+          <t>22/05/2026 06:07 a. m.</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
@@ -3612,24 +3564,24 @@
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>“Se acaban los peajes”: Gustavo Petro se pronunció tras anuncio de la ANI sobre medida que aplicará en una región del país</t>
+          <t>Adelante Andalucía rechaza la vía Rufián para las generales</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/se-acaban-los-peajes-gustavo-petro-se-pronuncio-tras-anuncio-de-la-ani-sobre-medida-que-aplicara-en-una-region-del-pais/202628/</t>
+          <t>https://elpais.com/espana/elecciones-andalucia/2026-05-22/adelante-andalucia-rechaza-la-via-rufian-para-las-generales.html</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:41 p. m.</t>
+          <t>22/05/2026 04:56 a. m.</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -3639,24 +3591,24 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>El canciller de Cuba, Bruno Rodríguez Parrilla, acusa a Marco Rubio de “instigar una agresión militar” contra la isla</t>
+          <t>Miguel Ángel Rodríguez aviva la polémica sobre su acceso a información privilegiada con un tuit irónico sobre Sánchez: “Tú también vas P’alante”</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/mundo/articulo/el-canciller-de-cuba-bruno-rodriguez-parrilla-acusa-a-marco-rubio-de-instigar-una-agresion-militar-contra-la-isla/202650/</t>
+          <t>https://elpais.com/espana/madrid/2026-05-22/miguel-angel-rodriguez-aviva-la-polemica-sobre-su-acceso-a-informacion-privilgiada-con-un-tuit-ironico-sobre-sanchez-tu-tambien-vas-palante.html</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:41 p. m.</t>
+          <t>22/05/2026 04:42 a. m.</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
@@ -3666,24 +3618,24 @@
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>El presidente Gustavo Petro visitará al papa León XIV en el Vaticano: esta es la fecha del encuentro</t>
+          <t>¿Por qué ‘El Rosco’ y ‘Pasapalabra’ no son lo mismo? Preguntas y respuestas de la guerra entre Antena 3 y Telecinco</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/el-presidente-gustavo-petro-visitara-al-papa-leon-xiv-en-el-vaticano-esta-es-la-fecha-del-encuentro/202651/</t>
+          <t>https://elpais.com/television/2026-05-22/por-que-el-rosco-y-pasapalabra-no-son-lo-mismo-preguntas-y-respuestas-de-la-guerra-entre-antena-3-y-telecinco.html</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:41 p. m.</t>
+          <t>22/05/2026 04:01 a. m.</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -3693,24 +3645,24 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>CNE dejó en firme candidatura de Abelardo de la Espriella tras estudiar queja por supuestas irregularidades en la recolección de firmas</t>
+          <t>Relato en primera persona del maltrato israelí a la flotilla: “Colocaron una bandera israelí frente a mí y me dieron dos bofetadas”</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/cne-dejo-en-firme-candidatura-de-abelardo-de-la-espriella-tras-estudiar-queja-por-supuestas-irregularidades-en-la-recoleccion-de-firmas/202649/</t>
+          <t>https://elpais.com/internacional/2026-05-22/relato-en-primera-persona-del-maltrato-israeli-a-la-flotilla-colocaron-un-bandera-israeli-frente-a-mi-me-quitaron-los-calcetines-y-me-abofetearon.html</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:41 p. m.</t>
+          <t>21/05/2026 10:30 p. m.</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
@@ -3720,24 +3672,24 @@
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>Tres muertos y 44 heridos: saldo parcial del brutal choque entre comunidades indígenas en Cauca</t>
+          <t>Los Mossos concluyen que Jonathan Andic hizo, cuatro días antes de la muerte de su padre en Montserrat, una ruta casi exacta</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/cali/articulo/tres-muertos-y-44-heridos-saldo-parcial-del-brutal-choque-entre-comunidades-indigenas-en-cauca/202626/</t>
+          <t>https://elpais.com/espana/catalunya/2026-05-22/los-mossos-concluyen-que-jonathan-andic-hizo-cuatro-dias-antes-de-la-muerte-de-su-padre-en-montserrat-una-ruta-casi-exacta.html</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 03:41 p. m.</t>
+          <t>21/05/2026 10:30 p. m.</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -3747,24 +3699,24 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Vándalos atacaron la sede de Paloma Valencia y Juan Daniel Oviedo en Bogotá; dejaron mensajes alusivos a Iván Cepeda</t>
+          <t>Izan Llunas, el cantante que emocionó a Pedro Almodóvar: “No tuve una infancia normal”</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/vandalos-atacaron-la-sede-de-paloma-valencia-y-juan-daniel-oviedo-en-bogota-dejaron-mensajes-alusivos-a-ivan-cepeda/202617/</t>
+          <t>https://elpais.com/gente/2026-05-22/izan-llunas-el-cantante-que-emociono-a-pedro-almodovar-no-tuve-una-infancia-normal.html</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 03:41 p. m.</t>
+          <t>21/05/2026 10:30 p. m.</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
@@ -3774,22 +3726,26 @@
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>Gustavo Petro agitó las redes sociales por hablar de la constituyente: le pasaron factura por promesa que hizo en mármol</t>
+          <t>Los vecinos sin casa por culpa de la línea 7B de Metro ganan en los tribunales y se acuerdan de Ayuso: “Nos dijo que no podían darnos más”</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/gustavo-petro-agito-las-redes-sociales-por-hablar-de-la-constituyente-le-pasaron-factura-por-promesa-que-hizo-en-marmol/202638/</t>
+          <t>https://elpais.com/espana/madrid/2026-05-22/los-vecinos-sin-casa-por-culpa-de-la-linea-7b-de-metro-ganan-en-los-tribunales-y-se-acuerdan-de-ayuso-nos-dijo-que-no-podian-darnos-mas.html</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="inlineStr"/>
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>22/05/2026 08:44 a. m.</t>
+        </is>
+      </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -3797,22 +3753,26 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Lesión de Neymar alerta en Brasil con el Mundial 2026 a la vuelta: médico del Santos dio parte oficial</t>
+          <t>Fabián Ríos pide oraciones por Francisco Bolívar tras salida de ‘Sin senos sí hay paraíso’: ¿Qué le pasó?</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/lesion-de-neymar-alerta-en-brasil-con-el-mundial-2026-a-la-vuelta-medico-del-santos-dio-parte-oficial/202648/</t>
+          <t>https://www.vanguardia.com/entretenimiento/tendencias/2026/05/21/que-paso-con-francisco-bolivar-fabian-rios-pide-oraciones-tras-salida-de-sin-senos-si-hay-paraiso/</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="6" t="inlineStr"/>
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>22/05/2026 08:44 a. m.</t>
+        </is>
+      </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -3820,22 +3780,26 @@
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>Carlos Vives le hace honor a la Selección Colombia y hace importante anuncio</t>
+          <t>Tendencias</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/cultura/articulo/carlos-vives-le-hace-honor-a-la-seleccion-colombia-y-hace-importante-anuncio/202654/</t>
+          <t>https://www.vanguardia.com/entretenimiento/tendencias/</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="inlineStr"/>
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>22/05/2026 08:20 a. m.</t>
+        </is>
+      </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -3843,22 +3807,26 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Si no pudo ir, así podrá vivir el Mundial 2026 en Colombia: ‘Fan Zone’, la llamativa apuesta de la FCF</t>
+          <t>Horóscopo del viernes 22 de mayo de 2026: Predicciones y el vuelo de las ideas</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/si-no-pudo-ir-asi-podra-vivir-el-mundial-2026-en-colombia-fan-zone-la-llamativa-apuesta-de-la-fcf/202618/</t>
+          <t>https://www.vanguardia.com/entretenimiento/tendencias/2026/05/21/horoscopo-del-viernes-22-de-mayo-de-2026-predicciones-y-el-vuelo-de-las-ideas/</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="6" t="inlineStr"/>
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>22/05/2026 07:42 a. m.</t>
+        </is>
+      </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -3866,22 +3834,26 @@
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>Ola de críticas contra Jhon Jáder Durán por salir con botella en mano: video hunde sueño del Mundial</t>
+          <t>Enfrentamientos entre Misak y Nasa en Silvia dejan seis muertos y más de 60 heridos</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/ola-de-criticas-contra-jhon-jader-duran-por-salir-con-botella-en-mano-video-hunde-sueno-del-mundial/202655/</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/22/enfrentamientos-entre-misak-y-nasa-en-silvia-dejan-seis-muertos-y-mas-de-60-heridos/</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="inlineStr"/>
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>22/05/2026 07:42 a. m.</t>
+        </is>
+      </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -3889,22 +3861,26 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Paloma Valencia propone regalar neveras nuevas; recuerdan cuando Daniel Quintero ofrecía lavadoras</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/paloma-valencia-propone-regalar-neveras-nuevas-recuerdan-cuando-daniel-quintero-ofrecia-lavadoras/202631/</t>
+          <t>https://www.vanguardia.com/colombia/</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="6" t="inlineStr"/>
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>22/05/2026 07:36 a. m.</t>
+        </is>
+      </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -3912,22 +3888,26 @@
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>Iván Cepeda presentó en Bogotá un paquete de medidas sociales con las que busca ganar la Presidencia: habría salario mínimo vital para líderes sociales</t>
+          <t>Capturan otra vez a Valentina Mor por presuntos robos a turistas en Medellín</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/ivan-cepeda-presento-en-bogota-un-paquete-de-medidas-sociales-con-las-que-busca-ganar-la-presidencia-habria-salario-minimo-vital-para-lideres-sociales/202642/</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/22/capturan-otra-vez-a-valentina-mor-por-presuntos-robos-a-turistas-en-medellin/</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="inlineStr"/>
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>21/05/2026 09:19 p. m.</t>
+        </is>
+      </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -3935,22 +3915,26 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>La Casa de la Constitución: el centro en el que se adelantará el proceso de referendo contra la constituyente de Petro</t>
+          <t>Petro habló de un supuesto saqueo a las pensiones: “el robo de la salud se queda en pañales”</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/la-casa-de-la-constitucion-el-centro-en-el-que-se-adelantara-el-proceso-de-referendo-contra-la-constituyente-de-petro/202646/</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/21/petro-hablo-de-un-supuesto-saqueo-a-las-pensiones-el-robo-de-la-salud-se-queda-en-panales/</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="6" t="inlineStr"/>
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>21/05/2026 08:19 p. m.</t>
+        </is>
+      </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -3958,22 +3942,26 @@
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>“No acepto”: vinculados al crimen de Yulixa Toloza se declararon inocentes. Detalles de la imputación</t>
+          <t>Fenómeno de ‘El Niño’ ya estaría afectando a Colombia:  enciende alarmas por posible crisis energética</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/articulo/no-acepto-vinculados-al-crimen-de-yulixa-toloza-se-declararon-inocentes-detalles-de-la-imputacion/202647/</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/21/fenomeno-de-el-nino-ya-estaria-afectando-a-colombia-enciende-alarmas-por-posible-crisis-energetica/</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="inlineStr"/>
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>21/05/2026 07:31 p. m.</t>
+        </is>
+      </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -3981,22 +3969,26 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Colombia anuncia cierre de puente internacional con Ecuador: esta es la razón de la medida</t>
+          <t>Nueva encuesta presidencial: Iván Cepeda lidera, pero perdería en segunda vuelta</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/articulo/colombia-anuncia-cierre-de-puente-internacional-con-ecuador-esta-es-la-razon-de-la-medida/202607/</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/21/nueva-encuesta-presidencial-ivan-cepeda-lidera-pero-perderia-en-segunda-vuelta/</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="6" t="inlineStr"/>
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>21/05/2026 05:20 p. m.</t>
+        </is>
+      </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -4004,22 +3996,26 @@
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>Pacífico 1: obras en punto clave de la vía avanzan en su estabilización y manejo controlado del tráfico</t>
+          <t>En fotos: así quedó la sede de Paloma Valencia tras ataque vandálico en Bogotá</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/articulo/pacifico-1-obras-en-punto-clave-de-la-via-avanzan-en-su-estabilizacion-y-manejo-controlado-del-trafico/202623/</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/21/en-fotos-asi-quedo-la-sede-de-paloma-valencia-tras-ataque-vandalico-en-bogota/</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="inlineStr"/>
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>21/05/2026 04:50 p. m.</t>
+        </is>
+      </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -4027,24 +4023,24 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>“Empecemos a trabajar como seres civilizados”: procurador Eljach tras enfrentamientos entre comunidades misak y nasa</t>
+          <t>Enfermería en Colombia: ¿Por qué hay déficit crítico de profesionales y cómo enfrentarlo?</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/articulo/empecemos-a-trabajar-como-seres-civilizados-procurador-eljach-tras-enfrentamientos-entre-comunidades-misak-y-nasa/202625/</t>
+          <t>https://www.vanguardia.com/entretenimiento/salud/2026/05/21/enfermeria-en-colombia-por-que-hay-deficit-critico-de-profesionales-y-como-enfrentarlo/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 07:18 p. m.</t>
+          <t>21/05/2026 04:15 p. m.</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
@@ -4054,24 +4050,24 @@
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>Cero y van tres: la ANI dejó plantados otra vez a alcaldes del Oriente antioqueño</t>
+          <t>Brutal enfrentamiento entre indígenas terminó en tragedia: tres muertos y varios heridos</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/antioquia/la-ani-deja-plantados-a-alcaldes-oriente-antioqueno-MP36820268</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/21/brutal-enfrentamiento-entre-indigenas-termino-en-tragedia-tres-muertos-y-varios-heridos/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:56 p. m.</t>
+          <t>21/05/2026 03:20 p. m.</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -4081,24 +4077,24 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Indignante: funcionario de la Secretaría de Movilidad fue agredido por un hombre en la Comuna 13; alcalde pide justicia</t>
+          <t>Caso Yulixa Toloza: revelan qué provocó realmente su muerte tras cirugía en Beauty Láser</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/medellin/funcionario-publico-agredido-en-la-comuna-13-alcalde-rechaza-la-situacion-JM36819246</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/21/caso-yulixa-toloza-revelan-que-provoco-realmente-su-muerte-tras-cirugia-en-beauty-lase/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:47 p. m.</t>
+          <t>21/05/2026 02:25 p. m.</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
@@ -4108,24 +4104,24 @@
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>La historia de Dafne: se la robaron hace 44 años en una clínica de Medellín y su familia aún la busca</t>
+          <t>Corte Constitucional: no pagar alimentos puede ser violencia económica en Colombia</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/medellin/robo-bebe-dafne-desaparecida-familia-busqueda-FM36818490</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/21/corte-constitucional-no-pagar-alimentos-puede-ser-violencia-economica-en-colombia/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:41 p. m.</t>
+          <t>22/05/2026 08:19 a. m.</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -4135,24 +4131,24 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Según encuesta CB Global, habría empate técnico entre Iván Cepeda y Abelardo de la Espriella en primera vuelta</t>
+          <t>Petro mediará en disputa entre pueblos Misak y Nasa del Cauca</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/especiales/elecciones-2026/encuesta-cb-global-empate-tecnico-cepeda-abelardo-paloma-fajardo-HM36812306</t>
+          <t>https://www.lasillavacia.com/en-vivo/petro-mediara-en-disputa-entre-pueblos-misak-y-nasa-del-cauca/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:41 p. m.</t>
+          <t>22/05/2026 07:19 a. m.</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
@@ -4162,24 +4158,24 @@
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>Encuesta Invamer: Cepeda lidera con 44,9 %, Abelardo sube a 31,6 % y Paloma baja a 14%</t>
+          <t>Desayune informado con las claves de este 22 de mayo de 2026</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/especiales/elecciones-2026/encuesta-invamer-abelardo-ivan-cepeda-paloma-valencia-elecciones-2026-JM36817835</t>
+          <t>https://www.lasillavacia.com/en-vivo/desayune-informado-con-las-claves-de-este-22-de-mayo-de-2026/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:41 p. m.</t>
+          <t>21/05/2026 07:40 p. m.</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -4189,24 +4185,24 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Neymar sufrió lesión y preocupa a Brasil de cara al Mundial</t>
+          <t>Duerma informado con las movidas de este 21 de mayo de 2026</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/deportes/futbol/neymar-lesion-pantorilla-santos-mundial-brasil-EM36815652</t>
+          <t>https://www.lasillavacia.com/en-vivo/duerma-informado-con-las-movidas-de-este-21-de-mayo-de-2026/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:41 p. m.</t>
+          <t>21/05/2026 07:30 p. m.</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
@@ -4216,24 +4212,24 @@
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>¿Y los niños? En estos temas sobre la infancia se rajan los programas de candidatos a la presidencia, segúnNiñezYa</t>
+          <t>Invamer: Cepeda al frente con 44 % y Abelardo dobla a Paloma</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/especiales/elecciones-2026/candidatos-presidencia-se-rajan-propuestas-ninez-ON36803094</t>
+          <t>https://www.lasillavacia.com/en-vivo/invamer-cepeda-al-frente-con-44-y-abelardo-dobla-a-paloma/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:41 p. m.</t>
+          <t>21/05/2026 06:53 p. m.</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -4243,24 +4239,24 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>¿Cómo calcular la prima de junio de 2026 y cuánto recibirán quienes ganan el salario mínimo? Estas son las fechas y condiciones para el pago</t>
+          <t>CNE negó solicitud para tumbar la candidatura de De la Espriella</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/negocios/finanzas/prima-junio-2026-colombia-cuanto-recibiran-como-se-calcula-DM36811424</t>
+          <t>https://www.lasillavacia.com/en-vivo/cne-nego-solicitud-para-tumbar-la-candidatura-de-de-la-espriella/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:41 p. m.</t>
+          <t>21/05/2026 06:14 p. m.</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
@@ -4270,24 +4266,24 @@
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>Encuesta Guarumo: Cepeda lidera con 37,1 %; siguen Abelardo con 27,5 % y Paloma con 21,7 %, ¿y en segunda vuelta?</t>
+          <t>Petro se reunirá con el Papa León XIV en El Vaticano</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/especiales/elecciones-2026/encuesta-guarumo-mayo-2026-cepeda-lidera-GM36810017</t>
+          <t>https://www.lasillavacia.com/en-vivo/petro-se-reunira-con-el-papa-leon-xiv-en-el-vaticano/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 03:41 p. m.</t>
+          <t>21/05/2026 05:48 p. m.</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -4297,24 +4293,24 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>¿Monta en metro y aún no ha renovado su Cívica Classic? Pilas que queda poco tiempo para hacerlo</t>
+          <t>Vandalizada sede de Paloma en Bogotá. Uribismo señala a Cepeda</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/medellin/renovar-civica-classic-metro-medellin-NN36802780</t>
+          <t>https://www.lasillavacia.com/en-vivo/vandalizada-sede-de-paloma-en-bogota-uribismo-senala-a-cepeda/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 03:41 p. m.</t>
+          <t>21/05/2026 04:44 p. m.</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
@@ -4324,24 +4320,24 @@
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>Irene Vélez sería investigada en escándalo por millonario saqueo de regalías</t>
+          <t>Guarumo: Cepeda se mantiene en el 37%, Abelardo con 27% y Paloma 21%</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/ministra-ambiente-investigada-caso-corrupcion-regalias-GN36803757</t>
+          <t>https://www.lasillavacia.com/en-vivo/guarumo-cepeda-se-mantiene-en-el-37-abelardo-con-27-y-paloma-21/</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 03:41 p. m.</t>
+          <t>21/05/2026 04:40 p. m.</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -4351,24 +4347,24 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Arjona regresa a Medellín, ¿cuándo y dónde será el concierto del guatemalteco?</t>
+          <t>MinDefensa instala PMU por enfrentamientos entre comunidades indígenas</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/cultura/musica/ricardo-arjona-concierto-medellin-envigado-2026-AN36802626</t>
+          <t>https://www.lasillavacia.com/en-vivo/mindefensa-instala-pmu-por-enfrentamientos-entre-comunidades-indigenas/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 03:41 p. m.</t>
+          <t>21/05/2026 03:22 p. m.</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
@@ -4378,24 +4374,24 @@
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>Tres muertos y 44 heridos dejan enfrentamientos entre comunidades Misak y Nasa en Cauca</t>
+          <t>Corte Constitucional aplazó discusión sobre el futuro de la ley de encuestas</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/tres-muertos-44-heridos-enfrentamientos-comunidades-misak-nasa-cauca-CN36804547</t>
+          <t>https://www.lasillavacia.com/en-vivo/corte-constitucional-aplazo-discusion-sobre-el-futuro-de-la-ley-de-encuestas/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 03:41 p. m.</t>
+          <t>21/05/2026 02:08 p. m.</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -4405,24 +4401,24 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>UdeA y EAFIT, entre mejores universidades del país, según Nature</t>
+          <t>Aunque de vacaciones, Ricardo Roa aparece de gira por Ecopetrol</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/tendencias/nature-index-2025-universidad-antioquia-eafit-colombia-ranking-cientifico-GN36806617</t>
+          <t>https://www.lasillavacia.com/en-vivo/aunque-de-vacaciones-ricardo-roa-aparece-de-gira-por-ecopetrol/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 03:41 p. m.</t>
+          <t>21/05/2026 01:15 p. m.</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
@@ -4432,24 +4428,24 @@
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>Sede de Paloma Valencia y Juan D. Oviedo en Bogotá fue vandalizada; piden garantías de seguridad</t>
+          <t>Diario de Campaña: agarrón en el CNE y campaña de Abelardo contrató a Atlas</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/politica/campana-de-paloma-valencia-denuncia-ataques-a-sede-en-bogota-HN36803037</t>
+          <t>https://www.lasillavacia.com/en-vivo/diario-de-campana-agarron-en-el-cne-y-campana-de-abelardo-contrato-a-atlas/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 03:41 p. m.</t>
+          <t>21/05/2026 12:57 p. m.</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -4459,24 +4455,24 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Oficial: Conmebol emitió dura sanción contra el DIM por desmanes en el partido contra Flamengo en el Atanasio</t>
+          <t>Cepeda hablará con Consejo Gremial sobre aportes a programas sociales</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/deportes/futbol/dim-vs-flamengo-copa-libertadores-2026-sanciones-conmebol-GN36806819</t>
+          <t>https://www.lasillavacia.com/en-vivo/cepeda-hablara-con-consejo-gremial-sobre-aportes-a-programas-sociales/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 02:41 p. m.</t>
+          <t>21/05/2026 12:19 p. m.</t>
         </is>
       </c>
       <c r="B149" s="6" t="inlineStr">
@@ -4486,24 +4482,24 @@
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>Michael Jackson es hoy el número uno en la lista Billboard Artist 100 y es el sexto en hacerlo póstumamente</t>
+          <t>MinHacienda culpa al BanRep por subida de tasas de deuda pública</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/cultura/musica/michael-jackson-lidera-billboard-artist-tras-exito-de-su-pelicula-EL36796211</t>
+          <t>https://www.lasillavacia.com/en-vivo/minhacienda-culpa-al-banrep-por-subida-de-tasas-de-deuda-publica/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 02:41 p. m.</t>
+          <t>21/05/2026 11:25 a. m.</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -4513,24 +4509,24 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Colombia podría sufrir por energía en el Mundial 2026; consumo subiría hasta 5%</t>
+          <t>Campaña de Abelardo contrató a encuestadora Atlas por $195 millones</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/negocios/energia-colombia-mundial-2026-consumo-embalses-racionamiento-FL36799840</t>
+          <t>https://www.lasillavacia.com/en-vivo/campana-de-abelardo-contrato-a-encuestadora-atlas-por-195-millones/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 02:41 p. m.</t>
+          <t>21/05/2026 11:14 a. m.</t>
         </is>
       </c>
       <c r="B151" s="6" t="inlineStr">
@@ -4540,24 +4536,24 @@
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>El próximo gobierno deberá emitir más deuda sin importar quién gane en las elecciones: JP Morgan</t>
+          <t>“Petro prohibió votar por mí”: Roy Barreras por su lugar en encuestas</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/negocios/deuda-colombia-2026-jpmorgan-proximo-gobierno-emision-deuda-CN36802044</t>
+          <t>https://www.lasillavacia.com/en-vivo/petro-prohibio-votar-por-mi-roy-barreras-por-su-lugar-en-encuestas/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 02:41 p. m.</t>
+          <t>21/05/2026 09:58 a. m.</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -4567,24 +4563,24 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Se conoce la causa de muerte de Yulixa Toloza: Medicina Legal ya dio informe</t>
+          <t>Agarrón entre magistrados del CNE por suspensión de encuestas a AtlasIntel</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/embolia-pulmonar-causa-muerte-yulixa-toloza-centro-estetico-bogota-LL36799543</t>
+          <t>https://www.lasillavacia.com/en-vivo/agarron-entre-magistrados-del-cne-por-suspension-de-encuestas-a-atlasintel/</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 02:41 p. m.</t>
+          <t>21/05/2026 09:04 a. m.</t>
         </is>
       </c>
       <c r="B153" s="6" t="inlineStr">
@@ -4594,24 +4590,24 @@
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>Colombia tiene menos de 4 meses para evitar una crisis energética: Andesco</t>
+          <t>Consejo de Estado tumbó suspensión de capturas de cabecillas paisas</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/negocios/colombia-cuatro-meses-evitar-crisis-energetica-el-nino-2026-andesco-MN36800972</t>
+          <t>https://www.lasillavacia.com/en-vivo/consejo-de-estado-tumbo-suspension-de-capturas-de-cabecillas-paisas/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 01:41 p. m.</t>
+          <t>21/05/2026 09:00 a. m.</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -4621,24 +4617,24 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>¿Quién operó a Yulixa Toloza? Medio venezolano controvierte versiones y aseguró que fue un cirujano certificado</t>
+          <t>Le enseñamos a detectar desinformación en elecciones</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/quien-opero-yulixa-toloza-medio-venezolano-asegura-cirujano-certificado-CL36797630</t>
+          <t>https://www.lasillavacia.com/en-vivo/le-ensenamos-a-detectar-desinformacion-en-elecciones/</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 12:41 p. m.</t>
+          <t>21/05/2026 08:07 a. m.</t>
         </is>
       </c>
       <c r="B155" s="6" t="inlineStr">
@@ -4648,24 +4644,24 @@
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>Así suena la canción oficial de la Selección Colombia rumbo al Mundial de Norteamérica</t>
+          <t>Por “reciprocidad”, Colombia expulsa a encargado de Embajada de Bolivia</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/deportes/futbol/cancion-barras-incondicionales-seleccion-colombia-carlos-vives-IL36796781</t>
+          <t>https://www.lasillavacia.com/en-vivo/por-reciprocidad-colombia-expulsa-a-encargado-de-embajada-de-bolivia/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 12:41 p. m.</t>
+          <t>22/05/2026 08:14 a. m.</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -4675,24 +4671,24 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Matronas de barrios populares y corregimientos de Medellín llevan su cocina a La Pascasia</t>
+          <t>Escándalo en Computadores para Educar: 41.000 equipos inútiles y un posible detrimento de 60.000 millones de pesos</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/cultura/gastronomia/feria-gastronomica-matronas-urbanas-medellin-pascasia-carmen-acosta-JL36795639</t>
+          <t>https://cambiocolombia.com/poder/articulo/2026/5/escandalo-en-computadores-para-educar-41000-equipos-inutiles-y-un-posible-detrimento-de-60000-millones-de-pesos</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 12:41 p. m.</t>
+          <t>21/05/2026 07:00 p. m.</t>
         </is>
       </c>
       <c r="B157" s="6" t="inlineStr">
@@ -4702,24 +4698,24 @@
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>Erradicación manual cayó 92% con Petro y contratos siguen sin destrabarse</t>
+          <t>¿Aumento de precios? Fenavi advierte que bloqueos en vía a Buenaventura impactarían abastecimiento de pollo y huevo</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/erradicacion-manuel-redujo-gobierno-gustavo-petro-no-hay-contratos-ML36795494</t>
+          <t>https://cambiocolombia.com/pais/articulo/2026/5/aumento-de-precios-fenavi-advierte-que-bloqueos-en-via-a-buenaventura-impactarian-abastecimiento-de-pollo-y-huevo</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 10:41 a. m.</t>
+          <t>21/05/2026 06:00 p. m.</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -4729,24 +4725,24 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Hombre fue condenado en Estados Unidos a 30 años de cárcel por delitos sexuales contra menores en Medellín</t>
+          <t>Así es el USS Nimitz, el portaviones que Estados Unidos desplegó en el Caribe frente a Cuba</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/medellin/condena-carcel-ramon-arellano-delitos-sexuales-en-medellin-estados-unidos-CL36791425</t>
+          <t>https://cambiocolombia.com/internacional/articulo/2026/5/asi-es-el-uss-nimitz-el-portaviones-que-estados-unidos-desplego-en-el-caribe-frente-a-cuba</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 09:41 a. m.</t>
+          <t>21/05/2026 06:00 p. m.</t>
         </is>
       </c>
       <c r="B159" s="6" t="inlineStr">
@@ -4756,24 +4752,24 @@
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>Estas son las leyendas del fútbol que aparecen en “Dai Dai”, la nueva canción de Shakira para el Mundial 2026</t>
+          <t>“Mis excompañeros me trataban de traidora”: alias Karina, explica por qué no fue a la JEP</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/tendencias/leyendas-futbol-aparecen-dai-dai-cancion-shakira-mundial-KK36784086</t>
+          <t>https://cambiocolombia.com/conflicto-armado-en-colombia/articulo/2026/5/mis-excompaneros-me-trataban-de-traidora-alias-karina-explica-por-que-no-fue-a-la-jep</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 09:41 a. m.</t>
+          <t>21/05/2026 04:45 p. m.</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -4783,24 +4779,24 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Este es el prontuario de los siete cabecillas de la Paz Urbana a los que les reactivaron las órdenes de captura</t>
+          <t>Disputa territorial entre comunidades indígenas deja tres muertos y varios heridos en el Cauca</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/medellin/delitos-cabecillas-paz-urbana-ordenes-captura-consejo-de-estado-AK36784848</t>
+          <t>https://cambiocolombia.com/pais/articulo/2026/5/disputa-territorial-entre-comunidades-indigenas-deja-tres-muertos-y-varios-heridos-en-el-cauca</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:41 a. m.</t>
+          <t>21/05/2026 04:30 p. m.</t>
         </is>
       </c>
       <c r="B161" s="6" t="inlineStr">
@@ -4810,22 +4806,26 @@
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>Caso Yulixa Toloza: ¿qué pasa con los controles a ‘clínicas de garaje’?</t>
+          <t>Defensoría alerta por crisis humanitaria en cárceles y centros de detención del país</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/yulixa-toloza-que-pasa-controles-clinicas-garaje-EF36777605</t>
+          <t>https://cambiocolombia.com/pais/articulo/2026/5/defensoria-alerta-por-crisis-humanitaria-en-carceles-y-centros-de-detencion-del-pais</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="3" t="inlineStr"/>
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>21/05/2026 04:00 p. m.</t>
+        </is>
+      </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -4833,24 +4833,24 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Operativo destapa helicóptero con pasado oscuro y motor Rolls-Royce</t>
+          <t>¿Por qué los transportadores de servicio público están protestando en Cali?: alcalde Eder dice que no cederá a bloqueos</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/ejercito-incauta-helicoptero-de-la-mafia-NG33717192</t>
+          <t>https://cambiocolombia.com/pais/articulo/2026/5/por-que-los-transportadores-de-servicio-publico-estan-protestando-en-cali-alcalde-eder-dice-que-no-cedera-a-bloqueos</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 07:05 p. m.</t>
+          <t>21/05/2026 03:20 p. m.</t>
         </is>
       </c>
       <c r="B163" s="6" t="inlineStr">
@@ -4860,24 +4860,24 @@
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>Paloma Valencia y Abelardo de la Espriella vencerían a Iván Cepeda en segunda vuelta, según la encuesta de Guarumo</t>
+          <t>Alcaldía de Kennedy sella cinco centros estéticos por no cumplir con los requisitos</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-22/paloma-valencia-y-abelardo-de-la-espriella-vencerian-a-ivan-cepeda-en-segunda-vuelta-segun-la-encuesta-de-guarumo.html</t>
+          <t>https://cambiocolombia.com/pais/articulo/2026/5/alcaldia-de-kennedy-sella-cinco-centros-esteticos-por-no-cumplir-con-los-requisitos</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 07:00 p. m.</t>
+          <t>21/05/2026 03:20 p. m.</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -4887,24 +4887,24 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>Hora 20 y EL PAÍS en elecciones: ¿Cuál es el país con el que sueñan los jóvenes?</t>
+          <t>¿Habrá racionamiento de agua en Bogotá por la llegada del Fenómeno del Niño?</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/hora-20/2026-05-22/hora-20-y-el-pais-en-elecciones-cual-es-el-pais-con-el-que-suenan-los-jovenes.html</t>
+          <t>https://cambiocolombia.com/pais/articulo/2026/5/habra-racionamiento-de-agua-en-bogota-por-la-llegada-del-fenomeno-del-nino</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 06:51 p. m.</t>
+          <t>21/05/2026 01:30 p. m.</t>
         </is>
       </c>
       <c r="B165" s="6" t="inlineStr">
@@ -4914,24 +4914,24 @@
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>Sheinbaum intenta relanzar la relación con Estados Unidos recibiendo al jefe de Seguridad Interior de Trump</t>
+          <t>Por título de Julián Bedoya, piden a la Corte confirmar condena contra exfuncionarios de la Universidad de Medellín</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/mexico/2026-05-21/sheinbaum-intenta-relanzar-la-relacion-con-estados-unidos-recibiendo-al-jefe-de-seguridad-interior-de-trump.html</t>
+          <t>https://cambiocolombia.com/poder/articulo/2026/5/por-titulo-de-julian-bedoya-piden-a-la-corte-confirmar-condena-contra-exfuncionarios-de-la-universidad-de-medellin</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 06:46 p. m.</t>
+          <t>21/05/2026 12:22 p. m.</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>El ICE detiene en Florida a la hermana de la jefa del conglomerado militar cubano Gaesa</t>
+          <t>¿Atlas Intel podrá divulgar encuestas en la recta final de la campaña electoral?</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/us/2026-05-21/el-ice-detiene-en-florida-a-la-hermana-de-la-jefa-del-conglomerado-militar-cubano-gaesa.html</t>
+          <t>https://cambiocolombia.com/elecciones-colombia-2026/articulo/2026/5/atlas-intel-podra-divulgar-encuestas-en-la-recta-final-de-la-campana-electoral</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:44 p. m.</t>
+          <t>21/05/2026 10:42 a. m.</t>
         </is>
       </c>
       <c r="B167" s="6" t="inlineStr">
@@ -4968,24 +4968,24 @@
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>Videoanálisis | La derecha tradicional también flaquea en Colombia</t>
+          <t>Cae red que expedía documentos colombianos falsos a extranjeros para enviarlos a Estados Unidos</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-21/videoanalisis-la-derecha-tradicional-tambien-flaquea-en-colombia.html</t>
+          <t>https://cambiocolombia.com/pais/articulo/2026/5/cae-red-que-expedia-documentos-colombianos-falsos-a-extranjeros-para-enviarlos-a-estados-unidos</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:37 p. m.</t>
+          <t>21/05/2026 06:00 a. m.</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -4995,24 +4995,24 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Sheinbaum aprovecha la reforma judicial para colar un paquete electoral por la vía rápida</t>
+          <t>Percepción positiva sobre la minería aumentó en el último año según estudio Brújula Minera</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/mexico/2026-05-21/sheinbaum-aprovecha-la-reforma-judicial-para-colar-un-paquete-electoral-por-la-via-rapida.html</t>
+          <t>https://cambiocolombia.com/economia/articulo/2026/5/percepcion-positiva-sobre-la-mineria-aumento-en-el-ultimo-ano-segun-estudio-brujula-minera</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:30 p. m.</t>
+          <t>20/05/2026 07:30 p. m.</t>
         </is>
       </c>
       <c r="B169" s="6" t="inlineStr">
@@ -5022,24 +5022,24 @@
       </c>
       <c r="C169" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>Radiografía de la salud mental en el mundo: 1.200 millones de personas viven con trastornos psiquiátricos</t>
+          <t>Consejo de Estado frena beneficio a siete cabecillas de bandas de Medellín que negocian con el Gobierno</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/salud-y-bienestar/2026-05-22/radiografia-de-la-salud-mental-en-el-mundo-1200-millones-de-personas-viven-con-trastornos-psiquiatricos.html</t>
+          <t>https://cambiocolombia.com/justicia/articulo/2026/5/consejo-de-estado-frena-beneficio-a-siete-cabecillas-de-bandas-de-medellin-que-negocian-con-el-gobierno</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:13 p. m.</t>
+          <t>20/05/2026 05:32 p. m.</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -5049,24 +5049,24 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>La CNTE prepara un paro nacional indefinido el 1 de junio, ¿qué exigen los maestros?</t>
+          <t>El obstáculo que enfrenta Colombia para juzgar a los capturados por el caso de Yulixa Toloza</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/mexico/2026-05-21/la-cnte-prepara-un-paro-nacional-indefinido-el-1-de-junio-que-exigen-los-maestros.html</t>
+          <t>https://cambiocolombia.com/pais/articulo/2026/5/el-obstaculo-que-enfrenta-colombia-para-juzgar-a-los-capturados-por-el-caso-de-yulixa-toloza</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:01 p. m.</t>
+          <t>20/05/2026 05:30 p. m.</t>
         </is>
       </c>
       <c r="B171" s="6" t="inlineStr">
@@ -5076,24 +5076,24 @@
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Cambio Colombia</t>
         </is>
       </c>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>Emanciparse, una misión cada vez más imposible para los jóvenes: necesitan el 99% de su sueldo para irse a vivir solos</t>
+          <t>Olmedo López admite ante una jueza su responsabilidad en el robo a la UNGRD</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/sociedad/2026-05-21/emanciparse-una-mision-cada-vez-mas-imposible-para-los-jovenes-necesitan-el-99-de-su-sueldo-para-irse-a-vivir-solos.html</t>
+          <t>https://cambiocolombia.com/pais/articulo/2026/5/olmedo-lopez-admite-ante-una-jueza-su-responsabilidad-en-el-robo-a-la-ungrd</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:50 p. m.</t>
+          <t>22/05/2026 07:07 a. m.</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -5103,24 +5103,24 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>El Gobierno de Milei amenaza con devorarse a sí mismo</t>
+          <t>Kevin Mier se luce con Cruz Azul en la final del Torneo Clausura en México</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/argentina/2026-05-22/el-gobierno-de-milei-amenaza-con-devorarse-a-si-mismo.html</t>
+          <t>https://www.elcolombiano.com/deportes/futbol/kevin-mier-partido-cruz-azul-final-pumas-torneo-clausura-mexico-NP36826597</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:28 p. m.</t>
+          <t>22/05/2026 07:07 a. m.</t>
         </is>
       </c>
       <c r="B173" s="6" t="inlineStr">
@@ -5130,24 +5130,24 @@
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D173" s="7" t="inlineStr">
         <is>
-          <t>Trump da marcha atrás y anuncia el envío de 5.000 soldados adicionales de Estados Unidos a Polonia</t>
+          <t>Fiscalía de Venezuela imputó a capturados por crimen de Yulixa ¿el proceso seguirá en ese país?</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/internacional/2026-05-21/trump-da-marcha-atras-y-anuncia-el-envio-de-5000-soldados-adicionales-de-estados-unidos-a-polonia.html</t>
+          <t>https://www.elcolombiano.com/colombia/yulixa-toloza-fiscalia-de-venezuela-imputa-cargos-contra-detenidos-KP36826936</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:26 p. m.</t>
+          <t>22/05/2026 07:07 a. m.</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -5157,24 +5157,24 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>António Costa: “La Unión Europea necesita a México, el mundo necesita a México”</t>
+          <t>Se conoce la fecha de la reunión de Gustavo Petro y el papa León,¿será antes de su salida del gobierno?</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/mexico/economia/2026-05-21/antonio-costa-la-union-europea-necesita-a-mexico-el-mundo-necesita-a-mexico.html</t>
+          <t>https://www.elcolombiano.com/colombia/visita-reunion-de-gustavo-petro-y-el-papa-antes-de-su-salida-del-gobierno-NP36827082</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:17 p. m.</t>
+          <t>22/05/2026 07:07 a. m.</t>
         </is>
       </c>
       <c r="B175" s="6" t="inlineStr">
@@ -5184,24 +5184,24 @@
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>Óscar Puente llama a la “colaboración inteligente” entre la izquierda en las elecciones</t>
+          <t>Encapuchados vandalizaron sede del partido MIRA y Galán acusa a Petro de incentivar ataques</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/espana/2026-05-21/oscar-puente-llama-a-la-colaboracion-inteligente-entre-la-izquierda-en-las-elecciones.html</t>
+          <t>https://www.elcolombiano.com/colombia/encapuchados-vandalizaron-sede-partido-mira-galan-acusa-petro-incentivar-ataques-EP36827650</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 03:50 p. m.</t>
+          <t>22/05/2026 07:07 a. m.</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -5211,24 +5211,24 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Telefónica vende su sede histórica de Gran Vía al empresario Tomás Olivo por más de 200 millones</t>
+          <t>Mismo caso de Yulixa Toloza: Hallaron cuerpo de mujer desaparecida en México tras procedimiento estético</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/economia/2026-05-21/telefonica-vende-su-sede-historica-de-gran-via-a-un-empresario-murciano-por-mas-de-200-millones.html</t>
+          <t>https://www.elcolombiano.com/internacional/asesinato-mujer-procedimiento-estetico-puebla-mexico-desaparicion-IP36827249</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 03:42 p. m.</t>
+          <t>22/05/2026 07:07 a. m.</t>
         </is>
       </c>
       <c r="B177" s="6" t="inlineStr">
@@ -5238,24 +5238,24 @@
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>Luis Almagro, exsecretario de la OEA, anuncia su respaldo a Paloma Valencia y critica a Abelardo de la Espriella: “Se presenta como un fiestero en Miami”</t>
+          <t>¡Qué calor! Medellín rompió récord y registró 33,8°C en una estación de medición del Ideam</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/2026-05-21/luis-almagro-exsecretario-de-la-oea-anuncia-su-respaldo-a-paloma-valencia-y-critica-a-abelardo-de-la-espriella-se-presenta-como-un-fiestero-en-miami.html</t>
+          <t>https://www.elcolombiano.com/medellin/por-que-hace-tanto-calor-en-medellin-valle-de-aburra-ideam-siata-HP36827707</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 03:24 p. m.</t>
+          <t>22/05/2026 06:07 a. m.</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -5265,24 +5265,24 @@
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Puig anuncia la ruptura de las negociaciones para fusionarse con Estée Lauder</t>
+          <t>Pep Guardiola se marcha del Manchester City tras una década llena de gloria y títulos</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/economia/2026-05-21/puig-rompe-las-negociaciones-para-fusionarse-con-estee-lauder.html</t>
+          <t>https://www.elcolombiano.com/deportes/futbol/pep-guardiola-fin-de-una-decada-de-logros-con-manchester-city-en-premier-league-y-champions-JP36826285</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 03:09 p. m.</t>
+          <t>22/05/2026 06:07 a. m.</t>
         </is>
       </c>
       <c r="B179" s="6" t="inlineStr">
@@ -5292,24 +5292,24 @@
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>Las figuras no justifican el sueldo en una corrida petardo</t>
+          <t>Gasto público ya pesa más que la inversión en el PIB de Colombia, un hecho inédito</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/cultura/2026-05-21/las-figuras-no-justifican-el-sueldo-en-una-corrida-petardo.html</t>
+          <t>https://www.elcolombiano.com/negocios/gasto-publico-supera-inversion-pib-colombia-economia-2026-CP36822550</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 02:43 p. m.</t>
+          <t>22/05/2026 06:07 a. m.</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -5319,24 +5319,24 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Detenida en Brasil una abogada con 21 millones de seguidores en redes por lavar dinero para el crimen organizado</t>
+          <t>Lío por fotomultas: ‘hueco’ sería de $263.000 millones en cuatro municipios de Antioquia</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/america/2026-05-21/detenida-en-brasil-una-abogada-con-21-millones-de-seguidores-en-redes-por-lavar-dinero-para-el-crimen-organizado.html</t>
+          <t>https://www.elcolombiano.com/medellin/fotomultas-medellin-itagui-bello-sabaneta-supertransporte-multas-irregulares-KP36826268</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 02:31 p. m.</t>
+          <t>22/05/2026 06:07 a. m.</t>
         </is>
       </c>
       <c r="B181" s="6" t="inlineStr">
@@ -5346,24 +5346,24 @@
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D181" s="7" t="inlineStr">
         <is>
-          <t>La Policía detiene a tres personas como cooperadoras del crimen del cantaor Matías de Paula</t>
+          <t>El préstamo, hasta ahora desconocido, de Olmedo López a la campaña Petro en 2018</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/espana/2026-05-21/la-policia-detiene-a-tres-personas-como-cooperadoras-del-crimen-del-cantaor-matias-de-paula.html</t>
+          <t>https://www.elcolombiano.com/colombia/prestamo-olmedo-lopez-a-la-campana-petro-en-2018-investigacion-fiscalia-DP36826216</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 02:08 p. m.</t>
+          <t>22/05/2026 06:07 a. m.</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -5373,24 +5373,24 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Stellantis prevé elevar su facturación casi un 25% en cinco años hasta los 200.000 millones para revitalizar el negocio</t>
+          <t>A palo y machete: la historia detrás del territorio por el que se matan indígenas en el Cauca</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/economia/2026-05-21/stellantis-preve-elevar-su-facturacion-casi-un-25-hasta-los-200000-millones-en-cinco-anos-para-revitalizar-el-negocio.html</t>
+          <t>https://www.elcolombiano.com/colombia/silvia-cauca-por-que-se-enfrenta-indigenas-misak-y-nasa-DP36826140</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 02:08 p. m.</t>
+          <t>22/05/2026 05:07 a. m.</t>
         </is>
       </c>
       <c r="B183" s="6" t="inlineStr">
@@ -5400,24 +5400,24 @@
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D183" s="7" t="inlineStr">
         <is>
-          <t>Renuncia el ministro de Trabajo de Bolivia, el primer cambio en el Gobierno de Paz por las protestas</t>
+          <t>Análisis de encuestas: Cepeda se frena y Abelardo repunta a 9 días de las elecciones</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/america/2026-05-21/renuncia-el-ministro-de-trabajo-de-bolivia-el-primer-cambio-en-el-gobierno-de-paz-por-las-protestas.html</t>
+          <t>https://www.elcolombiano.com/colombia/analisis-de-encuestas-cepeda-se-frena-y-abelardo-repunta-CP36825676</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 12:48 p. m.</t>
+          <t>22/05/2026 12:07 a. m.</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -5427,26 +5427,22 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Un juez de Madrid archiva la denuncia de Begoña Gómez contra Vito Quiles por acoso</t>
+          <t>Así habría llegado dinero de ‘Pipe Tuluá’ a campaña de Gustavo Petro en 2022</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/espana/2026-05-21/un-juez-de-madrid-archiva-la-denuncia-de-begona-gomez-contra-vito-quiles-por-acoso.html</t>
+          <t>https://www.elcolombiano.com/colombia/campana-presidencial-gustavo-petro-financiacion-pipe-tulua-extraditado-GP36825461</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="6" t="inlineStr">
-        <is>
-          <t>21/05/2026 12:45 p. m.</t>
-        </is>
-      </c>
+      <c r="A185" s="6" t="inlineStr"/>
       <c r="B185" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5454,26 +5450,22 @@
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D185" s="7" t="inlineStr">
         <is>
-          <t>El Supremo obliga a Antena 3 a dejar de emitir ‘El Rosco’ de ‘Pasapalabra’</t>
+          <t>Encuesta Invamer: Aprobación de Gustavo Petro sigue cayendo mes tras mes a poco tiempo de terminar su mandato</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/television/2026-05-21/el-supremo-obliga-a-atresmedia-a-dejar-de-emitir-el-rosco-de-pasapalabra.html</t>
+          <t>https://www.elcolombiano.com/especiales/elecciones-2026/encuesta-invamer-aprobacion-petro-cae-tendencia-disminuir-MP36821782</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="3" t="inlineStr">
-        <is>
-          <t>21/05/2026 11:44 a. m.</t>
-        </is>
-      </c>
+      <c r="A186" s="3" t="inlineStr"/>
       <c r="B186" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5481,26 +5473,22 @@
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>Los Javis en Cannes: “Federico García Lorca no es una idea, sino una persona a la que asesinaron por maricón”</t>
+          <t>Oficial: Conmebol emitió dura sanción contra el DIM por desmanes en el partido contra Flamengo en el Atanasio</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/cultura/cine/2026-05-21/los-javis-en-cannes-federico-garcia-lorca-no-es-una-idea-sino-una-persona-a-la-que-asesinaron-por-maricon.html</t>
+          <t>https://www.elcolombiano.com/deportes/futbol/dim-vs-flamengo-copa-libertadores-2026-sanciones-conmebol-GN36806819</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="6" t="inlineStr">
-        <is>
-          <t>21/05/2026 10:26 a. m.</t>
-        </is>
-      </c>
+      <c r="A187" s="6" t="inlineStr"/>
       <c r="B187" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5508,26 +5496,22 @@
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D187" s="7" t="inlineStr">
         <is>
-          <t>La Audiencia Nacional ordena el bloqueo de 490.780 euros de las cuentas bancarias de Zapatero</t>
+          <t>Operativo destapa helicóptero con pasado oscuro y motor Rolls-Royce</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/espana/2026-05-21/la-audiencia-nacional-ordena-el-bloqueo-de-cuentas-bancarias-de-zapatero.html</t>
+          <t>https://www.elcolombiano.com/colombia/ejercito-incauta-helicoptero-de-la-mafia-NG33717192</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="3" t="inlineStr">
-        <is>
-          <t>21/05/2026 10:00 a. m.</t>
-        </is>
-      </c>
+      <c r="A188" s="3" t="inlineStr"/>
       <c r="B188" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5535,26 +5519,22 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Las pirámides egipcias fueron construidas a prueba de terremotos</t>
+          <t>Cero y van tres: la ANI dejó plantados otra vez a alcaldes del Oriente antioqueño</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/ciencia/2026-05-21/las-piramides-egipcias-fueron-construidas-a-prueba-de-terremotos.html</t>
+          <t>https://www.elcolombiano.com/antioquia/la-ani-deja-plantados-a-alcaldes-oriente-antioqueno-MP36820268</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="6" t="inlineStr">
-        <is>
-          <t>21/05/2026 09:49 a. m.</t>
-        </is>
-      </c>
+      <c r="A189" s="6" t="inlineStr"/>
       <c r="B189" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5562,26 +5542,22 @@
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D189" s="7" t="inlineStr">
         <is>
-          <t>Estados Unidos despliega su portaviones ‘USS Nimitz’ en el Caribe en plena campaña contra Cuba</t>
+          <t>En la Comuna 13 un conductor de grúa recibió ‘piedrazo’ y terminó fracturado; ya identificaron al responsable</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/internacional/2026-05-21/estados-unidos-despliega-su-portaviones-uss-nimitz-en-el-caribe-en-plena-campana-contra-cuba.html</t>
+          <t>https://www.elcolombiano.com/medellin/funcionario-publico-agredido-en-la-comuna-13-alcalde-rechaza-la-situacion-JM36819246</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="3" t="inlineStr">
-        <is>
-          <t>21/05/2026 07:12 a. m.</t>
-        </is>
-      </c>
+      <c r="A190" s="3" t="inlineStr"/>
       <c r="B190" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5589,26 +5565,22 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>El Supremo anula el registro único de alquileres turísticos al considerar que el Estado carece de competencias para crearlo</t>
+          <t>Neymar sufrió lesión y preocupa a Brasil de cara al Mundial</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/economia/2026-05-21/el-supremo-anula-el-registro-unico-de-alquileres-turisticos-al-considerar-que-el-estado-carece-de-competencias-para-crearlo.html</t>
+          <t>https://www.elcolombiano.com/deportes/futbol/neymar-lesion-pantorilla-santos-mundial-brasil-EM36815652</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="6" t="inlineStr">
-        <is>
-          <t>20/05/2026 10:30 p. m.</t>
-        </is>
-      </c>
+      <c r="A191" s="6" t="inlineStr"/>
       <c r="B191" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5616,26 +5588,22 @@
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D191" s="7" t="inlineStr">
         <is>
-          <t>Siete carreras con un buen sueldo y una nota de acceso asequible</t>
+          <t>Matronas de barrios populares y corregimientos de Medellín llevan su cocina a La Pascasia</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/educacion/2026-05-21/siete-carreras-con-un-buen-sueldo-y-una-nota-de-acceso-asequible.html</t>
+          <t>https://www.elcolombiano.com/cultura/gastronomia/feria-gastronomica-matronas-urbanas-medellin-pascasia-carmen-acosta-JL36795639</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="3" t="inlineStr">
-        <is>
-          <t>20/05/2026 10:30 p. m.</t>
-        </is>
-      </c>
+      <c r="A192" s="3" t="inlineStr"/>
       <c r="B192" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5643,26 +5611,22 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>El sendero en el que murió Isak Andic: un camino “sin riesgo” con un solo punto donde caer al vacío</t>
+          <t>Seis muertos y un centenar de heridos dejan enfrentamientos entre comunidades Misak y Nasa en Cauca</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/espana/catalunya/2026-05-21/el-sendero-en-el-que-murio-isak-andic-un-camino-sin-riesgo-con-un-solo-punto-donde-caer-al-vacio.html</t>
+          <t>https://www.elcolombiano.com/colombia/tres-muertos-44-heridos-enfrentamientos-comunidades-misak-nasa-cauca-CN36804547</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="6" t="inlineStr">
-        <is>
-          <t>21/05/2026 07:00 p. m.</t>
-        </is>
-      </c>
+      <c r="A193" s="6" t="inlineStr"/>
       <c r="B193" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5670,26 +5634,22 @@
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D193" s="7" t="inlineStr">
         <is>
-          <t>¿Aumento de precios? Fenavi advierte que bloqueos en vía a Buenaventura impactarían abastecimiento de pollo y huevo</t>
+          <t>¿Cómo calcular la prima de junio de 2026 y cuánto recibirán quienes ganan el salario mínimo? Estas son las fechas y condiciones para el pago</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/pais/articulo/2026/5/aumento-de-precios-fenavi-advierte-que-bloqueos-en-via-a-buenaventura-impactarian-abastecimiento-de-pollo-y-huevo</t>
+          <t>https://www.elcolombiano.com/negocios/finanzas/prima-junio-2026-colombia-cuanto-recibiran-como-se-calcula-DM36811424</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="3" t="inlineStr">
-        <is>
-          <t>21/05/2026 06:00 p. m.</t>
-        </is>
-      </c>
+      <c r="A194" s="3" t="inlineStr"/>
       <c r="B194" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5697,26 +5657,22 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Así es el USS Nimitz, el portaviones que Estados Unidos desplegó en el Caribe frente a Cuba</t>
+          <t>¿Quién operó a Yulixa Toloza? Medio venezolano controvierte versiones y aseguró que fue un cirujano certificado</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/internacional/articulo/2026/5/asi-es-el-uss-nimitz-el-portaviones-que-estados-unidos-desplego-en-el-caribe-frente-a-cuba</t>
+          <t>https://www.elcolombiano.com/colombia/quien-opero-yulixa-toloza-medio-venezolano-asegura-cirujano-certificado-CL36797630</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="6" t="inlineStr">
-        <is>
-          <t>21/05/2026 06:00 p. m.</t>
-        </is>
-      </c>
+      <c r="A195" s="6" t="inlineStr"/>
       <c r="B195" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5724,26 +5680,22 @@
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D195" s="7" t="inlineStr">
         <is>
-          <t>“Mis excompañeros me trataban de traidora”: alias Karina, explica por qué no fue a la JEP</t>
+          <t>UdeA y EAFIT, entre mejores universidades del país, según Nature</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/conflicto-armado-en-colombia/articulo/2026/5/mis-excompaneros-me-trataban-de-traidora-alias-karina-explica-por-que-no-fue-a-la-jep</t>
+          <t>https://www.elcolombiano.com/tendencias/nature-index-2025-universidad-antioquia-eafit-colombia-ranking-cientifico-GN36806617</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="3" t="inlineStr">
-        <is>
-          <t>21/05/2026 04:45 p. m.</t>
-        </is>
-      </c>
+      <c r="A196" s="3" t="inlineStr"/>
       <c r="B196" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5751,26 +5703,22 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>Disputa territorial entre comunidades indígenas deja tres muertos y varios heridos en Cauca</t>
+          <t>Ricardo Arjona regresa a Medellín, ¿cuándo y dónde será el concierto del guatemalteco?</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/pais/articulo/2026/5/disputa-territorial-entre-comunidades-indigenas-deja-tres-muertos-y-varios-heridos-en-cauca</t>
+          <t>https://www.elcolombiano.com/cultura/musica/ricardo-arjona-concierto-medellin-envigado-2026-AN36802626</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="6" t="inlineStr">
-        <is>
-          <t>21/05/2026 04:30 p. m.</t>
-        </is>
-      </c>
+      <c r="A197" s="6" t="inlineStr"/>
       <c r="B197" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5778,26 +5726,22 @@
       </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D197" s="7" t="inlineStr">
         <is>
-          <t>Defensoría alerta por crisis humanitaria en cárceles y centros de detención del país</t>
+          <t>Erradicación manual cayó 92% con Petro y contratos siguen sin destrabarse</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/pais/articulo/2026/5/defensoria-alerta-por-crisis-humanitaria-en-carceles-y-centros-de-detencion-del-pais</t>
+          <t>https://www.elcolombiano.com/colombia/erradicacion-manuel-redujo-gobierno-gustavo-petro-no-hay-contratos-ML36795494</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="3" t="inlineStr">
-        <is>
-          <t>21/05/2026 04:00 p. m.</t>
-        </is>
-      </c>
+      <c r="A198" s="3" t="inlineStr"/>
       <c r="B198" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5805,26 +5749,22 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>¿Por qué los transportadores de servicio público están protestando en Cali?: alcalde Eder dice que no cederá a bloqueos</t>
+          <t>Irene Vélez sería investigada en escándalo por millonario saqueo de regalías</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/pais/articulo/2026/5/por-que-los-transportadores-de-servicio-publico-estan-protestando-en-cali-alcalde-eder-dice-que-no-cedera-a-bloqueos</t>
+          <t>https://www.elcolombiano.com/colombia/ministra-ambiente-investigada-caso-corrupcion-regalias-GN36803757</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="6" t="inlineStr">
-        <is>
-          <t>21/05/2026 03:20 p. m.</t>
-        </is>
-      </c>
+      <c r="A199" s="6" t="inlineStr"/>
       <c r="B199" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5832,26 +5772,22 @@
       </c>
       <c r="C199" s="6" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D199" s="7" t="inlineStr">
         <is>
-          <t>Alcaldía de Kennedy sella cinco centros estéticos por no cumplir con los requisitos</t>
+          <t>Encuesta Invamer: Cepeda lidera con 44.6 %, Abelardo sube a 31.6 % y Paloma baja a 14%</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/pais/articulo/2026/5/alcaldia-de-kennedy-sella-cinco-centros-esteticos-por-no-cumplir-con-los-requisitos</t>
+          <t>https://www.elcolombiano.com/especiales/elecciones-2026/encuesta-invamer-resultados-mayo-2026-JM36817835</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="3" t="inlineStr">
-        <is>
-          <t>21/05/2026 03:20 p. m.</t>
-        </is>
-      </c>
+      <c r="A200" s="3" t="inlineStr"/>
       <c r="B200" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5859,26 +5795,22 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>¿Habrá racionamiento de agua en Bogotá por la llegada del Fenómeno del Niño?</t>
+          <t>Según encuesta CB Global, habría empate técnico entre Iván Cepeda y Abelardo de la Espriella en primera vuelta</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/pais/articulo/2026/5/habra-racionamiento-de-agua-en-bogota-por-la-llegada-del-fenomeno-del-nino</t>
+          <t>https://www.elcolombiano.com/especiales/elecciones-2026/encuesta-cb-global-empate-tecnico-cepeda-abelardo-paloma-fajardo-HM36812306</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="6" t="inlineStr">
-        <is>
-          <t>21/05/2026 01:30 p. m.</t>
-        </is>
-      </c>
+      <c r="A201" s="6" t="inlineStr"/>
       <c r="B201" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5886,105 +5818,105 @@
       </c>
       <c r="C201" s="6" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D201" s="7" t="inlineStr">
         <is>
-          <t>Por título de Julián Bedoya, piden a la Corte confirmar condena contra exfuncionarios de la Universidad de Medellín</t>
+          <t>¿Y los niños? En estos temas sobre la infancia se rajan los programas de candidatos a la presidencia, segúnNiñezYa</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/poder/articulo/2026/5/por-titulo-de-julian-bedoya-piden-a-la-corte-confirmar-condena-contra-exfuncionarios-de-la-universidad-de-medellin</t>
+          <t>https://www.elcolombiano.com/especiales/elecciones-2026/candidatos-presidencia-se-rajan-propuestas-ninez-ON36803094</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="3" t="inlineStr">
-        <is>
-          <t>21/05/2026 12:22 p. m.</t>
-        </is>
-      </c>
-      <c r="B202" s="3" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C202" s="3" t="inlineStr">
-        <is>
-          <t>Cambio Colombia</t>
-        </is>
-      </c>
-      <c r="D202" s="4" t="inlineStr">
-        <is>
-          <t>¿Atlas Intel podrá divulgar encuestas en la recta final de la campaña electoral?</t>
-        </is>
-      </c>
-      <c r="E202" s="5" t="inlineStr">
-        <is>
-          <t>https://cambiocolombia.com/elecciones-colombia-2026/articulo/2026/5/atlas-intel-podra-divulgar-encuestas-en-la-recta-final-de-la-campana-electoral</t>
+      <c r="A202" s="9" t="inlineStr">
+        <is>
+          <t>22/05/2026 08:00 a. m.</t>
+        </is>
+      </c>
+      <c r="B202" s="9" t="inlineStr">
+        <is>
+          <t>Entidad Oficial</t>
+        </is>
+      </c>
+      <c r="C202" s="9" t="inlineStr">
+        <is>
+          <t>Procuraduría General de la Nación</t>
+        </is>
+      </c>
+      <c r="D202" s="10" t="inlineStr">
+        <is>
+          <t>Debido a brote de tuberculosis en el centro carcelario de San Gil, Santander, Procuraduría solicitó información sobre la atención privados de la libertad</t>
+        </is>
+      </c>
+      <c r="E202" s="11" t="inlineStr">
+        <is>
+          <t>https://www.procuraduria.gov.co/Pages/debido-brote-tuberculosis-centro-carcelario-san-gil-santander-solicito-informacion-atencion.aspx</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="6" t="inlineStr">
-        <is>
-          <t>21/05/2026 10:42 a. m.</t>
-        </is>
-      </c>
-      <c r="B203" s="6" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C203" s="6" t="inlineStr">
-        <is>
-          <t>Cambio Colombia</t>
-        </is>
-      </c>
-      <c r="D203" s="7" t="inlineStr">
-        <is>
-          <t>Cae red que expedía documentos colombianos falsos a extranjeros para enviarlos a Estados Unidos</t>
-        </is>
-      </c>
-      <c r="E203" s="8" t="inlineStr">
-        <is>
-          <t>https://cambiocolombia.com/pais/articulo/2026/5/cae-red-que-expedia-documentos-colombianos-falsos-a-extranjeros-para-enviarlos-a-estados-unidos</t>
+      <c r="A203" s="12" t="inlineStr">
+        <is>
+          <t>22/05/2026 06:30 a. m.</t>
+        </is>
+      </c>
+      <c r="B203" s="12" t="inlineStr">
+        <is>
+          <t>Entidad Oficial</t>
+        </is>
+      </c>
+      <c r="C203" s="12" t="inlineStr">
+        <is>
+          <t>Procuraduría General de la Nación</t>
+        </is>
+      </c>
+      <c r="D203" s="13" t="inlineStr">
+        <is>
+          <t>Procuraduría insta a mandatarios locales a fortalecer la gestión de riesgo de desastres para garantizar la seguridad en las elecciones presidenciales de 2026</t>
+        </is>
+      </c>
+      <c r="E203" s="14" t="inlineStr">
+        <is>
+          <t>https://www.procuraduria.gov.co/Pages/procuraduria-insta-mandatarios-locales-fortalecer-gestion-riesgo-desastres-garantizar-seguridad-elecciones-presidenciales.aspx</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="3" t="inlineStr">
-        <is>
-          <t>21/05/2026 06:00 a. m.</t>
-        </is>
-      </c>
-      <c r="B204" s="3" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C204" s="3" t="inlineStr">
-        <is>
-          <t>Cambio Colombia</t>
-        </is>
-      </c>
-      <c r="D204" s="4" t="inlineStr">
-        <is>
-          <t>Percepción positiva sobre la minería aumentó en el último año según estudio Brújula Minera</t>
-        </is>
-      </c>
-      <c r="E204" s="5" t="inlineStr">
-        <is>
-          <t>https://cambiocolombia.com/economia/articulo/2026/5/percepcion-positiva-sobre-la-mineria-aumento-en-el-ultimo-ano-segun-estudio-brujula-minera</t>
+      <c r="A204" s="9" t="inlineStr">
+        <is>
+          <t>22/05/2026 06:02 a. m.</t>
+        </is>
+      </c>
+      <c r="B204" s="9" t="inlineStr">
+        <is>
+          <t>Entidad Oficial</t>
+        </is>
+      </c>
+      <c r="C204" s="9" t="inlineStr">
+        <is>
+          <t>Fiscalía General de la Nación</t>
+        </is>
+      </c>
+      <c r="D204" s="10" t="inlineStr">
+        <is>
+          <t>Asegurados hombres que habrían sido contactados para desaparecer el vehículo usado para trasladar y abandonar a mujer que murió luego de procedimiento estético</t>
+        </is>
+      </c>
+      <c r="E204" s="11" t="inlineStr">
+        <is>
+          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-hombres-que-habrian-sido-contactados-para-desaparecer-el-vehiculo-usado-para-trasladar-y-abandonar-a-mujer-que-murio-luego-de-procedimiento-estetico/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="6" t="inlineStr">
         <is>
-          <t>20/05/2026 07:30 p. m.</t>
+          <t>21/05/2026 05:24 p. m.</t>
         </is>
       </c>
       <c r="B205" s="6" t="inlineStr">
@@ -5994,24 +5926,24 @@
       </c>
       <c r="C205" s="6" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D205" s="7" t="inlineStr">
         <is>
-          <t>Consejo de Estado frena beneficio a siete cabecillas de bandas de Medellín que negocian con el Gobierno</t>
+          <t>La Barra Incondicional: El sello de Carlos Vives y la FCF crean los nuevos cánticos para alentar a la Selección Colombia</t>
         </is>
       </c>
       <c r="E205" s="8" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/justicia/articulo/2026/5/consejo-de-estado-frena-beneficio-a-siete-cabecillas-de-bandas-de-medellin-que-negocian-con-el-gobierno</t>
+          <t>https://canaltrece.com.co/noticias/la-barra-incondicional-el-sello-de-carlos-vives-y-la-fcf-crean-los-nuevos-canticos-para-alentar-a-la-seleccion-colombia/</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>20/05/2026 05:32 p. m.</t>
+          <t>21/05/2026 05:17 p. m.</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -6021,24 +5953,24 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>El obstáculo que enfrenta Colombia para juzgar a los capturados por el caso de Yulixa Toloza</t>
+          <t>Sebastián González presenta “Cómo Pudiste”: La nueva voz de la música popular colombiana</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/pais/articulo/2026/5/el-obstaculo-que-enfrenta-colombia-para-juzgar-a-los-capturados-por-el-caso-de-yulixa-toloza</t>
+          <t>https://canaltrece.com.co/noticias/sebastian-gonzalez-presenta-como-pudiste-la-nueva-voz-de-la-musica-popular-colombiana/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
         <is>
-          <t>20/05/2026 05:30 p. m.</t>
+          <t>21/05/2026 05:11 p. m.</t>
         </is>
       </c>
       <c r="B207" s="6" t="inlineStr">
@@ -6048,24 +5980,24 @@
       </c>
       <c r="C207" s="6" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D207" s="7" t="inlineStr">
         <is>
-          <t>Olmedo López admite ante una jueza su responsabilidad en el robo a la UNGRD</t>
+          <t>Andariega: El documental que retrata la vida de las recolectoras de café itinerantes llega a salas de cine</t>
         </is>
       </c>
       <c r="E207" s="8" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/pais/articulo/2026/5/olmedo-lopez-admite-ante-una-jueza-su-responsabilidad-en-el-robo-a-la-ungrd</t>
+          <t>https://canaltrece.com.co/noticias/andariega-el-documental-que-retrata-la-vida-de-las-recolectoras-de-cafe-itinerantes-llega-a-salas-de-cine/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>20/05/2026 03:30 p. m.</t>
+          <t>21/05/2026 05:07 p. m.</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -6075,24 +6007,24 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>Ataque con drones por parte de estructuras ilegales dejan un soldado muerto y otros cuatro uniformados heridos en el  sur de Bolívar</t>
+          <t>Bogotá se convierte en la capital parrillera de Latinoamérica con «El Papá de los Asados»</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/ataque-drones-estructuras-ilegales-sur-bolivar</t>
+          <t>https://canaltrece.com.co/noticias/bogota-se-convierte-en-la-capital-parrillera-de-latinoamerica-con-el-papa-de-los-asados/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:24 p. m.</t>
+          <t>21/05/2026 04:59 p. m.</t>
         </is>
       </c>
       <c r="B209" s="6" t="inlineStr">
@@ -6107,19 +6039,19 @@
       </c>
       <c r="D209" s="7" t="inlineStr">
         <is>
-          <t>La Barra Incondicional: El sello de Carlos Vives y la FCF crean los nuevos cánticos para alentar a la Selección Colombia</t>
+          <t>Fumaratto celebra 10 años de carrera y anuncia su desembarco en Europa con ‘Énfasis Tour’</t>
         </is>
       </c>
       <c r="E209" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/la-barra-incondicional-el-sello-de-carlos-vives-y-la-fcf-crean-los-nuevos-canticos-para-alentar-a-la-seleccion-colombia/</t>
+          <t>https://canaltrece.com.co/noticias/fumaratto-celebra-10-anos-de-carrera-y-anuncia-su-desembarco-en-europa-con-enfasis-tour/</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:17 p. m.</t>
+          <t>21/05/2026 04:44 p. m.</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -6134,19 +6066,19 @@
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>Sebastián González presenta “Cómo Pudiste”: La nueva voz de la música popular colombiana</t>
+          <t>Smart Fit Run 2026: La cadena de gimnasios más grande de Latinoamérica debuta en las calles de Bogotá</t>
         </is>
       </c>
       <c r="E210" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/sebastian-gonzalez-presenta-como-pudiste-la-nueva-voz-de-la-musica-popular-colombiana/</t>
+          <t>https://canaltrece.com.co/noticias/smart-fit-run-2026-la-cadena-de-gimnasios-mas-grande-de-latinoamerica-debuta-en-las-calles-de-bogota/</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 05:11 p. m.</t>
+          <t>21/05/2026 04:20 p. m.</t>
         </is>
       </c>
       <c r="B211" s="6" t="inlineStr">
@@ -6161,19 +6093,19 @@
       </c>
       <c r="D211" s="7" t="inlineStr">
         <is>
-          <t>Andariega: El documental que retrata la vida de las recolectoras de café itinerantes llega a salas de cine</t>
+          <t>El arte de saber cuándo callar: La hiperpersonalización real que exigen los usuarios en 2026</t>
         </is>
       </c>
       <c r="E211" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/andariega-el-documental-que-retrata-la-vida-de-las-recolectoras-de-cafe-itinerantes-llega-a-salas-de-cine/</t>
+          <t>https://canaltrece.com.co/noticias/el-arte-de-saber-cuando-callar-la-hiperpersonalizacion-real-que-exigen-los-usuarios-en-2026/</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 05:07 p. m.</t>
+          <t>21/05/2026 04:10 p. m.</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -6188,19 +6120,19 @@
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>Bogotá se convierte en la capital parrillera de Latinoamérica con «El Papá de los Asados»</t>
+          <t>Convocatoria abierta: Ofrecen 300 becas gratuitas de empleo para jóvenes en Bogotá y Cundinamarca</t>
         </is>
       </c>
       <c r="E212" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/bogota-se-convierte-en-la-capital-parrillera-de-latinoamerica-con-el-papa-de-los-asados/</t>
+          <t>https://canaltrece.com.co/noticias/convocatoria-abierta-ofrecen-300-becas-gratuitas-de-empleo-para-jovenes-en-bogota-y-cundinamarca/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:59 p. m.</t>
+          <t>21/05/2026 01:43 p. m.</t>
         </is>
       </c>
       <c r="B213" s="6" t="inlineStr">
@@ -6215,19 +6147,19 @@
       </c>
       <c r="D213" s="7" t="inlineStr">
         <is>
-          <t>Fumaratto celebra 10 años de carrera y anuncia su desembarco en Europa con ‘Énfasis Tour’</t>
+          <t>VASSAR Festival de Creadores llega al Parque El Country en Bogotá</t>
         </is>
       </c>
       <c r="E213" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/fumaratto-celebra-10-anos-de-carrera-y-anuncia-su-desembarco-en-europa-con-enfasis-tour/</t>
+          <t>https://canaltrece.com.co/noticias/vassar-festival-de-creadores-bogota-2026/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:44 p. m.</t>
+          <t>21/05/2026 01:37 p. m.</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -6242,19 +6174,19 @@
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>Smart Fit Run 2026: La cadena de gimnasios más grande de Latinoamérica debuta en las calles de Bogotá</t>
+          <t>Danibet Colombia Mundial 2026 analizará a la Selección partido a partido</t>
         </is>
       </c>
       <c r="E214" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/smart-fit-run-2026-la-cadena-de-gimnasios-mas-grande-de-latinoamerica-debuta-en-las-calles-de-bogota/</t>
+          <t>https://canaltrece.com.co/noticias/danibet-colombia-mundial-2026-analisis-seleccion/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 04:20 p. m.</t>
+          <t>21/05/2026 01:32 p. m.</t>
         </is>
       </c>
       <c r="B215" s="6" t="inlineStr">
@@ -6269,19 +6201,19 @@
       </c>
       <c r="D215" s="7" t="inlineStr">
         <is>
-          <t>El arte de saber cuándo callar: La hiperpersonalización real que exigen los usuarios en 2026</t>
+          <t>Expopet 2026 llega a Corferias para las familias interespecie</t>
         </is>
       </c>
       <c r="E215" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/el-arte-de-saber-cuando-callar-la-hiperpersonalizacion-real-que-exigen-los-usuarios-en-2026/</t>
+          <t>https://canaltrece.com.co/noticias/expopet-2026-llega-a-corferias-para-las-familias-interespecie/</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 04:10 p. m.</t>
+          <t>21/05/2026 01:23 p. m.</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -6296,19 +6228,19 @@
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t>Convocatoria abierta: Ofrecen 300 becas gratuitas de empleo para jóvenes en Bogotá y Cundinamarca</t>
+          <t>Mangle Sonoro Comadrita llega a Bogotá con agenda de conciertos</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/convocatoria-abierta-ofrecen-300-becas-gratuitas-de-empleo-para-jovenes-en-bogota-y-cundinamarca/</t>
+          <t>https://canaltrece.com.co/noticias/mangle-sonoro-comadrita-agenda-bogota/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 01:43 p. m.</t>
+          <t>21/05/2026 01:05 p. m.</t>
         </is>
       </c>
       <c r="B217" s="6" t="inlineStr">
@@ -6323,19 +6255,19 @@
       </c>
       <c r="D217" s="7" t="inlineStr">
         <is>
-          <t>VASSAR Festival de Creadores llega al Parque El Country en Bogotá</t>
+          <t>Conecta el País de la Belleza es la serie que Colombia necesitaba</t>
         </is>
       </c>
       <c r="E217" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/vassar-festival-de-creadores-bogota-2026/</t>
+          <t>https://canaltrece.com.co/regiones/conecta-el-pais-de-la-belleza-serie-canal-trece/</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 01:37 p. m.</t>
+          <t>20/05/2026 10:47 p. m.</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -6350,19 +6282,19 @@
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>Danibet Colombia Mundial 2026 analizará a la Selección partido a partido</t>
+          <t>Cuarteto de Nos Colombia 2026 confirma conciertos en Cali, Medellín y Bogotá</t>
         </is>
       </c>
       <c r="E218" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/danibet-colombia-mundial-2026-analisis-seleccion/</t>
+          <t>https://canaltrece.com.co/noticias/cuarteto-de-nos-colombia-2026-tour-puertas/</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 01:32 p. m.</t>
+          <t>20/05/2026 10:42 p. m.</t>
         </is>
       </c>
       <c r="B219" s="6" t="inlineStr">
@@ -6377,19 +6309,19 @@
       </c>
       <c r="D219" s="7" t="inlineStr">
         <is>
-          <t>Expopet 2026 llega a Corferias para las familias interespecie</t>
+          <t>Morat Ya Es Mañana World Tour 2027 anuncia fechas en Estados Unidos y Canadá</t>
         </is>
       </c>
       <c r="E219" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/expopet-2026-llega-a-corferias-para-las-familias-interespecie/</t>
+          <t>https://canaltrece.com.co/noticias/morat-ya-es-manana-world-tour-2027-anuncia-fechas-en-estados-unidos-y-canada/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>21/05/2026 01:23 p. m.</t>
+          <t>20/05/2026 10:36 p. m.</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -6404,19 +6336,19 @@
       </c>
       <c r="D220" s="4" t="inlineStr">
         <is>
-          <t>Mangle Sonoro Comadrita llega a Bogotá con agenda de conciertos</t>
+          <t>Monsieur Periné Instrucciones Para Ser Feliz Tour llega a Bogotá</t>
         </is>
       </c>
       <c r="E220" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/mangle-sonoro-comadrita-agenda-bogota/</t>
+          <t>https://canaltrece.com.co/noticias/monsieur-perine-instrucciones-para-ser-feliz-tour-bogota/</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 01:05 p. m.</t>
+          <t>20/05/2026 10:31 p. m.</t>
         </is>
       </c>
       <c r="B221" s="6" t="inlineStr">
@@ -6431,19 +6363,19 @@
       </c>
       <c r="D221" s="7" t="inlineStr">
         <is>
-          <t>Conecta el País de la Belleza es la serie que Colombia necesitaba</t>
+          <t>Mari La Carajita y Manira estrenan Pida la bendición</t>
         </is>
       </c>
       <c r="E221" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/regiones/conecta-el-pais-de-la-belleza-serie-canal-trece/</t>
+          <t>https://canaltrece.com.co/noticias/mari-la-carajita-y-manira-pida-la-bendicion/</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>20/05/2026 10:47 p. m.</t>
+          <t>20/05/2026 10:26 p. m.</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -6458,19 +6390,19 @@
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t>Cuarteto de Nos Colombia 2026 confirma conciertos en Cali, Medellín y Bogotá</t>
+          <t>Gran Tomatina Colombiana 2026 llega a Sutamarchán con ambiente mundialista</t>
         </is>
       </c>
       <c r="E222" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/cuarteto-de-nos-colombia-2026-tour-puertas/</t>
+          <t>https://canaltrece.com.co/regiones/gran-tomatina-colombiana-2026-sutamarchan/</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="6" t="inlineStr">
         <is>
-          <t>20/05/2026 10:42 p. m.</t>
+          <t>20/05/2026 10:16 a. m.</t>
         </is>
       </c>
       <c r="B223" s="6" t="inlineStr">
@@ -6485,19 +6417,19 @@
       </c>
       <c r="D223" s="7" t="inlineStr">
         <is>
-          <t>Morat Ya Es Mañana World Tour 2027 anuncia fechas en Estados Unidos y Canadá</t>
+          <t>Día Mundial de las Abejas 2026: «Juntos por las personas y el planeta» para proteger a nuestros polinizadores</t>
         </is>
       </c>
       <c r="E223" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/morat-ya-es-manana-world-tour-2027-anuncia-fechas-en-estados-unidos-y-canada/</t>
+          <t>https://canaltrece.com.co/noticias/dia-mundial-de-las-abejas-2026-juntos-por-las-personas-y-el-planeta-para-proteger-a-nuestros-polinizadores/</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>20/05/2026 10:36 p. m.</t>
+          <t>20/05/2026 10:10 a. m.</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -6512,19 +6444,19 @@
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>Monsieur Periné Instrucciones Para Ser Feliz Tour llega a Bogotá</t>
+          <t>Festivales y grandes conciertos en Colombia: La agenda imperdible para el segundo semestre de 2026</t>
         </is>
       </c>
       <c r="E224" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/monsieur-perine-instrucciones-para-ser-feliz-tour-bogota/</t>
+          <t>https://canaltrece.com.co/noticias/festivales-y-grandes-conciertos-en-colombia-la-agenda-imperdible-para-el-segundo-semestre-de-2026/</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
         <is>
-          <t>20/05/2026 10:31 p. m.</t>
+          <t>20/05/2026 09:59 a. m.</t>
         </is>
       </c>
       <c r="B225" s="6" t="inlineStr">
@@ -6539,19 +6471,19 @@
       </c>
       <c r="D225" s="7" t="inlineStr">
         <is>
-          <t>Mari La Carajita y Manira estrenan Pida la bendición</t>
+          <t>Elecciones Presidenciales 2026: Guía de votación para colombianos en América Latina</t>
         </is>
       </c>
       <c r="E225" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/mari-la-carajita-y-manira-pida-la-bendicion/</t>
+          <t>https://canaltrece.com.co/noticias/elecciones-presidenciales-2026-guia-de-votacion-para-colombianos-en-america-latina/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>20/05/2026 10:26 p. m.</t>
+          <t>20/05/2026 09:53 a. m.</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -6566,19 +6498,19 @@
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t>Gran Tomatina Colombiana 2026 llega a Sutamarchán con ambiente mundialista</t>
+          <t>Elecciones Presidenciales 2026: Así se votará desde España del 25 al 31 de mayo</t>
         </is>
       </c>
       <c r="E226" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/regiones/gran-tomatina-colombiana-2026-sutamarchan/</t>
+          <t>https://canaltrece.com.co/noticias/elecciones-presidenciales-2026-asi-se-votara-desde-espana-del-25-al-31-de-mayo/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="6" t="inlineStr">
         <is>
-          <t>20/05/2026 10:16 a. m.</t>
+          <t>20/05/2026 09:47 a. m.</t>
         </is>
       </c>
       <c r="B227" s="6" t="inlineStr">
@@ -6593,19 +6525,19 @@
       </c>
       <c r="D227" s="7" t="inlineStr">
         <is>
-          <t>Día Mundial de las Abejas 2026: «Juntos por las personas y el planeta» para proteger a nuestros polinizadores</t>
+          <t>Colombianos en Estados Unidos: Así se votará en las elecciones presidenciales de 2026</t>
         </is>
       </c>
       <c r="E227" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/dia-mundial-de-las-abejas-2026-juntos-por-las-personas-y-el-planeta-para-proteger-a-nuestros-polinizadores/</t>
+          <t>https://canaltrece.com.co/noticias/colombianos-en-estados-unidos-asi-se-votara-en-las-elecciones-presidenciales-de-2026/</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>20/05/2026 10:10 a. m.</t>
+          <t>20/05/2026 09:39 a. m.</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -6620,19 +6552,19 @@
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t>Festivales y grandes conciertos en Colombia: La agenda imperdible para el segundo semestre de 2026</t>
+          <t>Elecciones Presidenciales en Colombia: Paso a paso para consultar su puesto de votación este 31 de mayo</t>
         </is>
       </c>
       <c r="E228" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/festivales-y-grandes-conciertos-en-colombia-la-agenda-imperdible-para-el-segundo-semestre-de-2026/</t>
+          <t>https://canaltrece.com.co/noticias/elecciones-presidenciales-en-colombia-paso-a-paso-para-consultar-su-puesto-de-votacion-este-31-de-mayo/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="6" t="inlineStr">
         <is>
-          <t>20/05/2026 09:59 a. m.</t>
+          <t>20/05/2026 09:33 a. m.</t>
         </is>
       </c>
       <c r="B229" s="6" t="inlineStr">
@@ -6647,19 +6579,19 @@
       </c>
       <c r="D229" s="7" t="inlineStr">
         <is>
-          <t>Elecciones Presidenciales 2026: Guía de votación para colombianos en América Latina</t>
+          <t>El dolor de una madre: La historia de Yulitza Toloza y el último adiós desde Arauca</t>
         </is>
       </c>
       <c r="E229" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/elecciones-presidenciales-2026-guia-de-votacion-para-colombianos-en-america-latina/</t>
+          <t>https://canaltrece.com.co/noticias/el-dolor-de-una-madre-la-historia-de-yulitza-toloza-y-el-ultimo-adios-desde-arauca/</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>20/05/2026 09:53 a. m.</t>
+          <t>20/05/2026 09:13 a. m.</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -6674,19 +6606,19 @@
       </c>
       <c r="D230" s="4" t="inlineStr">
         <is>
-          <t>Elecciones Presidenciales 2026: Así se votará desde España del 25 al 31 de mayo</t>
+          <t>Orgullo del Valle: Gerónimo Mayac, el niño prodigio de 12 años que busca apoyo para representar a Colombia en el mundial de matemáticas en Singapur</t>
         </is>
       </c>
       <c r="E230" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/elecciones-presidenciales-2026-asi-se-votara-desde-espana-del-25-al-31-de-mayo/</t>
+          <t>https://canaltrece.com.co/noticias/orgullo-del-valle-geronimo-mayac-el-nino-prodigio-de-12-anos-que-busca-apoyo-para-representar-a-colombia-en-el-mundial-de-matematicas-en-singapur/</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
         <is>
-          <t>20/05/2026 09:47 a. m.</t>
+          <t>19/05/2026 07:02 p. m.</t>
         </is>
       </c>
       <c r="B231" s="6" t="inlineStr">
@@ -6701,19 +6633,19 @@
       </c>
       <c r="D231" s="7" t="inlineStr">
         <is>
-          <t>Colombianos en Estados Unidos: Así se votará en las elecciones presidenciales de 2026</t>
+          <t>Portugal Colombia Mundial 2026 mueve redes por comentario de Roberto Martínez</t>
         </is>
       </c>
       <c r="E231" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/colombianos-en-estados-unidos-asi-se-votara-en-las-elecciones-presidenciales-de-2026/</t>
+          <t>https://canaltrece.com.co/noticias/portugal-colombia-mundial-2026-roberto-martinez/</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>20/05/2026 09:39 a. m.</t>
+          <t>19/05/2026 06:52 p. m.</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -6728,19 +6660,19 @@
       </c>
       <c r="D232" s="4" t="inlineStr">
         <is>
-          <t>Elecciones Presidenciales en Colombia: Paso a paso para consultar su puesto de votación este 31 de mayo</t>
+          <t>Romeo Santos Prince Royce Bogotá confirma concierto en 2026</t>
         </is>
       </c>
       <c r="E232" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/elecciones-presidenciales-en-colombia-paso-a-paso-para-consultar-su-puesto-de-votacion-este-31-de-mayo/</t>
+          <t>https://canaltrece.com.co/noticias/romeo-santos-prince-royce-bogota-2026/</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
         <is>
-          <t>20/05/2026 09:33 a. m.</t>
+          <t>19/05/2026 06:47 p. m.</t>
         </is>
       </c>
       <c r="B233" s="6" t="inlineStr">
@@ -6755,19 +6687,19 @@
       </c>
       <c r="D233" s="7" t="inlineStr">
         <is>
-          <t>El dolor de una madre: La historia de Yulitza Toloza y el último adiós desde Arauca</t>
+          <t>Shakira Dai Dai Mundial 2026 une música, fútbol y educación</t>
         </is>
       </c>
       <c r="E233" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/el-dolor-de-una-madre-la-historia-de-yulitza-toloza-y-el-ultimo-adios-desde-arauca/</t>
+          <t>https://canaltrece.com.co/noticias/shakira-dai-dai-mundial-2026-educacion/</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>20/05/2026 09:13 a. m.</t>
+          <t>19/05/2026 06:38 p. m.</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -6782,1232 +6714,17 @@
       </c>
       <c r="D234" s="4" t="inlineStr">
         <is>
-          <t>Orgullo del Valle: Gerónimo Mayac, el niño prodigio de 12 años que busca apoyo para representar a Colombia en el mundial de matemáticas en Singapur</t>
+          <t>Baum Festival 2026 prende Bogotá con dos días de electrónica</t>
         </is>
       </c>
       <c r="E234" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/orgullo-del-valle-geronimo-mayac-el-nino-prodigio-de-12-anos-que-busca-apoyo-para-representar-a-colombia-en-el-mundial-de-matematicas-en-singapur/</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="6" t="inlineStr">
-        <is>
-          <t>19/05/2026 07:02 p. m.</t>
-        </is>
-      </c>
-      <c r="B235" s="6" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C235" s="6" t="inlineStr">
-        <is>
-          <t>Canal Trece</t>
-        </is>
-      </c>
-      <c r="D235" s="7" t="inlineStr">
-        <is>
-          <t>Portugal Colombia Mundial 2026 mueve redes por comentario de Roberto Martínez</t>
-        </is>
-      </c>
-      <c r="E235" s="8" t="inlineStr">
-        <is>
-          <t>https://canaltrece.com.co/noticias/portugal-colombia-mundial-2026-roberto-martinez/</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="3" t="inlineStr">
-        <is>
-          <t>19/05/2026 06:52 p. m.</t>
-        </is>
-      </c>
-      <c r="B236" s="3" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C236" s="3" t="inlineStr">
-        <is>
-          <t>Canal Trece</t>
-        </is>
-      </c>
-      <c r="D236" s="4" t="inlineStr">
-        <is>
-          <t>Romeo Santos Prince Royce Bogotá confirma concierto en 2026</t>
-        </is>
-      </c>
-      <c r="E236" s="5" t="inlineStr">
-        <is>
-          <t>https://canaltrece.com.co/noticias/romeo-santos-prince-royce-bogota-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="6" t="inlineStr">
-        <is>
-          <t>19/05/2026 06:47 p. m.</t>
-        </is>
-      </c>
-      <c r="B237" s="6" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C237" s="6" t="inlineStr">
-        <is>
-          <t>Canal Trece</t>
-        </is>
-      </c>
-      <c r="D237" s="7" t="inlineStr">
-        <is>
-          <t>Shakira Dai Dai Mundial 2026 une música, fútbol y educación</t>
-        </is>
-      </c>
-      <c r="E237" s="8" t="inlineStr">
-        <is>
-          <t>https://canaltrece.com.co/noticias/shakira-dai-dai-mundial-2026-educacion/</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="3" t="inlineStr">
-        <is>
-          <t>19/05/2026 06:38 p. m.</t>
-        </is>
-      </c>
-      <c r="B238" s="3" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C238" s="3" t="inlineStr">
-        <is>
-          <t>Canal Trece</t>
-        </is>
-      </c>
-      <c r="D238" s="4" t="inlineStr">
-        <is>
-          <t>Baum Festival 2026 prende Bogotá con dos días de electrónica</t>
-        </is>
-      </c>
-      <c r="E238" s="5" t="inlineStr">
-        <is>
           <t>https://canaltrece.com.co/noticias/baum-festival-2026-bogota-corferias/</t>
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="9" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B239" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C239" s="9" t="inlineStr">
-        <is>
-          <t>Ministerio de Minas y Energía</t>
-        </is>
-      </c>
-      <c r="D239" s="10" t="inlineStr">
-        <is>
-          <t>Gobierno expide nueva resolución que acelera la entrada de proyectos de energía limpia y fortalece la confiabilidad eléctrica del país</t>
-        </is>
-      </c>
-      <c r="E239" s="11" t="inlineStr">
-        <is>
-          <t>https://www.minenergia.gov.co/es/sala-de-prensa/noticias-index/gobierno-expide-nueva-resolucion-que-acelera-la-entrada-de-proyectos-de-energia-limpia-y-fortalece-la-confiabilidad-electrica-del-pais/</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="12" t="inlineStr">
-        <is>
-          <t>21/05/2026 12:00 p. m.</t>
-        </is>
-      </c>
-      <c r="B240" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C240" s="12" t="inlineStr">
-        <is>
-          <t>Ministerio de Relaciones Exteriores (Cancillería)</t>
-        </is>
-      </c>
-      <c r="D240" s="13" t="inlineStr">
-        <is>
-          <t>La Academia Diplomática Augusto Ramírez Ocampo publica el listado definitivo de Admitidos a presentar Pruebas Escritas Fase I del Concurso de Ingreso a la Carrera Diplomática y Consular 2028</t>
-        </is>
-      </c>
-      <c r="E240" s="14" t="inlineStr">
-        <is>
-          <t>https://www.cancilleria.gov.co/newsroom/Noticias</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="9" t="inlineStr">
-        <is>
-          <t>21/05/2026 02:45 p. m.</t>
-        </is>
-      </c>
-      <c r="B241" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C241" s="9" t="inlineStr">
-        <is>
-          <t>Ministerio del Interior</t>
-        </is>
-      </c>
-      <c r="D241" s="10" t="inlineStr">
-        <is>
-          <t>Avanza seguimiento a acuerdos de Consulta Previa del Complejo Penitenciario de Jamundí</t>
-        </is>
-      </c>
-      <c r="E241" s="11" t="inlineStr">
-        <is>
-          <t>https://www.mininterior.gov.co/micrositios/direccion-de-autoridad-nacional-y-consulta-previa/avanza-seguimiento-a-acuerdos-de-consulta-previa-del-complejo-penitenciario-de-jamundi/</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="12" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B242" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C242" s="12" t="inlineStr">
-        <is>
-          <t>Ministerio de Educación Nacional</t>
-        </is>
-      </c>
-      <c r="D242" s="13" t="inlineStr">
-        <is>
-          <t>La universidad pública que esperó Suba durante años ahora se pensará con su gente</t>
-        </is>
-      </c>
-      <c r="E242" s="14" t="inlineStr">
-        <is>
-          <t>https://www.mineducacion.gov.co/portal/salaprensa/Comunicados/428987:La-universidad-publica-que-espero-Suba-durante-anos-ahora-se-pensara-con-su-gente</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="9" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B243" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C243" s="9" t="inlineStr">
-        <is>
-          <t>Ministerio de Educación Nacional</t>
-        </is>
-      </c>
-      <c r="D243" s="10" t="inlineStr">
-        <is>
-          <t>¡Atención!  Se abre la convocatoria del Concurso Nacional de Escritura ‘Historias de Paz’ 2026</t>
-        </is>
-      </c>
-      <c r="E243" s="11" t="inlineStr">
-        <is>
-          <t>https://www.mineducacion.gov.co/portal/salaprensa/Comunicados/428979:Atencion-Se-abre-la-convocatoria-del-Concurso-Nacional-de-Escritura-Historias-de-Paz-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="12" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B244" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C244" s="12" t="inlineStr">
-        <is>
-          <t>Ministerio de Educación Nacional</t>
-        </is>
-      </c>
-      <c r="D244" s="13" t="inlineStr">
-        <is>
-          <t>La universidad pública que esperó Suba durante años ahora se pensará con su gente</t>
-        </is>
-      </c>
-      <c r="E244" s="14" t="inlineStr">
-        <is>
-          <t>https://www.mineducacion.gov.co/portal/salaprensa/Comunicados/428987:La-universidad-publica-que-espero-Suba-durante-anos-ahora-se-pensara-con-su-gente</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="9" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B245" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C245" s="9" t="inlineStr">
-        <is>
-          <t>Ministerio de Educación Nacional</t>
-        </is>
-      </c>
-      <c r="D245" s="10" t="inlineStr">
-        <is>
-          <t>¡Atención!  Se abre la convocatoria del Concurso Nacional de Escritura ‘Historias de Paz’ 2026</t>
-        </is>
-      </c>
-      <c r="E245" s="11" t="inlineStr">
-        <is>
-          <t>https://www.mineducacion.gov.co/portal/salaprensa/Comunicados/428979:Atencion-Se-abre-la-convocatoria-del-Concurso-Nacional-de-Escritura-Historias-de-Paz-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="12" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B246" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C246" s="12" t="inlineStr">
-        <is>
-          <t>Ministerio de Comercio, Industria y Turismo</t>
-        </is>
-      </c>
-      <c r="D246" s="13" t="inlineStr">
-        <is>
-          <t>MinCIT, junto con la Agencia Presidencial de Cooperación Internacional y TICA, realizará talleres internacionales sobre turismo médico</t>
-        </is>
-      </c>
-      <c r="E246" s="14" t="inlineStr">
-        <is>
-          <t>https://www.mincit.gov.co/prensa/noticias/turismo/mincit-talleres-internacionales-turismo-medico</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="9" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B247" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C247" s="9" t="inlineStr">
-        <is>
-          <t>Ministerio de Comercio, Industria y Turismo</t>
-        </is>
-      </c>
-      <c r="D247" s="10" t="inlineStr">
-        <is>
-          <t>Colombia muestra oportunidades de inversión y Ventanilla Única de Inversión entre empresarios franceses</t>
-        </is>
-      </c>
-      <c r="E247" s="11" t="inlineStr">
-        <is>
-          <t>https://www.mincit.gov.co/prensa/noticias/comercio/colombia-muestra-oportunidades-inversion-francia</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="12" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B248" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C248" s="12" t="inlineStr">
-        <is>
-          <t>Ministerio de Tecnologías de la Información y las Comunicaciones</t>
-        </is>
-      </c>
-      <c r="D248" s="13" t="inlineStr">
-        <is>
-          <t>El campo del Valle del Cauca se conecta con el futuro: AGROTECH llega a Palmira para transformar la producción rural</t>
-        </is>
-      </c>
-      <c r="E248" s="14" t="inlineStr">
-        <is>
-          <t>https://www.mintic.gov.co/portal/inicio/Sala-de-prensa/Noticias/438123:El-campo-del-Valle-del-Cauca-se-conecta-con-el-futuro-AGROTECH-llega-a-Palmira-para-transformar-la-produccion-rural</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="9" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B249" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C249" s="9" t="inlineStr">
-        <is>
-          <t>Ministerio de Tecnologías de la Información y las Comunicaciones</t>
-        </is>
-      </c>
-      <c r="D249" s="10" t="inlineStr">
-        <is>
-          <t>El Ministerio TIC recibió 35 solicitudes para el uso de la banda de 900 MHz. en 139 municipios del país</t>
-        </is>
-      </c>
-      <c r="E249" s="11" t="inlineStr">
-        <is>
-          <t>https://www.mintic.gov.co/portal/inicio/Sala-de-prensa/Noticias/438121:El-Ministerio-TIC-recibio-35-solicitudes-para-el-uso-de-la-banda-de-900-MHz-en-139-municipios-del-pais</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="12" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B250" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C250" s="12" t="inlineStr">
-        <is>
-          <t>Ministerio de Tecnologías de la Información y las Comunicaciones</t>
-        </is>
-      </c>
-      <c r="D250" s="13" t="inlineStr">
-        <is>
-          <t>Chocó abre sus puertas a la innovación y la transformación digital de Colombia 5.0</t>
-        </is>
-      </c>
-      <c r="E250" s="14" t="inlineStr">
-        <is>
-          <t>https://www.mintic.gov.co/portal/inicio/Sala-de-prensa/Noticias/438103:Choco-abre-sus-puertas-a-la-innovacion-y-la-transformacion-digital-de-Colombia-5-0</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="9" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B251" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C251" s="9" t="inlineStr">
-        <is>
-          <t>Ministerio de Tecnologías de la Información y las Comunicaciones</t>
-        </is>
-      </c>
-      <c r="D251" s="10" t="inlineStr">
-        <is>
-          <t>Avanza la conectividad en la Amazonía: Gobierno Nacional garantiza recursos para el Plan de Fibra Óptica</t>
-        </is>
-      </c>
-      <c r="E251" s="11" t="inlineStr">
-        <is>
-          <t>https://www.mintic.gov.co/portal/inicio/Sala-de-prensa/Noticias/438101:Avanza-la-conectividad-en-la-Amazonia-Gobierno-Nacional-garantiza-recursos-para-el-Plan-de-Fibra-Optica</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="12" t="inlineStr">
-        <is>
-          <t>21/05/2026 08:46 p. m.</t>
-        </is>
-      </c>
-      <c r="B252" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C252" s="12" t="inlineStr">
-        <is>
-          <t>Superintendencia Nacional de Salud</t>
-        </is>
-      </c>
-      <c r="D252" s="13" t="inlineStr">
-        <is>
-          <t>Supersalud lidera seminario sobre prevención del suicidio y salud mental juvenil en Nariño</t>
-        </is>
-      </c>
-      <c r="E252" s="14" t="inlineStr">
-        <is>
-          <t>https://wcmportal.supersalud.gov.co/portalweb/Comunicaciones/Lists/Noticias/Noticia.aspx?ID=2574</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="9" t="inlineStr">
-        <is>
-          <t>21/05/2026 01:45 p. m.</t>
-        </is>
-      </c>
-      <c r="B253" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C253" s="9" t="inlineStr">
-        <is>
-          <t>Superintendencia Nacional de Salud</t>
-        </is>
-      </c>
-      <c r="D253" s="10" t="inlineStr">
-        <is>
-          <t>Supersalud avanza en auditoría integral al modelo de salud del FOMAG y advierte incumplimientos de órdenes previas</t>
-        </is>
-      </c>
-      <c r="E253" s="11" t="inlineStr">
-        <is>
-          <t>https://wcmportal.supersalud.gov.co/portalweb/Comunicaciones/Lists/Noticias/Noticia.aspx?ID=2573</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="12" t="inlineStr">
-        <is>
-          <t>21/05/2026 03:50 p. m.</t>
-        </is>
-      </c>
-      <c r="B254" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C254" s="12" t="inlineStr">
-        <is>
-          <t>Ministerio de Ciencia, Tecnología e Innovación</t>
-        </is>
-      </c>
-      <c r="D254" s="13" t="inlineStr">
-        <is>
-          <t>Gobierno Nacional avanza en la democratización del conocimiento para las comunidades afrocolombianas del país</t>
-        </is>
-      </c>
-      <c r="E254" s="14" t="inlineStr">
-        <is>
-          <t>https://minciencias.gov.co/sala_de_prensa/gobierno-nacional-avanza-en-la-democratizacion-del-conocimiento-para-las-0</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="9" t="inlineStr">
-        <is>
-          <t>21/05/2026 07:00 a. m.</t>
-        </is>
-      </c>
-      <c r="B255" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C255" s="9" t="inlineStr">
-        <is>
-          <t>Procuraduría General de la Nación</t>
-        </is>
-      </c>
-      <c r="D255" s="10" t="inlineStr">
-        <is>
-          <t>Procuraduría suspendió provisionalmente al Notario Único de la Hormiga, Putumayo, por presunta indebida participación en política</t>
-        </is>
-      </c>
-      <c r="E255" s="11" t="inlineStr">
-        <is>
-          <t>https://www.procuraduria.gov.co/Pages/procuraduria-suspendio-provisionalmente-notario-unico-hormiga-putumayo-presunta-indebida-participacion.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="12" t="inlineStr">
-        <is>
-          <t>21/05/2026 02:00 a. m.</t>
-        </is>
-      </c>
-      <c r="B256" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C256" s="12" t="inlineStr">
-        <is>
-          <t>Procuraduría General de la Nación</t>
-        </is>
-      </c>
-      <c r="D256" s="13" t="inlineStr">
-        <is>
-          <t>Procurador General, Gregorio Eljach, rindió homenaje a la raza negra</t>
-        </is>
-      </c>
-      <c r="E256" s="14" t="inlineStr">
-        <is>
-          <t>https://www.procuraduria.gov.co/Pages/procurador-general-gregorio-eljach-rindio-homenaje-raza-negra.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="9" t="inlineStr">
-        <is>
-          <t>21/05/2026 12:00 p. m.</t>
-        </is>
-      </c>
-      <c r="B257" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C257" s="9" t="inlineStr">
-        <is>
-          <t>Procuraduría General de la Nación</t>
-        </is>
-      </c>
-      <c r="D257" s="10" t="inlineStr">
-        <is>
-          <t>“Reafirmamos nuestro compromiso con la garantía de los derechos de la población negra, afrocolombiana, raizal y palenquera”: Procurador General, Gregorio Eljach</t>
-        </is>
-      </c>
-      <c r="E257" s="11" t="inlineStr">
-        <is>
-          <t>https://www.procuraduria.gov.co/Pages/reafirmamos-nuestro-compromiso-garantia-derechos-poblacion-negra-afrocolombiana-raizal-palenquera.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="12" t="inlineStr">
-        <is>
-          <t>21/05/2026 06:30 a. m.</t>
-        </is>
-      </c>
-      <c r="B258" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C258" s="12" t="inlineStr">
-        <is>
-          <t>Procuraduría General de la Nación</t>
-        </is>
-      </c>
-      <c r="D258" s="13" t="inlineStr">
-        <is>
-          <t>Acciones de la Procuraduría llevaron a INVÍAS a anunciar trabajos en vía Panamericana por más de 14 mil millones de pesos</t>
-        </is>
-      </c>
-      <c r="E258" s="14" t="inlineStr">
-        <is>
-          <t>https://www.procuraduria.gov.co/Pages/acciones-procuraduria-llevaron-invias-anunciar-trabajos-via-panamericana-mas-14-mil-millones.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="9" t="inlineStr">
-        <is>
-          <t>21/05/2026 02:45 p. m.</t>
-        </is>
-      </c>
-      <c r="B259" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C259" s="9" t="inlineStr">
-        <is>
-          <t>Ministerio de Vivienda, Ciudad y Territorio</t>
-        </is>
-      </c>
-      <c r="D259" s="10" t="inlineStr">
-        <is>
-          <t>Gobierno abre convocatoria para obras e interventoría del Programa Barrios y Veredas de Paz en Ipiales, Nariño</t>
-        </is>
-      </c>
-      <c r="E259" s="11" t="inlineStr">
-        <is>
-          <t>https://minvivienda.gov.co/sala-de-prensa/gobierno-abre-convocatoria-para-obras-e-interventoria-del-programa-barrios-y-veredas-de-paz-en-ipiales-narino</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="12" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B260" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C260" s="12" t="inlineStr">
-        <is>
-          <t>Ministerio de Transporte</t>
-        </is>
-      </c>
-      <c r="D260" s="13" t="inlineStr">
-        <is>
-          <t>Plataforma RNDC restablece su operación tras superar intermitencia tecnológica</t>
-        </is>
-      </c>
-      <c r="E260" s="14" t="inlineStr">
-        <is>
-          <t>https://mintransporte.gov.co/publicaciones/12351/plataforma-rndc-restablece-su-operacion-tras-superar-intermitencia-tecnologica/</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="9" t="inlineStr">
-        <is>
-          <t>21/05/2026 05:11 p. m.</t>
-        </is>
-      </c>
-      <c r="B261" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C261" s="9" t="inlineStr">
-        <is>
-          <t>Fiscalía General de la Nación</t>
-        </is>
-      </c>
-      <c r="D261" s="10" t="inlineStr">
-        <is>
-          <t>Condenan a más de 16 años de prisión a responsable del crimen de un hombre en Anserma (Caldas)</t>
-        </is>
-      </c>
-      <c r="E261" s="11" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/condenan-a-mas-de-16-anos-de-prision-a-responsable-del-crimen-de-un-hombre-en-anserma-caldas/</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="12" t="inlineStr">
-        <is>
-          <t>21/05/2026 05:01 p. m.</t>
-        </is>
-      </c>
-      <c r="B262" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C262" s="12" t="inlineStr">
-        <is>
-          <t>Fiscalía General de la Nación</t>
-        </is>
-      </c>
-      <c r="D262" s="13" t="inlineStr">
-        <is>
-          <t>Presunto responsable del crimen de un hombre en La Dorada (Caldas) fue asegurado</t>
-        </is>
-      </c>
-      <c r="E262" s="14" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/seguridad-territorial/presunto-responsable-del-crimen-de-un-hombre-en-la-dorada-caldas-fue-asegurado/</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="9" t="inlineStr">
-        <is>
-          <t>21/05/2026 04:51 p. m.</t>
-        </is>
-      </c>
-      <c r="B263" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C263" s="9" t="inlineStr">
-        <is>
-          <t>Fiscalía General de la Nación</t>
-        </is>
-      </c>
-      <c r="D263" s="10" t="inlineStr">
-        <is>
-          <t>Afectación a grupo delincuencial dedicado al tráfico local de estupefacientes en Viterbo (Caldas)</t>
-        </is>
-      </c>
-      <c r="E263" s="11" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/afectacion-a-grupo-delincuencial-dedicado-al-trafico-local-de-estupefacientes-en-viterbo-caldas/</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="12" t="inlineStr">
-        <is>
-          <t>21/05/2026 04:44 p. m.</t>
-        </is>
-      </c>
-      <c r="B264" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C264" s="12" t="inlineStr">
-        <is>
-          <t>Fiscalía General de la Nación</t>
-        </is>
-      </c>
-      <c r="D264" s="13" t="inlineStr">
-        <is>
-          <t>Procesado señalado abusador sexual de una menor de edad en Palmira (Valle del Cauca)</t>
-        </is>
-      </c>
-      <c r="E264" s="14" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/procesado-senalado-abusador-sexual-de-una-menor-de-edad-en-palmira-valle-del-cauca/</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="9" t="inlineStr">
-        <is>
-          <t>21/05/2026 04:38 p. m.</t>
-        </is>
-      </c>
-      <c r="B265" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C265" s="9" t="inlineStr">
-        <is>
-          <t>Fiscalía General de la Nación</t>
-        </is>
-      </c>
-      <c r="D265" s="10" t="inlineStr">
-        <is>
-          <t>Asegurado presunto integrante del Clan del Golfo presuntamente involucrado en varios delitos en Zarzal (Valle del Cauca)</t>
-        </is>
-      </c>
-      <c r="E265" s="11" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-integrante-del-clan-del-golfo-presuntamente-involucrado-en-varios-delitos-en-zarzal-valle-del-cauca/</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="12" t="inlineStr">
-        <is>
-          <t>21/05/2026 04:35 p. m.</t>
-        </is>
-      </c>
-      <c r="B266" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C266" s="12" t="inlineStr">
-        <is>
-          <t>Fiscalía General de la Nación</t>
-        </is>
-      </c>
-      <c r="D266" s="13" t="inlineStr">
-        <is>
-          <t>Condenan a más de 16 años a responsables del crimen de un hombre en Dosquebradas</t>
-        </is>
-      </c>
-      <c r="E266" s="14" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/condenan-a-mas-de-16-anos-a-responsables-del-crimen-de-un-hombre-en-dosquebradas/</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="9" t="inlineStr">
-        <is>
-          <t>21/05/2026 04:31 p. m.</t>
-        </is>
-      </c>
-      <c r="B267" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C267" s="9" t="inlineStr">
-        <is>
-          <t>Fiscalía General de la Nación</t>
-        </is>
-      </c>
-      <c r="D267" s="10" t="inlineStr">
-        <is>
-          <t>Capturado con fines de extradición presunto cabecilla del ‘Clan Cotes’ que estaría involucrado en tráfico de estupefacientes</t>
-        </is>
-      </c>
-      <c r="E267" s="11" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/crimen-organizado/capturado-con-fines-de-extradicion-presunto-cabecilla-del-clan-cotes-que-estaria-involucrado-en-trafico-de-estupefacientes/</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="12" t="inlineStr">
-        <is>
-          <t>21/05/2026 04:24 p. m.</t>
-        </is>
-      </c>
-      <c r="B268" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C268" s="12" t="inlineStr">
-        <is>
-          <t>Fiscalía General de la Nación</t>
-        </is>
-      </c>
-      <c r="D268" s="13" t="inlineStr">
-        <is>
-          <t>Asegurados presuntos responsable de asesinar a un menor de edad en San Andrés</t>
-        </is>
-      </c>
-      <c r="E268" s="14" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurados-presuntos-responsable-de-asesinar-a-un-menor-de-edad-en-san-andres/</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="9" t="inlineStr">
-        <is>
-          <t>21/05/2026 03:38 p. m.</t>
-        </is>
-      </c>
-      <c r="B269" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C269" s="9" t="inlineStr">
-        <is>
-          <t>Fiscalía General de la Nación</t>
-        </is>
-      </c>
-      <c r="D269" s="10" t="inlineStr">
-        <is>
-          <t>Confirman condena contra exalcalde de Anzoátegui por irregularidades en contratos para el mantenimiento de maquinaria pesada</t>
-        </is>
-      </c>
-      <c r="E269" s="11" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/confirman-condena-contra-exalcalde-de-anzoategui-por-irregularidades-en-contratos-para-el-mantenimiento-de-maquinaria-pesada/</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="3" t="inlineStr">
-        <is>
-          <t>20/05/2026 07:38 p. m.</t>
-        </is>
-      </c>
-      <c r="B270" s="3" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C270" s="3" t="inlineStr">
-        <is>
-          <t>El Espectador</t>
-        </is>
-      </c>
-      <c r="D270" s="4" t="inlineStr">
-        <is>
-          <t>¿Abelardo de la Espriella es la salvación de Colombia?| La Pulla</t>
-        </is>
-      </c>
-      <c r="E270" s="5" t="inlineStr">
-        <is>
-          <t>https://www.elespectador.com/opinion/columnistas/la-pulla/la-pulla-abelardo-de-la-espriella-es-la-salvacion-de-colombia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="6" t="inlineStr">
-        <is>
-          <t>20/05/2026 07:35 p. m.</t>
-        </is>
-      </c>
-      <c r="B271" s="6" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C271" s="6" t="inlineStr">
-        <is>
-          <t>El Espectador</t>
-        </is>
-      </c>
-      <c r="D271" s="7" t="inlineStr">
-        <is>
-          <t>Encuesta Invamer: Iván Cepeda ganaría en todos los escenarios de la segunda vuelta</t>
-        </is>
-      </c>
-      <c r="E271" s="8" t="inlineStr">
-        <is>
-          <t>https://www.elespectador.com/politica/elecciones-colombia-2026/encuesta-invamer-cepeda-le-ganaria-a-de-la-espriella-y-valencia-en-todos-los-escenarios-de-la-segunda-vuelta-noticias-hoy/</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="3" t="inlineStr">
-        <is>
-          <t>20/05/2026 07:26 p. m.</t>
-        </is>
-      </c>
-      <c r="B272" s="3" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C272" s="3" t="inlineStr">
-        <is>
-          <t>El Espectador</t>
-        </is>
-      </c>
-      <c r="D272" s="4" t="inlineStr">
-        <is>
-          <t>EE. UU. busca multar a migrantes con USD 18.000 para recuperar los costos de la deportación</t>
-        </is>
-      </c>
-      <c r="E272" s="5" t="inlineStr">
-        <is>
-          <t>https://www.elespectador.com/mundo/america/estados-unidos-busca-multar-a-migrantes-con-usd-18000-para-recuperar-los-costos-de-la-deportacion/</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="6" t="inlineStr">
-        <is>
-          <t>20/05/2026 07:23 p. m.</t>
-        </is>
-      </c>
-      <c r="B273" s="6" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C273" s="6" t="inlineStr">
-        <is>
-          <t>El Espectador</t>
-        </is>
-      </c>
-      <c r="D273" s="7" t="inlineStr">
-        <is>
-          <t>Ejército despliega más de 120 soldados por enfrentamientos entre comunidad nasa y misak</t>
-        </is>
-      </c>
-      <c r="E273" s="8" t="inlineStr">
-        <is>
-          <t>https://www.elespectador.com/judicial/ejercito-despliega-mas-de-120-soldados-por-enfrentamientos-entre-comunidad-nasa-y-misak/</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="3" t="inlineStr">
-        <is>
-          <t>20/05/2026 07:20 p. m.</t>
-        </is>
-      </c>
-      <c r="B274" s="3" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C274" s="3" t="inlineStr">
-        <is>
-          <t>El Espectador</t>
-        </is>
-      </c>
-      <c r="D274" s="4" t="inlineStr">
-        <is>
-          <t>Sebastián Villa, figura en Copa Libertadores: marcó y asistió en el triunfo de su equipo</t>
-        </is>
-      </c>
-      <c r="E274" s="5" t="inlineStr">
-        <is>
-          <t>https://www.elespectador.com/deportes/futbol-mundial/sebastian-villa-figura-en-copa-libertadores-marco-y-asistio-en-el-triunfo-de-su-equipo/</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="6" t="inlineStr">
-        <is>
-          <t>20/05/2026 07:15 p. m.</t>
-        </is>
-      </c>
-      <c r="B275" s="6" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C275" s="6" t="inlineStr">
-        <is>
-          <t>El Espectador</t>
-        </is>
-      </c>
-      <c r="D275" s="7" t="inlineStr">
-        <is>
-          <t>Más apoyo para el ciclismo colombiano: así funcionará la alianza con LATAM</t>
-        </is>
-      </c>
-      <c r="E275" s="8" t="inlineStr">
-        <is>
-          <t>https://www.elespectador.com/deportes/ciclismo/mas-apoyo-para-el-ciclismo-colombiano-asi-funcionara-la-alianza-con-latam/</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="3" t="inlineStr">
-        <is>
-          <t>20/05/2026 07:10 p. m.</t>
-        </is>
-      </c>
-      <c r="B276" s="3" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C276" s="3" t="inlineStr">
-        <is>
-          <t>El Espectador</t>
-        </is>
-      </c>
-      <c r="D276" s="4" t="inlineStr">
-        <is>
-          <t>No aceptaron cargos: Sequera y Hernández, imputados por dos cargos en el caso Yulixa Toloza</t>
-        </is>
-      </c>
-      <c r="E276" s="5" t="inlineStr">
-        <is>
-          <t>https://www.elespectador.com/bogota/audiencia-en-vivo-del-caso-yulixa-toloza-fiscalia-entrega-mas-detalles-de-la-investigacion/</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="6" t="inlineStr">
-        <is>
-          <t>20/05/2026 07:04 p. m.</t>
-        </is>
-      </c>
-      <c r="B277" s="6" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C277" s="6" t="inlineStr">
-        <is>
-          <t>El Espectador</t>
-        </is>
-      </c>
-      <c r="D277" s="7" t="inlineStr">
-        <is>
-          <t>Invamer: Cepeda (44,6 %), De la Espriella (31,6 %) y Valencia (14 %) lideran la contienda</t>
-        </is>
-      </c>
-      <c r="E277" s="8" t="inlineStr">
-        <is>
-          <t>https://www.elespectador.com/politica/elecciones-colombia-2026/encuesta-invamer-ivan-cepeda-abelardo-de-la-espriella-y-paloma-valencia-lideran-la-contienda-asi-les-fue/</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" s="3" t="inlineStr">
-        <is>
-          <t>20/05/2026 07:02 p. m.</t>
-        </is>
-      </c>
-      <c r="B278" s="3" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C278" s="3" t="inlineStr">
-        <is>
-          <t>El Espectador</t>
-        </is>
-      </c>
-      <c r="D278" s="4" t="inlineStr">
-        <is>
-          <t>Mauricio García Villegas aboga por volver a la razón “Antes de perder el juicio”</t>
-        </is>
-      </c>
-      <c r="E278" s="5" t="inlineStr">
-        <is>
-          <t>https://www.elespectador.com/el-magazin-cultural/mauricio-garcia-villegas-aboga-por-volver-a-la-razon-antes-de-perder-el-juicio/</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="6" t="inlineStr">
-        <is>
-          <t>20/05/2026 07:02 p. m.</t>
-        </is>
-      </c>
-      <c r="B279" s="6" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C279" s="6" t="inlineStr">
-        <is>
-          <t>El Espectador</t>
-        </is>
-      </c>
-      <c r="D279" s="7" t="inlineStr">
-        <is>
-          <t>Chancla de Call of Duty: ¿Cómo conseguir la nueva arma por el Día de la Madre?</t>
-        </is>
-      </c>
-      <c r="E279" s="8" t="inlineStr">
-        <is>
-          <t>https://www.elespectador.com/tecnologia/videojuegos/chancla-de-call-of-duty-como-conseguir-la-nueva-arma-por-el-dia-de-la-madre/</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E279"/>
+  <autoFilter ref="A1:E234"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -8242,51 +6959,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E232" r:id="rId231"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E233" r:id="rId232"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E234" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E235" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E237" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E241" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E242" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E243" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E244" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E245" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E246" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E247" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E248" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E249" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E250" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E251" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E252" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E253" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E254" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E255" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E256" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E257" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E258" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E259" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E260" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E261" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E262" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E263" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E264" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E265" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E266" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E267" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E268" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E269" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E270" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E271" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E272" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E273" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E274" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E275" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E276" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E277" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E278" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E279" r:id="rId278"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/ultimahora.xlsx
+++ b/public/ultimahora.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Todas las noticias" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Todas las noticias'!$A$1:$E$354</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Todas las noticias'!$A$1:$E$319</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -41,7 +41,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -61,16 +61,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFEF5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EAF2FB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5FBFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -106,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -130,24 +120,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -515,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E354"/>
+  <dimension ref="A1:E319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -555,7 +527,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:30 p. m.</t>
+          <t>30/05/2026 08:33 p. m.</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -570,19 +542,19 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Stefany Cuadrado, Kevin Quintero y Edwin Matiz hicieron un reconocimiento al velódromo de Mosquera</t>
+          <t>#ElFiltro: video sobre supuestos tarjetones marcados a favor de Abelardo de la Espriella y Paloma Valencia no corresponde a elecciones presidenciales</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/deportes/ciclismo/stefany-cuadrado-kevin-quintero-y-edwin-matiz-hicieron-un-reconocimiento-al-velodromo-de-mosquera-3559570</t>
+          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/elfiltro-video-sobre-supuestos-tarjetones-marcados-a-favor-de-abelardo-de-la-espriella-y-paloma-valencia-no-corresponde-a-elecciones-presidenciales-3559703</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:21 p. m.</t>
+          <t>30/05/2026 08:29 p. m.</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -597,19 +569,19 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Lotería de Risaralda: conozca los números ganadores del viernes 29 de mayo de 2026</t>
+          <t>Cristhian Mosquera, español de raíces colombianas, aguanta críticas y burlas tras cometer penalti decisivo en la final de la Champions League</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/economia/finanzas-personales/loteria-de-risaralda-conozca-los-numeros-ganadores-del-viernes-29-de-mayo-de-3559596</t>
+          <t>https://www.eltiempo.com/deportes/futbol-internacional/cristhian-mosquera-espanol-de-raices-colombianas-aguanta-criticas-y-burlas-tras-cometer-penalti-decisivo-en-la-final-de-la-champions-league-3559704</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:17 p. m.</t>
+          <t>30/05/2026 08:13 p. m.</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -624,19 +596,19 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Millonarios cierra el semestre con clasificación y humillación al Atlético FC en la Copa Colombia: 1-8</t>
+          <t>Cuentas Claras / Air-e, patrimonio que cae casi en su totalidad</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/deportes/futbol-colombiano/millonarios-cierra-el-semestre-con-clasificacion-y-humillacion-al-atletico-fc-en-la-copa-colombia-1-3559594</t>
+          <t>https://www.eltiempo.com/economia/sectores/cuentas-claras-air-e-patrimonio-que-cae-casi-en-su-totalidad-3559633</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:10 p. m.</t>
+          <t>30/05/2026 08:01 p. m.</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -651,19 +623,19 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>A una década de la intervención del Bronx, Leidy desanda los pasos del infierno al que llegó de niña, y donde permaneció 10 años</t>
+          <t>Alejandro Char responde a los señalamientos del presidente Gustavo Petro y asegura que Barranquilla financia la mayor parte del PAE</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/bogota/a-una-decada-de-la-intervencion-del-bronx-leidy-desanda-los-pasos-del-infierno-al-que-llego-de-nina-y-donde-permanecio-10-anos-3559592</t>
+          <t>https://www.eltiempo.com/politica/gobierno/alejandro-char-responde-a-los-senalamientos-del-presidente-gustavo-petro-y-asegura-que-barranquilla-financia-la-mayor-parte-del-pae-3559696</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:08 p. m.</t>
+          <t>30/05/2026 07:31 p. m.</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -678,19 +650,19 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>#ElFiltro: EL TIEMPO no publicó que Sofía Petro vaticinó 'estallido social' si gana Abelardo de la Espriella en elecciones 2026; es una imagen falsa</t>
+          <t>Entrevista de Westcol con Abelardo de la Espriella: porte legal de armas, megacárceles y las principales propuestas de su plan de gobierno</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/elfiltro-el-tiempo-no-publico-que-sofia-petro-vaticino-estallido-social-si-gana-abelardo-de-la-espriella-en-elecciones-2026-es-una-imagen-falsa-3559591</t>
+          <t>https://www.eltiempo.com/cultura/gente/entrevista-de-westcol-con-abelardo-de-la-espriella-su-plan-de-construir-10-megacarceles-y-las-apuestas-clave-de-su-programa-de-gobierno-3559697</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:07 p. m.</t>
+          <t>30/05/2026 07:00 p. m.</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -705,19 +677,19 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Barcelona le 'roba' al Bayern Múnich la joya de la corona de la Liga Premier por una estrambótica cifra</t>
+          <t>Autoridades de Nariño investigan amenazas de grupo armado contra campesinos previo a elecciones presidenciales: ‘Se va a exigir certificado electoral’</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/deportes/futbol-internacional/barcelona-le-roba-al-bayern-munich-la-joya-de-la-corona-de-la-liga-premier-por-una-estrambotica-cifra-3559574</t>
+          <t>https://www.eltiempo.com/colombia/cali/autoridades-de-narino-investigan-amenazas-de-grupo-armado-contra-campesinos-previo-a-elecciones-presidenciales-se-va-a-exigir-certificado-electoral-3559695</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:01 p. m.</t>
+          <t>30/05/2026 06:57 p. m.</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -732,19 +704,19 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>El futuro está en juego</t>
+          <t>Andrés Llinás pone el pecho por el mal semestre de Millonarios y les habla claro a los hinchas: 'No estuvimos a la altura'</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/opinion/caricaturas/el-futuro-esta-en-juego-3559559</t>
+          <t>https://www.eltiempo.com/deportes/futbol-colombiano/andres-llinas-pone-el-pecho-por-el-mal-semestre-de-millonarios-y-les-habla-claro-a-los-hinchas-no-estuvimos-a-la-altura-3559691</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:01 p. m.</t>
+          <t>30/05/2026 06:36 p. m.</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -759,19 +731,19 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Fuerte verano</t>
+          <t>Abuelita de Pereira envió $700 mil al Nequi equivocado y lanza desesperado llamado para recuperar su dinero: 'Devuélvanme la platica'</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/opinion/caricaturas/fuerte-verano-3559558</t>
+          <t>https://www.eltiempo.com/cultura/gente/abuelita-de-pereira-envio-700-mil-al-nequi-equivocado-y-lanza-desesperado-llamado-para-recuperar-su-dinero-devuelvanme-la-platica-3559693</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:01 p. m.</t>
+          <t>30/05/2026 06:31 p. m.</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -786,19 +758,19 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Tecnoproselitismo</t>
+          <t>De caminatas en el campo a innovación sostenible: la historia de Fungalic, el proyecto que transforma residuos en soluciones con hongos</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/opinion/caricaturas/tecnoproselitismo-3559557</t>
+          <t>https://www.eltiempo.com/colombia/medellin/de-caminatas-en-el-campo-a-innovacion-sostenible-la-historia-de-fungalic-el-proyecto-que-transforma-residuos-en-soluciones-con-hongos-3559692</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:01 p. m.</t>
+          <t>30/05/2026 06:30 p. m.</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -813,19 +785,19 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>A prueba la primera línea del metro</t>
+          <t>Así blindará Bogotá su seguridad para las elecciones de este domingo 29 de mayo: 11.000 policías, 2.100 soldados y ley seca</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/opinion/caricaturas/a-prueba-la-primera-linea-del-metro-3559556</t>
+          <t>https://www.eltiempo.com/bogota/asi-blindara-bogota-su-seguridad-para-las-elecciones-de-este-domingo-29-de-mayo-11-000-policias-2-100-soldados-y-ley-seca-3559689</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:01 p. m.</t>
+          <t>30/05/2026 05:57 p. m.</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -840,19 +812,19 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Por quién votar</t>
+          <t>La USO respalda fortalecer la exploración de hidrocarburos para garantizar la sostenibilidad de Ecopetrol de cara a las elecciones presidenciales</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/opinion/columnistas/por-quien-votar-3559553</t>
+          <t>https://www.eltiempo.com/economia/sectores/la-union-sindical-obrera-uso-respalda-fortalecer-la-exploracion-de-hidrocarburos-para-garantizar-la-sostenibilidad-de-ecopetrol-3559690</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:01 p. m.</t>
+          <t>30/05/2026 05:48 p. m.</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -867,19 +839,19 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Carta de navegación</t>
+          <t>109 vidas perdidas en 2026: así acompaña Medellín a las familias que enfrentan el duelo por accidentes de tránsito</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/opinion/editorial/carta-de-navegacion-3559547</t>
+          <t>https://www.eltiempo.com/colombia/medellin/109-vidas-perdidas-en-2026-asi-acompana-medellin-a-las-familias-que-enfrentan-el-duelo-por-accidentes-de-transito-3559687</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:01 p. m.</t>
+          <t>30/05/2026 05:43 p. m.</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -894,19 +866,19 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Propuestas grandilocuentes, capacidades limitadas: la seguridad en las elecciones presidenciales</t>
+          <t>Exclusivo: habla esposa del candidato presidencial Santiago Botero, desalojado en Cartagena por presunto caso de violencia intrafamiliar</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/opinion/columnistas/propuestas-grandilocuentes-capacidades-limitadas-la-seguridad-en-las-elecciones-presidenciales-3559527</t>
+          <t>https://www.eltiempo.com/colombia/otras-ciudades/exclusivo-habla-esposa-del-candidato-presidencial-santiago-botero-desalojado-en-cartagena-por-violencia-intrafamiliar-a-horas-de-abrirse-las-urnas-3559682</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:01 p. m.</t>
+          <t>30/05/2026 05:40 p. m.</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -921,19 +893,19 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>El eterno femenino</t>
+          <t>Falleció el cuñado de alias ‘Castor’ tras más de dos meses hospitalizado: estaba herido desde la balacera afuera de billar en el norte de Barranquilla</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/opinion/columnistas/el-eterno-femenino-3559518</t>
+          <t>https://www.eltiempo.com/colombia/barranquilla/fallecio-el-cunado-de-alias-castor-tras-mas-de-dos-meses-hospitalizado-estaba-herido-desde-la-balacera-afuera-de-billar-en-el-norte-de-barranquilla-3559688</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:01 p. m.</t>
+          <t>30/05/2026 05:15 p. m.</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -948,19 +920,19 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Paloma presidenta</t>
+          <t>Tragedia en la vía Santa Marta-Palomino: una pasajera se cayó cuando intentaba subirse a la buseta y murió arrollada por el mismo vehículo</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/opinion/columnistas/paloma-presidenta-3559509</t>
+          <t>https://www.eltiempo.com/colombia/otras-ciudades/tragedia-en-la-via-santa-marta-palomino-una-pasajera-se-cayo-cuando-intentaba-subirse-a-la-buseta-y-murio-arrollada-por-el-mismo-vehiculo-3559683</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:01 p. m.</t>
+          <t>30/05/2026 05:12 p. m.</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -975,19 +947,19 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>La elección más sencilla</t>
+          <t>Shakira comparte video bailando con los Ghetto Kids, el grupo ugandés que la acompañará en la final del Mundial 2026</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/opinion/columnistas/la-eleccion-mas-sencilla-3559445</t>
+          <t>https://www.eltiempo.com/cultura/gente/shakira-comparte-video-bailando-con-los-ghetto-kids-el-grupo-ugandes-que-la-acompanara-en-la-final-del-mundial-3559686</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:01 p. m.</t>
+          <t>30/05/2026 05:05 p. m.</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1002,19 +974,19 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>‘La Constitución soy yo’</t>
+          <t>Revelan el detrás de cámaras de 'Dai Dai', el video de Shakira del Mundial 2026, con Luis Díaz y las estrellas del Bayern Múnich</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/opinion/columnistas/la-constitucion-soy-yo-3559442</t>
+          <t>https://www.eltiempo.com/deportes/futbol-internacional/revelan-el-detras-de-camaras-de-dai-dai-el-video-de-shakira-del-mundial-2026-con-luis-diaz-y-las-estrellas-del-bayern-munich-3559684</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:01 p. m.</t>
+          <t>30/05/2026 04:39 p. m.</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -1029,19 +1001,19 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>‘Autopoiesis’</t>
+          <t>Meteorito explota en Estados Unidos y genera un potente estruendo que se escuchó en varios estados</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/opinion/columnistas/autopoiesis-3559440</t>
+          <t>https://www.eltiempo.com/mundo/eeuu-y-canada/meteorito-explota-en-estados-unidos-y-genera-un-potente-estruendo-que-se-escucho-en-varios-estados-3559677</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:01 p. m.</t>
+          <t>30/05/2026 04:36 p. m.</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1056,19 +1028,19 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Colombia, un país al borde del abismo</t>
+          <t>Juan Valdez le propone que tome café colombiano con el ‘sabor’ de su apellido</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/opinion/columnistas/colombia-un-pais-al-borde-del-abismo-3559437</t>
+          <t>https://www.eltiempo.com/economia/empresas/juan-valdez-le-propone-que-tome-cafe-colombiano-con-el-sabor-de-su-apellido-3559680</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 09:59 p. m.</t>
+          <t>30/05/2026 04:34 p. m.</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -1083,19 +1055,19 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Conozca acá los resultados del último sorteo de la Lotería de Medellín del viernes 29 de mayo de 2026</t>
+          <t>Disturbios en París tras el triunfo del PSG en la Champions: 79 detenidos, caos y un policía herido</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/economia/finanzas-personales/conozca-aca-los-resultados-del-ultimo-sorteo-de-la-loteria-de-medellin-del-viernes-29-de-mayo-de-3559589</t>
+          <t>https://www.eltiempo.com/mundo/europa/disturbios-en-paris-tras-el-triunfo-del-psg-en-la-champions-79-detenidos-caos-y-un-policia-herido-3559681</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 03:15 a. m.</t>
+          <t>31/05/2026 01:37 a. m.</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1110,19 +1082,19 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>“Paloma no tiene apoyos clandestinos, ni esconde apoyos”: Álvaro Uribe se reunió con la candidata ad portas de elecciones</t>
+          <t>Millones de usuarios recibirán devolución por cobros indebidos en facturas de gas: cómo reclamar el dinero</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/politica/paloma-valencia-no-tiene-apoyos-clandestinos-alvaro-uribe-reunion-candidata-centro-democratico-400843</t>
+          <t>https://www.lafm.com.co/actualidad/devolucion-facturas-gas-cobros-indebidos-guia-reclamar-dinero-400897</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 02:54 a. m.</t>
+          <t>31/05/2026 01:05 a. m.</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -1137,19 +1109,19 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Alejandro Estrada se corona ganador de La Casa de los Famosos 2026</t>
+          <t>“Los tengo que parar de entrenar”: la revelación de Luis Enrique sobre la plantilla del PSG</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/entretenimiento/alejandro-estrada-nuevo-ganador-la-casa-de-los-famosos-2026-400840</t>
+          <t>https://www.lafm.com.co/deportes/luis-enrique-aseguro-que-debe-parar-de-entrenar-a-jugadores-psg-400896</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 02:51 a. m.</t>
+          <t>31/05/2026 12:43 a. m.</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1164,19 +1136,19 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Certificado electoral 2026: pasos para obtener una copia si perdió el documento</t>
+          <t>Anuncian cierres viales por obras del Regiotram Occidente en Bogotá y Cundinamarca: rutas y fechas clave</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/actualidad/pasos-para-obtener-copia-certificado-electoral-400841</t>
+          <t>https://www.lafm.com.co/actualidad/cierres-por-obras-del-regiotram-occidente-afectaran-vias-en-bogota-y-cundinamarca-400895</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 02:13 a. m.</t>
+          <t>30/05/2026 09:39 p. m.</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1191,19 +1163,19 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Beneficios para estudiantes que votan: así funciona el descuento en matrícula</t>
+          <t>Video mostraría los últimos minutos de Alexander Avendaño en Guatapé; lo estarían golpeando antes de caer al embalse: “Ahóguenlo”</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/politica/beneficios-estudiantes-certificado-electoral-400837</t>
+          <t>https://www.lafm.com.co/actualidad/video-alexander-avendano-ultimos-minutos-antes-de-caer-al-embalse-guatape-400876</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 01:52 a. m.</t>
+          <t>30/05/2026 08:30 p. m.</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,19 +1190,19 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>La ciudad colombiana que entró al ranking de las más felices del mundo en 2026</t>
+          <t>Mincomercio responde al anuncio de Ecuador sobre aranceles en remate de la campaña electoral</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/sociedad/medellin-entre-ciudades-mas-felices-del-mundo-ranking-400833</t>
+          <t>https://www.lafm.com.co/economia/ministra-de-comercio-aranceles-ecuador-campana-electoral-colombia-abelardo-de-la-espriella-daniel-noboa-400883</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 01:38 a. m.</t>
+          <t>30/05/2026 08:22 p. m.</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -1245,19 +1217,19 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>SuperSalud selló el servicio de cirugía plástica de la Clínica de Obesidad y Envejecimiento: hay varias denuncias</t>
+          <t>Medios iraníes dicen que borrador de acuerdo con EEUU incluye desbloqueo de USD 12.000 millones en activos</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/sociedad/supersalud-sello-servicio-cirugia-plastica-clinica-obesidad-envejecimiento-denuncias-pacientes-400826</t>
+          <t>https://www.lafm.com.co/internacional/ormuz-negociaciones-trump-naval-estrecho-dinero-borrador-400888</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 01:00 a. m.</t>
+          <t>30/05/2026 08:21 p. m.</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1272,19 +1244,19 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Elecciones 2026: ¿cuántos votos se necesitan para ganar la Presidencia en primera vuelta?</t>
+          <t>¿Juan Fernando Quintero se va de River Plate? Las posibles salidas de ídolos colombianos tras el Mundial 2026</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/politica/elecciones-2026-cuantos-votos-se-necesitan-para-ganar-la-presidencia-en-primera-vuelta-400821</t>
+          <t>https://www.lafm.com.co/deportes/quintero-podria-salir-de-river-plate-tras-el-mundial-2026-carrascal-james-rodriguez-400886</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 12:33 a. m.</t>
+          <t>30/05/2026 07:32 p. m.</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -1299,19 +1271,19 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Registraduría responde a Petro y defiende la seguridad de las actas electorales: “el código hash sigue vigente”</t>
+          <t>Procuraduría indaga si funcionario de la ANT en Arauca participa indebidamente en política</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/politica/registraduria-responde-petro-defiende-seguridad-actas-electorales-400828</t>
+          <t>https://www.lafm.com.co/politica/procuraduria-indaga-funcionario-ant-arauca-participacion-indebida-en-politica-400887</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 12:24 a. m.</t>
+          <t>30/05/2026 07:10 p. m.</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1326,19 +1298,19 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Calendario lunar de junio 2026: ¿Cuál es el mejor día del mes para cortar el cabello para que crezca?</t>
+          <t>Alejandro Estrada: ¿Quién es el ganador de La Casa de los Famosos 2026 y cuánto dinero se llevó?</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/sociedad/calendario-lunar-junio-2026-mejor-dia-cortar-cabello-para-que-crezca-400829</t>
+          <t>https://www.lafm.com.co/entretenimiento/quien-es-alejandro-estrada-ganador-de-la-casa-de-los-famosos-2026-400881</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 11:35 p. m.</t>
+          <t>30/05/2026 06:12 p. m.</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -1353,19 +1325,19 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Enrique Peñalosa defendió el metro elevado y lanzó pullas al presidente Petro: “Dice muchas mentiras”</t>
+          <t>Todo lo que se sabe del desalojo del candidato presidencial Santiago Botero por presunta violencia intrafamiliar: 'Echó a su esposa y a su hijo'</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/actualidad/enrique-penalosa-defendio-metro-elevado-critico-a-gustavo-petro-400827</t>
+          <t>https://www.lafm.com.co/actualidad/por-que-desalojaron-a-santiago-botero-por-presunto-caso-de-violencia-intrafamiliar-400878</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 11:11 p. m.</t>
+          <t>30/05/2026 05:59 p. m.</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1380,19 +1352,19 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>El fenómeno Tim Payne, la inesperada estrella del Mundial 2026: pasó del anonimato a la fama internacional en 48 horas</t>
+          <t>Elecciones presidenciales: así funcionará el Puesto de Mando Unificado Cibernético para evitar delitos electorales</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/deportes/fenomeno-tim-payne-viral-en-48-horas-400825</t>
+          <t>https://www.lafm.com.co/orden-publico/elecciones-presidenciales-puesto-mando-unificado-cibernetico-policia-nacionall-400879</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 11:02 p. m.</t>
+          <t>30/05/2026 05:54 p. m.</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -1407,19 +1379,19 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Elecciones presidenciales 2026: esta es la multa por incumplir la ley seca</t>
+          <t>La Casa de los Famosos confirma temporada 4: todo lo que se sabe hasta ahora</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/politica/elecciones-presidenciales-2026-multa-incumplir-ley-seca-millon-ochocientos-mil-pesos-400823</t>
+          <t>https://www.lafm.com.co/entretenimiento/la-casa-de-los-famosos-tendra-temporada-4-esto-se-sabe-400849</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:37 p. m.</t>
+          <t>30/05/2026 05:40 p. m.</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1434,19 +1406,19 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>FOTOS | Nuevos iPhone 18 Pro y Pro Max: pantallas se acercarían a las 7 pulgadas</t>
+          <t>Gobierno Nacional instala PMU y despliega más de 280 mil uniformados para garantizar la seguridad en las elecciones</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/sociedad/tamano-pantalla-iphone-18-pro-max-mas-grande-de-la-marca-apple-400820</t>
+          <t>https://www.lafm.com.co/politica/gobierno-nacional-instala-pmu-y-despliega-mas-de-280-mil-uniformados-para-garantizar-la-seguridad-en-las-elecciones-400880</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 06:32 p. m.</t>
+          <t>28/05/2026 04:03 p. m.</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -1461,19 +1433,19 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Último sorteo Lotería de Medellín: resultado premio mayor hoy 29 de mayo de 2026</t>
+          <t>Procuraduría pide explicaciones por muerte de estudiante luego de una pelea de boxeo en colegio de Suba</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/sociedad/sorteo-loteria-de-medellin-resultado-premio-mayor-29-de-mayo-2026-400802</t>
+          <t>https://www.lafm.com.co/sociedad/procuraduria-pide-explicacion-muerte-estudiante-practicando-boxeo-400885</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 12:52 a. m.</t>
+          <t>05/05/2026 01:51 p. m.</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1488,19 +1460,19 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Ecuador eliminará aranceles a productos colombianos tras diálogo entre Daniel Noboa y Abelardo de la Espriella</t>
+          <t>“Las mujeres se respetan”: Paloma Valencia rechaza agresiones contra exparejas de Santiago Botero y Alejandro Bermeo</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/politica/ecuador-eliminara-aranceles-a-productos-colombianos-400831</t>
+          <t>https://www.lafm.com.co/politica/paloma-valencia-yamile-trigueros-manuela-echeverri-violencia-genero-mujeres-santiago-botero-alejandro-bermeo-400890</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>25/05/2026 10:56 p. m.</t>
+          <t>28/04/2026 02:31 p. m.</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -1515,19 +1487,19 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>MinDefensa sobre muerte de disidentes en el Guaviare: "las asonadas le abrieron espacio a los criminales"</t>
+          <t>Estremecedor caso de abuso y secuestro contra una menor indígena en Cali: la víctima tiene cuatro años</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/actualidad/ministro-de-defensa-habla-sobre-la-muerte-de-disidentes-en-el-guaviare-400824</t>
+          <t>https://www.lafm.com.co/sociedad/estremecedor-caso-de-abuso-sexual-y-secuestro-contra-una-menor-indigena-en-cali-victima-tiene-cuatro-anos-400882</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>16/05/2026 01:33 a. m.</t>
+          <t>12/03/2026 07:16 p. m.</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1542,12 +1514,12 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Colpensiones explicó cuánto deben pagar los colombianos por una semana de pensión en 2026</t>
+          <t>Sociedad de Cirugía Plástica respalda regulación para combatir procedimientos estéticos ilegales</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/economia/cuanto-cuesta-una-semana-de-pension-2026-400832</t>
+          <t>https://www.lafm.com.co/sociedad/sociedad-cirugia-plastica-regulacion-procedimientos-esteticos-ilegales-400884</t>
         </is>
       </c>
     </row>
@@ -1565,12 +1537,12 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Fórmulas vicepresidenciales 2026: lista completa de candidatos en el tarjetón</t>
+          <t>"Comprometámonos a respetar los resultados”: Procurador asegura que Colombia está lista para votar en paz este domingo</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/politica/formulas-vicepresidenciales-elecciones-2026-lista-completa-candidatos-tarjeton-400835</t>
+          <t>https://www.lafm.com.co/politica/elecciones-presidenciales-procurador-gregorio-eljach-pide-respetar-los-resultados-colombia-esta-lista-para-votar-en-paz-400893</t>
         </is>
       </c>
     </row>
@@ -1588,12 +1560,12 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>¿Cómo identificar señales de manipulación y establecer límites? Julián Matheus explica</t>
+          <t>Prima para empleadas domésticas por días: cómo calcularla paso a paso y cuánto deben pagar en 2026</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/sociedad/manipulacion-senales-y-limites-julian-matheus-psicologo-400834</t>
+          <t>https://www.lafm.com.co/economia/prima-empleadas-domesticas-por-dias-como-calcular-en-2026-400892</t>
         </is>
       </c>
     </row>
@@ -1611,19 +1583,19 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Después de nueve años, Slayer vuelve a Colombia: detalles de la boletería, localidades y escenario</t>
+          <t>Soacha declara alerta amarilla hospitalaria por sobreocupación en urgencias que supera el 200 %</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/entretenimiento/slayer-colombia-thrash-metal-boleteria-localidades-escenario-400830</t>
+          <t>https://www.lafm.com.co/sociedad/hospitales-soacha-alerta-amarilla-ocupacion-maximo-crisis-salud-medicamentos-400877</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 12:00 a. m.</t>
+          <t>31/05/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1638,19 +1610,19 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Petro se subió a un carro por la ventana para defender su gestión en particular entrevista con influenciadores: “La gente se me junta mucho”</t>
+          <t>Karina García barajó la posibilidad de que su hija Isabella se sume a ‘La casa de los famosos Colombia’ en 2027 y le llovieron críticas</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/30/petro-se-subio-a-un-carro-por-la-ventana-para-defender-su-gestion-en-particular-entrevista-con-influenciadores-la-gente-se-me-junta-mucho/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/karina-garcia-barajo-la-posibilidad-de-que-su-hija-isabella-se-sume-a-la-casa-de-los-famosos-colombia-en-2027-y-le-llovieron-criticas/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 12:00 a. m.</t>
+          <t>31/05/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -1665,19 +1637,19 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Richard Ríos descartó una salida al Real Madrid para reunirse nuevamente con Mourinho</t>
+          <t>Abelardo de la Espriella aseguró que defendería a Westcol si mata a un ladrón: “Así venga con un peluche, le disparas”</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/deportes/2026/05/30/richard-rios-descarto-una-salida-al-real-madrid-para-reunirse-nuevamente-con-mourinho/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/abelardo-de-la-espriella-aseguro-que-defenderia-a-westcol-si-mata-a-un-ladron-asi-venga-con-un-peluche-le-disparas/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 12:00 a. m.</t>
+          <t>31/05/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1692,19 +1664,19 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Caribeña Noche, resultado del último sorteo hoy sábado 30 de mayo</t>
+          <t>Colombia ante las urnas: Izquierda, derecha y un ‘outsider’ se disputan la presidencia</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/30/caribena-noche-resultado-del-ultimo-sorteo-hoy-sabado-30-de-mayo/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/colombia-ante-las-urnas-izquierda-derecha-y-un-outsider-se-disputan-la-presidencia/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 12:00 a. m.</t>
+          <t>31/05/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
@@ -1719,19 +1691,19 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Los candidatos tienen todo listo para su jornada electoral: en estos puntos votarán los principales aspirantes a la Casa de Nariño</t>
+          <t>Lo que esconde el clóset de los candidatos presidenciales: los mensajes en la ropa de Cepeda, Valencia y De la Espriella</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/30/candidatos-tienen-todo-listo-para-su-jornada-electoral-en-estos-puntos-votaran-los-principales-aspirantes-a-la-casa-de-narino/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/ivan-cepeda-abelardo-de-la-espriella-y-paloma-valencia-convierten-su-ropa-en-mensaje-clave-de-campana/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 12:00 a. m.</t>
+          <t>31/05/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1746,19 +1718,19 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Alejandro Estrada, esta es la historia del ganador de la tercera temporada de ‘La casa de los famosos Colombia’</t>
+          <t>Debate programático entre una política de paz o una política de seguridad que la desconozca o subordine</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/30/alejandro-estrada-esta-es-la-historia-del-ganador-de-la-tercera-temporada-de-la-casa-de-los-famosos-colombia/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/debate-programatico-entre-una-politica-de-paz-o-una-politica-de-seguridad-que-la-desconozca-o-subordine/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 12:00 a. m.</t>
+          <t>31/05/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -1773,19 +1745,19 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Ojo viajeros: Avianca lanzó alerta urgente por nueva estafa que afecta a pasajeros con tiquetes ya comprados</t>
+          <t>IPS advierten que medida del Gobierno de aumentar el giro directo no resolverá por sí solo la crisis del sistema de salud: esto propusieron</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/30/ojo-viajeros-avianca-lanzo-alerta-urgente-por-nueva-estafa-que-afecta-a-pasajeros-con-tiquetes-ya-comprados/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/ips-advierten-que-medida-del-gobierno-de-aumentar-el-giro-directo-no-resolvera-por-si-solo-la-crisis-del-sistema-de-salud-esto-propusieron/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 12:00 a. m.</t>
+          <t>31/05/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1800,19 +1772,19 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Paola Turbay anunció que votará por Paloma Valencia en primera vuelta: “Va a enfrentar uno de los retos más grandes de la historia”</t>
+          <t>Estados Alterados, Funk Tribu, Karen Lizarazo, Jungle y más: estos son los lanzamientos destacados de la semana</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/30/paola-turbay-anuncio-que-votara-por-paloma-valencia-en-primera-vuelta-va-a-enfrentar-uno-de-los-retos-mas-grandes-de-la-historia/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/estados-alterados-funk-tribu-karen-lizarazo-jungle-y-mas-estos-son-los-lanzamientos-destacados-de-la-semana/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 12:00 a. m.</t>
+          <t>31/05/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -1827,19 +1799,19 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>La Registraduría le respondió a Petro sobre el riesgo de alteración de los escrutinios: “Vale la pena precisar”</t>
+          <t>Iván Duque resaltó la importancia de su gobierno para las elecciones de 2026:  dos de sus funcionarios podrán ser vicepresidente</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/30/la-registraduria-le-respondio-a-petro-sobre-el-riesgo-de-alteracion-de-los-escrutinios-vale-la-pena-precisar/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/ivan-duque-resalto-la-importancia-de-su-gobierno-para-las-elecciones-de-2026-dos-de-sus-funcionarios-podran-ser-vicepresidente/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 12:00 a. m.</t>
+          <t>31/05/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -1854,19 +1826,19 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>En Medellín se ejecutó un proceso de extinción de dominio sobre 42 inmuebles en los que se robaban el agua, la energía y el gas</t>
+          <t>La IA como herramienta de comunicación política en la campaña presidencial: ruido, emociones y degradación de la deliberación pública</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/30/en-medellin-se-ejecuto-un-proceso-de-extincion-de-dominio-sobre-42-inmuebles-en-los-que-se-robaban-el-agua-la-energia-y-el-gas/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/la-ia-como-herramienta-de-comunicacion-politica-en-la-campana-presidencial-ruido-emociones-y-degradacion-de-la-deliberacion-publica/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 12:00 a. m.</t>
+          <t>31/05/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -1881,19 +1853,19 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Carlos Vives reveló detalles de un apasionado beso que se dio con Amparo Grisales en una grabación: “Qué cosa más increíble”</t>
+          <t>Elementos comunes sobre la paz en el escenario electoral</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/30/carlos-vives-revelo-detalles-de-un-apasionado-beso-que-se-dio-con-amparo-grisales-en-una-grabacion-que-cosa-mas-increible/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/los-denominadores-comunes-de-los-escenarios-electorales/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 12:00 a. m.</t>
+          <t>31/05/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -1908,19 +1880,19 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>El mercado en Colombia es cada vez más caro: estos son los factores que están disparando el precio de los alimentos</t>
+          <t>Colombia 2026: realismo hemisférico para el próximo gobierno</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/30/el-mercado-en-colombia-es-cada-vez-mas-caro-estos-son-los-factores-que-estan-disparando-el-precio-de-los-alimentos/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/colombia-2026-realismo-hemisferico-para-el-proximo-gobierno/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 12:00 a. m.</t>
+          <t>31/05/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -1935,19 +1907,19 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>El Tiempo respaldó la denuncia penal de Jineth Bedoya contra Gabriel Meluk por presunto acoso sexual laboral</t>
+          <t>Gobernar en la polarización: El complejo escenario legislativo para Iván Cepeda</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/30/el-tiempo-respaldo-la-denuncia-penal-de-jineth-bedoya-contra-gabriel-meluk-por-presunto-acoso-sexual-laboral/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/gobernar-en-la-polarizacion-el-complejo-escenario-legislativo-para-ivan-cepeda/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 12:00 a. m.</t>
+          <t>31/05/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -1962,19 +1934,19 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Simón Mesa Soto salió en defensa de la adaptación extranjera de ‘Un Poeta’: “No veo nada malo en ganar dinero con mi trabajo”</t>
+          <t>La Procuraduría desplegará un ejército de vigilancia para las elecciones presidenciales en Colombia</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/30/simon-mesa-soto-salio-en-defensa-de-la-adaptacion-extranjera-de-un-poeta-no-veo-nada-malo-en-ganar-dinero-con-mi-trabajo/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/la-procuraduria-desplegara-un-ejercito-de-vigilancia-para-las-elecciones-presidenciales-en-colombia/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 12:00 a. m.</t>
+          <t>31/05/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -1989,12 +1961,12 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Mala noticia para quienes tienen tarjeta de crédito: puede salir más caro hacer compras en junio</t>
+          <t>Nuevos detalles de la denuncia contra el senador Alejandro Bermeo: víctima relató amenazas, golpes y presunto abuso tras una relación de dos años</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/30/mala-noticia-para-quienes-tienen-tarjeta-de-credito-puede-salir-mas-caro-hacer-compras-en-junio/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/nuevos-detalles-de-la-denuncia-contra-el-senador-alejandro-bermeo-victima-relato-amenazas-golpes-y-presunto-abuso-tras-una-relacion-de-dos-anos/</t>
         </is>
       </c>
     </row>
@@ -2016,12 +1988,12 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Sheila Gandara encendió las redes sociales con sesión de fotos y una supuesta indirecta para Juanda Caribe: “Una mejor versión”</t>
+          <t>Esposa de Santiago Botero habló del calvario que vivió junto al candidato: “Soporté muchos meses de violencia intrafamiliar”</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/30/sheila-gandara-encendio-las-redes-sociales-con-sesion-de-fotos-y-una-supuesta-indirecta-para-juanda-caribe-una-mejor-version/</t>
+          <t>https://www.infobae.com/colombia/2026/05/30/esposa-de-santiago-botero-hablo-del-calvario-que-vivio-junto-al-candidato-soporte-muchos-meses-de-violencia-intrafamiliar/</t>
         </is>
       </c>
     </row>
@@ -2043,12 +2015,12 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Ecuador eliminará aranceles a las exportaciones colombianas desde el 1 de junio: así lo anunció el presidente Daniel Noboa</t>
+          <t>Lanzan alerta desde la gobernación del Magdalena por posibles cortes de energía durante las elecciones presidenciales</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/30/ecuador-eliminara-los-aranceles-a-exportaciones-colombianas-desde-el-1-de-junio-asi-lo-anuncio-el-presidente-daniel-noboa/</t>
+          <t>https://www.infobae.com/colombia/2026/05/30/lanzan-alerta-desde-la-gobernacion-del-magdalena-por-posibles-cortes-de-energia-durante-las-elecciones-presidenciales/</t>
         </is>
       </c>
     </row>
@@ -2070,12 +2042,12 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Una manada de toros y vacas generó caos en Caldas, dos de los animales se metieron a una tienda: “¡Se desbocó!”</t>
+          <t>Gustavo Petro compartió una canción electrónica en sus redes sociales: “Entramos a nuevos géneros del techno”</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/30/una-manada-de-toros-y-vacas-genero-caos-en-caldas-dos-de-los-animales-se-metieron-a-una-tienda-se-desboco/</t>
+          <t>https://www.infobae.com/colombia/2026/05/30/gustavo-petro-compartio-una-cancion-electronica-en-sus-redes-sociales-entramos-a-nuevos-generos-del-techno/</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2069,12 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>El ministro de Defensa explicó el operativo para garantizar la seguridad electoral y pidió “no vender la democracia por un tamal”</t>
+          <t>Vicky Dávila respondió a Paloma Valencia y pidió unión para derrotar a Iván Cepeda: “No fue abandono, fue decepción”</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/30/el-ministro-de-defensa-explico-el-operativo-para-garantizar-la-seguridad-electoral-y-pidio-no-vender-la-democracia-por-un-tamal/</t>
+          <t>https://www.infobae.com/colombia/2026/05/30/vicky-davila-respondio-a-paloma-valencia-y-pidio-union-para-derrotar-a-ivan-cepeda-no-fue-abandono-fue-decepcion/</t>
         </is>
       </c>
     </row>
@@ -2124,19 +2096,19 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Esto es lo que puede pasar si el voto en blanco gana las elecciones en Colombia</t>
+          <t>Armando Benedetti anticipó que buscará la Alcaldía de Barranquilla después de que termine el Gobierno Petro: “Hay una oportunidad”</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/30/esto-es-lo-que-puede-pasar-si-el-voto-en-blanco-gana-las-elecciones-en-colombia/</t>
+          <t>https://www.infobae.com/colombia/2026/05/30/armando-benedetti-anticipo-que-buscara-la-alcaldia-de-barranquilla-despues-que-termine-el-gobierno-petro-hay-una-oportunidad/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 12:00 a. m.</t>
+          <t>30/05/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -2151,19 +2123,19 @@
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Así reaccionó Alejandro Estrada tras ser anunciado como el ganador de ‘La casa de los famosos Colombia’</t>
+          <t>Así funciona la ley colombiana para quienes deciden no votar: no tendría beneficios</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/29/en-vivo-la-casa-de-los-famosos-colombia-define-al-ganador-de-la-tercera-temporada-en-su-gran-final/</t>
+          <t>https://www.infobae.com/colombia/2026/05/30/asi-funciona-la-ley-colombiana-para-quienes-deciden-no-votar-no-tendria-beneficios/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:50 p. m.</t>
+          <t>30/05/2026 09:00 p. m.</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2173,24 +2145,24 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Resultado Lotería de Santander: sorteo del viernes 29 de mayo de 2026</t>
+          <t>Torre de Tokio: vecinos espías</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/loterias/2026/05/29/resultado-loteria-de-santander-sorteo-del-viernes-29-de-mayo-de-2026/</t>
+          <t>https://www.elespectador.com/mundo/columna-torre-de-tokio-vecinos-espias/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:50 p. m.</t>
+          <t>30/05/2026 08:58 p. m.</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -2200,24 +2172,24 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Loterias</t>
+          <t>El montaje judicial que tuvo al borde de la muerte a una lideresa de El Salado</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/loterias/</t>
+          <t>https://www.elespectador.com/judicial/el-montaje-judicial-contra-una-lideresa-de-el-salado-que-la-tuvo-al-borde-de-la-muerte/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:41 p. m.</t>
+          <t>30/05/2026 08:55 p. m.</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2227,24 +2199,24 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>A la cárcel implicado en ataque sicarial en discoteca de Bucaramanga</t>
+          <t>Una mujer permanece en estado crítico luego de ser quemada por su expareja en Neiva</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/judicial/2026/05/29/a-la-carcel-fue-enviado-implicado-en-ataque-sicarial-en-discoteca-de-bucaramanga/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/una-mujer-fue-rociada-con-gasolina-y-quemada-por-su-expareja-en-neiva-el-agresor-esta-libre/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:41 p. m.</t>
+          <t>30/05/2026 08:25 p. m.</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
@@ -2254,24 +2226,24 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Judicial</t>
+          <t>SpaceX, OpenAI y Anthropic impulsan nueva ola de inversión en Asia</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/judicial/</t>
+          <t>https://www.elespectador.com/economia/empresas/el-exito-de-spacex-y-openai-impulsa-apuestas-por-los-proximos-ganadores-asiaticos-en-ia/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:41 p. m.</t>
+          <t>30/05/2026 08:21 p. m.</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2281,24 +2253,24 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Super Astro Luna: número y signo ganador del sorteo del viernes 29 de mayo de 2026</t>
+          <t>Movida Electoral: Así fue el último día de los candidatos presidenciales antes de elección</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/loterias/2026/05/29/super-astro-luna-numero-y-signo-ganador-del-sorteo-del-viernes-29-de-mayo-de-2026/</t>
+          <t>https://www.elespectador.com/politica/elecciones-colombia-2026/cepeda-realizo-155-actos-publicos-de-la-espriella-aceptaria-curul-de-oposicion-si-pierde-valencia-recorre-iglesias-noticias-hoy/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:38 p. m.</t>
+          <t>30/05/2026 08:05 p. m.</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -2308,24 +2280,24 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Sancionada Ley Miguel Uribe Turbay a pocos días de cumplirse un año del atentado que acabó con su vida</t>
+          <t>¿Quiénes encabezan la disputa por la presidencia? Todo lo que debe saber de los candidatos</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/29/ley-miguel-uribe-turbay-fue-sancionada-a-pocos-dias-de-cumplirse-un-ano-del-atentado-que-acabo-con-su-vida/</t>
+          <t>https://www.elespectador.com/politica/elecciones-colombia-2026/candidatos-presidenciales-quienes-son-los-aspirantes-que-encabezan-la-campana-perfiles-y-equipos-noticias-hoy/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:38 p. m.</t>
+          <t>30/05/2026 08:01 p. m.</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2335,24 +2307,24 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Entre euforia, disturbios y cientos de detenidos, París festeja su segunda Orejona</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/</t>
+          <t>https://www.elespectador.com/mundo/entre-euforia-disturbios-y-cientos-de-detenidos-paris-festeja-su-segunda-orejona/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 06:28 p. m.</t>
+          <t>30/05/2026 08:00 p. m.</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -2362,24 +2334,24 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Supersalud ordena acciones urgentes a Cafam por retrasos en entrega de fármacos</t>
+          <t>Receta para preparar lomo con salsa de hongos y pimienta</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/29/supersalud-ordena-acciones-urgentes-a-cafam-por-retrasos-en-entrega-de-farmacos/</t>
+          <t>https://www.elespectador.com/gastronomia-y-recetas/receta-para-preparar-lomo-con-salsa-de-hongos-y-pimienta/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 06:12 p. m.</t>
+          <t>30/05/2026 08:00 p. m.</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2389,24 +2361,24 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Exembajador ligado a Carlos Ramón González permanece en cargo diplomático</t>
+          <t>5 novedades del primer SUV eléctrico de Subaru en Colombia: Trailseeker</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/29/exembajador-ligado-a-carlos-ramon-gonzalez-permanece-en-cargo-diplomatico/</t>
+          <t>https://www.elespectador.com/autos/5-novedades-del-primer-suv-electrico-de-subaru-en-colombia-trailseeker/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 05:59 p. m.</t>
+          <t>30/05/2026 07:21 p. m.</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -2416,24 +2388,24 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Corte Constitucional alerta por hacinamiento y falta de agua en cárcel de Cómbita</t>
+          <t>El nuevo video de Dilan Cruz reabrió el debate, pero no cambió el expediente</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/29/corte-constitucional-alerta-por-hacinamiento-y-falta-de-agua-en-carcel-de-combita/</t>
+          <t>https://www.elespectador.com/judicial/dilan-cruz-el-video-que-se-volvio-viral-y-la-evidencia-que-ya-estaba-en-el-proceso/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 05:15 p. m.</t>
+          <t>30/05/2026 08:59 p. m.</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2443,24 +2415,24 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Ecuador incauta 105 bloques de droga cerca de Colombia y captura a cuatro hombres</t>
+          <t>Colombia, lista para ir a las urnas y elegir a su nuevo presidente(a)</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/29/ecuador-incauta-105-bloques-de-droga-cerca-de-colombia-y-captura-a-cuatro-hombres/</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/colombia-lista-para-ir-a-las-urnas-y-elegir-a-su-nuevo-presidentea-cb20</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 03:16 p. m.</t>
+          <t>30/05/2026 08:06 p. m.</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
@@ -2470,24 +2442,24 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Metro de Bogotá inicia pruebas autónomas de trenes sobre el viaducto elevado</t>
+          <t>Andrés Llinás y una carta abierta por mal semestre de Millonarios; "no estuvimos a la altura"</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/29/metro-de-bogota-inicia-pruebas-autonomas-de-trenes-sobre-el-viaducto-elevado/</t>
+          <t>https://www.noticiascaracol.com/golcaracol/futbol-colombiano/andres-llinas-y-una-carta-abierta-por-mal-semestre-de-millonarios-no-estuvimos-a-la-altura-rg10</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 03:15 p. m.</t>
+          <t>30/05/2026 06:50 p. m.</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2497,24 +2469,24 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Caso Yulixa Toloza: necropsia reveló fracturas en costillas, 11 heridas y un trauma severo</t>
+          <t>Luis Javier Suárez y sus goles con Sporting Lisboa le valieron un reconocimiento en Portugal</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/29/caso-yulixa-toloza-necropsia-revelo-fracturas-en-costillas-11-heridas-y-un-trauma-severo/</t>
+          <t>https://www.noticiascaracol.com/golcaracol/colombianos-en-el-exterior/luis-javier-suarez-y-sus-goles-con-sporting-lisboa-le-valieron-un-reconocimiento-en-portugal-rg10</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 02:11 p. m.</t>
+          <t>30/05/2026 04:23 p. m.</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
@@ -2524,24 +2496,24 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Así fue la recuperación de 48 cuerpos tras combates entre disidencias de ‘Iván Mordisco’ y ‘Calarcá’</t>
+          <t>Video | Encuentran sin vida a joven que cayó al embalse de Guatapé durante fiesta en una embarcación</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/29/asi-fue-la-recuperacion-de-48-cuerpos-tras-enfrentamientos-en-disidencias-de-alias-ivan-mordisco-y-calarca/</t>
+          <t>https://www.noticiascaracol.com/colombia/video-encuentran-sin-vida-a-joven-que-cayo-al-embalse-de-guatape-durante-fiesta-en-una-embarcacion-rg10</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 01:08 p. m.</t>
+          <t>30/05/2026 04:15 p. m.</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2551,24 +2523,24 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Denuncian penalmente a Gabriel Meluk por presunto acoso sexual en El Tiempo</t>
+          <t>Murió Kelly Curtis, actriz y hermana de Jamie Lee Curtis, a los 69 años</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/29/denuncian-penalmente-a-gabriel-meluk-por-presunto-acoso-sexual-en-el-tiempo/</t>
+          <t>https://www.noticiascaracol.com/entretenimiento/murio-kelly-curtis-actriz-y-hermana-de-jamie-lee-curtis-a-los-69-anos-cb20</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 12:28 p. m.</t>
+          <t>30/05/2026 03:49 p. m.</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -2578,24 +2550,24 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Pelea por brutal ataque a un perro terminó con un joven asesinado</t>
+          <t>Resultados Super Astro Sol hoy, sábado 30 de mayo de 2026: números ganadores del último sorteo</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/29/pelea-por-brutal-ataque-a-un-perro-termino-con-un-joven-asesinado/</t>
+          <t>https://www.noticiascaracol.com/economia/resultados-super-astro-sol-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-del-ultimo-sorteo-so35</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:49 p. m.</t>
+          <t>30/05/2026 03:21 p. m.</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2605,24 +2577,24 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>A Petro lo pusieron a hacer la rutina de los soldados del Ejército durante entrevista</t>
+          <t>¿Mercenarios colombianos en México? Así carteles de la droga estarían reclutando exmilitares</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/a-petro-lo-pusieron-a-hacer-la-rutina-de-los-soldados-del-ejercito-durante-entrevista-rs15</t>
+          <t>https://www.noticiascaracol.com/mundo/mercenarios-colombianos-en-mexico-asi-carteles-de-la-droga-estarian-reclutando-exmilitares-rg10</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:48 p. m.</t>
+          <t>30/05/2026 02:07 p. m.</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
@@ -2632,24 +2604,24 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>"Intervención ramplona en política": Oviedo a Petro | Recap - programa completo 29 de mayo de 2026</t>
+          <t>Resultados Dorado Tarde hoy, sábado 30 de mayo de 2026: números ganadores del último sorteo</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/recap/intervencion-ramplona-en-politica-oviedo-a-petro-recap-programa-completo-29-de-mayo-de-2026-pr30</t>
+          <t>https://www.noticiascaracol.com/economia/resultados-dorado-tarde-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-del-ultimo-sorteo-so35</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:23 p. m.</t>
+          <t>30/05/2026 02:04 p. m.</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2659,24 +2631,24 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Fatal accidente en rally: el copiloto falleció y su hermano lucha por su vida</t>
+          <t>Resultados Caribeña Día hoy, sábado 30 de mayo de 2026: números ganadores del último sorteo</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/mundo/fatal-accidente-en-rally-el-copiloto-fallecio-y-su-hermano-lucha-por-su-vida-cb20</t>
+          <t>https://www.noticiascaracol.com/economia/resultados-caribena-dia-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-del-ultimo-sorteo-so35</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:08 p. m.</t>
+          <t>30/05/2026 01:55 p. m.</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
@@ -2686,24 +2658,24 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Oviedo arremete contra Petro por eventos en la costa: "Es una intervención ramplona en política"</t>
+          <t>Resultados Sinuano Día hoy, sábado 30 de mayo de 2026: números ganadores del último sorteo</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/elecciones/presidenciales/oviedo-arremete-contra-petro-por-eventos-en-la-costa-es-una-intervencion-ramplona-en-politica-pr30</t>
+          <t>https://www.noticiascaracol.com/economia/resultados-sinuano-dia-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-del-ultimo-sorteo-so35</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 09:57 p. m.</t>
+          <t>30/05/2026 01:42 p. m.</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -2713,24 +2685,24 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Resultados de loterías de Medellín, Santander, Risaralda y MiLoto hoy 29 de mayo de 2026</t>
+          <t>“No tengo palabras”: Alfredo Iván Guzmán, hijo del exalcalde de Tame, tras recuperar su libertad</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/resultados-de-loterias-de-medellin-santander-risaralda-y-miloto-hoy-29-de-mayo-de-2026-so35</t>
+          <t>https://www.noticiascaracol.com/colombia/no-tengo-palabras-alfredo-ivan-guzman-hijo-del-exalcalde-de-tame-tras-recuperar-su-libertad-rg10</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 09:57 p. m.</t>
+          <t>30/05/2026 12:54 p. m.</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
@@ -2740,24 +2712,24 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>MiLoto, resultado del último sorteo hoy viernes 29 de mayo de 2026</t>
+          <t>Resultados Chontico Día hoy, sábado 30 de mayo de 2026: números ganadores</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/miloto-resultado-del-ultimo-sorteo-hoy-viernes-29-de-mayo-de-2026-so35</t>
+          <t>https://www.noticiascaracol.com/economia/resultados-chontico-dia-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-so35</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 09:57 p. m.</t>
+          <t>30/05/2026 12:38 p. m.</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -2767,24 +2739,24 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Lotería de Risaralda, resultados del último sorteo hoy viernes 29 de mayo de 2026</t>
+          <t>Vanessa Pulgarín, la colombiana que logró la primera corona de Miss Grand International All Stars</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/loteria-de-risaralda-resultados-del-ultimo-sorteo-hoy-viernes-29-de-mayo-de-2026-so35</t>
+          <t>https://www.noticiascaracol.com/entretenimiento/vanessa-pulgarin-la-colombiana-que-logro-la-primera-corona-de-miss-grand-international-all-stars-rg10</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 09:56 p. m.</t>
+          <t>30/05/2026 11:39 a. m.</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
@@ -2794,24 +2766,24 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Lotería de Santander, resultados del último sorteo hoy viernes 29 de mayo de 2026</t>
+          <t>El Parque Nacional Natural Tayrona cerrará sus puertas por 15 días: ¿por qué?</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/loteria-de-santander-resultados-del-ultimo-sorteo-hoy-viernes-29-de-mayo-de-2026-so35</t>
+          <t>https://www.noticiascaracol.com/colombia/el-parque-nacional-natural-tayrona-cerrara-sus-puertas-por-15-dias-por-que-rg10</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 09:56 p. m.</t>
+          <t>30/05/2026 11:36 a. m.</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -2821,24 +2793,24 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Lotería de Medellín, resultados del último sorteo hoy viernes 29 de mayo de 2026</t>
+          <t>Polémica en final de Champions League; ¿era mano en el Arsenal y penalti para el PSG?</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/loteria-de-medellin-resultados-del-ultimo-sorteo-hoy-viernes-29-de-mayo-de-2026-so35</t>
+          <t>https://www.noticiascaracol.com/golcaracol/polemica-en-final-de-champions-league-era-mano-en-el-arsenal-y-penalti-para-el-psg-rg10</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 09:55 p. m.</t>
+          <t>30/05/2026 11:20 a. m.</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
@@ -2848,24 +2820,24 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Astro Luna, resultado del último sorteo hoy viernes 29 de mayo de 2026</t>
+          <t>Ganadores del Desafío Siglo XXI se casarán: video de la emotiva propuesta de matrimonio</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/astro-luna-resultado-del-ultimo-sorteo-hoy-viernes-29-de-mayo-de-2026-so35</t>
+          <t>https://www.noticiascaracol.com/entretenimiento/ganadores-del-desafio-siglo-xxi-se-casaran-video-de-la-emotiva-propuesta-de-matrimonio-rs15</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 09:55 p. m.</t>
+          <t>30/05/2026 10:45 a. m.</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -2875,24 +2847,24 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Caribeña Noche, resultado del último sorteo hoy viernes 29 de mayo de 2026</t>
+          <t>Video l Tim Payne, el futbolista viral, disputó un torneo en Colombia: vea cómo lucía en el 2011</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/caribena-noche-resultado-del-ultimo-sorteo-hoy-viernes-29-de-mayo-de-2026-so35</t>
+          <t>https://www.noticiascaracol.com/lomastrinado/video-l-tim-payne-el-futbolista-viral-disputo-un-torneo-en-colombia-vea-como-lucia-en-el-2011-rs15</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 09:55 p. m.</t>
+          <t>30/05/2026 10:42 a. m.</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
@@ -2902,24 +2874,24 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Sinuano Noche, resultado del último sorteo hoy viernes 29 de mayo de 2026</t>
+          <t>Así está la salud de Donald Trump, según el más reciente chequeo médico de la Casa Blanca</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/sinuano-noche-resultado-del-ultimo-sorteo-hoy-viernes-29-de-mayo-de-2026-so35</t>
+          <t>https://www.noticiascaracol.com/mundo/asi-esta-la-salud-de-donald-trump-segun-el-mas-reciente-chequeo-medico-de-la-casa-blanca-cb20</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:45 p. m.</t>
+          <t>30/05/2026 10:23 a. m.</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -2929,24 +2901,24 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Peridis: “¡Créanme!”</t>
+          <t>Resultados Dorado Mañana hoy, sábado 30 de mayo de 2026: números ganadores del último sorteo</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/opinion/2026-05-30/peridis-creanme.html</t>
+          <t>https://www.noticiascaracol.com/economia/resultados-dorado-manana-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-del-ultimo-sorteo-so35</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:45 p. m.</t>
+          <t>30/05/2026 10:00 a. m.</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
@@ -2956,24 +2928,24 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Riki Blanco: modales</t>
+          <t>Elecciones presidenciales 2026: cierres viales y desvíos clave de movilidad en Bogotá</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/opinion/2026-05-30/riki-blanco-modales.html</t>
+          <t>https://www.noticiascaracol.com/colombia/bogota-elecciones-presidenciales-2026-cierres-viales-y-desvios-clave-de-movilidad-en-bogota-rg10</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:45 p. m.</t>
+          <t>30/05/2026 09:30 a. m.</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -2983,24 +2955,24 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>El Roto: el desconcierto</t>
+          <t>Cancillería se pronunció tras anuncio de Daniel Noboa sobre la eliminación de aranceles a Colombia</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/opinion/2026-05-30/el-roto-el-desconcierto.html</t>
+          <t>https://www.noticiascaracol.com/colombia/cancilleria-se-pronuncio-tras-anuncio-de-daniel-noboa-sobre-la-eliminacion-de-aranceles-a-colombia-rg10</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:45 p. m.</t>
+          <t>30/05/2026 08:45 a. m.</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
@@ -3010,24 +2982,24 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Cucarachas en el sistema financiero</t>
+          <t>Altos mandos militares de Cuba y EE. UU. se reunieron: ¿cuáles fueron los temas tratados?</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/economia/2026-05-30/cucarachas-en-el-sistema-financiero.html</t>
+          <t>https://www.noticiascaracol.com/mundo/altos-mandos-militares-de-cuba-y-ee-uu-se-reunieron-cuales-fueron-los-temas-tratados-cb20</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:30 p. m.</t>
+          <t>30/05/2026 08:22 a. m.</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3037,24 +3009,24 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>La memoria de una careta y dos vejigas de vaca</t>
+          <t>Supersalud ordenó cierre del servicio de cirugía estética de la Clínica de Obesidad y Envejecimiento</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/espana/catalunya/2026-05-30/la-memoria-de-una-careta-y-dos-vejigas-de-vaca.html</t>
+          <t>https://www.noticiascaracol.com/colombia/bogota/supersalud-ordeno-cierre-del-servicio-de-cirugia-estetica-de-la-clinica-de-obesidad-y-envejecimiento-rg10</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:30 p. m.</t>
+          <t>30/05/2026 07:52 a. m.</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
@@ -3064,24 +3036,24 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>El peligroso discurso del complot</t>
+          <t>Europa vs. Sudamérica: quién ha ganado más Mundiales en la historia</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/espana/2026-05-30/el-peligroso-discurso-del-complot.html</t>
+          <t>https://www.noticiascaracol.com/golcaracol/europa-vs-sudamerica-quien-ha-ganado-mas-mundiales-en-la-historia-cb20</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:30 p. m.</t>
+          <t>30/05/2026 07:26 a. m.</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3091,24 +3063,24 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Renfe inmoviliza en Cataluña dos trenes al día por culpa de los grafiteros</t>
+          <t>Murió Edgar Morin, uno de los filósofos contemporáneos más influyentes de Francia, a los 104 años</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/espana/catalunya/2026-05-30/renfe-inmoviliza-en-cataluna-dos-trenes-al-dia-por-culpa-de-los-grafiteros.html</t>
+          <t>https://www.noticiascaracol.com/mundo/murio-edgar-morin-uno-de-los-filosofos-contemporaneos-mas-influyentes-de-francia-a-los-104-anos-cb20</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:30 p. m.</t>
+          <t>30/05/2026 06:43 a. m.</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
@@ -3118,24 +3090,24 @@
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Tres meses de cierre de Ormuz: cientos de buques varados en el golfo Pérsico mientras sus cascos se llenan de moluscos</t>
+          <t>Bombazo en la Premier League; Liverpool tomó radical decisión con Arne Slot</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/internacional/2026-05-30/tres-meses-de-cierre-de-ormuz-cientos-de-buques-varados-en-el-golfo-persico-mientras-sus-cascos-se-llenan-de-moluscos.html</t>
+          <t>https://www.noticiascaracol.com/golcaracol/bombazo-en-la-premier-league-liverpool-tomo-radical-decision-con-arne-slot-cb20</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:30 p. m.</t>
+          <t>30/05/2026 08:54 p. m.</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3145,24 +3117,24 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>La jubilación de los bandidos</t>
+          <t>Estos son los 11 candidatos a la Presidencia de Colombia 2026</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/opinion/2026-05-30/la-jubilacion-de-los-bandidos.html</t>
+          <t>https://www.noticiasrcn.com/colombia/cuales-son-los-11-candidatos-a-la-presidencia-de-colombia-2026-1026269</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:30 p. m.</t>
+          <t>30/05/2026 07:44 p. m.</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
@@ -3172,24 +3144,24 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Píos, leones, inocentes: ¿qué nos dice la cultura de los papas?</t>
+          <t>Secuestró y violó a una niña de cuatro años tras engañar a su madre con regalarle un mercado en Cali</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/babelia/2026-05-30/pios-leones-inocentes-que-nos-dice-la-cultura-de-los-papas.html</t>
+          <t>https://www.noticiasrcn.com/colombia/secuestro-y-violo-a-una-nina-de-cuatro-anos-tras-enganar-a-su-madre-con-regalarle-un-mercado-en-cali-1026264</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:30 p. m.</t>
+          <t>30/05/2026 04:28 p. m.</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3199,24 +3171,24 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>El tráfico infernal de la megalópolis turca</t>
+          <t>Cadáveres de disidentes fueron cargados con explosivos para detonarlos en traslado a Medicina Legal</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/internacional/historias-de-corresponsal/2026-05-30/el-trafico-infernal-de-la-megalopolis-turca.html</t>
+          <t>https://www.noticiasrcn.com/colombia/cadaveres-de-disidentes-fueron-cargados-con-explosivos-para-detonarlos-en-traslado-a-medicina-legal-1026237</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:30 p. m.</t>
+          <t>30/05/2026 03:50 p. m.</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
@@ -3226,24 +3198,24 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Carmen Calvo, presidenta del Consejo de Estado: “El sueldo de expresidente tendría que ser suficiente porque el honor del cargo es inmaterial”</t>
+          <t>Más de 700 familias damnificadas y con el agua a la cintura al desbordarse tres ríos en Cabuyaro, Meta</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/espana/2026-05-30/carmen-calvo-presidenta-del-consejo-de-estado-el-sueldo-de-expresidente-tendria-que-ser-suficiente-porque-el-honor-del-cargo-es-inmaterial.html</t>
+          <t>https://www.noticiasrcn.com/colombia/mas-de-700-familias-damnificadas-y-con-el-agua-a-la-cintura-por-el-desbordamiento-de-tres-rios-en-cabuyaro-meta-1026229</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:30 p. m.</t>
+          <t>30/05/2026 03:32 p. m.</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3253,24 +3225,24 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Alejandro Martínez Rico, psiquiatra: “Si el termostato de los padres está roto, el del niño difícilmente se mantendrá estable”</t>
+          <t>Elecciones Colombia: recompensas de $50 y $200 millones por actores armados y planes de atentados</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/mamas-papas/expertos/2026-05-30/alejandro-martinez-rico-psiquiatra-si-el-termostato-de-los-padres-esta-roto-el-del-nino-dificilmente-se-mantendra-estable.html</t>
+          <t>https://www.noticiasrcn.com/colombia/elecciones-colombia-recompensas-de-50-y-200-millones-por-actores-armados-y-planes-de-atentados-1026224</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:30 p. m.</t>
+          <t>30/05/2026 02:52 p. m.</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
@@ -3280,24 +3252,24 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Cataluña amplía los créditos al 0% para la entrada de un piso: “Es la única ventaja que tenemos frente a los fondos buitre”</t>
+          <t>Video revelador: hallan el cuerpo del joven de 22 años que se lanzó al embalse de Guatapé huyendo de agresión</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/espana/catalunya/2026-05-30/cataluna-amplia-los-creditos-al-0-para-la-entrada-de-un-piso-es-la-unica-ventaja-que-tenemos-frente-a-los-fondos-buitre.html</t>
+          <t>https://www.noticiasrcn.com/colombia/video-del-joven-de-22-anos-hallado-muerto-en-guatape-1026206</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:30 p. m.</t>
+          <t>30/05/2026 01:36 p. m.</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -3307,24 +3279,24 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Antonio Arias, entre el alfa y el omega</t>
+          <t>Bogotá entrará en alerta amarilla hospitalaria por elecciones: ¿qué significa esto?</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/babelia/2026-05-30/antonio-arias-entre-el-alfa-y-el-omega.html</t>
+          <t>https://www.noticiasrcn.com/colombia/bogota-entrara-en-alerta-amarilla-hospitalaria-por-elecciones-1025976</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:30 p. m.</t>
+          <t>30/05/2026 12:56 p. m.</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
@@ -3334,24 +3306,24 @@
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Cuatro amigas que compran cosas</t>
+          <t>“Se está dejando utilizar”: Santiago Botero se pronunció tras el desalojo en su vivienda en Cartagena</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/opinion/2026-05-30/cuatro-amigas-que-compran-cosas.html</t>
+          <t>https://www.noticiasrcn.com/colombia/santiago-botero-se-pronuncio-tras-escandalo-de-desalojo-de-su-vivienda-1026192</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:30 p. m.</t>
+          <t>30/05/2026 12:07 p. m.</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -3361,24 +3333,24 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>¿Conspiración? Merecemos una explicación algo mejor</t>
+          <t>Autoridades ordenaron desalojo a propiedad de Santiago Botero: es acusado de violencia intrafamiliar</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/opinion/2026-05-30/conspiracion-merecemos-una-explicacion-algo-mejor.html</t>
+          <t>https://www.noticiasrcn.com/colombia/santiago-botero-es-desalojado-y-acusado-de-violencia-intrafamiliar-1026185</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:30 p. m.</t>
+          <t>30/05/2026 11:43 a. m.</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
@@ -3388,24 +3360,24 @@
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>Diez noches, un estadio y una sola ley: la de Bad Bunny y el negocio de las residencias</t>
+          <t>Colombia, lista para votar: el llamado a respetar los resultados</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/cultura/2026-05-30/diez-noches-un-estadio-y-una-sola-ley-la-de-bad-bunny-y-el-negocio-de-las-residencias.html</t>
+          <t>https://www.noticiasrcn.com/colombia/colombia-lista-para-votar-el-llamado-a-respetar-los-resultados-1026172</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:30 p. m.</t>
+          <t>30/05/2026 08:53 p. m.</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3415,24 +3387,24 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>No hay revolución real sin revolución mental</t>
+          <t>Video muestra el momento exacto en que meteoro cae en EE. UU. con fuerza de 300 toneladas de TNT</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/eps/2026-05-30/no-hay-revolucion-real-sin-revolucion-mental.html</t>
+          <t>https://www.bluradio.com/mundo/video-muestra-el-momento-exacto-en-que-meteoro-cae-en-ee-uu-con-fuerza-de-300-toneladas-de-tnt-cb20</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:30 p. m.</t>
+          <t>30/05/2026 08:51 p. m.</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
@@ -3442,24 +3414,24 @@
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>Una inteligencia de otro mundo</t>
+          <t>Super Astro Luna, resultado del último sorteo hoy sábado 30 de mayo de 2026</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/opinion/2026-05-30/una-inteligencia-de-otro-mundo.html</t>
+          <t>https://www.bluradio.com/economia/juegos-de-azar/super-astro-luna-resultado-del-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-so35</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:30 p. m.</t>
+          <t>30/05/2026 08:51 p. m.</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3469,24 +3441,24 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>La única española que declaró en el Comité de Actividades Antiamericanas</t>
+          <t>Caribeña Noche, resultado del último sorteo hoy sábado 30 de mayo de 2026</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/babelia/2026-05-30/ernestina-gonzalez-la-bibliotecaria-antifascista.html</t>
+          <t>https://www.bluradio.com/economia/juegos-de-azar/caribena-noche-resultado-del-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-so35</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 04:20 p. m.</t>
+          <t>30/05/2026 08:51 p. m.</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
@@ -3496,24 +3468,24 @@
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>Estados Unidos e Irán admiten un preacuerdo, pero discrepan sobre sus términos</t>
+          <t>Sinuano Noche, resultado del último sorteo hoy sábado 30 de mayo de 2026</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/internacional/2026-05-29/estados-unidos-e-iran-admiten-un-preacuerdo-pero-discrepan-sobre-sus-terminos.html</t>
+          <t>https://www.bluradio.com/economia/juegos-de-azar/sinuano-noche-resultado-del-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-so35</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 11:51 a. m.</t>
+          <t>30/05/2026 08:51 p. m.</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -3523,24 +3495,24 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Roland Garros multará al tenista Adolfo Daniel Vallejo por sus comentarios sexistas</t>
+          <t>Resultados del Dorado Noche: último sorteo hoy, sábado 30 de mayo de 2026, números ganadores</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/deportes/tenis/2026-05-29/roland-garros-multara-al-tenista-adolfo-daniel-vallejo-por-sus-comentarios-sexistas-este-partido-deberia-haberlo-pitado-un-hombre.html</t>
+          <t>https://www.bluradio.com/economia/juegos-de-azar/resultados-del-dorado-noche-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-so35</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:24 a. m.</t>
+          <t>30/05/2026 08:50 p. m.</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
@@ -3550,24 +3522,24 @@
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>Camila ya tiene papeles: la venezolana ha completado con éxito su regularización en España</t>
+          <t>Loterías de Boyacá, Cauca, Extra de Colombia y Baloto: resultados sorteos hoy sábado 30 de mayo</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/espana/2026-05-29/camila-ya-tiene-papeles-la-venezolana-ha-completado-con-exito-su-regularizacion-en-espana.html</t>
+          <t>https://www.bluradio.com/economia/juegos-de-azar/loterias-de-boyaca-cauca-extra-de-colombia-y-baloto-resultados-sorteos-hoy-sabado-30-de-mayo-so35</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 07:42 a. m.</t>
+          <t>30/05/2026 08:50 p. m.</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -3577,24 +3549,24 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Dos heridos al impactar un dron ruso contra un edificio de viviendas en Rumania</t>
+          <t>Baloto y Revancha, resultados del último sorteo hoy sábado 30 de mayo de 2026</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/internacional/2026-05-29/dos-heridos-al-impactar-un-dron-ruso-contra-un-edificio-en-rumania.html</t>
+          <t>https://www.bluradio.com/economia/juegos-de-azar/baloto-y-revancha-resultados-del-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-so35</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 07:19 a. m.</t>
+          <t>30/05/2026 08:50 p. m.</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
@@ -3604,24 +3576,24 @@
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>La Feria del Libro de Madrid arranca con el tradicional paseo de la reina Letizia</t>
+          <t>Extra de Colombia, resultados del último sorteo de este sábado 30 de mayo de 2026</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/cultura/2026-05-29/la-feria-del-libro-de-madrid-arranca-con-el-tradicional-paseo-de-la-reina-letizia.html</t>
+          <t>https://www.bluradio.com/economia/juegos-de-azar/extra-de-colombia-resultados-del-ultimo-sorteo-de-este-sabado-30-de-mayo-de-2026-so35</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 07:18 a. m.</t>
+          <t>30/05/2026 08:49 p. m.</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -3631,24 +3603,24 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Aznar vuelve a la carga contra Sánchez: “La única salida posible son unas nuevas elecciones”</t>
+          <t>Lotería del Cauca sábado 30 de mayo de 2026, resultados del último sorteo, premio mayor y secos</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/espana/2026-05-29/aznar-vuelve-a-la-carga-contra-sanchez-la-unica-salida-posible-son-unas-nuevas-elecciones.html</t>
+          <t>https://www.bluradio.com/economia/juegos-de-azar/loteria-del-cauca-sabado-30-de-mayo-de-2026-resultados-del-ultimo-sorteo-premio-mayor-y-secos-so35</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 06:01 a. m.</t>
+          <t>30/05/2026 08:49 p. m.</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
@@ -3658,24 +3630,24 @@
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>La defensa usa una caída previa y la artrosis de Isak Andic para concluir que su muerte en Montserrat fue accidental</t>
+          <t>Lotería Boyacá, resultados del último sorteo hoy sábado 30 de mayo de 2026</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/espana/catalunya/2026-05-29/la-defensa-usa-una-caida-previa-y-la-artrosis-de-isak-andic-para-concluir-que-su-muerte-en-montserrat-fue-accidental.html</t>
+          <t>https://www.bluradio.com/economia/juegos-de-azar/loteria-boyaca-resultados-del-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-so35</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>28/05/2026 10:30 p. m.</t>
+          <t>30/05/2026 08:46 p. m.</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -3685,24 +3657,24 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Simone Biles: “Odio el ejercicio, después de tantos años creo que me merezco un descanso”</t>
+          <t>Al menos seis personas estarían atrapadas tras el colapso de un edificio en Nueva Delhi</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/deportes/2026-05-29/simone-biles-odio-el-ejercicio-despues-de-tantos-anos-creo-que-me-merezco-un-descanso.html</t>
+          <t>https://www.bluradio.com/mundo/al-menos-seis-personas-estarian-atrapadas-tras-el-colapso-de-un-edificio-en-nueva-delhi-cb20</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>28/05/2026 10:30 p. m.</t>
+          <t>30/05/2026 08:04 p. m.</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
@@ -3712,24 +3684,24 @@
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>Sin hormonas: la odisea para encontrar Lenzetto, el medicamento más escaso de España</t>
+          <t>Encuentran muerta a adolescente de 14 años desaparecida hace una semana; investigan homicidio</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/sociedad/2026-05-29/sin-hormonas-la-odisea-para-encontrar-lenzetto-el-medicamento-mas-escaso-de-espana.html</t>
+          <t>https://www.bluradio.com/mundo/encuentran-muerta-a-adolescente-de-14-anos-desaparecida-hace-una-semana-investigan-homicidio-rs15</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:39 p. m.</t>
+          <t>30/05/2026 08:53 p. m.</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -3739,24 +3711,24 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>¿Quién es Tim Payne y por qué se volvió un fenómeno en las redes sociales a días del Mundial 2026?</t>
+          <t>Cristian Mosquera fue tendencia tras cometer penal en la final que perdió Arsenal ante PSG</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/lomastrinado/quien-es-tim-payne-y-por-que-se-volvio-un-fenomeno-en-las-redes-sociales-a-dias-del-mundial-2026-rg10</t>
+          <t>https://www.eluniversal.com.co/deportes/2026/05/30/cristian-mosquera-fue-tendencia-tras-cometer-penal-en-la-final-que-perdio-arsenal-ante-psg/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:17 p. m.</t>
+          <t>30/05/2026 08:53 p. m.</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
@@ -3766,24 +3738,24 @@
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>Resultados Super Astro Luna hoy 29 de mayo de 2026: números ganadores del último sorteo</t>
+          <t>Deportes</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/resultados-super-astro-luna-hoy-29-de-mayo-de-2026-numeros-ganadores-del-ultimo-sorteo-so35</t>
+          <t>https://www.eluniversal.com.co/deportes/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:08 p. m.</t>
+          <t>30/05/2026 08:46 p. m.</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -3793,24 +3765,24 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Resultados Lotería de Risaralda del viernes 29 de mayo de 2026: vea aquí los números ganadores</t>
+          <t>Más de 300 detenidos en Francia tras los disturbios por la victoria del PSG</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/loteria-de-risaralda-29-de-mayo-de-2026-resultados-numeros-ganadores-so35</t>
+          <t>https://www.eluniversal.com.co/mundo/2026/05/30/mas-de-300-detenidos-en-francia-tras-los-disturbios-por-la-victoria-del-psg/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:03 p. m.</t>
+          <t>30/05/2026 06:58 p. m.</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
@@ -3820,24 +3792,24 @@
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>Resultados Lotería de Medellín, Santander y Risaralda hoy 29 de mayo de 2026: ganadores del sorteo</t>
+          <t>En entrevista con Westcol, Abelardo de la Espriella rechaza acusaciones</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/resultados-loteria-de-medellin-santander-y-risaralda-hoy-29-de-mayo-de-2026-ganadores-del-sorteo-so35</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/30/en-entrevista-con-westcol-abelardo-de-la-espriella-rechaza-acusaciones/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:00 p. m.</t>
+          <t>30/05/2026 06:40 p. m.</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -3847,24 +3819,24 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Resultados Lotería de Santander del 29 de mayo de 2026: números ganadores de este viernes</t>
+          <t>Petro rechaza supuesta injerencia de Estados Unidos y Ecuador en elecciones</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/loteria-de-santander-29-mayo-2026-resultados-numeros-ganadores-de-hoy-so35</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/30/petro-rechaza-supuesta-injerencia-de-estados-unidos-y-ecuador-en-elecciones/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:00 p. m.</t>
+          <t>30/05/2026 06:40 p. m.</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
@@ -3874,24 +3846,24 @@
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>Resultados Lotería de Medellín del viernes 29 de mayo de 2026: estos son los números ganadores</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/loteria-de-medellin-29-de-mayo-2026-cuales-son-los-numeros-ganadores-so35</t>
+          <t>https://www.eluniversal.com.co/colombia/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:00 p. m.</t>
+          <t>30/05/2026 06:37 p. m.</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -3901,24 +3873,24 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Resultados Sinuano Noche último sorteo del 29 de mayo de 2026: números ganadores</t>
+          <t>“Gracias, amigo”: el gesto de Arensman a Egan que emocionó en el Giro</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/sinuano-noche-29-de-mayo-2026-resultados-numeros-ganadores-de-hoy-so35</t>
+          <t>https://www.eluniversal.com.co/deportes/2026/05/30/gracias-amigo-el-gesto-de-arensman-a-egan-que-emociono-en-el-giro/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:00 p. m.</t>
+          <t>30/05/2026 05:56 p. m.</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
@@ -3928,24 +3900,24 @@
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>Resultados Caribeña Noche último sorteo del viernes 29 de mayo de 2026: números ganadores</t>
+          <t>Más de 10.400 funcionarios vigilarán las elecciones por orden de Procuraduría</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/caribena-noche-29-de-mayo-2026-resultados-numeros-ganadores-de-hoy-so35</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/30/mas-de-10400-funcionarios-vigilaran-las-elecciones-por-orden-de-procuraduria/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 09:54 p. m.</t>
+          <t>30/05/2026 05:23 p. m.</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -3955,24 +3927,24 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Corte Suprema absuelve a adolescente que tuvo relaciones con menor de 12 años: ¿por qué?</t>
+          <t>El PSG, el equipo de Luis Enrique, entra al club de los gigantes de Europa</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/judicial/corte-suprema-absuelve-a-menor-de-edad-que-tuvo-relaciones-con-menor-de-12-anos-por-que-rg10</t>
+          <t>https://www.eluniversal.com.co/deportes/2026/05/30/el-psg-el-equipo-de-luis-enrique-entra-al-club-de-los-gigantes-de-europa/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 08:07 p. m.</t>
+          <t>30/05/2026 05:10 p. m.</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
@@ -3982,24 +3954,24 @@
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>Daniel Noboa, presidente de Ecuador, dice que quitará aranceles a Colombia el 1 de junio: ¿por qué?</t>
+          <t>Samuel Morales y Juank Ricardo anuncian el fin de su unión musical</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/mundo/daniel-noboa-presidente-de-ecuador-dice-que-quitara-aranceles-a-colombia-el-1-de-junio-por-que-rg10</t>
+          <t>https://www.eluniversal.com.co/farandula/2026/05/30/samuel-morales-y-juank-ricardo-anuncian-el-fin-de-su-union-musical/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 07:38 p. m.</t>
+          <t>30/05/2026 05:10 p. m.</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -4009,24 +3981,24 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Jefe militar de Estados Unidos se reúne con alto mando del Ejército de Cuba en Guantánamo</t>
+          <t>Farándula</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/mundo/jefe-militar-de-estados-unidos-se-reune-con-alto-mando-del-ejercito-de-cuba-en-guantanamo-rg10</t>
+          <t>https://www.eluniversal.com.co/farandula/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 07:20 p. m.</t>
+          <t>30/05/2026 05:01 p. m.</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
@@ -4036,24 +4008,24 @@
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>Expediente Yulixa Toloza y los 4 hallazgos principales de Medicina Legal en la necropsia del cuerpo</t>
+          <t>Así capturaron a alias ‘Tato’ en Arjona con más de 350 dosis de estupefaciente</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/judicial/expediente-yuliza-toloza-y-los-4-hallazgos-principales-de-medicina-legal-en-la-necropsia-del-cuerpo-rg10</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/asi-capturaron-a-alias-tato-en-arjona-con-mas-de-350-dosis-de-estupefaciente/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 07:04 p. m.</t>
+          <t>30/05/2026 04:58 p. m.</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -4063,24 +4035,24 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Avianca alerta por estafas: falsos cobros por combustible en tiquetes aéreos</t>
+          <t>No resistió: falleció cuñado de alias ‘Castor’ dos meses después de sufrir atentado</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/avianca-alerta-por-estafas-falsos-cobros-por-combustible-en-tiquetes-aereos-so35</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/no-resistio-fallecio-cunado-de-alias-castor-dos-meses-despues-de-sufrir-atentado/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 06:56 p. m.</t>
+          <t>30/05/2026 04:46 p. m.</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
@@ -4090,24 +4062,24 @@
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>Resultados Chontico Noche último sorteo hoy, viernes 29 de mayo de 2026: números ganadores</t>
+          <t>Donald Trump critica al papa por Irán y llama “inútil” al alcalde de Chicago</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/chontico-noche-29-mayo-2026-resultados-numeros-ganadores-de-hoy-so35</t>
+          <t>https://www.eluniversal.com.co/mundo/2026/05/30/donald-trump-critica-al-papa-por-iran-y-llama-inutil-al-alcalde-de-chicago/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 06:16 p. m.</t>
+          <t>30/05/2026 04:34 p. m.</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -4117,24 +4089,24 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Passport Bros: la dinámica de explotación sexual de extranjeros para encontrar pareja en Colombia</t>
+          <t>“Están utilizando a mi familia”: Santiago Botero tras escándalo por orden de desalojo</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/mundo/passport-bros-la-dinamica-de-explotacion-sexual-de-extranjeros-para-encontrar-pareja-en-colombia-rg10</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/30/estan-utilizando-a-mi-familia-santiago-botero-tras-escandalo-por-orden-de-desalojo/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 06:03 p. m.</t>
+          <t>30/05/2026 04:33 p. m.</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
@@ -4144,24 +4116,24 @@
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>Video | Montaña rusa falla y deja atrapadas personas a casi 30 metros de altura</t>
+          <t>Green card: así afectarían los cambios migratorios a colombianos</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/mundo/video-montana-rusa-falla-y-deja-atrapadas-personas-a-casi-30-metros-de-altura-rg10</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/30/green-card-asi-afectarian-los-cambios-migratorios-a-colombianos/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 05:57 p. m.</t>
+          <t>30/05/2026 03:22 p. m.</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -4171,24 +4143,24 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Liberan a Alfredo Iván Guzmán, hijo del exalcalde de Tame, Arauca, Alfredo Guzmán</t>
+          <t>Petro afirma que Colombia seguirá apoyando a Ecuador en materia energética</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/liberan-a-alfredo-ivan-guzman-hijo-del-exalcalde-de-tame-arauca-alfredo-guzman-rg10</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/30/petro-afirma-que-colombia-seguira-apoyando-a-ecuador-en-materia-energetica/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 04:46 p. m.</t>
+          <t>30/05/2026 12:33 p. m.</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
@@ -4198,24 +4170,24 @@
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>Menor de 13 años en Bogotá desapareció tras salir de su colegio: fue vista en cámaras con un hombre</t>
+          <t>Así despiden a Jhaider Garizao, el joven que se ahogó en una playa de Bocagrande</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/bogota/menor-de-13-anos-en-bogota-desaparecio-tras-salir-de-su-colegio-fue-vista-en-camaras-con-un-hombre-rg10</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/asi-despiden-a-jhaider-garizao-el-joven-que-se-ahogo-en-una-playa-de-bocagrande/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 04:44 p. m.</t>
+          <t>30/05/2026 11:54 a. m.</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -4225,24 +4197,24 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Memoria y política: él es Iván Cepeda, el senador que busca llegar a la Casa de Nariño</t>
+          <t>Cayó alias ‘El Chinchurria’ en Bolívar: tenía un revólver y acumula 15 anotaciones</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/memoria-y-politica-el-es-ivan-cepeda-el-senador-que-busca-llegar-a-la-casa-de-narino-rg10</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/cayo-alias-el-chinchurria-en-mompox-acumulaba-15-anotaciones-judiciales/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 04:42 p. m.</t>
+          <t>30/05/2026 11:13 a. m.</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
@@ -4252,24 +4224,24 @@
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>Movilidad Bogotá confirma: no hay restricción de parrillero de moto este fin de semana de elecciones</t>
+          <t>Por enésima vez cayó ‘Chawalita’ en Cartagena: suma más de 12 anotaciones</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/bogota/movilidad-bogota-confirma-no-hay-restriccion-de-parrillero-de-moto-este-fin-de-semana-de-elecciones-so35</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/por-enesima-vez-cayo-chawalita-en-cartagena-suma-mas-de-12-anotaciones/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 04:36 p. m.</t>
+          <t>30/05/2026 10:46 a. m.</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -4279,24 +4251,24 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Mujer descubrió que tenía cáncer tras un abrazo con su mamá: "Me salvó la vida"</t>
+          <t>Bolívar se blinda para las elecciones con operativos de control y prevención</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/mundo/mujer-descubrio-que-tenia-cancer-tras-un-abrazo-con-su-mama-me-salvo-la-vida-rg10</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/bolivar-se-blinda-para-las-elecciones-con-operativos-de-control-y-prevencion/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 04:06 p. m.</t>
+          <t>30/05/2026 10:04 a. m.</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
@@ -4306,24 +4278,24 @@
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>Así cayó médico en Bogotá señalado de agresión sexual contra dos niñas de 7 y 10 años en una EPS</t>
+          <t>Mientras jugaba en un casino, sicario le quitó la vida a Johnny Rodríguez</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/judicial/asi-cayo-medico-en-bogota-senalado-de-agresion-sexual-contra-dos-ninas-de-7-y-10-anos-en-una-eps-rg10</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/mientras-jugaba-en-un-casino-sicario-le-quito-la-vida-a-johnny-rodriguez/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 03:46 p. m.</t>
+          <t>30/05/2026 08:46 a. m.</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -4333,26 +4305,22 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Ley seca en elecciones 2026: a estas sanciones se expone quien no cumpla la medida</t>
+          <t>Investigan muerte de un recluso en la Penitenciaría El Bosque de Barranquilla</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/ley-seca-en-elecciones-2026-a-estas-sanciones-se-expone-quien-no-cumpla-la-medida-so35</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/investigan-muerte-de-un-recluso-en-la-penitenciaria-el-bosque-de-barranquilla/</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="6" t="inlineStr">
-        <is>
-          <t>29/05/2026 03:30 p. m.</t>
-        </is>
-      </c>
+      <c r="A143" s="6" t="inlineStr"/>
       <c r="B143" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -4360,26 +4328,22 @@
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>Colombia vs. Costa Rica; cuándo juegan, precios de las boletas, hora y dónde ver EN VIVO por TV</t>
+          <t>Premios Excelencia El Universal 2026: ya están abiertas las postulaciones</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/golcaracol/seleccion-colombia/colombia-vs-costa-rica-cuando-juegan-precios-de-las-boletas-hora-y-donde-ver-en-vivo-por-tv-so35</t>
+          <t>https://www.eluniversal.com.co/cartagena/2026/05/26/premios-excelencia-el-universal-2026-ya-estan-abiertas-las-postulaciones/</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="3" t="inlineStr">
-        <is>
-          <t>29/05/2026 03:30 p. m.</t>
-        </is>
-      </c>
+      <c r="A144" s="3" t="inlineStr"/>
       <c r="B144" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -4387,24 +4351,24 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Super Astro Sol resultados hoy 29 de mayo de 2026: estos son los números ganadores del último sorteo</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/super-astro-sol-resultados-hoy-29-de-mayo-de-2026-estos-son-los-numeros-ganadores-del-ultimo-sorteo-so35</t>
+          <t>https://www.eluniversal.com.co/cartagena/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 03:03 p. m.</t>
+          <t>30/05/2026 08:44 p. m.</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
@@ -4414,24 +4378,24 @@
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>Los cambios que vienen desde julio 2026 para trabajadores: recargos y jornada laboral</t>
+          <t>Candidatos presidenciales Colombia 2026: nombres, fotos y principales propuestas</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/los-cambios-que-vienen-desde-julio-2026-para-trabajadores-recargos-y-jornada-laboral-so35</t>
+          <t>https://caracol.com.co/2026/05/27/candidatos-presidenciales-colombia-2026-nombres-fotos-y-principales-propuestas/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:26 p. m.</t>
+          <t>30/05/2026 08:38 p. m.</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -4441,24 +4405,24 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>El periodista Gabriel Meluk se pronuncia en un comunicado frente a denuncias por presunto acoso sexual laboral</t>
+          <t>Fecha y hora para elegir al próximo presidente: ¿Cuándo se conocen los resultados oficiales?</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/articulo/el-periodista-gabriel-meluk-se-pronuncia-en-un-comunicado-frente-a-denuncias-por-presunto-acoso-sexual-laboral/202626/</t>
+          <t>https://caracol.com.co/2026/05/28/fecha-y-hora-para-elegir-al-proximo-presidente-cuando-se-conocen-los-resultados-oficiales/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:24 p. m.</t>
+          <t>30/05/2026 08:37 p. m.</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
@@ -4468,24 +4432,24 @@
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>“El mejor momento de mi vida”: Las primeras declaraciones de Alejandro Estrada tras ganar ‘La Casa de los Famosos’; reacciones en redes</t>
+          <t>¿Quién ganaría en segunda vuelta? Escenarios, según últimas encuestas presidenciales de mayo 2026</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/gente/articulo/el-mejor-momento-de-mi-vida-las-primeras-declaraciones-de-alejandro-estrada-tras-ganar-la-casa-de-los-famosos-reacciones-en-redes/202658/</t>
+          <t>https://caracol.com.co/2026/05/27/quien-ganaria-en-segunda-vuelta-escenarios-segun-ultimas-encuestas-presidenciales-de-mayo-2026/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:05 p. m.</t>
+          <t>30/05/2026 08:37 p. m.</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -4495,24 +4459,24 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Alineaciones Arsenal vs. PSG por la final de la Champions League</t>
+          <t>Elecciones presidenciales: horarios de Ley seca y cierre de fronteras</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/alineaciones-arsenal-vs-psg-por-la-final-de-la-champions-league/202626/</t>
+          <t>https://caracol.com.co/2026/05/28/elecciones-presidenciales-horarios-de-ley-seca-y-cierre-de-fronteras/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 09:54 p. m.</t>
+          <t>30/05/2026 08:36 p. m.</t>
         </is>
       </c>
       <c r="B149" s="6" t="inlineStr">
@@ -4522,24 +4486,24 @@
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>River Plate se refuerza pensando en un cruce con Santa Fe o Caracas en la Sudamericana: fichaje de lujo mundialista</t>
+          <t>¿Qué cosas puede y no puede hacer un jurado de votación? Registraduría Nacional explica</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/river-plate-se-refuerza-pensando-en-un-eventual-cruce-con-santa-fe-en-la-sudamericana-fichaje-de-lujo-mundialista/202618/</t>
+          <t>https://caracol.com.co/2026/05/30/que-cosas-puede-y-no-puede-hacer-un-jurado-de-votacion-registraduria-nacional-explica/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 09:54 p. m.</t>
+          <t>30/05/2026 08:35 p. m.</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -4549,24 +4513,24 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>¿Quién es Alejandro Estrada? La historia detrás del ganador de ‘La casa de los famosos’</t>
+          <t>¿Cómo van las elecciones Colombia 2026 en el exterior? Registraduría confirmó fecha para resultados</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/gente/articulo/quien-es-alejandro-estrada-la-historia-detras-del-ganador-de-la-casa-de-los-famosos/202626/</t>
+          <t>https://caracol.com.co/2026/05/26/como-van-las-elecciones-colombia-2026-en-el-exterior-registraduria-confirmo-fecha-para-resultados/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 08:54 p. m.</t>
+          <t>30/05/2026 07:55 p. m.</t>
         </is>
       </c>
       <c r="B151" s="6" t="inlineStr">
@@ -4576,24 +4540,24 @@
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>Alejandro Estrada es el ganador de ‘La casa de los famosos’; celebración es viral</t>
+          <t>Pedagogía Electoral: ¿Qué hacer y qué no este domingo de elecciones presidenciales?</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/gente/articulo/en-vivo-final-de-la-casa-de-los-famosos-3-inicia-la-cuenta-regresiva-para-conocer-al-ganador/202638/</t>
+          <t>https://caracol.com.co/2026/05/31/pedagogia-electoral-que-hacer-y-que-no-este-domingo-de-elecciones-presidenciales/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 08:54 p. m.</t>
+          <t>30/05/2026 07:50 p. m.</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -4603,24 +4567,24 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>El diario ‘El Tiempo’ se pronuncia sobre denuncia por acoso sexual laboral contra Gabriel Meluk: “Apoyamos las acciones tendientes a la protección de las víctimas”</t>
+          <t>Colombia se alista para las elecciones presidenciales 2026</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/articulo/el-diario-el-tiempo-se-pronuncia-sobre-denuncia-por-acoso-sexual-laboral-contra-gabriel-meluk-apoyamos-las-acciones-tendientes-a-la-proteccion-de-las-victimas/202616/</t>
+          <t>https://caracol.com.co/2026/05/31/colombia-se-alista-para-las-elecciones-presidenciales-2026/</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 07:54 p. m.</t>
+          <t>30/05/2026 06:35 p. m.</t>
         </is>
       </c>
       <c r="B153" s="6" t="inlineStr">
@@ -4630,24 +4594,24 @@
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>Luis Díaz habló sobre la capitanía de la Selección Colombia en el Mundial 2026: claro mensaje a James Rodríguez</t>
+          <t>Al menos 336 arrestados y un policía herido es el balance de los festejos del PSG en Francia</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/luis-diaz-hablo-sobre-la-capitania-de-la-seleccion-colombia-en-el-mundial-2026-claro-mensaje-a-james-rodriguez/202642/</t>
+          <t>https://caracol.com.co/2026/05/30/al-menos-336-arrestados-y-un-policia-herido-es-el-balance-de-los-festejos-del-psg-en-francia/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 07:54 p. m.</t>
+          <t>30/05/2026 05:59 p. m.</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -4657,24 +4621,24 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Con esto salió Luis Díaz cuando le preguntaron por la final Junior vs. Nacional: no se calló</t>
+          <t>Kevin Viveros salvó al Paranaense y se trepó a la cima de los goleadores del Brasileirao</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/con-esto-salio-luis-diaz-cuando-le-preguntaron-por-la-final-junior-vs-nacional-no-se-callo/202639/</t>
+          <t>https://caracol.com.co/2026/05/30/kevin-viveros-salvo-al-paranaense-y-se-trepo-a-la-cima-de-los-goleadores-del-brasileirao/</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 07:54 p. m.</t>
+          <t>30/05/2026 04:49 p. m.</t>
         </is>
       </c>
       <c r="B155" s="6" t="inlineStr">
@@ -4684,24 +4648,24 @@
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>Jineth Bedoya, directora de ‘No es hora de callar’, denunció al periodista Gabriel Meluk por acoso sexual laboral</t>
+          <t>PSG y Aston Villa disputarán la Supercopa de Europa 2026: Fecha y hora</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/bogota/articulo/jineth-bedoya-directora-de-no-es-hora-de-callar-denuncio-al-periodista-gabriel-meluk-por-acoso-sexual-laboral/202600/</t>
+          <t>https://caracol.com.co/2026/05/30/psg-y-aston-villa-disputaran-la-supercopa-de-europa-2026-fecha-y-hora/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 07:54 p. m.</t>
+          <t>30/05/2026 04:22 p. m.</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -4711,24 +4675,24 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Abelardo de la Espriella habló con el presidente de Ecuador, Daniel Noboa, y logró que ese país tumbara los aranceles contra Colombia</t>
+          <t>Sociedad de Cirugía Plástica respalda las iniciativas para combatir la medicina ilegal</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/abelardo-de-la-espriella-hablo-con-el-presidente-de-ecuador-daniel-noboa-y-logro-que-ese-pais-tumbara-los-aranceles-contra-colombia/202615/</t>
+          <t>https://caracol.com.co/2026/05/30/sociedad-de-cirugia-plastica-respalda-las-iniciativas-para-combatir-la-medicina-ilegal/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 06:54 p. m.</t>
+          <t>30/05/2026 04:06 p. m.</t>
         </is>
       </c>
       <c r="B157" s="6" t="inlineStr">
@@ -4738,24 +4702,24 @@
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>ELN dejó en libertad a Iván Alfredo Guzmán y aseguró que investigó supuestos nexos de su familia</t>
+          <t>PSG entra en la historia: así quedó el palmarés de la Champions League tras su bicampeonato</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/articulo/eln-dejo-en-libertad-a-ivan-alfredo-guzman-y-aseguro-que-investigo-supuestos-nexos-de-su-familia/202603/</t>
+          <t>https://caracol.com.co/2026/05/30/psg-entra-en-la-historia-asi-quedo-el-palmares-de-la-champions-league-tras-su-bicampeonato/</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 06:54 p. m.</t>
+          <t>30/05/2026 03:14 p. m.</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -4765,24 +4729,24 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>“Aquí entrego el poder”: Gustavo Petro empezó a despedirse de su mandato y volvió a hablar de las elecciones del 31 de mayo</t>
+          <t>Luis Enrique tras consagrarse Bicampeón de Champions: “Esto sólo se lo había visto hacer al Madrid”</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/aqui-entrego-el-poder-gustavo-petro-empezo-a-despedirse-de-su-mandato-y-volvio-a-hablar-de-las-elecciones-del-31-de-mayo/202634/</t>
+          <t>https://caracol.com.co/2026/05/30/luis-enrique-tras-consagrarse-bicampeon-de-champions-esto-solo-se-lo-habia-visto-hacer-al-madrid/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 06:54 p. m.</t>
+          <t>30/05/2026 02:24 p. m.</t>
         </is>
       </c>
       <c r="B159" s="6" t="inlineStr">
@@ -4792,24 +4756,24 @@
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>“Diciendo y haciendo”: Abelardo de la Espriella asegura que hará un importante anuncio a los colombianos</t>
+          <t>Pacto Histórico tendrá más de 112,000 testigos en todo el país para las elecciones presidenciales</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/confidenciales/articulo/diciendo-y-haciendo-abelardo-de-la-espriella-asegura-que-hara-un-importante-anuncio-a-los-colombianos/202616/</t>
+          <t>https://caracol.com.co/2026/05/30/pacto-historico-tendra-mas-de-112000-testigos-en-todo-el-pais-para-las-elecciones-presidenciales/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 05:54 p. m.</t>
+          <t>30/05/2026 01:35 p. m.</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -4819,24 +4783,24 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>¿Qué podría pasar con el precio del dólar en Colombia si Iván Cepeda gana las elecciones este domingo, 31 de mayo?</t>
+          <t>“Que ganen las ideas y no las mentiras”: Mindefensa al instalar PMU para evitar riesgos cibernéticos</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/economia/macroeconomia/articulo/que-podria-pasar-con-el-precio-del-dolar-en-colombia-si-ivan-cepeda-gana-las-elecciones-este-domingo-31-de-mayo/202654/</t>
+          <t>https://caracol.com.co/2026/05/30/que-ganen-las-ideas-y-no-las-mentiras-mindefensa-al-instalar-pmu-para-evitar-riesgos-ciberneticos/</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 04:54 p. m.</t>
+          <t>30/05/2026 01:30 p. m.</t>
         </is>
       </c>
       <c r="B161" s="6" t="inlineStr">
@@ -4846,24 +4810,24 @@
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>Édgar Rentería, reconocido exbeisbolista, votará por Abelardo de la Espriella: “Estoy firme por la patria”</t>
+          <t>Elecciones en Venezuela: excandidato González Urrutia respalda convocar nuevas presidenciales</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/confidenciales/articulo/edgar-renteria-reconocido-exbeisbolista-votara-por-abelardo-de-la-espriella/202606/</t>
+          <t>https://caracol.com.co/2026/05/30/elecciones-en-venezuela-excandidato-gonzalez-urrutia-respalda-convocar-nuevas-presidenciales/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 03:54 p. m.</t>
+          <t>30/05/2026 01:16 p. m.</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -4873,24 +4837,24 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>A Petro no le gustó que Carlos Fernando Galán negara el uso de un colegio a pocos días de elecciones: “¡Qué ignorancia!”</t>
+          <t>Bogotá fue testigo de la “Feria Gastronómica Europea” con 17 expositores y entrada gratuita</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/a-petro-no-le-gusto-que-carlos-fernando-galan-negara-el-uso-de-un-colegio-a-pocos-dias-de-elecciones-que-ignorancia/202612/</t>
+          <t>https://caracol.com.co/2026/05/30/bogota-fue-testigo-de-la-feria-gastronomica-europea-con-17-expositores-y-entrada-gratuita/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 02:54 p. m.</t>
+          <t>30/05/2026 12:25 p. m.</t>
         </is>
       </c>
       <c r="B163" s="6" t="inlineStr">
@@ -4900,24 +4864,24 @@
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>Estos fueron los gestos burlescos del exembajador Daniel Garcés Carabalí que generaron incomodidad en plena audiencia</t>
+          <t>Gobierno instaló PMU nacional para blindar la jornada electoral de este domingo 31 de mayo</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/articulo/estos-fueron-los-gestos-burlescos-del-exembajador-daniel-garces-carabali-que-generaron-incomodidad-en-plena-audiencia/202616/</t>
+          <t>https://caracol.com.co/2026/05/30/gobierno-instala-pmu-nacional-para-blindar-la-jornada-electoral-de-este-domingo-31-de-mayo/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 02:54 p. m.</t>
+          <t>30/05/2026 12:17 p. m.</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -4927,22 +4891,26 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>José Manuel Restrepo le contesta a Aida Quilcué por polémica frase sobre las universidades: “La tiranía de la mediocridad”</t>
+          <t>Droguerías CAFAM se pronuncian frente a las medidas impuestas por la SuperSalud: ¿Qué dijeron?</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/semana-tv/semana-el-debate/articulo/jose-manuel-restrepo-le-responde-duro-a-aida-quilcue-por-polemica-frase-sobre-universidades-la-tirania-de-la-mediocridad/202624/</t>
+          <t>https://caracol.com.co/2026/05/30/droguerias-cafam-se-pronuncian-frente-a-las-medidas-impuestas-por-la-supersalud-que-dijeron/</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="6" t="inlineStr"/>
+      <c r="A165" s="6" t="inlineStr">
+        <is>
+          <t>30/05/2026 08:40 p. m.</t>
+        </is>
+      </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -4950,22 +4918,26 @@
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>Picante respuesta de Néstor Lorenzo hacia los duros críticos de la Selección Colombia: habló de frente</t>
+          <t>Las propuestas de Abelardo de la Espriella: seguridad total de “mano dura” y el crecimiento económico acelerado</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/picante-respuesta-de-nestor-lorenzo-hacia-los-duros-criticos-de-la-seleccion-colombia-hablo-de-frente/202636/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/las-propuestas-de-abelardo-de-la-espriella-seguridad-total-de-mano-dura-y-el-crecimiento-economico-acelerado.html</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="3" t="inlineStr"/>
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>30/05/2026 08:34 p. m.</t>
+        </is>
+      </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -4973,22 +4945,26 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Sebastián Villa desmintió lo dicho en su contra: duro dardo por su sacada del Mundial 2026</t>
+          <t>Las propuestas de Iván Cepeda, tres revoluciones y más inversión social</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/sebastian-villa-desmintio-lo-dicho-en-su-contra-duro-dardo-por-su-sacada-del-mundial-2026/202640/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/las-propuestas-de-ivan-cepeda-tres-revoluciones-y-mas-inversion-social.html</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="6" t="inlineStr"/>
+      <c r="A167" s="6" t="inlineStr">
+        <is>
+          <t>30/05/2026 08:21 p. m.</t>
+        </is>
+      </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -4996,22 +4972,26 @@
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>Figo no es cortés con Colombia y le hace advertencia para el Mundial 2026: “Que tengan cuidado”</t>
+          <t>Las propuestas de Paloma Valencia: seguridad total y reactivación petrolera</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/figo-no-es-cortes-con-colombia-y-le-hace-advertencia-para-el-mundial-2026-que-tengan-cuidado/202640/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/las-propuestas-de-paloma-valencia-seguridad-total-y-reactivacion-petrolera.html</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="3" t="inlineStr"/>
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>30/05/2026 07:57 p. m.</t>
+        </is>
+      </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5019,22 +4999,26 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Estados Unidos toma drástica decisión para el Mundial 2026: hizo prohibición alrededor de los estadios</t>
+          <t>Iván Cepeda: “Es necesario, dentro del capitalismo, pasar a un modelo socialmente equitativo”</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/estados-unidos-toma-drastica-decision-para-el-mundial-2026-hizo-prohibicion-alrededor-de-los-estadios/202655/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/daniel-coronell-entrevista-a-ivan-cepeda-a-pocas-horas-de-las-elecciones.html</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="6" t="inlineStr"/>
+      <c r="A169" s="6" t="inlineStr">
+        <is>
+          <t>30/05/2026 07:25 p. m.</t>
+        </is>
+      </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5042,22 +5026,26 @@
       </c>
       <c r="C169" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>“Ahora, los que llaman los nunca son los mismos paracos de siempre”: fuerte declaración de Gustavo Petro desde Barranquilla</t>
+          <t>Estados Unidos ataca un barco que trataba de atravesar el estrecho de Ormuz rumbo a Irán</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/ahora-los-que-llaman-los-nunca-son-los-mismos-paracos-de-siempre-fuerte-declaracion-de-gustavo-petro-desde-barranquilla/202642/</t>
+          <t>https://elpais.com/internacional/2026-05-31/estados-unidos-ataca-un-barco-que-trataba-de-atravesar-el-estrecho-de-ormuz-rumbo-a-iran.html</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="3" t="inlineStr"/>
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>30/05/2026 06:28 p. m.</t>
+        </is>
+      </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5065,22 +5053,26 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>A dos días de las elecciones, Gustavo Petro anunció que presentará la ley Yulixa: estos son los detalles del proyecto</t>
+          <t>Abelardo de la Espriella cierra su campaña en una entrevista con Westcol: “Quien demuestre la idoneidad física y psicológica podrá portar un arma en la era del tigre”</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/a-dos-dias-de-las-elecciones-gustavo-petro-anuncio-que-presentara-la-ley-yulixa-estos-son-los-detalles-del-proyecto/202610/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-30/abelardo-de-la-espriella-cierra-su-campana-en-una-entrevista-con-westcol-esta-no-es-una-candidatura-sino-un-movimiento-popular.html</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="6" t="inlineStr"/>
+      <c r="A171" s="6" t="inlineStr">
+        <is>
+          <t>30/05/2026 06:07 p. m.</t>
+        </is>
+      </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5088,22 +5080,26 @@
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>Expertos responden si las elecciones están blindadas: “El mayor riesgo es el voto desinformado”</t>
+          <t>Noboa insiste en convertir la guerra arancelaria en herramienta electoral en Colombia</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/expertos-responden-si-las-elecciones-estan-blindadas-el-mayor-riesgo-es-el-voto-desinformado/202637/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-30/noboa-insiste-en-convertir-la-guerra-arancelaria-en-herramienta-electoral-en-colombia.html</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="3" t="inlineStr"/>
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>30/05/2026 05:30 p. m.</t>
+        </is>
+      </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5111,22 +5107,26 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Denuncian amenaza contra la representante a la Cámara por Bogotá Claudia Romero: le enviaron una corona fúnebre hasta su residencia</t>
+          <t>Vox abraza una internacional blanca para unir Europa y lograr un “efecto salida” de emigrantes</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/articulo/denuncian-amenaza-contra-la-representante-a-la-camara-por-bogota-claudia-romero-le-enviaron-una-corona-funebre-hasta-su-residencia/202656/</t>
+          <t>https://elpais.com/espana/2026-05-30/vox-abraza-una-internacional-blanca-para-unir-europa-y-lograr-un-efecto-salida-de-emigrantes.html</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="6" t="inlineStr"/>
+      <c r="A173" s="6" t="inlineStr">
+        <is>
+          <t>30/05/2026 05:25 p. m.</t>
+        </is>
+      </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5134,22 +5134,26 @@
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D173" s="7" t="inlineStr">
         <is>
-          <t>Volcamiento de camión en la vía Bogotá-La Calera generó fuertes afectaciones al tránsito</t>
+          <t>Paloma Valencia: “A los guerrilleros les voy a hacer sentir la mano de acero de la mujer colombiana”</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/vehiculos/articulo/volcamiento-de-camion-en-la-via-bogota-la-calera-genero-fuertes-afectaciones-al-transito/202631/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-30/paloma-valencia-se-reune-con-cuatro-influenciadores-a-15-horas-del-inicio-de-las-elecciones.html</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="3" t="inlineStr"/>
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>30/05/2026 05:15 p. m.</t>
+        </is>
+      </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5157,22 +5161,26 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>“Combinación mortal”: Medicina Legal advierte por licor artesanal que en el cuerpo se transforma en cianuro</t>
+          <t>Elecciones Colombia 2026, en vivo | Cepeda en su entrevista final con Coronell: “Hay obstinación en no querer escuchar lo que digo y lo que represento”</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/articulo/combinacion-mortal-medicina-legal-advierte-por-licor-artesanal-que-en-el-cuerpo-se-transforma-en-cianuro/202632/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-30/elecciones-presidenciales-en-colombia-2026-en-vivo.html</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="6" t="inlineStr"/>
+      <c r="A175" s="6" t="inlineStr">
+        <is>
+          <t>30/05/2026 04:51 p. m.</t>
+        </is>
+      </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5180,24 +5188,24 @@
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>Gobernador del Guaviare pide apoyo al Gobierno tras combates entre disidencias que dejaron 48 muertos: “Heridos han llegado a las casas buscando ayuda”</t>
+          <t>Bad Bunny en Madrid: el alucinante jolgorio del perreo y el amor</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/florencia/articulo/gobernador-del-guaviare-pide-apoyo-al-gobierno-tras-combates-entre-disidencias-que-dejaron-48-muertos-heridos-han-llegado-a-las-casas-buscando-ayuda/202607/</t>
+          <t>https://elpais.com/cultura/2026-05-30/bad-bunny-en-madrid-el-alucinante-jolgorio-del-perreo-y-el-amor.html</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 09:54 p. m.</t>
+          <t>30/05/2026 04:49 p. m.</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -5207,24 +5215,24 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>21 municipios en riesgo electoral y récord en testigos: así llega Antioquia a las elecciones</t>
+          <t>Más de un centenar de detenidos en París en los incidentes producidos tras la victoria del PSG en la Champions</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/antioquia/antioquia-riesgo-electoral-testigos-preparacion-elecciones-presidenciales-2026-PG37135846</t>
+          <t>https://elpais.com/deportes/futbol/2026-05-30/mas-de-un-centenar-de-detenidos-en-paris-en-los-incidentes-producidos-tras-la-victoria-del-psg-en-la-champions.html</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 09:54 p. m.</t>
+          <t>30/05/2026 04:40 p. m.</t>
         </is>
       </c>
       <c r="B177" s="6" t="inlineStr">
@@ -5234,24 +5242,24 @@
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>Liga de Campeones de Europa: final de 2.500 millones de euros</t>
+          <t>Vitinha, tras ganar la Champions: “Somos el mejor equipo del mundo”</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/deportes/futbol/final-champions-league-arsenal-psg-donde-ver-colombia-PG37135965</t>
+          <t>https://elpais.com/deportes/futbol/2026-05-30/vitinha-tras-ganar-la-champions-somos-el-mejor-equipo-del-mundo.html</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 08:54 p. m.</t>
+          <t>30/05/2026 04:22 p. m.</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -5261,24 +5269,24 @@
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>DIM empató contra Leones F.C. en la Copa Betplay-2026</t>
+          <t>Resultados de las elecciones en Colombia 2026: cuándo se conocerán las votaciones y a qué hora inicia el preconteo</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/deportes/futbol/dim-leones-empate-copa-betplay-2026-hoy-DG37134575</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-30/resultados-de-las-elecciones-en-colombia-2026-cuando-se-conoceran-las-votaciones-y-a-que-hora-inicia-el-preconteo.html</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 08:54 p. m.</t>
+          <t>30/05/2026 04:20 p. m.</t>
         </is>
       </c>
       <c r="B179" s="6" t="inlineStr">
@@ -5288,24 +5296,24 @@
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>“¡Vienen a bombardear!”: Los Lobos y disidencias de las Farc libran una guerra por el oro ilegal en Ecuador</t>
+          <t>El PAN cierra filas con Maru Campos frente a la petición de juicio político de Morena</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/internacional/los-lobos-disidencias-farc-guerra-oro-ilegal-ecuador-IG37135278</t>
+          <t>https://elpais.com/mexico/2026-05-30/el-pan-cierra-filas-con-maru-campos-frente-a-la-peticion-de-juicio-politico-de-morena.html</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 08:54 p. m.</t>
+          <t>30/05/2026 04:17 p. m.</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -5315,24 +5323,24 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>La Loma El Escobero sigue cerrada por emergencia invernal: habilitarían un carril este sábado</t>
+          <t>Detenido el presidente municipal de Cuautla Jesús Corona por sus presuntos vínculos con la delincuencia organizada</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/antioquia/loma-el-escobero-cerrada-emergencia-invernal-IG37135629</t>
+          <t>https://elpais.com/mexico/2026-05-30/detenido-el-presidente-municipal-de-cuautla-jesus-corona-por-sus-presuntos-vinculos-con-la-delincuencia-organizada.html</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 08:54 p. m.</t>
+          <t>30/05/2026 03:37 p. m.</t>
         </is>
       </c>
       <c r="B181" s="6" t="inlineStr">
@@ -5342,24 +5350,24 @@
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D181" s="7" t="inlineStr">
         <is>
-          <t>Oficina del Comisionado de Paz no sabe cómo contactar a “Calarcá” y lleva más de dos años negociando con él</t>
+          <t>El ajedrecista Carlsen en gran crisis: tres derrotas en cinco rondas</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/oficina-comisionado-de-paz-no-sabe-paradero-de-calarca-KG37135078</t>
+          <t>https://elpais.com/deportes/2026-05-30/el-ajedrecista-carlsen-en-gran-crisis-tres-derrotas-en-cinco-rondas.html</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 07:54 p. m.</t>
+          <t>30/05/2026 03:35 p. m.</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -5369,24 +5377,24 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>ISA respondió a Petro por denuncias sobre contratos en Perú</t>
+          <t>Ventura, vigésima Puerta Grande a pesar de fallar con el rejón de muerte</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/negocios/isa-responde-petro-denuncias-contratos-peru-financiacion-politica-DG37133123</t>
+          <t>https://elpais.com/cultura/2026-05-30/ventura-vigesima-puerta-grande-a-pesar-de-fallar-con-el-rejon-de-muerte.html</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 07:54 p. m.</t>
+          <t>30/05/2026 03:15 p. m.</t>
         </is>
       </c>
       <c r="B183" s="6" t="inlineStr">
@@ -5396,24 +5404,24 @@
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D183" s="7" t="inlineStr">
         <is>
-          <t>Estudiantes de Turbo protestan por inundaciones en su colegio: “Queremos estudiar, no nadar”</t>
+          <t>Muere Julio Le Parc, artista de la luz y el movimiento</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/antioquia/estudiante-turbo-colegio-inundacion-currulao-uraba-MG37133816</t>
+          <t>https://elpais.com/argentina/2026-05-30/muere-julio-le-parc-artista-de-la-luz-y-el-movimiento.html</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 07:54 p. m.</t>
+          <t>30/05/2026 03:14 p. m.</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -5423,24 +5431,24 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Ni la lluvia aplacó la fiesta naranja en el Polideportivo Sur y Envigado se coronó campeón en la B</t>
+          <t>PSG - Arsenal: la final de la Champions League 2026 en Budapest, en imágenes</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/deportes/futbol/envigado-campeon-de-la-b-polideportivo-sur-MG37133348</t>
+          <t>https://elpais.com/deportes/2026-05-30/psg-arsenal-la-final-de-la-champions-league-2026-en-budapest-en-imagenes.html</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 06:54 p. m.</t>
+          <t>30/05/2026 02:54 p. m.</t>
         </is>
       </c>
       <c r="B185" s="6" t="inlineStr">
@@ -5450,24 +5458,24 @@
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D185" s="7" t="inlineStr">
         <is>
-          <t>Murió Marcia Lucas, la editora de Star Wars y Taxi Driver</t>
+          <t>La gloria le vuelve a dar un portazo al Arsenal en la Champions</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/tendencias/marcia-lucas-editora-de-star-wars-y-taxi-driver-GG37132949</t>
+          <t>https://elpais.com/deportes/futbol/2026-05-30/la-gloria-le-vuelve-a-dar-un-portazo-al-arsenal-en-la-champions.html</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 05:54 p. m.</t>
+          <t>30/05/2026 02:50 p. m.</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -5477,24 +5485,24 @@
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>Superfinanciera informó que la usura en junio es de 28,79%, con alza frente a mayo</t>
+          <t>La grandeza premia al doble campeón PSG, que tumba en los penaltis al Arsenal</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/negocios/tasa-usura-colombia-junio-2026-superfinanciera-AH37127250</t>
+          <t>https://elpais.com/deportes/futbol/2026-05-30/la-grandeza-premia-al-doble-campeon-psg-que-tumba-en-los-penaltis-al-arsenal.html</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 05:54 p. m.</t>
+          <t>30/05/2026 01:10 p. m.</t>
         </is>
       </c>
       <c r="B187" s="6" t="inlineStr">
@@ -5504,24 +5512,24 @@
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D187" s="7" t="inlineStr">
         <is>
-          <t>ELN liberó al hijo del exalcalde de Tame, Arauca, tras cinco días de secuestro</t>
+          <t>Cantando y bailando, así ha recibido Madrid a Bad Bunny: “Con ganas de perreo, pero sin entrada”</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/ivan-alfredo-guzman-eln-libera-hijo-exalcalde-tame-arauca-PH37128689</t>
+          <t>https://elpais.com/cultura/2026-05-30/bienvenidos-al-madrid-de-bad-bunny-con-ganas-de-perreo-pero-sin-entrada.html</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 05:54 p. m.</t>
+          <t>30/05/2026 10:41 a. m.</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -5531,24 +5539,24 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Bloqueo de siete días amenaza continuidad de la operación de Cerrejón en La Guajira</t>
+          <t>Se rompe la cuerda de la bandera de España durante el izado en el desfile del Día de las Fuerzas Armadas</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/negocios/bloqueo-linea-ferrea-cerrejon-riesgo-operacion-guajira-colombia-GH37128529</t>
+          <t>https://elpais.com/videos/2026-05-30/se-rompre-la-cuerda-de-la-bandera-de-espana-durante-el-izado-en-el-desfile-del-dia-de-las-fuerzas-armadas.html?autoplay=1</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 05:54 p. m.</t>
+          <t>30/05/2026 09:24 a. m.</t>
         </is>
       </c>
       <c r="B189" s="6" t="inlineStr">
@@ -5558,24 +5566,24 @@
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D189" s="7" t="inlineStr">
         <is>
-          <t>Estas claves reducirían en un 50% el riesgo del alzhéimer, según experto internacional</t>
+          <t>De la ‘Operación Kitchen’ a Leire Díez: las cloacas se retroalimentan</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/tendencias/tips-para-reducir-riesgo-de-alzheimer-MH37129104</t>
+          <t>https://elpais.com/espana/2026-05-30/de-la-operacion-kitchen-a-leire-diez-las-cloacas-se-retroalimentan.html</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 05:54 p. m.</t>
+          <t>30/05/2026 07:14 a. m.</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -5585,24 +5593,24 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>Hartos de esperar al Estado, transportadores hacen “vaca” para tapar más de 900 huecos en la Medellín-Bogotá</t>
+          <t>Los partidos de Sumar instan al PSOE a actuar: “¿Hay una trama? Se contesta con leyes, medidas y ejemplaridad”</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/antioquia/estado-transportadores-vaca-huecos-autopista-medellin-bogota-GH37128178</t>
+          <t>https://elpais.com/espana/catalunya/2026-05-30/los-partidos-de-sumar-instan-al-psoe-a-actuar-hay-una-trama-se-contesta-con-leyes-medidas-y-ejemplaridad.html</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 05:54 p. m.</t>
+          <t>30/05/2026 06:19 a. m.</t>
         </is>
       </c>
       <c r="B191" s="6" t="inlineStr">
@@ -5612,24 +5620,24 @@
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D191" s="7" t="inlineStr">
         <is>
-          <t>Avianca emitió alerta por llamadas fraudulentas para exigir cobros a sus usuarios</t>
+          <t>Lotería Nacional: resultados del sorteo del sábado 30 de mayo</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/negocios/avianca-alerta-fraudes-usuarios-colombia-GH37129438</t>
+          <t>https://elpais.com/sorteos/2026-05-30/loteria-nacional-sorteo-del-sabado-30-de-mayo.html</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 04:54 p. m.</t>
+          <t>30/05/2026 04:03 a. m.</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -5639,24 +5647,24 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>Por primera vez, Donald Trump pierde respaldo de la clase trabajadora blanca que impulsó su ascenso político, según encuestas</t>
+          <t>Muere Josefina Molina, pionera del cine español, a los 89 años</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/internacional/donald-trump-pierde-respaldo-clase-trabajadora-blanca-encuestas-CH37127036</t>
+          <t>https://elpais.com/cultura/2026-05-30/fallece-josefina-molina-pionera-del-cine-espanol-a-los-89-anos.html</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 04:54 p. m.</t>
+          <t>30/05/2026 02:22 a. m.</t>
         </is>
       </c>
       <c r="B193" s="6" t="inlineStr">
@@ -5666,24 +5674,24 @@
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D193" s="7" t="inlineStr">
         <is>
-          <t>Ciberataque expuso informes de cartera de EPM y la Hidroeléctrica de Caldas</t>
+          <t>Muere el filósofo francés Edgar Morin a los 104 años</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/antioquia/ciberataque-cartera-epm-hidroelectrica-de-caldas-seguridad-informatica-GH37126716</t>
+          <t>https://elpais.com/cultura/2026-05-30/muere-el-filosofo-frances-edgar-morin-a-los-104-anos.html</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 04:54 p. m.</t>
+          <t>29/05/2026 10:30 p. m.</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -5693,24 +5701,24 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Así se movió la plata para compra de votos en las legislativas: ¿aplicarán los mismos métodos en las elecciones presidenciales?</t>
+          <t>Donna Haraway, filósofa: “Vivimos en un mundo pronatalista y antiinfancia. Los bebés deberían ser escasos y valiosos”</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/elecciones-presidenciales-2026-alerta-compra-de-votos-GH37123555</t>
+          <t>https://elpais.com/ideas/2026-05-30/donna-haraway-filosofa-vivimos-en-un-mundo-pronatalista-y-antiinfancia-tener-bebes-deberia-ser-algo-escaso-y-valioso.html</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 04:54 p. m.</t>
+          <t>30/05/2026 08:34 p. m.</t>
         </is>
       </c>
       <c r="B195" s="6" t="inlineStr">
@@ -5725,19 +5733,19 @@
       </c>
       <c r="D195" s="7" t="inlineStr">
         <is>
-          <t>¿Alcanzará a tiempo? Hidroituango espera llegar a la cota 420 en noviembre para evitar riesgos de apagón</t>
+          <t>Tras revelación de EL COLOMBIANO, investigarán a personal del Hospital Nazareth por video de pedagogía electoral a favor de Cepeda</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/antioquia/hidroituango-cota-energia-apagon-fenomeno-del-nino-noviembre-BH37124063</t>
+          <t>https://www.elcolombiano.com/colombia/investigacion-hospital-nazareth-video-ivan-cepeda-IB37149809</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 03:54 p. m.</t>
+          <t>30/05/2026 07:01 p. m.</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -5752,19 +5760,19 @@
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>Acompañar a Colombia en todo el Mundial 2026 costaría cerca de $230 millones</t>
+          <t>Sindicato de Ecopetrol descarta apoyar a Cepeda y respalda candidatos que impulsen exploración petrolera y fracking</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/negocios/cuanto-cuesta-ir-al-mundial-2026-EH37122776</t>
+          <t>https://www.elcolombiano.com/negocios/uso-sindicato-ecopetrol-descarta-ivan-cepeda-fracking-HB37148843</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 03:54 p. m.</t>
+          <t>30/05/2026 07:01 p. m.</t>
         </is>
       </c>
       <c r="B197" s="6" t="inlineStr">
@@ -5779,19 +5787,19 @@
       </c>
       <c r="D197" s="7" t="inlineStr">
         <is>
-          <t>Así se enriqueció la novia de Petro</t>
+          <t>Polémica por colecta impulsada por sectores del petrismo para transportar votantes: advierten riesgos de trashumancia electoral</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/multimedia/videos/asi-se-enriquecio-la-novia-de-petro-IH37120899</t>
+          <t>https://www.elcolombiano.com/colombia/politica/polemica-colecta-imprenta-republicana-votos-medellin-LB37149002</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 02:54 p. m.</t>
+          <t>30/05/2026 05:01 p. m.</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -5806,19 +5814,19 @@
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>Tres pruebas de fuego: análisis de los rivales de Colombia en la fase de grupos del Mundial 2026</t>
+          <t>Cuerpos de disidentes muertos en Guaviare tenían explosivos para atentar contra la Fuerza Pública</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/deportes/futbol/analisis-rivales-seleccion-colombia-fase-grupos-mundial-2026-HE37119860</t>
+          <t>https://www.elcolombiano.com/colombia/explosivos-en-cuerpos-evacuados-tras-combates-guaviare-farc-JB37145950</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 09:54 a. m.</t>
+          <t>30/05/2026 05:01 p. m.</t>
         </is>
       </c>
       <c r="B199" s="6" t="inlineStr">
@@ -5833,19 +5841,19 @@
       </c>
       <c r="D199" s="7" t="inlineStr">
         <is>
-          <t>Maluma habló de las elecciones en Colombia y lanzó inesperada propuesta para llevar votantes</t>
+          <t>¿Será la hora de los 9 colombianos en el Mundial? Colombia necesita de sus goles</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/entretenimiento/maluma-hablo-elecciones-colombia-lanzo-inesperada-propuesta-votantes-IF37100945</t>
+          <t>https://www.elcolombiano.com/especiales/mundial-2026/seleccion-colombia-los-numero-9-mundial-goleadores-luis-suarez-jhon-cordoba-cucho-hernandez-deuda-goles-EB37147663</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 09:54 a. m.</t>
+          <t>30/05/2026 04:01 p. m.</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -5860,19 +5868,19 @@
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>¡Le interesa! Este domingo habrá café gratis y descuentos en 120 marcas en Antioquia presentando el certificado de votación</t>
+          <t>Aficionado del PSG viajó a Bucarest en lugar de Budapest y se perdió la final de la Champions League</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/medellin/descuentos-y-beneficios-en-medellin-por-votar-elecciones-2026-IF37102578</t>
+          <t>https://www.elcolombiano.com/deportes/aficionado-psg-error-viaje-final-champions-DB37143642</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 09:54 a. m.</t>
+          <t>30/05/2026 04:01 p. m.</t>
         </is>
       </c>
       <c r="B201" s="6" t="inlineStr">
@@ -5887,19 +5895,19 @@
       </c>
       <c r="D201" s="7" t="inlineStr">
         <is>
-          <t>CNE reporta cifra récord de 373.612 testigos electorales para elecciones presidenciales</t>
+          <t>La tasa de usura supera el 28% y hará más costosas las compras a crédito para el Mundial</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/testigos-electorales-presidenciales-2026-cne-NF37103196</t>
+          <t>https://www.elcolombiano.com/negocios/tasa-usura-junio-compras-credito-mundial-EB37144321</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 09:54 a. m.</t>
+          <t>30/05/2026 04:01 p. m.</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -5914,19 +5922,19 @@
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>Necropsia de Yulixa Toloza reveló 11 heridas con objeto cortopunzante y múltiples fracturas</t>
+          <t>Nacional vs. Junior: tres finalistas de 2015 repiten en la serie final del Apertura-2026</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/necropsia-yulixa-toloza-revelo-fracturas-y-heridas-JF37101594</t>
+          <t>https://www.elcolombiano.com/deportes/futbol/final-nacional-junior-repitentes-definicion-titulo-2015-liga-betplay-2026-1-PB37144830</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 07:54 a. m.</t>
+          <t>30/05/2026 04:01 p. m.</t>
         </is>
       </c>
       <c r="B203" s="6" t="inlineStr">
@@ -5941,19 +5949,19 @@
       </c>
       <c r="D203" s="7" t="inlineStr">
         <is>
-          <t>Néstor Lorenzo reconoció error con Sebastián Villa: “Me equivoqué en exponerlo”</t>
+          <t>Video | Giro en caso de Alexánder Avendaño, el joven hallado muerto en embalse El Peñol-Guatapé</t>
         </is>
       </c>
       <c r="E203" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/especiales/mundial-2026/seleccion-colombia-lorenzo-sebastian-villa-reconocio-error-prelista-mundial-HN37097606</t>
+          <t>https://www.elcolombiano.com/antioquia/video-alexander-avendano-hallado-muerto-embalse-el-penol-guatape-OB37144813</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 06:54 a. m.</t>
+          <t>30/05/2026 03:01 p. m.</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -5968,17 +5976,21 @@
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>¿Estado austero o más gasto público? Así manejarían las finanzas públicas Paloma, Cepeda y de la Espriella</t>
+          <t>PSG hace historia: bicampeón de la Champions tras vencer al Arsenal en una final épica</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/negocios/propuestas-economia-candidatos-presidenciales-2026-paloma-abelardo-cepeda-OM37086594</t>
+          <t>https://www.elcolombiano.com/deportes/futbol/psg-bicampeon-champions-final-arsenal-resultado-prorroga-penaltis-CB37143221</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="6" t="inlineStr"/>
+      <c r="A205" s="6" t="inlineStr">
+        <is>
+          <t>30/05/2026 02:01 p. m.</t>
+        </is>
+      </c>
       <c r="B205" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5991,19 +6003,19 @@
       </c>
       <c r="D205" s="7" t="inlineStr">
         <is>
-          <t>Operativo destapa helicóptero con pasado oscuro y motor Rolls-Royce</t>
+          <t>Prográmese y siga estas recomendaciones para votar el 31 de mayo</t>
         </is>
       </c>
       <c r="E205" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/ejercito-incauta-helicoptero-de-la-mafia-NG33717192</t>
+          <t>https://qhubomedellin.com/util-para-vos/recomendaciones-para-votar-el-31-de-mayo-presidenciales-EO36920523</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 09:49 p. m.</t>
+          <t>30/05/2026 02:01 p. m.</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -6013,24 +6025,24 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>¿Lloverá en elecciones 2026? Pronóstico del IDEAM para sábado 30 y domingo 31 de mayo</t>
+          <t>EN VIDEO: Cohete de Jeff Bezos explotó durante prueba de encendido</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/llovera-en-elecciones-2026-pronostico-del-ideam-para-sabado-30-y-domingo-31-de-mayo/</t>
+          <t>https://qhubomedellin.com/actualidad/internacional/cohete-de-jeff-bezos-explota-durante-prueba-de-encendido-NH37129271</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 08:42 p. m.</t>
+          <t>30/05/2026 12:01 p. m.</t>
         </is>
       </c>
       <c r="B207" s="6" t="inlineStr">
@@ -6040,24 +6052,24 @@
       </c>
       <c r="C207" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D207" s="7" t="inlineStr">
         <is>
-          <t>Última gran prueba rumbo a Roma: Vingegaard defiende la maglia rosa</t>
+          <t>Camila Osorio lo dejó todo, pero no pudo avanzar a octavos de final en Roland Garros</t>
         </is>
       </c>
       <c r="E207" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/ultima-gran-prueba-rumbo-a-roma-vingegaard-defiende-la-maglia-rosa/</t>
+          <t>https://www.elcolombiano.com/deportes/camila-osorio-kalinskaya-roland-garros-MG37139005</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 08:27 p. m.</t>
+          <t>30/05/2026 12:01 p. m.</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -6067,24 +6079,24 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>Última jornada definida: así quedó la tabla de la Liga Femenina tras la fecha 13</t>
+          <t>Exclusivo | Así le hacen campaña a Cepeda los equipos básicos del MinSalud en La Guajira</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/ultima-jornada-definida-asi-quedo-la-tabla-de-la-liga-femenina-tras-la-fecha-13/</t>
+          <t>https://www.elcolombiano.com/especiales/elecciones-2026/campana-cepeda-los-equipos-basicos-minsalud-en-la-guajira-NG37139848</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 07:47 p. m.</t>
+          <t>30/05/2026 11:01 a. m.</t>
         </is>
       </c>
       <c r="B209" s="6" t="inlineStr">
@@ -6094,24 +6106,24 @@
       </c>
       <c r="C209" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D209" s="7" t="inlineStr">
         <is>
-          <t>Noboa se mete en elecciones: anuncia eliminación de aranceles tras llamada con De la Espriella</t>
+          <t>Desde el 3 de junio habrá cierre en la vía San Nicolás–La Ceja, ¿por qué?</t>
         </is>
       </c>
       <c r="E209" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/noboa-se-mete-en-elecciones-anuncia-eliminacion-de-aranceles-tras-llamada-con-de-la-espriella/</t>
+          <t>https://www.elcolombiano.com/antioquia/cierres-viales-via-san-nicolas-rionegro-la-ceja-antioquia-BG37138584</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 07:19 p. m.</t>
+          <t>30/05/2026 11:01 a. m.</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -6121,24 +6133,24 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>Agenda deportiva de la semana: Champions, final de Liga y selecciones rumbo al Mundial</t>
+          <t>¡Ojo! Caficultores de Bello tienen hasta este 31 de mayo para acceder a apoyos en cultivos</t>
         </is>
       </c>
       <c r="E210" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/agenda-deportiva-de-la-semana-champions-final-de-liga-y-selecciones-rumbo-al-mundial/</t>
+          <t>https://www.elcolombiano.com/antioquia/plazo-caficultores-de-bello-antioquia-apoyos-cafetales-FG37138973</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 07:18 p. m.</t>
+          <t>30/05/2026 11:01 a. m.</t>
         </is>
       </c>
       <c r="B211" s="6" t="inlineStr">
@@ -6148,24 +6160,24 @@
       </c>
       <c r="C211" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D211" s="7" t="inlineStr">
         <is>
-          <t>Con pullas contra Abelardo y Alejandro Char, concluye gira del presidente Petro en el Caribe</t>
+          <t>Más de 100 exalcaldes de Antioquia anuncian su respaldo a Paloma Valencia y Juan Daniel Oviedo</t>
         </is>
       </c>
       <c r="E211" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/con-pullas-contra-abelardo-y-alejandro-char-concluye-gira-del-presidente-petro-en-el-caribe/</t>
+          <t>https://www.elcolombiano.com/antioquia/exalcaldes-antioquia-apoyan-paloma-valencia-HG37138834</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 06:59 p. m.</t>
+          <t>30/05/2026 10:01 a. m.</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -6175,24 +6187,24 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>CIDH se declara preocupada por violencia política en Colombia antes de las elecciones</t>
+          <t>Gobierno rechaza acuerdo entre Noboa y De la Espriella para eliminar aranceles: “es un injerencia deliberada” en elecciones</t>
         </is>
       </c>
       <c r="E212" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/29/cidh-se-declara-preocupada-por-violencia-politica-en-colombia-antes-de-las-elecciones/</t>
+          <t>https://www.elcolombiano.com/colombia/petro-arremete-contra-daniel-noboa-bernie-moreno-aranceles-elecciones-PG37137769</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 06:37 p. m.</t>
+          <t>30/05/2026 10:01 a. m.</t>
         </is>
       </c>
       <c r="B213" s="6" t="inlineStr">
@@ -6202,24 +6214,24 @@
       </c>
       <c r="C213" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D213" s="7" t="inlineStr">
         <is>
-          <t>Elecciones 2026: ¿se pueden juntar los descansos por votar en primera y segunda vuelta presidencial?</t>
+          <t>La exigencia física le pasó factura a David Alonso en Italia que correrá este domingo, ¿cómo y dónde ver la carrera?</t>
         </is>
       </c>
       <c r="E213" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/29/elecciones-2026-se-pueden-juntar-los-descansos-por-votar-en-primera-y-segunda-vuelta-presidencial/</t>
+          <t>https://www.elcolombiano.com/deportes/david-alonso-moto2-gp-italia-clasificacion-motogp-BG37137644</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 05:58 p. m.</t>
+          <t>30/05/2026 09:01 a. m.</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -6229,24 +6241,24 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>Alerta de desastre natural: Falla tectónica podría generar sismo de magnitud 9, según científicos</t>
+          <t>Candidato Santiago Botero fue desalojado de su casa tras impedir el ingreso de su esposa e hijo; tiene una denuncia por violencia intrafamiliar</t>
         </is>
       </c>
       <c r="E214" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/29/alerta-de-desastre-natural-falla-tectonica-podria-generar-sismo-de-magnitud-9-segun-cientificos/</t>
+          <t>https://www.elcolombiano.com/colombia/santiago-botero-desalojo-casa-cartagena-IG37136842</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 05:37 p. m.</t>
+          <t>30/05/2026 07:01 a. m.</t>
         </is>
       </c>
       <c r="B215" s="6" t="inlineStr">
@@ -6256,24 +6268,24 @@
       </c>
       <c r="C215" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D215" s="7" t="inlineStr">
         <is>
-          <t>México cambia la Constitución para anular elecciones si se comprueba “injerencia extranjera”</t>
+          <t>A lomo de mula y cruzando ríos: así logró reducir el hambre Antioquia</t>
         </is>
       </c>
       <c r="E215" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/29/mexico-cambia-la-constitucion-para-anular-elecciones-si-se-comprueba-injerencia-extranjera/</t>
+          <t>https://www.elcolombiano.com/antioquia/estrategia-contra-el-hambre-y-la-desnutricion-en-antioquia-JG37134638</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 05:32 p. m.</t>
+          <t>30/05/2026 07:01 a. m.</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -6283,24 +6295,24 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t>Avianca alerta sobre nueva modalidad de estafa que exige pagos adicionales por supuestos sobrecostos</t>
+          <t>Lo que debe saber para votar este domingo: ¿alguno podría ganar en primera vuelta?</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/29/avianca-alerta-sobre-nueva-modalidad-de-estafa-que-exige-pagos-adicionales-por-supuestos-sobrecostos/</t>
+          <t>https://www.elcolombiano.com/especiales/elecciones-2026/elecciones-2026-consulta-puesto-votacion-horarios-primera-vuelta-PG37135864</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 05:18 p. m.</t>
+          <t>30/05/2026 06:01 a. m.</t>
         </is>
       </c>
       <c r="B217" s="6" t="inlineStr">
@@ -6310,26 +6322,22 @@
       </c>
       <c r="C217" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D217" s="7" t="inlineStr">
         <is>
-          <t>Elecciones en Colombia 2026: ¿Puede pedir un nuevo tarjetón si se equivoca? Registraduría responde</t>
+          <t>Calor dispara en más de 50% la venta de ventiladores en El Hueco, en Medellín: estos son los más vendidos</t>
         </is>
       </c>
       <c r="E217" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/29/elecciones-en-colombia-2026-puede-pedir-un-nuevo-tarjeton-si-se-equivoca-registraduria-responde/</t>
+          <t>https://www.elcolombiano.com/medellin/calor-medellin-ventas-ventiladores-hueco-KG37131092</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="3" t="inlineStr">
-        <is>
-          <t>29/05/2026 05:12 p. m.</t>
-        </is>
-      </c>
+      <c r="A218" s="3" t="inlineStr"/>
       <c r="B218" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -6337,26 +6345,22 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>Petro anunció proyecto para reglamentar cirugías estéticas en Colombia tras crimen de Yulixa Toloza</t>
+          <t>21 municipios en riesgo electoral y récord en testigos: así llega Antioquia a las elecciones</t>
         </is>
       </c>
       <c r="E218" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/29/petro-anuncio-proyecto-para-reglamentar-cirugias-esteticas-en-colombia-tras-crimen-de-yulixa-toloza/</t>
+          <t>https://www.elcolombiano.com/antioquia/antioquia-riesgo-electoral-testigos-preparacion-elecciones-presidenciales-2026-PG37135846</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="6" t="inlineStr">
-        <is>
-          <t>29/05/2026 05:01 p. m.</t>
-        </is>
-      </c>
+      <c r="A219" s="6" t="inlineStr"/>
       <c r="B219" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -6364,26 +6368,22 @@
       </c>
       <c r="C219" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D219" s="7" t="inlineStr">
         <is>
-          <t>ELN dejó en libertad a Alfredo Iván Guzmán, hijo del exalcalde de Tame, Arauca</t>
+          <t>Así se enriqueció la novia de Petro</t>
         </is>
       </c>
       <c r="E219" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/29/eln-dejo-en-libertad-a-alfredo-ivan-guzman-hijo-de-exalcalde-de-tame-arauca/</t>
+          <t>https://www.elcolombiano.com/multimedia/videos/asi-se-enriquecio-la-novia-de-petro-IH37120899</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="3" t="inlineStr">
-        <is>
-          <t>29/05/2026 04:57 p. m.</t>
-        </is>
-      </c>
+      <c r="A220" s="3" t="inlineStr"/>
       <c r="B220" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -6391,26 +6391,22 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D220" s="4" t="inlineStr">
         <is>
-          <t>Estados Unidos actualiza Lista Clinton y saca 28 nombres colombianos</t>
+          <t>Operativo destapa helicóptero con pasado oscuro y motor Rolls-Royce</t>
         </is>
       </c>
       <c r="E220" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/29/estados-unidos-actualiza-lista-clinton-y-saca-28-nombres-colombianos/</t>
+          <t>https://www.elcolombiano.com/colombia/ejercito-incauta-helicoptero-de-la-mafia-NG33717192</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="6" t="inlineStr">
-        <is>
-          <t>29/05/2026 04:48 p. m.</t>
-        </is>
-      </c>
+      <c r="A221" s="6" t="inlineStr"/>
       <c r="B221" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -6418,26 +6414,22 @@
       </c>
       <c r="C221" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D221" s="7" t="inlineStr">
         <is>
-          <t>Dónde votar en Medellín y Barranquilla: Mesa y hora límite para elecciones presidenciales 2026</t>
+          <t>Voraz incendio consumió vivienda en Itagüí y dejó a una familia sin nada</t>
         </is>
       </c>
       <c r="E221" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/29/donde-votar-en-medellin-y-barranquilla-mesa-y-hora-limite-para-elecciones-presidenciales-2026/</t>
+          <t>https://www.elcolombiano.com/antioquia/incendio-vivienda-itagui-el-guayabo-una-familia-sin-nada-AG37135775</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="3" t="inlineStr">
-        <is>
-          <t>29/05/2026 04:34 p. m.</t>
-        </is>
-      </c>
+      <c r="A222" s="3" t="inlineStr"/>
       <c r="B222" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -6445,26 +6437,22 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t>Así operan las páginas falsas que suplantan a la FIFA para estafar usuarios y robar datos bancarios</t>
+          <t>¡Le interesa! Este domingo habrá café gratis y descuentos en 120 marcas en Antioquia presentando el certificado de votación</t>
         </is>
       </c>
       <c r="E222" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/29/asi-operan-las-paginas-falsas-que-suplantan-a-la-fifa-para-estafar-usuarios-y-robar-datos-bancarios/</t>
+          <t>https://www.elcolombiano.com/medellin/descuentos-y-beneficios-en-medellin-por-votar-elecciones-2026-IF37102578</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="6" t="inlineStr">
-        <is>
-          <t>29/05/2026 04:32 p. m.</t>
-        </is>
-      </c>
+      <c r="A223" s="6" t="inlineStr"/>
       <c r="B223" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -6472,26 +6460,22 @@
       </c>
       <c r="C223" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D223" s="7" t="inlineStr">
         <is>
-          <t>ACIET se suma a la defensa de las universidades tras polémica por declaraciones de Aída Quilcué</t>
+          <t>Maluma habló de las elecciones en Colombia y lanzó inesperada propuesta para llevar votantes</t>
         </is>
       </c>
       <c r="E223" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/29/aciet-se-suma-a-la-defensa-de-las-universidades-tras-polemica-por-declaraciones-de-aida-quilcue/</t>
+          <t>https://www.elcolombiano.com/entretenimiento/maluma-hablo-elecciones-colombia-lanzo-inesperada-propuesta-votantes-IF37100945</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="3" t="inlineStr">
-        <is>
-          <t>29/05/2026 04:15 p. m.</t>
-        </is>
-      </c>
+      <c r="A224" s="3" t="inlineStr"/>
       <c r="B224" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -6499,24 +6483,24 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>Concluyó reunión de Trump en la Casa Blanca sobre guerra en Irán, ¿hay acuerdo?</t>
+          <t>¿Qué proponen en materia de impuestos los candidatos presidenciales punteros?</t>
         </is>
       </c>
       <c r="E224" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/29/concluyo-reunion-de-trump-en-la-casa-blanca-sobre-guerra-en-iran-hay-acuerdo/</t>
+          <t>https://www.elcolombiano.com/especiales/elecciones-2026/yo-cuido-la-democracia/propuestas-de-los-candidatos-presidenciales-GB37052040</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 04:13 p. m.</t>
+          <t>30/05/2026 08:33 p. m.</t>
         </is>
       </c>
       <c r="B225" s="6" t="inlineStr">
@@ -6526,24 +6510,24 @@
       </c>
       <c r="C225" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D225" s="7" t="inlineStr">
         <is>
-          <t>Bogotá es la primera ciudad de Colombia en presentar proyecciones climáticas hasta 2100</t>
+          <t>Elecciones 2026: ¿a qué hora se conocerán los resultados en Colombia?</t>
         </is>
       </c>
       <c r="E225" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/29/bogota-es-la-primera-ciudad-de-colombia-en-presentar-proyecciones-climaticas-hasta-2100/</t>
+          <t>https://canaltrece.com.co/noticias/elecciones-2026-a-que-hora-se-conoceran-los-resultados-en-colombia/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 09:45 p. m.</t>
+          <t>30/05/2026 08:26 p. m.</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -6553,24 +6537,24 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t>¿Quién es Alejandro Estrada? La historia del ganador de La casa de los famosos</t>
+          <t>Elecciones 2026: cómo votar en el exterior y consultar su puesto</t>
         </is>
       </c>
       <c r="E226" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/farandula/2026/05/29/quien-es-alejandro-estrada-la-historia-del-ganador-de-la-casa-de-los-famosos/</t>
+          <t>https://canaltrece.com.co/noticias/elecciones-2026-como-votar-en-el-exterior-y-consultar-su-puesto/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 09:45 p. m.</t>
+          <t>30/05/2026 08:14 p. m.</t>
         </is>
       </c>
       <c r="B227" s="6" t="inlineStr">
@@ -6580,24 +6564,24 @@
       </c>
       <c r="C227" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D227" s="7" t="inlineStr">
         <is>
-          <t>Farándula</t>
+          <t>¿Dónde votar? Consulte su puesto para las elecciones presidenciales 2026</t>
         </is>
       </c>
       <c r="E227" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/farandula/</t>
+          <t>https://canaltrece.com.co/noticias/donde-votar-consulte-su-puesto-para-las-elecciones-presidenciales-2026/</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 09:29 p. m.</t>
+          <t>30/05/2026 08:03 p. m.</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -6607,24 +6591,24 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t>Capturan a hombre señalado de asesinar a un adulto mayor en medio de un hurto</t>
+          <t>Tarjetón elecciones 2026: ¿qué pasa con votos por candidatos retirados?</t>
         </is>
       </c>
       <c r="E228" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/29/capturan-a-hombre-senalado-de-quitarle-la-vida-a-un-adulto-mayor-en-medio-de-un-hurto/</t>
+          <t>https://canaltrece.com.co/noticias/tarjeton-elecciones-2026-que-pasa-con-votos-por-candidatos-retirados/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 09:26 p. m.</t>
+          <t>30/05/2026 07:58 p. m.</t>
         </is>
       </c>
       <c r="B229" s="6" t="inlineStr">
@@ -6634,24 +6618,24 @@
       </c>
       <c r="C229" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D229" s="7" t="inlineStr">
         <is>
-          <t>Alejandro Estrada es el ganador de La casa de los famosos 2026</t>
+          <t>Elecciones 2026: Procurador Eljach llama a votar temprano y en paz</t>
         </is>
       </c>
       <c r="E229" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/farandula/2026/05/29/alejandro-estrada-es-el-ganador-de-la-casa-de-los-famosos-2026/</t>
+          <t>https://canaltrece.com.co/noticias/elecciones-2026-procurador-eljach-llama-a-votar-temprano-y-en-paz/</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 09:06 p. m.</t>
+          <t>30/05/2026 07:52 p. m.</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -6661,24 +6645,24 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D230" s="4" t="inlineStr">
         <is>
-          <t>Luis Díaz le hace fuerza a Junior en la final: “Ojalá pueda salir campeón”</t>
+          <t>Elecciones presidenciales 2026: cómo marcar la tarjeta electoral</t>
         </is>
       </c>
       <c r="E230" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/deportes/2026/05/29/luis-diaz-le-hace-fuerza-a-junior-en-la-final-ojala-pueda-salir-campeon/</t>
+          <t>https://canaltrece.com.co/noticias/elecciones-presidenciales-2026-como-marcar-la-tarjeta-electoral/</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 09:02 p. m.</t>
+          <t>30/05/2026 05:48 p. m.</t>
         </is>
       </c>
       <c r="B231" s="6" t="inlineStr">
@@ -6688,24 +6672,24 @@
       </c>
       <c r="C231" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D231" s="7" t="inlineStr">
         <is>
-          <t>Sicarios en moto acabaron con Carlos Alberto Gutiérrez: tenía anotaciones</t>
+          <t>¡No lo bote! Las marcas y beneficios legales que premian su certificado electoral este 31 de mayo</t>
         </is>
       </c>
       <c r="E231" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/29/sicarios-en-moto-acabaron-con-carlos-alberto-gutierrez-tenia-anotaciones/</t>
+          <t>https://canaltrece.com.co/noticias/no-lo-bote-las-marcas-y-beneficios-legales-que-premian-su-certificado-electoral-este-31-de-mayo/</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 08:57 p. m.</t>
+          <t>30/05/2026 05:39 p. m.</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -6715,24 +6699,24 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D232" s="4" t="inlineStr">
         <is>
-          <t>Resultados La Fantástica Noche: 29 de mayo de 2026</t>
+          <t>Terremoto político y judicial: Santiago Botero Jaramillo, denunciado por presunta violencia intrafamiliar</t>
         </is>
       </c>
       <c r="E232" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/loterias/chances/2026/05/29/resultados-la-fantastica-noche-29-de-mayo-de-2026/</t>
+          <t>https://canaltrece.com.co/noticias/terremoto-politico-y-judicial-santiago-botero-jaramillo-denunciado-por-presunta-violencia-intrafamiliar/</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 08:18 p. m.</t>
+          <t>29/05/2026 11:07 a. m.</t>
         </is>
       </c>
       <c r="B233" s="6" t="inlineStr">
@@ -6742,24 +6726,24 @@
       </c>
       <c r="C233" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D233" s="7" t="inlineStr">
         <is>
-          <t>Golpe a red criminal de ‘Los Pachenca’ por extorsión: siete capturados</t>
+          <t>Myke Towers confirma concierto en Bogotá con su gira “Trap Kings”</t>
         </is>
       </c>
       <c r="E233" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/29/golpe-a-red-criminal-de-los-pachenca-por-extorsion-siete-capturados/</t>
+          <t>https://canaltrece.com.co/noticias/myke-towers-confirma-concierto-en-bogota-con-su-gira-trap-kings/</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 07:52 p. m.</t>
+          <t>29/05/2026 10:51 a. m.</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -6769,24 +6753,24 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D234" s="4" t="inlineStr">
         <is>
-          <t>Linda Caicedo lidera la convocatoria de Colombia para buscar el cupo al Mundial 2027</t>
+          <t>Acoso callejero Colombia: el 89% de las mujeres afirma haberlo sufrido</t>
         </is>
       </c>
       <c r="E234" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/deportes/2026/05/29/linda-caicedo-lidera-la-convocatoria-de-colombia-para-buscar-el-cupo-al-mundial-2027/</t>
+          <t>https://canaltrece.com.co/noticias/acoso-callejero-colombia-mujeres/</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 07:38 p. m.</t>
+          <t>29/05/2026 10:44 a. m.</t>
         </is>
       </c>
       <c r="B235" s="6" t="inlineStr">
@@ -6796,24 +6780,24 @@
       </c>
       <c r="C235" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D235" s="7" t="inlineStr">
         <is>
-          <t>Abelardo de la Espriella anuncia acuerdo con Daniel Noboa: promete eliminar aranceles</t>
+          <t>Outdoor femenino Colombia: la tendencia que une aventura, naturaleza y comunidad</t>
         </is>
       </c>
       <c r="E235" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/2026/05/29/abelardo-de-la-espriella-anuncia-acuerdo-con-daniel-noboa-promete-eliminar-aranceles/</t>
+          <t>https://canaltrece.com.co/noticias/outdoor-femenino-colombia/</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 07:38 p. m.</t>
+          <t>29/05/2026 10:35 a. m.</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -6823,24 +6807,24 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D236" s="4" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bibliotecas para inspirar Cali: nueva apuesta por la lectura y los proyectos de vida</t>
         </is>
       </c>
       <c r="E236" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/</t>
+          <t>https://canaltrece.com.co/noticias/bibliotecas-para-inspirar-cali/</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 07:25 p. m.</t>
+          <t>29/05/2026 10:32 a. m.</t>
         </is>
       </c>
       <c r="B237" s="6" t="inlineStr">
@@ -6850,24 +6834,24 @@
       </c>
       <c r="C237" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D237" s="7" t="inlineStr">
         <is>
-          <t>José Mejía y Logly Pirela, los amigos que salieron juntos y aparecieron sin vida</t>
+          <t>Detección temprana cáncer de mama Colombia: la importancia de las redes de apoyo</t>
         </is>
       </c>
       <c r="E237" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/29/jose-mejia-y-logly-pirela-los-amigos-que-salieron-juntos-y-aparecieron-sin-vida/</t>
+          <t>https://canaltrece.com.co/noticias/deteccion-temprana-cancer-de-mama-colombia/</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 06:41 p. m.</t>
+          <t>29/05/2026 10:27 a. m.</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -6877,24 +6861,24 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D238" s="4" t="inlineStr">
         <is>
-          <t>Álvaro Hernández y Mauro Manotas: dolor, autocrítica y promesa de volver por el ascenso</t>
+          <t>Cuidado del cabello y la piel en vacaciones: errores que debes evitar</t>
         </is>
       </c>
       <c r="E238" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/deportes/2026/05/29/alvaro-hernandez-y-mauro-manotas-dolor-autocritica-y-promesa-de-volver-por-el-ascenso/</t>
+          <t>https://canaltrece.com.co/noticias/cuidado-del-cabello-y-la-piel-en-vacaciones/</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 05:56 p. m.</t>
+          <t>29/05/2026 10:18 a. m.</t>
         </is>
       </c>
       <c r="B239" s="6" t="inlineStr">
@@ -6904,24 +6888,24 @@
       </c>
       <c r="C239" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D239" s="7" t="inlineStr">
         <is>
-          <t>Falleció Jaime Bernal Villegas, exrector de la UTB</t>
+          <t>Bebé de 6 meses El Espinal: avanzan investigaciones tras su fallecimiento</t>
         </is>
       </c>
       <c r="E239" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/cartagena/2026/05/29/fallecio-jaime-bernal-villegas-exrector-de-la-utb/</t>
+          <t>https://canaltrece.com.co/noticias/bebe-de-6-meses-el-espinal/</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 05:27 p. m.</t>
+          <t>29/05/2026 09:10 a. m.</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -6931,24 +6915,24 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D240" s="4" t="inlineStr">
         <is>
-          <t>Así actuará la Fiscalía en Bolívar si hay delitos durante las elecciones del 31 de mayo</t>
+          <t>Fiesta en El Campín: Morat cantará en la despedida de la Selección Colombia rumbo al Mundial 2026</t>
         </is>
       </c>
       <c r="E240" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/cartagena/2026/05/29/asi-actuara-la-fiscalia-en-bolivar-si-hay-delitos-durante-las-elecciones-del-31-de-mayo/</t>
+          <t>https://canaltrece.com.co/noticias/fiesta-en-el-campin-morat-cantara-en-la-despedida-de-la-seleccion-colombia-rumbo-al-mundial-2026/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 04:39 p. m.</t>
+          <t>29/05/2026 09:03 a. m.</t>
         </is>
       </c>
       <c r="B241" s="6" t="inlineStr">
@@ -6958,24 +6942,24 @@
       </c>
       <c r="C241" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D241" s="7" t="inlineStr">
         <is>
-          <t>La historia del músico barranquillero que Shakira invitó a colaborar</t>
+          <t>Orgullo colombiano: Kapo es coronado como ‘Compositor del Año’ en los SESAC Latina Music Awards 2026</t>
         </is>
       </c>
       <c r="E241" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/farandula/2026/05/29/la-historia-del-musico-barranquillero-que-shakira-invito-a-colaborar/</t>
+          <t>https://canaltrece.com.co/noticias/orgullo-colombiano-kapo-es-coronado-como-compositor-del-ano-en-los-sesac-latina-music-awards-2026/</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 04:26 p. m.</t>
+          <t>29/05/2026 08:56 a. m.</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -6985,24 +6969,24 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D242" s="4" t="inlineStr">
         <is>
-          <t>Video: pelea en pleno partido de Envigado y Real Cartagena, hubo expulsados</t>
+          <t>De Medellín para el mundo: elkno enciende la escena urbana con su dancehall “Ritmo”</t>
         </is>
       </c>
       <c r="E242" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/deportes/2026/05/29/video-pelea-en-pleno-partido-de-envigado-y-real-cartagena-hubo-expulsados/</t>
+          <t>https://canaltrece.com.co/noticias/de-medellin-para-el-mundo-elkno-enciende-la-escena-urbana-con-su-dancehall-ritmo/</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 04:26 p. m.</t>
+          <t>29/05/2026 08:53 a. m.</t>
         </is>
       </c>
       <c r="B243" s="6" t="inlineStr">
@@ -7012,24 +6996,24 @@
       </c>
       <c r="C243" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D243" s="7" t="inlineStr">
         <is>
-          <t>Deportes</t>
+          <t>Cine colombiano: ‘VOLAR’ llega a las salas con un retrato íntimo de la soledad en Bogotá</t>
         </is>
       </c>
       <c r="E243" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/deportes/</t>
+          <t>https://canaltrece.com.co/noticias/cine-colombiano-volar-llega-a-las-salas-con-un-retrato-intimo-de-la-soledad-en-bogota/</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 04:14 p. m.</t>
+          <t>29/05/2026 08:49 a. m.</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -7039,24 +7023,24 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D244" s="4" t="inlineStr">
         <is>
-          <t>En una caleta hidráulica: así escondían 560 kilos de droga que iban hacia Centroamérica</t>
+          <t>Desde República Dominicana para el despecho: Amneliz debuta en la música popular con “El Desquite”</t>
         </is>
       </c>
       <c r="E244" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/29/en-una-caleta-hidraulica-asi-escondian-560-kilos-de-droga-que-iban-hacia-centroamerica/</t>
+          <t>https://canaltrece.com.co/noticias/desde-republica-dominicana-para-el-despecho-amneliz-debuta-en-la-musica-popular-con-el-desquite/</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 03:38 p. m.</t>
+          <t>29/05/2026 08:45 a. m.</t>
         </is>
       </c>
       <c r="B245" s="6" t="inlineStr">
@@ -7066,24 +7050,24 @@
       </c>
       <c r="C245" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D245" s="7" t="inlineStr">
         <is>
-          <t>Jhaider Samuel Garizao, el joven que se ahogó en una playa de Bocagrande</t>
+          <t>Giro en el caso de Mía Cataleya: Revelan crudos detalles de su ingreso al hospital y una captura en El Espinal</t>
         </is>
       </c>
       <c r="E245" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/29/jhaider-samuel-garizao-el-joven-que-se-ahogo-en-una-playa-de-bocagrande/</t>
+          <t>https://canaltrece.com.co/noticias/giro-en-el-caso-de-mia-cataleya-revelan-crudos-detalles-de-su-ingreso-al-hospital-y-una-captura-en-el-espinal/</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 03:16 p. m.</t>
+          <t>29/05/2026 08:24 a. m.</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -7093,24 +7077,24 @@
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D246" s="4" t="inlineStr">
         <is>
-          <t>Video: golazo de Envigado ante Real Cartagena en la final del Torneo BetPlay</t>
+          <t>«Vi una pierna afuera»: Los crudos testimonios del hallazgo del profesor Kevin Santiago Ángel en Kennedy</t>
         </is>
       </c>
       <c r="E246" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/deportes/2026/05/29/video-golazo-de-envigado-ante-real-cartagena-en-la-final-del-torneo-betplay/</t>
+          <t>https://canaltrece.com.co/noticias/vi-una-pierna-afuera-los-crudos-testimonios-del-hallazgo-del-profesor-kevin-santiago-angel-en-kennedy/</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 03:01 p. m.</t>
+          <t>29/05/2026 08:12 a. m.</t>
         </is>
       </c>
       <c r="B247" s="6" t="inlineStr">
@@ -7120,24 +7104,24 @@
       </c>
       <c r="C247" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D247" s="7" t="inlineStr">
         <is>
-          <t>Yorlanis Gutierrez, la mujer hallada sin vida y con signos de violencia en una vía</t>
+          <t>Giro en el caso de Ana María Meza: Fiscalía confirma que se investiga como presunto feminicidio</t>
         </is>
       </c>
       <c r="E247" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/29/yorlanis-gutierrez-la-mujer-hallada-sin-vida-a-un-costado-de-una-via/</t>
+          <t>https://canaltrece.com.co/noticias/giro-en-el-caso-de-ana-maria-meza-fiscalia-confirma-que-se-investiga-como-presunto-feminicidio/</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 02:48 p. m.</t>
+          <t>29/05/2026 08:08 a. m.</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -7147,22 +7131,26 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D248" s="4" t="inlineStr">
         <is>
-          <t>Condenado por intentar matar a su expareja en Cartagena: también quiso abusarla sexualmente</t>
+          <t>El silencio forzado de Afganistán: El año en que las mujeres perdieron el derecho a existir en público</t>
         </is>
       </c>
       <c r="E248" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/29/condenado-por-intentar-quitarle-la-vida-a-su-expareja-en-cartagena-tambien-quiso-abusarla/</t>
+          <t>https://canaltrece.com.co/noticias/el-silencio-forzado-de-afganistan-el-ano-en-que-las-mujeres-perdieron-el-derecho-a-existir-en-publico/</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="6" t="inlineStr"/>
+      <c r="A249" s="6" t="inlineStr">
+        <is>
+          <t>28/05/2026 11:24 a. m.</t>
+        </is>
+      </c>
       <c r="B249" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7170,22 +7158,26 @@
       </c>
       <c r="C249" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D249" s="7" t="inlineStr">
         <is>
-          <t>Premios Excelencia El Universal 2026: ya están abiertas las postulaciones</t>
+          <t>Jóvenes elecciones Colombia 2026: TikTok e IA cambian las campañas</t>
         </is>
       </c>
       <c r="E249" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/cartagena/2026/05/26/premios-excelencia-el-universal-2026-ya-estan-abiertas-las-postulaciones/</t>
+          <t>https://canaltrece.com.co/noticias/jovenes-elecciones-colombia-2026/</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="3" t="inlineStr"/>
+      <c r="A250" s="3" t="inlineStr">
+        <is>
+          <t>28/05/2026 11:18 a. m.</t>
+        </is>
+      </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7193,24 +7185,24 @@
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D250" s="4" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Seguridad en vehículos de trabajo: la tecnología redefine el transporte de carga</t>
         </is>
       </c>
       <c r="E250" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/cartagena/</t>
+          <t>https://canaltrece.com.co/noticias/seguridad-en-vehiculos-de-trabajo/</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 07:45 p. m.</t>
+          <t>28/05/2026 10:45 a. m.</t>
         </is>
       </c>
       <c r="B251" s="6" t="inlineStr">
@@ -7220,24 +7212,24 @@
       </c>
       <c r="C251" s="6" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D251" s="7" t="inlineStr">
         <is>
-          <t>Atlético de Madrid se burla del Barça con falsas ofertas y aviva la tensión por Julián Álvarez</t>
+          <t>De Mar y Río lanza “Cantaré”, un homenaje al Pacífico colombiano</t>
         </is>
       </c>
       <c r="E251" s="8" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/deportes/articulo/2026/5/atletico-de-madrid-se-burla-del-barca-con-falsas-ofertas-y-aviva-la-tension-por-julian-alvarez</t>
+          <t>https://canaltrece.com.co/noticias/de-mar-y-rio-lanza-cantare-un-homenaje-al-pacifico-colombiano/</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 07:15 p. m.</t>
+          <t>28/05/2026 10:04 a. m.</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -7247,24 +7239,24 @@
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D252" s="4" t="inlineStr">
         <is>
-          <t>Jineth Bedoya denuncia a Gabriel Meluk ante la Fiscalía por presunto acoso: “Merecemos espacios laborales seguros”</t>
+          <t>Helipuertos en Bogotá: la nueva tendencia para vivir experiencias exclusivas</t>
         </is>
       </c>
       <c r="E252" s="5" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/genero/articulo/2026/5/jineth-bedoya-denuncia-a-gabriel-meluk-ante-la-fiscalia-por-presunto-acoso-merecemos-espacios-laborales-seguros</t>
+          <t>https://canaltrece.com.co/noticias/helipuertos-en-bogota-experiencias/</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 04:15 p. m.</t>
+          <t>28/05/2026 10:00 a. m.</t>
         </is>
       </c>
       <c r="B253" s="6" t="inlineStr">
@@ -7274,24 +7266,24 @@
       </c>
       <c r="C253" s="6" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D253" s="7" t="inlineStr">
         <is>
-          <t>Campaña de Paloma Valencia niega que Nicolás Pérez fuera gerente y lo señala por presuntos maltratos a mujeres del equipo</t>
+          <t>Orgullo vallenato: Jorge Celedón hace historia y conquista el #1 de la radio en Centroamérica</t>
         </is>
       </c>
       <c r="E253" s="8" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/elecciones-colombia-2026/articulo/2026/5/campana-de-paloma-valencia-niega-que-nicolas-perez-fuera-gerente-y-lo-senala-por-presuntos-maltratos-a-mujeres-del-equipo</t>
+          <t>https://canaltrece.com.co/noticias/orgullo-vallenato-jorge-celedon-hace-historia-y-conquista-el-1-de-la-radio-en-centroamerica/</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 12:15 p. m.</t>
+          <t>28/05/2026 09:58 a. m.</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -7301,24 +7293,24 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D254" s="4" t="inlineStr">
         <is>
-          <t>¿Quiénes no podrán votar en las elecciones presidenciales de 2026?</t>
+          <t>Alea Animal Distinta: el himno de autenticidad y empoderamiento femenino</t>
         </is>
       </c>
       <c r="E254" s="5" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/pais/articulo/2026/5/quienes-no-podran-votar-en-las-elecciones-presidenciales-de-2026</t>
+          <t>https://canaltrece.com.co/noticias/alea-animal-distinta-video/</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 12:00 p. m.</t>
+          <t>30/05/2026 08:19 p. m.</t>
         </is>
       </c>
       <c r="B255" s="6" t="inlineStr">
@@ -7328,24 +7320,24 @@
       </c>
       <c r="C255" s="6" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D255" s="7" t="inlineStr">
         <is>
-          <t>Desempleo en Colombia se ubicó en 8,8 por ciento en abril. ¿Qué pasa en el mercado laboral según el Dane?</t>
+          <t>Elecciones Colombia este domingo 31 de mayo: horarios de votación y recomendaciones para la jornada electoral</t>
         </is>
       </c>
       <c r="E255" s="8" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/economia/articulo/2026/5/desempleo-en-colombia-se-ubico-en-88-por-ciento-en-abril-que-pasa-en-el-mercado-laboral-segun-el-dane</t>
+          <t>https://www.semana.com/politica/articulo/elecciones-colombia-este-domingo-31-de-mayo-horarios-de-votacion-y-recomendaciones-para-la-jornada-electoral/202636/</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 11:30 a. m.</t>
+          <t>30/05/2026 08:19 p. m.</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -7355,24 +7347,24 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr">
         <is>
-          <t>Récord de testigos electorales para las presidenciales del 31 de mayo</t>
+          <t>Cómo consultar el puesto de votación para las elecciones de 2026; link de consulta</t>
         </is>
       </c>
       <c r="E256" s="5" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/elecciones-colombia-2026/articulo/2026/5/record-de-testigos-electorales-para-las-presidenciales-del-31-de-mayo</t>
+          <t>https://www.semana.com/nacion/articulo/como-consultar-el-puesto-de-votacion-para-las-elecciones-de-2026-link-de-consulta/202639/</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 08:20 a. m.</t>
+          <t>30/05/2026 07:01 p. m.</t>
         </is>
       </c>
       <c r="B257" s="6" t="inlineStr">
@@ -7382,24 +7374,24 @@
       </c>
       <c r="C257" s="6" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D257" s="7" t="inlineStr">
         <is>
-          <t>César Gaviria pide votar por Paloma Valencia para "restaurar el orden" y la seguridad en Colombia</t>
+          <t>Abelardo de la Espriella habla con Westcol en Barranquilla: “Yo nunca he defendido narcotraficantes, eso es una leyenda urbana”</t>
         </is>
       </c>
       <c r="E257" s="8" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/poder/articulo/2026/5/cesar-gaviria-pide-votar-por-paloma-valencia-para-restaurar-el-orden-y-la-seguridad-en-colombia</t>
+          <t>https://www.semana.com/politica/articulo/abelardo-de-la-espriella-habla-con-westcol-en-barranquilla-yo-nunca-he-defendido-narcotraficantes-eso-es-una-leyenda-urbana/202659/</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 06:53 a. m.</t>
+          <t>30/05/2026 07:01 p. m.</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -7409,24 +7401,24 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D258" s="4" t="inlineStr">
         <is>
-          <t>Ley seca en Bogotá: Alcaldía confirma restricciones por elecciones presidenciales este domingo</t>
+          <t>🔴 Elecciones Colombia 2026 EN VIVO | Siga en directo las últimas noticias: horarios de votación de la jornada electoral</t>
         </is>
       </c>
       <c r="E258" s="5" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/pais/articulo/2026/5/ley-seca-en-bogota-alcaldia-confirma-restricciones-por-elecciones-presidenciales-este-domingo</t>
+          <t>https://www.semana.com/nacion/articulo/elecciones-colombia-2026-en-vivo-siga-en-directo-las-ultimas-noticias-horarios-de-votacion-de-la-jornada-electoral/202656/</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="6" t="inlineStr">
         <is>
-          <t>28/05/2026 07:30 p. m.</t>
+          <t>30/05/2026 04:01 p. m.</t>
         </is>
       </c>
       <c r="B259" s="6" t="inlineStr">
@@ -7436,24 +7428,24 @@
       </c>
       <c r="C259" s="6" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D259" s="7" t="inlineStr">
         <is>
-          <t>Gobierno anuncia más de 93.000 millones para el Hospital Universitario San Juan de Dios: ¿en qué se van a utilizar?</t>
+          <t>VIDEO | Así fue la vibrante tanda de penaltis en la final de la Champions League que dejó al PSG campeón</t>
         </is>
       </c>
       <c r="E259" s="8" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/pais/articulo/2026/5/gobierno-anuncia-mas-de-93000-millones-para-el-hospital-universitario-san-juan-de-dios-en-que-se-van-a-utilizar</t>
+          <t>https://www.semana.com/deportes/articulo/video-asi-fue-la-vibrante-tanda-de-penaltis-en-la-final-de-la-champions-league-que-dejo-al-psg-campeon/202641/</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>28/05/2026 07:00 p. m.</t>
+          <t>30/05/2026 03:01 p. m.</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
@@ -7463,24 +7455,24 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t>Capturan a alias La Churca, presunta integrante del ELN vinculada a un atentado en Boyacá</t>
+          <t>PSG retiene su corona de la Champions League: bicampeón ante Arsenal por penales</t>
         </is>
       </c>
       <c r="E260" s="5" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/conflicto-armado-en-colombia/articulo/2026/5/capturan-a-alias-la-churca-presunta-integrante-del-eln-vinculada-a-un-atentado-en-boyaca</t>
+          <t>https://www.semana.com/deportes/articulo/psg-retiene-su-corona-de-la-champions-league-bicampeon-ante-arsenal-por-penales/202608/</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="6" t="inlineStr">
         <is>
-          <t>28/05/2026 06:15 p. m.</t>
+          <t>30/05/2026 04:01 a. m.</t>
         </is>
       </c>
       <c r="B261" s="6" t="inlineStr">
@@ -7490,24 +7482,24 @@
       </c>
       <c r="C261" s="6" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D261" s="7" t="inlineStr">
         <is>
-          <t>Gobierno Petro reanuda diálogos con bandas criminales en Medellín tras suspensión por fiesta vallenata</t>
+          <t>“Respetaremos los resultados”: Armando Benedetti explica el blindaje de seguridad del Gobierno Petro para las elecciones del domingo</t>
         </is>
       </c>
       <c r="E261" s="8" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/pais/articulo/2026/5/gobierno-petro-reanuda-dialogos-con-bandas-criminales-en-medellin-tras-suspension-por-fiesta-vallenata</t>
+          <t>https://www.semana.com/politica/articulo/respetaremos-los-resultados-armando-benedetti-explica-el-blindaje-de-seguridad-del-gobierno-petro-para-las-elecciones-del-domingo/202659/</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>28/05/2026 06:00 p. m.</t>
+          <t>30/05/2026 04:01 a. m.</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
@@ -7517,24 +7509,24 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D262" s="4" t="inlineStr">
         <is>
-          <t>¿Cuándo se entregará el laboratorio de robótica en colegio de Ciudad Bolívar? Distrito y Gobierno acordaron fecha</t>
+          <t>“La gente podrá salir libre y en paz”: presidente del CNE, Cristian Quiroz, sobre las elecciones presidenciales</t>
         </is>
       </c>
       <c r="E262" s="5" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/pais/articulo/2026/5/cuando-se-entregara-el-laboratorio-de-robotica-en-colegio-de-ciudad-bolivar-distrito-y-gobierno-acordaron-fecha</t>
+          <t>https://www.semana.com/mejor-colombia/elecciones/articulo/la-gente-podra-salir-a-votar-libre-y-en-paz-presidente-del-cne-da-parte-de-tranquilidad-para-las-elecciones-del-domingo/202600/</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="6" t="inlineStr">
         <is>
-          <t>28/05/2026 04:45 p. m.</t>
+          <t>30/05/2026 04:01 a. m.</t>
         </is>
       </c>
       <c r="B263" s="6" t="inlineStr">
@@ -7544,24 +7536,24 @@
       </c>
       <c r="C263" s="6" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D263" s="7" t="inlineStr">
         <is>
-          <t>'Absténgase de difundir propaganda electoral': Consejo de Estado al presidente Gustavo Petro</t>
+          <t>Los días difíciles de Paloma Valencia: con un cambio de estrategia, que la llevó a atacar a Abelardo de la Espriella, así llega a las elecciones la candidata del Centro Democrático</t>
         </is>
       </c>
       <c r="E263" s="8" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/poder/articulo/2026/5/abstengase-de-difundir-propaganda-electoral-consejo-de-estado-al-presidente-gustavo-petro</t>
+          <t>https://www.semana.com/politica/articulo/los-dias-dificiles-de-paloma-valencia-con-un-cambio-de-estrategia-que-la-llevo-a-atacar-a-abelardo-de-la-espriella-asi-llega-a-las-elecciones-la-candidata-del-centro-democratico/202608/</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>28/05/2026 04:00 p. m.</t>
+          <t>30/05/2026 04:01 a. m.</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
@@ -7571,24 +7563,24 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D264" s="4" t="inlineStr">
         <is>
-          <t>Estados Unidos e Irán llegan a un acuerdo de prorrogar la tregua mientras crece la tensión militar en Medio Oriente</t>
+          <t>Los contrastes de Aida Quilcué y José Manuel Restrepo: estos son los perfiles de los candidatos a la Vicepresidencia más opcionados</t>
         </is>
       </c>
       <c r="E264" s="5" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/internacional/articulo/2026/5/estados-unidos-e-iran-llegan-a-un-acuerdo-de-prorrogar-la-tregua-mientras-crece-la-tension-militar-en-medio-oriente</t>
+          <t>https://www.semana.com/politica/articulo/los-contrastes-de-aida-quilcue-y-jose-manuel-restrepo-estos-son-los-perfiles-de-los-candidatos-a-la-vicepresidencia-mas-opcionados/202625/</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="6" t="inlineStr">
         <is>
-          <t>28/05/2026 04:00 p. m.</t>
+          <t>30/05/2026 03:01 a. m.</t>
         </is>
       </c>
       <c r="B265" s="6" t="inlineStr">
@@ -7598,24 +7590,24 @@
       </c>
       <c r="C265" s="6" t="inlineStr">
         <is>
-          <t>Cambio Colombia</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D265" s="7" t="inlineStr">
         <is>
-          <t>Ojo con las falsas boletas para el partido de despedida de la Selección Colombia: así operan los estafadores</t>
+          <t>La última elección de Sergio Fajardo: el profesor busca la Presidencia reivindicando una forma diferente de hacer política</t>
         </is>
       </c>
       <c r="E265" s="8" t="inlineStr">
         <is>
-          <t>https://cambiocolombia.com/pais/articulo/2026/5/ojo-con-las-falsas-boletas-para-el-partido-de-despedida-de-la-seleccion-colombia-asi-operan-los-estafadores</t>
+          <t>https://www.semana.com/politica/articulo/la-ultima-eleccion-de-sergio-fajardo-el-profesor-busca-la-presidencia-reivindicando-una-forma-diferente-de-hacer-politica/202654/</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 07:43 p. m.</t>
+          <t>30/05/2026 03:01 a. m.</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -7625,24 +7617,24 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D266" s="4" t="inlineStr">
         <is>
-          <t>Duerma informado con las claves de este 29 de mayo de 2026</t>
+          <t>Abelardo de la Espriella e Iván Cepeda buscan ganar la Presidencia, en primera vuelta, este domingo 31 de mayo: ¿esto se puede resolver ya?</t>
         </is>
       </c>
       <c r="E266" s="5" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/duerma-informado-con-las-claves-de-este-29-de-mayo-de-2026/</t>
+          <t>https://www.semana.com/politica/articulo/abelardo-de-la-espriella-e-ivan-cepeda-buscan-ganar-la-presidencia-en-primera-vuelta-este-domingo-31-de-mayo-esto-se-puede-resolver-ya/202655/</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 07:40 p. m.</t>
+          <t>30/05/2026 02:01 a. m.</t>
         </is>
       </c>
       <c r="B267" s="6" t="inlineStr">
@@ -7652,24 +7644,24 @@
       </c>
       <c r="C267" s="6" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D267" s="7" t="inlineStr">
         <is>
-          <t>Noboa habla con Abelardo y anuncia que quitará aranceles el 1 de junio</t>
+          <t>Esta es la lista de urgencias económicas que recibirá el nuevo Gobierno. Diagnóstico de 13 gremios claves</t>
         </is>
       </c>
       <c r="E267" s="8" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/noboa-habla-con-abelardo-y-anuncia-que-quitara-aranceles-el-1-de-junio/</t>
+          <t>https://www.semana.com/economia/empresas/articulo/esta-es-la-lista-de-urgencias-economicas-que-recibira-el-nuevo-gobierno-diagnostico-de-13-gremios-claves/202652/</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 06:48 p. m.</t>
+          <t>30/05/2026 01:01 a. m.</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
@@ -7679,24 +7671,24 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr">
         <is>
-          <t>Dane: Desempleo en Colombia se mantuvo en 8,8% en abril de 2026</t>
+          <t>“Mi papá estaría orgulloso”, la historia de los 70 años de Pajares Salinas</t>
         </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/dane-desempleo-en-colombia-se-mantuvo-en-88-en-abril-de-2026/</t>
+          <t>https://www.semana.com/cultura/articulo/mi-papa-estaria-orgulloso-la-historia-de-los-70-anos-de-pajares-salinas/202601/</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 05:57 p. m.</t>
+          <t>30/05/2026 01:01 a. m.</t>
         </is>
       </c>
       <c r="B269" s="6" t="inlineStr">
@@ -7706,26 +7698,22 @@
       </c>
       <c r="C269" s="6" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D269" s="7" t="inlineStr">
         <is>
-          <t>ELN liberó a Iván Alfredo Guzmán, hijo del exalcalde de Tame, Arauca</t>
+          <t>El sistema de salud llega enfermo al próximo cuatrienio. ¿Aún tiene remedio?</t>
         </is>
       </c>
       <c r="E269" s="8" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/eln-libero-a-ivan-alfredo-guzman-hijo-del-exalcalde-de-tame-arauca/</t>
+          <t>https://www.semana.com/nacion/articulo/el-sistema-de-salud-llega-enfermo-al-proximo-cuatrienio-aun-tiene-remedio/202650/</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="3" t="inlineStr">
-        <is>
-          <t>29/05/2026 05:19 p. m.</t>
-        </is>
-      </c>
+      <c r="A270" s="3" t="inlineStr"/>
       <c r="B270" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7733,26 +7721,22 @@
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D270" s="4" t="inlineStr">
         <is>
-          <t>Petro se reunirá con Zohran Mamdani, el alcalde de Nueva York</t>
+          <t>Mercados votan antes que las urnas: dólar, deuda y acciones en alerta</t>
         </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/petro-se-reunira-con-zohran-mamdani-el-alcalde-de-nueva-york/</t>
+          <t>https://www.semana.com/economia/inversionistas/articulo/mercados-votan-antes-que-las-urnas-dolar-deuda-y-acciones-en-alerta/202600/</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="6" t="inlineStr">
-        <is>
-          <t>29/05/2026 04:26 p. m.</t>
-        </is>
-      </c>
+      <c r="A271" s="6" t="inlineStr"/>
       <c r="B271" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7760,26 +7744,22 @@
       </c>
       <c r="C271" s="6" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D271" s="7" t="inlineStr">
         <is>
-          <t>Recuperados 48 cuerpos tras combates entre Mordisco y Calarcá en Guaviare</t>
+          <t>Julia Loktev habla con Arcadia sobre documentar en tiempo real la tiranía que apagó la prensa libre</t>
         </is>
       </c>
       <c r="E271" s="8" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/recuperados-48-cuerpos-tras-combates-entre-mordisco-y-calarca-en-guaviare/</t>
+          <t>https://www.semana.com/cultura/articulo/julia-loktev-habla-con-arcadia-sobre-documentar-la-tirania-y-como-apago-la-prensa-libre-en-tiempo-real/202600/</t>
         </is>
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="3" t="inlineStr">
-        <is>
-          <t>29/05/2026 03:36 p. m.</t>
-        </is>
-      </c>
+      <c r="A272" s="3" t="inlineStr"/>
       <c r="B272" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7787,26 +7767,22 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D272" s="4" t="inlineStr">
         <is>
-          <t>Polymarket paga publicaciones a favor de Abelardo y políticos de derecha</t>
+          <t>Balón de letras: diez libros sobre balompié a menos de dos semanas de la cita mundialista</t>
         </is>
       </c>
       <c r="E272" s="5" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/polymarket-paga-publicaciones-a-favor-de-abelardo-y-politicos-de-derecha/</t>
+          <t>https://www.semana.com/cultura/articulo/balon-de-letras-diez-libros-sobre-balompie-a-menos-de-dos-semanas-de-la-cita-mundialista/202600/</t>
         </is>
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="6" t="inlineStr">
-        <is>
-          <t>29/05/2026 02:23 p. m.</t>
-        </is>
-      </c>
+      <c r="A273" s="6" t="inlineStr"/>
       <c r="B273" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7814,26 +7790,22 @@
       </c>
       <c r="C273" s="6" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D273" s="7" t="inlineStr">
         <is>
-          <t>Tras salida de El Tiempo, Jineth Bedoya denuncia a Gabriel Meluk por acoso</t>
+          <t>‘Marginalia’, de Juan Andrés Arango: Los márgenes como destino</t>
         </is>
       </c>
       <c r="E273" s="8" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/tras-salida-de-el-tiempo-jineth-bedoya-denuncia-a-gabriel-meluk-por-acoso/</t>
+          <t>https://www.semana.com/cultura/libros/articulo/marginalia-de-juan-andres-arango-los-margenes-como-destino/202600/</t>
         </is>
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="3" t="inlineStr">
-        <is>
-          <t>29/05/2026 01:50 p. m.</t>
-        </is>
-      </c>
+      <c r="A274" s="3" t="inlineStr"/>
       <c r="B274" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7841,26 +7813,22 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D274" s="4" t="inlineStr">
         <is>
-          <t>Diario de Campaña: la recta final hacia primera vuelta</t>
+          <t>Vitinha, tras el título de Champions League con el PSG, manda contundente mensaje a Colombia: ojo, Lorenzo</t>
         </is>
       </c>
       <c r="E274" s="5" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/diario-de-campana-asi-esta-la-recta-final-hacia-primera-vuelta/</t>
+          <t>https://www.semana.com/deportes/articulo/vitinha-tras-el-titulo-de-champions-league-con-el-psg-manda-contundente-mensaje-a-colombia-ojo-lorenzo/202631/</t>
         </is>
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="6" t="inlineStr">
-        <is>
-          <t>29/05/2026 01:36 p. m.</t>
-        </is>
-      </c>
+      <c r="A275" s="6" t="inlineStr"/>
       <c r="B275" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7868,26 +7836,22 @@
       </c>
       <c r="C275" s="6" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D275" s="7" t="inlineStr">
         <is>
-          <t>“Nos quitarán las oportunidades de vida”: Petro en el Caribe</t>
+          <t>El récord negativo que Messi tiene en la historia de los Mundiales: ni siquiera él lo puede cambiar</t>
         </is>
       </c>
       <c r="E275" s="8" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/nos-quitaran-las-oportunidades-de-vida-petro-en-el-caribe/</t>
+          <t>https://www.semana.com/deportes/articulo/el-record-negativo-que-messi-tiene-en-la-historia-de-los-mundiales-ni-siquiera-el-lo-puede-cambiar/202600/</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="3" t="inlineStr">
-        <is>
-          <t>29/05/2026 12:24 p. m.</t>
-        </is>
-      </c>
+      <c r="A276" s="3" t="inlineStr"/>
       <c r="B276" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7895,26 +7859,22 @@
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D276" s="4" t="inlineStr">
         <is>
-          <t>Termina inscripción de testigos con el Centro Democrático a la cabeza</t>
+          <t>Néstor Lorenzo responde si hubo o no dos listas de convocados de Colombia al Mundial: dio su versión</t>
         </is>
       </c>
       <c r="E276" s="5" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/termina-inscripcion-de-testigos-con-el-centro-democratico-a-la-cabeza/</t>
+          <t>https://www.semana.com/deportes/articulo/nestor-lorenzo-responde-si-hubo-o-no-dos-listas-de-convocados-de-colombia-al-mundial-dio-su-version/202650/</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="6" t="inlineStr">
-        <is>
-          <t>29/05/2026 11:06 a. m.</t>
-        </is>
-      </c>
+      <c r="A277" s="6" t="inlineStr"/>
       <c r="B277" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7922,26 +7882,22 @@
       </c>
       <c r="C277" s="6" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D277" s="7" t="inlineStr">
         <is>
-          <t>Partidos reiteran a sus bases moverse por Paloma y Oviedo</t>
+          <t>Luis Díaz habló sobre la capitanía de la Selección Colombia en el Mundial 2026: claro mensaje a James Rodríguez</t>
         </is>
       </c>
       <c r="E277" s="8" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/partidos-reiteran-a-sus-bases-moverse-por-paloma-y-oviedo/</t>
+          <t>https://www.semana.com/deportes/articulo/luis-diaz-hablo-sobre-la-capitania-de-la-seleccion-colombia-en-el-mundial-2026-claro-mensaje-a-james-rodriguez/202642/</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="3" t="inlineStr">
-        <is>
-          <t>29/05/2026 10:16 a. m.</t>
-        </is>
-      </c>
+      <c r="A278" s="3" t="inlineStr"/>
       <c r="B278" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7949,26 +7905,22 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D278" s="4" t="inlineStr">
         <is>
-          <t>ABC de la Democracia: aprenda en 90 minutos</t>
+          <t>Picante respuesta de Néstor Lorenzo hacia los duros críticos de la Selección Colombia: habló de frente</t>
         </is>
       </c>
       <c r="E278" s="5" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/abc-de-la-democracia-aprenda-en-90-minutos/</t>
+          <t>https://www.semana.com/deportes/articulo/picante-respuesta-de-nestor-lorenzo-hacia-los-duros-criticos-de-la-seleccion-colombia-hablo-de-frente/202636/</t>
         </is>
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="6" t="inlineStr">
-        <is>
-          <t>29/05/2026 09:48 a. m.</t>
-        </is>
-      </c>
+      <c r="A279" s="6" t="inlineStr"/>
       <c r="B279" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7976,26 +7928,22 @@
       </c>
       <c r="C279" s="6" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D279" s="7" t="inlineStr">
         <is>
-          <t>Pese a orden de Petro, Óscar Muñoz sigue en la embajada de Guyana</t>
+          <t>El compromiso al que llegaron Abelardo de la Espriella y Westcol: “Vas a ver todo lo que muerde el tigre”</t>
         </is>
       </c>
       <c r="E279" s="8" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/pese-a-orden-de-petro-oscar-munoz-sigue-en-la-embajada-de-guyana/</t>
+          <t>https://www.semana.com/politica/articulo/el-compromiso-al-que-llegaron-abelardo-de-la-espriella-y-westcol-vas-a-ver-todo-lo-que-muerde-el-tigre/202627/</t>
         </is>
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="3" t="inlineStr">
-        <is>
-          <t>29/05/2026 08:23 a. m.</t>
-        </is>
-      </c>
+      <c r="A280" s="3" t="inlineStr"/>
       <c r="B280" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -8003,26 +7951,22 @@
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D280" s="4" t="inlineStr">
         <is>
-          <t>Bogotá entra en ley seca desde las seis de la tarde por las presidenciales</t>
+          <t>Bernie Moreno envió mensaje previo a las elecciones presidenciales: “El futuro de Colombia puede ser más brillante que nunca”</t>
         </is>
       </c>
       <c r="E280" s="5" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/bogota-entra-en-ley-seca-desde-las-seis-de-la-tarde-por-las-presidenciales/</t>
+          <t>https://www.semana.com/politica/articulo/bernie-moreno-envio-mensaje-previo-a-las-elecciones-presidenciales-el-futuro-de-colombia-puede-ser-mas-brillante-que-nunca/202641/</t>
         </is>
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="6" t="inlineStr">
-        <is>
-          <t>29/05/2026 07:25 a. m.</t>
-        </is>
-      </c>
+      <c r="A281" s="6" t="inlineStr"/>
       <c r="B281" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -8030,26 +7974,22 @@
       </c>
       <c r="C281" s="6" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D281" s="7" t="inlineStr">
         <is>
-          <t>Desayune informado con las movidas de este 29 de mayo de 2026</t>
+          <t>Abelardo de la Espriella lanza dardo a Petro en entrevista con Westcol: “Es un costeño chimbo”</t>
         </is>
       </c>
       <c r="E281" s="8" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/desayune-informado-con-las-movidas-de-este-29-de-mayo-de-2026/</t>
+          <t>https://www.semana.com/politica/articulo/abelardo-de-la-espriella-lanza-dardo-a-petro-en-entrevista-con-westcol-es-un-costeno-chimbo/202633/</t>
         </is>
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="3" t="inlineStr">
-        <is>
-          <t>28/05/2026 06:57 p. m.</t>
-        </is>
-      </c>
+      <c r="A282" s="3" t="inlineStr"/>
       <c r="B282" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -8057,26 +7997,22 @@
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D282" s="4" t="inlineStr">
         <is>
-          <t>Duerma informado con las claves de este 28 de mayo de 2026</t>
+          <t>Alejandro Char respondió a los señalamientos de Gustavo Petro: “Es triste verlo salir de la Casa de Nariño destilando odio”</t>
         </is>
       </c>
       <c r="E282" s="5" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/duerma-informado-con-las-claves-de-este-28-de-mayo-de-2026/</t>
+          <t>https://www.semana.com/politica/articulo/alejandro-char-respondio-a-los-senalamientos-de-gustavo-petro-es-triste-verlo-salir-de-la-casa-de-narino-destilando-odio/202610/</t>
         </is>
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="6" t="inlineStr">
-        <is>
-          <t>28/05/2026 06:34 p. m.</t>
-        </is>
-      </c>
+      <c r="A283" s="6" t="inlineStr"/>
       <c r="B283" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -8084,26 +8020,22 @@
       </c>
       <c r="C283" s="6" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D283" s="7" t="inlineStr">
         <is>
-          <t>ELN se atribuyó el secuestro de hijo del exalcalde de Tame, Arauca</t>
+          <t>Así encontraron el cuerpo de joven que murió en aguas del embalse El Peñol-Guatapé: “Logramos la recuperación”</t>
         </is>
       </c>
       <c r="E283" s="8" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/eln-se-atribuyo-el-secuestro-de-hijo-del-exalcalde-de-tame-arauca/</t>
+          <t>https://www.semana.com/nacion/medellin/articulo/asi-encontraron-el-cuerpo-de-joven-que-murio-en-aguas-del-embalse-el-penol-guatape-logramos-la-recuperacion/202605/</t>
         </is>
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="3" t="inlineStr">
-        <is>
-          <t>28/05/2026 05:45 p. m.</t>
-        </is>
-      </c>
+      <c r="A284" s="3" t="inlineStr"/>
       <c r="B284" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -8111,24 +8043,24 @@
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>Consejo de Estado ordena a Petro que no difunda propaganda electoral</t>
+          <t>Procurador Gregorio Eljach entregó un parte de tranquilidad para las elecciones e invitó a los colombianos a votar temprano</t>
         </is>
       </c>
       <c r="E284" s="5" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/consejo-de-estado-ordena-a-petro-que-no-difunda-propaganda-electoral/</t>
+          <t>https://www.semana.com/nacion/articulo/procurador-gregorio-eljach-entrego-un-parte-de-tranquilidad-para-las-elecciones-e-invito-a-los-colombianos-a-votar-temprano/202652/</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="6" t="inlineStr">
         <is>
-          <t>28/05/2026 04:42 p. m.</t>
+          <t>30/05/2026 07:50 p. m.</t>
         </is>
       </c>
       <c r="B285" s="6" t="inlineStr">
@@ -8138,24 +8070,24 @@
       </c>
       <c r="C285" s="6" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D285" s="7" t="inlineStr">
         <is>
-          <t>Uribe cuestiona que Cepeda quiera a Velásquez en su gabinete</t>
+          <t>Resultado Culona Noche: número ganador de hoy sábado 30 de mayo de 2026</t>
         </is>
       </c>
       <c r="E285" s="8" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/uribe-cuestiona-que-cepeda-quiera-a-velasquez-en-su-gabinete/</t>
+          <t>https://www.vanguardia.com/loterias/2026/05/30/resultado-culona-noche-numero-ganador-de-hoy-sabado-30-de-mayo-de-2026/</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 11:07 a. m.</t>
+          <t>30/05/2026 07:50 p. m.</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
@@ -8165,24 +8097,24 @@
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>Myke Towers confirma concierto en Bogotá con su gira “Trap Kings”</t>
+          <t>Loterias</t>
         </is>
       </c>
       <c r="E286" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/myke-towers-confirma-concierto-en-bogota-con-su-gira-trap-kings/</t>
+          <t>https://www.vanguardia.com/loterias/</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:51 a. m.</t>
+          <t>30/05/2026 07:22 p. m.</t>
         </is>
       </c>
       <c r="B287" s="6" t="inlineStr">
@@ -8192,24 +8124,24 @@
       </c>
       <c r="C287" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D287" s="7" t="inlineStr">
         <is>
-          <t>Acoso callejero Colombia: el 89% de las mujeres afirma haberlo sufrido</t>
+          <t>OEA hará seguimiento a denuncias contra Petro por participación en política</t>
         </is>
       </c>
       <c r="E287" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/acoso-callejero-colombia-mujeres/</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/30/oea-hara-seguimiento-a-denuncias-contra-petro-por-participacion-en-politica/</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:44 a. m.</t>
+          <t>30/05/2026 07:22 p. m.</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
@@ -8219,24 +8151,24 @@
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
         <is>
-          <t>Outdoor femenino Colombia: la tendencia que une aventura, naturaleza y comunidad</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E288" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/outdoor-femenino-colombia/</t>
+          <t>https://www.vanguardia.com/colombia/</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:35 a. m.</t>
+          <t>30/05/2026 07:01 p. m.</t>
         </is>
       </c>
       <c r="B289" s="6" t="inlineStr">
@@ -8246,24 +8178,24 @@
       </c>
       <c r="C289" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D289" s="7" t="inlineStr">
         <is>
-          <t>Bibliotecas para inspirar Cali: nueva apuesta por la lectura y los proyectos de vida</t>
+          <t>“Nadie vende su voto”: el mensaje de Petro a horas de las elecciones presidenciales</t>
         </is>
       </c>
       <c r="E289" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/bibliotecas-para-inspirar-cali/</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/30/nadie-vende-su-voto-el-mensaje-de-petro-a-horas-de-las-elecciones-presidenciales/</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:32 a. m.</t>
+          <t>30/05/2026 06:06 p. m.</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -8273,24 +8205,24 @@
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>Detección temprana cáncer de mama Colombia: la importancia de las redes de apoyo</t>
+          <t>Contratista de Ecopetrol resultó herido tras ataque a bala en Tibú, Norte de Santander</t>
         </is>
       </c>
       <c r="E290" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/deteccion-temprana-cancer-de-mama-colombia/</t>
+          <t>https://www.vanguardia.com/judicial/2026/05/30/contratista-de-ecopetrol-resulto-herido-tras-ataque-a-bala-en-tibu-norte-de-santander/</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:27 a. m.</t>
+          <t>30/05/2026 06:06 p. m.</t>
         </is>
       </c>
       <c r="B291" s="6" t="inlineStr">
@@ -8300,24 +8232,24 @@
       </c>
       <c r="C291" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D291" s="7" t="inlineStr">
         <is>
-          <t>Cuidado del cabello y la piel en vacaciones: errores que debes evitar</t>
+          <t>Judicial</t>
         </is>
       </c>
       <c r="E291" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/cuidado-del-cabello-y-la-piel-en-vacaciones/</t>
+          <t>https://www.vanguardia.com/judicial/</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:18 a. m.</t>
+          <t>30/05/2026 04:55 p. m.</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
@@ -8327,24 +8259,24 @@
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>Bebé de 6 meses El Espinal: avanzan investigaciones tras su fallecimiento</t>
+          <t>Candidato Santiago Botero respondió luego de la orden de desalojo en su contra en caso de violencia intrafamiliar</t>
         </is>
       </c>
       <c r="E292" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/bebe-de-6-meses-el-espinal/</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/30/candidato-santiago-botero-respondio-luego-de-la-orden-de-desalojo-en-su-contra-en-caso-de-violencia-intrafamiliar/</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 09:10 a. m.</t>
+          <t>30/05/2026 04:19 p. m.</t>
         </is>
       </c>
       <c r="B293" s="6" t="inlineStr">
@@ -8354,24 +8286,24 @@
       </c>
       <c r="C293" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D293" s="7" t="inlineStr">
         <is>
-          <t>Fiesta en El Campín: Morat cantará en la despedida de la Selección Colombia rumbo al Mundial 2026</t>
+          <t>Denuncian que equipos básicos de Minsalud le estarían haciendo campaña a Cepeda en La Guajira</t>
         </is>
       </c>
       <c r="E293" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/fiesta-en-el-campin-morat-cantara-en-la-despedida-de-la-seleccion-colombia-rumbo-al-mundial-2026/</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/30/denuncian-que-equipos-basicos-de-minsalud-le-estarian-haciendo-campana-a-cepeda-en-la-guajira/</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 09:03 a. m.</t>
+          <t>30/05/2026 04:03 p. m.</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
@@ -8381,24 +8313,24 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>Orgullo colombiano: Kapo es coronado como ‘Compositor del Año’ en los SESAC Latina Music Awards 2026</t>
+          <t>Activan Puesto de Mando Unificado para vigilar las elecciones presidenciales</t>
         </is>
       </c>
       <c r="E294" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/orgullo-colombiano-kapo-es-coronado-como-compositor-del-ano-en-los-sesac-latina-music-awards-2026/</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/30/activan-puesto-de-mando-unificado-para-vigilar-las-elecciones-presidenciales/</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 08:56 a. m.</t>
+          <t>30/05/2026 02:54 p. m.</t>
         </is>
       </c>
       <c r="B295" s="6" t="inlineStr">
@@ -8408,24 +8340,24 @@
       </c>
       <c r="C295" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D295" s="7" t="inlineStr">
         <is>
-          <t>De Medellín para el mundo: elkno enciende la escena urbana con su dancehall “Ritmo”</t>
+          <t>“Ahóguenlo” revelan video que muestra los últimos minutos de Alexander Avendaño</t>
         </is>
       </c>
       <c r="E295" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/de-medellin-para-el-mundo-elkno-enciende-la-escena-urbana-con-su-dancehall-ritmo/</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/30/ahoguenlo-revelan-video-que-muestra-los-ultimos-minutos-de-alexander-avendano/</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 08:53 a. m.</t>
+          <t>30/05/2026 02:19 p. m.</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
@@ -8435,24 +8367,24 @@
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>Cine colombiano: ‘VOLAR’ llega a las salas con un retrato íntimo de la soledad en Bogotá</t>
+          <t>Mindefensa alerta que varios cadáveres recuperados tras combates en Guaviare tenían explosivos</t>
         </is>
       </c>
       <c r="E296" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/cine-colombiano-volar-llega-a-las-salas-con-un-retrato-intimo-de-la-soledad-en-bogota/</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/30/mindefensa-alerta-que-varios-cadaveres-recuperados-tras-combates-en-guaviare-tenian-explosivos/</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 08:49 a. m.</t>
+          <t>30/05/2026 01:27 p. m.</t>
         </is>
       </c>
       <c r="B297" s="6" t="inlineStr">
@@ -8462,24 +8394,24 @@
       </c>
       <c r="C297" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D297" s="7" t="inlineStr">
         <is>
-          <t>Desde República Dominicana para el despecho: Amneliz debuta en la música popular con “El Desquite”</t>
+          <t>Cárcel para médico de Bogotá por presunto abuso de dos niñas en las consultas</t>
         </is>
       </c>
       <c r="E297" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/desde-republica-dominicana-para-el-despecho-amneliz-debuta-en-la-musica-popular-con-el-desquite/</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/30/carcel-para-medico-de-bogota-por-presunto-abuso-de-dos-ninas-en-las-consultas/</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 08:45 a. m.</t>
+          <t>30/05/2026 01:23 p. m.</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
@@ -8489,24 +8421,24 @@
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D298" s="4" t="inlineStr">
         <is>
-          <t>Giro en el caso de Mía Cataleya: Revelan crudos detalles de su ingreso al hospital y una captura en El Espinal</t>
+          <t>Gobierno negocia con Calarcá desde 2023 pero no tiene forma de contactarlo</t>
         </is>
       </c>
       <c r="E298" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/giro-en-el-caso-de-mia-cataleya-revelan-crudos-detalles-de-su-ingreso-al-hospital-y-una-captura-en-el-espinal/</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/30/gobierno-negocia-con-calarca-desde-2023-pero-no-tiene-forma-de-contactarlo/</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 08:24 a. m.</t>
+          <t>30/05/2026 10:43 a. m.</t>
         </is>
       </c>
       <c r="B299" s="6" t="inlineStr">
@@ -8516,24 +8448,24 @@
       </c>
       <c r="C299" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D299" s="7" t="inlineStr">
         <is>
-          <t>«Vi una pierna afuera»: Los crudos testimonios del hallazgo del profesor Kevin Santiago Ángel en Kennedy</t>
+          <t>Cancillería desmiente a Noboa y afirma que CAN obligó retiro de aranceles a Colombia</t>
         </is>
       </c>
       <c r="E299" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/vi-una-pierna-afuera-los-crudos-testimonios-del-hallazgo-del-profesor-kevin-santiago-angel-en-kennedy/</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/30/cancilleria-desmiente-a-noboa-y-afirma-que-can-obligo-retiro-de-aranceles-a-colombia/</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 08:12 a. m.</t>
+          <t>30/05/2026 05:26 p. m.</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
@@ -8543,24 +8475,24 @@
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D300" s="4" t="inlineStr">
         <is>
-          <t>Giro en el caso de Ana María Meza: Fiscalía confirma que se investiga como presunto feminicidio</t>
+          <t>Cepeda llega a primera vuelta sin revelar sus asesores económicos</t>
         </is>
       </c>
       <c r="E300" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/giro-en-el-caso-de-ana-maria-meza-fiscalia-confirma-que-se-investiga-como-presunto-feminicidio/</t>
+          <t>https://www.lasillavacia.com/en-vivo/cepeda-llega-a-primera-vuelta-sin-revelar-sus-asesores-economicos/</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 08:08 a. m.</t>
+          <t>30/05/2026 01:54 p. m.</t>
         </is>
       </c>
       <c r="B301" s="6" t="inlineStr">
@@ -8570,24 +8502,24 @@
       </c>
       <c r="C301" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D301" s="7" t="inlineStr">
         <is>
-          <t>El silencio forzado de Afganistán: El año en que las mujeres perdieron el derecho a existir en público</t>
+          <t>El último acto de campaña de Paloma será una entrevista con Mr Stiven TC</t>
         </is>
       </c>
       <c r="E301" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/el-silencio-forzado-de-afganistan-el-ano-en-que-las-mujeres-perdieron-el-derecho-a-existir-en-publico/</t>
+          <t>https://www.lasillavacia.com/en-vivo/el-ultimo-acto-de-campana-de-paloma-sera-una-entrevista-con-mr-stiven-tc/</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
         <is>
-          <t>28/05/2026 11:24 a. m.</t>
+          <t>30/05/2026 01:31 p. m.</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
@@ -8597,24 +8529,24 @@
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D302" s="4" t="inlineStr">
         <is>
-          <t>Jóvenes elecciones Colombia 2026: TikTok e IA cambian las campañas</t>
+          <t>Aumentó la violencia por conflicto armado antes de elecciones: Cerac</t>
         </is>
       </c>
       <c r="E302" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/jovenes-elecciones-colombia-2026/</t>
+          <t>https://www.lasillavacia.com/en-vivo/aumento-la-violencia-por-conflicto-armado-antes-de-elecciones-cerac/</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="6" t="inlineStr">
         <is>
-          <t>28/05/2026 11:18 a. m.</t>
+          <t>30/05/2026 11:21 a. m.</t>
         </is>
       </c>
       <c r="B303" s="6" t="inlineStr">
@@ -8624,24 +8556,24 @@
       </c>
       <c r="C303" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D303" s="7" t="inlineStr">
         <is>
-          <t>Seguridad en vehículos de trabajo: la tecnología redefine el transporte de carga</t>
+          <t>La Cancillería anuncia que derogará medidas económicas contra Ecuador</t>
         </is>
       </c>
       <c r="E303" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/seguridad-en-vehiculos-de-trabajo/</t>
+          <t>https://www.lasillavacia.com/en-vivo/la-cancilleria-anuncia-que-derogara-medidas-economicas-contra-ecuador/</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
         <is>
-          <t>28/05/2026 10:45 a. m.</t>
+          <t>30/05/2026 09:52 a. m.</t>
         </is>
       </c>
       <c r="B304" s="3" t="inlineStr">
@@ -8651,24 +8583,24 @@
       </c>
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D304" s="4" t="inlineStr">
         <is>
-          <t>De Mar y Río lanza “Cantaré”, un homenaje al Pacífico colombiano</t>
+          <t>“No se trata de si yo tengo un jaguar y otro tiene un tigre”: Petro</t>
         </is>
       </c>
       <c r="E304" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/de-mar-y-rio-lanza-cantare-un-homenaje-al-pacifico-colombiano/</t>
+          <t>https://www.lasillavacia.com/en-vivo/no-se-trata-de-si-yo-tengo-un-jaguar-y-otro-tiene-un-tigre-petro/</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="6" t="inlineStr">
         <is>
-          <t>28/05/2026 10:04 a. m.</t>
+          <t>30/05/2026 09:00 a. m.</t>
         </is>
       </c>
       <c r="B305" s="6" t="inlineStr">
@@ -8678,24 +8610,24 @@
       </c>
       <c r="C305" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D305" s="7" t="inlineStr">
         <is>
-          <t>Helipuertos en Bogotá: la nueva tendencia para vivir experiencias exclusivas</t>
+          <t>Caquetá vota bajo presión armada y cansado de la extorsión y otras noticias</t>
         </is>
       </c>
       <c r="E305" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/helipuertos-en-bogota-experiencias/</t>
+          <t>https://www.lasillavacia.com/en-vivo/caqueta-vota-bajo-presion-armada-y-cansado-de-la-extorsion-y-otras-noticias/</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="3" t="inlineStr">
         <is>
-          <t>28/05/2026 10:00 a. m.</t>
+          <t>29/05/2026 07:43 p. m.</t>
         </is>
       </c>
       <c r="B306" s="3" t="inlineStr">
@@ -8705,24 +8637,24 @@
       </c>
       <c r="C306" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D306" s="4" t="inlineStr">
         <is>
-          <t>Orgullo vallenato: Jorge Celedón hace historia y conquista el #1 de la radio en Centroamérica</t>
+          <t>Duerma informado con las claves de este 29 de mayo de 2026</t>
         </is>
       </c>
       <c r="E306" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/orgullo-vallenato-jorge-celedon-hace-historia-y-conquista-el-1-de-la-radio-en-centroamerica/</t>
+          <t>https://www.lasillavacia.com/en-vivo/duerma-informado-con-las-claves-de-este-29-de-mayo-de-2026/</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="6" t="inlineStr">
         <is>
-          <t>28/05/2026 09:58 a. m.</t>
+          <t>29/05/2026 07:40 p. m.</t>
         </is>
       </c>
       <c r="B307" s="6" t="inlineStr">
@@ -8732,24 +8664,24 @@
       </c>
       <c r="C307" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D307" s="7" t="inlineStr">
         <is>
-          <t>Alea Animal Distinta: el himno de autenticidad y empoderamiento femenino</t>
+          <t>Noboa habla con Abelardo y anuncia que quitará aranceles el 1 de junio</t>
         </is>
       </c>
       <c r="E307" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/alea-animal-distinta-video/</t>
+          <t>https://www.lasillavacia.com/en-vivo/noboa-habla-con-abelardo-y-anuncia-que-quitara-aranceles-el-1-de-junio/</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
         <is>
-          <t>28/05/2026 09:56 a. m.</t>
+          <t>29/05/2026 06:48 p. m.</t>
         </is>
       </c>
       <c r="B308" s="3" t="inlineStr">
@@ -8759,24 +8691,24 @@
       </c>
       <c r="C308" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D308" s="4" t="inlineStr">
         <is>
-          <t>El regreso a la raíz: Karen Lizarazo estrena su esperado álbum “El Tiempo Perfecto”</t>
+          <t>Dane: Desempleo en Colombia se mantuvo en 8,8% en abril de 2026</t>
         </is>
       </c>
       <c r="E308" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/el-regreso-a-la-raiz-karen-lizarazo-estrena-su-esperado-album-el-tiempo-perfecto/</t>
+          <t>https://www.lasillavacia.com/en-vivo/dane-desempleo-en-colombia-se-mantuvo-en-88-en-abril-de-2026/</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="6" t="inlineStr">
         <is>
-          <t>28/05/2026 09:54 a. m.</t>
+          <t>29/05/2026 05:57 p. m.</t>
         </is>
       </c>
       <c r="B309" s="6" t="inlineStr">
@@ -8786,24 +8718,24 @@
       </c>
       <c r="C309" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D309" s="7" t="inlineStr">
         <is>
-          <t>Maiguai Te Espero: así suena la melancolía tropical del dúo colombiano</t>
+          <t>ELN liberó a Iván Alfredo Guzmán, hijo del exalcalde de Tame, Arauca</t>
         </is>
       </c>
       <c r="E309" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/maiguai-te-espero-video/</t>
+          <t>https://www.lasillavacia.com/en-vivo/eln-libero-a-ivan-alfredo-guzman-hijo-del-exalcalde-de-tame-arauca/</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
         <is>
-          <t>28/05/2026 09:50 a. m.</t>
+          <t>29/05/2026 05:19 p. m.</t>
         </is>
       </c>
       <c r="B310" s="3" t="inlineStr">
@@ -8813,24 +8745,24 @@
       </c>
       <c r="C310" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D310" s="4" t="inlineStr">
         <is>
-          <t>Ari Villalba Aquellos ojos verdes: así es el homenaje al bolero y la memoria</t>
+          <t>Petro se reunirá con Zohran Mamdani, el alcalde de Nueva York</t>
         </is>
       </c>
       <c r="E310" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/ari-villalba-aquellos-ojos-verdes/</t>
+          <t>https://www.lasillavacia.com/en-vivo/petro-se-reunira-con-zohran-mamdani-el-alcalde-de-nueva-york/</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="6" t="inlineStr">
         <is>
-          <t>28/05/2026 09:42 a. m.</t>
+          <t>29/05/2026 04:26 p. m.</t>
         </is>
       </c>
       <c r="B311" s="6" t="inlineStr">
@@ -8840,24 +8772,24 @@
       </c>
       <c r="C311" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D311" s="7" t="inlineStr">
         <is>
-          <t>Electrodomésticos eficientes ahorro energía: cómo reducir el gasto mensual en casa</t>
+          <t>Recuperados 48 cuerpos tras combates entre Mordisco y Calarcá en Guaviare</t>
         </is>
       </c>
       <c r="E311" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/electrodomesticos-eficientes-ahorro-energia/</t>
+          <t>https://www.lasillavacia.com/en-vivo/recuperados-48-cuerpos-tras-combates-entre-mordisco-y-calarca-en-guaviare/</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="3" t="inlineStr">
         <is>
-          <t>28/05/2026 09:39 a. m.</t>
+          <t>29/05/2026 03:36 p. m.</t>
         </is>
       </c>
       <c r="B312" s="3" t="inlineStr">
@@ -8867,24 +8799,24 @@
       </c>
       <c r="C312" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D312" s="4" t="inlineStr">
         <is>
-          <t>El regreso de un mito tropical: Tato Marenco revive “Boquita Salá” junto a la orquesta de Pacho Galán</t>
+          <t>Polymarket paga publicaciones a favor de Abelardo y políticos de derecha</t>
         </is>
       </c>
       <c r="E312" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/el-regreso-de-un-mito-tropical-tato-marenco-revive-boquita-sala-junto-a-la-orquesta-de-pacho-galan/</t>
+          <t>https://www.lasillavacia.com/en-vivo/polymarket-paga-publicaciones-a-favor-de-abelardo-y-politicos-de-derecha/</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="6" t="inlineStr">
         <is>
-          <t>28/05/2026 09:34 a. m.</t>
+          <t>29/05/2026 02:23 p. m.</t>
         </is>
       </c>
       <c r="B313" s="6" t="inlineStr">
@@ -8894,24 +8826,24 @@
       </c>
       <c r="C313" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D313" s="7" t="inlineStr">
         <is>
-          <t>Monsieur Periné llega a Netflix: “Aguaráchate” musicaliza la serie documental de James Rodríguez</t>
+          <t>Tras salida de El Tiempo, Jineth Bedoya denuncia a Gabriel Meluk por acoso</t>
         </is>
       </c>
       <c r="E313" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/monsieur-perine-llega-a-netflix-aguarachate-musicaliza-la-serie-documental-de-james-rodriguez/</t>
+          <t>https://www.lasillavacia.com/en-vivo/tras-salida-de-el-tiempo-jineth-bedoya-denuncia-a-gabriel-meluk-por-acoso/</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="3" t="inlineStr">
         <is>
-          <t>28/05/2026 09:28 a. m.</t>
+          <t>29/05/2026 01:50 p. m.</t>
         </is>
       </c>
       <c r="B314" s="3" t="inlineStr">
@@ -8921,24 +8853,24 @@
       </c>
       <c r="C314" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D314" s="4" t="inlineStr">
         <is>
-          <t>Revolución de «perrihijos» en Bogotá: El 67% de los hogares ya tiene una mascota</t>
+          <t>Diario de Campaña: la recta final hacia primera vuelta</t>
         </is>
       </c>
       <c r="E314" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/revolucion-de-perrihijos-en-bogota-el-67-de-los-hogares-ya-tiene-una-mascota/</t>
+          <t>https://www.lasillavacia.com/en-vivo/diario-de-campana-asi-esta-la-recta-final-hacia-primera-vuelta/</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="6" t="inlineStr">
         <is>
-          <t>28/05/2026 09:24 a. m.</t>
+          <t>29/05/2026 01:36 p. m.</t>
         </is>
       </c>
       <c r="B315" s="6" t="inlineStr">
@@ -8948,1075 +8880,130 @@
       </c>
       <c r="C315" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D315" s="7" t="inlineStr">
         <is>
-          <t>La IA llega al P&amp;L: Bogotá será sede del Spark AI Summit 2026</t>
+          <t>“Nos quitarán las oportunidades de vida”: Petro en el Caribe</t>
         </is>
       </c>
       <c r="E315" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/la-ia-llega-al-pl-bogota-sera-sede-del-spark-ai-summit-2026/</t>
+          <t>https://www.lasillavacia.com/en-vivo/nos-quitaran-las-oportunidades-de-vida-petro-en-el-caribe/</t>
         </is>
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="9" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B316" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C316" s="9" t="inlineStr">
-        <is>
-          <t>Ministerio de Minas y Energía</t>
-        </is>
-      </c>
-      <c r="D316" s="10" t="inlineStr">
-        <is>
-          <t>Gobierno Nacional une vivienda y energía limpia para transformar hogares populares con Colombia Solar</t>
-        </is>
-      </c>
-      <c r="E316" s="11" t="inlineStr">
-        <is>
-          <t>https://www.minenergia.gov.co/es/sala-de-prensa/noticias-index/gobierno-nacional-une-vivienda-y-energia-limpia-para-transformar-hogares-populares-con-colombia-solar/</t>
+      <c r="A316" s="3" t="inlineStr">
+        <is>
+          <t>29/05/2026 12:24 p. m.</t>
+        </is>
+      </c>
+      <c r="B316" s="3" t="inlineStr">
+        <is>
+          <t>Medio de Comunicación</t>
+        </is>
+      </c>
+      <c r="C316" s="3" t="inlineStr">
+        <is>
+          <t>La Silla Vacía</t>
+        </is>
+      </c>
+      <c r="D316" s="4" t="inlineStr">
+        <is>
+          <t>Termina inscripción de testigos con el Centro Democrático a la cabeza</t>
+        </is>
+      </c>
+      <c r="E316" s="5" t="inlineStr">
+        <is>
+          <t>https://www.lasillavacia.com/en-vivo/termina-inscripcion-de-testigos-con-el-centro-democratico-a-la-cabeza/</t>
         </is>
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="12" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B317" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C317" s="12" t="inlineStr">
-        <is>
-          <t>Ministerio de Igualdad y Equidad</t>
-        </is>
-      </c>
-      <c r="D317" s="13" t="inlineStr">
-        <is>
-          <t>Juventudes que Mueven el Territorio: Más de 1500 jóvenes en Colombia fortalecen sus habilidades para continuar liderando la transformación</t>
-        </is>
-      </c>
-      <c r="E317" s="14" t="inlineStr">
-        <is>
-          <t>https://www.minigualdadyequidad.gov.co/-/juventudes-mueven-territorio?redirect=%2Fnoticias</t>
+      <c r="A317" s="6" t="inlineStr">
+        <is>
+          <t>29/05/2026 11:06 a. m.</t>
+        </is>
+      </c>
+      <c r="B317" s="6" t="inlineStr">
+        <is>
+          <t>Medio de Comunicación</t>
+        </is>
+      </c>
+      <c r="C317" s="6" t="inlineStr">
+        <is>
+          <t>La Silla Vacía</t>
+        </is>
+      </c>
+      <c r="D317" s="7" t="inlineStr">
+        <is>
+          <t>Partidos reiteran a sus bases moverse por Paloma y Oviedo</t>
+        </is>
+      </c>
+      <c r="E317" s="8" t="inlineStr">
+        <is>
+          <t>https://www.lasillavacia.com/en-vivo/partidos-reiteran-a-sus-bases-moverse-por-paloma-y-oviedo/</t>
         </is>
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="9" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B318" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C318" s="9" t="inlineStr">
-        <is>
-          <t>Ministerio de Igualdad y Equidad</t>
-        </is>
-      </c>
-      <c r="D318" s="10" t="inlineStr">
-        <is>
-          <t>Por primera vez, el Consejo Nacional de Personas Mayores sesiona en territorio</t>
-        </is>
-      </c>
-      <c r="E318" s="11" t="inlineStr">
-        <is>
-          <t>https://www.minigualdadyequidad.gov.co/-/por-primera-vez-el-consejo-nacional-de-personas-mayores-sesiona-en-territorio?redirect=%2Fnoticias</t>
+      <c r="A318" s="3" t="inlineStr">
+        <is>
+          <t>29/05/2026 10:16 a. m.</t>
+        </is>
+      </c>
+      <c r="B318" s="3" t="inlineStr">
+        <is>
+          <t>Medio de Comunicación</t>
+        </is>
+      </c>
+      <c r="C318" s="3" t="inlineStr">
+        <is>
+          <t>La Silla Vacía</t>
+        </is>
+      </c>
+      <c r="D318" s="4" t="inlineStr">
+        <is>
+          <t>ABC de la Democracia: aprenda en 90 minutos</t>
+        </is>
+      </c>
+      <c r="E318" s="5" t="inlineStr">
+        <is>
+          <t>https://www.lasillavacia.com/en-vivo/abc-de-la-democracia-aprenda-en-90-minutos/</t>
         </is>
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="12" t="inlineStr">
-        <is>
-          <t>29/05/2026 05:57 p. m.</t>
-        </is>
-      </c>
-      <c r="B319" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C319" s="12" t="inlineStr">
-        <is>
-          <t>Ministerio del Interior</t>
-        </is>
-      </c>
-      <c r="D319" s="13" t="inlineStr">
-        <is>
-          <t>FORMACIÓN QUE PROTEGE TERRITORIO: LA CONSULTA PREVIA POR TODO EL TOLIMA</t>
-        </is>
-      </c>
-      <c r="E319" s="14" t="inlineStr">
-        <is>
-          <t>https://www.mininterior.gov.co/campanas/formacion-que-protege-territorio-la-consulta-previa-por-todo-el-tolima/</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="9" t="inlineStr">
-        <is>
-          <t>29/05/2026 05:09 p. m.</t>
-        </is>
-      </c>
-      <c r="B320" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C320" s="9" t="inlineStr">
-        <is>
-          <t>Ministerio del Interior</t>
-        </is>
-      </c>
-      <c r="D320" s="10" t="inlineStr">
-        <is>
-          <t>Quibdó culmina 16 consultas previas para fortalecer la conectividad en el Chocó.</t>
-        </is>
-      </c>
-      <c r="E320" s="11" t="inlineStr">
-        <is>
-          <t>https://www.mininterior.gov.co/micrositios/direccion-de-autoridad-nacional-y-consulta-previa/quibdo-culmina-16-consultas-previas-para-fortalecer-la-conectividad-en-el-choco/</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" s="12" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B321" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C321" s="12" t="inlineStr">
-        <is>
-          <t>Ministerio de Educación Nacional</t>
-        </is>
-      </c>
-      <c r="D321" s="13" t="inlineStr">
-        <is>
-          <t>Gustavo Petro lleva educación superior al Vichada y $21 mil millones para la primera sede universitaria pública del departamento</t>
-        </is>
-      </c>
-      <c r="E321" s="14" t="inlineStr">
-        <is>
-          <t>https://www.mineducacion.gov.co/portal/salaprensa/Comunicados/429109:Gustavo-Petro-lleva-educacion-superior-al-Vichada-y-21-mil-millones-para-la-primera-sede-universitaria-publica-del-departamento</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" s="9" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B322" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C322" s="9" t="inlineStr">
-        <is>
-          <t>Ministerio de Educación Nacional</t>
-        </is>
-      </c>
-      <c r="D322" s="10" t="inlineStr">
-        <is>
-          <t>Más de 1,1 millones de estudiantes ya participaron en ‘Quiero Ser, Quiero Saber’</t>
-        </is>
-      </c>
-      <c r="E322" s="11" t="inlineStr">
-        <is>
-          <t>https://www.mineducacion.gov.co/portal/salaprensa/Comunicados/429105:Mas-de-1-1-millones-de-estudiantes-ya-participaron-en-Quiero-Ser-Quiero-Saber</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="12" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B323" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C323" s="12" t="inlineStr">
-        <is>
-          <t>Ministerio de Educación Nacional</t>
-        </is>
-      </c>
-      <c r="D323" s="13" t="inlineStr">
-        <is>
-          <t>Ministerio de Educación pidió suspender sesión para elección de rector en la Universidad del Tolima por recusación a miembros del CSU y denuncias de irregularidades</t>
-        </is>
-      </c>
-      <c r="E323" s="14" t="inlineStr">
-        <is>
-          <t>https://www.mineducacion.gov.co/portal/salaprensa/Comunicados/429101:Ministerio-de-Educacion-pidio-suspender-sesion-para-eleccion-de-rector-en-la-Universidad-del-Tolima-por-recusacion-a-miembros-del-CSU-y-denuncias-de-irregularidades</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" s="9" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B324" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C324" s="9" t="inlineStr">
-        <is>
-          <t>Ministerio de Educación Nacional</t>
-        </is>
-      </c>
-      <c r="D324" s="10" t="inlineStr">
-        <is>
-          <t>El Gobierno del Cambio presenta una propuesta para que ninguna crisis le quite la escuela a las y los estudiantes del país</t>
-        </is>
-      </c>
-      <c r="E324" s="11" t="inlineStr">
-        <is>
-          <t>https://www.mineducacion.gov.co/portal/salaprensa/Comunicados/429108:El-Gobierno-del-Cambio-presenta-una-propuesta-para-que-ninguna-crisis-le-quite-la-escuela-a-las-y-los-estudiantes-del-pais</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="12" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B325" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C325" s="12" t="inlineStr">
-        <is>
-          <t>Ministerio de Educación Nacional</t>
-        </is>
-      </c>
-      <c r="D325" s="13" t="inlineStr">
-        <is>
-          <t>Gustavo Petro lleva educación superior al Vichada y $21 mil millones para la primera sede universitaria pública del departamento</t>
-        </is>
-      </c>
-      <c r="E325" s="14" t="inlineStr">
-        <is>
-          <t>https://www.mineducacion.gov.co/portal/salaprensa/Comunicados/429109:Gustavo-Petro-lleva-educacion-superior-al-Vichada-y-21-mil-millones-para-la-primera-sede-universitaria-publica-del-departamento</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" s="9" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B326" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C326" s="9" t="inlineStr">
-        <is>
-          <t>Ministerio de Educación Nacional</t>
-        </is>
-      </c>
-      <c r="D326" s="10" t="inlineStr">
-        <is>
-          <t>Más de 1,1 millones de estudiantes ya participaron en ‘Quiero Ser, Quiero Saber’</t>
-        </is>
-      </c>
-      <c r="E326" s="11" t="inlineStr">
-        <is>
-          <t>https://www.mineducacion.gov.co/portal/salaprensa/Comunicados/429105:Mas-de-1-1-millones-de-estudiantes-ya-participaron-en-Quiero-Ser-Quiero-Saber</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" s="12" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B327" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C327" s="12" t="inlineStr">
-        <is>
-          <t>Ministerio de Educación Nacional</t>
-        </is>
-      </c>
-      <c r="D327" s="13" t="inlineStr">
-        <is>
-          <t>Ministerio de Educación pidió suspender sesión para elección de rector en la Universidad del Tolima por recusación a miembros del CSU y denuncias de irregularidades</t>
-        </is>
-      </c>
-      <c r="E327" s="14" t="inlineStr">
-        <is>
-          <t>https://www.mineducacion.gov.co/portal/salaprensa/Comunicados/429101:Ministerio-de-Educacion-pidio-suspender-sesion-para-eleccion-de-rector-en-la-Universidad-del-Tolima-por-recusacion-a-miembros-del-CSU-y-denuncias-de-irregularidades</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" s="9" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B328" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C328" s="9" t="inlineStr">
-        <is>
-          <t>Ministerio del Trabajo</t>
-        </is>
-      </c>
-      <c r="D328" s="10" t="inlineStr">
-        <is>
-          <t>”Que América Latina observe nuestras elecciones y nuestras reformas laborales demuestra que Colombia recuperó su liderazgo democrático”: ministro Antonio Sanguino</t>
-        </is>
-      </c>
-      <c r="E328" s="11" t="inlineStr">
-        <is>
-          <t>https://www.mintrabajo.gov.co/web/guest/que-america-latina-observe-nuestras-elecciones-y-nuestras-reformas-laborales-demuestra-que-colombia-recuper%C3%B3-su-liderazgo-democr%C3%A1tico-ministro-antonio-sanguino</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="12" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B329" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C329" s="12" t="inlineStr">
-        <is>
-          <t>Ministerio del Trabajo</t>
-        </is>
-      </c>
-      <c r="D329" s="13" t="inlineStr">
-        <is>
-          <t>Gobierno Nacional presenta política pública para la formalización laboral, la protección social y la dignidad de las y los trabajadores de la cultura</t>
-        </is>
-      </c>
-      <c r="E329" s="14" t="inlineStr">
-        <is>
-          <t>https://www.mintrabajo.gov.co/web/guest/gobierno-nacional-presenta-pol%C3%ADtica-p%C3%BAblica-para-la-formalizaci%C3%B3n-laboral-la-protecci%C3%B3n-social-y-la-dignidad-de-las-y-los-trabajadores-de-la-cultura</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" s="9" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B330" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C330" s="9" t="inlineStr">
-        <is>
-          <t>Ministerio del Trabajo</t>
-        </is>
-      </c>
-      <c r="D330" s="10" t="inlineStr">
-        <is>
-          <t>“Hoy el mundo mira a Colombia como referente en derechos laborales y libertad sindical”: viceministra Sandra Muñoz</t>
-        </is>
-      </c>
-      <c r="E330" s="11" t="inlineStr">
-        <is>
-          <t>https://www.mintrabajo.gov.co/web/guest/hoy-el-mundo-mira-a-colombia-como-referente-en-derechos-laborales-y-libertad-sindical-viceministra-sandra-mu%C3%B1oz</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" s="12" t="inlineStr">
-        <is>
-          <t>29/05/2026 08:10 p. m.</t>
-        </is>
-      </c>
-      <c r="B331" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C331" s="12" t="inlineStr">
-        <is>
-          <t>Superintendencia Nacional de Salud</t>
-        </is>
-      </c>
-      <c r="D331" s="13" t="inlineStr">
-        <is>
-          <t>Supersalud impone medida cautelar a CAFAM por más de un millón de medicamentos pendientes de entrega</t>
-        </is>
-      </c>
-      <c r="E331" s="14" t="inlineStr">
-        <is>
-          <t>https://wcmportal.supersalud.gov.co/portalweb/Comunicaciones/Lists/Noticias/Noticia.aspx?ID=2583</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="9" t="inlineStr">
-        <is>
-          <t>29/05/2026 03:00 a. m.</t>
-        </is>
-      </c>
-      <c r="B332" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C332" s="9" t="inlineStr">
-        <is>
-          <t>Procuraduría General de la Nación</t>
-        </is>
-      </c>
-      <c r="D332" s="10" t="inlineStr">
-        <is>
-          <t>Cargos a exsecretario General de Corpochivor por presunto acoso sexual</t>
-        </is>
-      </c>
-      <c r="E332" s="11" t="inlineStr">
-        <is>
-          <t>https://www.procuraduria.gov.co/Pages/cargos-exsecretario-general-corpochivor-por-presunto-acoso-sexual.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="12" t="inlineStr">
-        <is>
-          <t>29/05/2026 12:00 p. m.</t>
-        </is>
-      </c>
-      <c r="B333" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C333" s="12" t="inlineStr">
-        <is>
-          <t>Procuraduría General de la Nación</t>
-        </is>
-      </c>
-      <c r="D333" s="13" t="inlineStr">
-        <is>
-          <t>Procuraduría activa vigilancia preventiva por riesgo de incendios forestales en Tolima</t>
-        </is>
-      </c>
-      <c r="E333" s="14" t="inlineStr">
-        <is>
-          <t>https://www.procuraduria.gov.co/Pages/procuraduria-activa-vigilancia-preventiva-riesgo-incendios-forestales-tolima.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="9" t="inlineStr">
-        <is>
-          <t>29/05/2026 08:00 a. m.</t>
-        </is>
-      </c>
-      <c r="B334" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C334" s="9" t="inlineStr">
-        <is>
-          <t>Procuraduría General de la Nación</t>
-        </is>
-      </c>
-      <c r="D334" s="10" t="inlineStr">
-        <is>
-          <t>Suspensión de tres meses a expersonera de Marsella, Risaralda, por incumplir plazo para responder solicitud a una asociación de mujeres</t>
-        </is>
-      </c>
-      <c r="E334" s="11" t="inlineStr">
-        <is>
-          <t>https://www.procuraduria.gov.co/Pages/suspension-tres-meses-expersonera-marsella-risaralda-por-incumplir-plazo-para-responder-solicitud-asociacion.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" s="12" t="inlineStr">
-        <is>
-          <t>29/05/2026 06:30 a. m.</t>
-        </is>
-      </c>
-      <c r="B335" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C335" s="12" t="inlineStr">
-        <is>
-          <t>Procuraduría General de la Nación</t>
-        </is>
-      </c>
-      <c r="D335" s="13" t="inlineStr">
-        <is>
-          <t>Procuraduría refuerza acciones para proteger la Ciénaga de la Virgen</t>
-        </is>
-      </c>
-      <c r="E335" s="14" t="inlineStr">
-        <is>
-          <t>https://www.procuraduria.gov.co/Pages/procuraduria-refuerza-acciones-para-proteger-cienaga-virgen.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="9" t="inlineStr">
-        <is>
-          <t>29/05/2026 05:33 p. m.</t>
-        </is>
-      </c>
-      <c r="B336" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C336" s="9" t="inlineStr">
-        <is>
-          <t>Fiscalía General de la Nación</t>
-        </is>
-      </c>
-      <c r="D336" s="10" t="inlineStr">
-        <is>
-          <t>Fiscalía activa plan especial para acompañar jornada de elecciones presidenciales en Meta</t>
-        </is>
-      </c>
-      <c r="E336" s="11" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/fiscalia-activa-plan-especial-para-acompanar-jornada-de-elecciones-presidenciales-en-meta/</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="12" t="inlineStr">
-        <is>
-          <t>29/05/2026 05:21 p. m.</t>
-        </is>
-      </c>
-      <c r="B337" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C337" s="12" t="inlineStr">
-        <is>
-          <t>Fiscalía General de la Nación</t>
-        </is>
-      </c>
-      <c r="D337" s="13" t="inlineStr">
-        <is>
-          <t>Fiscalía activa estrategia especial para garantizar atención durante la jornada de elecciones presidenciales en Chocó</t>
-        </is>
-      </c>
-      <c r="E337" s="14" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/fiscalia-activa-estrategia-especial-para-garantizar-atencion-durante-la-jornada-de-elecciones-presidenciales-en-choco/</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" s="9" t="inlineStr">
-        <is>
-          <t>29/05/2026 05:17 p. m.</t>
-        </is>
-      </c>
-      <c r="B338" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C338" s="9" t="inlineStr">
-        <is>
-          <t>Fiscalía General de la Nación</t>
-        </is>
-      </c>
-      <c r="D338" s="10" t="inlineStr">
-        <is>
-          <t>Fiscalía activa plan estratégico en Cauca para acompañar elecciones presidenciales</t>
-        </is>
-      </c>
-      <c r="E338" s="11" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/fiscalia-activa-plan-estrategico-en-cauca-para-acompanar-elecciones-presidenciales/</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" s="12" t="inlineStr">
-        <is>
-          <t>29/05/2026 05:12 p. m.</t>
-        </is>
-      </c>
-      <c r="B339" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C339" s="12" t="inlineStr">
-        <is>
-          <t>Fiscalía General de la Nación</t>
-        </is>
-      </c>
-      <c r="D339" s="13" t="inlineStr">
-        <is>
-          <t>Asegurado hombre que habría participado en ataque sicarial ocurrido en el barrio Café Madrid en Bucaramanga</t>
-        </is>
-      </c>
-      <c r="E339" s="14" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-hombre-que-habria-participado-en-ataque-sicarial-ocurrido-en-el-barrio-cafe-madrid-en-bucaramanga/</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" s="9" t="inlineStr">
-        <is>
-          <t>29/05/2026 05:01 p. m.</t>
-        </is>
-      </c>
-      <c r="B340" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C340" s="9" t="inlineStr">
-        <is>
-          <t>Fiscalía General de la Nación</t>
-        </is>
-      </c>
-      <c r="D340" s="10" t="inlineStr">
-        <is>
-          <t>En Sucre más de 150 servidores de la Fiscalía acompañarán las elecciones presidenciales</t>
-        </is>
-      </c>
-      <c r="E340" s="11" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/en-sucre-mas-de-150-servidores-de-la-fiscalia-acompanaran-las-elecciones-presidenciales/</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" s="12" t="inlineStr">
-        <is>
-          <t>29/05/2026 04:51 p. m.</t>
-        </is>
-      </c>
-      <c r="B341" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C341" s="12" t="inlineStr">
-        <is>
-          <t>Fiscalía General de la Nación</t>
-        </is>
-      </c>
-      <c r="D341" s="13" t="inlineStr">
-        <is>
-          <t>En Córdoba más de 170 servidores de la Fiscalía acompañarán jornada de elecciones presidenciales</t>
-        </is>
-      </c>
-      <c r="E341" s="14" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/en-cordoba-mas-de-170-servidores-de-la-fiscalia-acompanaran-jornada-de-elecciones-presidenciales/</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" s="9" t="inlineStr">
-        <is>
-          <t>29/05/2026 04:44 p. m.</t>
-        </is>
-      </c>
-      <c r="B342" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C342" s="9" t="inlineStr">
-        <is>
-          <t>Fiscalía General de la Nación</t>
-        </is>
-      </c>
-      <c r="D342" s="10" t="inlineStr">
-        <is>
-          <t>Fiscalía activa dispositivo en Antioquia para acompañar jornada de elecciones presidenciales</t>
-        </is>
-      </c>
-      <c r="E342" s="11" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/fiscalia-activa-dispositivo-en-antioquia-para-acompanar-jornada-de-elecciones-presidenciales/</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" s="12" t="inlineStr">
-        <is>
-          <t>29/05/2026 04:31 p. m.</t>
-        </is>
-      </c>
-      <c r="B343" s="12" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C343" s="12" t="inlineStr">
-        <is>
-          <t>Fiscalía General de la Nación</t>
-        </is>
-      </c>
-      <c r="D343" s="13" t="inlineStr">
-        <is>
-          <t>Asegurado presunto responsable del asesinato de un comerciante de zapatos en Ibagué</t>
-        </is>
-      </c>
-      <c r="E343" s="14" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/asegurado-presunto-responsable-del-asesinato-de-un-comerciante-de-zapatos-en-ibague/</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" s="9" t="inlineStr">
-        <is>
-          <t>29/05/2026 04:21 p. m.</t>
-        </is>
-      </c>
-      <c r="B344" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Oficial</t>
-        </is>
-      </c>
-      <c r="C344" s="9" t="inlineStr">
-        <is>
-          <t>Fiscalía General de la Nación</t>
-        </is>
-      </c>
-      <c r="D344" s="10" t="inlineStr">
-        <is>
-          <t>Un hombre que intentó abusar y asesinar sexualmente de su expareja fue condenado a 16 años de prisión</t>
-        </is>
-      </c>
-      <c r="E344" s="11" t="inlineStr">
-        <is>
-          <t>https://www.fiscalia.gov.co/colombia/noticias/un-hombre-que-intento-abusar-y-asesinar-sexualmente-de-su-expareja-fue-condenado-a-16-anos-de-prision/</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" s="6" t="inlineStr">
-        <is>
-          <t>28/05/2026 09:50 p. m.</t>
-        </is>
-      </c>
-      <c r="B345" s="6" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C345" s="6" t="inlineStr">
-        <is>
-          <t>El Espectador</t>
-        </is>
-      </c>
-      <c r="D345" s="7" t="inlineStr">
-        <is>
-          <t>Concejo de Bogotá propone sello QR para verificar legalidad de centros de estética</t>
-        </is>
-      </c>
-      <c r="E345" s="8" t="inlineStr">
-        <is>
-          <t>https://www.elespectador.com/bogota/concejo-de-bogota-propone-sello-qr-para-verificar-legalidad-de-centros-de-estetica/</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" s="3" t="inlineStr">
-        <is>
-          <t>28/05/2026 09:45 p. m.</t>
-        </is>
-      </c>
-      <c r="B346" s="3" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C346" s="3" t="inlineStr">
-        <is>
-          <t>El Espectador</t>
-        </is>
-      </c>
-      <c r="D346" s="4" t="inlineStr">
-        <is>
-          <t>Movida Electoral: Cepeda, De la Espriella y Valencia ultiman estrategias a horas de elección</t>
-        </is>
-      </c>
-      <c r="E346" s="5" t="inlineStr">
-        <is>
-          <t>https://www.elespectador.com/politica/elecciones-colombia-2026/territorios-pdet-se-unen-a-cepeda-de-la-espriella-se-reune-con-noboa-valencia-anuncia-stream-con-mrstiven-noticias-hoy/</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" s="6" t="inlineStr">
-        <is>
-          <t>28/05/2026 08:58 p. m.</t>
-        </is>
-      </c>
-      <c r="B347" s="6" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C347" s="6" t="inlineStr">
-        <is>
-          <t>El Espectador</t>
-        </is>
-      </c>
-      <c r="D347" s="7" t="inlineStr">
-        <is>
-          <t>La historia de la magistrada que habría ordenado pago de una pensión de COP 1.600 millones</t>
-        </is>
-      </c>
-      <c r="E347" s="8" t="inlineStr">
-        <is>
-          <t>https://www.elespectador.com/judicial/la-historia-de-la-magistrada-que-habria-ordenado-pago-de-una-pension-de-cop-1600-millones/</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" s="3" t="inlineStr">
-        <is>
-          <t>28/05/2026 08:57 p. m.</t>
-        </is>
-      </c>
-      <c r="B348" s="3" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C348" s="3" t="inlineStr">
-        <is>
-          <t>El Espectador</t>
-        </is>
-      </c>
-      <c r="D348" s="4" t="inlineStr">
-        <is>
-          <t>¡La selección femenina de Colombia presentó convocatoria clave para acercarse al Mundial!</t>
-        </is>
-      </c>
-      <c r="E348" s="5" t="inlineStr">
-        <is>
-          <t>https://www.elespectador.com/deportes/seleccion-colombia/la-seleccion-femenina-de-colombia-presento-convocatoria-clave-para-acercarse-al-mundial/</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" s="6" t="inlineStr">
-        <is>
-          <t>28/05/2026 08:55 p. m.</t>
-        </is>
-      </c>
-      <c r="B349" s="6" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C349" s="6" t="inlineStr">
-        <is>
-          <t>El Espectador</t>
-        </is>
-      </c>
-      <c r="D349" s="7" t="inlineStr">
-        <is>
-          <t>El sistema internacional se reconfigura: ¿qué opciones tiene Colombia?</t>
-        </is>
-      </c>
-      <c r="E349" s="8" t="inlineStr">
-        <is>
-          <t>https://www.elespectador.com/mundo/america/el-sistema-internacional-se-reconfigura-que-opciones-tiene-colombia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" s="3" t="inlineStr">
-        <is>
-          <t>28/05/2026 08:50 p. m.</t>
-        </is>
-      </c>
-      <c r="B350" s="3" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C350" s="3" t="inlineStr">
-        <is>
-          <t>El Espectador</t>
-        </is>
-      </c>
-      <c r="D350" s="4" t="inlineStr">
-        <is>
-          <t>¿Va a votar este domingo? Así será la operación de Transmilenio y el SITP en Bogotá</t>
-        </is>
-      </c>
-      <c r="E350" s="5" t="inlineStr">
-        <is>
-          <t>https://www.elespectador.com/bogota/elecciones-en-bogota-2026-asi-funcionaran-transmilenio-y-sitp-este-31-de-mayo/</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" s="6" t="inlineStr">
-        <is>
-          <t>28/05/2026 08:43 p. m.</t>
-        </is>
-      </c>
-      <c r="B351" s="6" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C351" s="6" t="inlineStr">
-        <is>
-          <t>El Espectador</t>
-        </is>
-      </c>
-      <c r="D351" s="7" t="inlineStr">
-        <is>
-          <t>Movilidad hoy, 29 de mayo: volcamiento de camión en la localidad de Chapinero</t>
-        </is>
-      </c>
-      <c r="E351" s="8" t="inlineStr">
-        <is>
-          <t>https://www.elespectador.com/bogota/movilidad-hoy-viernes-29-de-mayo-asi-esta-el-trafico-en-las-vias-de-bogota/</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" s="3" t="inlineStr">
-        <is>
-          <t>28/05/2026 08:35 p. m.</t>
-        </is>
-      </c>
-      <c r="B352" s="3" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C352" s="3" t="inlineStr">
-        <is>
-          <t>El Espectador</t>
-        </is>
-      </c>
-      <c r="D352" s="4" t="inlineStr">
-        <is>
-          <t>“Votar no es obligatorio, pero es una obligación moral de los colombianos” | Entrevista</t>
-        </is>
-      </c>
-      <c r="E352" s="5" t="inlineStr">
-        <is>
-          <t>https://www.elespectador.com/especiales/votar-no-es-obligatorio-pero-es-una-obligacion-moral-de-los-colombianos-entrevista/</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" s="6" t="inlineStr">
-        <is>
-          <t>28/05/2026 08:28 p. m.</t>
-        </is>
-      </c>
-      <c r="B353" s="6" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C353" s="6" t="inlineStr">
-        <is>
-          <t>El Espectador</t>
-        </is>
-      </c>
-      <c r="D353" s="7" t="inlineStr">
-        <is>
-          <t>Presidente Petro terminó gira en la costa Caribe con referencias a elección presidencial</t>
-        </is>
-      </c>
-      <c r="E353" s="8" t="inlineStr">
-        <is>
-          <t>https://www.elespectador.com/politica/elecciones-colombia-2026/presidente-gustavo-petro-termino-gira-en-el-caribe-sobre-eleccion-presidencial-de-la-espriella-y-cepeda-noticas-hoy/</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" s="3" t="inlineStr">
-        <is>
-          <t>28/05/2026 08:28 p. m.</t>
-        </is>
-      </c>
-      <c r="B354" s="3" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C354" s="3" t="inlineStr">
-        <is>
-          <t>El Espectador</t>
-        </is>
-      </c>
-      <c r="D354" s="4" t="inlineStr">
-        <is>
-          <t>¡Envigado, campeón! El equipo naranja resistió y conquistó el Torneo BetPlay 2026-I</t>
-        </is>
-      </c>
-      <c r="E354" s="5" t="inlineStr">
-        <is>
-          <t>https://www.elespectador.com/deportes/futbol-colombiano/otros-equipos/envigado-campeon-el-equipo-naranja-resistio-con-diez-hombres-y-conquisto-el-torneo-betplay/</t>
+      <c r="A319" s="6" t="inlineStr">
+        <is>
+          <t>29/05/2026 09:48 a. m.</t>
+        </is>
+      </c>
+      <c r="B319" s="6" t="inlineStr">
+        <is>
+          <t>Medio de Comunicación</t>
+        </is>
+      </c>
+      <c r="C319" s="6" t="inlineStr">
+        <is>
+          <t>La Silla Vacía</t>
+        </is>
+      </c>
+      <c r="D319" s="7" t="inlineStr">
+        <is>
+          <t>Pese a orden de Petro, Óscar Muñoz sigue en la embajada de Guyana</t>
+        </is>
+      </c>
+      <c r="E319" s="8" t="inlineStr">
+        <is>
+          <t>https://www.lasillavacia.com/en-vivo/pese-a-orden-de-petro-oscar-munoz-sigue-en-la-embajada-de-guyana/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E354"/>
+  <autoFilter ref="A1:E319"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -10336,41 +9323,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E317" r:id="rId316"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E318" r:id="rId317"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E319" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E320" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E321" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E322" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E323" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E324" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E325" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E326" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E327" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E328" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E329" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E330" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E331" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E332" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E333" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E334" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E335" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E336" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E337" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E338" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E339" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E340" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E341" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E342" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E343" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E344" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E345" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E346" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E347" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E348" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E349" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E350" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E351" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E352" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E353" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E354" r:id="rId353"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/ultimahora.xlsx
+++ b/public/ultimahora.xlsx
@@ -527,7 +527,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:33 p. m.</t>
+          <t>30/05/2026 09:24 p. m.</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -542,19 +542,19 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>#ElFiltro: video sobre supuestos tarjetones marcados a favor de Abelardo de la Espriella y Paloma Valencia no corresponde a elecciones presidenciales</t>
+          <t>Baloto y Baloto Revancha: conozca aquí los resultados del último sorteo del sábado 30 de mayo de 2026</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/elfiltro-video-sobre-supuestos-tarjetones-marcados-a-favor-de-abelardo-de-la-espriella-y-paloma-valencia-no-corresponde-a-elecciones-presidenciales-3559703</t>
+          <t>https://www.eltiempo.com/economia/finanzas-personales/baloto-y-baloto-revancha-conozca-aqui-los-resultados-del-ultimo-sorteo-del-sabado-30-de-mayo-de-3559713</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:29 p. m.</t>
+          <t>30/05/2026 09:01 p. m.</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -569,19 +569,19 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Cristhian Mosquera, español de raíces colombianas, aguanta críticas y burlas tras cometer penalti decisivo en la final de la Champions League</t>
+          <t>De una biblioteca comunitaria al Kennedy Space Center: el sueño espacial de cinco jóvenes bogotanos</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/deportes/futbol-internacional/cristhian-mosquera-espanol-de-raices-colombianas-aguanta-criticas-y-burlas-tras-cometer-penalti-decisivo-en-la-final-de-la-champions-league-3559704</t>
+          <t>https://www.eltiempo.com/bogota/de-una-biblioteca-comunitaria-al-kennedy-space-center-el-sueno-espacial-de-cinco-jovenes-bogotanos-3558559</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:13 p. m.</t>
+          <t>30/05/2026 08:33 p. m.</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -596,19 +596,19 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Cuentas Claras / Air-e, patrimonio que cae casi en su totalidad</t>
+          <t>#ElFiltro: video sobre supuestos tarjetones marcados a favor de Abelardo de la Espriella y Paloma Valencia no corresponde a elecciones presidenciales</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/economia/sectores/cuentas-claras-air-e-patrimonio-que-cae-casi-en-su-totalidad-3559633</t>
+          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/elfiltro-video-sobre-supuestos-tarjetones-marcados-a-favor-de-abelardo-de-la-espriella-y-paloma-valencia-no-corresponde-a-elecciones-presidenciales-3559703</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:01 p. m.</t>
+          <t>30/05/2026 08:29 p. m.</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -623,19 +623,19 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Alejandro Char responde a los señalamientos del presidente Gustavo Petro y asegura que Barranquilla financia la mayor parte del PAE</t>
+          <t>Cristhian Mosquera, español de raíces colombianas, aguanta críticas y burlas tras cometer penalti decisivo en la final de la Champions League</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/politica/gobierno/alejandro-char-responde-a-los-senalamientos-del-presidente-gustavo-petro-y-asegura-que-barranquilla-financia-la-mayor-parte-del-pae-3559696</t>
+          <t>https://www.eltiempo.com/deportes/futbol-internacional/cristhian-mosquera-espanol-de-raices-colombianas-aguanta-criticas-y-burlas-tras-cometer-penalti-decisivo-en-la-final-de-la-champions-league-3559704</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 07:31 p. m.</t>
+          <t>30/05/2026 08:13 p. m.</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -650,19 +650,19 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Entrevista de Westcol con Abelardo de la Espriella: porte legal de armas, megacárceles y las principales propuestas de su plan de gobierno</t>
+          <t>Cuentas Claras / Air-e, patrimonio que cae casi en su totalidad</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/cultura/gente/entrevista-de-westcol-con-abelardo-de-la-espriella-su-plan-de-construir-10-megacarceles-y-las-apuestas-clave-de-su-programa-de-gobierno-3559697</t>
+          <t>https://www.eltiempo.com/economia/sectores/cuentas-claras-air-e-patrimonio-que-cae-casi-en-su-totalidad-3559633</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 07:00 p. m.</t>
+          <t>30/05/2026 08:01 p. m.</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -677,19 +677,19 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Autoridades de Nariño investigan amenazas de grupo armado contra campesinos previo a elecciones presidenciales: ‘Se va a exigir certificado electoral’</t>
+          <t>Alejandro Char responde a los señalamientos del presidente Gustavo Petro y asegura que Barranquilla financia la mayor parte del PAE</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/colombia/cali/autoridades-de-narino-investigan-amenazas-de-grupo-armado-contra-campesinos-previo-a-elecciones-presidenciales-se-va-a-exigir-certificado-electoral-3559695</t>
+          <t>https://www.eltiempo.com/politica/gobierno/alejandro-char-responde-a-los-senalamientos-del-presidente-gustavo-petro-y-asegura-que-barranquilla-financia-la-mayor-parte-del-pae-3559696</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 06:57 p. m.</t>
+          <t>30/05/2026 07:31 p. m.</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -704,19 +704,19 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Andrés Llinás pone el pecho por el mal semestre de Millonarios y les habla claro a los hinchas: 'No estuvimos a la altura'</t>
+          <t>Entrevista de Westcol con Abelardo de la Espriella: porte legal de armas, megacárceles y las principales propuestas de su plan de gobierno</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/deportes/futbol-colombiano/andres-llinas-pone-el-pecho-por-el-mal-semestre-de-millonarios-y-les-habla-claro-a-los-hinchas-no-estuvimos-a-la-altura-3559691</t>
+          <t>https://www.eltiempo.com/cultura/gente/entrevista-de-westcol-con-abelardo-de-la-espriella-su-plan-de-construir-10-megacarceles-y-las-apuestas-clave-de-su-programa-de-gobierno-3559697</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 06:36 p. m.</t>
+          <t>30/05/2026 07:00 p. m.</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -731,19 +731,19 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Abuelita de Pereira envió $700 mil al Nequi equivocado y lanza desesperado llamado para recuperar su dinero: 'Devuélvanme la platica'</t>
+          <t>Autoridades de Nariño investigan amenazas de grupo armado contra campesinos previo a elecciones presidenciales: ‘Se va a exigir certificado electoral’</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/cultura/gente/abuelita-de-pereira-envio-700-mil-al-nequi-equivocado-y-lanza-desesperado-llamado-para-recuperar-su-dinero-devuelvanme-la-platica-3559693</t>
+          <t>https://www.eltiempo.com/colombia/cali/autoridades-de-narino-investigan-amenazas-de-grupo-armado-contra-campesinos-previo-a-elecciones-presidenciales-se-va-a-exigir-certificado-electoral-3559695</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 06:31 p. m.</t>
+          <t>30/05/2026 06:57 p. m.</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -758,19 +758,19 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>De caminatas en el campo a innovación sostenible: la historia de Fungalic, el proyecto que transforma residuos en soluciones con hongos</t>
+          <t>Andrés Llinás pone el pecho por el mal semestre de Millonarios y les habla claro a los hinchas: 'No estuvimos a la altura'</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/colombia/medellin/de-caminatas-en-el-campo-a-innovacion-sostenible-la-historia-de-fungalic-el-proyecto-que-transforma-residuos-en-soluciones-con-hongos-3559692</t>
+          <t>https://www.eltiempo.com/deportes/futbol-colombiano/andres-llinas-pone-el-pecho-por-el-mal-semestre-de-millonarios-y-les-habla-claro-a-los-hinchas-no-estuvimos-a-la-altura-3559691</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 06:30 p. m.</t>
+          <t>30/05/2026 06:36 p. m.</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -785,19 +785,19 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Así blindará Bogotá su seguridad para las elecciones de este domingo 29 de mayo: 11.000 policías, 2.100 soldados y ley seca</t>
+          <t>Abuelita de Pereira envió $700 mil al Nequi equivocado y lanza desesperado llamado para recuperar su dinero: 'Devuélvanme la platica'</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/bogota/asi-blindara-bogota-su-seguridad-para-las-elecciones-de-este-domingo-29-de-mayo-11-000-policias-2-100-soldados-y-ley-seca-3559689</t>
+          <t>https://www.eltiempo.com/cultura/gente/abuelita-de-pereira-envio-700-mil-al-nequi-equivocado-y-lanza-desesperado-llamado-para-recuperar-su-dinero-devuelvanme-la-platica-3559693</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 05:57 p. m.</t>
+          <t>30/05/2026 06:31 p. m.</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,19 +812,19 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>La USO respalda fortalecer la exploración de hidrocarburos para garantizar la sostenibilidad de Ecopetrol de cara a las elecciones presidenciales</t>
+          <t>De caminatas en el campo a innovación sostenible: la historia de Fungalic, el proyecto que transforma residuos en soluciones con hongos</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/economia/sectores/la-union-sindical-obrera-uso-respalda-fortalecer-la-exploracion-de-hidrocarburos-para-garantizar-la-sostenibilidad-de-ecopetrol-3559690</t>
+          <t>https://www.eltiempo.com/colombia/medellin/de-caminatas-en-el-campo-a-innovacion-sostenible-la-historia-de-fungalic-el-proyecto-que-transforma-residuos-en-soluciones-con-hongos-3559692</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 05:48 p. m.</t>
+          <t>30/05/2026 06:30 p. m.</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -839,19 +839,19 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>109 vidas perdidas en 2026: así acompaña Medellín a las familias que enfrentan el duelo por accidentes de tránsito</t>
+          <t>Así blindará Bogotá su seguridad para las elecciones de este domingo 29 de mayo: 11.000 policías, 2.100 soldados y ley seca</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/colombia/medellin/109-vidas-perdidas-en-2026-asi-acompana-medellin-a-las-familias-que-enfrentan-el-duelo-por-accidentes-de-transito-3559687</t>
+          <t>https://www.eltiempo.com/bogota/asi-blindara-bogota-su-seguridad-para-las-elecciones-de-este-domingo-29-de-mayo-11-000-policias-2-100-soldados-y-ley-seca-3559689</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 05:43 p. m.</t>
+          <t>30/05/2026 05:57 p. m.</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -866,19 +866,19 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Exclusivo: habla esposa del candidato presidencial Santiago Botero, desalojado en Cartagena por presunto caso de violencia intrafamiliar</t>
+          <t>La USO respalda fortalecer la exploración de hidrocarburos para garantizar la sostenibilidad de Ecopetrol de cara a las elecciones presidenciales</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/colombia/otras-ciudades/exclusivo-habla-esposa-del-candidato-presidencial-santiago-botero-desalojado-en-cartagena-por-violencia-intrafamiliar-a-horas-de-abrirse-las-urnas-3559682</t>
+          <t>https://www.eltiempo.com/economia/sectores/la-union-sindical-obrera-uso-respalda-fortalecer-la-exploracion-de-hidrocarburos-para-garantizar-la-sostenibilidad-de-ecopetrol-3559690</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 05:40 p. m.</t>
+          <t>30/05/2026 05:48 p. m.</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -893,19 +893,19 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Falleció el cuñado de alias ‘Castor’ tras más de dos meses hospitalizado: estaba herido desde la balacera afuera de billar en el norte de Barranquilla</t>
+          <t>109 vidas perdidas en 2026: así acompaña Medellín a las familias que enfrentan el duelo por accidentes de tránsito</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/colombia/barranquilla/fallecio-el-cunado-de-alias-castor-tras-mas-de-dos-meses-hospitalizado-estaba-herido-desde-la-balacera-afuera-de-billar-en-el-norte-de-barranquilla-3559688</t>
+          <t>https://www.eltiempo.com/colombia/medellin/109-vidas-perdidas-en-2026-asi-acompana-medellin-a-las-familias-que-enfrentan-el-duelo-por-accidentes-de-transito-3559687</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 05:15 p. m.</t>
+          <t>30/05/2026 05:43 p. m.</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -920,19 +920,19 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Tragedia en la vía Santa Marta-Palomino: una pasajera se cayó cuando intentaba subirse a la buseta y murió arrollada por el mismo vehículo</t>
+          <t>Exclusivo: habla esposa del candidato presidencial Santiago Botero, desalojado en Cartagena por presunto caso de violencia intrafamiliar</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/colombia/otras-ciudades/tragedia-en-la-via-santa-marta-palomino-una-pasajera-se-cayo-cuando-intentaba-subirse-a-la-buseta-y-murio-arrollada-por-el-mismo-vehiculo-3559683</t>
+          <t>https://www.eltiempo.com/colombia/otras-ciudades/exclusivo-habla-esposa-del-candidato-presidencial-santiago-botero-desalojado-en-cartagena-por-violencia-intrafamiliar-a-horas-de-abrirse-las-urnas-3559682</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 05:12 p. m.</t>
+          <t>30/05/2026 05:40 p. m.</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -947,19 +947,19 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Shakira comparte video bailando con los Ghetto Kids, el grupo ugandés que la acompañará en la final del Mundial 2026</t>
+          <t>Falleció el cuñado de alias ‘Castor’ tras más de dos meses hospitalizado: estaba herido desde la balacera afuera de billar en el norte de Barranquilla</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/cultura/gente/shakira-comparte-video-bailando-con-los-ghetto-kids-el-grupo-ugandes-que-la-acompanara-en-la-final-del-mundial-3559686</t>
+          <t>https://www.eltiempo.com/colombia/barranquilla/fallecio-el-cunado-de-alias-castor-tras-mas-de-dos-meses-hospitalizado-estaba-herido-desde-la-balacera-afuera-de-billar-en-el-norte-de-barranquilla-3559688</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 05:05 p. m.</t>
+          <t>30/05/2026 05:15 p. m.</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -974,19 +974,19 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Revelan el detrás de cámaras de 'Dai Dai', el video de Shakira del Mundial 2026, con Luis Díaz y las estrellas del Bayern Múnich</t>
+          <t>Tragedia en la vía Santa Marta-Palomino: una pasajera se cayó cuando intentaba subirse a la buseta y murió arrollada por el mismo vehículo</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/deportes/futbol-internacional/revelan-el-detras-de-camaras-de-dai-dai-el-video-de-shakira-del-mundial-2026-con-luis-diaz-y-las-estrellas-del-bayern-munich-3559684</t>
+          <t>https://www.eltiempo.com/colombia/otras-ciudades/tragedia-en-la-via-santa-marta-palomino-una-pasajera-se-cayo-cuando-intentaba-subirse-a-la-buseta-y-murio-arrollada-por-el-mismo-vehiculo-3559683</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 04:39 p. m.</t>
+          <t>30/05/2026 05:12 p. m.</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -1001,19 +1001,19 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Meteorito explota en Estados Unidos y genera un potente estruendo que se escuchó en varios estados</t>
+          <t>Shakira comparte video bailando con los Ghetto Kids, el grupo ugandés que la acompañará en la final del Mundial 2026</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/mundo/eeuu-y-canada/meteorito-explota-en-estados-unidos-y-genera-un-potente-estruendo-que-se-escucho-en-varios-estados-3559677</t>
+          <t>https://www.eltiempo.com/cultura/gente/shakira-comparte-video-bailando-con-los-ghetto-kids-el-grupo-ugandes-que-la-acompanara-en-la-final-del-mundial-3559686</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 04:36 p. m.</t>
+          <t>30/05/2026 05:05 p. m.</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1028,19 +1028,19 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Juan Valdez le propone que tome café colombiano con el ‘sabor’ de su apellido</t>
+          <t>Revelan el detrás de cámaras de 'Dai Dai', el video de Shakira del Mundial 2026, con Luis Díaz y las estrellas del Bayern Múnich</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/economia/empresas/juan-valdez-le-propone-que-tome-cafe-colombiano-con-el-sabor-de-su-apellido-3559680</t>
+          <t>https://www.eltiempo.com/deportes/futbol-internacional/revelan-el-detras-de-camaras-de-dai-dai-el-video-de-shakira-del-mundial-2026-con-luis-diaz-y-las-estrellas-del-bayern-munich-3559684</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 04:34 p. m.</t>
+          <t>30/05/2026 04:39 p. m.</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -1055,12 +1055,12 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Disturbios en París tras el triunfo del PSG en la Champions: 79 detenidos, caos y un policía herido</t>
+          <t>Meteorito explota en Estados Unidos y genera un potente estruendo que se escuchó en varios estados</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/mundo/europa/disturbios-en-paris-tras-el-triunfo-del-psg-en-la-champions-79-detenidos-caos-y-un-policia-herido-3559681</t>
+          <t>https://www.eltiempo.com/mundo/eeuu-y-canada/meteorito-explota-en-estados-unidos-y-genera-un-potente-estruendo-que-se-escucho-en-varios-estados-3559677</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 12:43 a. m.</t>
+          <t>30/05/2026 10:52 p. m.</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1136,19 +1136,19 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Anuncian cierres viales por obras del Regiotram Occidente en Bogotá y Cundinamarca: rutas y fechas clave</t>
+          <t>Prima para empleadas domésticas por días: cómo calcularla paso a paso y cuánto deben pagar en 2026</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/actualidad/cierres-por-obras-del-regiotram-occidente-afectaran-vias-en-bogota-y-cundinamarca-400895</t>
+          <t>https://www.lafm.com.co/economia/prima-empleadas-domesticas-por-dias-como-calcular-en-2026-400892</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 09:39 p. m.</t>
+          <t>30/05/2026 08:30 p. m.</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1163,19 +1163,19 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Video mostraría los últimos minutos de Alexander Avendaño en Guatapé; lo estarían golpeando antes de caer al embalse: “Ahóguenlo”</t>
+          <t>Mincomercio responde al anuncio de Ecuador sobre aranceles en remate de la campaña electoral</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/actualidad/video-alexander-avendano-ultimos-minutos-antes-de-caer-al-embalse-guatape-400876</t>
+          <t>https://www.lafm.com.co/economia/ministra-de-comercio-aranceles-ecuador-campana-electoral-colombia-abelardo-de-la-espriella-daniel-noboa-400883</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:30 p. m.</t>
+          <t>30/05/2026 08:22 p. m.</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1190,19 +1190,19 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Mincomercio responde al anuncio de Ecuador sobre aranceles en remate de la campaña electoral</t>
+          <t>Medios iraníes dicen que borrador de acuerdo con EEUU incluye desbloqueo de USD 12.000 millones en activos</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/economia/ministra-de-comercio-aranceles-ecuador-campana-electoral-colombia-abelardo-de-la-espriella-daniel-noboa-400883</t>
+          <t>https://www.lafm.com.co/internacional/ormuz-negociaciones-trump-naval-estrecho-dinero-borrador-400888</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:22 p. m.</t>
+          <t>30/05/2026 08:21 p. m.</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -1217,19 +1217,19 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Medios iraníes dicen que borrador de acuerdo con EEUU incluye desbloqueo de USD 12.000 millones en activos</t>
+          <t>¿Juan Fernando Quintero se va de River Plate? Las posibles salidas de ídolos colombianos tras el Mundial 2026</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/internacional/ormuz-negociaciones-trump-naval-estrecho-dinero-borrador-400888</t>
+          <t>https://www.lafm.com.co/deportes/quintero-podria-salir-de-river-plate-tras-el-mundial-2026-carrascal-james-rodriguez-400886</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:21 p. m.</t>
+          <t>30/05/2026 07:32 p. m.</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1244,19 +1244,19 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>¿Juan Fernando Quintero se va de River Plate? Las posibles salidas de ídolos colombianos tras el Mundial 2026</t>
+          <t>Procuraduría indaga si funcionario de la ANT en Arauca participa indebidamente en política</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/deportes/quintero-podria-salir-de-river-plate-tras-el-mundial-2026-carrascal-james-rodriguez-400886</t>
+          <t>https://www.lafm.com.co/politica/procuraduria-indaga-funcionario-ant-arauca-participacion-indebida-en-politica-400887</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 07:32 p. m.</t>
+          <t>30/05/2026 07:10 p. m.</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -1271,19 +1271,19 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Procuraduría indaga si funcionario de la ANT en Arauca participa indebidamente en política</t>
+          <t>Alejandro Estrada: ¿Quién es el ganador de La Casa de los Famosos 2026 y cuánto dinero se llevó?</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/politica/procuraduria-indaga-funcionario-ant-arauca-participacion-indebida-en-politica-400887</t>
+          <t>https://www.lafm.com.co/entretenimiento/quien-es-alejandro-estrada-ganador-de-la-casa-de-los-famosos-2026-400881</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 07:10 p. m.</t>
+          <t>30/05/2026 06:12 p. m.</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1298,19 +1298,19 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Alejandro Estrada: ¿Quién es el ganador de La Casa de los Famosos 2026 y cuánto dinero se llevó?</t>
+          <t>Todo lo que se sabe del desalojo del candidato presidencial Santiago Botero por presunta violencia intrafamiliar: 'Echó a su esposa y a su hijo'</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/entretenimiento/quien-es-alejandro-estrada-ganador-de-la-casa-de-los-famosos-2026-400881</t>
+          <t>https://www.lafm.com.co/actualidad/por-que-desalojaron-a-santiago-botero-por-presunto-caso-de-violencia-intrafamiliar-400878</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 06:12 p. m.</t>
+          <t>30/05/2026 05:59 p. m.</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -1325,19 +1325,19 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Todo lo que se sabe del desalojo del candidato presidencial Santiago Botero por presunta violencia intrafamiliar: 'Echó a su esposa y a su hijo'</t>
+          <t>Elecciones presidenciales: así funcionará el Puesto de Mando Unificado Cibernético para evitar delitos electorales</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/actualidad/por-que-desalojaron-a-santiago-botero-por-presunto-caso-de-violencia-intrafamiliar-400878</t>
+          <t>https://www.lafm.com.co/orden-publico/elecciones-presidenciales-puesto-mando-unificado-cibernetico-policia-nacionall-400879</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 05:59 p. m.</t>
+          <t>30/05/2026 05:54 p. m.</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1352,19 +1352,19 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Elecciones presidenciales: así funcionará el Puesto de Mando Unificado Cibernético para evitar delitos electorales</t>
+          <t>La Casa de los Famosos confirma temporada 4: todo lo que se sabe hasta ahora</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/orden-publico/elecciones-presidenciales-puesto-mando-unificado-cibernetico-policia-nacionall-400879</t>
+          <t>https://www.lafm.com.co/entretenimiento/la-casa-de-los-famosos-tendra-temporada-4-esto-se-sabe-400849</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 05:54 p. m.</t>
+          <t>30/05/2026 05:40 p. m.</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -1379,19 +1379,19 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>La Casa de los Famosos confirma temporada 4: todo lo que se sabe hasta ahora</t>
+          <t>Gobierno Nacional instala PMU y despliega más de 280 mil uniformados para garantizar la seguridad en las elecciones</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/entretenimiento/la-casa-de-los-famosos-tendra-temporada-4-esto-se-sabe-400849</t>
+          <t>https://www.lafm.com.co/politica/gobierno-nacional-instala-pmu-y-despliega-mas-de-280-mil-uniformados-para-garantizar-la-seguridad-en-las-elecciones-400880</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 05:40 p. m.</t>
+          <t>28/05/2026 04:03 p. m.</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1406,19 +1406,19 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Gobierno Nacional instala PMU y despliega más de 280 mil uniformados para garantizar la seguridad en las elecciones</t>
+          <t>Procuraduría pide explicaciones por muerte de estudiante luego de una pelea de boxeo en colegio de Suba</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/politica/gobierno-nacional-instala-pmu-y-despliega-mas-de-280-mil-uniformados-para-garantizar-la-seguridad-en-las-elecciones-400880</t>
+          <t>https://www.lafm.com.co/sociedad/procuraduria-pide-explicacion-muerte-estudiante-practicando-boxeo-400885</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>28/05/2026 04:03 p. m.</t>
+          <t>21/05/2026 03:16 p. m.</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Procuraduría pide explicaciones por muerte de estudiante luego de una pelea de boxeo en colegio de Suba</t>
+          <t>🔴 EN VIVO| Elecciones presidenciales Colombia 31 de mayo: siga el minuto a minuto, resultados y últimas noticias</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/sociedad/procuraduria-pide-explicacion-muerte-estudiante-practicando-boxeo-400885</t>
+          <t>https://www.lafm.com.co/politica/elecciones-colombia-31-de-mayo-en-vivo-resultados-ultimas-noticias-400899</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>"Comprometámonos a respetar los resultados”: Procurador asegura que Colombia está lista para votar en paz este domingo</t>
+          <t>Anuncian cierres viales por obras del Regiotram Occidente en Bogotá y Cundinamarca: rutas y fechas clave</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/politica/elecciones-presidenciales-procurador-gregorio-eljach-pide-respetar-los-resultados-colombia-esta-lista-para-votar-en-paz-400893</t>
+          <t>https://www.lafm.com.co/actualidad/cierres-por-obras-del-regiotram-occidente-afectaran-vias-en-bogota-y-cundinamarca-400895</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Prima para empleadas domésticas por días: cómo calcularla paso a paso y cuánto deben pagar en 2026</t>
+          <t>"Comprometámonos a respetar los resultados”: Procurador asegura que Colombia está lista para votar en paz este domingo</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/economia/prima-empleadas-domesticas-por-dias-como-calcular-en-2026-400892</t>
+          <t>https://www.lafm.com.co/politica/elecciones-presidenciales-procurador-gregorio-eljach-pide-respetar-los-resultados-colombia-esta-lista-para-votar-en-paz-400893</t>
         </is>
       </c>
     </row>
@@ -1610,12 +1610,12 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Karina García barajó la posibilidad de que su hija Isabella se sume a ‘La casa de los famosos Colombia’ en 2027 y le llovieron críticas</t>
+          <t>Claptone anunció su regreso a Colombia con un show especial: fecha, lugar y precios de boletería</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/karina-garcia-barajo-la-posibilidad-de-que-su-hija-isabella-se-sume-a-la-casa-de-los-famosos-colombia-en-2027-y-le-llovieron-criticas/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/claptone-anuncio-su-regreso-a-colombia-con-un-show-especial-fecha-lugar-y-precios-de-boleteria/</t>
         </is>
       </c>
     </row>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Abelardo de la Espriella aseguró que defendería a Westcol si mata a un ladrón: “Así venga con un peluche, le disparas”</t>
+          <t>Denuncian que clínica de Ibagué estaría usando pantallas de turnos para hacer campaña contra el petrismo: Supersalud anunció investigación</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/abelardo-de-la-espriella-aseguro-que-defenderia-a-westcol-si-mata-a-un-ladron-asi-venga-con-un-peluche-le-disparas/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/denuncian-que-clinica-de-ibague-estaria-usando-pantallas-de-turnos-para-hacer-campana-contra-el-petrismo-supersalud-anuncio-investigacion/</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Colombia ante las urnas: Izquierda, derecha y un ‘outsider’ se disputan la presidencia</t>
+          <t>Bernie Moreno publicó una carta para los colombianos antes de las elecciones: “El mundo será testigo de la lucha por la democracia”</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/colombia-ante-las-urnas-izquierda-derecha-y-un-outsider-se-disputan-la-presidencia/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/bernie-moreno-publico-una-carta-para-los-colombianos-antes-de-las-elecciones-el-mundo-sera-testigo-de-la-lucha-por-la-democracia/</t>
         </is>
       </c>
     </row>
@@ -1691,12 +1691,12 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Lo que esconde el clóset de los candidatos presidenciales: los mensajes en la ropa de Cepeda, Valencia y De la Espriella</t>
+          <t>Entre lágrimas, adulta mayor pide que le devuelvan $700.000 que envió por error a una cuenta de Nequi</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/ivan-cepeda-abelardo-de-la-espriella-y-paloma-valencia-convierten-su-ropa-en-mensaje-clave-de-campana/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/entre-lagrimas-adulta-mayor-pide-que-le-devuelvan-700000-que-envio-por-error-a-una-cuenta-de-nequi/</t>
         </is>
       </c>
     </row>
@@ -1718,12 +1718,12 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Debate programático entre una política de paz o una política de seguridad que la desconozca o subordine</t>
+          <t>Karina García barajó la posibilidad de que su hija Isabella se sume a ‘La casa de los famosos Colombia’ en 2027 y le llovieron críticas</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/debate-programatico-entre-una-politica-de-paz-o-una-politica-de-seguridad-que-la-desconozca-o-subordine/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/karina-garcia-barajo-la-posibilidad-de-que-su-hija-isabella-se-sume-a-la-casa-de-los-famosos-colombia-en-2027-y-le-llovieron-criticas/</t>
         </is>
       </c>
     </row>
@@ -1745,12 +1745,12 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>IPS advierten que medida del Gobierno de aumentar el giro directo no resolverá por sí solo la crisis del sistema de salud: esto propusieron</t>
+          <t>Abelardo de la Espriella aseguró que defendería a Westcol si mata a un ladrón: “Así venga con un peluche, le disparas”</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/ips-advierten-que-medida-del-gobierno-de-aumentar-el-giro-directo-no-resolvera-por-si-solo-la-crisis-del-sistema-de-salud-esto-propusieron/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/abelardo-de-la-espriella-aseguro-que-defenderia-a-westcol-si-mata-a-un-ladron-asi-venga-con-un-peluche-le-disparas/</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1772,12 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Estados Alterados, Funk Tribu, Karen Lizarazo, Jungle y más: estos son los lanzamientos destacados de la semana</t>
+          <t>Colombia ante las urnas: Izquierda, derecha y un ‘outsider’ se disputan la presidencia</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/estados-alterados-funk-tribu-karen-lizarazo-jungle-y-mas-estos-son-los-lanzamientos-destacados-de-la-semana/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/colombia-ante-las-urnas-izquierda-derecha-y-un-outsider-se-disputan-la-presidencia/</t>
         </is>
       </c>
     </row>
@@ -1799,12 +1799,12 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Iván Duque resaltó la importancia de su gobierno para las elecciones de 2026:  dos de sus funcionarios podrán ser vicepresidente</t>
+          <t>Lo que esconde el clóset de los candidatos presidenciales: los mensajes en la ropa de Cepeda, Valencia y De la Espriella</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/ivan-duque-resalto-la-importancia-de-su-gobierno-para-las-elecciones-de-2026-dos-de-sus-funcionarios-podran-ser-vicepresidente/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/ivan-cepeda-abelardo-de-la-espriella-y-paloma-valencia-convierten-su-ropa-en-mensaje-clave-de-campana/</t>
         </is>
       </c>
     </row>
@@ -1826,12 +1826,12 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>La IA como herramienta de comunicación política en la campaña presidencial: ruido, emociones y degradación de la deliberación pública</t>
+          <t>Debate programático entre una política de paz o una política de seguridad que la desconozca o subordine</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/la-ia-como-herramienta-de-comunicacion-politica-en-la-campana-presidencial-ruido-emociones-y-degradacion-de-la-deliberacion-publica/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/debate-programatico-entre-una-politica-de-paz-o-una-politica-de-seguridad-que-la-desconozca-o-subordine/</t>
         </is>
       </c>
     </row>
@@ -1853,12 +1853,12 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Elementos comunes sobre la paz en el escenario electoral</t>
+          <t>IPS advierten que medida del Gobierno de aumentar el giro directo no resolverá por sí solo la crisis del sistema de salud: esto propusieron</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/los-denominadores-comunes-de-los-escenarios-electorales/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/ips-advierten-que-medida-del-gobierno-de-aumentar-el-giro-directo-no-resolvera-por-si-solo-la-crisis-del-sistema-de-salud-esto-propusieron/</t>
         </is>
       </c>
     </row>
@@ -1880,12 +1880,12 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Colombia 2026: realismo hemisférico para el próximo gobierno</t>
+          <t>Estados Alterados, Funk Tribu, Karen Lizarazo, Jungle y más: estos son los lanzamientos destacados de la semana</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/colombia-2026-realismo-hemisferico-para-el-proximo-gobierno/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/estados-alterados-funk-tribu-karen-lizarazo-jungle-y-mas-estos-son-los-lanzamientos-destacados-de-la-semana/</t>
         </is>
       </c>
     </row>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Gobernar en la polarización: El complejo escenario legislativo para Iván Cepeda</t>
+          <t>Iván Duque resaltó la importancia de su gobierno para las elecciones de 2026:  dos de sus funcionarios podrán ser vicepresidente</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/gobernar-en-la-polarizacion-el-complejo-escenario-legislativo-para-ivan-cepeda/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/ivan-duque-resalto-la-importancia-de-su-gobierno-para-las-elecciones-de-2026-dos-de-sus-funcionarios-podran-ser-vicepresidente/</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>La Procuraduría desplegará un ejército de vigilancia para las elecciones presidenciales en Colombia</t>
+          <t>La IA como herramienta de comunicación política en la campaña presidencial: ruido, emociones y degradación de la deliberación pública</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/la-procuraduria-desplegara-un-ejercito-de-vigilancia-para-las-elecciones-presidenciales-en-colombia/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/la-ia-como-herramienta-de-comunicacion-politica-en-la-campana-presidencial-ruido-emociones-y-degradacion-de-la-deliberacion-publica/</t>
         </is>
       </c>
     </row>
@@ -1961,19 +1961,19 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Nuevos detalles de la denuncia contra el senador Alejandro Bermeo: víctima relató amenazas, golpes y presunto abuso tras una relación de dos años</t>
+          <t>Elementos comunes sobre la paz en el escenario electoral</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/nuevos-detalles-de-la-denuncia-contra-el-senador-alejandro-bermeo-victima-relato-amenazas-golpes-y-presunto-abuso-tras-una-relacion-de-dos-anos/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/los-denominadores-comunes-de-los-escenarios-electorales/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 12:00 a. m.</t>
+          <t>31/05/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -1988,19 +1988,19 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Esposa de Santiago Botero habló del calvario que vivió junto al candidato: “Soporté muchos meses de violencia intrafamiliar”</t>
+          <t>Colombia 2026: realismo hemisférico para el próximo gobierno</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/30/esposa-de-santiago-botero-hablo-del-calvario-que-vivio-junto-al-candidato-soporte-muchos-meses-de-violencia-intrafamiliar/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/colombia-2026-realismo-hemisferico-para-el-proximo-gobierno/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 12:00 a. m.</t>
+          <t>31/05/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
@@ -2015,19 +2015,19 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Lanzan alerta desde la gobernación del Magdalena por posibles cortes de energía durante las elecciones presidenciales</t>
+          <t>Gobernar en la polarización: El complejo escenario legislativo para Iván Cepeda</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/30/lanzan-alerta-desde-la-gobernacion-del-magdalena-por-posibles-cortes-de-energia-durante-las-elecciones-presidenciales/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/gobernar-en-la-polarizacion-el-complejo-escenario-legislativo-para-ivan-cepeda/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 12:00 a. m.</t>
+          <t>31/05/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2042,19 +2042,19 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Gustavo Petro compartió una canción electrónica en sus redes sociales: “Entramos a nuevos géneros del techno”</t>
+          <t>La Procuraduría desplegará un ejército de vigilancia para las elecciones presidenciales en Colombia</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/30/gustavo-petro-compartio-una-cancion-electronica-en-sus-redes-sociales-entramos-a-nuevos-generos-del-techno/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/la-procuraduria-desplegara-un-ejercito-de-vigilancia-para-las-elecciones-presidenciales-en-colombia/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 12:00 a. m.</t>
+          <t>31/05/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Vicky Dávila respondió a Paloma Valencia y pidió unión para derrotar a Iván Cepeda: “No fue abandono, fue decepción”</t>
+          <t>Nuevos detalles de la denuncia contra el senador Alejandro Bermeo: víctima relató amenazas, golpes y presunto abuso tras una relación de dos años</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/30/vicky-davila-respondio-a-paloma-valencia-y-pidio-union-para-derrotar-a-ivan-cepeda-no-fue-abandono-fue-decepcion/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/nuevos-detalles-de-la-denuncia-contra-el-senador-alejandro-bermeo-victima-relato-amenazas-golpes-y-presunto-abuso-tras-una-relacion-de-dos-anos/</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Armando Benedetti anticipó que buscará la Alcaldía de Barranquilla después de que termine el Gobierno Petro: “Hay una oportunidad”</t>
+          <t>Esposa de Santiago Botero habló del calvario que vivió junto al candidato: “Soporté muchos meses de violencia intrafamiliar”</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/30/armando-benedetti-anticipo-que-buscara-la-alcaldia-de-barranquilla-despues-que-termine-el-gobierno-petro-hay-una-oportunidad/</t>
+          <t>https://www.infobae.com/colombia/2026/05/30/esposa-de-santiago-botero-hablo-del-calvario-que-vivio-junto-al-candidato-soporte-muchos-meses-de-violencia-intrafamiliar/</t>
         </is>
       </c>
     </row>
@@ -2123,19 +2123,19 @@
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Así funciona la ley colombiana para quienes deciden no votar: no tendría beneficios</t>
+          <t>Lanzan alerta desde la gobernación del Magdalena por posibles cortes de energía durante las elecciones presidenciales</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/30/asi-funciona-la-ley-colombiana-para-quienes-deciden-no-votar-no-tendria-beneficios/</t>
+          <t>https://www.infobae.com/colombia/2026/05/30/lanzan-alerta-desde-la-gobernacion-del-magdalena-por-posibles-cortes-de-energia-durante-las-elecciones-presidenciales/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 09:00 p. m.</t>
+          <t>30/05/2026 09:30 p. m.</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2145,24 +2145,24 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Torre de Tokio: vecinos espías</t>
+          <t>Resultados Caribeña Noche, último sorteo hoy sábado, 30 de mayo de 2026: números ganadores</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/mundo/columna-torre-de-tokio-vecinos-espias/</t>
+          <t>https://www.noticiascaracol.com/economia/resultados-caribena-noche-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-rg10</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:58 p. m.</t>
+          <t>30/05/2026 09:30 p. m.</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -2172,24 +2172,24 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>El montaje judicial que tuvo al borde de la muerte a una lideresa de El Salado</t>
+          <t>Resultados Sinuano Noche, último sorteo hoy sábado, 30 de mayo de 2026: números ganadores</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/judicial/el-montaje-judicial-contra-una-lideresa-de-el-salado-que-la-tuvo-al-borde-de-la-muerte/</t>
+          <t>https://www.noticiascaracol.com/economia/resultados-sinuano-noche-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-rg10</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:55 p. m.</t>
+          <t>30/05/2026 09:15 p. m.</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2199,24 +2199,24 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Una mujer permanece en estado crítico luego de ser quemada por su expareja en Neiva</t>
+          <t>Resultados Dorado Noche, último sorteo hoy sábado, 30 de mayo de 2026: números ganadores</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/una-mujer-fue-rociada-con-gasolina-y-quemada-por-su-expareja-en-neiva-el-agresor-esta-libre/</t>
+          <t>https://www.noticiascaracol.com/economia/resultados-dorado-noche-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-rg10</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:25 p. m.</t>
+          <t>30/05/2026 08:59 p. m.</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
@@ -2226,24 +2226,24 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>SpaceX, OpenAI y Anthropic impulsan nueva ola de inversión en Asia</t>
+          <t>Colombia, lista para ir a las urnas y elegir a su nuevo presidente(a)</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/economia/empresas/el-exito-de-spacex-y-openai-impulsa-apuestas-por-los-proximos-ganadores-asiaticos-en-ia/</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/colombia-lista-para-ir-a-las-urnas-y-elegir-a-su-nuevo-presidentea-cb20</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:21 p. m.</t>
+          <t>30/05/2026 08:06 p. m.</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2253,24 +2253,24 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Movida Electoral: Así fue el último día de los candidatos presidenciales antes de elección</t>
+          <t>Andrés Llinás y una carta abierta por mal semestre de Millonarios; "no estuvimos a la altura"</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/politica/elecciones-colombia-2026/cepeda-realizo-155-actos-publicos-de-la-espriella-aceptaria-curul-de-oposicion-si-pierde-valencia-recorre-iglesias-noticias-hoy/</t>
+          <t>https://www.noticiascaracol.com/golcaracol/futbol-colombiano/andres-llinas-y-una-carta-abierta-por-mal-semestre-de-millonarios-no-estuvimos-a-la-altura-rg10</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:05 p. m.</t>
+          <t>30/05/2026 06:50 p. m.</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -2280,24 +2280,24 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>¿Quiénes encabezan la disputa por la presidencia? Todo lo que debe saber de los candidatos</t>
+          <t>Luis Javier Suárez y sus goles con Sporting Lisboa le valieron un reconocimiento en Portugal</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/politica/elecciones-colombia-2026/candidatos-presidenciales-quienes-son-los-aspirantes-que-encabezan-la-campana-perfiles-y-equipos-noticias-hoy/</t>
+          <t>https://www.noticiascaracol.com/golcaracol/colombianos-en-el-exterior/luis-javier-suarez-y-sus-goles-con-sporting-lisboa-le-valieron-un-reconocimiento-en-portugal-rg10</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:01 p. m.</t>
+          <t>30/05/2026 04:23 p. m.</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2307,24 +2307,24 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Entre euforia, disturbios y cientos de detenidos, París festeja su segunda Orejona</t>
+          <t>Video | Encuentran sin vida a joven que cayó al embalse de Guatapé durante fiesta en una embarcación</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/mundo/entre-euforia-disturbios-y-cientos-de-detenidos-paris-festeja-su-segunda-orejona/</t>
+          <t>https://www.noticiascaracol.com/colombia/video-encuentran-sin-vida-a-joven-que-cayo-al-embalse-de-guatape-durante-fiesta-en-una-embarcacion-rg10</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:00 p. m.</t>
+          <t>30/05/2026 04:15 p. m.</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -2334,24 +2334,24 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Receta para preparar lomo con salsa de hongos y pimienta</t>
+          <t>Murió Kelly Curtis, actriz y hermana de Jamie Lee Curtis, a los 69 años</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/gastronomia-y-recetas/receta-para-preparar-lomo-con-salsa-de-hongos-y-pimienta/</t>
+          <t>https://www.noticiascaracol.com/entretenimiento/murio-kelly-curtis-actriz-y-hermana-de-jamie-lee-curtis-a-los-69-anos-cb20</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:00 p. m.</t>
+          <t>30/05/2026 03:49 p. m.</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2361,24 +2361,24 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>5 novedades del primer SUV eléctrico de Subaru en Colombia: Trailseeker</t>
+          <t>Resultados Super Astro Sol hoy, sábado 30 de mayo de 2026: números ganadores del último sorteo</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/autos/5-novedades-del-primer-suv-electrico-de-subaru-en-colombia-trailseeker/</t>
+          <t>https://www.noticiascaracol.com/economia/resultados-super-astro-sol-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-del-ultimo-sorteo-so35</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 07:21 p. m.</t>
+          <t>30/05/2026 03:21 p. m.</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -2388,24 +2388,24 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>El nuevo video de Dilan Cruz reabrió el debate, pero no cambió el expediente</t>
+          <t>¿Mercenarios colombianos en México? Así carteles de la droga estarían reclutando exmilitares</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/judicial/dilan-cruz-el-video-que-se-volvio-viral-y-la-evidencia-que-ya-estaba-en-el-proceso/</t>
+          <t>https://www.noticiascaracol.com/mundo/mercenarios-colombianos-en-mexico-asi-carteles-de-la-droga-estarian-reclutando-exmilitares-rg10</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:59 p. m.</t>
+          <t>30/05/2026 02:07 p. m.</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2420,19 +2420,19 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Colombia, lista para ir a las urnas y elegir a su nuevo presidente(a)</t>
+          <t>Resultados Dorado Tarde hoy, sábado 30 de mayo de 2026: números ganadores del último sorteo</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/colombia-lista-para-ir-a-las-urnas-y-elegir-a-su-nuevo-presidentea-cb20</t>
+          <t>https://www.noticiascaracol.com/economia/resultados-dorado-tarde-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-del-ultimo-sorteo-so35</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:06 p. m.</t>
+          <t>30/05/2026 02:04 p. m.</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
@@ -2447,19 +2447,19 @@
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Andrés Llinás y una carta abierta por mal semestre de Millonarios; "no estuvimos a la altura"</t>
+          <t>Resultados Caribeña Día hoy, sábado 30 de mayo de 2026: números ganadores del último sorteo</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/golcaracol/futbol-colombiano/andres-llinas-y-una-carta-abierta-por-mal-semestre-de-millonarios-no-estuvimos-a-la-altura-rg10</t>
+          <t>https://www.noticiascaracol.com/economia/resultados-caribena-dia-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-del-ultimo-sorteo-so35</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 06:50 p. m.</t>
+          <t>30/05/2026 01:55 p. m.</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2474,19 +2474,19 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Luis Javier Suárez y sus goles con Sporting Lisboa le valieron un reconocimiento en Portugal</t>
+          <t>Resultados Sinuano Día hoy, sábado 30 de mayo de 2026: números ganadores del último sorteo</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/golcaracol/colombianos-en-el-exterior/luis-javier-suarez-y-sus-goles-con-sporting-lisboa-le-valieron-un-reconocimiento-en-portugal-rg10</t>
+          <t>https://www.noticiascaracol.com/economia/resultados-sinuano-dia-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-del-ultimo-sorteo-so35</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 04:23 p. m.</t>
+          <t>30/05/2026 01:42 p. m.</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
@@ -2501,19 +2501,19 @@
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Video | Encuentran sin vida a joven que cayó al embalse de Guatapé durante fiesta en una embarcación</t>
+          <t>“No tengo palabras”: Alfredo Iván Guzmán, hijo del exalcalde de Tame, tras recuperar su libertad</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/video-encuentran-sin-vida-a-joven-que-cayo-al-embalse-de-guatape-durante-fiesta-en-una-embarcacion-rg10</t>
+          <t>https://www.noticiascaracol.com/colombia/no-tengo-palabras-alfredo-ivan-guzman-hijo-del-exalcalde-de-tame-tras-recuperar-su-libertad-rg10</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 04:15 p. m.</t>
+          <t>30/05/2026 12:54 p. m.</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2528,19 +2528,19 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Murió Kelly Curtis, actriz y hermana de Jamie Lee Curtis, a los 69 años</t>
+          <t>Resultados Chontico Día hoy, sábado 30 de mayo de 2026: números ganadores</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/entretenimiento/murio-kelly-curtis-actriz-y-hermana-de-jamie-lee-curtis-a-los-69-anos-cb20</t>
+          <t>https://www.noticiascaracol.com/economia/resultados-chontico-dia-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-so35</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 03:49 p. m.</t>
+          <t>30/05/2026 12:38 p. m.</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -2555,19 +2555,19 @@
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Resultados Super Astro Sol hoy, sábado 30 de mayo de 2026: números ganadores del último sorteo</t>
+          <t>Vanessa Pulgarín, la colombiana que logró la primera corona de Miss Grand International All Stars</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/resultados-super-astro-sol-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-del-ultimo-sorteo-so35</t>
+          <t>https://www.noticiascaracol.com/entretenimiento/vanessa-pulgarin-la-colombiana-que-logro-la-primera-corona-de-miss-grand-international-all-stars-rg10</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 03:21 p. m.</t>
+          <t>30/05/2026 11:39 a. m.</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2582,19 +2582,19 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>¿Mercenarios colombianos en México? Así carteles de la droga estarían reclutando exmilitares</t>
+          <t>El Parque Nacional Natural Tayrona cerrará sus puertas por 15 días: ¿por qué?</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/mundo/mercenarios-colombianos-en-mexico-asi-carteles-de-la-droga-estarian-reclutando-exmilitares-rg10</t>
+          <t>https://www.noticiascaracol.com/colombia/el-parque-nacional-natural-tayrona-cerrara-sus-puertas-por-15-dias-por-que-rg10</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 02:07 p. m.</t>
+          <t>30/05/2026 11:36 a. m.</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
@@ -2609,19 +2609,19 @@
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Resultados Dorado Tarde hoy, sábado 30 de mayo de 2026: números ganadores del último sorteo</t>
+          <t>Polémica en final de Champions League; ¿era mano en el Arsenal y penalti para el PSG?</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/resultados-dorado-tarde-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-del-ultimo-sorteo-so35</t>
+          <t>https://www.noticiascaracol.com/golcaracol/polemica-en-final-de-champions-league-era-mano-en-el-arsenal-y-penalti-para-el-psg-rg10</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 02:04 p. m.</t>
+          <t>30/05/2026 11:20 a. m.</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2636,19 +2636,19 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Resultados Caribeña Día hoy, sábado 30 de mayo de 2026: números ganadores del último sorteo</t>
+          <t>Ganadores del Desafío Siglo XXI se casarán: video de la emotiva propuesta de matrimonio</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/resultados-caribena-dia-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-del-ultimo-sorteo-so35</t>
+          <t>https://www.noticiascaracol.com/entretenimiento/ganadores-del-desafio-siglo-xxi-se-casaran-video-de-la-emotiva-propuesta-de-matrimonio-rs15</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 01:55 p. m.</t>
+          <t>30/05/2026 10:45 a. m.</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
@@ -2663,19 +2663,19 @@
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Resultados Sinuano Día hoy, sábado 30 de mayo de 2026: números ganadores del último sorteo</t>
+          <t>Video l Tim Payne, el futbolista viral, disputó un torneo en Colombia: vea cómo lucía en el 2011</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/resultados-sinuano-dia-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-del-ultimo-sorteo-so35</t>
+          <t>https://www.noticiascaracol.com/lomastrinado/video-l-tim-payne-el-futbolista-viral-disputo-un-torneo-en-colombia-vea-como-lucia-en-el-2011-rs15</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 01:42 p. m.</t>
+          <t>30/05/2026 10:42 a. m.</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -2690,19 +2690,19 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>“No tengo palabras”: Alfredo Iván Guzmán, hijo del exalcalde de Tame, tras recuperar su libertad</t>
+          <t>Así está la salud de Donald Trump, según el más reciente chequeo médico de la Casa Blanca</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/no-tengo-palabras-alfredo-ivan-guzman-hijo-del-exalcalde-de-tame-tras-recuperar-su-libertad-rg10</t>
+          <t>https://www.noticiascaracol.com/mundo/asi-esta-la-salud-de-donald-trump-segun-el-mas-reciente-chequeo-medico-de-la-casa-blanca-cb20</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 12:54 p. m.</t>
+          <t>30/05/2026 10:23 a. m.</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
@@ -2717,19 +2717,19 @@
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Resultados Chontico Día hoy, sábado 30 de mayo de 2026: números ganadores</t>
+          <t>Resultados Dorado Mañana hoy, sábado 30 de mayo de 2026: números ganadores del último sorteo</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/resultados-chontico-dia-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-so35</t>
+          <t>https://www.noticiascaracol.com/economia/resultados-dorado-manana-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-del-ultimo-sorteo-so35</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 12:38 p. m.</t>
+          <t>30/05/2026 10:00 a. m.</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -2744,19 +2744,19 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Vanessa Pulgarín, la colombiana que logró la primera corona de Miss Grand International All Stars</t>
+          <t>Elecciones presidenciales 2026: cierres viales y desvíos clave de movilidad en Bogotá</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/entretenimiento/vanessa-pulgarin-la-colombiana-que-logro-la-primera-corona-de-miss-grand-international-all-stars-rg10</t>
+          <t>https://www.noticiascaracol.com/colombia/bogota-elecciones-presidenciales-2026-cierres-viales-y-desvios-clave-de-movilidad-en-bogota-rg10</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 11:39 a. m.</t>
+          <t>30/05/2026 09:30 a. m.</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
@@ -2771,19 +2771,19 @@
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>El Parque Nacional Natural Tayrona cerrará sus puertas por 15 días: ¿por qué?</t>
+          <t>Cancillería se pronunció tras anuncio de Daniel Noboa sobre la eliminación de aranceles a Colombia</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/el-parque-nacional-natural-tayrona-cerrara-sus-puertas-por-15-dias-por-que-rg10</t>
+          <t>https://www.noticiascaracol.com/colombia/cancilleria-se-pronuncio-tras-anuncio-de-daniel-noboa-sobre-la-eliminacion-de-aranceles-a-colombia-rg10</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 11:36 a. m.</t>
+          <t>30/05/2026 08:45 a. m.</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -2798,19 +2798,19 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Polémica en final de Champions League; ¿era mano en el Arsenal y penalti para el PSG?</t>
+          <t>Altos mandos militares de Cuba y EE. UU. se reunieron: ¿cuáles fueron los temas tratados?</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/golcaracol/polemica-en-final-de-champions-league-era-mano-en-el-arsenal-y-penalti-para-el-psg-rg10</t>
+          <t>https://www.noticiascaracol.com/mundo/altos-mandos-militares-de-cuba-y-ee-uu-se-reunieron-cuales-fueron-los-temas-tratados-cb20</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 11:20 a. m.</t>
+          <t>30/05/2026 08:22 a. m.</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
@@ -2825,19 +2825,19 @@
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Ganadores del Desafío Siglo XXI se casarán: video de la emotiva propuesta de matrimonio</t>
+          <t>Supersalud ordenó cierre del servicio de cirugía estética de la Clínica de Obesidad y Envejecimiento</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/entretenimiento/ganadores-del-desafio-siglo-xxi-se-casaran-video-de-la-emotiva-propuesta-de-matrimonio-rs15</t>
+          <t>https://www.noticiascaracol.com/colombia/bogota/supersalud-ordeno-cierre-del-servicio-de-cirugia-estetica-de-la-clinica-de-obesidad-y-envejecimiento-rg10</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 10:45 a. m.</t>
+          <t>30/05/2026 09:27 p. m.</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -2847,24 +2847,24 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Video l Tim Payne, el futbolista viral, disputó un torneo en Colombia: vea cómo lucía en el 2011</t>
+          <t>Elecciones 2026: ¿cuántos votos se necesitan para ganar en primera vuelta?</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/lomastrinado/video-l-tim-payne-el-futbolista-viral-disputo-un-torneo-en-colombia-vea-como-lucia-en-el-2011-rs15</t>
+          <t>https://canaltrece.com.co/noticias/elecciones-2026-cuantos-votos-se-necesitan-para-ganar-en-primera-vuelta/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 10:42 a. m.</t>
+          <t>30/05/2026 09:09 p. m.</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
@@ -2874,24 +2874,24 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Así está la salud de Donald Trump, según el más reciente chequeo médico de la Casa Blanca</t>
+          <t>Segunda vuelta presidencial 2026: fecha y cómo funcionaría en Colombia</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/mundo/asi-esta-la-salud-de-donald-trump-segun-el-mas-reciente-chequeo-medico-de-la-casa-blanca-cb20</t>
+          <t>https://canaltrece.com.co/noticias/segunda-vuelta-presidencial-2026-fecha-y-como-funcionaria-en-colombia/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 10:23 a. m.</t>
+          <t>30/05/2026 08:33 p. m.</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -2901,24 +2901,24 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Resultados Dorado Mañana hoy, sábado 30 de mayo de 2026: números ganadores del último sorteo</t>
+          <t>Elecciones 2026: ¿a qué hora se conocerán los resultados en Colombia?</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/resultados-dorado-manana-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-del-ultimo-sorteo-so35</t>
+          <t>https://canaltrece.com.co/noticias/elecciones-2026-a-que-hora-se-conoceran-los-resultados-en-colombia/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 10:00 a. m.</t>
+          <t>30/05/2026 08:26 p. m.</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
@@ -2928,24 +2928,24 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Elecciones presidenciales 2026: cierres viales y desvíos clave de movilidad en Bogotá</t>
+          <t>Elecciones 2026: cómo votar en el exterior y consultar su puesto</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/bogota-elecciones-presidenciales-2026-cierres-viales-y-desvios-clave-de-movilidad-en-bogota-rg10</t>
+          <t>https://canaltrece.com.co/noticias/elecciones-2026-como-votar-en-el-exterior-y-consultar-su-puesto/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 09:30 a. m.</t>
+          <t>30/05/2026 08:14 p. m.</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -2955,24 +2955,24 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Cancillería se pronunció tras anuncio de Daniel Noboa sobre la eliminación de aranceles a Colombia</t>
+          <t>¿Dónde votar? Consulte su puesto para las elecciones presidenciales 2026</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/cancilleria-se-pronuncio-tras-anuncio-de-daniel-noboa-sobre-la-eliminacion-de-aranceles-a-colombia-rg10</t>
+          <t>https://canaltrece.com.co/noticias/donde-votar-consulte-su-puesto-para-las-elecciones-presidenciales-2026/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:45 a. m.</t>
+          <t>30/05/2026 08:03 p. m.</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
@@ -2982,24 +2982,24 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Altos mandos militares de Cuba y EE. UU. se reunieron: ¿cuáles fueron los temas tratados?</t>
+          <t>Tarjetón elecciones 2026: ¿qué pasa con votos por candidatos retirados?</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/mundo/altos-mandos-militares-de-cuba-y-ee-uu-se-reunieron-cuales-fueron-los-temas-tratados-cb20</t>
+          <t>https://canaltrece.com.co/noticias/tarjeton-elecciones-2026-que-pasa-con-votos-por-candidatos-retirados/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:22 a. m.</t>
+          <t>30/05/2026 07:58 p. m.</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3009,24 +3009,24 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Supersalud ordenó cierre del servicio de cirugía estética de la Clínica de Obesidad y Envejecimiento</t>
+          <t>Elecciones 2026: Procurador Eljach llama a votar temprano y en paz</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/bogota/supersalud-ordeno-cierre-del-servicio-de-cirugia-estetica-de-la-clinica-de-obesidad-y-envejecimiento-rg10</t>
+          <t>https://canaltrece.com.co/noticias/elecciones-2026-procurador-eljach-llama-a-votar-temprano-y-en-paz/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 07:52 a. m.</t>
+          <t>30/05/2026 07:52 p. m.</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
@@ -3036,24 +3036,24 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Europa vs. Sudamérica: quién ha ganado más Mundiales en la historia</t>
+          <t>Elecciones presidenciales 2026: cómo marcar la tarjeta electoral</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/golcaracol/europa-vs-sudamerica-quien-ha-ganado-mas-mundiales-en-la-historia-cb20</t>
+          <t>https://canaltrece.com.co/noticias/elecciones-presidenciales-2026-como-marcar-la-tarjeta-electoral/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 07:26 a. m.</t>
+          <t>30/05/2026 05:48 p. m.</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3063,24 +3063,24 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Murió Edgar Morin, uno de los filósofos contemporáneos más influyentes de Francia, a los 104 años</t>
+          <t>¡No lo bote! Las marcas y beneficios legales que premian su certificado electoral este 31 de mayo</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/mundo/murio-edgar-morin-uno-de-los-filosofos-contemporaneos-mas-influyentes-de-francia-a-los-104-anos-cb20</t>
+          <t>https://canaltrece.com.co/noticias/no-lo-bote-las-marcas-y-beneficios-legales-que-premian-su-certificado-electoral-este-31-de-mayo/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 06:43 a. m.</t>
+          <t>30/05/2026 05:39 p. m.</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
@@ -3090,24 +3090,24 @@
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Bombazo en la Premier League; Liverpool tomó radical decisión con Arne Slot</t>
+          <t>Terremoto político y judicial: Santiago Botero Jaramillo, denunciado por presunta violencia intrafamiliar</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/golcaracol/bombazo-en-la-premier-league-liverpool-tomo-radical-decision-con-arne-slot-cb20</t>
+          <t>https://canaltrece.com.co/noticias/terremoto-politico-y-judicial-santiago-botero-jaramillo-denunciado-por-presunta-violencia-intrafamiliar/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:54 p. m.</t>
+          <t>29/05/2026 11:07 a. m.</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3117,24 +3117,24 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Estos son los 11 candidatos a la Presidencia de Colombia 2026</t>
+          <t>Myke Towers confirma concierto en Bogotá con su gira “Trap Kings”</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/cuales-son-los-11-candidatos-a-la-presidencia-de-colombia-2026-1026269</t>
+          <t>https://canaltrece.com.co/noticias/myke-towers-confirma-concierto-en-bogota-con-su-gira-trap-kings/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 07:44 p. m.</t>
+          <t>29/05/2026 10:51 a. m.</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
@@ -3144,24 +3144,24 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Secuestró y violó a una niña de cuatro años tras engañar a su madre con regalarle un mercado en Cali</t>
+          <t>Acoso callejero Colombia: el 89% de las mujeres afirma haberlo sufrido</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/secuestro-y-violo-a-una-nina-de-cuatro-anos-tras-enganar-a-su-madre-con-regalarle-un-mercado-en-cali-1026264</t>
+          <t>https://canaltrece.com.co/noticias/acoso-callejero-colombia-mujeres/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 04:28 p. m.</t>
+          <t>29/05/2026 10:44 a. m.</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3171,24 +3171,24 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Cadáveres de disidentes fueron cargados con explosivos para detonarlos en traslado a Medicina Legal</t>
+          <t>Outdoor femenino Colombia: la tendencia que une aventura, naturaleza y comunidad</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/cadaveres-de-disidentes-fueron-cargados-con-explosivos-para-detonarlos-en-traslado-a-medicina-legal-1026237</t>
+          <t>https://canaltrece.com.co/noticias/outdoor-femenino-colombia/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 03:50 p. m.</t>
+          <t>29/05/2026 10:35 a. m.</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
@@ -3198,24 +3198,24 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Más de 700 familias damnificadas y con el agua a la cintura al desbordarse tres ríos en Cabuyaro, Meta</t>
+          <t>Bibliotecas para inspirar Cali: nueva apuesta por la lectura y los proyectos de vida</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/mas-de-700-familias-damnificadas-y-con-el-agua-a-la-cintura-por-el-desbordamiento-de-tres-rios-en-cabuyaro-meta-1026229</t>
+          <t>https://canaltrece.com.co/noticias/bibliotecas-para-inspirar-cali/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 03:32 p. m.</t>
+          <t>29/05/2026 10:32 a. m.</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3225,24 +3225,24 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Elecciones Colombia: recompensas de $50 y $200 millones por actores armados y planes de atentados</t>
+          <t>Detección temprana cáncer de mama Colombia: la importancia de las redes de apoyo</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/elecciones-colombia-recompensas-de-50-y-200-millones-por-actores-armados-y-planes-de-atentados-1026224</t>
+          <t>https://canaltrece.com.co/noticias/deteccion-temprana-cancer-de-mama-colombia/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 02:52 p. m.</t>
+          <t>29/05/2026 10:27 a. m.</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
@@ -3252,24 +3252,24 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Video revelador: hallan el cuerpo del joven de 22 años que se lanzó al embalse de Guatapé huyendo de agresión</t>
+          <t>Cuidado del cabello y la piel en vacaciones: errores que debes evitar</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/video-del-joven-de-22-anos-hallado-muerto-en-guatape-1026206</t>
+          <t>https://canaltrece.com.co/noticias/cuidado-del-cabello-y-la-piel-en-vacaciones/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 01:36 p. m.</t>
+          <t>29/05/2026 10:18 a. m.</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -3279,24 +3279,24 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Bogotá entrará en alerta amarilla hospitalaria por elecciones: ¿qué significa esto?</t>
+          <t>Bebé de 6 meses El Espinal: avanzan investigaciones tras su fallecimiento</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/bogota-entrara-en-alerta-amarilla-hospitalaria-por-elecciones-1025976</t>
+          <t>https://canaltrece.com.co/noticias/bebe-de-6-meses-el-espinal/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 12:56 p. m.</t>
+          <t>29/05/2026 09:10 a. m.</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
@@ -3306,24 +3306,24 @@
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>“Se está dejando utilizar”: Santiago Botero se pronunció tras el desalojo en su vivienda en Cartagena</t>
+          <t>Fiesta en El Campín: Morat cantará en la despedida de la Selección Colombia rumbo al Mundial 2026</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/santiago-botero-se-pronuncio-tras-escandalo-de-desalojo-de-su-vivienda-1026192</t>
+          <t>https://canaltrece.com.co/noticias/fiesta-en-el-campin-morat-cantara-en-la-despedida-de-la-seleccion-colombia-rumbo-al-mundial-2026/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 12:07 p. m.</t>
+          <t>29/05/2026 09:03 a. m.</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -3333,24 +3333,24 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Autoridades ordenaron desalojo a propiedad de Santiago Botero: es acusado de violencia intrafamiliar</t>
+          <t>Orgullo colombiano: Kapo es coronado como ‘Compositor del Año’ en los SESAC Latina Music Awards 2026</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/santiago-botero-es-desalojado-y-acusado-de-violencia-intrafamiliar-1026185</t>
+          <t>https://canaltrece.com.co/noticias/orgullo-colombiano-kapo-es-coronado-como-compositor-del-ano-en-los-sesac-latina-music-awards-2026/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 11:43 a. m.</t>
+          <t>29/05/2026 08:56 a. m.</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
@@ -3360,24 +3360,24 @@
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>Colombia, lista para votar: el llamado a respetar los resultados</t>
+          <t>De Medellín para el mundo: elkno enciende la escena urbana con su dancehall “Ritmo”</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/colombia-lista-para-votar-el-llamado-a-respetar-los-resultados-1026172</t>
+          <t>https://canaltrece.com.co/noticias/de-medellin-para-el-mundo-elkno-enciende-la-escena-urbana-con-su-dancehall-ritmo/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:53 p. m.</t>
+          <t>29/05/2026 08:53 a. m.</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3387,24 +3387,24 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Video muestra el momento exacto en que meteoro cae en EE. UU. con fuerza de 300 toneladas de TNT</t>
+          <t>Cine colombiano: ‘VOLAR’ llega a las salas con un retrato íntimo de la soledad en Bogotá</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/mundo/video-muestra-el-momento-exacto-en-que-meteoro-cae-en-ee-uu-con-fuerza-de-300-toneladas-de-tnt-cb20</t>
+          <t>https://canaltrece.com.co/noticias/cine-colombiano-volar-llega-a-las-salas-con-un-retrato-intimo-de-la-soledad-en-bogota/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:51 p. m.</t>
+          <t>29/05/2026 08:49 a. m.</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
@@ -3414,24 +3414,24 @@
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>Super Astro Luna, resultado del último sorteo hoy sábado 30 de mayo de 2026</t>
+          <t>Desde República Dominicana para el despecho: Amneliz debuta en la música popular con “El Desquite”</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/super-astro-luna-resultado-del-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-so35</t>
+          <t>https://canaltrece.com.co/noticias/desde-republica-dominicana-para-el-despecho-amneliz-debuta-en-la-musica-popular-con-el-desquite/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:51 p. m.</t>
+          <t>29/05/2026 08:45 a. m.</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3441,24 +3441,24 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Caribeña Noche, resultado del último sorteo hoy sábado 30 de mayo de 2026</t>
+          <t>Giro en el caso de Mía Cataleya: Revelan crudos detalles de su ingreso al hospital y una captura en El Espinal</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/caribena-noche-resultado-del-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-so35</t>
+          <t>https://canaltrece.com.co/noticias/giro-en-el-caso-de-mia-cataleya-revelan-crudos-detalles-de-su-ingreso-al-hospital-y-una-captura-en-el-espinal/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:51 p. m.</t>
+          <t>29/05/2026 08:24 a. m.</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
@@ -3468,24 +3468,24 @@
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>Sinuano Noche, resultado del último sorteo hoy sábado 30 de mayo de 2026</t>
+          <t>«Vi una pierna afuera»: Los crudos testimonios del hallazgo del profesor Kevin Santiago Ángel en Kennedy</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/sinuano-noche-resultado-del-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-so35</t>
+          <t>https://canaltrece.com.co/noticias/vi-una-pierna-afuera-los-crudos-testimonios-del-hallazgo-del-profesor-kevin-santiago-angel-en-kennedy/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:51 p. m.</t>
+          <t>29/05/2026 08:12 a. m.</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -3495,24 +3495,24 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Resultados del Dorado Noche: último sorteo hoy, sábado 30 de mayo de 2026, números ganadores</t>
+          <t>Giro en el caso de Ana María Meza: Fiscalía confirma que se investiga como presunto feminicidio</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/resultados-del-dorado-noche-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-so35</t>
+          <t>https://canaltrece.com.co/noticias/giro-en-el-caso-de-ana-maria-meza-fiscalia-confirma-que-se-investiga-como-presunto-feminicidio/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:50 p. m.</t>
+          <t>29/05/2026 08:08 a. m.</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
@@ -3522,24 +3522,24 @@
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>Loterías de Boyacá, Cauca, Extra de Colombia y Baloto: resultados sorteos hoy sábado 30 de mayo</t>
+          <t>El silencio forzado de Afganistán: El año en que las mujeres perdieron el derecho a existir en público</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/loterias-de-boyaca-cauca-extra-de-colombia-y-baloto-resultados-sorteos-hoy-sabado-30-de-mayo-so35</t>
+          <t>https://canaltrece.com.co/noticias/el-silencio-forzado-de-afganistan-el-ano-en-que-las-mujeres-perdieron-el-derecho-a-existir-en-publico/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:50 p. m.</t>
+          <t>28/05/2026 11:24 a. m.</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -3549,24 +3549,24 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Baloto y Revancha, resultados del último sorteo hoy sábado 30 de mayo de 2026</t>
+          <t>Jóvenes elecciones Colombia 2026: TikTok e IA cambian las campañas</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/baloto-y-revancha-resultados-del-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-so35</t>
+          <t>https://canaltrece.com.co/noticias/jovenes-elecciones-colombia-2026/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:50 p. m.</t>
+          <t>28/05/2026 11:18 a. m.</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>Extra de Colombia, resultados del último sorteo de este sábado 30 de mayo de 2026</t>
+          <t>Seguridad en vehículos de trabajo: la tecnología redefine el transporte de carga</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/extra-de-colombia-resultados-del-ultimo-sorteo-de-este-sabado-30-de-mayo-de-2026-so35</t>
+          <t>https://canaltrece.com.co/noticias/seguridad-en-vehiculos-de-trabajo/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:49 p. m.</t>
+          <t>28/05/2026 10:45 a. m.</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -3603,24 +3603,24 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Lotería del Cauca sábado 30 de mayo de 2026, resultados del último sorteo, premio mayor y secos</t>
+          <t>De Mar y Río lanza “Cantaré”, un homenaje al Pacífico colombiano</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/loteria-del-cauca-sabado-30-de-mayo-de-2026-resultados-del-ultimo-sorteo-premio-mayor-y-secos-so35</t>
+          <t>https://canaltrece.com.co/noticias/de-mar-y-rio-lanza-cantare-un-homenaje-al-pacifico-colombiano/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:49 p. m.</t>
+          <t>28/05/2026 10:04 a. m.</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
@@ -3630,24 +3630,24 @@
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>Lotería Boyacá, resultados del último sorteo hoy sábado 30 de mayo de 2026</t>
+          <t>Helipuertos en Bogotá: la nueva tendencia para vivir experiencias exclusivas</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/loteria-boyaca-resultados-del-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-so35</t>
+          <t>https://canaltrece.com.co/noticias/helipuertos-en-bogota-experiencias/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:46 p. m.</t>
+          <t>30/05/2026 09:07 p. m.</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -3657,24 +3657,24 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Al menos seis personas estarían atrapadas tras el colapso de un edificio en Nueva Delhi</t>
+          <t>MICROLINGOTES</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/mundo/al-menos-seis-personas-estarian-atrapadas-tras-el-colapso-de-un-edificio-en-nueva-delhi-cb20</t>
+          <t>https://www.elespectador.com/opinion/columnistas/oscar-alarcon/microlingotes-247/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:04 p. m.</t>
+          <t>30/05/2026 09:00 p. m.</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
@@ -3684,24 +3684,24 @@
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>Encuentran muerta a adolescente de 14 años desaparecida hace una semana; investigan homicidio</t>
+          <t>Torre de Tokio: vecinos espías</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/mundo/encuentran-muerta-a-adolescente-de-14-anos-desaparecida-hace-una-semana-investigan-homicidio-rs15</t>
+          <t>https://www.elespectador.com/mundo/columna-torre-de-tokio-vecinos-espias/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:53 p. m.</t>
+          <t>30/05/2026 08:58 p. m.</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -3711,24 +3711,24 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Cristian Mosquera fue tendencia tras cometer penal en la final que perdió Arsenal ante PSG</t>
+          <t>El montaje judicial que tuvo al borde de la muerte a una lideresa de El Salado</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/deportes/2026/05/30/cristian-mosquera-fue-tendencia-tras-cometer-penal-en-la-final-que-perdio-arsenal-ante-psg/</t>
+          <t>https://www.elespectador.com/judicial/el-montaje-judicial-contra-una-lideresa-de-el-salado-que-la-tuvo-al-borde-de-la-muerte/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:53 p. m.</t>
+          <t>30/05/2026 08:55 p. m.</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
@@ -3738,24 +3738,24 @@
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>Deportes</t>
+          <t>Una mujer permanece en estado crítico luego de ser quemada por su expareja en Neiva</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/deportes/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/una-mujer-fue-rociada-con-gasolina-y-quemada-por-su-expareja-en-neiva-el-agresor-esta-libre/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:46 p. m.</t>
+          <t>30/05/2026 08:25 p. m.</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -3765,24 +3765,24 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Más de 300 detenidos en Francia tras los disturbios por la victoria del PSG</t>
+          <t>SpaceX, OpenAI y Anthropic impulsan nueva ola de inversión en Asia</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/mundo/2026/05/30/mas-de-300-detenidos-en-francia-tras-los-disturbios-por-la-victoria-del-psg/</t>
+          <t>https://www.elespectador.com/economia/empresas/el-exito-de-spacex-y-openai-impulsa-apuestas-por-los-proximos-ganadores-asiaticos-en-ia/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 06:58 p. m.</t>
+          <t>30/05/2026 08:21 p. m.</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
@@ -3792,24 +3792,24 @@
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>En entrevista con Westcol, Abelardo de la Espriella rechaza acusaciones</t>
+          <t>Movida Electoral: Así fue el último día de los candidatos presidenciales antes de elección</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/2026/05/30/en-entrevista-con-westcol-abelardo-de-la-espriella-rechaza-acusaciones/</t>
+          <t>https://www.elespectador.com/politica/elecciones-colombia-2026/cepeda-realizo-155-actos-publicos-de-la-espriella-aceptaria-curul-de-oposicion-si-pierde-valencia-recorre-iglesias-noticias-hoy/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 06:40 p. m.</t>
+          <t>30/05/2026 08:05 p. m.</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -3819,24 +3819,24 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Petro rechaza supuesta injerencia de Estados Unidos y Ecuador en elecciones</t>
+          <t>¿Quiénes encabezan la disputa por la presidencia? Todo lo que debe saber de los candidatos</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/2026/05/30/petro-rechaza-supuesta-injerencia-de-estados-unidos-y-ecuador-en-elecciones/</t>
+          <t>https://www.elespectador.com/politica/elecciones-colombia-2026/candidatos-presidenciales-quienes-son-los-aspirantes-que-encabezan-la-campana-perfiles-y-equipos-noticias-hoy/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 06:40 p. m.</t>
+          <t>30/05/2026 08:01 p. m.</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
@@ -3846,24 +3846,24 @@
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Entre euforia, disturbios y cientos de detenidos, París festeja su segunda Orejona</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/</t>
+          <t>https://www.elespectador.com/mundo/entre-euforia-disturbios-y-cientos-de-detenidos-paris-festeja-su-segunda-orejona/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 06:37 p. m.</t>
+          <t>30/05/2026 08:00 p. m.</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -3873,24 +3873,24 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>“Gracias, amigo”: el gesto de Arensman a Egan que emocionó en el Giro</t>
+          <t>Receta para preparar lomo con salsa de hongos y pimienta</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/deportes/2026/05/30/gracias-amigo-el-gesto-de-arensman-a-egan-que-emociono-en-el-giro/</t>
+          <t>https://www.elespectador.com/gastronomia-y-recetas/receta-para-preparar-lomo-con-salsa-de-hongos-y-pimienta/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 05:56 p. m.</t>
+          <t>30/05/2026 08:00 p. m.</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
@@ -3900,24 +3900,24 @@
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>Más de 10.400 funcionarios vigilarán las elecciones por orden de Procuraduría</t>
+          <t>5 novedades del primer SUV eléctrico de Subaru en Colombia: Trailseeker</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/2026/05/30/mas-de-10400-funcionarios-vigilaran-las-elecciones-por-orden-de-procuraduria/</t>
+          <t>https://www.elespectador.com/autos/5-novedades-del-primer-suv-electrico-de-subaru-en-colombia-trailseeker/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 05:23 p. m.</t>
+          <t>30/05/2026 09:02 p. m.</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -3927,24 +3927,24 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>El PSG, el equipo de Luis Enrique, entra al club de los gigantes de Europa</t>
+          <t>Las propuestas de Sergio Fajardo: el cambio serio y seguro es el único camino viable</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/deportes/2026/05/30/el-psg-el-equipo-de-luis-enrique-entra-al-club-de-los-gigantes-de-europa/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-30/elecciones-presidenciales-en-colombia-2026-en-vivo.html</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 05:10 p. m.</t>
+          <t>30/05/2026 08:40 p. m.</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
@@ -3954,24 +3954,24 @@
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>Samuel Morales y Juank Ricardo anuncian el fin de su unión musical</t>
+          <t>Las propuestas de Abelardo de la Espriella: seguridad total de “mano dura” y el crecimiento económico acelerado</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/farandula/2026/05/30/samuel-morales-y-juank-ricardo-anuncian-el-fin-de-su-union-musical/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/las-propuestas-de-abelardo-de-la-espriella-seguridad-total-de-mano-dura-y-el-crecimiento-economico-acelerado.html</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 05:10 p. m.</t>
+          <t>30/05/2026 08:34 p. m.</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -3981,24 +3981,24 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Farándula</t>
+          <t>Las propuestas de Iván Cepeda, tres revoluciones y más inversión social</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/farandula/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/las-propuestas-de-ivan-cepeda-tres-revoluciones-y-mas-inversion-social.html</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 05:01 p. m.</t>
+          <t>30/05/2026 08:21 p. m.</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
@@ -4008,24 +4008,24 @@
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>Así capturaron a alias ‘Tato’ en Arjona con más de 350 dosis de estupefaciente</t>
+          <t>Las propuestas de Paloma Valencia: seguridad total y reactivación petrolera</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/asi-capturaron-a-alias-tato-en-arjona-con-mas-de-350-dosis-de-estupefaciente/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/las-propuestas-de-paloma-valencia-seguridad-total-y-reactivacion-petrolera.html</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 04:58 p. m.</t>
+          <t>30/05/2026 07:57 p. m.</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -4035,24 +4035,24 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>No resistió: falleció cuñado de alias ‘Castor’ dos meses después de sufrir atentado</t>
+          <t>Iván Cepeda: “Es necesario, dentro del capitalismo, pasar a un modelo socialmente equitativo”</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/no-resistio-fallecio-cunado-de-alias-castor-dos-meses-despues-de-sufrir-atentado/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/daniel-coronell-entrevista-a-ivan-cepeda-a-pocas-horas-de-las-elecciones.html</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 04:46 p. m.</t>
+          <t>30/05/2026 07:25 p. m.</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
@@ -4062,24 +4062,24 @@
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>Donald Trump critica al papa por Irán y llama “inútil” al alcalde de Chicago</t>
+          <t>Estados Unidos ataca un barco que trataba de atravesar el estrecho de Ormuz rumbo a Irán</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/mundo/2026/05/30/donald-trump-critica-al-papa-por-iran-y-llama-inutil-al-alcalde-de-chicago/</t>
+          <t>https://elpais.com/internacional/2026-05-31/estados-unidos-ataca-un-barco-que-trataba-de-atravesar-el-estrecho-de-ormuz-rumbo-a-iran.html</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 04:34 p. m.</t>
+          <t>30/05/2026 06:28 p. m.</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -4089,24 +4089,24 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>“Están utilizando a mi familia”: Santiago Botero tras escándalo por orden de desalojo</t>
+          <t>Abelardo de la Espriella cierra su campaña en una entrevista con Westcol: “Quien demuestre la idoneidad física y psicológica podrá portar un arma en la era del tigre”</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/2026/05/30/estan-utilizando-a-mi-familia-santiago-botero-tras-escandalo-por-orden-de-desalojo/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-30/abelardo-de-la-espriella-cierra-su-campana-en-una-entrevista-con-westcol-esta-no-es-una-candidatura-sino-un-movimiento-popular.html</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 04:33 p. m.</t>
+          <t>30/05/2026 06:07 p. m.</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
@@ -4116,24 +4116,24 @@
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>Green card: así afectarían los cambios migratorios a colombianos</t>
+          <t>Noboa insiste en convertir la guerra arancelaria en herramienta electoral en Colombia</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/2026/05/30/green-card-asi-afectarian-los-cambios-migratorios-a-colombianos/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-30/noboa-insiste-en-convertir-la-guerra-arancelaria-en-herramienta-electoral-en-colombia.html</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 03:22 p. m.</t>
+          <t>30/05/2026 05:30 p. m.</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -4143,24 +4143,24 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Petro afirma que Colombia seguirá apoyando a Ecuador en materia energética</t>
+          <t>Vox abraza una internacional blanca para unir Europa y lograr un “efecto salida” de emigrantes</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/2026/05/30/petro-afirma-que-colombia-seguira-apoyando-a-ecuador-en-materia-energetica/</t>
+          <t>https://elpais.com/espana/2026-05-30/vox-abraza-una-internacional-blanca-para-unir-europa-y-lograr-un-efecto-salida-de-emigrantes.html</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 12:33 p. m.</t>
+          <t>30/05/2026 05:25 p. m.</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
@@ -4170,24 +4170,24 @@
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>Así despiden a Jhaider Garizao, el joven que se ahogó en una playa de Bocagrande</t>
+          <t>Paloma Valencia: “A los guerrilleros les voy a hacer sentir la mano de acero de la mujer colombiana”</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/asi-despiden-a-jhaider-garizao-el-joven-que-se-ahogo-en-una-playa-de-bocagrande/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-30/paloma-valencia-se-reune-con-cuatro-influenciadores-a-15-horas-del-inicio-de-las-elecciones.html</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 11:54 a. m.</t>
+          <t>30/05/2026 04:51 p. m.</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -4197,24 +4197,24 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Cayó alias ‘El Chinchurria’ en Bolívar: tenía un revólver y acumula 15 anotaciones</t>
+          <t>Bad Bunny en Madrid: el alucinante jolgorio del perreo y el amor</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/cayo-alias-el-chinchurria-en-mompox-acumulaba-15-anotaciones-judiciales/</t>
+          <t>https://elpais.com/cultura/2026-05-30/bad-bunny-en-madrid-el-alucinante-jolgorio-del-perreo-y-el-amor.html</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 11:13 a. m.</t>
+          <t>30/05/2026 04:49 p. m.</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
@@ -4224,24 +4224,24 @@
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>Por enésima vez cayó ‘Chawalita’ en Cartagena: suma más de 12 anotaciones</t>
+          <t>Más de un centenar de detenidos en París en los incidentes producidos tras la victoria del PSG en la Champions</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/por-enesima-vez-cayo-chawalita-en-cartagena-suma-mas-de-12-anotaciones/</t>
+          <t>https://elpais.com/deportes/futbol/2026-05-30/mas-de-un-centenar-de-detenidos-en-paris-en-los-incidentes-producidos-tras-la-victoria-del-psg-en-la-champions.html</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 10:46 a. m.</t>
+          <t>30/05/2026 04:40 p. m.</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -4251,24 +4251,24 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Bolívar se blinda para las elecciones con operativos de control y prevención</t>
+          <t>Vitinha, tras ganar la Champions: “Somos el mejor equipo del mundo”</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/bolivar-se-blinda-para-las-elecciones-con-operativos-de-control-y-prevencion/</t>
+          <t>https://elpais.com/deportes/futbol/2026-05-30/vitinha-tras-ganar-la-champions-somos-el-mejor-equipo-del-mundo.html</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 10:04 a. m.</t>
+          <t>30/05/2026 04:22 p. m.</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
@@ -4278,24 +4278,24 @@
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>Mientras jugaba en un casino, sicario le quitó la vida a Johnny Rodríguez</t>
+          <t>Resultados de las elecciones en Colombia 2026: cuándo se conocerán las votaciones y a qué hora inicia el preconteo</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/mientras-jugaba-en-un-casino-sicario-le-quito-la-vida-a-johnny-rodriguez/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-30/resultados-de-las-elecciones-en-colombia-2026-cuando-se-conoceran-las-votaciones-y-a-que-hora-inicia-el-preconteo.html</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:46 a. m.</t>
+          <t>30/05/2026 04:20 p. m.</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -4305,22 +4305,26 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Investigan muerte de un recluso en la Penitenciaría El Bosque de Barranquilla</t>
+          <t>El PAN cierra filas con Maru Campos frente a la petición de juicio político de Morena</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/investigan-muerte-de-un-recluso-en-la-penitenciaria-el-bosque-de-barranquilla/</t>
+          <t>https://elpais.com/mexico/2026-05-30/el-pan-cierra-filas-con-maru-campos-frente-a-la-peticion-de-juicio-politico-de-morena.html</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="6" t="inlineStr"/>
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>30/05/2026 04:17 p. m.</t>
+        </is>
+      </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -4328,22 +4332,26 @@
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>Premios Excelencia El Universal 2026: ya están abiertas las postulaciones</t>
+          <t>Detenido el presidente municipal de Cuautla Jesús Corona por sus presuntos vínculos con la delincuencia organizada</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/cartagena/2026/05/26/premios-excelencia-el-universal-2026-ya-estan-abiertas-las-postulaciones/</t>
+          <t>https://elpais.com/mexico/2026-05-30/detenido-el-presidente-municipal-de-cuautla-jesus-corona-por-sus-presuntos-vinculos-con-la-delincuencia-organizada.html</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="3" t="inlineStr"/>
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>30/05/2026 03:37 p. m.</t>
+        </is>
+      </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -4351,24 +4359,24 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>El ajedrecista Carlsen en gran crisis: tres derrotas en cinco rondas</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/cartagena/</t>
+          <t>https://elpais.com/deportes/2026-05-30/el-ajedrecista-carlsen-en-gran-crisis-tres-derrotas-en-cinco-rondas.html</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:44 p. m.</t>
+          <t>30/05/2026 03:35 p. m.</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
@@ -4378,24 +4386,24 @@
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>Candidatos presidenciales Colombia 2026: nombres, fotos y principales propuestas</t>
+          <t>Ventura, vigésima Puerta Grande a pesar de fallar con el rejón de muerte</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/27/candidatos-presidenciales-colombia-2026-nombres-fotos-y-principales-propuestas/</t>
+          <t>https://elpais.com/cultura/2026-05-30/ventura-vigesima-puerta-grande-a-pesar-de-fallar-con-el-rejon-de-muerte.html</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:38 p. m.</t>
+          <t>30/05/2026 03:15 p. m.</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -4405,24 +4413,24 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Fecha y hora para elegir al próximo presidente: ¿Cuándo se conocen los resultados oficiales?</t>
+          <t>Muere Julio Le Parc, artista de la luz y el movimiento</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/28/fecha-y-hora-para-elegir-al-proximo-presidente-cuando-se-conocen-los-resultados-oficiales/</t>
+          <t>https://elpais.com/argentina/2026-05-30/muere-julio-le-parc-artista-de-la-luz-y-el-movimiento.html</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:37 p. m.</t>
+          <t>30/05/2026 03:14 p. m.</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
@@ -4432,24 +4440,24 @@
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>¿Quién ganaría en segunda vuelta? Escenarios, según últimas encuestas presidenciales de mayo 2026</t>
+          <t>PSG - Arsenal: la final de la Champions League 2026 en Budapest, en imágenes</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/27/quien-ganaria-en-segunda-vuelta-escenarios-segun-ultimas-encuestas-presidenciales-de-mayo-2026/</t>
+          <t>https://elpais.com/deportes/2026-05-30/psg-arsenal-la-final-de-la-champions-league-2026-en-budapest-en-imagenes.html</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:37 p. m.</t>
+          <t>30/05/2026 02:54 p. m.</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -4459,24 +4467,24 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Elecciones presidenciales: horarios de Ley seca y cierre de fronteras</t>
+          <t>La gloria le vuelve a dar un portazo al Arsenal en la Champions</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/28/elecciones-presidenciales-horarios-de-ley-seca-y-cierre-de-fronteras/</t>
+          <t>https://elpais.com/deportes/futbol/2026-05-30/la-gloria-le-vuelve-a-dar-un-portazo-al-arsenal-en-la-champions.html</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:36 p. m.</t>
+          <t>30/05/2026 02:50 p. m.</t>
         </is>
       </c>
       <c r="B149" s="6" t="inlineStr">
@@ -4486,24 +4494,24 @@
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>¿Qué cosas puede y no puede hacer un jurado de votación? Registraduría Nacional explica</t>
+          <t>La grandeza premia al doble campeón PSG, que tumba en los penaltis al Arsenal</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/que-cosas-puede-y-no-puede-hacer-un-jurado-de-votacion-registraduria-nacional-explica/</t>
+          <t>https://elpais.com/deportes/futbol/2026-05-30/la-grandeza-premia-al-doble-campeon-psg-que-tumba-en-los-penaltis-al-arsenal.html</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:35 p. m.</t>
+          <t>30/05/2026 01:10 p. m.</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -4513,24 +4521,24 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>¿Cómo van las elecciones Colombia 2026 en el exterior? Registraduría confirmó fecha para resultados</t>
+          <t>Cantando y bailando, así ha recibido Madrid a Bad Bunny: “Con ganas de perreo, pero sin entrada”</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/26/como-van-las-elecciones-colombia-2026-en-el-exterior-registraduria-confirmo-fecha-para-resultados/</t>
+          <t>https://elpais.com/cultura/2026-05-30/bienvenidos-al-madrid-de-bad-bunny-con-ganas-de-perreo-pero-sin-entrada.html</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 07:55 p. m.</t>
+          <t>30/05/2026 10:41 a. m.</t>
         </is>
       </c>
       <c r="B151" s="6" t="inlineStr">
@@ -4540,24 +4548,24 @@
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>Pedagogía Electoral: ¿Qué hacer y qué no este domingo de elecciones presidenciales?</t>
+          <t>Se rompe la cuerda de la bandera de España durante el izado en el desfile del Día de las Fuerzas Armadas</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/31/pedagogia-electoral-que-hacer-y-que-no-este-domingo-de-elecciones-presidenciales/</t>
+          <t>https://elpais.com/videos/2026-05-30/se-rompre-la-cuerda-de-la-bandera-de-espana-durante-el-izado-en-el-desfile-del-dia-de-las-fuerzas-armadas.html?autoplay=1</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 07:50 p. m.</t>
+          <t>30/05/2026 09:24 a. m.</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -4567,24 +4575,24 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Colombia se alista para las elecciones presidenciales 2026</t>
+          <t>De la ‘Operación Kitchen’ a Leire Díez: las cloacas se retroalimentan</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/31/colombia-se-alista-para-las-elecciones-presidenciales-2026/</t>
+          <t>https://elpais.com/espana/2026-05-30/de-la-operacion-kitchen-a-leire-diez-las-cloacas-se-retroalimentan.html</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 06:35 p. m.</t>
+          <t>30/05/2026 07:14 a. m.</t>
         </is>
       </c>
       <c r="B153" s="6" t="inlineStr">
@@ -4594,24 +4602,24 @@
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>Al menos 336 arrestados y un policía herido es el balance de los festejos del PSG en Francia</t>
+          <t>Los partidos de Sumar instan al PSOE a actuar: “¿Hay una trama? Se contesta con leyes, medidas y ejemplaridad”</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/al-menos-336-arrestados-y-un-policia-herido-es-el-balance-de-los-festejos-del-psg-en-francia/</t>
+          <t>https://elpais.com/espana/catalunya/2026-05-30/los-partidos-de-sumar-instan-al-psoe-a-actuar-hay-una-trama-se-contesta-con-leyes-medidas-y-ejemplaridad.html</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 05:59 p. m.</t>
+          <t>30/05/2026 06:19 a. m.</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -4621,24 +4629,24 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Kevin Viveros salvó al Paranaense y se trepó a la cima de los goleadores del Brasileirao</t>
+          <t>Lotería Nacional: resultados del sorteo del sábado 30 de mayo</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/kevin-viveros-salvo-al-paranaense-y-se-trepo-a-la-cima-de-los-goleadores-del-brasileirao/</t>
+          <t>https://elpais.com/sorteos/2026-05-30/loteria-nacional-sorteo-del-sabado-30-de-mayo.html</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 04:49 p. m.</t>
+          <t>30/05/2026 04:03 a. m.</t>
         </is>
       </c>
       <c r="B155" s="6" t="inlineStr">
@@ -4648,24 +4656,24 @@
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>PSG y Aston Villa disputarán la Supercopa de Europa 2026: Fecha y hora</t>
+          <t>Muere Josefina Molina, pionera del cine español, a los 89 años</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/psg-y-aston-villa-disputaran-la-supercopa-de-europa-2026-fecha-y-hora/</t>
+          <t>https://elpais.com/cultura/2026-05-30/fallece-josefina-molina-pionera-del-cine-espanol-a-los-89-anos.html</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 04:22 p. m.</t>
+          <t>30/05/2026 02:22 a. m.</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -4675,24 +4683,24 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Sociedad de Cirugía Plástica respalda las iniciativas para combatir la medicina ilegal</t>
+          <t>Muere el filósofo francés Edgar Morin a los 104 años</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/sociedad-de-cirugia-plastica-respalda-las-iniciativas-para-combatir-la-medicina-ilegal/</t>
+          <t>https://elpais.com/cultura/2026-05-30/muere-el-filosofo-frances-edgar-morin-a-los-104-anos.html</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 04:06 p. m.</t>
+          <t>29/05/2026 10:30 p. m.</t>
         </is>
       </c>
       <c r="B157" s="6" t="inlineStr">
@@ -4702,24 +4710,24 @@
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>PSG entra en la historia: así quedó el palmarés de la Champions League tras su bicampeonato</t>
+          <t>Donna Haraway, filósofa: “Vivimos en un mundo pronatalista y antiinfancia. Los bebés deberían ser escasos y valiosos”</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/psg-entra-en-la-historia-asi-quedo-el-palmares-de-la-champions-league-tras-su-bicampeonato/</t>
+          <t>https://elpais.com/ideas/2026-05-30/donna-haraway-filosofa-vivimos-en-un-mundo-pronatalista-y-antiinfancia-tener-bebes-deberia-ser-algo-escaso-y-valioso.html</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 03:14 p. m.</t>
+          <t>30/05/2026 08:54 p. m.</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -4729,24 +4737,24 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Luis Enrique tras consagrarse Bicampeón de Champions: “Esto sólo se lo había visto hacer al Madrid”</t>
+          <t>Estos son los 11 candidatos a la Presidencia de Colombia 2026</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/luis-enrique-tras-consagrarse-bicampeon-de-champions-esto-solo-se-lo-habia-visto-hacer-al-madrid/</t>
+          <t>https://www.noticiasrcn.com/colombia/cuales-son-los-11-candidatos-a-la-presidencia-de-colombia-2026-1026269</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 02:24 p. m.</t>
+          <t>30/05/2026 07:44 p. m.</t>
         </is>
       </c>
       <c r="B159" s="6" t="inlineStr">
@@ -4756,24 +4764,24 @@
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>Pacto Histórico tendrá más de 112,000 testigos en todo el país para las elecciones presidenciales</t>
+          <t>Secuestró y violó a una niña de cuatro años tras engañar a su madre con regalarle un mercado en Cali</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/pacto-historico-tendra-mas-de-112000-testigos-en-todo-el-pais-para-las-elecciones-presidenciales/</t>
+          <t>https://www.noticiasrcn.com/colombia/secuestro-y-violo-a-una-nina-de-cuatro-anos-tras-enganar-a-su-madre-con-regalarle-un-mercado-en-cali-1026264</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 01:35 p. m.</t>
+          <t>30/05/2026 04:28 p. m.</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -4783,24 +4791,24 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>“Que ganen las ideas y no las mentiras”: Mindefensa al instalar PMU para evitar riesgos cibernéticos</t>
+          <t>Cadáveres de disidentes fueron cargados con explosivos para detonarlos en traslado a Medicina Legal</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/que-ganen-las-ideas-y-no-las-mentiras-mindefensa-al-instalar-pmu-para-evitar-riesgos-ciberneticos/</t>
+          <t>https://www.noticiasrcn.com/colombia/cadaveres-de-disidentes-fueron-cargados-con-explosivos-para-detonarlos-en-traslado-a-medicina-legal-1026237</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 01:30 p. m.</t>
+          <t>30/05/2026 03:50 p. m.</t>
         </is>
       </c>
       <c r="B161" s="6" t="inlineStr">
@@ -4810,24 +4818,24 @@
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>Elecciones en Venezuela: excandidato González Urrutia respalda convocar nuevas presidenciales</t>
+          <t>Más de 700 familias damnificadas y con el agua a la cintura al desbordarse tres ríos en Cabuyaro, Meta</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/elecciones-en-venezuela-excandidato-gonzalez-urrutia-respalda-convocar-nuevas-presidenciales/</t>
+          <t>https://www.noticiasrcn.com/colombia/mas-de-700-familias-damnificadas-y-con-el-agua-a-la-cintura-por-el-desbordamiento-de-tres-rios-en-cabuyaro-meta-1026229</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 01:16 p. m.</t>
+          <t>30/05/2026 03:32 p. m.</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -4837,24 +4845,24 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Bogotá fue testigo de la “Feria Gastronómica Europea” con 17 expositores y entrada gratuita</t>
+          <t>Elecciones Colombia: recompensas de $50 y $200 millones por actores armados y planes de atentados</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/bogota-fue-testigo-de-la-feria-gastronomica-europea-con-17-expositores-y-entrada-gratuita/</t>
+          <t>https://www.noticiasrcn.com/colombia/elecciones-colombia-recompensas-de-50-y-200-millones-por-actores-armados-y-planes-de-atentados-1026224</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 12:25 p. m.</t>
+          <t>30/05/2026 02:52 p. m.</t>
         </is>
       </c>
       <c r="B163" s="6" t="inlineStr">
@@ -4864,24 +4872,24 @@
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>Gobierno instaló PMU nacional para blindar la jornada electoral de este domingo 31 de mayo</t>
+          <t>Video revelador: hallan el cuerpo del joven de 22 años que se lanzó al embalse de Guatapé huyendo de agresión</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/gobierno-instala-pmu-nacional-para-blindar-la-jornada-electoral-de-este-domingo-31-de-mayo/</t>
+          <t>https://www.noticiasrcn.com/colombia/video-del-joven-de-22-anos-hallado-muerto-en-guatape-1026206</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 12:17 p. m.</t>
+          <t>30/05/2026 01:36 p. m.</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -4891,24 +4899,24 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>Droguerías CAFAM se pronuncian frente a las medidas impuestas por la SuperSalud: ¿Qué dijeron?</t>
+          <t>Bogotá entrará en alerta amarilla hospitalaria por elecciones: ¿qué significa esto?</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/droguerias-cafam-se-pronuncian-frente-a-las-medidas-impuestas-por-la-supersalud-que-dijeron/</t>
+          <t>https://www.noticiasrcn.com/colombia/bogota-entrara-en-alerta-amarilla-hospitalaria-por-elecciones-1025976</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:40 p. m.</t>
+          <t>30/05/2026 12:56 p. m.</t>
         </is>
       </c>
       <c r="B165" s="6" t="inlineStr">
@@ -4918,24 +4926,24 @@
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>Las propuestas de Abelardo de la Espriella: seguridad total de “mano dura” y el crecimiento económico acelerado</t>
+          <t>“Se está dejando utilizar”: Santiago Botero se pronunció tras el desalojo en su vivienda en Cartagena</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/las-propuestas-de-abelardo-de-la-espriella-seguridad-total-de-mano-dura-y-el-crecimiento-economico-acelerado.html</t>
+          <t>https://www.noticiasrcn.com/colombia/santiago-botero-se-pronuncio-tras-escandalo-de-desalojo-de-su-vivienda-1026192</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:34 p. m.</t>
+          <t>30/05/2026 12:07 p. m.</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -4945,24 +4953,24 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Las propuestas de Iván Cepeda, tres revoluciones y más inversión social</t>
+          <t>Autoridades ordenaron desalojo a propiedad de Santiago Botero: es acusado de violencia intrafamiliar</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/las-propuestas-de-ivan-cepeda-tres-revoluciones-y-mas-inversion-social.html</t>
+          <t>https://www.noticiasrcn.com/colombia/santiago-botero-es-desalojado-y-acusado-de-violencia-intrafamiliar-1026185</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:21 p. m.</t>
+          <t>30/05/2026 11:43 a. m.</t>
         </is>
       </c>
       <c r="B167" s="6" t="inlineStr">
@@ -4972,24 +4980,24 @@
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>Las propuestas de Paloma Valencia: seguridad total y reactivación petrolera</t>
+          <t>Colombia, lista para votar: el llamado a respetar los resultados</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/las-propuestas-de-paloma-valencia-seguridad-total-y-reactivacion-petrolera.html</t>
+          <t>https://www.noticiasrcn.com/colombia/colombia-lista-para-votar-el-llamado-a-respetar-los-resultados-1026172</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57 p. m.</t>
+          <t>30/05/2026 08:53 p. m.</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -4999,24 +5007,24 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Iván Cepeda: “Es necesario, dentro del capitalismo, pasar a un modelo socialmente equitativo”</t>
+          <t>Video muestra el momento exacto en que meteoro cae en EE. UU. con fuerza de 300 toneladas de TNT</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/daniel-coronell-entrevista-a-ivan-cepeda-a-pocas-horas-de-las-elecciones.html</t>
+          <t>https://www.bluradio.com/mundo/video-muestra-el-momento-exacto-en-que-meteoro-cae-en-ee-uu-con-fuerza-de-300-toneladas-de-tnt-cb20</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 07:25 p. m.</t>
+          <t>30/05/2026 08:51 p. m.</t>
         </is>
       </c>
       <c r="B169" s="6" t="inlineStr">
@@ -5026,24 +5034,24 @@
       </c>
       <c r="C169" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>Estados Unidos ataca un barco que trataba de atravesar el estrecho de Ormuz rumbo a Irán</t>
+          <t>Super Astro Luna, resultado del último sorteo hoy sábado 30 de mayo de 2026</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/internacional/2026-05-31/estados-unidos-ataca-un-barco-que-trataba-de-atravesar-el-estrecho-de-ormuz-rumbo-a-iran.html</t>
+          <t>https://www.bluradio.com/economia/juegos-de-azar/super-astro-luna-resultado-del-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-so35</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 06:28 p. m.</t>
+          <t>30/05/2026 08:51 p. m.</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -5053,24 +5061,24 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Abelardo de la Espriella cierra su campaña en una entrevista con Westcol: “Quien demuestre la idoneidad física y psicológica podrá portar un arma en la era del tigre”</t>
+          <t>Caribeña Noche, resultado del último sorteo hoy sábado 30 de mayo de 2026</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-30/abelardo-de-la-espriella-cierra-su-campana-en-una-entrevista-con-westcol-esta-no-es-una-candidatura-sino-un-movimiento-popular.html</t>
+          <t>https://www.bluradio.com/economia/juegos-de-azar/caribena-noche-resultado-del-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-so35</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 06:07 p. m.</t>
+          <t>30/05/2026 08:51 p. m.</t>
         </is>
       </c>
       <c r="B171" s="6" t="inlineStr">
@@ -5080,24 +5088,24 @@
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>Noboa insiste en convertir la guerra arancelaria en herramienta electoral en Colombia</t>
+          <t>Sinuano Noche, resultado del último sorteo hoy sábado 30 de mayo de 2026</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-30/noboa-insiste-en-convertir-la-guerra-arancelaria-en-herramienta-electoral-en-colombia.html</t>
+          <t>https://www.bluradio.com/economia/juegos-de-azar/sinuano-noche-resultado-del-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-so35</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 05:30 p. m.</t>
+          <t>30/05/2026 08:51 p. m.</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -5107,24 +5115,24 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Vox abraza una internacional blanca para unir Europa y lograr un “efecto salida” de emigrantes</t>
+          <t>Resultados del Dorado Noche: último sorteo hoy, sábado 30 de mayo de 2026, números ganadores</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/espana/2026-05-30/vox-abraza-una-internacional-blanca-para-unir-europa-y-lograr-un-efecto-salida-de-emigrantes.html</t>
+          <t>https://www.bluradio.com/economia/juegos-de-azar/resultados-del-dorado-noche-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-so35</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 05:25 p. m.</t>
+          <t>30/05/2026 08:50 p. m.</t>
         </is>
       </c>
       <c r="B173" s="6" t="inlineStr">
@@ -5134,24 +5142,24 @@
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D173" s="7" t="inlineStr">
         <is>
-          <t>Paloma Valencia: “A los guerrilleros les voy a hacer sentir la mano de acero de la mujer colombiana”</t>
+          <t>Loterías de Boyacá, Cauca, Extra de Colombia y Baloto: resultados sorteos hoy sábado 30 de mayo</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-30/paloma-valencia-se-reune-con-cuatro-influenciadores-a-15-horas-del-inicio-de-las-elecciones.html</t>
+          <t>https://www.bluradio.com/economia/juegos-de-azar/loterias-de-boyaca-cauca-extra-de-colombia-y-baloto-resultados-sorteos-hoy-sabado-30-de-mayo-so35</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 05:15 p. m.</t>
+          <t>30/05/2026 08:50 p. m.</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -5161,24 +5169,24 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Elecciones Colombia 2026, en vivo | Cepeda en su entrevista final con Coronell: “Hay obstinación en no querer escuchar lo que digo y lo que represento”</t>
+          <t>Baloto y Revancha, resultados del último sorteo hoy sábado 30 de mayo de 2026</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-30/elecciones-presidenciales-en-colombia-2026-en-vivo.html</t>
+          <t>https://www.bluradio.com/economia/juegos-de-azar/baloto-y-revancha-resultados-del-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-so35</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 04:51 p. m.</t>
+          <t>30/05/2026 08:50 p. m.</t>
         </is>
       </c>
       <c r="B175" s="6" t="inlineStr">
@@ -5188,24 +5196,24 @@
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>Bad Bunny en Madrid: el alucinante jolgorio del perreo y el amor</t>
+          <t>Extra de Colombia, resultados del último sorteo de este sábado 30 de mayo de 2026</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/cultura/2026-05-30/bad-bunny-en-madrid-el-alucinante-jolgorio-del-perreo-y-el-amor.html</t>
+          <t>https://www.bluradio.com/economia/juegos-de-azar/extra-de-colombia-resultados-del-ultimo-sorteo-de-este-sabado-30-de-mayo-de-2026-so35</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 04:49 p. m.</t>
+          <t>30/05/2026 08:49 p. m.</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -5215,24 +5223,24 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Más de un centenar de detenidos en París en los incidentes producidos tras la victoria del PSG en la Champions</t>
+          <t>Lotería del Cauca sábado 30 de mayo de 2026, resultados del último sorteo, premio mayor y secos</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/deportes/futbol/2026-05-30/mas-de-un-centenar-de-detenidos-en-paris-en-los-incidentes-producidos-tras-la-victoria-del-psg-en-la-champions.html</t>
+          <t>https://www.bluradio.com/economia/juegos-de-azar/loteria-del-cauca-sabado-30-de-mayo-de-2026-resultados-del-ultimo-sorteo-premio-mayor-y-secos-so35</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 04:40 p. m.</t>
+          <t>30/05/2026 08:49 p. m.</t>
         </is>
       </c>
       <c r="B177" s="6" t="inlineStr">
@@ -5242,24 +5250,24 @@
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>Vitinha, tras ganar la Champions: “Somos el mejor equipo del mundo”</t>
+          <t>Lotería Boyacá, resultados del último sorteo hoy sábado 30 de mayo de 2026</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/deportes/futbol/2026-05-30/vitinha-tras-ganar-la-champions-somos-el-mejor-equipo-del-mundo.html</t>
+          <t>https://www.bluradio.com/economia/juegos-de-azar/loteria-boyaca-resultados-del-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-so35</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 04:22 p. m.</t>
+          <t>30/05/2026 08:46 p. m.</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -5269,24 +5277,24 @@
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Resultados de las elecciones en Colombia 2026: cuándo se conocerán las votaciones y a qué hora inicia el preconteo</t>
+          <t>Al menos seis personas estarían atrapadas tras el colapso de un edificio en Nueva Delhi</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-30/resultados-de-las-elecciones-en-colombia-2026-cuando-se-conoceran-las-votaciones-y-a-que-hora-inicia-el-preconteo.html</t>
+          <t>https://www.bluradio.com/mundo/al-menos-seis-personas-estarian-atrapadas-tras-el-colapso-de-un-edificio-en-nueva-delhi-cb20</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 04:20 p. m.</t>
+          <t>30/05/2026 08:04 p. m.</t>
         </is>
       </c>
       <c r="B179" s="6" t="inlineStr">
@@ -5296,24 +5304,24 @@
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>El PAN cierra filas con Maru Campos frente a la petición de juicio político de Morena</t>
+          <t>Encuentran muerta a adolescente de 14 años desaparecida hace una semana; investigan homicidio</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/mexico/2026-05-30/el-pan-cierra-filas-con-maru-campos-frente-a-la-peticion-de-juicio-politico-de-morena.html</t>
+          <t>https://www.bluradio.com/mundo/encuentran-muerta-a-adolescente-de-14-anos-desaparecida-hace-una-semana-investigan-homicidio-rs15</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 04:17 p. m.</t>
+          <t>30/05/2026 08:53 p. m.</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -5323,24 +5331,24 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Detenido el presidente municipal de Cuautla Jesús Corona por sus presuntos vínculos con la delincuencia organizada</t>
+          <t>Cristian Mosquera fue tendencia tras cometer penal en la final que perdió Arsenal ante PSG</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/mexico/2026-05-30/detenido-el-presidente-municipal-de-cuautla-jesus-corona-por-sus-presuntos-vinculos-con-la-delincuencia-organizada.html</t>
+          <t>https://www.eluniversal.com.co/deportes/2026/05/30/cristian-mosquera-fue-tendencia-tras-cometer-penal-en-la-final-que-perdio-arsenal-ante-psg/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 03:37 p. m.</t>
+          <t>30/05/2026 08:53 p. m.</t>
         </is>
       </c>
       <c r="B181" s="6" t="inlineStr">
@@ -5350,24 +5358,24 @@
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D181" s="7" t="inlineStr">
         <is>
-          <t>El ajedrecista Carlsen en gran crisis: tres derrotas en cinco rondas</t>
+          <t>Deportes</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/deportes/2026-05-30/el-ajedrecista-carlsen-en-gran-crisis-tres-derrotas-en-cinco-rondas.html</t>
+          <t>https://www.eluniversal.com.co/deportes/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 03:35 p. m.</t>
+          <t>30/05/2026 08:46 p. m.</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -5377,24 +5385,24 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Ventura, vigésima Puerta Grande a pesar de fallar con el rejón de muerte</t>
+          <t>Más de 300 detenidos en Francia tras los disturbios por la victoria del PSG</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/cultura/2026-05-30/ventura-vigesima-puerta-grande-a-pesar-de-fallar-con-el-rejon-de-muerte.html</t>
+          <t>https://www.eluniversal.com.co/mundo/2026/05/30/mas-de-300-detenidos-en-francia-tras-los-disturbios-por-la-victoria-del-psg/</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 03:15 p. m.</t>
+          <t>30/05/2026 06:58 p. m.</t>
         </is>
       </c>
       <c r="B183" s="6" t="inlineStr">
@@ -5404,24 +5412,24 @@
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D183" s="7" t="inlineStr">
         <is>
-          <t>Muere Julio Le Parc, artista de la luz y el movimiento</t>
+          <t>En entrevista con Westcol, Abelardo de la Espriella rechaza acusaciones</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/argentina/2026-05-30/muere-julio-le-parc-artista-de-la-luz-y-el-movimiento.html</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/30/en-entrevista-con-westcol-abelardo-de-la-espriella-rechaza-acusaciones/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 03:14 p. m.</t>
+          <t>30/05/2026 06:40 p. m.</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -5431,24 +5439,24 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>PSG - Arsenal: la final de la Champions League 2026 en Budapest, en imágenes</t>
+          <t>Petro rechaza supuesta injerencia de Estados Unidos y Ecuador en elecciones</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/deportes/2026-05-30/psg-arsenal-la-final-de-la-champions-league-2026-en-budapest-en-imagenes.html</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/30/petro-rechaza-supuesta-injerencia-de-estados-unidos-y-ecuador-en-elecciones/</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 02:54 p. m.</t>
+          <t>30/05/2026 06:40 p. m.</t>
         </is>
       </c>
       <c r="B185" s="6" t="inlineStr">
@@ -5458,24 +5466,24 @@
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D185" s="7" t="inlineStr">
         <is>
-          <t>La gloria le vuelve a dar un portazo al Arsenal en la Champions</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/deportes/futbol/2026-05-30/la-gloria-le-vuelve-a-dar-un-portazo-al-arsenal-en-la-champions.html</t>
+          <t>https://www.eluniversal.com.co/colombia/</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 02:50 p. m.</t>
+          <t>30/05/2026 06:37 p. m.</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -5485,24 +5493,24 @@
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>La grandeza premia al doble campeón PSG, que tumba en los penaltis al Arsenal</t>
+          <t>“Gracias, amigo”: el gesto de Arensman a Egan que emocionó en el Giro</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/deportes/futbol/2026-05-30/la-grandeza-premia-al-doble-campeon-psg-que-tumba-en-los-penaltis-al-arsenal.html</t>
+          <t>https://www.eluniversal.com.co/deportes/2026/05/30/gracias-amigo-el-gesto-de-arensman-a-egan-que-emociono-en-el-giro/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 01:10 p. m.</t>
+          <t>30/05/2026 05:56 p. m.</t>
         </is>
       </c>
       <c r="B187" s="6" t="inlineStr">
@@ -5512,24 +5520,24 @@
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D187" s="7" t="inlineStr">
         <is>
-          <t>Cantando y bailando, así ha recibido Madrid a Bad Bunny: “Con ganas de perreo, pero sin entrada”</t>
+          <t>Más de 10.400 funcionarios vigilarán las elecciones por orden de Procuraduría</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/cultura/2026-05-30/bienvenidos-al-madrid-de-bad-bunny-con-ganas-de-perreo-pero-sin-entrada.html</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/30/mas-de-10400-funcionarios-vigilaran-las-elecciones-por-orden-de-procuraduria/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 10:41 a. m.</t>
+          <t>30/05/2026 05:23 p. m.</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -5539,24 +5547,24 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Se rompe la cuerda de la bandera de España durante el izado en el desfile del Día de las Fuerzas Armadas</t>
+          <t>El PSG, el equipo de Luis Enrique, entra al club de los gigantes de Europa</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/videos/2026-05-30/se-rompre-la-cuerda-de-la-bandera-de-espana-durante-el-izado-en-el-desfile-del-dia-de-las-fuerzas-armadas.html?autoplay=1</t>
+          <t>https://www.eluniversal.com.co/deportes/2026/05/30/el-psg-el-equipo-de-luis-enrique-entra-al-club-de-los-gigantes-de-europa/</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 09:24 a. m.</t>
+          <t>30/05/2026 05:10 p. m.</t>
         </is>
       </c>
       <c r="B189" s="6" t="inlineStr">
@@ -5566,24 +5574,24 @@
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D189" s="7" t="inlineStr">
         <is>
-          <t>De la ‘Operación Kitchen’ a Leire Díez: las cloacas se retroalimentan</t>
+          <t>Samuel Morales y Juank Ricardo anuncian el fin de su unión musical</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/espana/2026-05-30/de-la-operacion-kitchen-a-leire-diez-las-cloacas-se-retroalimentan.html</t>
+          <t>https://www.eluniversal.com.co/farandula/2026/05/30/samuel-morales-y-juank-ricardo-anuncian-el-fin-de-su-union-musical/</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 07:14 a. m.</t>
+          <t>30/05/2026 05:10 p. m.</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -5593,24 +5601,24 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>Los partidos de Sumar instan al PSOE a actuar: “¿Hay una trama? Se contesta con leyes, medidas y ejemplaridad”</t>
+          <t>Farándula</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/espana/catalunya/2026-05-30/los-partidos-de-sumar-instan-al-psoe-a-actuar-hay-una-trama-se-contesta-con-leyes-medidas-y-ejemplaridad.html</t>
+          <t>https://www.eluniversal.com.co/farandula/</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 06:19 a. m.</t>
+          <t>30/05/2026 05:01 p. m.</t>
         </is>
       </c>
       <c r="B191" s="6" t="inlineStr">
@@ -5620,24 +5628,24 @@
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D191" s="7" t="inlineStr">
         <is>
-          <t>Lotería Nacional: resultados del sorteo del sábado 30 de mayo</t>
+          <t>Así capturaron a alias ‘Tato’ en Arjona con más de 350 dosis de estupefaciente</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/sorteos/2026-05-30/loteria-nacional-sorteo-del-sabado-30-de-mayo.html</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/asi-capturaron-a-alias-tato-en-arjona-con-mas-de-350-dosis-de-estupefaciente/</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 04:03 a. m.</t>
+          <t>30/05/2026 04:58 p. m.</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -5647,24 +5655,24 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>Muere Josefina Molina, pionera del cine español, a los 89 años</t>
+          <t>No resistió: falleció cuñado de alias ‘Castor’ dos meses después de sufrir atentado</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/cultura/2026-05-30/fallece-josefina-molina-pionera-del-cine-espanol-a-los-89-anos.html</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/no-resistio-fallecio-cunado-de-alias-castor-dos-meses-despues-de-sufrir-atentado/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 02:22 a. m.</t>
+          <t>30/05/2026 04:46 p. m.</t>
         </is>
       </c>
       <c r="B193" s="6" t="inlineStr">
@@ -5674,24 +5682,24 @@
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D193" s="7" t="inlineStr">
         <is>
-          <t>Muere el filósofo francés Edgar Morin a los 104 años</t>
+          <t>Donald Trump critica al papa por Irán y llama “inútil” al alcalde de Chicago</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/cultura/2026-05-30/muere-el-filosofo-frances-edgar-morin-a-los-104-anos.html</t>
+          <t>https://www.eluniversal.com.co/mundo/2026/05/30/donald-trump-critica-al-papa-por-iran-y-llama-inutil-al-alcalde-de-chicago/</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:30 p. m.</t>
+          <t>30/05/2026 04:34 p. m.</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -5701,24 +5709,24 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Donna Haraway, filósofa: “Vivimos en un mundo pronatalista y antiinfancia. Los bebés deberían ser escasos y valiosos”</t>
+          <t>“Están utilizando a mi familia”: Santiago Botero tras escándalo por orden de desalojo</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/ideas/2026-05-30/donna-haraway-filosofa-vivimos-en-un-mundo-pronatalista-y-antiinfancia-tener-bebes-deberia-ser-algo-escaso-y-valioso.html</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/30/estan-utilizando-a-mi-familia-santiago-botero-tras-escandalo-por-orden-de-desalojo/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:34 p. m.</t>
+          <t>30/05/2026 04:33 p. m.</t>
         </is>
       </c>
       <c r="B195" s="6" t="inlineStr">
@@ -5728,24 +5736,24 @@
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D195" s="7" t="inlineStr">
         <is>
-          <t>Tras revelación de EL COLOMBIANO, investigarán a personal del Hospital Nazareth por video de pedagogía electoral a favor de Cepeda</t>
+          <t>Green card: así afectarían los cambios migratorios a colombianos</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/investigacion-hospital-nazareth-video-ivan-cepeda-IB37149809</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/30/green-card-asi-afectarian-los-cambios-migratorios-a-colombianos/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 07:01 p. m.</t>
+          <t>30/05/2026 03:22 p. m.</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -5755,24 +5763,24 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>Sindicato de Ecopetrol descarta apoyar a Cepeda y respalda candidatos que impulsen exploración petrolera y fracking</t>
+          <t>Petro afirma que Colombia seguirá apoyando a Ecuador en materia energética</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/negocios/uso-sindicato-ecopetrol-descarta-ivan-cepeda-fracking-HB37148843</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/30/petro-afirma-que-colombia-seguira-apoyando-a-ecuador-en-materia-energetica/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 07:01 p. m.</t>
+          <t>30/05/2026 12:33 p. m.</t>
         </is>
       </c>
       <c r="B197" s="6" t="inlineStr">
@@ -5782,24 +5790,24 @@
       </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D197" s="7" t="inlineStr">
         <is>
-          <t>Polémica por colecta impulsada por sectores del petrismo para transportar votantes: advierten riesgos de trashumancia electoral</t>
+          <t>Así despiden a Jhaider Garizao, el joven que se ahogó en una playa de Bocagrande</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/politica/polemica-colecta-imprenta-republicana-votos-medellin-LB37149002</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/asi-despiden-a-jhaider-garizao-el-joven-que-se-ahogo-en-una-playa-de-bocagrande/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 05:01 p. m.</t>
+          <t>30/05/2026 11:54 a. m.</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -5809,24 +5817,24 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>Cuerpos de disidentes muertos en Guaviare tenían explosivos para atentar contra la Fuerza Pública</t>
+          <t>Cayó alias ‘El Chinchurria’ en Bolívar: tenía un revólver y acumula 15 anotaciones</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/explosivos-en-cuerpos-evacuados-tras-combates-guaviare-farc-JB37145950</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/cayo-alias-el-chinchurria-en-mompox-acumulaba-15-anotaciones-judiciales/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 05:01 p. m.</t>
+          <t>30/05/2026 11:13 a. m.</t>
         </is>
       </c>
       <c r="B199" s="6" t="inlineStr">
@@ -5836,24 +5844,24 @@
       </c>
       <c r="C199" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D199" s="7" t="inlineStr">
         <is>
-          <t>¿Será la hora de los 9 colombianos en el Mundial? Colombia necesita de sus goles</t>
+          <t>Por enésima vez cayó ‘Chawalita’ en Cartagena: suma más de 12 anotaciones</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/especiales/mundial-2026/seleccion-colombia-los-numero-9-mundial-goleadores-luis-suarez-jhon-cordoba-cucho-hernandez-deuda-goles-EB37147663</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/por-enesima-vez-cayo-chawalita-en-cartagena-suma-mas-de-12-anotaciones/</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 04:01 p. m.</t>
+          <t>30/05/2026 10:46 a. m.</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -5863,24 +5871,24 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>Aficionado del PSG viajó a Bucarest en lugar de Budapest y se perdió la final de la Champions League</t>
+          <t>Bolívar se blinda para las elecciones con operativos de control y prevención</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/deportes/aficionado-psg-error-viaje-final-champions-DB37143642</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/bolivar-se-blinda-para-las-elecciones-con-operativos-de-control-y-prevencion/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 04:01 p. m.</t>
+          <t>30/05/2026 10:04 a. m.</t>
         </is>
       </c>
       <c r="B201" s="6" t="inlineStr">
@@ -5890,24 +5898,24 @@
       </c>
       <c r="C201" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D201" s="7" t="inlineStr">
         <is>
-          <t>La tasa de usura supera el 28% y hará más costosas las compras a crédito para el Mundial</t>
+          <t>Mientras jugaba en un casino, sicario le quitó la vida a Johnny Rodríguez</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/negocios/tasa-usura-junio-compras-credito-mundial-EB37144321</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/mientras-jugaba-en-un-casino-sicario-le-quito-la-vida-a-johnny-rodriguez/</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 04:01 p. m.</t>
+          <t>30/05/2026 08:46 a. m.</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -5917,26 +5925,22 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>Nacional vs. Junior: tres finalistas de 2015 repiten en la serie final del Apertura-2026</t>
+          <t>Investigan muerte de un recluso en la Penitenciaría El Bosque de Barranquilla</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/deportes/futbol/final-nacional-junior-repitentes-definicion-titulo-2015-liga-betplay-2026-1-PB37144830</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/investigan-muerte-de-un-recluso-en-la-penitenciaria-el-bosque-de-barranquilla/</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="6" t="inlineStr">
-        <is>
-          <t>30/05/2026 04:01 p. m.</t>
-        </is>
-      </c>
+      <c r="A203" s="6" t="inlineStr"/>
       <c r="B203" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5944,26 +5948,22 @@
       </c>
       <c r="C203" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D203" s="7" t="inlineStr">
         <is>
-          <t>Video | Giro en caso de Alexánder Avendaño, el joven hallado muerto en embalse El Peñol-Guatapé</t>
+          <t>Premios Excelencia El Universal 2026: ya están abiertas las postulaciones</t>
         </is>
       </c>
       <c r="E203" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/antioquia/video-alexander-avendano-hallado-muerto-embalse-el-penol-guatape-OB37144813</t>
+          <t>https://www.eluniversal.com.co/cartagena/2026/05/26/premios-excelencia-el-universal-2026-ya-estan-abiertas-las-postulaciones/</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="3" t="inlineStr">
-        <is>
-          <t>30/05/2026 03:01 p. m.</t>
-        </is>
-      </c>
+      <c r="A204" s="3" t="inlineStr"/>
       <c r="B204" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5971,24 +5971,24 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>PSG hace historia: bicampeón de la Champions tras vencer al Arsenal en una final épica</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/deportes/futbol/psg-bicampeon-champions-final-arsenal-resultado-prorroga-penaltis-CB37143221</t>
+          <t>https://www.eluniversal.com.co/cartagena/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 02:01 p. m.</t>
+          <t>30/05/2026 08:50 p. m.</t>
         </is>
       </c>
       <c r="B205" s="6" t="inlineStr">
@@ -5998,24 +5998,24 @@
       </c>
       <c r="C205" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D205" s="7" t="inlineStr">
         <is>
-          <t>Prográmese y siga estas recomendaciones para votar el 31 de mayo</t>
+          <t>Elecciones en Colombia 2026: ¿Puede pedir un nuevo tarjetón si se equivoca? Registraduría responde</t>
         </is>
       </c>
       <c r="E205" s="8" t="inlineStr">
         <is>
-          <t>https://qhubomedellin.com/util-para-vos/recomendaciones-para-votar-el-31-de-mayo-presidenciales-EO36920523</t>
+          <t>https://caracol.com.co/2026/05/29/elecciones-en-colombia-2026-puede-pedir-un-nuevo-tarjeton-si-se-equivoca-registraduria-responde/</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 02:01 p. m.</t>
+          <t>30/05/2026 08:44 p. m.</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -6025,24 +6025,24 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>EN VIDEO: Cohete de Jeff Bezos explotó durante prueba de encendido</t>
+          <t>Candidatos presidenciales Colombia 2026: nombres, fotos y principales propuestas</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
         <is>
-          <t>https://qhubomedellin.com/actualidad/internacional/cohete-de-jeff-bezos-explota-durante-prueba-de-encendido-NH37129271</t>
+          <t>https://caracol.com.co/2026/05/27/candidatos-presidenciales-colombia-2026-nombres-fotos-y-principales-propuestas/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 12:01 p. m.</t>
+          <t>30/05/2026 08:38 p. m.</t>
         </is>
       </c>
       <c r="B207" s="6" t="inlineStr">
@@ -6052,24 +6052,24 @@
       </c>
       <c r="C207" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D207" s="7" t="inlineStr">
         <is>
-          <t>Camila Osorio lo dejó todo, pero no pudo avanzar a octavos de final en Roland Garros</t>
+          <t>Fecha y hora para elegir al próximo presidente: ¿Cuándo se conocen los resultados oficiales?</t>
         </is>
       </c>
       <c r="E207" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/deportes/camila-osorio-kalinskaya-roland-garros-MG37139005</t>
+          <t>https://caracol.com.co/2026/05/28/fecha-y-hora-para-elegir-al-proximo-presidente-cuando-se-conocen-los-resultados-oficiales/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 12:01 p. m.</t>
+          <t>30/05/2026 08:37 p. m.</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -6079,24 +6079,24 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>Exclusivo | Así le hacen campaña a Cepeda los equipos básicos del MinSalud en La Guajira</t>
+          <t>¿Quién ganaría en segunda vuelta? Escenarios, según últimas encuestas presidenciales de mayo 2026</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/especiales/elecciones-2026/campana-cepeda-los-equipos-basicos-minsalud-en-la-guajira-NG37139848</t>
+          <t>https://caracol.com.co/2026/05/27/quien-ganaria-en-segunda-vuelta-escenarios-segun-ultimas-encuestas-presidenciales-de-mayo-2026/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 11:01 a. m.</t>
+          <t>30/05/2026 08:37 p. m.</t>
         </is>
       </c>
       <c r="B209" s="6" t="inlineStr">
@@ -6106,24 +6106,24 @@
       </c>
       <c r="C209" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D209" s="7" t="inlineStr">
         <is>
-          <t>Desde el 3 de junio habrá cierre en la vía San Nicolás–La Ceja, ¿por qué?</t>
+          <t>Elecciones presidenciales: horarios de Ley seca y cierre de fronteras</t>
         </is>
       </c>
       <c r="E209" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/antioquia/cierres-viales-via-san-nicolas-rionegro-la-ceja-antioquia-BG37138584</t>
+          <t>https://caracol.com.co/2026/05/28/elecciones-presidenciales-horarios-de-ley-seca-y-cierre-de-fronteras/</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 11:01 a. m.</t>
+          <t>30/05/2026 08:36 p. m.</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -6133,24 +6133,24 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>¡Ojo! Caficultores de Bello tienen hasta este 31 de mayo para acceder a apoyos en cultivos</t>
+          <t>¿Qué cosas puede y no puede hacer un jurado de votación? Registraduría Nacional explica</t>
         </is>
       </c>
       <c r="E210" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/antioquia/plazo-caficultores-de-bello-antioquia-apoyos-cafetales-FG37138973</t>
+          <t>https://caracol.com.co/2026/05/30/que-cosas-puede-y-no-puede-hacer-un-jurado-de-votacion-registraduria-nacional-explica/</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 11:01 a. m.</t>
+          <t>30/05/2026 08:35 p. m.</t>
         </is>
       </c>
       <c r="B211" s="6" t="inlineStr">
@@ -6160,24 +6160,24 @@
       </c>
       <c r="C211" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D211" s="7" t="inlineStr">
         <is>
-          <t>Más de 100 exalcaldes de Antioquia anuncian su respaldo a Paloma Valencia y Juan Daniel Oviedo</t>
+          <t>¿Cómo van las elecciones Colombia 2026 en el exterior? Registraduría confirmó fecha para resultados</t>
         </is>
       </c>
       <c r="E211" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/antioquia/exalcaldes-antioquia-apoyan-paloma-valencia-HG37138834</t>
+          <t>https://caracol.com.co/2026/05/26/como-van-las-elecciones-colombia-2026-en-el-exterior-registraduria-confirmo-fecha-para-resultados/</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 10:01 a. m.</t>
+          <t>30/05/2026 07:55 p. m.</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -6187,24 +6187,24 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>Gobierno rechaza acuerdo entre Noboa y De la Espriella para eliminar aranceles: “es un injerencia deliberada” en elecciones</t>
+          <t>Pedagogía Electoral: ¿Qué hacer y qué no este domingo de elecciones presidenciales?</t>
         </is>
       </c>
       <c r="E212" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/petro-arremete-contra-daniel-noboa-bernie-moreno-aranceles-elecciones-PG37137769</t>
+          <t>https://caracol.com.co/2026/05/31/pedagogia-electoral-que-hacer-y-que-no-este-domingo-de-elecciones-presidenciales/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 10:01 a. m.</t>
+          <t>30/05/2026 07:50 p. m.</t>
         </is>
       </c>
       <c r="B213" s="6" t="inlineStr">
@@ -6214,24 +6214,24 @@
       </c>
       <c r="C213" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D213" s="7" t="inlineStr">
         <is>
-          <t>La exigencia física le pasó factura a David Alonso en Italia que correrá este domingo, ¿cómo y dónde ver la carrera?</t>
+          <t>Colombia se alista para las elecciones presidenciales 2026</t>
         </is>
       </c>
       <c r="E213" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/deportes/david-alonso-moto2-gp-italia-clasificacion-motogp-BG37137644</t>
+          <t>https://caracol.com.co/2026/05/31/colombia-se-alista-para-las-elecciones-presidenciales-2026/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 09:01 a. m.</t>
+          <t>30/05/2026 06:35 p. m.</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -6241,24 +6241,24 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>Candidato Santiago Botero fue desalojado de su casa tras impedir el ingreso de su esposa e hijo; tiene una denuncia por violencia intrafamiliar</t>
+          <t>Al menos 336 arrestados y un policía herido es el balance de los festejos del PSG en Francia</t>
         </is>
       </c>
       <c r="E214" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/santiago-botero-desalojo-casa-cartagena-IG37136842</t>
+          <t>https://caracol.com.co/2026/05/30/al-menos-336-arrestados-y-un-policia-herido-es-el-balance-de-los-festejos-del-psg-en-francia/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 07:01 a. m.</t>
+          <t>30/05/2026 05:59 p. m.</t>
         </is>
       </c>
       <c r="B215" s="6" t="inlineStr">
@@ -6268,24 +6268,24 @@
       </c>
       <c r="C215" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D215" s="7" t="inlineStr">
         <is>
-          <t>A lomo de mula y cruzando ríos: así logró reducir el hambre Antioquia</t>
+          <t>Kevin Viveros salvó al Paranaense y se trepó a la cima de los goleadores del Brasileirao</t>
         </is>
       </c>
       <c r="E215" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/antioquia/estrategia-contra-el-hambre-y-la-desnutricion-en-antioquia-JG37134638</t>
+          <t>https://caracol.com.co/2026/05/30/kevin-viveros-salvo-al-paranaense-y-se-trepo-a-la-cima-de-los-goleadores-del-brasileirao/</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 07:01 a. m.</t>
+          <t>30/05/2026 04:49 p. m.</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -6295,24 +6295,24 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t>Lo que debe saber para votar este domingo: ¿alguno podría ganar en primera vuelta?</t>
+          <t>PSG y Aston Villa disputarán la Supercopa de Europa 2026: Fecha y hora</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/especiales/elecciones-2026/elecciones-2026-consulta-puesto-votacion-horarios-primera-vuelta-PG37135864</t>
+          <t>https://caracol.com.co/2026/05/30/psg-y-aston-villa-disputaran-la-supercopa-de-europa-2026-fecha-y-hora/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 06:01 a. m.</t>
+          <t>30/05/2026 04:22 p. m.</t>
         </is>
       </c>
       <c r="B217" s="6" t="inlineStr">
@@ -6322,22 +6322,26 @@
       </c>
       <c r="C217" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D217" s="7" t="inlineStr">
         <is>
-          <t>Calor dispara en más de 50% la venta de ventiladores en El Hueco, en Medellín: estos son los más vendidos</t>
+          <t>Sociedad de Cirugía Plástica respalda las iniciativas para combatir la medicina ilegal</t>
         </is>
       </c>
       <c r="E217" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/medellin/calor-medellin-ventas-ventiladores-hueco-KG37131092</t>
+          <t>https://caracol.com.co/2026/05/30/sociedad-de-cirugia-plastica-respalda-las-iniciativas-para-combatir-la-medicina-ilegal/</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="3" t="inlineStr"/>
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>30/05/2026 04:06 p. m.</t>
+        </is>
+      </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -6345,22 +6349,26 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>21 municipios en riesgo electoral y récord en testigos: así llega Antioquia a las elecciones</t>
+          <t>PSG entra en la historia: así quedó el palmarés de la Champions League tras su bicampeonato</t>
         </is>
       </c>
       <c r="E218" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/antioquia/antioquia-riesgo-electoral-testigos-preparacion-elecciones-presidenciales-2026-PG37135846</t>
+          <t>https://caracol.com.co/2026/05/30/psg-entra-en-la-historia-asi-quedo-el-palmares-de-la-champions-league-tras-su-bicampeonato/</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="6" t="inlineStr"/>
+      <c r="A219" s="6" t="inlineStr">
+        <is>
+          <t>30/05/2026 03:14 p. m.</t>
+        </is>
+      </c>
       <c r="B219" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -6368,22 +6376,26 @@
       </c>
       <c r="C219" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D219" s="7" t="inlineStr">
         <is>
-          <t>Así se enriqueció la novia de Petro</t>
+          <t>Luis Enrique tras consagrarse Bicampeón de Champions: “Esto sólo se lo había visto hacer al Madrid”</t>
         </is>
       </c>
       <c r="E219" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/multimedia/videos/asi-se-enriquecio-la-novia-de-petro-IH37120899</t>
+          <t>https://caracol.com.co/2026/05/30/luis-enrique-tras-consagrarse-bicampeon-de-champions-esto-solo-se-lo-habia-visto-hacer-al-madrid/</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="3" t="inlineStr"/>
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>30/05/2026 02:24 p. m.</t>
+        </is>
+      </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -6391,22 +6403,26 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D220" s="4" t="inlineStr">
         <is>
-          <t>Operativo destapa helicóptero con pasado oscuro y motor Rolls-Royce</t>
+          <t>Pacto Histórico tendrá más de 112,000 testigos en todo el país para las elecciones presidenciales</t>
         </is>
       </c>
       <c r="E220" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/ejercito-incauta-helicoptero-de-la-mafia-NG33717192</t>
+          <t>https://caracol.com.co/2026/05/30/pacto-historico-tendra-mas-de-112000-testigos-en-todo-el-pais-para-las-elecciones-presidenciales/</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="6" t="inlineStr"/>
+      <c r="A221" s="6" t="inlineStr">
+        <is>
+          <t>30/05/2026 01:35 p. m.</t>
+        </is>
+      </c>
       <c r="B221" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -6414,22 +6430,26 @@
       </c>
       <c r="C221" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D221" s="7" t="inlineStr">
         <is>
-          <t>Voraz incendio consumió vivienda en Itagüí y dejó a una familia sin nada</t>
+          <t>“Que ganen las ideas y no las mentiras”: Mindefensa al instalar PMU para evitar riesgos cibernéticos</t>
         </is>
       </c>
       <c r="E221" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/antioquia/incendio-vivienda-itagui-el-guayabo-una-familia-sin-nada-AG37135775</t>
+          <t>https://caracol.com.co/2026/05/30/que-ganen-las-ideas-y-no-las-mentiras-mindefensa-al-instalar-pmu-para-evitar-riesgos-ciberneticos/</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="3" t="inlineStr"/>
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t>30/05/2026 01:30 p. m.</t>
+        </is>
+      </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -6437,22 +6457,26 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t>¡Le interesa! Este domingo habrá café gratis y descuentos en 120 marcas en Antioquia presentando el certificado de votación</t>
+          <t>Elecciones en Venezuela: excandidato González Urrutia respalda convocar nuevas presidenciales</t>
         </is>
       </c>
       <c r="E222" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/medellin/descuentos-y-beneficios-en-medellin-por-votar-elecciones-2026-IF37102578</t>
+          <t>https://caracol.com.co/2026/05/30/elecciones-en-venezuela-excandidato-gonzalez-urrutia-respalda-convocar-nuevas-presidenciales/</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="6" t="inlineStr"/>
+      <c r="A223" s="6" t="inlineStr">
+        <is>
+          <t>30/05/2026 01:16 p. m.</t>
+        </is>
+      </c>
       <c r="B223" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -6460,22 +6484,26 @@
       </c>
       <c r="C223" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D223" s="7" t="inlineStr">
         <is>
-          <t>Maluma habló de las elecciones en Colombia y lanzó inesperada propuesta para llevar votantes</t>
+          <t>Bogotá fue testigo de la “Feria Gastronómica Europea” con 17 expositores y entrada gratuita</t>
         </is>
       </c>
       <c r="E223" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/entretenimiento/maluma-hablo-elecciones-colombia-lanzo-inesperada-propuesta-votantes-IF37100945</t>
+          <t>https://caracol.com.co/2026/05/30/bogota-fue-testigo-de-la-feria-gastronomica-europea-con-17-expositores-y-entrada-gratuita/</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="3" t="inlineStr"/>
+      <c r="A224" s="3" t="inlineStr">
+        <is>
+          <t>30/05/2026 12:25 p. m.</t>
+        </is>
+      </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -6483,24 +6511,24 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>¿Qué proponen en materia de impuestos los candidatos presidenciales punteros?</t>
+          <t>Gobierno instaló PMU nacional para blindar la jornada electoral de este domingo 31 de mayo</t>
         </is>
       </c>
       <c r="E224" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/especiales/elecciones-2026/yo-cuido-la-democracia/propuestas-de-los-candidatos-presidenciales-GB37052040</t>
+          <t>https://caracol.com.co/2026/05/30/gobierno-instala-pmu-nacional-para-blindar-la-jornada-electoral-de-este-domingo-31-de-mayo/</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:33 p. m.</t>
+          <t>30/05/2026 08:38 p. m.</t>
         </is>
       </c>
       <c r="B225" s="6" t="inlineStr">
@@ -6510,24 +6538,24 @@
       </c>
       <c r="C225" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D225" s="7" t="inlineStr">
         <is>
-          <t>Elecciones 2026: ¿a qué hora se conocerán los resultados en Colombia?</t>
+          <t>Tras revelación de EL COLOMBIANO, investigarán a personal del Hospital Nazareth por video de pedagogía electoral a favor de Cepeda</t>
         </is>
       </c>
       <c r="E225" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/elecciones-2026-a-que-hora-se-conoceran-los-resultados-en-colombia/</t>
+          <t>https://www.elcolombiano.com/colombia/investigacion-hospital-nazareth-video-ivan-cepeda-IB37149809</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:26 p. m.</t>
+          <t>30/05/2026 06:33 p. m.</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -6537,24 +6565,24 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t>Elecciones 2026: cómo votar en el exterior y consultar su puesto</t>
+          <t>Sindicato de Ecopetrol descarta apoyar a Cepeda y respalda candidatos que impulsen exploración petrolera y fracking</t>
         </is>
       </c>
       <c r="E226" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/elecciones-2026-como-votar-en-el-exterior-y-consultar-su-puesto/</t>
+          <t>https://www.elcolombiano.com/negocios/uso-sindicato-ecopetrol-descarta-ivan-cepeda-fracking-HB37148843</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:14 p. m.</t>
+          <t>30/05/2026 06:33 p. m.</t>
         </is>
       </c>
       <c r="B227" s="6" t="inlineStr">
@@ -6564,24 +6592,24 @@
       </c>
       <c r="C227" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D227" s="7" t="inlineStr">
         <is>
-          <t>¿Dónde votar? Consulte su puesto para las elecciones presidenciales 2026</t>
+          <t>Polémica por colecta impulsada por sectores del petrismo para transportar votantes: advierten riesgos de trashumancia electoral</t>
         </is>
       </c>
       <c r="E227" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/donde-votar-consulte-su-puesto-para-las-elecciones-presidenciales-2026/</t>
+          <t>https://www.elcolombiano.com/colombia/politica/polemica-colecta-imprenta-republicana-votos-medellin-LB37149002</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:03 p. m.</t>
+          <t>30/05/2026 04:33 p. m.</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -6591,24 +6619,24 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t>Tarjetón elecciones 2026: ¿qué pasa con votos por candidatos retirados?</t>
+          <t>Cuerpos de disidentes muertos en Guaviare tenían explosivos para atentar contra la Fuerza Pública</t>
         </is>
       </c>
       <c r="E228" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/tarjeton-elecciones-2026-que-pasa-con-votos-por-candidatos-retirados/</t>
+          <t>https://www.elcolombiano.com/colombia/explosivos-en-cuerpos-evacuados-tras-combates-guaviare-farc-JB37145950</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 07:58 p. m.</t>
+          <t>30/05/2026 04:33 p. m.</t>
         </is>
       </c>
       <c r="B229" s="6" t="inlineStr">
@@ -6618,24 +6646,24 @@
       </c>
       <c r="C229" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D229" s="7" t="inlineStr">
         <is>
-          <t>Elecciones 2026: Procurador Eljach llama a votar temprano y en paz</t>
+          <t>¿Será la hora de los 9 colombianos en el Mundial? Colombia necesita de sus goles</t>
         </is>
       </c>
       <c r="E229" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/elecciones-2026-procurador-eljach-llama-a-votar-temprano-y-en-paz/</t>
+          <t>https://www.elcolombiano.com/especiales/mundial-2026/seleccion-colombia-los-numero-9-mundial-goleadores-luis-suarez-jhon-cordoba-cucho-hernandez-deuda-goles-EB37147663</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 07:52 p. m.</t>
+          <t>30/05/2026 03:33 p. m.</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -6645,24 +6673,24 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D230" s="4" t="inlineStr">
         <is>
-          <t>Elecciones presidenciales 2026: cómo marcar la tarjeta electoral</t>
+          <t>Aficionado del PSG viajó a Bucarest en lugar de Budapest y se perdió la final de la Champions League</t>
         </is>
       </c>
       <c r="E230" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/elecciones-presidenciales-2026-como-marcar-la-tarjeta-electoral/</t>
+          <t>https://www.elcolombiano.com/deportes/aficionado-psg-error-viaje-final-champions-DB37143642</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 05:48 p. m.</t>
+          <t>30/05/2026 03:33 p. m.</t>
         </is>
       </c>
       <c r="B231" s="6" t="inlineStr">
@@ -6672,24 +6700,24 @@
       </c>
       <c r="C231" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D231" s="7" t="inlineStr">
         <is>
-          <t>¡No lo bote! Las marcas y beneficios legales que premian su certificado electoral este 31 de mayo</t>
+          <t>La tasa de usura supera el 28% y hará más costosas las compras a crédito para el Mundial</t>
         </is>
       </c>
       <c r="E231" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/no-lo-bote-las-marcas-y-beneficios-legales-que-premian-su-certificado-electoral-este-31-de-mayo/</t>
+          <t>https://www.elcolombiano.com/negocios/tasa-usura-junio-compras-credito-mundial-EB37144321</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 05:39 p. m.</t>
+          <t>30/05/2026 03:33 p. m.</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -6699,24 +6727,24 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D232" s="4" t="inlineStr">
         <is>
-          <t>Terremoto político y judicial: Santiago Botero Jaramillo, denunciado por presunta violencia intrafamiliar</t>
+          <t>Nacional vs. Junior: tres finalistas de 2015 repiten en la serie final del Apertura-2026</t>
         </is>
       </c>
       <c r="E232" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/terremoto-politico-y-judicial-santiago-botero-jaramillo-denunciado-por-presunta-violencia-intrafamiliar/</t>
+          <t>https://www.elcolombiano.com/deportes/futbol/final-nacional-junior-repitentes-definicion-titulo-2015-liga-betplay-2026-1-PB37144830</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 11:07 a. m.</t>
+          <t>30/05/2026 03:33 p. m.</t>
         </is>
       </c>
       <c r="B233" s="6" t="inlineStr">
@@ -6726,24 +6754,24 @@
       </c>
       <c r="C233" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D233" s="7" t="inlineStr">
         <is>
-          <t>Myke Towers confirma concierto en Bogotá con su gira “Trap Kings”</t>
+          <t>Video | Giro en caso de Alexánder Avendaño, el joven hallado muerto en embalse El Peñol-Guatapé</t>
         </is>
       </c>
       <c r="E233" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/myke-towers-confirma-concierto-en-bogota-con-su-gira-trap-kings/</t>
+          <t>https://www.elcolombiano.com/antioquia/video-alexander-avendano-hallado-muerto-embalse-el-penol-guatape-OB37144813</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:51 a. m.</t>
+          <t>30/05/2026 02:33 p. m.</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -6753,24 +6781,24 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D234" s="4" t="inlineStr">
         <is>
-          <t>Acoso callejero Colombia: el 89% de las mujeres afirma haberlo sufrido</t>
+          <t>PSG hace historia: bicampeón de la Champions tras vencer al Arsenal en una final épica</t>
         </is>
       </c>
       <c r="E234" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/acoso-callejero-colombia-mujeres/</t>
+          <t>https://www.elcolombiano.com/deportes/futbol/psg-bicampeon-champions-final-arsenal-resultado-prorroga-penaltis-CB37143221</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:44 a. m.</t>
+          <t>30/05/2026 01:33 p. m.</t>
         </is>
       </c>
       <c r="B235" s="6" t="inlineStr">
@@ -6780,24 +6808,24 @@
       </c>
       <c r="C235" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D235" s="7" t="inlineStr">
         <is>
-          <t>Outdoor femenino Colombia: la tendencia que une aventura, naturaleza y comunidad</t>
+          <t>Prográmese y siga estas recomendaciones para votar el 31 de mayo</t>
         </is>
       </c>
       <c r="E235" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/outdoor-femenino-colombia/</t>
+          <t>https://qhubomedellin.com/util-para-vos/recomendaciones-para-votar-el-31-de-mayo-presidenciales-EO36920523</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:35 a. m.</t>
+          <t>30/05/2026 01:33 p. m.</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -6807,24 +6835,24 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D236" s="4" t="inlineStr">
         <is>
-          <t>Bibliotecas para inspirar Cali: nueva apuesta por la lectura y los proyectos de vida</t>
+          <t>EN VIDEO: Cohete de Jeff Bezos explotó durante prueba de encendido</t>
         </is>
       </c>
       <c r="E236" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/bibliotecas-para-inspirar-cali/</t>
+          <t>https://qhubomedellin.com/actualidad/internacional/cohete-de-jeff-bezos-explota-durante-prueba-de-encendido-NH37129271</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:32 a. m.</t>
+          <t>30/05/2026 11:33 a. m.</t>
         </is>
       </c>
       <c r="B237" s="6" t="inlineStr">
@@ -6834,24 +6862,24 @@
       </c>
       <c r="C237" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D237" s="7" t="inlineStr">
         <is>
-          <t>Detección temprana cáncer de mama Colombia: la importancia de las redes de apoyo</t>
+          <t>Camila Osorio lo dejó todo, pero no pudo avanzar a octavos de final en Roland Garros</t>
         </is>
       </c>
       <c r="E237" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/deteccion-temprana-cancer-de-mama-colombia/</t>
+          <t>https://www.elcolombiano.com/deportes/camila-osorio-kalinskaya-roland-garros-MG37139005</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:27 a. m.</t>
+          <t>30/05/2026 11:33 a. m.</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -6861,24 +6889,24 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D238" s="4" t="inlineStr">
         <is>
-          <t>Cuidado del cabello y la piel en vacaciones: errores que debes evitar</t>
+          <t>Exclusivo | Así le hacen campaña a Cepeda los equipos básicos del MinSalud en La Guajira</t>
         </is>
       </c>
       <c r="E238" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/cuidado-del-cabello-y-la-piel-en-vacaciones/</t>
+          <t>https://www.elcolombiano.com/especiales/elecciones-2026/campana-cepeda-los-equipos-basicos-minsalud-en-la-guajira-NG37139848</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:18 a. m.</t>
+          <t>30/05/2026 10:33 a. m.</t>
         </is>
       </c>
       <c r="B239" s="6" t="inlineStr">
@@ -6888,24 +6916,24 @@
       </c>
       <c r="C239" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D239" s="7" t="inlineStr">
         <is>
-          <t>Bebé de 6 meses El Espinal: avanzan investigaciones tras su fallecimiento</t>
+          <t>Desde el 3 de junio habrá cierre en la vía San Nicolás–La Ceja, ¿por qué?</t>
         </is>
       </c>
       <c r="E239" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/bebe-de-6-meses-el-espinal/</t>
+          <t>https://www.elcolombiano.com/antioquia/cierres-viales-via-san-nicolas-rionegro-la-ceja-antioquia-BG37138584</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 09:10 a. m.</t>
+          <t>30/05/2026 10:33 a. m.</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -6915,24 +6943,24 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D240" s="4" t="inlineStr">
         <is>
-          <t>Fiesta en El Campín: Morat cantará en la despedida de la Selección Colombia rumbo al Mundial 2026</t>
+          <t>¡Ojo! Caficultores de Bello tienen hasta este 31 de mayo para acceder a apoyos en cultivos</t>
         </is>
       </c>
       <c r="E240" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/fiesta-en-el-campin-morat-cantara-en-la-despedida-de-la-seleccion-colombia-rumbo-al-mundial-2026/</t>
+          <t>https://www.elcolombiano.com/antioquia/plazo-caficultores-de-bello-antioquia-apoyos-cafetales-FG37138973</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 09:03 a. m.</t>
+          <t>30/05/2026 10:33 a. m.</t>
         </is>
       </c>
       <c r="B241" s="6" t="inlineStr">
@@ -6942,24 +6970,24 @@
       </c>
       <c r="C241" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D241" s="7" t="inlineStr">
         <is>
-          <t>Orgullo colombiano: Kapo es coronado como ‘Compositor del Año’ en los SESAC Latina Music Awards 2026</t>
+          <t>Más de 100 exalcaldes de Antioquia anuncian su respaldo a Paloma Valencia y Juan Daniel Oviedo</t>
         </is>
       </c>
       <c r="E241" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/orgullo-colombiano-kapo-es-coronado-como-compositor-del-ano-en-los-sesac-latina-music-awards-2026/</t>
+          <t>https://www.elcolombiano.com/antioquia/exalcaldes-antioquia-apoyan-paloma-valencia-HG37138834</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 08:56 a. m.</t>
+          <t>30/05/2026 09:33 a. m.</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -6969,24 +6997,24 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D242" s="4" t="inlineStr">
         <is>
-          <t>De Medellín para el mundo: elkno enciende la escena urbana con su dancehall “Ritmo”</t>
+          <t>Gobierno rechaza acuerdo entre Noboa y De la Espriella para eliminar aranceles: “es un injerencia deliberada” en elecciones</t>
         </is>
       </c>
       <c r="E242" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/de-medellin-para-el-mundo-elkno-enciende-la-escena-urbana-con-su-dancehall-ritmo/</t>
+          <t>https://www.elcolombiano.com/colombia/petro-arremete-contra-daniel-noboa-bernie-moreno-aranceles-elecciones-PG37137769</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 08:53 a. m.</t>
+          <t>30/05/2026 09:33 a. m.</t>
         </is>
       </c>
       <c r="B243" s="6" t="inlineStr">
@@ -6996,24 +7024,24 @@
       </c>
       <c r="C243" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D243" s="7" t="inlineStr">
         <is>
-          <t>Cine colombiano: ‘VOLAR’ llega a las salas con un retrato íntimo de la soledad en Bogotá</t>
+          <t>La exigencia física le pasó factura a David Alonso en Italia que correrá este domingo, ¿cómo y dónde ver la carrera?</t>
         </is>
       </c>
       <c r="E243" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/cine-colombiano-volar-llega-a-las-salas-con-un-retrato-intimo-de-la-soledad-en-bogota/</t>
+          <t>https://www.elcolombiano.com/deportes/david-alonso-moto2-gp-italia-clasificacion-motogp-BG37137644</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 08:49 a. m.</t>
+          <t>30/05/2026 08:33 a. m.</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -7023,24 +7051,24 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D244" s="4" t="inlineStr">
         <is>
-          <t>Desde República Dominicana para el despecho: Amneliz debuta en la música popular con “El Desquite”</t>
+          <t>Candidato Santiago Botero fue desalojado de su casa tras impedir el ingreso de su esposa e hijo; tiene una denuncia por violencia intrafamiliar</t>
         </is>
       </c>
       <c r="E244" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/desde-republica-dominicana-para-el-despecho-amneliz-debuta-en-la-musica-popular-con-el-desquite/</t>
+          <t>https://www.elcolombiano.com/colombia/santiago-botero-desalojo-casa-cartagena-IG37136842</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 08:45 a. m.</t>
+          <t>30/05/2026 06:33 a. m.</t>
         </is>
       </c>
       <c r="B245" s="6" t="inlineStr">
@@ -7050,24 +7078,24 @@
       </c>
       <c r="C245" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D245" s="7" t="inlineStr">
         <is>
-          <t>Giro en el caso de Mía Cataleya: Revelan crudos detalles de su ingreso al hospital y una captura en El Espinal</t>
+          <t>A lomo de mula y cruzando ríos: así logró reducir el hambre Antioquia</t>
         </is>
       </c>
       <c r="E245" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/giro-en-el-caso-de-mia-cataleya-revelan-crudos-detalles-de-su-ingreso-al-hospital-y-una-captura-en-el-espinal/</t>
+          <t>https://www.elcolombiano.com/antioquia/estrategia-contra-el-hambre-y-la-desnutricion-en-antioquia-JG37134638</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 08:24 a. m.</t>
+          <t>30/05/2026 06:33 a. m.</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -7077,24 +7105,24 @@
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D246" s="4" t="inlineStr">
         <is>
-          <t>«Vi una pierna afuera»: Los crudos testimonios del hallazgo del profesor Kevin Santiago Ángel en Kennedy</t>
+          <t>Lo que debe saber para votar este domingo: ¿alguno podría ganar en primera vuelta?</t>
         </is>
       </c>
       <c r="E246" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/vi-una-pierna-afuera-los-crudos-testimonios-del-hallazgo-del-profesor-kevin-santiago-angel-en-kennedy/</t>
+          <t>https://www.elcolombiano.com/especiales/elecciones-2026/elecciones-2026-consulta-puesto-votacion-horarios-primera-vuelta-PG37135864</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 08:12 a. m.</t>
+          <t>30/05/2026 05:33 a. m.</t>
         </is>
       </c>
       <c r="B247" s="6" t="inlineStr">
@@ -7104,26 +7132,22 @@
       </c>
       <c r="C247" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D247" s="7" t="inlineStr">
         <is>
-          <t>Giro en el caso de Ana María Meza: Fiscalía confirma que se investiga como presunto feminicidio</t>
+          <t>Calor dispara en más de 50% la venta de ventiladores en El Hueco, en Medellín: estos son los más vendidos</t>
         </is>
       </c>
       <c r="E247" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/giro-en-el-caso-de-ana-maria-meza-fiscalia-confirma-que-se-investiga-como-presunto-feminicidio/</t>
+          <t>https://www.elcolombiano.com/medellin/calor-medellin-ventas-ventiladores-hueco-KG37131092</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="3" t="inlineStr">
-        <is>
-          <t>29/05/2026 08:08 a. m.</t>
-        </is>
-      </c>
+      <c r="A248" s="3" t="inlineStr"/>
       <c r="B248" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7131,26 +7155,22 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D248" s="4" t="inlineStr">
         <is>
-          <t>El silencio forzado de Afganistán: El año en que las mujeres perdieron el derecho a existir en público</t>
+          <t>21 municipios en riesgo electoral y récord en testigos: así llega Antioquia a las elecciones</t>
         </is>
       </c>
       <c r="E248" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/el-silencio-forzado-de-afganistan-el-ano-en-que-las-mujeres-perdieron-el-derecho-a-existir-en-publico/</t>
+          <t>https://www.elcolombiano.com/antioquia/antioquia-riesgo-electoral-testigos-preparacion-elecciones-presidenciales-2026-PG37135846</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="6" t="inlineStr">
-        <is>
-          <t>28/05/2026 11:24 a. m.</t>
-        </is>
-      </c>
+      <c r="A249" s="6" t="inlineStr"/>
       <c r="B249" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7158,26 +7178,22 @@
       </c>
       <c r="C249" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D249" s="7" t="inlineStr">
         <is>
-          <t>Jóvenes elecciones Colombia 2026: TikTok e IA cambian las campañas</t>
+          <t>Así se enriqueció la novia de Petro</t>
         </is>
       </c>
       <c r="E249" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/jovenes-elecciones-colombia-2026/</t>
+          <t>https://www.elcolombiano.com/multimedia/videos/asi-se-enriquecio-la-novia-de-petro-IH37120899</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="3" t="inlineStr">
-        <is>
-          <t>28/05/2026 11:18 a. m.</t>
-        </is>
-      </c>
+      <c r="A250" s="3" t="inlineStr"/>
       <c r="B250" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7185,26 +7201,22 @@
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D250" s="4" t="inlineStr">
         <is>
-          <t>Seguridad en vehículos de trabajo: la tecnología redefine el transporte de carga</t>
+          <t>Operativo destapa helicóptero con pasado oscuro y motor Rolls-Royce</t>
         </is>
       </c>
       <c r="E250" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/seguridad-en-vehiculos-de-trabajo/</t>
+          <t>https://www.elcolombiano.com/colombia/ejercito-incauta-helicoptero-de-la-mafia-NG33717192</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="6" t="inlineStr">
-        <is>
-          <t>28/05/2026 10:45 a. m.</t>
-        </is>
-      </c>
+      <c r="A251" s="6" t="inlineStr"/>
       <c r="B251" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7212,26 +7224,22 @@
       </c>
       <c r="C251" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D251" s="7" t="inlineStr">
         <is>
-          <t>De Mar y Río lanza “Cantaré”, un homenaje al Pacífico colombiano</t>
+          <t>Voraz incendio consumió vivienda en Itagüí y dejó a una familia sin nada</t>
         </is>
       </c>
       <c r="E251" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/de-mar-y-rio-lanza-cantare-un-homenaje-al-pacifico-colombiano/</t>
+          <t>https://www.elcolombiano.com/antioquia/incendio-vivienda-itagui-el-guayabo-una-familia-sin-nada-AG37135775</t>
         </is>
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="3" t="inlineStr">
-        <is>
-          <t>28/05/2026 10:04 a. m.</t>
-        </is>
-      </c>
+      <c r="A252" s="3" t="inlineStr"/>
       <c r="B252" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7239,26 +7247,22 @@
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D252" s="4" t="inlineStr">
         <is>
-          <t>Helipuertos en Bogotá: la nueva tendencia para vivir experiencias exclusivas</t>
+          <t>¡Le interesa! Este domingo habrá café gratis y descuentos en 120 marcas en Antioquia presentando el certificado de votación</t>
         </is>
       </c>
       <c r="E252" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/helipuertos-en-bogota-experiencias/</t>
+          <t>https://www.elcolombiano.com/medellin/descuentos-y-beneficios-en-medellin-por-votar-elecciones-2026-IF37102578</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="6" t="inlineStr">
-        <is>
-          <t>28/05/2026 10:00 a. m.</t>
-        </is>
-      </c>
+      <c r="A253" s="6" t="inlineStr"/>
       <c r="B253" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7266,26 +7270,22 @@
       </c>
       <c r="C253" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D253" s="7" t="inlineStr">
         <is>
-          <t>Orgullo vallenato: Jorge Celedón hace historia y conquista el #1 de la radio en Centroamérica</t>
+          <t>Maluma habló de las elecciones en Colombia y lanzó inesperada propuesta para llevar votantes</t>
         </is>
       </c>
       <c r="E253" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/orgullo-vallenato-jorge-celedon-hace-historia-y-conquista-el-1-de-la-radio-en-centroamerica/</t>
+          <t>https://www.elcolombiano.com/entretenimiento/maluma-hablo-elecciones-colombia-lanzo-inesperada-propuesta-votantes-IF37100945</t>
         </is>
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="3" t="inlineStr">
-        <is>
-          <t>28/05/2026 09:58 a. m.</t>
-        </is>
-      </c>
+      <c r="A254" s="3" t="inlineStr"/>
       <c r="B254" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7293,24 +7293,24 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D254" s="4" t="inlineStr">
         <is>
-          <t>Alea Animal Distinta: el himno de autenticidad y empoderamiento femenino</t>
+          <t>¿Qué proponen en materia de impuestos los candidatos presidenciales punteros?</t>
         </is>
       </c>
       <c r="E254" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/alea-animal-distinta-video/</t>
+          <t>https://www.elcolombiano.com/especiales/elecciones-2026/yo-cuido-la-democracia/propuestas-de-los-candidatos-presidenciales-GB37052040</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:19 p. m.</t>
+          <t>30/05/2026 08:33 p. m.</t>
         </is>
       </c>
       <c r="B255" s="6" t="inlineStr">
@@ -7337,7 +7337,7 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:19 p. m.</t>
+          <t>30/05/2026 08:33 p. m.</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -7364,7 +7364,7 @@
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 07:01 p. m.</t>
+          <t>30/05/2026 07:33 p. m.</t>
         </is>
       </c>
       <c r="B257" s="6" t="inlineStr">
@@ -7391,7 +7391,7 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 07:01 p. m.</t>
+          <t>30/05/2026 06:33 p. m.</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -7418,7 +7418,7 @@
     <row r="259">
       <c r="A259" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 04:01 p. m.</t>
+          <t>30/05/2026 03:33 p. m.</t>
         </is>
       </c>
       <c r="B259" s="6" t="inlineStr">
@@ -7445,7 +7445,7 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 03:01 p. m.</t>
+          <t>30/05/2026 02:33 p. m.</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
@@ -7472,7 +7472,7 @@
     <row r="261">
       <c r="A261" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 04:01 a. m.</t>
+          <t>30/05/2026 03:33 a. m.</t>
         </is>
       </c>
       <c r="B261" s="6" t="inlineStr">
@@ -7499,7 +7499,7 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 04:01 a. m.</t>
+          <t>30/05/2026 03:33 a. m.</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
@@ -7526,7 +7526,7 @@
     <row r="263">
       <c r="A263" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 04:01 a. m.</t>
+          <t>30/05/2026 03:33 a. m.</t>
         </is>
       </c>
       <c r="B263" s="6" t="inlineStr">
@@ -7541,19 +7541,19 @@
       </c>
       <c r="D263" s="7" t="inlineStr">
         <is>
-          <t>Los días difíciles de Paloma Valencia: con un cambio de estrategia, que la llevó a atacar a Abelardo de la Espriella, así llega a las elecciones la candidata del Centro Democrático</t>
+          <t>La última elección de Sergio Fajardo: el profesor busca la Presidencia reivindicando una forma diferente de hacer política</t>
         </is>
       </c>
       <c r="E263" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/los-dias-dificiles-de-paloma-valencia-con-un-cambio-de-estrategia-que-la-llevo-a-atacar-a-abelardo-de-la-espriella-asi-llega-a-las-elecciones-la-candidata-del-centro-democratico/202608/</t>
+          <t>https://www.semana.com/politica/articulo/la-ultima-eleccion-de-sergio-fajardo-el-profesor-busca-la-presidencia-reivindicando-una-forma-diferente-de-hacer-politica/202654/</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 04:01 a. m.</t>
+          <t>30/05/2026 03:33 a. m.</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
@@ -7568,19 +7568,19 @@
       </c>
       <c r="D264" s="4" t="inlineStr">
         <is>
-          <t>Los contrastes de Aida Quilcué y José Manuel Restrepo: estos son los perfiles de los candidatos a la Vicepresidencia más opcionados</t>
+          <t>Los días difíciles de Paloma Valencia: con un cambio de estrategia, que la llevó a atacar a Abelardo de la Espriella, así llega a las elecciones la candidata del Centro Democrático</t>
         </is>
       </c>
       <c r="E264" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/los-contrastes-de-aida-quilcue-y-jose-manuel-restrepo-estos-son-los-perfiles-de-los-candidatos-a-la-vicepresidencia-mas-opcionados/202625/</t>
+          <t>https://www.semana.com/politica/articulo/los-dias-dificiles-de-paloma-valencia-con-un-cambio-de-estrategia-que-la-llevo-a-atacar-a-abelardo-de-la-espriella-asi-llega-a-las-elecciones-la-candidata-del-centro-democratico/202608/</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 03:01 a. m.</t>
+          <t>30/05/2026 03:33 a. m.</t>
         </is>
       </c>
       <c r="B265" s="6" t="inlineStr">
@@ -7595,19 +7595,19 @@
       </c>
       <c r="D265" s="7" t="inlineStr">
         <is>
-          <t>La última elección de Sergio Fajardo: el profesor busca la Presidencia reivindicando una forma diferente de hacer política</t>
+          <t>Los contrastes de Aida Quilcué y José Manuel Restrepo: estos son los perfiles de los candidatos a la Vicepresidencia más opcionados</t>
         </is>
       </c>
       <c r="E265" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/la-ultima-eleccion-de-sergio-fajardo-el-profesor-busca-la-presidencia-reivindicando-una-forma-diferente-de-hacer-politica/202654/</t>
+          <t>https://www.semana.com/politica/articulo/los-contrastes-de-aida-quilcue-y-jose-manuel-restrepo-estos-son-los-perfiles-de-los-candidatos-a-la-vicepresidencia-mas-opcionados/202625/</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 03:01 a. m.</t>
+          <t>30/05/2026 03:33 a. m.</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -7634,7 +7634,7 @@
     <row r="267">
       <c r="A267" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 02:01 a. m.</t>
+          <t>30/05/2026 01:33 a. m.</t>
         </is>
       </c>
       <c r="B267" s="6" t="inlineStr">
@@ -7649,19 +7649,19 @@
       </c>
       <c r="D267" s="7" t="inlineStr">
         <is>
-          <t>Esta es la lista de urgencias económicas que recibirá el nuevo Gobierno. Diagnóstico de 13 gremios claves</t>
+          <t>“Mi papá estaría orgulloso”, la historia de los 70 años de Pajares Salinas</t>
         </is>
       </c>
       <c r="E267" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/economia/empresas/articulo/esta-es-la-lista-de-urgencias-economicas-que-recibira-el-nuevo-gobierno-diagnostico-de-13-gremios-claves/202652/</t>
+          <t>https://www.semana.com/cultura/articulo/mi-papa-estaria-orgulloso-la-historia-de-los-70-anos-de-pajares-salinas/202601/</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 01:01 a. m.</t>
+          <t>30/05/2026 01:33 a. m.</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
@@ -7676,19 +7676,19 @@
       </c>
       <c r="D268" s="4" t="inlineStr">
         <is>
-          <t>“Mi papá estaría orgulloso”, la historia de los 70 años de Pajares Salinas</t>
+          <t>Esta es la lista de urgencias económicas que recibirá el nuevo Gobierno. Diagnóstico de 13 gremios claves</t>
         </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/cultura/articulo/mi-papa-estaria-orgulloso-la-historia-de-los-70-anos-de-pajares-salinas/202601/</t>
+          <t>https://www.semana.com/economia/empresas/articulo/esta-es-la-lista-de-urgencias-economicas-que-recibira-el-nuevo-gobierno-diagnostico-de-13-gremios-claves/202652/</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 01:01 a. m.</t>
+          <t>30/05/2026 12:33 a. m.</t>
         </is>
       </c>
       <c r="B269" s="6" t="inlineStr">

--- a/public/ultimahora.xlsx
+++ b/public/ultimahora.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Todas las noticias" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Todas las noticias'!$A$1:$E$319</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Todas las noticias'!$A$1:$E$305</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E319"/>
+  <dimension ref="A1:E305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 09:24 p. m.</t>
+          <t>31/05/2026 08:56 p. m.</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -542,19 +542,19 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Baloto y Baloto Revancha: conozca aquí los resultados del último sorteo del sábado 30 de mayo de 2026</t>
+          <t>Colombia vs. Costa Rica: ¿saturar a Luis Díaz o aprovechar para buscar relevos?</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/economia/finanzas-personales/baloto-y-baloto-revancha-conozca-aqui-los-resultados-del-ultimo-sorteo-del-sabado-30-de-mayo-de-3559713</t>
+          <t>https://www.eltiempo.com/deportes/futbol-internacional/colombia-vs-costa-rica-saturar-a-luis-diaz-o-aprovechar-para-buscar-relevos-3560980</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 09:01 p. m.</t>
+          <t>31/05/2026 08:49 p. m.</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -569,19 +569,19 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>De una biblioteca comunitaria al Kennedy Space Center: el sueño espacial de cinco jóvenes bogotanos</t>
+          <t>Elecciones presidenciales 2026: los departamentos donde ganaron Abelardo de la Espriella e Iván Cepeda en primera vuelta</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/bogota/de-una-biblioteca-comunitaria-al-kennedy-space-center-el-sueno-espacial-de-cinco-jovenes-bogotanos-3558559</t>
+          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/resultados-presidenciales-2026-primera-vuelta/elecciones-presidenciales-2026-los-departamentos-donde-ganaron-abelardo-de-la-espriella-e-ivan-cepeda-en-primera-vuelta-3560985</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:33 p. m.</t>
+          <t>31/05/2026 08:49 p. m.</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -596,19 +596,19 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>#ElFiltro: video sobre supuestos tarjetones marcados a favor de Abelardo de la Espriella y Paloma Valencia no corresponde a elecciones presidenciales</t>
+          <t>Elecciones presidenciales 2026: Miguel Uribe Londoño agradeció a todas las personas que lo acompañaron y dijo que la causa de su hijo seguirá vigente</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/elfiltro-video-sobre-supuestos-tarjetones-marcados-a-favor-de-abelardo-de-la-espriella-y-paloma-valencia-no-corresponde-a-elecciones-presidenciales-3559703</t>
+          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/resultados-presidenciales-2026-primera-vuelta/elecciones-presidenciales-2026-miguel-uribe-londono-agradecio-a-todas-las-personas-que-lo-acompanaron-y-dijo-que-la-causa-de-su-hijo-seguira-vigente-3560986</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:29 p. m.</t>
+          <t>31/05/2026 08:47 p. m.</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -623,19 +623,19 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Cristhian Mosquera, español de raíces colombianas, aguanta críticas y burlas tras cometer penalti decisivo en la final de la Champions League</t>
+          <t>Primera vuelta con sello nariñense: Iván Cepeda lidera, la abstención se debate y la seguridad se impone en sus 64 municipios</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/deportes/futbol-internacional/cristhian-mosquera-espanol-de-raices-colombianas-aguanta-criticas-y-burlas-tras-cometer-penalti-decisivo-en-la-final-de-la-champions-league-3559704</t>
+          <t>https://www.eltiempo.com/colombia/cali/primera-vuelta-con-sello-narinense-ivan-cepeda-lidera-la-abstencion-se-debate-y-la-seguridad-se-impone-en-sus-64-municipios-3560984</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:13 p. m.</t>
+          <t>31/05/2026 08:46 p. m.</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -650,19 +650,19 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Cuentas Claras / Air-e, patrimonio que cae casi en su totalidad</t>
+          <t>Abelardo de la Espriella e Iván Cepeda son los candidatos más votados en una primera vuelta en las elecciones presidenciales de Colombia</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/economia/sectores/cuentas-claras-air-e-patrimonio-que-cae-casi-en-su-totalidad-3559633</t>
+          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/abelardo-de-la-espriella-e-ivan-cepeda-superaron-la-votacion-en-primera-vuelta-de-gustavo-petro-en-2022-en-las-elecciones-de-colombia-3560981</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:01 p. m.</t>
+          <t>31/05/2026 08:37 p. m.</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -677,19 +677,19 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Alejandro Char responde a los señalamientos del presidente Gustavo Petro y asegura que Barranquilla financia la mayor parte del PAE</t>
+          <t>Bogotá transforma escombros clandestinos en material de construcción para las vías: así funciona el plan de economía circular para salvar a Doña Juana</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/politica/gobierno/alejandro-char-responde-a-los-senalamientos-del-presidente-gustavo-petro-y-asegura-que-barranquilla-financia-la-mayor-parte-del-pae-3559696</t>
+          <t>https://www.eltiempo.com/bogota/bogota-transforma-escombros-clandestinos-en-material-de-construccion-para-las-vias-asi-funciona-el-plan-de-economia-circular-para-salvar-a-dona-juana-3556875</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 07:31 p. m.</t>
+          <t>31/05/2026 08:24 p. m.</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -704,19 +704,19 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Entrevista de Westcol con Abelardo de la Espriella: porte legal de armas, megacárceles y las principales propuestas de su plan de gobierno</t>
+          <t>Javier Milei, presidente de Argentina, felicitó a Abelardo de la Espriella por ganar primera vuelta: 'Este resultado refleja el anhelo de libertad'</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/cultura/gente/entrevista-de-westcol-con-abelardo-de-la-espriella-su-plan-de-construir-10-megacarceles-y-las-apuestas-clave-de-su-programa-de-gobierno-3559697</t>
+          <t>https://www.eltiempo.com/mundo/latinoamerica/javier-milei-presidente-de-argentina-felicito-a-abelardo-de-la-espriella-por-su-paso-a-segunda-vuelta-este-resultado-refleja-el-anhelo-de-libertad-3560975</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 07:00 p. m.</t>
+          <t>31/05/2026 08:22 p. m.</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -731,19 +731,19 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Autoridades de Nariño investigan amenazas de grupo armado contra campesinos previo a elecciones presidenciales: ‘Se va a exigir certificado electoral’</t>
+          <t>¿Qué hacer si perdió el certificado electoral y quiere reclamar sus beneficios?</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/colombia/cali/autoridades-de-narino-investigan-amenazas-de-grupo-armado-contra-campesinos-previo-a-elecciones-presidenciales-se-va-a-exigir-certificado-electoral-3559695</t>
+          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/que-hacer-si-perdio-el-certificado-electoral-y-quiere-reclamar-sus-beneficios-3560971</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 06:57 p. m.</t>
+          <t>31/05/2026 08:20 p. m.</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -758,19 +758,19 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Andrés Llinás pone el pecho por el mal semestre de Millonarios y les habla claro a los hinchas: 'No estuvimos a la altura'</t>
+          <t>Fotos | Así celebraron los seguidores de Abelardo de la Espriella en Barranquilla, Bucaramanga, Cali y otras ciudades tras pasar a la segunda vuelta</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/deportes/futbol-colombiano/andres-llinas-pone-el-pecho-por-el-mal-semestre-de-millonarios-y-les-habla-claro-a-los-hinchas-no-estuvimos-a-la-altura-3559691</t>
+          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/fotos-asi-celebraron-los-seguidores-de-abelardo-de-la-espriella-en-barranquilla-bucaramanga-cali-y-otras-ciudades-tras-pasar-a-la-segunda-vuelta-3560961</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 06:36 p. m.</t>
+          <t>31/05/2026 08:11 p. m.</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -785,19 +785,19 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Abuelita de Pereira envió $700 mil al Nequi equivocado y lanza desesperado llamado para recuperar su dinero: 'Devuélvanme la platica'</t>
+          <t>El país votó en paz: así se desarrolló la primera vuelta presidencial en materia de orden público</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/cultura/gente/abuelita-de-pereira-envio-700-mil-al-nequi-equivocado-y-lanza-desesperado-llamado-para-recuperar-su-dinero-devuelvanme-la-platica-3559693</t>
+          <t>https://www.eltiempo.com/justicia/investigacion/el-pais-voto-en-paz-asi-se-desarrollo-la-primera-vuelta-presidencial-en-materia-de-orden-publico-3560938</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 06:31 p. m.</t>
+          <t>31/05/2026 08:10 p. m.</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,19 +812,19 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>De caminatas en el campo a innovación sostenible: la historia de Fungalic, el proyecto que transforma residuos en soluciones con hongos</t>
+          <t>Roy Barreras reiteró su apoyo a Iván Cepeda y le pidió 'abrir la campaña' para que Abelardo de la Espriella no sea presidente</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/colombia/medellin/de-caminatas-en-el-campo-a-innovacion-sostenible-la-historia-de-fungalic-el-proyecto-que-transforma-residuos-en-soluciones-con-hongos-3559692</t>
+          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/resultados-presidenciales-2026-primera-vuelta/roy-barreras-anuncio-su-apoyo-a-ivan-cepeda-y-le-pidio-abrir-la-campana-para-que-abelardo-de-la-espriella-no-sea-presidente-3560974</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 06:30 p. m.</t>
+          <t>31/05/2026 08:06 p. m.</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -839,19 +839,19 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Así blindará Bogotá su seguridad para las elecciones de este domingo 29 de mayo: 11.000 policías, 2.100 soldados y ley seca</t>
+          <t>Senador Bernie Moreno felicitó a Abelardo de la Espriella por obtener la mayor votación en la primera vuelta presidencial: 'La democracia ganó hoy'</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/bogota/asi-blindara-bogota-su-seguridad-para-las-elecciones-de-este-domingo-29-de-mayo-11-000-policias-2-100-soldados-y-ley-seca-3559689</t>
+          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/resultados-presidenciales-2026-primera-vuelta/senador-bernie-moreno-felicito-a-abelardo-de-la-espriella-por-obtener-la-mayor-votacion-en-la-primera-vuelta-presidencial-la-democracia-gano-hoy-3560976</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 05:57 p. m.</t>
+          <t>31/05/2026 08:03 p. m.</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -866,19 +866,19 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>La USO respalda fortalecer la exploración de hidrocarburos para garantizar la sostenibilidad de Ecopetrol de cara a las elecciones presidenciales</t>
+          <t>FOTOS | Los rostros desde la sede de campaña de Iván Cepeda y Aida Quilcué tras pasar a segunda vuelta presidencial contra Abelardo de la Espriella</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/economia/sectores/la-union-sindical-obrera-uso-respalda-fortalecer-la-exploracion-de-hidrocarburos-para-garantizar-la-sostenibilidad-de-ecopetrol-3559690</t>
+          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/fotos-los-rostros-desde-la-sede-de-campana-de-ivan-cepeda-y-aida-quilcue-tras-pasar-a-segunda-vuelta-presidencial-contra-abelardo-de-la-espriella-3560969</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 05:48 p. m.</t>
+          <t>31/05/2026 08:01 p. m.</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -893,19 +893,19 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>109 vidas perdidas en 2026: así acompaña Medellín a las familias que enfrentan el duelo por accidentes de tránsito</t>
+          <t>¿Se puede cambiar el puesto de votación para la segunda vuelta? Esto respondió la Registraduría Nacional del Estado Civil</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/colombia/medellin/109-vidas-perdidas-en-2026-asi-acompana-medellin-a-las-familias-que-enfrentan-el-duelo-por-accidentes-de-transito-3559687</t>
+          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/resultados-presidenciales-2026-primera-vuelta/se-puede-cambiar-el-puesto-de-votacion-para-la-segunda-vuelta-esto-respondio-la-registraduria-nacional-del-estado-civil-3560972</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 05:43 p. m.</t>
+          <t>31/05/2026 08:01 p. m.</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -920,19 +920,19 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Exclusivo: habla esposa del candidato presidencial Santiago Botero, desalojado en Cartagena por presunto caso de violencia intrafamiliar</t>
+          <t>Las reacciones de medios internacionales a la segunda vuelta entre Abelardo de la Espriella e Iván Cepeda por la Presidencia de Colombia</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/colombia/otras-ciudades/exclusivo-habla-esposa-del-candidato-presidencial-santiago-botero-desalojado-en-cartagena-por-violencia-intrafamiliar-a-horas-de-abrirse-las-urnas-3559682</t>
+          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/las-reacciones-de-medios-internacionales-a-la-segunda-vuelta-entre-abelardo-de-la-espriella-e-ivan-cepeda-por-la-presidencia-de-colombia-3560965</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 05:40 p. m.</t>
+          <t>31/05/2026 07:53 p. m.</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -947,19 +947,19 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Falleció el cuñado de alias ‘Castor’ tras más de dos meses hospitalizado: estaba herido desde la balacera afuera de billar en el norte de Barranquilla</t>
+          <t>Video | Neymar se roba el 'show' en victoria de Brasil: jugadores de Panamá hacen fila para tomarse una foto con él</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/colombia/barranquilla/fallecio-el-cunado-de-alias-castor-tras-mas-de-dos-meses-hospitalizado-estaba-herido-desde-la-balacera-afuera-de-billar-en-el-norte-de-barranquilla-3559688</t>
+          <t>https://www.eltiempo.com/deportes/futbol-internacional/video-neymar-se-roba-el-show-en-victoria-de-brasil-jugadores-de-panama-hacen-fila-para-tomarse-una-foto-con-el-3560973</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 05:15 p. m.</t>
+          <t>31/05/2026 07:40 p. m.</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -974,19 +974,19 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Tragedia en la vía Santa Marta-Palomino: una pasajera se cayó cuando intentaba subirse a la buseta y murió arrollada por el mismo vehículo</t>
+          <t>Iván Cepeda dice que se pronunciará luego de los resultados de comisión escrutadora sobre la primera vuelta presidencial de Colombia 2026</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/colombia/otras-ciudades/tragedia-en-la-via-santa-marta-palomino-una-pasajera-se-cayo-cuando-intentaba-subirse-a-la-buseta-y-murio-arrollada-por-el-mismo-vehiculo-3559683</t>
+          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/ivan-cepeda-dice-que-se-pronunciara-luego-de-los-resultados-de-comision-escrutadora-sobre-la-primera-vuelta-3560966</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 05:12 p. m.</t>
+          <t>31/05/2026 07:38 p. m.</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -1001,19 +1001,19 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Shakira comparte video bailando con los Ghetto Kids, el grupo ugandés que la acompañará en la final del Mundial 2026</t>
+          <t>Balance de la jornada electoral en el Valle del Cauca: participación masiva y orden público garantizado en 42 municipios</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/cultura/gente/shakira-comparte-video-bailando-con-los-ghetto-kids-el-grupo-ugandes-que-la-acompanara-en-la-final-del-mundial-3559686</t>
+          <t>https://www.eltiempo.com/colombia/cali/balance-de-la-jornada-electoral-en-el-valle-del-cauca-participacion-masiva-y-orden-publico-garantizado-en-42-municipios-3560964</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 05:05 p. m.</t>
+          <t>31/05/2026 07:37 p. m.</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1028,19 +1028,19 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Revelan el detrás de cámaras de 'Dai Dai', el video de Shakira del Mundial 2026, con Luis Díaz y las estrellas del Bayern Múnich</t>
+          <t>Estos son los 9 candidatos que fueron superados por el voto en blanco en las elecciones presidenciales de este 31 de mayo</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/deportes/futbol-internacional/revelan-el-detras-de-camaras-de-dai-dai-el-video-de-shakira-del-mundial-2026-con-luis-diaz-y-las-estrellas-del-bayern-munich-3559684</t>
+          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/estos-son-los-candidatos-que-fueron-superados-por-el-voto-en-blanco-en-las-elecciones-presidenciales-de-este-31-de-mayo-3560970</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 04:39 p. m.</t>
+          <t>31/05/2026 07:31 p. m.</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -1055,19 +1055,19 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Meteorito explota en Estados Unidos y genera un potente estruendo que se escuchó en varios estados</t>
+          <t>Gustavo Petro, Iván Duque, Juan Manuel Santos y los otros ganadores de la segunda vuelta en Colombia en los últimos años</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/mundo/eeuu-y-canada/meteorito-explota-en-estados-unidos-y-genera-un-potente-estruendo-que-se-escucho-en-varios-estados-3559677</t>
+          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/gustavo-petro-ivan-duque-juan-manuel-santos-y-los-otros-ganadores-de-la-segunda-vuelta-en-colombia-en-los-ultimos-anos-3560953</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 01:37 a. m.</t>
+          <t>01/06/2026 01:32 a. m.</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1082,19 +1082,19 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Millones de usuarios recibirán devolución por cobros indebidos en facturas de gas: cómo reclamar el dinero</t>
+          <t>“Ni se les ocurra desconocer la voluntad popular”: El mensaje de Abelardo de la Espriella camino a la segunda vuelta</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/actualidad/devolucion-facturas-gas-cobros-indebidos-guia-reclamar-dinero-400897</t>
+          <t>https://www.lafm.com.co/politica/abelardo-de-la-espriella-discurso-segunda-vuelta-elecciones-presidenciales-mensaje-gustavo-petro-ivan-cepeda-400969</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 01:05 a. m.</t>
+          <t>01/06/2026 12:57 a. m.</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -1109,19 +1109,19 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>“Los tengo que parar de entrenar”: la revelación de Luis Enrique sobre la plantilla del PSG</t>
+          <t>“No podemos volver a la muerte y a la exclusión”: el mensaje de Iván cepeda y Aida Quilcué tras la votación</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/deportes/luis-enrique-aseguro-que-debe-parar-de-entrenar-a-jugadores-psg-400896</t>
+          <t>https://www.lafm.com.co/politica/ivan-cepeda-aida-quilcue-no-aceptan-votaciones-elecciones-presidenciales-400965</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 10:52 p. m.</t>
+          <t>01/06/2026 12:39 a. m.</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1136,19 +1136,19 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Prima para empleadas domésticas por días: cómo calcularla paso a paso y cuánto deben pagar en 2026</t>
+          <t>¿Cuántos votos sacaron Abelardo de la Espriella e Iván Cepeda y cómo pasan a segunda vuelta presidencial?</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/economia/prima-empleadas-domesticas-por-dias-como-calcular-en-2026-400892</t>
+          <t>https://www.lafm.com.co/politica/segunda-vuelta-abelardo-de-la-espriella-ivan-cepeda-numero-total-de-votos-elecciones-colombia-400946</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:30 p. m.</t>
+          <t>01/06/2026 12:08 a. m.</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1163,19 +1163,19 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Mincomercio responde al anuncio de Ecuador sobre aranceles en remate de la campaña electoral</t>
+          <t>Álvaro Uribe se pronuncia tras derrota de Paloma Valencia y llama a elegir a Abelardo de la Espriella presidente</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/economia/ministra-de-comercio-aranceles-ecuador-campana-electoral-colombia-abelardo-de-la-espriella-daniel-noboa-400883</t>
+          <t>https://www.lafm.com.co/politica/alvaro-uribe-llama-a-elegir-a-abelardo-de-la-espriella-como-presidente-de-colombia-400958</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:22 p. m.</t>
+          <t>01/06/2026 12:03 a. m.</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1190,19 +1190,19 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Medios iraníes dicen que borrador de acuerdo con EEUU incluye desbloqueo de USD 12.000 millones en activos</t>
+          <t>¿De dónde saldrán los votos de Abelardo de la Espriella e Iván Cepeda para ganar en segunda vuelta?</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/internacional/ormuz-negociaciones-trump-naval-estrecho-dinero-borrador-400888</t>
+          <t>https://www.lafm.com.co/politica/abelardo-de-la-espriella-ivan-cepeda-segunda-vuelta-elecciones-presidenciales-2026-votos-400960</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:21 p. m.</t>
+          <t>31/05/2026 11:40 p. m.</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -1217,19 +1217,19 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>¿Juan Fernando Quintero se va de River Plate? Las posibles salidas de ídolos colombianos tras el Mundial 2026</t>
+          <t>Sergio Fajardo tras un millón de votos: “vamos a ser protagonistas de la segunda vuelta presidencial”</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/deportes/quintero-podria-salir-de-river-plate-tras-el-mundial-2026-carrascal-james-rodriguez-400886</t>
+          <t>https://www.lafm.com.co/politica/sergio-fajardo-cerca-millon-votos-anuncia-participacion-en-segunda-vuelta-400957</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 07:32 p. m.</t>
+          <t>31/05/2026 10:51 p. m.</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1244,19 +1244,19 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Procuraduría indaga si funcionario de la ANT en Arauca participa indebidamente en política</t>
+          <t>¿Quién es José Manuel Restrepo? El exministro que acompaña a Abelardo de la Espriella como fórmula vicepresidencial</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/politica/procuraduria-indaga-funcionario-ant-arauca-participacion-indebida-en-politica-400887</t>
+          <t>https://www.lafm.com.co/politica/quien-es-jose-manuel-restrepo-fomula-vicepresidencial-abelardo-de-la-espriella-exministro-400947</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 07:10 p. m.</t>
+          <t>31/05/2026 10:35 p. m.</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -1271,19 +1271,19 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Alejandro Estrada: ¿Quién es el ganador de La Casa de los Famosos 2026 y cuánto dinero se llevó?</t>
+          <t>Abelardo de la Espriella e Iván Cepeda: ¿Cuándo será la segunda vuelta presidencial en Colombia?</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/entretenimiento/quien-es-alejandro-estrada-ganador-de-la-casa-de-los-famosos-2026-400881</t>
+          <t>https://www.lafm.com.co/politica/fecha-segunda-vuelta-presidencial-abelardo-de-la-espriella-ivan-cepeda-colombia-400446</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 06:12 p. m.</t>
+          <t>31/05/2026 10:34 p. m.</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1298,19 +1298,19 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Todo lo que se sabe del desalojo del candidato presidencial Santiago Botero por presunta violencia intrafamiliar: 'Echó a su esposa y a su hijo'</t>
+          <t>Lista de ‘quemados’ en elecciones 2026: quiénes son los candidatos presidenciales que perdieron las votaciones del 31 de mayo</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/actualidad/por-que-desalojaron-a-santiago-botero-por-presunto-caso-de-violencia-intrafamiliar-400878</t>
+          <t>https://www.lafm.com.co/politica/elecciones-presidenciales-lista-quemados-2026-candidatos-que-perdieron-votacion-31-mayo-400945</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 05:59 p. m.</t>
+          <t>31/05/2026 08:36 p. m.</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -1325,19 +1325,19 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Elecciones presidenciales: así funcionará el Puesto de Mando Unificado Cibernético para evitar delitos electorales</t>
+          <t>Elecciones presidenciales: ¿Se puede cambiar el puesto de votación para la segunda vuelta?</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/orden-publico/elecciones-presidenciales-puesto-mando-unificado-cibernetico-policia-nacionall-400879</t>
+          <t>https://www.lafm.com.co/actualidad/elecciones-presidenciales-2026-cambio-puesto-votacion-inscripciones-segunda-vuelta-400459</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 05:54 p. m.</t>
+          <t>31/05/2026 07:13 p. m.</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1352,19 +1352,19 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>La Casa de los Famosos confirma temporada 4: todo lo que se sabe hasta ahora</t>
+          <t>Elecciones 2026 en Colombia: ¿se pueden acumular los descansos por votar en primera y segunda vuelta? Esto dice la ley</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/entretenimiento/la-casa-de-los-famosos-tendra-temporada-4-esto-se-sabe-400849</t>
+          <t>https://www.lafm.com.co/sociedad/ley-aclara-si-se-pueden-acumular-descansos-por-votar-en-primera-y-segunda-vuelta-2026-400935</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 05:40 p. m.</t>
+          <t>29/05/2026 12:52 a. m.</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -1379,19 +1379,19 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Gobierno Nacional instala PMU y despliega más de 280 mil uniformados para garantizar la seguridad en las elecciones</t>
+          <t>Abelardo de la Espriella el gran ganador en Antioquia: así votaron los paisas</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/politica/gobierno-nacional-instala-pmu-y-despliega-mas-de-280-mil-uniformados-para-garantizar-la-seguridad-en-las-elecciones-400880</t>
+          <t>https://www.lafm.com.co/politica/abelardo-de-la-espriella-elecciones-presidenciales-2026-ganador-antioquia-400949</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>28/05/2026 04:03 p. m.</t>
+          <t>27/05/2026 11:55 a. m.</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1406,19 +1406,19 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Procuraduría pide explicaciones por muerte de estudiante luego de una pelea de boxeo en colegio de Suba</t>
+          <t>¿Quién es Iván Cepeda? El congresista que busca la Presidencia en segunda vuelta 2026</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/sociedad/procuraduria-pide-explicacion-muerte-estudiante-practicando-boxeo-400885</t>
+          <t>https://www.lafm.com.co/politica/ivan-cepeda-perfil-politico-rumbo-segunda-vuelta-elecciones-presidenciales-colombia2026-400891</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026 03:16 p. m.</t>
+          <t>26/05/2026 01:05 p. m.</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -1433,19 +1433,19 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>🔴 EN VIVO| Elecciones presidenciales Colombia 31 de mayo: siga el minuto a minuto, resultados y últimas noticias</t>
+          <t>Líderes políticos de Antioquia se pronunciaron sobre los resultados de la primera vuelta</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/politica/elecciones-colombia-31-de-mayo-en-vivo-resultados-ultimas-noticias-400899</t>
+          <t>https://www.lafm.com.co/politica/reaccion-politicos-triunfo-abelardo-400951</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>05/05/2026 01:51 p. m.</t>
+          <t>20/05/2026 02:29 p. m.</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1460,19 +1460,19 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>“Las mujeres se respetan”: Paloma Valencia rechaza agresiones contra exparejas de Santiago Botero y Alejandro Bermeo</t>
+          <t>“Este millón de votos define la suerte del país”: Sergio Fajardo asegura que será decisivo en la segunda vuelta presidencial</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/politica/paloma-valencia-yamile-trigueros-manuela-echeverri-violencia-genero-mujeres-santiago-botero-alejandro-bermeo-400890</t>
+          <t>https://www.lafm.com.co/politica/sergio-fajardo-dice-que-su-millon-de-votos-seran-clave-en-segunda-vuelta-400954</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>28/04/2026 02:31 p. m.</t>
+          <t>05/05/2026 01:51 p. m.</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -1487,19 +1487,19 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Estremecedor caso de abuso y secuestro contra una menor indígena en Cali: la víctima tiene cuatro años</t>
+          <t>Paloma Valencia anuncia su respaldo a Abelardo de la Espriella en segunda vuelta: 'Colombia no caerá en el comunismo'</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/sociedad/estremecedor-caso-de-abuso-sexual-y-secuestro-contra-una-menor-indigena-en-cali-victima-tiene-cuatro-anos-400882</t>
+          <t>https://www.lafm.com.co/politica/paloma-valencia-anuncia-respaldo-a-abelardo-de-la-espriella-en-segunda-vuelta-400955</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>12/03/2026 07:16 p. m.</t>
+          <t>28/02/2026 03:55 a. m.</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Sociedad de Cirugía Plástica respalda regulación para combatir procedimientos estéticos ilegales</t>
+          <t>“Todo el uribismo la abandonó y se fue con Abelardo”: Roy Barreras cuestiona el respaldo de Paloma Valencia a De la Espriella</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/sociedad/sociedad-cirugia-plastica-regulacion-procedimientos-esteticos-ilegales-400884</t>
+          <t>https://www.lafm.com.co/politica/roy-barreras-resultados-primera-vuelta-paloma-valencia-sistema-electoral-analisis-votos-segunda-vuelta-400956</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Anuncian cierres viales por obras del Regiotram Occidente en Bogotá y Cundinamarca: rutas y fechas clave</t>
+          <t>“No acepto los resultados”: Gustavo Petro denuncia irregularidades tras primera vuelta y señala presunto fraude electoral en Colombia</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/actualidad/cierres-por-obras-del-regiotram-occidente-afectaran-vias-en-bogota-y-cundinamarca-400895</t>
+          <t>https://www.lafm.com.co/politica/presidente-petro-no-acepto-los-resultados-de-la-primera-vuelta-presidencial-2026-400963</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>"Comprometámonos a respetar los resultados”: Procurador asegura que Colombia está lista para votar en paz este domingo</t>
+          <t>Cuántos votos necesitan Abelardo De la Espriella e Iván Cepeda para ganar la presidencia en segunda vuelta</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/politica/elecciones-presidenciales-procurador-gregorio-eljach-pide-respetar-los-resultados-colombia-esta-lista-para-votar-en-paz-400893</t>
+          <t>https://www.lafm.com.co/politica/segunda-vuelta-elecciones-colombia-2026-cuantos-votos-necesitan-de-la-espriella-cepeda-para-la-presidencia-400961</t>
         </is>
       </c>
     </row>
@@ -1583,19 +1583,19 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Soacha declara alerta amarilla hospitalaria por sobreocupación en urgencias que supera el 200 %</t>
+          <t>Claudia López reacciona a los resultados presidenciales y dice que “Colombia quedó en un abismo difícil”</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/sociedad/hospitales-soacha-alerta-amarilla-ocupacion-maximo-crisis-salud-medicamentos-400877</t>
+          <t>https://www.lafm.com.co/politica/claudia-lopez-resultados-primera-vuelta-colombia-alerta-abismo-en-democracia-segunda-vuelta-400950</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 12:00 a. m.</t>
+          <t>01/06/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1610,19 +1610,19 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Claptone anunció su regreso a Colombia con un show especial: fecha, lugar y precios de boletería</t>
+          <t>Así votaron los colombianos en el exterior: Abelardo de la Espriella e Iván Cepeda lideraron en las urnas</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/claptone-anuncio-su-regreso-a-colombia-con-un-show-especial-fecha-lugar-y-precios-de-boleteria/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/asi-votaron-los-colombianos-en-el-exterior-abelardo-de-la-espriella-e-ivan-cepeda-lideraron-en-las-urnas/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 12:00 a. m.</t>
+          <t>01/06/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -1637,19 +1637,19 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Denuncian que clínica de Ibagué estaría usando pantallas de turnos para hacer campaña contra el petrismo: Supersalud anunció investigación</t>
+          <t>Prensa internacional registró la victoria de Abelardo de la Espriella en las elecciones presidenciales: “Una Colombia partida en dos”</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/denuncian-que-clinica-de-ibague-estaria-usando-pantallas-de-turnos-para-hacer-campana-contra-el-petrismo-supersalud-anuncio-investigacion/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/prensa-internacional-registro-la-victoria-de-abelardo-de-la-espriella-en-las-elecciones-presidenciales-una-colombia-partida-en-dos/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 12:00 a. m.</t>
+          <t>01/06/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1664,19 +1664,19 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Bernie Moreno publicó una carta para los colombianos antes de las elecciones: “El mundo será testigo de la lucha por la democracia”</t>
+          <t>Canciller Rosa Villavicencio entregó el primer balance sobre el desarrollo de las elecciones presidenciales en el exterior: “Han existido alteraciones”</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/bernie-moreno-publico-una-carta-para-los-colombianos-antes-de-las-elecciones-el-mundo-sera-testigo-de-la-lucha-por-la-democracia/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/canciller-rosa-villavicencio-entrego-el-primer-balance-sobre-el-desarrollo-de-las-elecciones-presidenciales-en-el-exterior-han-existido-alteraciones/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 12:00 a. m.</t>
+          <t>01/06/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
@@ -1691,19 +1691,19 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Entre lágrimas, adulta mayor pide que le devuelvan $700.000 que envió por error a una cuenta de Nequi</t>
+          <t>El resultado de la primera vuelta sacudió al país político: así reaccionaron a las elecciones entre De la Espriella e Iván Cepeda</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/entre-lagrimas-adulta-mayor-pide-que-le-devuelvan-700000-que-envio-por-error-a-una-cuenta-de-nequi/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/el-resultado-de-la-primera-vuelta-sacudio-al-pais-politico-asi-reaccionaron-a-las-elecciones-entre-de-la-espriella-e-ivan-cepeda/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 12:00 a. m.</t>
+          <t>01/06/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1718,19 +1718,19 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Karina García barajó la posibilidad de que su hija Isabella se sume a ‘La casa de los famosos Colombia’ en 2027 y le llovieron críticas</t>
+          <t>Tomás Uribe reaccionó al avance de Abelardo de la Espriella y celebró la derrota de Cepeda en primera vuelta: “Es una gran ganancia para Colombia”</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/karina-garcia-barajo-la-posibilidad-de-que-su-hija-isabella-se-sume-a-la-casa-de-los-famosos-colombia-en-2027-y-le-llovieron-criticas/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/tomas-uribe-reacciono-al-avance-de-abelardo-de-la-espriella-y-celebro-la-derrota-de-cepeda-en-primera-vuelta-es-una-gran-ganancia-para-colombia/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 12:00 a. m.</t>
+          <t>01/06/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -1745,19 +1745,19 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Abelardo de la Espriella aseguró que defendería a Westcol si mata a un ladrón: “Así venga con un peluche, le disparas”</t>
+          <t>El alcalde Federico Gutiérrez rechazó las declaraciones de Petro sobre resultados electorales: "Pasarás a la historia como el peor presidente de Colombia"</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/abelardo-de-la-espriella-aseguro-que-defenderia-a-westcol-si-mata-a-un-ladron-asi-venga-con-un-peluche-le-disparas/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/el-alcalde-federico-gutierrez-rechazo-las-declaraciones-de-petro-sobre-resultados-electorales-pasaras-a-la-historia-como-el-peor-presidente-de-colombia/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 12:00 a. m.</t>
+          <t>01/06/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1772,19 +1772,19 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Colombia ante las urnas: Izquierda, derecha y un ‘outsider’ se disputan la presidencia</t>
+          <t>De ‘Betty, la fea’ a series internacionales y darles nuevas caras a los candidatos, los  memes que dejaron las elecciones presidenciales</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/colombia-ante-las-urnas-izquierda-derecha-y-un-outsider-se-disputan-la-presidencia/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/los-memes-que-causaron-furor-en-redes-y-marcaron-la-jornada-electoral-en-colombia-una-valeriana-o-algo/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 12:00 a. m.</t>
+          <t>01/06/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -1799,19 +1799,19 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Lo que esconde el clóset de los candidatos presidenciales: los mensajes en la ropa de Cepeda, Valencia y De la Espriella</t>
+          <t>Resultado Chontico Noche: números ganadores del último sorteo hoy, domingo 31 de mayo de 2026</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/ivan-cepeda-abelardo-de-la-espriella-y-paloma-valencia-convierten-su-ropa-en-mensaje-clave-de-campana/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/resultado-chontico-noche-numeros-ganadores-del-ultimo-sorteo-hoy-domingo-31-de-mayo-de-2026/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 12:00 a. m.</t>
+          <t>01/06/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -1826,19 +1826,19 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Debate programático entre una política de paz o una política de seguridad que la desconozca o subordine</t>
+          <t>Claudia López explicó por qué Iván Cepeda quedó segundo en la primera vuelta de las elecciones presidenciales: “No te pueden hacer la campaña”</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/debate-programatico-entre-una-politica-de-paz-o-una-politica-de-seguridad-que-la-desconozca-o-subordine/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/claudia-lopez-explico-por-que-ivan-cepeda-quedo-segundo-en-la-primera-vuelta-de-las-elecciones-presidenciales-no-te-pueden-hacer-la-campana/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 12:00 a. m.</t>
+          <t>01/06/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -1853,19 +1853,19 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>IPS advierten que medida del Gobierno de aumentar el giro directo no resolverá por sí solo la crisis del sistema de salud: esto propusieron</t>
+          <t>Juan Daniel Oviedo calificó a Abelardo de la Espriella como un “candidato machista y homofóbico”</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/ips-advierten-que-medida-del-gobierno-de-aumentar-el-giro-directo-no-resolvera-por-si-solo-la-crisis-del-sistema-de-salud-esto-propusieron/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/juan-daniel-oviedo-califico-a-abelardo-de-la-espriella-como-un-candidato-machista-y-homofobico/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 12:00 a. m.</t>
+          <t>01/06/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -1880,19 +1880,19 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Estados Alterados, Funk Tribu, Karen Lizarazo, Jungle y más: estos son los lanzamientos destacados de la semana</t>
+          <t>Departamento de Estado se pronunció tras primera vuelta en Colombia: “EE. UU. apoya el derecho del pueblo colombiano a elegir libremente”</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/estados-alterados-funk-tribu-karen-lizarazo-jungle-y-mas-estos-son-los-lanzamientos-destacados-de-la-semana/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/departamento-de-estado-se-pronuncio-tras-primera-vuelta-en-colombia-ee-uu-apoya-el-derecho-del-pueblo-colombiano-a-elegir-libremente/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 12:00 a. m.</t>
+          <t>01/06/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -1907,19 +1907,19 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Iván Duque resaltó la importancia de su gobierno para las elecciones de 2026:  dos de sus funcionarios podrán ser vicepresidente</t>
+          <t>Bernie Moreno dio parte de tranquilidad en la primera vuelta y celebró victoria de Abelardo de la Espriella: “El trabajo no está terminado aún”</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/ivan-duque-resalto-la-importancia-de-su-gobierno-para-las-elecciones-de-2026-dos-de-sus-funcionarios-podran-ser-vicepresidente/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/bernie-moreno-dio-parte-de-tranquilidad-en-la-primera-vuelta-y-celebro-victoria-de-abelardo-de-la-espriella-el-trabajo-no-esta-terminado-aun/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 12:00 a. m.</t>
+          <t>01/06/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -1934,19 +1934,19 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>La IA como herramienta de comunicación política en la campaña presidencial: ruido, emociones y degradación de la deliberación pública</t>
+          <t>Gustavo Petro no reconoció los resultados electorales de la primera vuelta en Colombia: “Como presidente no los acepto”</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/la-ia-como-herramienta-de-comunicacion-politica-en-la-campana-presidencial-ruido-emociones-y-degradacion-de-la-deliberacion-publica/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/gustavo-petro-no-reconoce-los-resultados-electorales-de-la-primera-vuelta-como-presidente-no-los-acepto/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 12:00 a. m.</t>
+          <t>01/06/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -1961,19 +1961,19 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Elementos comunes sobre la paz en el escenario electoral</t>
+          <t>Exministro de Defensa de Juan Manuel Santos también anunció su apoyo a Abelardo de la Espriella para la segunda vuelta presidencial: “Recuperemos a Colombia”</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/los-denominadores-comunes-de-los-escenarios-electorales/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/exministro-de-defensa-de-juan-manuel-santos-tambien-anuncio-su-apoyo-a-abelardo-de-la-espriella-para-la-segunda-vuelta-presidencial-recuperemos-a-colombia/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 12:00 a. m.</t>
+          <t>01/06/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -1988,19 +1988,19 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Colombia 2026: realismo hemisférico para el próximo gobierno</t>
+          <t>Riña con arma blanca dejó un muerto en el sur de Bogotá, en plena ley seca: ocurrió a pocos metros de un CAI</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/colombia-2026-realismo-hemisferico-para-el-proximo-gobierno/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/rina-con-arma-blanca-dejo-un-muerto-en-el-sur-de-bogota-en-plena-ley-seca-ocurrio-a-pocos-metros-de-un-cai/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 12:00 a. m.</t>
+          <t>01/06/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Gobernar en la polarización: El complejo escenario legislativo para Iván Cepeda</t>
+          <t>Turista neerlandesa fue encontrada muerta en zona rural de Salento tras ser reportada como desaparecida</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/gobernar-en-la-polarizacion-el-complejo-escenario-legislativo-para-ivan-cepeda/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/turista-neerlandesa-fue-encontrada-muerta-en-zona-rural-de-salento-tras-ser-reportada-como-desaparecida/</t>
         </is>
       </c>
     </row>
@@ -2042,12 +2042,12 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>La Procuraduría desplegará un ejército de vigilancia para las elecciones presidenciales en Colombia</t>
+          <t>Elecciones en Colombia 2026, EN VIVO: De “abogado de paramiliatares” a “espía de las Farc”, las pullas entre De la Espriella y Cepeda ya iniciaron campaña</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/la-procuraduria-desplegara-un-ejercito-de-vigilancia-para-las-elecciones-presidenciales-en-colombia/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/elecciones-en-colombia-2026-en-vivo-reporte-de-orden-publico-apertura-de-mesas-y-noticias-relevantes-hoy-31-de-mayo/</t>
         </is>
       </c>
     </row>
@@ -2069,19 +2069,19 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Nuevos detalles de la denuncia contra el senador Alejandro Bermeo: víctima relató amenazas, golpes y presunto abuso tras una relación de dos años</t>
+          <t>Elecciones presidenciales desde Bogotá: Iván Cepeda venció a Abelardo de la Espriella en la capital</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/nuevos-detalles-de-la-denuncia-contra-el-senador-alejandro-bermeo-victima-relato-amenazas-golpes-y-presunto-abuso-tras-una-relacion-de-dos-anos/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/elecciones-presidenciales-en-vivo-desde-bogota-hoy-31-de-mayo-siga-el-minuto-a-minuto-de-las-votaciones/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 12:00 a. m.</t>
+          <t>31/05/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2096,19 +2096,19 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Esposa de Santiago Botero habló del calvario que vivió junto al candidato: “Soporté muchos meses de violencia intrafamiliar”</t>
+          <t>Sorpresa en las elecciones de Colombia: Abelardo de la Espriella gana la primera vuelta y disputará la presidencia con Iván Cepeda</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/30/esposa-de-santiago-botero-hablo-del-calvario-que-vivio-junto-al-candidato-soporte-muchos-meses-de-violencia-intrafamiliar/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/sorpresa-en-las-elecciones-de-colombia-abelardo-de-la-espriella-gana-la-primera-vuelta-y-disputara-la-presidencia-con-ivan-cepeda/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 12:00 a. m.</t>
+          <t>31/05/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -2123,19 +2123,19 @@
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Lanzan alerta desde la gobernación del Magdalena por posibles cortes de energía durante las elecciones presidenciales</t>
+          <t>Elecciones en Antioquia: Abelardo de la Espriella duplicó a Iván Cepeda</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/30/lanzan-alerta-desde-la-gobernacion-del-magdalena-por-posibles-cortes-de-energia-durante-las-elecciones-presidenciales/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/elecciones-en-antioquia-en-vivo/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 09:30 p. m.</t>
+          <t>31/05/2026 08:55 p. m.</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2150,19 +2150,19 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Resultados Caribeña Noche, último sorteo hoy sábado, 30 de mayo de 2026: números ganadores</t>
+          <t>Procurador general resalta la transparencia de las elecciones presidenciales en Colombia</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/resultados-caribena-noche-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/procurador-general-resalta-la-transparencia-de-las-elecciones-presidenciales-en-colombia-rg10</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 09:30 p. m.</t>
+          <t>31/05/2026 08:52 p. m.</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -2177,19 +2177,19 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Resultados Sinuano Noche, último sorteo hoy sábado, 30 de mayo de 2026: números ganadores</t>
+          <t>Abelardo de la Espriella pide veeduría internacional para segunda vuelta y lanza críticas a Cepeda</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/resultados-sinuano-noche-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/abelardo-de-la-espriella-pide-veeduria-internacional-para-segunda-vuelta-y-lanza-criticas-a-cepeda-rg10</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 09:15 p. m.</t>
+          <t>31/05/2026 08:21 p. m.</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2204,19 +2204,19 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Resultados Dorado Noche, último sorteo hoy sábado, 30 de mayo de 2026: números ganadores</t>
+          <t>Departamento de Estado de Estados Unidos se pronunció tras la jornada electoral en Colombia</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/resultados-dorado-noche-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/departamento-de-estado-de-estados-unidos-se-pronuncio-tras-la-jornada-electoral-en-colombia-rg10</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:59 p. m.</t>
+          <t>31/05/2026 08:13 p. m.</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
@@ -2231,19 +2231,19 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Colombia, lista para ir a las urnas y elegir a su nuevo presidente(a)</t>
+          <t>Defensoría del Pueblo advierte riesgos en segunda vuelta e hizo llamado a De La Espriella y Cepeda</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/colombia-lista-para-ir-a-las-urnas-y-elegir-a-su-nuevo-presidentea-cb20</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/defensoria-del-pueblo-advierte-riesgos-en-segunda-vuelta-e-hizo-llamado-a-de-la-espriella-y-cepeda-rg10</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:06 p. m.</t>
+          <t>31/05/2026 08:00 p. m.</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2258,19 +2258,19 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Andrés Llinás y una carta abierta por mal semestre de Millonarios; "no estuvimos a la altura"</t>
+          <t>Resultados Sinuano Noche último sorteo del 31 de mayo de 2026: números ganadores</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/golcaracol/futbol-colombiano/andres-llinas-y-una-carta-abierta-por-mal-semestre-de-millonarios-no-estuvimos-a-la-altura-rg10</t>
+          <t>https://www.noticiascaracol.com/economia/sinuano-noche-31-de-mayo-2026-resultados-numeros-ganadores-de-hoy-so35</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 06:50 p. m.</t>
+          <t>31/05/2026 08:00 p. m.</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -2285,19 +2285,19 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Luis Javier Suárez y sus goles con Sporting Lisboa le valieron un reconocimiento en Portugal</t>
+          <t>Resultados Caribeña Noche último sorteo del domingo 31 de mayo de 2026: números ganadores</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/golcaracol/colombianos-en-el-exterior/luis-javier-suarez-y-sus-goles-con-sporting-lisboa-le-valieron-un-reconocimiento-en-portugal-rg10</t>
+          <t>https://www.noticiascaracol.com/economia/caribena-noche-31-de-mayo-2026-resultados-numeros-ganadores-de-hoy-so35</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 04:23 p. m.</t>
+          <t>31/05/2026 08:00 p. m.</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2312,19 +2312,19 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Video | Encuentran sin vida a joven que cayó al embalse de Guatapé durante fiesta en una embarcación</t>
+          <t>Super Astro Luna resultados del domingo 31 de mayo de 2026: los números ganadores</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/video-encuentran-sin-vida-a-joven-que-cayo-al-embalse-de-guatape-durante-fiesta-en-una-embarcacion-rg10</t>
+          <t>https://www.noticiascaracol.com/economia/super-astro-luna-31-de-mayo-de-2026-cuales-son-los-numeros-ganadores-so35</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 04:15 p. m.</t>
+          <t>31/05/2026 07:55 p. m.</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -2339,19 +2339,19 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Murió Kelly Curtis, actriz y hermana de Jamie Lee Curtis, a los 69 años</t>
+          <t>Iván Cepeda esperará a resultados de comisiones escrutadoras para pronunciarse tras elecciones</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/entretenimiento/murio-kelly-curtis-actriz-y-hermana-de-jamie-lee-curtis-a-los-69-anos-cb20</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/ivan-cepeda-esperara-a-resultados-de-comisiones-escrutadoras-para-pronunciarse-tras-elecciones-rg10</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 03:49 p. m.</t>
+          <t>31/05/2026 07:49 p. m.</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2366,19 +2366,19 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Resultados Super Astro Sol hoy, sábado 30 de mayo de 2026: números ganadores del último sorteo</t>
+          <t>"A 'Cucho' Hernández se le ve mucho mejor jugando con otro '9', con un tanque al lado"</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/resultados-super-astro-sol-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-del-ultimo-sorteo-so35</t>
+          <t>https://www.noticiascaracol.com/golcaracol/seleccion-colombia/a-cucho-hernandez-se-le-ve-mucho-mejor-jugando-con-otro-9-con-un-tanque-al-lado-ex40</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 03:21 p. m.</t>
+          <t>31/05/2026 07:37 p. m.</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -2393,19 +2393,19 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>¿Mercenarios colombianos en México? Así carteles de la droga estarían reclutando exmilitares</t>
+          <t>¿Cómo votaron los departamentos con más municipios bajo riesgo por violencia en Colombia?</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/mundo/mercenarios-colombianos-en-mexico-asi-carteles-de-la-droga-estarian-reclutando-exmilitares-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/como-votaron-los-departamentos-con-mas-municipios-bajo-riesgo-por-violencia-en-colombia-rg10</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 02:07 p. m.</t>
+          <t>31/05/2026 07:12 p. m.</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2420,19 +2420,19 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Resultados Dorado Tarde hoy, sábado 30 de mayo de 2026: números ganadores del último sorteo</t>
+          <t>"Como presidente no acepto los resultados del preconteo": Petro tras las elecciones</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/resultados-dorado-tarde-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-del-ultimo-sorteo-so35</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/como-presidente-no-acepto-los-resultados-del-preconteo-petro-tras-las-elecciones-rg10</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 02:04 p. m.</t>
+          <t>31/05/2026 07:03 p. m.</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
@@ -2447,19 +2447,19 @@
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Resultados Caribeña Día hoy, sábado 30 de mayo de 2026: números ganadores del último sorteo</t>
+          <t>Juan Daniel Oviedo tras primera vuelta: “Los resultados se debaten entre los extremos populistas”</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/resultados-caribena-dia-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-del-ultimo-sorteo-so35</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/oviedo-tras-resultados-elecciones-los-resultados-se-debatan-entre-los-extremos-populistas-rg10</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 01:55 p. m.</t>
+          <t>31/05/2026 07:00 p. m.</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2474,19 +2474,19 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Resultados Sinuano Día hoy, sábado 30 de mayo de 2026: números ganadores del último sorteo</t>
+          <t>Resultados Chontico Noche último sorteo hoy, domingo 31 de mayo de 2026: números ganadores</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/resultados-sinuano-dia-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-del-ultimo-sorteo-so35</t>
+          <t>https://www.noticiascaracol.com/economia/chontico-noche-31-mayo-2026-resultados-numeros-ganadores-de-hoy-so35</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 01:42 p. m.</t>
+          <t>31/05/2026 07:00 p. m.</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
@@ -2501,19 +2501,19 @@
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>“No tengo palabras”: Alfredo Iván Guzmán, hijo del exalcalde de Tame, tras recuperar su libertad</t>
+          <t>Resultados Dorado Noche, último sorteo hoy domingo 31 de mayo de 2026: números ganadores</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/no-tengo-palabras-alfredo-ivan-guzman-hijo-del-exalcalde-de-tame-tras-recuperar-su-libertad-rg10</t>
+          <t>https://www.noticiascaracol.com/economia/dorado-noche-31-de-mayo-de-2026-cuales-son-los-numeros-ganadores-so35</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 12:54 p. m.</t>
+          <t>31/05/2026 06:46 p. m.</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2528,19 +2528,19 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Resultados Chontico Día hoy, sábado 30 de mayo de 2026: números ganadores</t>
+          <t>¿Cómo votaron los colombianos en España en las elecciones presidenciales? Resultados de preconteo</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/resultados-chontico-dia-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-so35</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/como-votaron-los-colombianos-en-espana-en-las-elecciones-presidenciales-de-2026-resultados-del-100-de-preconteo-rg10</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 12:38 p. m.</t>
+          <t>31/05/2026 06:41 p. m.</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -2555,19 +2555,19 @@
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Vanessa Pulgarín, la colombiana que logró la primera corona de Miss Grand International All Stars</t>
+          <t>"Colombianos, hemos perdido": Álvaro Uribe tras la primera vuelta de las elecciones presidenciales</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/entretenimiento/vanessa-pulgarin-la-colombiana-que-logro-la-primera-corona-de-miss-grand-international-all-stars-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/colombianos-hemos-perdido-alvaro-uribe-tras-la-primera-vuelta-presidencial-en-colombia-rg10</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 11:39 a. m.</t>
+          <t>31/05/2026 06:36 p. m.</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2582,19 +2582,19 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>El Parque Nacional Natural Tayrona cerrará sus puertas por 15 días: ¿por qué?</t>
+          <t>Elecciones en Colombia: voto en blanco vence a seis candidatos y supera los 400.000 sufragios</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/el-parque-nacional-natural-tayrona-cerrara-sus-puertas-por-15-dias-por-que-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/elecciones-en-colombia-voto-en-blanco-vence-a-seis-candidatos-y-supera-los-400-000-sufragios-rg10</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 11:36 a. m.</t>
+          <t>31/05/2026 06:32 p. m.</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
@@ -2609,19 +2609,19 @@
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Polémica en final de Champions League; ¿era mano en el Arsenal y penalti para el PSG?</t>
+          <t>Sergio Fajardo habla tras su derrota en las elecciones presidenciales: "No nos vamos a resignar"</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/golcaracol/polemica-en-final-de-champions-league-era-mano-en-el-arsenal-y-penalti-para-el-psg-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/sergio-fajardo-habla-tras-su-derrota-en-las-elecciones-presidenciales-de-2026-no-nos-vamos-a-resignar-rg10</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 11:20 a. m.</t>
+          <t>31/05/2026 06:30 p. m.</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2636,19 +2636,19 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Ganadores del Desafío Siglo XXI se casarán: video de la emotiva propuesta de matrimonio</t>
+          <t>"Yo sé que Iván es un hombre decente": Claudia López tras finalizar la primera vuelta presidencial</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/entretenimiento/ganadores-del-desafio-siglo-xxi-se-casaran-video-de-la-emotiva-propuesta-de-matrimonio-rs15</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/yo-se-que-ivan-es-un-hombre-decente-claudia-lopez-tras-finalizar-la-primera-vuelta-presidencial-rg10</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 10:45 a. m.</t>
+          <t>31/05/2026 06:26 p. m.</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
@@ -2663,19 +2663,19 @@
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Video l Tim Payne, el futbolista viral, disputó un torneo en Colombia: vea cómo lucía en el 2011</t>
+          <t>Paloma Valencia anuncia su apoyo a Abelardo de la Espriella para la segunda vuelta</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/lomastrinado/video-l-tim-payne-el-futbolista-viral-disputo-un-torneo-en-colombia-vea-como-lucia-en-el-2011-rs15</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/paloma-valencia-anuncia-su-apoyo-a-abelardo-de-la-espriella-para-la-segunda-vuelta-rg10</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 10:42 a. m.</t>
+          <t>31/05/2026 06:07 p. m.</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -2690,19 +2690,19 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Así está la salud de Donald Trump, según el más reciente chequeo médico de la Casa Blanca</t>
+          <t>Abelardo de la Espriella habla tras confirmarse segunda vuelta presidencial contra Iván Cepeda</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/mundo/asi-esta-la-salud-de-donald-trump-segun-el-mas-reciente-chequeo-medico-de-la-casa-blanca-cb20</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/abelardo-de-la-espriella-habla-tras-confirmarse-segunda-vuelta-presidencial-contra-ivan-cepeda-rg10</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 10:23 a. m.</t>
+          <t>31/05/2026 05:55 p. m.</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
@@ -2717,19 +2717,19 @@
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Resultados Dorado Mañana hoy, sábado 30 de mayo de 2026: números ganadores del último sorteo</t>
+          <t>Resultados elecciones Colombia: De la Espriella ganó en Antioquia en primera vuelta; Cepeda, segundo</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/resultados-dorado-manana-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-del-ultimo-sorteo-so35</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/resultados-elecciones-colombia-de-la-espriella-gano-en-antioquia-en-primera-vuelta-cepeda-segundo-rg10</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 10:00 a. m.</t>
+          <t>31/05/2026 05:44 p. m.</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -2744,19 +2744,19 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Elecciones presidenciales 2026: cierres viales y desvíos clave de movilidad en Bogotá</t>
+          <t>Elecciones en Colombia: así votó la región Caribe en la primera vuelta presidencial</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/bogota-elecciones-presidenciales-2026-cierres-viales-y-desvios-clave-de-movilidad-en-bogota-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/elecciones-en-colombia-asi-voto-la-region-caribe-en-la-primera-vuelta-presidencial-rg10</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 09:30 a. m.</t>
+          <t>31/05/2026 05:42 p. m.</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
@@ -2771,19 +2771,19 @@
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Cancillería se pronunció tras anuncio de Daniel Noboa sobre la eliminación de aranceles a Colombia</t>
+          <t>Abelardo de la Espriella e Iván Cepeda pasan a segunda vuelta en elecciones Colombia 2026</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/cancilleria-se-pronuncio-tras-anuncio-de-daniel-noboa-sobre-la-eliminacion-de-aranceles-a-colombia-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/abelardo-de-la-espriella-e-ivan-cepeda-pasan-a-segunda-vuelta-en-elecciones-colombia-2026-rg10</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:45 a. m.</t>
+          <t>31/05/2026 05:40 p. m.</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -2798,19 +2798,19 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Altos mandos militares de Cuba y EE. UU. se reunieron: ¿cuáles fueron los temas tratados?</t>
+          <t>Ministerio de Defensa entrega balance tras elecciones presidenciales: “La alerta se eleva aun más”</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/mundo/altos-mandos-militares-de-cuba-y-ee-uu-se-reunieron-cuales-fueron-los-temas-tratados-cb20</t>
+          <t>https://www.noticiascaracol.com/colombia/ministerio-de-defensa-entrega-balance-tras-elecciones-presidenciales-la-alerta-se-eleva-aun-mas</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:22 a. m.</t>
+          <t>31/05/2026 05:40 p. m.</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
@@ -2825,19 +2825,19 @@
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Supersalud ordenó cierre del servicio de cirugía estética de la Clínica de Obesidad y Envejecimiento</t>
+          <t>¿Cuándo será la segunda vuelta presidencial en Colombia? Esto dice el calendario electoral</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/bogota/supersalud-ordeno-cierre-del-servicio-de-cirugia-estetica-de-la-clinica-de-obesidad-y-envejecimiento-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/cuando-sera-la-segunda-vuelta-presidencial-en-colombia-esto-dice-el-calendario-electoral-rg10</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 09:27 p. m.</t>
+          <t>31/05/2026 05:35 p. m.</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -2847,24 +2847,24 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Elecciones 2026: ¿cuántos votos se necesitan para ganar en primera vuelta?</t>
+          <t>Así fue la votación en Bogotá: resultados de las elecciones presidenciales Colombia 2026</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/elecciones-2026-cuantos-votos-se-necesitan-para-ganar-en-primera-vuelta/</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/elecciones-presidenciales-colombia-2026-resultados-de-la-votacion-en-bogota-rg10</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 09:09 p. m.</t>
+          <t>31/05/2026 05:14 p. m.</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
@@ -2874,24 +2874,24 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Segunda vuelta presidencial 2026: fecha y cómo funcionaría en Colombia</t>
+          <t>Jurados de votación llegaron ebrios a mesas electorales en Antioquia: serán sancionados</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/segunda-vuelta-presidencial-2026-fecha-y-como-funcionaria-en-colombia/</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/jurados-de-votacion-llegaron-en-ebrios-a-mesas-electorales-en-antioquia-seran-sancionados-rg10</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:33 p. m.</t>
+          <t>31/05/2026 04:33 p. m.</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -2901,24 +2901,24 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Elecciones 2026: ¿a qué hora se conocerán los resultados en Colombia?</t>
+          <t>Registrador Hernán Penagos da balance tras el cierre de urnas en las elecciones presidenciales</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/elecciones-2026-a-que-hora-se-conoceran-los-resultados-en-colombia/</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/registrador-hernan-penagos-da-balance-tras-el-cierre-de-urnas-en-las-elecciones-presidenciales-rg10</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:26 p. m.</t>
+          <t>31/05/2026 04:23 p. m.</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
@@ -2928,24 +2928,24 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Elecciones 2026: cómo votar en el exterior y consultar su puesto</t>
+          <t>Gobierno de Ecuador oficializa el fin de los aranceles del 100 % a las importaciones de Colombia</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/elecciones-2026-como-votar-en-el-exterior-y-consultar-su-puesto/</t>
+          <t>https://www.noticiascaracol.com/mundo/gobierno-de-ecuador-oficializa-el-fin-de-los-aranceles-del-100-a-las-importaciones-de-colombia-cb20</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:14 p. m.</t>
+          <t>31/05/2026 08:52 p. m.</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -2955,24 +2955,24 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>¿Dónde votar? Consulte su puesto para las elecciones presidenciales 2026</t>
+          <t>Mapa Electoral 2026: así votó Colombia en las elecciones presidenciales del 31 de mayo</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/donde-votar-consulte-su-puesto-para-las-elecciones-presidenciales-2026/</t>
+          <t>https://www.elespectador.com/politica/mapa-electoral-2026-que-candidato-gano-en-cada-departamento/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:03 p. m.</t>
+          <t>31/05/2026 08:36 p. m.</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
@@ -2982,24 +2982,24 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Tarjetón elecciones 2026: ¿qué pasa con votos por candidatos retirados?</t>
+          <t>Cundinamarca nuevamente inclinó su voto por la derecha: así fue la jornada electoral</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/tarjeton-elecciones-2026-que-pasa-con-votos-por-candidatos-retirados/</t>
+          <t>https://www.elespectador.com/colombia/cundinamarca/cundinamarca-nuevamente-inclino-su-voto-por-la-derecha-asi-fue-la-jornada-electoral/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 07:58 p. m.</t>
+          <t>31/05/2026 08:31 p. m.</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3009,24 +3009,24 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Elecciones 2026: Procurador Eljach llama a votar temprano y en paz</t>
+          <t>Resultados elecciones en Colombia 2026 EN VIVO: estas son las cifras finales del preconteo</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/elecciones-2026-procurador-eljach-llama-a-votar-temprano-y-en-paz/</t>
+          <t>https://www.elespectador.com/politica/elecciones-colombia-2026/resultados-elecciones-presidenciales-colombia-2026-en-vivo-quien-gano/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 07:52 p. m.</t>
+          <t>31/05/2026 08:22 p. m.</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
@@ -3036,24 +3036,24 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Elecciones presidenciales 2026: cómo marcar la tarjeta electoral</t>
+          <t>¿De la Espriella o Cepeda?: este sería la ruta de las fórmulas a la Vicepresidencia</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/elecciones-presidenciales-2026-como-marcar-la-tarjeta-electoral/</t>
+          <t>https://www.elespectador.com/politica/elecciones-colombia-2026/juan-daniel-oviedo-edna-bonilla-y-leonardo-huerta-este-seria-su-camino-entre-abelardo-de-la-espriella-o-ivan-cepeda-noticias-hoy/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 05:48 p. m.</t>
+          <t>31/05/2026 08:19 p. m.</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3063,24 +3063,24 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>¡No lo bote! Las marcas y beneficios legales que premian su certificado electoral este 31 de mayo</t>
+          <t>Edgar Morin, el caminante (Homenaje)</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/no-lo-bote-las-marcas-y-beneficios-legales-que-premian-su-certificado-electoral-este-31-de-mayo/</t>
+          <t>https://www.elespectador.com/el-magazin-cultural/edgar-morin-el-caminante-homenaje/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 05:39 p. m.</t>
+          <t>31/05/2026 08:12 p. m.</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
@@ -3090,24 +3090,24 @@
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Terremoto político y judicial: Santiago Botero Jaramillo, denunciado por presunta violencia intrafamiliar</t>
+          <t>Elecciones a la presidencia: en Cali y Valle, Cepeda obtuvo la mayoría de los votos</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/terremoto-politico-y-judicial-santiago-botero-jaramillo-denunciado-por-presunta-violencia-intrafamiliar/</t>
+          <t>https://www.elespectador.com/colombia/cali/elecciones-a-la-presidencia-los-resultados-en-cali-y-valle-del-cauca/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 11:07 a. m.</t>
+          <t>31/05/2026 08:12 p. m.</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3117,24 +3117,24 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Myke Towers confirma concierto en Bogotá con su gira “Trap Kings”</t>
+          <t>Nicolás Maduro y su esposa “elevan oraciones” antes de su próxima audiencia en Nueva York</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/myke-towers-confirma-concierto-en-bogota-con-su-gira-trap-kings/</t>
+          <t>https://www.elespectador.com/mundo/venezuela/nicolas-maduro-y-su-esposa-dicen-tener-una-fe-inquebrantable-en-la-victoria-de-la-verdad/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:51 a. m.</t>
+          <t>31/05/2026 08:08 p. m.</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
@@ -3144,24 +3144,24 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Acoso callejero Colombia: el 89% de las mujeres afirma haberlo sufrido</t>
+          <t>Iván Cepeda se pronuncia tras quedar segundo en las votaciones: negó resultados de preconteo</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/acoso-callejero-colombia-mujeres/</t>
+          <t>https://www.elespectador.com/politica/elecciones-colombia-2026/ivan-cepeda-se-pronuncia-tras-quedar-segundo-en-las-votaciones-nego-resultados-de-preconteo/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:44 a. m.</t>
+          <t>31/05/2026 08:01 p. m.</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3171,24 +3171,24 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Outdoor femenino Colombia: la tendencia que une aventura, naturaleza y comunidad</t>
+          <t>Presunta participación en política y delitos electorales: el saldo judicial de la jornada</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/outdoor-femenino-colombia/</t>
+          <t>https://www.elespectador.com/judicial/presunta-participacion-en-politica-y-delitos-electorales-el-saldo-judicial-de-la-jornada/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:35 a. m.</t>
+          <t>31/05/2026 08:00 p. m.</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
@@ -3198,24 +3198,24 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Bibliotecas para inspirar Cali: nueva apuesta por la lectura y los proyectos de vida</t>
+          <t>El Mundial viene con instrucciones nuevas</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/bibliotecas-para-inspirar-cali/</t>
+          <t>https://www.elespectador.com/opinion/columnistas/antonio-casale/el-mundial-viene-con-instrucciones-nuevas-columna-de-antonio-casale/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:32 a. m.</t>
+          <t>31/05/2026 08:43 p. m.</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3225,24 +3225,24 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Detección temprana cáncer de mama Colombia: la importancia de las redes de apoyo</t>
+          <t>¿Cuántos votos sacó Petro en primera vuelta 2022? Diferencia de votos con De la Espriella y Cepeda</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/deteccion-temprana-cancer-de-mama-colombia/</t>
+          <t>https://caracol.com.co/2026/06/01/cuantos-votos-saco-petro-en-primera-vuelta-2022-diferencia-de-votos-con-de-la-espriella-y-cepeda/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:27 a. m.</t>
+          <t>31/05/2026 08:39 p. m.</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
@@ -3252,24 +3252,24 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Cuidado del cabello y la piel en vacaciones: errores que debes evitar</t>
+          <t>🔴 Boletín ELECCIONES 2026 EN VIVO: Confirmada segunda vuelta Abelardo de la Espriella e Iván Cepeda</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/cuidado-del-cabello-y-la-piel-en-vacaciones/</t>
+          <t>https://caracol.com.co/2026/05/31/resultados-registraduria-en-vivo-ultimo-boletin-y-conteo-de-votos-en-directo-quien-lidera/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 10:18 a. m.</t>
+          <t>31/05/2026 08:10 p. m.</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -3279,24 +3279,24 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Bebé de 6 meses El Espinal: avanzan investigaciones tras su fallecimiento</t>
+          <t>Petro quiere perpetuarse en el poder desconociendo voluntad del pueblo colombiano: De La Espriella</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/bebe-de-6-meses-el-espinal/</t>
+          <t>https://caracol.com.co/2026/06/01/petro-quiere-perpetuarse-en-el-poder-desconociendo-voluntad-del-pueblo-colombiano-de-la-espriella/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 09:10 a. m.</t>
+          <t>31/05/2026 07:59 p. m.</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
@@ -3306,24 +3306,24 @@
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Fiesta en El Campín: Morat cantará en la despedida de la Selección Colombia rumbo al Mundial 2026</t>
+          <t>Segunda vuelta presidencial: ¿Cuándo se posesiona el nuevo presidente de Colombia 2026?</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/fiesta-en-el-campin-morat-cantara-en-la-despedida-de-la-seleccion-colombia-rumbo-al-mundial-2026/</t>
+          <t>https://caracol.com.co/2026/06/01/segunda-vuelta-presidencial-cuando-se-posesiona-el-nuevo-presidente-de-colombia-2026/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 09:03 a. m.</t>
+          <t>31/05/2026 07:50 p. m.</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -3333,24 +3333,24 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Orgullo colombiano: Kapo es coronado como ‘Compositor del Año’ en los SESAC Latina Music Awards 2026</t>
+          <t>Iván Cepeda aseguró que hay un desfase en los resultados preliminares: “son 885.000 personas”</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/orgullo-colombiano-kapo-es-coronado-como-compositor-del-ano-en-los-sesac-latina-music-awards-2026/</t>
+          <t>https://caracol.com.co/2026/06/01/ivan-cepeda-desconoce-resultados-preliminares-y-asegura-que-hay-un-desfase-son-885000-votos/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 08:56 a. m.</t>
+          <t>31/05/2026 07:50 p. m.</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
@@ -3360,24 +3360,24 @@
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>De Medellín para el mundo: elkno enciende la escena urbana con su dancehall “Ritmo”</t>
+          <t>“Petro no sabe ni entiende lo que dice”: exregistrador Galindo por denuncia de fraude en elecciones</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/de-medellin-para-el-mundo-elkno-enciende-la-escena-urbana-con-su-dancehall-ritmo/</t>
+          <t>https://caracol.com.co/2026/06/01/petro-no-sabe-ni-entiende-lo-que-dice-exregistrador-galindo-por-denuncia-de-fraude-en-elecciones/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 08:53 a. m.</t>
+          <t>31/05/2026 07:30 p. m.</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3387,24 +3387,24 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Cine colombiano: ‘VOLAR’ llega a las salas con un retrato íntimo de la soledad en Bogotá</t>
+          <t>“Abelardo de la Espriella es un peligro para Colombia”: Claudia López</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/cine-colombiano-volar-llega-a-las-salas-con-un-retrato-intimo-de-la-soledad-en-bogota/</t>
+          <t>https://caracol.com.co/2026/06/01/abelardo-de-la-espriella-es-un-peligro-para-colombia-claudia-lopez/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 08:49 a. m.</t>
+          <t>31/05/2026 07:13 p. m.</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
@@ -3414,24 +3414,24 @@
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>Desde República Dominicana para el despecho: Amneliz debuta en la música popular con “El Desquite”</t>
+          <t>El presidente Gustavo Petro no aceptó los resultados del preconteo electoral</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/desde-republica-dominicana-para-el-despecho-amneliz-debuta-en-la-musica-popular-con-el-desquite/</t>
+          <t>https://caracol.com.co/2026/06/01/el-presidente-gustavo-petro-no-acepto-los-resultados-del-preconteo-electoral/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 08:45 a. m.</t>
+          <t>31/05/2026 07:10 p. m.</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3441,24 +3441,24 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Giro en el caso de Mía Cataleya: Revelan crudos detalles de su ingreso al hospital y una captura en El Espinal</t>
+          <t>Último boletín elecciones ATLÁNTICO: Registraduría confirma quién ganó en Barranquilla y la región</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/giro-en-el-caso-de-mia-cataleya-revelan-crudos-detalles-de-su-ingreso-al-hospital-y-una-captura-en-el-espinal/</t>
+          <t>https://caracol.com.co/2026/05/31/elecciones-2026-en-vivo-barranquilla-asi-avanzan-las-votaciones-hoy-31-de-mayo-de-2026/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 08:24 a. m.</t>
+          <t>31/05/2026 07:01 p. m.</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
@@ -3468,24 +3468,24 @@
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>«Vi una pierna afuera»: Los crudos testimonios del hallazgo del profesor Kevin Santiago Ángel en Kennedy</t>
+          <t>Hemos perdido, asumo mi responsabilidad: Álvaro Uribe tras resultados de primera vuelta presidencial</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/vi-una-pierna-afuera-los-crudos-testimonios-del-hallazgo-del-profesor-kevin-santiago-angel-en-kennedy/</t>
+          <t>https://caracol.com.co/2026/06/01/hemos-perdido-asumo-mi-responsabilidad-alvaro-uribe-tras-resultados-de-primera-vuelta-presidencial/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>29/05/2026 08:12 a. m.</t>
+          <t>31/05/2026 07:01 p. m.</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -3495,24 +3495,24 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Giro en el caso de Ana María Meza: Fiscalía confirma que se investiga como presunto feminicidio</t>
+          <t>¿Cómo votaron los departamentos en las elecciones 2026? Así quedó el mapa político de Colombia</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/giro-en-el-caso-de-ana-maria-meza-fiscalia-confirma-que-se-investiga-como-presunto-feminicidio/</t>
+          <t>https://caracol.com.co/2026/06/01/como-votaron-los-departamentos-en-las-elecciones-2026-asi-quedo-el-mapa-politico-de-colombia/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 08:08 a. m.</t>
+          <t>31/05/2026 07:00 p. m.</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
@@ -3522,24 +3522,24 @@
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>El silencio forzado de Afganistán: El año en que las mujeres perdieron el derecho a existir en público</t>
+          <t>“Seremos protagonistas de lo que falta en estas elecciones”: Sergio Fajardo</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/el-silencio-forzado-de-afganistan-el-ano-en-que-las-mujeres-perdieron-el-derecho-a-existir-en-publico/</t>
+          <t>https://caracol.com.co/2026/06/01/seremos-protagonistas-de-lo-que-falta-en-estas-elecciones-sergio-fajardo/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>28/05/2026 11:24 a. m.</t>
+          <t>31/05/2026 06:48 p. m.</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -3549,24 +3549,24 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Jóvenes elecciones Colombia 2026: TikTok e IA cambian las campañas</t>
+          <t>Así quedó el último boletín de la Registraduría: ¿Cuántos votos sacaron De la Espriella y Cepeda?</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/jovenes-elecciones-colombia-2026/</t>
+          <t>https://caracol.com.co/2026/05/31/asi-quedo-el-ultimo-boletin-de-la-registraduria-cuantos-votos-sacaron-de-la-espriella-y-cepeda/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>28/05/2026 11:18 a. m.</t>
+          <t>31/05/2026 06:34 p. m.</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>Seguridad en vehículos de trabajo: la tecnología redefine el transporte de carga</t>
+          <t>“Yo, como proyecto político, me debo a Bogotá”: Juan Daniel Oviedo tras primera vuelta presidencial</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/seguridad-en-vehiculos-de-trabajo/</t>
+          <t>https://caracol.com.co/2026/05/31/yo-como-proyecto-politico-me-debo-a-bogota-juan-daniel-oviedo-tras-primera-vuelta-presidencial/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>28/05/2026 10:45 a. m.</t>
+          <t>31/05/2026 06:32 p. m.</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -3603,24 +3603,24 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>De Mar y Río lanza “Cantaré”, un homenaje al Pacífico colombiano</t>
+          <t>Así quedó la votación en Magdalena: Últimos resultados de la Registraduría</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/de-mar-y-rio-lanza-cantare-un-homenaje-al-pacifico-colombiano/</t>
+          <t>https://caracol.com.co/2026/05/31/asi-quedo-la-votacion-en-magdalena-ultimos-resultados-de-la-registraduria/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>28/05/2026 10:04 a. m.</t>
+          <t>31/05/2026 06:26 p. m.</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
@@ -3630,24 +3630,24 @@
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>Helipuertos en Bogotá: la nueva tendencia para vivir experiencias exclusivas</t>
+          <t>Jornada electoral transcurrió con total normalidad en Antioquia pese a denuncias de constreñimiento</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/helipuertos-en-bogota-experiencias/</t>
+          <t>https://caracol.com.co/2026/05/31/jornada-electoral-transcurrio-con-total-normalidad-en-antioquia-pese-a-denuncias-de-constrenimiento/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 09:07 p. m.</t>
+          <t>31/05/2026 06:26 p. m.</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -3657,24 +3657,24 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>MICROLINGOTES</t>
+          <t>Paloma Valencia anunció respaldo presidencial a Abelardo de la Espriella en la segunda vuelta</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/opinion/columnistas/oscar-alarcon/microlingotes-247/</t>
+          <t>https://caracol.com.co/2026/05/31/paloma-valencia-anuncio-respaldo-a-presidencial-abelardo-de-la-espriella-en-la-segunda-vuelta/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 09:00 p. m.</t>
+          <t>31/05/2026 06:11 p. m.</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
@@ -3684,24 +3684,24 @@
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>Torre de Tokio: vecinos espías</t>
+          <t>Reacciones a la segunda vuelta presidencial entre de Abelardo de la Espriella e Iván Cepeda</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/mundo/columna-torre-de-tokio-vecinos-espias/</t>
+          <t>https://caracol.com.co/2026/05/31/reacciones-a-la-segunda-vuelta-presidencial-entre-de-abelardo-de-la-espriella-e-ivan-cepeda/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:58 p. m.</t>
+          <t>31/05/2026 05:47 p. m.</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -3711,24 +3711,24 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>El montaje judicial que tuvo al borde de la muerte a una lideresa de El Salado</t>
+          <t>Capturaron a tres personas e impusieron 29 comparendos durante las elecciones en el Tolima</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/judicial/el-montaje-judicial-contra-una-lideresa-de-el-salado-que-la-tuvo-al-borde-de-la-muerte/</t>
+          <t>https://caracol.com.co/2026/05/31/capturaron-a-tres-personas-e-impusieron-29-comparendos-durante-las-elecciones-en-el-tolima/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:55 p. m.</t>
+          <t>31/05/2026 05:35 p. m.</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
@@ -3738,24 +3738,24 @@
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>Una mujer permanece en estado crítico luego de ser quemada por su expareja en Neiva</t>
+          <t>Elecciones Cúcuta HOY: ¿Quién ganó en el departamento Norte de Santander? Resultados Registraduría</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/una-mujer-fue-rociada-con-gasolina-y-quemada-por-su-expareja-en-neiva-el-agresor-esta-libre/</t>
+          <t>https://caracol.com.co/2026/05/31/votaciones-en-cucuta-hoy-horario-para-votar-y-ultimas-noticias-de-elecciones-en-norte-de-santander/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:25 p. m.</t>
+          <t>31/05/2026 08:40 p. m.</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -3765,24 +3765,24 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>SpaceX, OpenAI y Anthropic impulsan nueva ola de inversión en Asia</t>
+          <t>La dura advertencia de Abelardo De la Espriella a Petro: “el pueblo lo va enfrentar”</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/economia/empresas/el-exito-de-spacex-y-openai-impulsa-apuestas-por-los-proximos-ganadores-asiaticos-en-ia/</t>
+          <t>https://www.vanguardia.com/politica/elecciones/2026/05/31/la-dura-advertencia-de-abelardo-de-la-espriella-a-petro-el-pueblo-lo-va-enfrentar/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:21 p. m.</t>
+          <t>31/05/2026 08:40 p. m.</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
@@ -3792,24 +3792,24 @@
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>Movida Electoral: Así fue el último día de los candidatos presidenciales antes de elección</t>
+          <t>Elecciones</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/politica/elecciones-colombia-2026/cepeda-realizo-155-actos-publicos-de-la-espriella-aceptaria-curul-de-oposicion-si-pierde-valencia-recorre-iglesias-noticias-hoy/</t>
+          <t>https://www.vanguardia.com/politica/elecciones/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:05 p. m.</t>
+          <t>31/05/2026 08:21 p. m.</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -3819,24 +3819,24 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>¿Quiénes encabezan la disputa por la presidencia? Todo lo que debe saber de los candidatos</t>
+          <t>Iván Duque alerta sobre “amenaza” de Gustavo Petro a la democracia tras elecciones</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/politica/elecciones-colombia-2026/candidatos-presidenciales-quienes-son-los-aspirantes-que-encabezan-la-campana-perfiles-y-equipos-noticias-hoy/</t>
+          <t>https://www.vanguardia.com/politica/elecciones/2026/05/31/ivan-duque-alerta-sobre-amenaza-de-gustavo-petro-a-la-democracia-tras-elecciones/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:01 p. m.</t>
+          <t>31/05/2026 08:21 p. m.</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
@@ -3846,24 +3846,24 @@
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>Entre euforia, disturbios y cientos de detenidos, París festeja su segunda Orejona</t>
+          <t>Super Astro Luna: número y signo ganador del sorteo del domingo 31 de mayo de 2026</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/mundo/entre-euforia-disturbios-y-cientos-de-detenidos-paris-festeja-su-segunda-orejona/</t>
+          <t>https://www.vanguardia.com/loterias/2026/05/31/super-astro-luna-numero-y-signo-ganador-del-sorteo-del-domingo-31-de-mayo-de-2026/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:00 p. m.</t>
+          <t>31/05/2026 08:21 p. m.</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -3873,24 +3873,24 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Receta para preparar lomo con salsa de hongos y pimienta</t>
+          <t>Loterias</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/gastronomia-y-recetas/receta-para-preparar-lomo-con-salsa-de-hongos-y-pimienta/</t>
+          <t>https://www.vanguardia.com/loterias/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:00 p. m.</t>
+          <t>31/05/2026 08:21 p. m.</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
@@ -3900,24 +3900,24 @@
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>5 novedades del primer SUV eléctrico de Subaru en Colombia: Trailseeker</t>
+          <t>Resultado Caribeña Noche: qué cayó hoy domingo 31 de mayo de 2026</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/autos/5-novedades-del-primer-suv-electrico-de-subaru-en-colombia-trailseeker/</t>
+          <t>https://www.vanguardia.com/loterias/2026/05/31/resultado-caribena-noche-que-cayo-hoy-domingo-31-de-mayo-de-2026/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 09:02 p. m.</t>
+          <t>31/05/2026 04:55 p. m.</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -3927,24 +3927,24 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Las propuestas de Sergio Fajardo: el cambio serio y seguro es el único camino viable</t>
+          <t>Capturan a alias ‘Chalia’ en el Chocó</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-30/elecciones-presidenciales-en-colombia-2026-en-vivo.html</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/31/capturan-a-alias-chalia-en-el-choco/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:40 p. m.</t>
+          <t>31/05/2026 04:55 p. m.</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
@@ -3954,24 +3954,24 @@
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>Las propuestas de Abelardo de la Espriella: seguridad total de “mano dura” y el crecimiento económico acelerado</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/las-propuestas-de-abelardo-de-la-espriella-seguridad-total-de-mano-dura-y-el-crecimiento-economico-acelerado.html</t>
+          <t>https://www.vanguardia.com/colombia/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:34 p. m.</t>
+          <t>31/05/2026 04:14 p. m.</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -3981,24 +3981,24 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Las propuestas de Iván Cepeda, tres revoluciones y más inversión social</t>
+          <t>Elecciones transparente y tranquilas: balance de observadores de Unión Europea</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/las-propuestas-de-ivan-cepeda-tres-revoluciones-y-mas-inversion-social.html</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/31/elecciones-transparente-y-tranquilas-balance-de-observadores-de-union-europea/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:21 p. m.</t>
+          <t>31/05/2026 03:38 p. m.</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
@@ -4008,24 +4008,24 @@
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>Las propuestas de Paloma Valencia: seguridad total y reactivación petrolera</t>
+          <t>Habitantes de Islas del Rosario, en Cartagena, advierten que no participarán en votaciones por falta de energía</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/las-propuestas-de-paloma-valencia-seguridad-total-y-reactivacion-petrolera.html</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/31/habitantes-de-islas-del-rosario-en-cartagena-advierten-que-no-participaran-en-votaciones-por-falta-de-energia/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 07:57 p. m.</t>
+          <t>31/05/2026 03:26 p. m.</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -4035,24 +4035,24 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Iván Cepeda: “Es necesario, dentro del capitalismo, pasar a un modelo socialmente equitativo”</t>
+          <t>Emergencia en Quindío: vehículo choca contra una fonda en el sector de Barragán</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/daniel-coronell-entrevista-a-ivan-cepeda-a-pocas-horas-de-las-elecciones.html</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/31/emergencia-en-quindio-vehiculo-choca-contra-una-fonda-en-el-sector-de-barragan/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 07:25 p. m.</t>
+          <t>31/05/2026 03:09 p. m.</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
@@ -4062,24 +4062,24 @@
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>Estados Unidos ataca un barco que trataba de atravesar el estrecho de Ormuz rumbo a Irán</t>
+          <t>Procuraduría abrió investigación al ministro Sanguino por posible participación en política</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/internacional/2026-05-31/estados-unidos-ataca-un-barco-que-trataba-de-atravesar-el-estrecho-de-ormuz-rumbo-a-iran.html</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/31/procuraduria-abrio-investigacion-al-ministro-sanguino-por-posible-participacion-en-politica/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 06:28 p. m.</t>
+          <t>31/05/2026 02:28 p. m.</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -4089,24 +4089,24 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Abelardo de la Espriella cierra su campaña en una entrevista con Westcol: “Quien demuestre la idoneidad física y psicológica podrá portar un arma en la era del tigre”</t>
+          <t>Medicina legal inicia proceso de identificación de los cuerpos de 48 disidentes</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-30/abelardo-de-la-espriella-cierra-su-campana-en-una-entrevista-con-westcol-esta-no-es-una-candidatura-sino-un-movimiento-popular.html</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/31/medicina-legal-inicia-proceso-de-identificacion-de-los-cuerpos-de-48-disidentes/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 06:07 p. m.</t>
+          <t>31/05/2026 02:26 p. m.</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
@@ -4116,24 +4116,24 @@
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>Noboa insiste en convertir la guerra arancelaria en herramienta electoral en Colombia</t>
+          <t>Santander, entre los departamentos con fallas en redes de telecomunicaciones durante la jornada electoral</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-30/noboa-insiste-en-convertir-la-guerra-arancelaria-en-herramienta-electoral-en-colombia.html</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/31/santander-entre-los-departamentos-con-fallas-en-redes-de-telecomunicaciones-durante-la-jornada-electoral/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 05:30 p. m.</t>
+          <t>31/05/2026 02:01 p. m.</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -4143,24 +4143,24 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Vox abraza una internacional blanca para unir Europa y lograr un “efecto salida” de emigrantes</t>
+          <t>Elecciones presidenciales: incautan $110 millones y capturan a una persona en operativos de la Policía</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/espana/2026-05-30/vox-abraza-una-internacional-blanca-para-unir-europa-y-lograr-un-efecto-salida-de-emigrantes.html</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/31/elecciones-presidenciales-incautan-110-millones-y-capturan-a-una-persona-en-operativos-de-la-policia/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 05:25 p. m.</t>
+          <t>31/05/2026 01:40 p. m.</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
@@ -4170,24 +4170,24 @@
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>Paloma Valencia: “A los guerrilleros les voy a hacer sentir la mano de acero de la mujer colombiana”</t>
+          <t>Identifican grupo de personas que presuntamente compraba votos en Popayán</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-30/paloma-valencia-se-reune-con-cuatro-influenciadores-a-15-horas-del-inicio-de-las-elecciones.html</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/31/identifican-grupo-de-personas-que-presuntamente-compraba-votos-en-popayan/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 04:51 p. m.</t>
+          <t>31/05/2026 11:52 a. m.</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -4197,24 +4197,24 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Bad Bunny en Madrid: el alucinante jolgorio del perreo y el amor</t>
+          <t>Cárcel para médico de Bogotá por presunto abuso de dos niñas en las consultas</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/cultura/2026-05-30/bad-bunny-en-madrid-el-alucinante-jolgorio-del-perreo-y-el-amor.html</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/30/carcel-para-medico-de-bogota-por-presunto-abuso-de-dos-ninas-en-las-consultas/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 04:49 p. m.</t>
+          <t>31/05/2026 08:35 p. m.</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
@@ -4224,24 +4224,24 @@
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>Más de un centenar de detenidos en París en los incidentes producidos tras la victoria del PSG en la Champions</t>
+          <t>Brasil no perdona y golea a Panamá como preparación para el Mundial</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/deportes/futbol/2026-05-30/mas-de-un-centenar-de-detenidos-en-paris-en-los-incidentes-producidos-tras-la-victoria-del-psg-en-la-champions.html</t>
+          <t>https://www.bluradio.com/deportes/futbol/brasil-no-perdona-y-golea-a-panama-como-preparacion-para-el-mundial-cb20</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 04:40 p. m.</t>
+          <t>31/05/2026 08:26 p. m.</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -4251,24 +4251,24 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Vitinha, tras ganar la Champions: “Somos el mejor equipo del mundo”</t>
+          <t>Se acorta diferencia de votos entre el Petrismo y el Charismo en Barranquilla: así quedó la cuenta</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/deportes/futbol/2026-05-30/vitinha-tras-ganar-la-champions-somos-el-mejor-equipo-del-mundo.html</t>
+          <t>https://www.bluradio.com/regiones/caribe/se-acorta-diferencia-de-votos-entre-el-petrismo-y-el-charismo-en-barranquilla-asi-quedo-la-cuenta-rg10</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 04:22 p. m.</t>
+          <t>31/05/2026 08:23 p. m.</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
@@ -4278,24 +4278,24 @@
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>Resultados de las elecciones en Colombia 2026: cuándo se conocerán las votaciones y a qué hora inicia el preconteo</t>
+          <t>De La Espriella ofrece su "respeto" a Paloma Valencia y señala a Cepeda de "impedido"</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-30/resultados-de-las-elecciones-en-colombia-2026-cuando-se-conoceran-las-votaciones-y-a-que-hora-inicia-el-preconteo.html</t>
+          <t>https://www.bluradio.com/nacion/elecciones/promesas-y-propuestas/de-la-espriella-ofrece-su-respeto-a-paloma-valencia-y-senala-a-cepeda-de-impedido-rs15</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 04:20 p. m.</t>
+          <t>31/05/2026 07:58 p. m.</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -4305,24 +4305,24 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>El PAN cierra filas con Maru Campos frente a la petición de juicio político de Morena</t>
+          <t>Cepeda llama a De La Espriella como “estafador de estafadores” y aún no reconoce resultados</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/mexico/2026-05-30/el-pan-cierra-filas-con-maru-campos-frente-a-la-peticion-de-juicio-politico-de-morena.html</t>
+          <t>https://www.bluradio.com/nacion/elecciones/cepeda-llama-a-de-la-espriella-como-estafador-de-estafadores-y-aun-no-reconoce-resultados-rs15</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 04:17 p. m.</t>
+          <t>31/05/2026 07:53 p. m.</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
@@ -4332,24 +4332,24 @@
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>Detenido el presidente municipal de Cuautla Jesús Corona por sus presuntos vínculos con la delincuencia organizada</t>
+          <t>Aida Quilcué, fórmula vicepresidencial de Cepeda: "Aún no aceptamos resultados; tenemos que revisar"</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/mexico/2026-05-30/detenido-el-presidente-municipal-de-cuautla-jesus-corona-por-sus-presuntos-vinculos-con-la-delincuencia-organizada.html</t>
+          <t>https://www.bluradio.com/nacion/elecciones/promesas-y-propuestas/aida-quilcue-formula-vicepresidencial-de-cepeda-aun-no-aceptamos-resultados-tenemos-que-revisar-so35</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 03:37 p. m.</t>
+          <t>31/05/2026 07:51 p. m.</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -4359,24 +4359,24 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>El ajedrecista Carlsen en gran crisis: tres derrotas en cinco rondas</t>
+          <t>Abelardo De la Espriella y movimiento Creemos, grandes ganadores de la primera vuelta en Medellín</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/deportes/2026-05-30/el-ajedrecista-carlsen-en-gran-crisis-tres-derrotas-en-cinco-rondas.html</t>
+          <t>https://www.bluradio.com/regiones/antioquia/abelardo-de-la-espriella-y-movimiento-creemos-grandes-ganadores-de-la-primera-vuelta-en-medellin-rg10</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 03:35 p. m.</t>
+          <t>31/05/2026 07:45 p. m.</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
@@ -4386,24 +4386,24 @@
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>Ventura, vigésima Puerta Grande a pesar de fallar con el rejón de muerte</t>
+          <t>No hay paso entre Manizales y Murillo: deslizamiento cerca al Nevado del Ruiz genera bloqueo</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/cultura/2026-05-30/ventura-vigesima-puerta-grande-a-pesar-de-fallar-con-el-rejon-de-muerte.html</t>
+          <t>https://www.bluradio.com/nacion/no-hay-paso-entre-manizales-y-murillo-deslizamiento-cerca-al-nevado-del-ruiz-genera-bloqueo-rg10</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 03:15 p. m.</t>
+          <t>31/05/2026 07:33 p. m.</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -4413,24 +4413,24 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Muere Julio Le Parc, artista de la luz y el movimiento</t>
+          <t>El uribismo perdió en Antioquia: De la Espriella arrasó con la candidatura de Paloma Valencia</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/argentina/2026-05-30/muere-julio-le-parc-artista-de-la-luz-y-el-movimiento.html</t>
+          <t>https://www.bluradio.com/regiones/antioquia/el-uribismo-perdio-en-antioquia-de-la-espriella-arraso-con-la-candidatura-de-paloma-valencia-rg10</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 03:14 p. m.</t>
+          <t>31/05/2026 07:23 p. m.</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
@@ -4440,24 +4440,24 @@
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>PSG - Arsenal: la final de la Champions League 2026 en Budapest, en imágenes</t>
+          <t>Dorado Noche, resultado del último sorteo hoy domingo 31 de mayo de 2026</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/deportes/2026-05-30/psg-arsenal-la-final-de-la-champions-league-2026-en-budapest-en-imagenes.html</t>
+          <t>https://www.bluradio.com/economia/juegos-de-azar/dorado-noche-resultado-del-ultimo-sorteo-hoy-domingo-31-de-mayo-de-2026-so35</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 02:54 p. m.</t>
+          <t>31/05/2026 07:22 p. m.</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -4467,24 +4467,24 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>La gloria le vuelve a dar un portazo al Arsenal en la Champions</t>
+          <t>Caribeña Noche, resultado del último sorteo hoy domingo 31 de mayo de 2026</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/deportes/futbol/2026-05-30/la-gloria-le-vuelve-a-dar-un-portazo-al-arsenal-en-la-champions.html</t>
+          <t>https://www.bluradio.com/economia/juegos-de-azar/caribena-noche-resultado-del-ultimo-sorteo-hoy-domingo-31-de-mayo-de-2026-so35</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 02:50 p. m.</t>
+          <t>31/05/2026 07:21 p. m.</t>
         </is>
       </c>
       <c r="B149" s="6" t="inlineStr">
@@ -4494,24 +4494,24 @@
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>La grandeza premia al doble campeón PSG, que tumba en los penaltis al Arsenal</t>
+          <t>Sinuano Noche, resultados del último sorteo hoy domingo 31 de mayo de 2026</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/deportes/futbol/2026-05-30/la-grandeza-premia-al-doble-campeon-psg-que-tumba-en-los-penaltis-al-arsenal.html</t>
+          <t>https://www.bluradio.com/economia/juegos-de-azar/sinuano-noche-resultados-del-ultimo-sorteo-hoy-domingo-31-de-mayo-de-2026-so35</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 01:10 p. m.</t>
+          <t>31/05/2026 07:15 p. m.</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Cantando y bailando, así ha recibido Madrid a Bad Bunny: “Con ganas de perreo, pero sin entrada”</t>
+          <t>Petro no acepta resultados del preconteo y asegura que solo reconocerá escrutinios oficiales</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/cultura/2026-05-30/bienvenidos-al-madrid-de-bad-bunny-con-ganas-de-perreo-pero-sin-entrada.html</t>
+          <t>https://www.bluradio.com/nacion/elecciones/petro-no-acepta-resultados-del-preconteo-y-asegura-que-solo-reconocera-escrutinios-rg10</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 10:41 a. m.</t>
+          <t>31/05/2026 08:31 p. m.</t>
         </is>
       </c>
       <c r="B151" s="6" t="inlineStr">
@@ -4548,24 +4548,24 @@
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>Se rompe la cuerda de la bandera de España durante el izado en el desfile del Día de las Fuerzas Armadas</t>
+          <t>Si va al Mundial 2026: ¿Puede votar desde allí por Abelardo de la Espriella o Iván Cepeda?</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/videos/2026-05-30/se-rompre-la-cuerda-de-la-bandera-de-espana-durante-el-izado-en-el-desfile-del-dia-de-las-fuerzas-armadas.html?autoplay=1</t>
+          <t>https://www.semana.com/deportes/articulo/si-va-al-mundial-2026-puede-votar-desde-alli-por-abelardo-de-la-espriella-o-ivan-cepeda/202633/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 09:24 a. m.</t>
+          <t>31/05/2026 08:10 p. m.</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -4575,24 +4575,24 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>De la ‘Operación Kitchen’ a Leire Díez: las cloacas se retroalimentan</t>
+          <t>¿Cuántos votos se necesitan para ganar la segunda vuelta en Colombia? Estas son las cuentas</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/espana/2026-05-30/de-la-operacion-kitchen-a-leire-diez-las-cloacas-se-retroalimentan.html</t>
+          <t>https://www.semana.com/politica/articulo/cuantos-votos-se-necesitan-para-ganar-la-segunda-vuelta-en-colombia/202622/</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 07:14 a. m.</t>
+          <t>31/05/2026 08:01 p. m.</t>
         </is>
       </c>
       <c r="B153" s="6" t="inlineStr">
@@ -4602,24 +4602,24 @@
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>Los partidos de Sumar instan al PSOE a actuar: “¿Hay una trama? Se contesta con leyes, medidas y ejemplaridad”</t>
+          <t>Abelardo de la Espriella habla desde un planchón en Barranquilla, tras su triunfo: “Que Estados Unidos y otros países vigilen la segunda vuelta”</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/espana/catalunya/2026-05-30/los-partidos-de-sumar-instan-al-psoe-a-actuar-hay-una-trama-se-contesta-con-leyes-medidas-y-ejemplaridad.html</t>
+          <t>https://www.semana.com/politica/articulo/abelardo-de-la-espriella-habla-desde-un-planchon-en-barranquilla-tras-su-triunfo-en-la-primera-vuelta/202652/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 06:19 a. m.</t>
+          <t>31/05/2026 07:58 p. m.</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -4629,24 +4629,24 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Lotería Nacional: resultados del sorteo del sábado 30 de mayo</t>
+          <t>Juan Daniel Oviedo se pronuncia tras su derrota: “Es increíble que Colombia se debata su futuro alrededor de la homofobia y el machismo”</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/sorteos/2026-05-30/loteria-nacional-sorteo-del-sabado-30-de-mayo.html</t>
+          <t>https://www.semana.com/politica/articulo/juan-daniel-oviedo-se-pronuncia-tras-su-derrota-es-increible-que-colombia-se-debata-su-futuro-alrededor-de-la-homofobia-y-el-machismo/202659/</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 04:03 a. m.</t>
+          <t>31/05/2026 07:58 p. m.</t>
         </is>
       </c>
       <c r="B155" s="6" t="inlineStr">
@@ -4656,24 +4656,24 @@
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>Muere Josefina Molina, pionera del cine español, a los 89 años</t>
+          <t>Elecciones Colombia en el exterior: mapa de cómo votaron los colombianos este domingo, 31 de mayo</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/cultura/2026-05-30/fallece-josefina-molina-pionera-del-cine-espanol-a-los-89-anos.html</t>
+          <t>https://www.semana.com/politica/articulo/elecciones-colombia-en-el-exterior-mapa-de-como-votaron-los-colombianos-este-domingo-31-de-mayo/202601/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 02:22 a. m.</t>
+          <t>31/05/2026 07:58 p. m.</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -4683,24 +4683,24 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Muere el filósofo francés Edgar Morin a los 104 años</t>
+          <t>Iván Cepeda cuestiona los resultados de la primera vuelta presidencial: advierte sobre un “desfase” de 885.000 cédulas en el censo electoral</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/cultura/2026-05-30/muere-el-filosofo-frances-edgar-morin-a-los-104-anos.html</t>
+          <t>https://www.semana.com/politica/articulo/ivan-cepeda-cuestiona-los-resultados-de-la-primera-vuelta-presidencial-advierte-sobre-un-desfase-de-885000-cedulas-en-el-censo-electoral/202600/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 10:30 p. m.</t>
+          <t>31/05/2026 07:58 p. m.</t>
         </is>
       </c>
       <c r="B157" s="6" t="inlineStr">
@@ -4710,24 +4710,24 @@
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>Donna Haraway, filósofa: “Vivimos en un mundo pronatalista y antiinfancia. Los bebés deberían ser escasos y valiosos”</t>
+          <t>Gustavo Petro reacciona a la primera vuelta presidencial: “No acepto los resultados del preconteo”</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/ideas/2026-05-30/donna-haraway-filosofa-vivimos-en-un-mundo-pronatalista-y-antiinfancia-tener-bebes-deberia-ser-algo-escaso-y-valioso.html</t>
+          <t>https://www.semana.com/politica/articulo/gustavo-petro-reacciona-a-la-primera-vuelta-presidencial-no-acepto-los-resultados-del-preconteo/202631/</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:54 p. m.</t>
+          <t>31/05/2026 06:58 p. m.</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -4737,24 +4737,24 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Estos son los 11 candidatos a la Presidencia de Colombia 2026</t>
+          <t>Segunda vuelta presidencial Colombia 2026: Fecha oficial y lo que debe saber</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/cuales-son-los-11-candidatos-a-la-presidencia-de-colombia-2026-1026269</t>
+          <t>https://www.semana.com/politica/articulo/cuando-es-la-segunda-vuelta-presidencial-de-las-elecciones-en-colombia-2026-fechas-claves/202657/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 07:44 p. m.</t>
+          <t>31/05/2026 06:58 p. m.</t>
         </is>
       </c>
       <c r="B159" s="6" t="inlineStr">
@@ -4764,24 +4764,24 @@
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>Secuestró y violó a una niña de cuatro años tras engañar a su madre con regalarle un mercado en Cali</t>
+          <t>“SEMANA merece reconocimiento por informar con veracidad a sus lectores y por su compromiso con la independencia”: Andrei Roman, CEO de AtlasIntel</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/secuestro-y-violo-a-una-nina-de-cuatro-anos-tras-enganar-a-su-madre-con-regalarle-un-mercado-en-cali-1026264</t>
+          <t>https://www.semana.com/confidenciales/articulo/semana-merece-reconocimiento-por-informar-con-veracidad-a-sus-lectores-y-por-su-compromiso-con-la-independencia-andrei-roman-ceo-de-atlasintel/202623/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 04:28 p. m.</t>
+          <t>31/05/2026 06:58 p. m.</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -4791,24 +4791,24 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Cadáveres de disidentes fueron cargados con explosivos para detonarlos en traslado a Medicina Legal</t>
+          <t>“Ganó el doctor Abelardo de la Espriella. Cumplimos la palabra, votaremos por él y pedimos que se vote por él”: Álvaro Uribe</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/cadaveres-de-disidentes-fueron-cargados-con-explosivos-para-detonarlos-en-traslado-a-medicina-legal-1026237</t>
+          <t>https://www.semana.com/politica/articulo/gano-el-doctor-abelardo-de-la-espriella-cumplimos-la-palabra-votaremos-por-el-y-pedimos-que-se-vote-por-el-alvaro-uribe/202627/</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 03:50 p. m.</t>
+          <t>31/05/2026 06:58 p. m.</t>
         </is>
       </c>
       <c r="B161" s="6" t="inlineStr">
@@ -4818,24 +4818,24 @@
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>Más de 700 familias damnificadas y con el agua a la cintura al desbordarse tres ríos en Cabuyaro, Meta</t>
+          <t>Quién es Iván Cepeda, el candidato del Pacto Histórico que va a segunda vuelta</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/mas-de-700-familias-damnificadas-y-con-el-agua-a-la-cintura-por-el-desbordamiento-de-tres-rios-en-cabuyaro-meta-1026229</t>
+          <t>https://www.semana.com/politica/articulo/quien-es-ivan-cepeda-biografia-trayectoria-profesional-y-politica-del-candidato-a-la-presidencia-de-colombia/202620/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 03:32 p. m.</t>
+          <t>31/05/2026 06:58 p. m.</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -4845,24 +4845,24 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Elecciones Colombia: recompensas de $50 y $200 millones por actores armados y planes de atentados</t>
+          <t>Quién es Abelardo de la Espriella, el candidato que busca la Presidencia en segunda vuelta</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/elecciones-colombia-recompensas-de-50-y-200-millones-por-actores-armados-y-planes-de-atentados-1026224</t>
+          <t>https://www.semana.com/politica/articulo/quien-es-abelardo-de-la-espriella-el-candidato-que-busca-la-presidencia-en-segunda-vuelta/202634/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 02:52 p. m.</t>
+          <t>31/05/2026 06:58 p. m.</t>
         </is>
       </c>
       <c r="B163" s="6" t="inlineStr">
@@ -4872,24 +4872,24 @@
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>Video revelador: hallan el cuerpo del joven de 22 años que se lanzó al embalse de Guatapé huyendo de agresión</t>
+          <t>Paloma Valencia reconoce derrota y anuncia su apoyo a Abelardo de la Espriella</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/video-del-joven-de-22-anos-hallado-muerto-en-guatape-1026206</t>
+          <t>https://www.semana.com/politica/articulo/paloma-valencia-reconoce-derrota-y-anuncia-apoya-a-abelardo-de-al-espriella/202623/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 01:36 p. m.</t>
+          <t>31/05/2026 06:58 p. m.</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -4899,24 +4899,24 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>Bogotá entrará en alerta amarilla hospitalaria por elecciones: ¿qué significa esto?</t>
+          <t>¿Se puede cambiar el puesto de votación para segunda vuelta presidencial? Registraduría responde</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/bogota-entrara-en-alerta-amarilla-hospitalaria-por-elecciones-1025976</t>
+          <t>https://www.semana.com/politica/articulo/se-puede-cambiar-el-puesto-de-votacion-para-segunda-vuelta-presidencial-registraduria-responde/202646/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 12:56 p. m.</t>
+          <t>31/05/2026 04:58 p. m.</t>
         </is>
       </c>
       <c r="B165" s="6" t="inlineStr">
@@ -4926,24 +4926,24 @@
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>“Se está dejando utilizar”: Santiago Botero se pronunció tras el desalojo en su vivienda en Cartagena</t>
+          <t>La Champions League se pronunció y eligió al mejor jugador de la temporada: no irá al Mundial 2026</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/santiago-botero-se-pronuncio-tras-escandalo-de-desalojo-de-su-vivienda-1026192</t>
+          <t>https://www.semana.com/deportes/articulo/la-champions-league-se-pronuncio-y-eligio-el-mejor-jugador-de-la-temporada-no-ira-al-mundial-2026/202601/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 12:07 p. m.</t>
+          <t>31/05/2026 04:58 p. m.</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -4953,24 +4953,24 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Autoridades ordenaron desalojo a propiedad de Santiago Botero: es acusado de violencia intrafamiliar</t>
+          <t>¿Quién es Pilar Rueda, la esposa de Iván Cepeda? Así es la familia del candidato del Pacto Histórico</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/santiago-botero-es-desalojado-y-acusado-de-violencia-intrafamiliar-1026185</t>
+          <t>https://www.semana.com/politica/articulo/pilar-rueda-la-esposa-de-ivan-cepeda-asi-es-la-familia-del-candidato-del-pacto-historico/202650/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 11:43 a. m.</t>
+          <t>31/05/2026 04:58 p. m.</t>
         </is>
       </c>
       <c r="B167" s="6" t="inlineStr">
@@ -4980,24 +4980,24 @@
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>Colombia, lista para votar: el llamado a respetar los resultados</t>
+          <t>¿Quién es Ana Lucía Pineda, la esposa de Abelardo de la Espriella, candidato por la presidencia en Colombia?</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/colombia-lista-para-votar-el-llamado-a-respetar-los-resultados-1026172</t>
+          <t>https://www.semana.com/politica/articulo/quien-es-ana-lucia-pineda-la-esposa-de-abelardo-de-la-espriella-candidato-por-la-presidencia-en-colombia/202645/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:53 p. m.</t>
+          <t>31/05/2026 03:58 p. m.</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -5007,24 +5007,24 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Video muestra el momento exacto en que meteoro cae en EE. UU. con fuerza de 300 toneladas de TNT</t>
+          <t>Vingegaard es campeón del Giro de Italia; Egan, fenomenal: es top 10 y aumenta su historia en el ciclismo mundial</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/mundo/video-muestra-el-momento-exacto-en-que-meteoro-cae-en-ee-uu-con-fuerza-de-300-toneladas-de-tnt-cb20</t>
+          <t>https://www.semana.com/deportes/ciclismo/articulo/vingegaard-es-campeon-del-giro-de-italia-y-egan-fenomenal-top-10-y-aumenta-su-historia-en-el-ciclismo-mundial/202625/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:51 p. m.</t>
+          <t>31/05/2026 12:58 p. m.</t>
         </is>
       </c>
       <c r="B169" s="6" t="inlineStr">
@@ -5034,26 +5034,22 @@
       </c>
       <c r="C169" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>Super Astro Luna, resultado del último sorteo hoy sábado 30 de mayo de 2026</t>
+          <t>¿Hasta qué hora es la ley seca en Colombia? Conozca el momento exacto en que finaliza la restricción</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/super-astro-luna-resultado-del-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-so35</t>
+          <t>https://www.semana.com/nacion/articulo/hasta-que-hora-es-la-ley-seca-en-colombia-conozca-el-momento-exacto-en-que-finaliza-la-restriccion/202622/</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="3" t="inlineStr">
-        <is>
-          <t>30/05/2026 08:51 p. m.</t>
-        </is>
-      </c>
+      <c r="A170" s="3" t="inlineStr"/>
       <c r="B170" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5061,26 +5057,22 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Caribeña Noche, resultado del último sorteo hoy sábado 30 de mayo de 2026</t>
+          <t>Brasil y Ancelotti hablaron desde el Maracaná y advierten a sus máximos rivales en el Mundial 2026 con gran goleada</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/caribena-noche-resultado-del-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-so35</t>
+          <t>https://www.semana.com/deportes/articulo/brasil-y-ancelotti-hablaron-desde-el-maracana-y-advierten-a-sus-maximos-rivales-en-el-mundial-2026-con-gran-goleada/202621/</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="6" t="inlineStr">
-        <is>
-          <t>30/05/2026 08:51 p. m.</t>
-        </is>
-      </c>
+      <c r="A171" s="6" t="inlineStr"/>
       <c r="B171" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5088,26 +5080,22 @@
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>Sinuano Noche, resultado del último sorteo hoy sábado 30 de mayo de 2026</t>
+          <t>Hijo de Zinedine Zidane se ilusiona con jugar el Mundial 2026: convocatoria oficial desde África resalta su nombre</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/sinuano-noche-resultado-del-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-so35</t>
+          <t>https://www.semana.com/deportes/articulo/hijo-de-zinedine-zidane-se-ilusiona-con-jugar-el-mundial-2026-convocatoria-oficial-desde-africa-resalta-su-nombre/202626/</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="3" t="inlineStr">
-        <is>
-          <t>30/05/2026 08:51 p. m.</t>
-        </is>
-      </c>
+      <c r="A172" s="3" t="inlineStr"/>
       <c r="B172" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5115,26 +5103,22 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Resultados del Dorado Noche: último sorteo hoy, sábado 30 de mayo de 2026, números ganadores</t>
+          <t>Los partidos del Mundial 2026 que se disputarán el 21 de junio, día de la segunda vuelta entre Abelardo de la Espriella e Iván Cepeda: ¿incidirá en las votaciones?</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/resultados-del-dorado-noche-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-numeros-ganadores-so35</t>
+          <t>https://www.semana.com/deportes/articulo/los-partidos-del-mundial-2026-que-se-disputaran-el-21-de-junio-dia-de-la-segunda-vuelta-entre-abelardo-de-la-espriella-e-ivan-cepeda-incidira-en-las-votaciones/202619/</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="6" t="inlineStr">
-        <is>
-          <t>30/05/2026 08:50 p. m.</t>
-        </is>
-      </c>
+      <c r="A173" s="6" t="inlineStr"/>
       <c r="B173" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5142,26 +5126,22 @@
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D173" s="7" t="inlineStr">
         <is>
-          <t>Loterías de Boyacá, Cauca, Extra de Colombia y Baloto: resultados sorteos hoy sábado 30 de mayo</t>
+          <t>Elecciones presidenciales 2026 EN VIVO | Abelardo de la Espriella e Iván Cepeda se enfrentarán en segunda vuelta: reacciones y últimas noticias</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/loterias-de-boyaca-cauca-extra-de-colombia-y-baloto-resultados-sorteos-hoy-sabado-30-de-mayo-so35</t>
+          <t>https://www.semana.com/nacion/articulo/resultados-elecciones-colombia-2026-en-vivo-habla-abelardo-de-la-espriella-y-anticipa-que-cambiara-la-historia/202622/</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="3" t="inlineStr">
-        <is>
-          <t>30/05/2026 08:50 p. m.</t>
-        </is>
-      </c>
+      <c r="A174" s="3" t="inlineStr"/>
       <c r="B174" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5169,26 +5149,22 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Baloto y Revancha, resultados del último sorteo hoy sábado 30 de mayo de 2026</t>
+          <t>Aída Quilcué no reconoce los resultados arrojados por el preconteo y habla de caminar en una “minga”</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/baloto-y-revancha-resultados-del-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-so35</t>
+          <t>https://www.semana.com/politica/articulo/aida-quilcue-no-reconoce-los-resultados-arrojados-por-el-preconteo-y-habla-de-caminar-en-una-minga/202610/</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="6" t="inlineStr">
-        <is>
-          <t>30/05/2026 08:50 p. m.</t>
-        </is>
-      </c>
+      <c r="A175" s="6" t="inlineStr"/>
       <c r="B175" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5196,26 +5172,22 @@
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>Extra de Colombia, resultados del último sorteo de este sábado 30 de mayo de 2026</t>
+          <t>¿Se le dañó el certificado electoral? Esto es lo que debe hacer para no perder sus beneficios</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/extra-de-colombia-resultados-del-ultimo-sorteo-de-este-sabado-30-de-mayo-de-2026-so35</t>
+          <t>https://www.semana.com/politica/articulo/se-le-dano-el-certificado-electoral-esto-es-lo-que-debe-hacer-para-no-perder-sus-beneficios/202628/</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="3" t="inlineStr">
-        <is>
-          <t>30/05/2026 08:49 p. m.</t>
-        </is>
-      </c>
+      <c r="A176" s="3" t="inlineStr"/>
       <c r="B176" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5223,26 +5195,22 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Lotería del Cauca sábado 30 de mayo de 2026, resultados del último sorteo, premio mayor y secos</t>
+          <t>“¡Qué peligro! Gustavo Petro quiere quedarse en el poder”: reacciones porque el presidente no aceptó resultados electorales</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/loteria-del-cauca-sabado-30-de-mayo-de-2026-resultados-del-ultimo-sorteo-premio-mayor-y-secos-so35</t>
+          <t>https://www.semana.com/politica/articulo/que-peligro-gustavo-petro-quiere-quedarse-en-el-poder-reacciones-porque-el-presidente-no-acepto-resultados-electorales/202643/</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="6" t="inlineStr">
-        <is>
-          <t>30/05/2026 08:49 p. m.</t>
-        </is>
-      </c>
+      <c r="A177" s="6" t="inlineStr"/>
       <c r="B177" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5250,26 +5218,22 @@
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>Lotería Boyacá, resultados del último sorteo hoy sábado 30 de mayo de 2026</t>
+          <t>Roy Barreras se inclina por el Pacto Histórico en segunda vuelta y manda mensaje a Iván Cepeda: “Debe abrirse al centro”</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/loteria-boyaca-resultados-del-ultimo-sorteo-hoy-sabado-30-de-mayo-de-2026-so35</t>
+          <t>https://www.semana.com/nacion/cali/articulo/roy-barreras-se-inclina-por-el-pacto-historico-en-segunda-vuelta-y-manda-mensaje-a-ivan-cepeda-debe-abrirse-al-centro/202645/</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="3" t="inlineStr">
-        <is>
-          <t>30/05/2026 08:46 p. m.</t>
-        </is>
-      </c>
+      <c r="A178" s="3" t="inlineStr"/>
       <c r="B178" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5277,26 +5241,22 @@
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Al menos seis personas estarían atrapadas tras el colapso de un edificio en Nueva Delhi</t>
+          <t>Mapa de los resultados de la primera vuelta | Así votó Colombia este domingo, 31 de mayo</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/mundo/al-menos-seis-personas-estarian-atrapadas-tras-el-colapso-de-un-edificio-en-nueva-delhi-cb20</t>
+          <t>https://www.semana.com/nacion/cali/articulo/mapa-de-los-resultados-de-la-primera-vuelta-asi-voto-colombia-este-domingo-31-de-mayo/202635/</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="6" t="inlineStr">
-        <is>
-          <t>30/05/2026 08:04 p. m.</t>
-        </is>
-      </c>
+      <c r="A179" s="6" t="inlineStr"/>
       <c r="B179" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5304,26 +5264,22 @@
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>Encuentran muerta a adolescente de 14 años desaparecida hace una semana; investigan homicidio</t>
+          <t>Ministro de Defensa lanza advertencia tras votaciones: “La alerta se incrementa aún más”</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/mundo/encuentran-muerta-a-adolescente-de-14-anos-desaparecida-hace-una-semana-investigan-homicidio-rs15</t>
+          <t>https://www.semana.com/politica/articulo/ministro-de-defensa-lanza-advertencia-tras-votaciones-la-alerta-se-incrementa-aun-mas/202622/</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="3" t="inlineStr">
-        <is>
-          <t>30/05/2026 08:53 p. m.</t>
-        </is>
-      </c>
+      <c r="A180" s="3" t="inlineStr"/>
       <c r="B180" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5331,24 +5287,24 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Cristian Mosquera fue tendencia tras cometer penal en la final que perdió Arsenal ante PSG</t>
+          <t>El Ideam entregó el pronóstico del clima para las primeras horas de junio: “Probabilidad de lluvias en distintos sectores”</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/deportes/2026/05/30/cristian-mosquera-fue-tendencia-tras-cometer-penal-en-la-final-que-perdio-arsenal-ante-psg/</t>
+          <t>https://www.semana.com/nacion/bogota/articulo/el-ideam-entrego-el-pronostico-del-clima-para-las-primeras-horas-de-junio-probabilidad-de-lluvias-en-distintos-sectores/202647/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:53 p. m.</t>
+          <t>31/05/2026 08:05 p. m.</t>
         </is>
       </c>
       <c r="B181" s="6" t="inlineStr">
@@ -5358,24 +5314,24 @@
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D181" s="7" t="inlineStr">
         <is>
-          <t>Deportes</t>
+          <t>¿Quién es Iván Cepeda, el líder de izquierda que llega a la segunda vuelta presidencial?</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/deportes/</t>
+          <t>https://www.noticiasrcn.com/colombia/quien-es-ivan-cepeda-quien-llega-a-segunda-vuelta-presidencial-1026606</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:46 p. m.</t>
+          <t>31/05/2026 07:59 p. m.</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -5385,24 +5341,24 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Más de 300 detenidos en Francia tras los disturbios por la victoria del PSG</t>
+          <t>Juan Daniel Oviedo se aparta de la decisión de Paloma Valencia de sumarse a la campaña de la Espriella</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/mundo/2026/05/30/mas-de-300-detenidos-en-francia-tras-los-disturbios-por-la-victoria-del-psg/</t>
+          <t>https://www.noticiasrcn.com/colombia/juan-daniel-oviedo-se-aparta-de-la-decision-de-paloma-valencia-de-sumarse-a-la-campana-de-la-espriella-1026587</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 06:58 p. m.</t>
+          <t>31/05/2026 07:47 p. m.</t>
         </is>
       </c>
       <c r="B183" s="6" t="inlineStr">
@@ -5412,24 +5368,24 @@
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D183" s="7" t="inlineStr">
         <is>
-          <t>En entrevista con Westcol, Abelardo de la Espriella rechaza acusaciones</t>
+          <t>“Obtuvimos 10 millones de votos mal contados”: Iván Cepeda tras preconteo electoral</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/2026/05/30/en-entrevista-con-westcol-abelardo-de-la-espriella-rechaza-acusaciones/</t>
+          <t>https://www.noticiasrcn.com/colombia/obtuvimos-10-millones-de-votos-mal-contados-ivan-cepeda-denuncio-irregularidades-en-elecciones-1026594</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 06:40 p. m.</t>
+          <t>31/05/2026 07:41 p. m.</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -5439,24 +5395,24 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Petro rechaza supuesta injerencia de Estados Unidos y Ecuador en elecciones</t>
+          <t>8 capturas, 10 noticias criminales y 77 desaparecidos en las urnas: Fiscalía sobre su plan de acción durante las elecciones</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/2026/05/30/petro-rechaza-supuesta-injerencia-de-estados-unidos-y-ecuador-en-elecciones/</t>
+          <t>https://www.noticiasrcn.com/colombia/fiscalia-mantiene-plan-de-accion-contra-delitos-en-las-elecciones-2026-1026569</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 06:40 p. m.</t>
+          <t>31/05/2026 07:37 p. m.</t>
         </is>
       </c>
       <c r="B185" s="6" t="inlineStr">
@@ -5466,24 +5422,24 @@
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D185" s="7" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>¿Se puede modificar el puesto de votación para la segunda vuelta de las elecciones 2026?</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/</t>
+          <t>https://www.noticiasrcn.com/colombia/no-se-puede-cambiar-el-puesto-de-votacion-para-la-segunda-vuelta-de-las-elecciones-1026588</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 06:37 p. m.</t>
+          <t>31/05/2026 07:30 p. m.</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -5493,24 +5449,24 @@
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>“Gracias, amigo”: el gesto de Arensman a Egan que emocionó en el Giro</t>
+          <t>Abelardo de la Espriella, el ‘outsider’ millonario que se disputa la Presidencia de Colombia</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/deportes/2026/05/30/gracias-amigo-el-gesto-de-arensman-a-egan-que-emociono-en-el-giro/</t>
+          <t>https://www.noticiasrcn.com/colombia/quien-es-abelardo-de-la-espriella-el-tigre-candidato-a-la-presidencia-de-colombia-1026581</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 05:56 p. m.</t>
+          <t>31/05/2026 07:21 p. m.</t>
         </is>
       </c>
       <c r="B187" s="6" t="inlineStr">
@@ -5520,24 +5476,24 @@
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D187" s="7" t="inlineStr">
         <is>
-          <t>Más de 10.400 funcionarios vigilarán las elecciones por orden de Procuraduría</t>
+          <t>Presidente Gustavo Petro no aceptó resultados del preconteo y denunció alteraciones en software</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/2026/05/30/mas-de-10400-funcionarios-vigilaran-las-elecciones-por-orden-de-procuraduria/</t>
+          <t>https://www.noticiasrcn.com/colombia/gustavo-petro-no-acepto-resultados-en-primera-vuelta-y-denuncio-irregularidades-1026575</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 05:23 p. m.</t>
+          <t>31/05/2026 07:14 p. m.</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -5547,24 +5503,24 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>El PSG, el equipo de Luis Enrique, entra al club de los gigantes de Europa</t>
+          <t>Así reaccionaron “los quemados” a los resultados de primera vuelta</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/deportes/2026/05/30/el-psg-el-equipo-de-luis-enrique-entra-al-club-de-los-gigantes-de-europa/</t>
+          <t>https://www.noticiasrcn.com/colombia/asi-reaccionaron-los-quemados-a-los-resultados-de-primera-vuelta-1026544</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 05:10 p. m.</t>
+          <t>31/05/2026 06:57 p. m.</t>
         </is>
       </c>
       <c r="B189" s="6" t="inlineStr">
@@ -5574,24 +5530,24 @@
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D189" s="7" t="inlineStr">
         <is>
-          <t>Samuel Morales y Juank Ricardo anuncian el fin de su unión musical</t>
+          <t>Así quedó el mapa político en primera vuelta: regiones que lideraron de la Espriella y Cepeda</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/farandula/2026/05/30/samuel-morales-y-juank-ricardo-anuncian-el-fin-de-su-union-musical/</t>
+          <t>https://www.noticiasrcn.com/colombia/asi-quedo-el-mapa-politico-en-primera-vuelta-regiones-que-lideraron-de-la-espriella-y-cepeda-1026528</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 05:10 p. m.</t>
+          <t>31/05/2026 06:39 p. m.</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -5601,24 +5557,24 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>Farándula</t>
+          <t>Sergio Fajardo habla sobre lo que le pedirá a sus votantes de cara a la segunda vuelta</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/farandula/</t>
+          <t>https://www.noticiasrcn.com/colombia/que-pasara-con-los-votos-de-sergio-fajardo-en-la-segunda-vuelta-presidencial-1026542</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 05:01 p. m.</t>
+          <t>31/05/2026 08:01 p. m.</t>
         </is>
       </c>
       <c r="B191" s="6" t="inlineStr">
@@ -5628,24 +5584,24 @@
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D191" s="7" t="inlineStr">
         <is>
-          <t>Así capturaron a alias ‘Tato’ en Arjona con más de 350 dosis de estupefaciente</t>
+          <t>Petro se niega a aceptar los resultados de la primera vuelta</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/asi-capturaron-a-alias-tato-en-arjona-con-mas-de-350-dosis-de-estupefaciente/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-06-01/petro-se-niega-a-aceptar-el-conteo-provisional-de-la-primera-vuelta.html</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 04:58 p. m.</t>
+          <t>31/05/2026 07:54 p. m.</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -5655,24 +5611,24 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>No resistió: falleció cuñado de alias ‘Castor’ dos meses después de sufrir atentado</t>
+          <t>Las propuestas de Abelardo de la Espriella: seguridad de “mano dura”, reducción del Estado y libertades tributarias</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/no-resistio-fallecio-cunado-de-alias-castor-dos-meses-despues-de-sufrir-atentado/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-06-01/las-propuestas-de-abelardo-de-la-espriella-seguridad-de-mano-dura-reduccion-del-estado-y-libertades-tributarias.html</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 04:46 p. m.</t>
+          <t>31/05/2026 07:48 p. m.</t>
         </is>
       </c>
       <c r="B193" s="6" t="inlineStr">
@@ -5682,24 +5638,24 @@
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D193" s="7" t="inlineStr">
         <is>
-          <t>Donald Trump critica al papa por Irán y llama “inútil” al alcalde de Chicago</t>
+          <t>Iván Cepeda pone en duda los resultados de la primera vuelta: “Solo nos pronunciaremos cuando las comisiones escrutadoras aclaren nuestras dudas”</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/mundo/2026/05/30/donald-trump-critica-al-papa-por-iran-y-llama-inutil-al-alcalde-de-chicago/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-06-01/ivan-cepeda-pone-en-duda-los-datos-conocidos-de-la-primera-vuelta-solo-nos-pronunciaremos-sobre-los-resultados-cuando-las-comisiones-escrutadoras-aclaren-nuestras-dudas.html</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 04:34 p. m.</t>
+          <t>31/05/2026 07:45 p. m.</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -5709,24 +5665,24 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>“Están utilizando a mi familia”: Santiago Botero tras escándalo por orden de desalojo</t>
+          <t>Las propuestas de Iván Cepeda: tres revoluciones, rechazo a la militarización y continuidad</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/2026/05/30/estan-utilizando-a-mi-familia-santiago-botero-tras-escandalo-por-orden-de-desalojo/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-06-01/las-propuestas-de-ivan-cepeda-tres-revoluciones-rechazo-a-la-militarizacion-y-continuidad.html</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 04:33 p. m.</t>
+          <t>31/05/2026 07:34 p. m.</t>
         </is>
       </c>
       <c r="B195" s="6" t="inlineStr">
@@ -5736,24 +5692,24 @@
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D195" s="7" t="inlineStr">
         <is>
-          <t>Green card: así afectarían los cambios migratorios a colombianos</t>
+          <t>Iván Cepeda, el candidato inalterable que promete continuidad</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/2026/05/30/green-card-asi-afectarian-los-cambios-migratorios-a-colombianos/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-06-01/ivan-cepeda-el-candidato-inalterable-que-promete-continuidad.html</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 03:22 p. m.</t>
+          <t>31/05/2026 07:22 p. m.</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -5763,24 +5719,24 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>Petro afirma que Colombia seguirá apoyando a Ecuador en materia energética</t>
+          <t>Sergio Fajardo valoriza su millón de votos: “Vamos a ser protagonistas de estas elecciones”</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/2026/05/30/petro-afirma-que-colombia-seguira-apoyando-a-ecuador-en-materia-energetica/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-06-01/sergio-fajardo-valoriza-su-millon-de-votos-vamos-a-ser-protagonistas-de-estas-elecciones.html</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 12:33 p. m.</t>
+          <t>31/05/2026 07:18 p. m.</t>
         </is>
       </c>
       <c r="B197" s="6" t="inlineStr">
@@ -5790,24 +5746,24 @@
       </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D197" s="7" t="inlineStr">
         <is>
-          <t>Así despiden a Jhaider Garizao, el joven que se ahogó en una playa de Bocagrande</t>
+          <t>Abelardo de la Espriella celebra su victoria en la primera vuelta: “Petro y Cepeda son un par de bandidos que vamos a jubilar”</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/asi-despiden-a-jhaider-garizao-el-joven-que-se-ahogo-en-una-playa-de-bocagrande/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-06-01/abelardo-de-la-espriella-celebra-su-victoria-en-la-primera-vuelta-vamos-a-derrotar-la-tirania-y-el-absolutismo.html</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 11:54 a. m.</t>
+          <t>31/05/2026 07:06 p. m.</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -5817,24 +5773,24 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>Cayó alias ‘El Chinchurria’ en Bolívar: tenía un revólver y acumula 15 anotaciones</t>
+          <t>Paloma Valencia acepta su derrota y apoya a Abelardo de la Espriella</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/cayo-alias-el-chinchurria-en-mompox-acumulaba-15-anotaciones-judiciales/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-06-01/paloma-valencia-acepta-su-derrota-y-apoya-a-abelardo-de-la-espriella.html</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 11:13 a. m.</t>
+          <t>31/05/2026 06:35 p. m.</t>
         </is>
       </c>
       <c r="B199" s="6" t="inlineStr">
@@ -5844,24 +5800,24 @@
       </c>
       <c r="C199" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D199" s="7" t="inlineStr">
         <is>
-          <t>Por enésima vez cayó ‘Chawalita’ en Cartagena: suma más de 12 anotaciones</t>
+          <t>El presidente Kast llama a la “esperanza” a horas de su primera Cuenta Pública, mientras la desaprobación aumenta a un 53%</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/por-enesima-vez-cayo-chawalita-en-cartagena-suma-mas-de-12-anotaciones/</t>
+          <t>https://elpais.com/chile/2026-05-31/el-presidente-kast-llama-a-la-esperanza-a-horas-de-su-primera-cuenta-publica-mientras-la-desaprobacion-aumenta-a-un-53.html</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 10:46 a. m.</t>
+          <t>31/05/2026 06:23 p. m.</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -5871,24 +5827,24 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>Bolívar se blinda para las elecciones con operativos de control y prevención</t>
+          <t>Abelardo de la Espriella, el abogado del diablo que quiere ser presidente de Colombia</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/bolivar-se-blinda-para-las-elecciones-con-operativos-de-control-y-prevencion/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/abelardo-de-la-espriella-abogado-del-diablo-que-quiere-ser-presidente-de-colombia.html</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 10:04 a. m.</t>
+          <t>31/05/2026 06:15 p. m.</t>
         </is>
       </c>
       <c r="B201" s="6" t="inlineStr">
@@ -5898,24 +5854,24 @@
       </c>
       <c r="C201" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D201" s="7" t="inlineStr">
         <is>
-          <t>Mientras jugaba en un casino, sicario le quitó la vida a Johnny Rodríguez</t>
+          <t>Las claves de la primera vuelta en Colombia: el auge ultra, la unidad en la izquierda y la importancia de los votos del centro</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/mientras-jugaba-en-un-casino-sicario-le-quito-la-vida-a-johnny-rodriguez/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/las-claves-de-la-primera-vuelta-en-colombia-el-auge-ultra-unidad-en-la-izquierda-y-los-votos-del-centro-claves.html</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:46 a. m.</t>
+          <t>31/05/2026 06:05 p. m.</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -5925,22 +5881,26 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>Investigan muerte de un recluso en la Penitenciaría El Bosque de Barranquilla</t>
+          <t>La izquierda de Iván Cepeda se ve obligada a remontar para asegurar un segundo Gobierno progresista</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/30/investigan-muerte-de-un-recluso-en-la-penitenciaria-el-bosque-de-barranquilla/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/la-izquierda-de-ivan-cepeda-se-ve-obligada-a-remontar-para-asegurar-un-segundo-gobierno-progresista.html</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="6" t="inlineStr"/>
+      <c r="A203" s="6" t="inlineStr">
+        <is>
+          <t>31/05/2026 06:02 p. m.</t>
+        </is>
+      </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5948,22 +5908,26 @@
       </c>
       <c r="C203" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D203" s="7" t="inlineStr">
         <is>
-          <t>Premios Excelencia El Universal 2026: ya están abiertas las postulaciones</t>
+          <t>De la Espriella y Cepeda se disputarán la presidencia de Colombia mientras Petro cuestiona los resultados</t>
         </is>
       </c>
       <c r="E203" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/cartagena/2026/05/26/premios-excelencia-el-universal-2026-ya-estan-abiertas-las-postulaciones/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/de-la-espriella-y-cepeda-se-disputaran-la-presidencia-de-colombia-con-un-pais-partido-en-dos.html</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="3" t="inlineStr"/>
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>31/05/2026 05:47 p. m.</t>
+        </is>
+      </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5971,24 +5935,24 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>La derecha colombiana se vuelca con el ultra Abelardo de la Espriella y da la espalda a Álvaro Uribe</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/cartagena/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/la-derecha-colombiana-se-vuelca-con-el-ultra-abelardo-de-la-espriella-y-da-la-espalda-a-alvaro-uribe.html</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:50 p. m.</t>
+          <t>31/05/2026 05:00 p. m.</t>
         </is>
       </c>
       <c r="B205" s="6" t="inlineStr">
@@ -5998,24 +5962,24 @@
       </c>
       <c r="C205" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D205" s="7" t="inlineStr">
         <is>
-          <t>Elecciones en Colombia 2026: ¿Puede pedir un nuevo tarjetón si se equivoca? Registraduría responde</t>
+          <t>Las gafas más icónicas de Ray-Ban bajan 80 euros en AliExpress: una oferta imbatible por tiempo limitado</t>
         </is>
       </c>
       <c r="E205" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/29/elecciones-en-colombia-2026-puede-pedir-un-nuevo-tarjeton-si-se-equivoca-registraduria-responde/</t>
+          <t>https://elpais.com/hemeroteca/2026-06-01/</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:44 p. m.</t>
+          <t>31/05/2026 04:29 p. m.</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -6025,24 +5989,24 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>Candidatos presidenciales Colombia 2026: nombres, fotos y principales propuestas</t>
+          <t>Muere bajo custodia del régimen de Ortega el líder indígena nicaragüense Brooklyn Rivera tras casi tres años de arresto político</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/27/candidatos-presidenciales-colombia-2026-nombres-fotos-y-principales-propuestas/</t>
+          <t>https://elpais.com/america/2026-05-31/muere-bajo-custodia-del-regimen-de-ortega-el-lider-indigena-nicaraguense-brooklyn-rivera-tras-casi-tres-anos-de-arresto-politico.html</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:38 p. m.</t>
+          <t>31/05/2026 04:09 p. m.</t>
         </is>
       </c>
       <c r="B207" s="6" t="inlineStr">
@@ -6052,24 +6016,24 @@
       </c>
       <c r="C207" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D207" s="7" t="inlineStr">
         <is>
-          <t>Fecha y hora para elegir al próximo presidente: ¿Cuándo se conocen los resultados oficiales?</t>
+          <t>Almería-Castellón y Málaga-Las Palmas, las semifinales por el ascenso a Primera División</t>
         </is>
       </c>
       <c r="E207" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/28/fecha-y-hora-para-elegir-al-proximo-presidente-cuando-se-conocen-los-resultados-oficiales/</t>
+          <t>https://elpais.com/deportes/futbol/2026-05-31/almeria-castellon-y-malaga-las-palmas-las-semifinales-por-el-ascenso-a-primera-division.html</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:37 p. m.</t>
+          <t>31/05/2026 03:59 p. m.</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -6079,24 +6043,24 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>¿Quién ganaría en segunda vuelta? Escenarios, según últimas encuestas presidenciales de mayo 2026</t>
+          <t>Resultados de las elecciones en Colombia 2026, en vivo | Abelardo de la Espriella hace un llamado a defender la democracia “por la razón o por la fuerza”</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/27/quien-ganaria-en-segunda-vuelta-escenarios-segun-ultimas-encuestas-presidenciales-de-mayo-2026/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/resultados-de-las-elecciones-colombia-2026-en-vivo.html</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:37 p. m.</t>
+          <t>31/05/2026 03:51 p. m.</t>
         </is>
       </c>
       <c r="B209" s="6" t="inlineStr">
@@ -6106,24 +6070,24 @@
       </c>
       <c r="C209" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D209" s="7" t="inlineStr">
         <is>
-          <t>Elecciones presidenciales: horarios de Ley seca y cierre de fronteras</t>
+          <t>Los Javis y Judeline, invitados de La Casita de Bad Bunny en su segundo concierto en Madrid</t>
         </is>
       </c>
       <c r="E209" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/28/elecciones-presidenciales-horarios-de-ley-seca-y-cierre-de-fronteras/</t>
+          <t>https://elpais.com/cultura/2026-05-31/los-javis-y-judeline-invitados-de-la-casita-de-bad-bunny-en-su-segundo-concierto-en-madrid.html</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:36 p. m.</t>
+          <t>31/05/2026 03:48 p. m.</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -6133,24 +6097,24 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>¿Qué cosas puede y no puede hacer un jurado de votación? Registraduría Nacional explica</t>
+          <t>Antonio Ferrera, creativo e histriónico, por la Puerta Grande</t>
         </is>
       </c>
       <c r="E210" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/que-cosas-puede-y-no-puede-hacer-un-jurado-de-votacion-registraduria-nacional-explica/</t>
+          <t>https://elpais.com/cultura/2026-05-31/antonio-ferrera-creativo-e-histrionico-por-la-puerta-grande.html</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:35 p. m.</t>
+          <t>31/05/2026 03:39 p. m.</t>
         </is>
       </c>
       <c r="B211" s="6" t="inlineStr">
@@ -6160,24 +6124,24 @@
       </c>
       <c r="C211" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D211" s="7" t="inlineStr">
         <is>
-          <t>¿Cómo van las elecciones Colombia 2026 en el exterior? Registraduría confirmó fecha para resultados</t>
+          <t>La campaña de ataques de EE UU contra supuestas narcolanchas supera los 200 muertos</t>
         </is>
       </c>
       <c r="E211" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/26/como-van-las-elecciones-colombia-2026-en-el-exterior-registraduria-confirmo-fecha-para-resultados/</t>
+          <t>https://elpais.com/america/2026-05-31/la-campana-de-ataques-de-ee-uu-contra-supuestas-narcolanchas-supera-los-200-muertos.html</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 07:55 p. m.</t>
+          <t>31/05/2026 12:14 p. m.</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -6187,24 +6151,24 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>Pedagogía Electoral: ¿Qué hacer y qué no este domingo de elecciones presidenciales?</t>
+          <t>Diez cosas que los correctores de la Selectividad aconsejan hacer (o evitar) en los exámenes de la PAU</t>
         </is>
       </c>
       <c r="E212" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/31/pedagogia-electoral-que-hacer-y-que-no-este-domingo-de-elecciones-presidenciales/</t>
+          <t>https://elpais.com/educacion/2026-05-31/diez-cosas-que-los-correctores-de-la-selectividad-aconsejan-hacer-o-evitar-en-los-examenes-de-la-pau.html</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 07:50 p. m.</t>
+          <t>31/05/2026 10:33 a. m.</t>
         </is>
       </c>
       <c r="B213" s="6" t="inlineStr">
@@ -6214,24 +6178,24 @@
       </c>
       <c r="C213" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D213" s="7" t="inlineStr">
         <is>
-          <t>Colombia se alista para las elecciones presidenciales 2026</t>
+          <t>Cabeza dura y puños de acero: Rafa Jódar remonta a Carreño y tiene derecho a soñar</t>
         </is>
       </c>
       <c r="E213" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/31/colombia-se-alista-para-las-elecciones-presidenciales-2026/</t>
+          <t>https://elpais.com/deportes/tenis/2026-05-31/rafa-jodar-remonta-a-carreno-y-se-endurece-rumbo-a-cuartos.html</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 06:35 p. m.</t>
+          <t>31/05/2026 08:58 a. m.</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -6241,24 +6205,24 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>Al menos 336 arrestados y un policía herido es el balance de los festejos del PSG en Francia</t>
+          <t>Marco Bezzecchi y Aprilia conquistan por primera vez el GP de Italia</t>
         </is>
       </c>
       <c r="E214" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/al-menos-336-arrestados-y-un-policia-herido-es-el-balance-de-los-festejos-del-psg-en-francia/</t>
+          <t>https://elpais.com/deportes/motociclismo/2026-05-31/marco-bezzecchi-y-aprilia-conquistan-por-primera-vez-el-gp-de-italia.html</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 05:59 p. m.</t>
+          <t>31/05/2026 07:55 a. m.</t>
         </is>
       </c>
       <c r="B215" s="6" t="inlineStr">
@@ -6268,24 +6232,24 @@
       </c>
       <c r="C215" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D215" s="7" t="inlineStr">
         <is>
-          <t>Kevin Viveros salvó al Paranaense y se trepó a la cima de los goleadores del Brasileirao</t>
+          <t>Miles de personas salen a la calle en Madrid contra la política sanitaria de Ayuso: “Ahoga la pública para engordar los seguros privados”</t>
         </is>
       </c>
       <c r="E215" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/kevin-viveros-salvo-al-paranaense-y-se-trepo-a-la-cima-de-los-goleadores-del-brasileirao/</t>
+          <t>https://elpais.com/espana/madrid/2026-05-31/miles-de-personas-salen-a-la-calle-en-madrid-contra-la-politica-sanitaria-de-ayuso-ahoga-la-publica-para-engordar-los-seguros-privados.html</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 04:49 p. m.</t>
+          <t>31/05/2026 07:39 a. m.</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -6295,24 +6259,24 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t>PSG y Aston Villa disputarán la Supercopa de Europa 2026: Fecha y hora</t>
+          <t>Sánchez pide tiempo frente a la oposición “marrullera” que quiere “derribar” al Gobierno con “malas artes”</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/psg-y-aston-villa-disputaran-la-supercopa-de-europa-2026-fecha-y-hora/</t>
+          <t>https://elpais.com/espana/2026-05-31/sanchez-cierra-el-congreso-de-las-juventudes-socialistas-en-madrid.html</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 04:22 p. m.</t>
+          <t>31/05/2026 07:01 a. m.</t>
         </is>
       </c>
       <c r="B217" s="6" t="inlineStr">
@@ -6322,24 +6286,24 @@
       </c>
       <c r="C217" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D217" s="7" t="inlineStr">
         <is>
-          <t>Sociedad de Cirugía Plástica respalda las iniciativas para combatir la medicina ilegal</t>
+          <t>Vuelta de tuerca en el tumor más letal: una terapia dirigida logra duplicar la supervivencia en el cáncer de páncreas</t>
         </is>
       </c>
       <c r="E217" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/sociedad-de-cirugia-plastica-respalda-las-iniciativas-para-combatir-la-medicina-ilegal/</t>
+          <t>https://elpais.com/salud-y-bienestar/2026-05-31/vuelta-de-tuerca-en-el-tumor-mas-letal-una-terapia-dirigida-logra-duplicar-la-supervivencia-en-el-cancer-de-pancreas.html</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 04:06 p. m.</t>
+          <t>31/05/2026 06:46 a. m.</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -6349,24 +6313,24 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>PSG entra en la historia: así quedó el palmarés de la Champions League tras su bicampeonato</t>
+          <t>780 detenidos y más de 200 heridos durante las celebraciones de la victoria del PSG en la Champions</t>
         </is>
       </c>
       <c r="E218" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/psg-entra-en-la-historia-asi-quedo-el-palmares-de-la-champions-league-tras-su-bicampeonato/</t>
+          <t>https://elpais.com/deportes/futbol/2026-05-30/mas-de-un-centenar-de-detenidos-en-paris-en-los-incidentes-producidos-tras-la-victoria-del-psg-en-la-champions.html</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 03:14 p. m.</t>
+          <t>30/05/2026 10:30 p. m.</t>
         </is>
       </c>
       <c r="B219" s="6" t="inlineStr">
@@ -6376,24 +6340,24 @@
       </c>
       <c r="C219" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D219" s="7" t="inlineStr">
         <is>
-          <t>Luis Enrique tras consagrarse Bicampeón de Champions: “Esto sólo se lo había visto hacer al Madrid”</t>
+          <t>‘Cape Fear’ en Apple TV, ‘La casa del dragón’ en HBO Max y otras series recomendadas para junio</t>
         </is>
       </c>
       <c r="E219" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/luis-enrique-tras-consagrarse-bicampeon-de-champions-esto-solo-se-lo-habia-visto-hacer-al-madrid/</t>
+          <t>https://elpais.com/television/series/2026-05-31/cape-fear-en-apple-tv-la-casa-del-dragon-en-hbo-max-y-otras-series-recomendadas-para-junio.html</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 02:24 p. m.</t>
+          <t>30/05/2026 04:51 p. m.</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -6403,24 +6367,24 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D220" s="4" t="inlineStr">
         <is>
-          <t>Pacto Histórico tendrá más de 112,000 testigos en todo el país para las elecciones presidenciales</t>
+          <t>Bad Bunny en Madrid: el alucinante jolgorio del perreo y el amor</t>
         </is>
       </c>
       <c r="E220" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/pacto-historico-tendra-mas-de-112000-testigos-en-todo-el-pais-para-las-elecciones-presidenciales/</t>
+          <t>https://elpais.com/cultura/2026-05-30/bad-bunny-en-madrid-el-alucinante-jolgorio-del-perreo-y-el-amor.html</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 01:35 p. m.</t>
+          <t>31/05/2026 07:58 p. m.</t>
         </is>
       </c>
       <c r="B221" s="6" t="inlineStr">
@@ -6430,24 +6394,24 @@
       </c>
       <c r="C221" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D221" s="7" t="inlineStr">
         <is>
-          <t>“Que ganen las ideas y no las mentiras”: Mindefensa al instalar PMU para evitar riesgos cibernéticos</t>
+          <t>Los totes de la primera vuelta presidencial</t>
         </is>
       </c>
       <c r="E221" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/que-ganen-las-ideas-y-no-las-mentiras-mindefensa-al-instalar-pmu-para-evitar-riesgos-ciberneticos/</t>
+          <t>https://www.elcolombiano.com/multimedia/videos/los-totes-de-la-primera-vuelta-presidencial-FM37191105</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 01:30 p. m.</t>
+          <t>31/05/2026 07:58 p. m.</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -6457,24 +6421,24 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t>Elecciones en Venezuela: excandidato González Urrutia respalda convocar nuevas presidenciales</t>
+          <t>“Hay un desfase que queremos verificar”: Cepeda no acepta la derrota y dice que esperará hasta el escrutinio</t>
         </is>
       </c>
       <c r="E222" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/elecciones-en-venezuela-excandidato-gonzalez-urrutia-respalda-convocar-nuevas-presidenciales/</t>
+          <t>https://www.elcolombiano.com/especiales/elecciones-2026/ivan-cepeda-no-acepta-derrota-resultados-elecciones-2026-OM37193379</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 01:16 p. m.</t>
+          <t>31/05/2026 06:58 p. m.</t>
         </is>
       </c>
       <c r="B223" s="6" t="inlineStr">
@@ -6484,24 +6448,24 @@
       </c>
       <c r="C223" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D223" s="7" t="inlineStr">
         <is>
-          <t>Bogotá fue testigo de la “Feria Gastronómica Europea” con 17 expositores y entrada gratuita</t>
+          <t>“Increíble que Colombia se debata su futuro alrededor de homofobia, machismo e irresponsabilidad”: Oviedo</t>
         </is>
       </c>
       <c r="E223" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/bogota-fue-testigo-de-la-feria-gastronomica-europea-con-17-expositores-y-entrada-gratuita/</t>
+          <t>https://www.elcolombiano.com/colombia/juan-daniel-oviedo-dice-a-quien-apoyar-elecciones-abelardo-cepeda-PN37189431</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 12:25 p. m.</t>
+          <t>31/05/2026 06:58 p. m.</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -6511,24 +6475,24 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>Gobierno instaló PMU nacional para blindar la jornada electoral de este domingo 31 de mayo</t>
+          <t>Así votó Antioquia en primera vuelta: De la Espriella (54%) dobló a Cepeda (25,4%)</t>
         </is>
       </c>
       <c r="E224" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/30/gobierno-instala-pmu-nacional-para-blindar-la-jornada-electoral-de-este-domingo-31-de-mayo/</t>
+          <t>https://www.elcolombiano.com/antioquia/antioquia-elecciones-presidenciales-colombia-2026-primera-vuelta-ON37188723</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:38 p. m.</t>
+          <t>31/05/2026 06:58 p. m.</t>
         </is>
       </c>
       <c r="B225" s="6" t="inlineStr">
@@ -6543,19 +6507,19 @@
       </c>
       <c r="D225" s="7" t="inlineStr">
         <is>
-          <t>Tras revelación de EL COLOMBIANO, investigarán a personal del Hospital Nazareth por video de pedagogía electoral a favor de Cepeda</t>
+          <t>Uribe y su derrota en las presidenciales: se la juega ahora por De la Espriella</t>
         </is>
       </c>
       <c r="E225" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/investigacion-hospital-nazareth-video-ivan-cepeda-IB37149809</t>
+          <t>https://www.elcolombiano.com/especiales/elecciones-2026/uribe-derrota-presidenciales-de-la-espriella-IM37190697</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 06:33 p. m.</t>
+          <t>31/05/2026 06:58 p. m.</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -6570,19 +6534,19 @@
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t>Sindicato de Ecopetrol descarta apoyar a Cepeda y respalda candidatos que impulsen exploración petrolera y fracking</t>
+          <t>Con más de 670.000 votos, De La Espriella barrió en Medellín en la primera vuelta</t>
         </is>
       </c>
       <c r="E226" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/negocios/uso-sindicato-ecopetrol-descarta-ivan-cepeda-fracking-HB37148843</t>
+          <t>https://www.elcolombiano.com/medellin/resultados-medellin-primera-vuelta-elecciones-presidenciales-2026-DN37188975</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 06:33 p. m.</t>
+          <t>31/05/2026 06:58 p. m.</t>
         </is>
       </c>
       <c r="B227" s="6" t="inlineStr">
@@ -6597,19 +6561,19 @@
       </c>
       <c r="D227" s="7" t="inlineStr">
         <is>
-          <t>Polémica por colecta impulsada por sectores del petrismo para transportar votantes: advierten riesgos de trashumancia electoral</t>
+          <t>“Anuncio mi apoyo a Abelardo e invito a que derrotemos a Cepeda”: Paloma Valencia reconoce resultados de primera vuelta</t>
         </is>
       </c>
       <c r="E227" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/politica/polemica-colecta-imprenta-republicana-votos-medellin-LB37149002</t>
+          <t>https://www.elcolombiano.com/colombia/paloma-valencia-apoyo-abelardo-de-la-espriella-segunda-vuelta-junio-2026-ON37188701</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 04:33 p. m.</t>
+          <t>31/05/2026 06:58 p. m.</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -6624,19 +6588,19 @@
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t>Cuerpos de disidentes muertos en Guaviare tenían explosivos para atentar contra la Fuerza Pública</t>
+          <t>Abelardo de la Espriella celebra su paso a segunda vuelta: “Vamos a derrotar la tiranía y el absolutismo”</t>
         </is>
       </c>
       <c r="E228" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/explosivos-en-cuerpos-evacuados-tras-combates-guaviare-farc-JB37145950</t>
+          <t>https://www.elcolombiano.com/colombia/abelardo-discurso-segunda-vuelta-elecciones-2026-celebracion-BN37189448</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 04:33 p. m.</t>
+          <t>31/05/2026 05:58 p. m.</t>
         </is>
       </c>
       <c r="B229" s="6" t="inlineStr">
@@ -6651,19 +6615,19 @@
       </c>
       <c r="D229" s="7" t="inlineStr">
         <is>
-          <t>¿Será la hora de los 9 colombianos en el Mundial? Colombia necesita de sus goles</t>
+          <t>“Este millón de votos decidirá el futuro de nuestro país” ¿Sergio Fajardo tomará partido y anunciará apoyos?</t>
         </is>
       </c>
       <c r="E229" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/especiales/mundial-2026/seleccion-colombia-los-numero-9-mundial-goleadores-luis-suarez-jhon-cordoba-cucho-hernandez-deuda-goles-EB37147663</t>
+          <t>https://www.elcolombiano.com/colombia/sergio-fajardo-elecciones-resultados-discurso-que-dijo-ON37187768</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 03:33 p. m.</t>
+          <t>31/05/2026 05:58 p. m.</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -6678,19 +6642,19 @@
       </c>
       <c r="D230" s="4" t="inlineStr">
         <is>
-          <t>Aficionado del PSG viajó a Bucarest en lugar de Budapest y se perdió la final de la Champions League</t>
+          <t>“¡Inés, una valeriana o algo!”: los divertidos memes que dejó la primera vuelta presidencial</t>
         </is>
       </c>
       <c r="E230" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/deportes/aficionado-psg-error-viaje-final-champions-DB37143642</t>
+          <t>https://www.elcolombiano.com/tendencias/memes-primera-vuelta-presidencial-mayo-2026-ON37182862</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 03:33 p. m.</t>
+          <t>31/05/2026 05:58 p. m.</t>
         </is>
       </c>
       <c r="B231" s="6" t="inlineStr">
@@ -6705,19 +6669,19 @@
       </c>
       <c r="D231" s="7" t="inlineStr">
         <is>
-          <t>La tasa de usura supera el 28% y hará más costosas las compras a crédito para el Mundial</t>
+          <t>Aunque encuestas mostraban a Cepeda ganando, Atlas Intel fue la que más se acercó al éxito de Abelardo</t>
         </is>
       </c>
       <c r="E231" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/negocios/tasa-usura-junio-compras-credito-mundial-EB37144321</t>
+          <t>https://www.elcolombiano.com/colombia/elecciones-2026-resultados-ivan-cepeda-departamentos-LN37183901</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 03:33 p. m.</t>
+          <t>31/05/2026 05:58 p. m.</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -6732,19 +6696,19 @@
       </c>
       <c r="D232" s="4" t="inlineStr">
         <is>
-          <t>Nacional vs. Junior: tres finalistas de 2015 repiten en la serie final del Apertura-2026</t>
+          <t>Hernán Penagos, otro de los grandes ganadores de la jornada electoral</t>
         </is>
       </c>
       <c r="E232" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/deportes/futbol/final-nacional-junior-repitentes-definicion-titulo-2015-liga-betplay-2026-1-PB37144830</t>
+          <t>https://www.elcolombiano.com/especiales/elecciones-2026/ciudadanos-consultar-actas-electorales-votacion-PN37183084</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 03:33 p. m.</t>
+          <t>31/05/2026 05:58 p. m.</t>
         </is>
       </c>
       <c r="B233" s="6" t="inlineStr">
@@ -6759,19 +6723,19 @@
       </c>
       <c r="D233" s="7" t="inlineStr">
         <is>
-          <t>Video | Giro en caso de Alexánder Avendaño, el joven hallado muerto en embalse El Peñol-Guatapé</t>
+          <t>El costo de la derrota: estos son los candidatos que no alcanzaron la reposición de votos en las presidenciales 2026</t>
         </is>
       </c>
       <c r="E233" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/antioquia/video-alexander-avendano-hallado-muerto-embalse-el-penol-guatape-OB37144813</t>
+          <t>https://www.elcolombiano.com/colombia/estos-son-candidatos-no-alcanzan-reposicion-votos-elecciones-2026-BN37184401</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 02:33 p. m.</t>
+          <t>31/05/2026 04:58 p. m.</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -6786,19 +6750,19 @@
       </c>
       <c r="D234" s="4" t="inlineStr">
         <is>
-          <t>PSG hace historia: bicampeón de la Champions tras vencer al Arsenal en una final épica</t>
+          <t>“Transparente y garantista”: la UE tumbó fantasma del fraude y dio balance de las elecciones presidenciales en Colombia</t>
         </is>
       </c>
       <c r="E234" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/deportes/futbol/psg-bicampeon-champions-final-arsenal-resultado-prorroga-penaltis-CB37143221</t>
+          <t>https://www.elcolombiano.com/colombia/union-europea-balance-elecciones-presidenciales-colombia-CC37179865</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 01:33 p. m.</t>
+          <t>31/05/2026 04:58 p. m.</t>
         </is>
       </c>
       <c r="B235" s="6" t="inlineStr">
@@ -6813,19 +6777,19 @@
       </c>
       <c r="D235" s="7" t="inlineStr">
         <is>
-          <t>Prográmese y siga estas recomendaciones para votar el 31 de mayo</t>
+          <t>Cinco capturas por presunta compra de votos y un joven con $110 millones en efectivo: los lunares de la jornada electoral de este 31 de mayo</t>
         </is>
       </c>
       <c r="E235" s="8" t="inlineStr">
         <is>
-          <t>https://qhubomedellin.com/util-para-vos/recomendaciones-para-votar-el-31-de-mayo-presidenciales-EO36920523</t>
+          <t>https://www.elcolombiano.com/colombia/cinco-capturas-compra-votos-joven-110-millones-lunares-jornada-electoral-31-mayo-GN37180688</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 01:33 p. m.</t>
+          <t>31/05/2026 03:58 p. m.</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -6840,19 +6804,19 @@
       </c>
       <c r="D236" s="4" t="inlineStr">
         <is>
-          <t>EN VIDEO: Cohete de Jeff Bezos explotó durante prueba de encendido</t>
+          <t>Conozca a los grandes “cerebros” detrás de las selecciones en el Mundial</t>
         </is>
       </c>
       <c r="E236" s="5" t="inlineStr">
         <is>
-          <t>https://qhubomedellin.com/actualidad/internacional/cohete-de-jeff-bezos-explota-durante-prueba-de-encendido-NH37129271</t>
+          <t>https://www.elcolombiano.com/especiales/mundial-2026/mejores-entrenadores-mundial-2026-ED37169287</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 11:33 a. m.</t>
+          <t>31/05/2026 03:58 p. m.</t>
         </is>
       </c>
       <c r="B237" s="6" t="inlineStr">
@@ -6867,19 +6831,19 @@
       </c>
       <c r="D237" s="7" t="inlineStr">
         <is>
-          <t>Camila Osorio lo dejó todo, pero no pudo avanzar a octavos de final en Roland Garros</t>
+          <t>En video | Análisis de los resultados de las elecciones presidenciales de este 31 de mayo</t>
         </is>
       </c>
       <c r="E237" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/deportes/camila-osorio-kalinskaya-roland-garros-MG37139005</t>
+          <t>https://www.elcolombiano.com/colombia/en-vivo-elecciones-presidenciales-2026-transmision-especial-MC37173249</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 11:33 a. m.</t>
+          <t>31/05/2026 02:58 p. m.</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -6894,19 +6858,19 @@
       </c>
       <c r="D238" s="4" t="inlineStr">
         <is>
-          <t>Exclusivo | Así le hacen campaña a Cepeda los equipos básicos del MinSalud en La Guajira</t>
+          <t>Europa se rinde ante Luis Díaz: top 10 de la Champions y figura absoluta</t>
         </is>
       </c>
       <c r="E238" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/especiales/elecciones-2026/campana-cepeda-los-equipos-basicos-minsalud-en-la-guajira-NG37139848</t>
+          <t>https://www.elcolombiano.com/deportes/futbol/luis-diaz-top-10-champions-bayern-munich-CC37172404</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 10:33 a. m.</t>
+          <t>31/05/2026 01:58 p. m.</t>
         </is>
       </c>
       <c r="B239" s="6" t="inlineStr">
@@ -6921,19 +6885,19 @@
       </c>
       <c r="D239" s="7" t="inlineStr">
         <is>
-          <t>Desde el 3 de junio habrá cierre en la vía San Nicolás–La Ceja, ¿por qué?</t>
+          <t>La MOE alerta por presunta compra de votos en Sucre durante las elecciones presidenciales</t>
         </is>
       </c>
       <c r="E239" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/antioquia/cierres-viales-via-san-nicolas-rionegro-la-ceja-antioquia-BG37138584</t>
+          <t>https://www.elcolombiano.com/especiales/elecciones-2026/moe-alerta-presunta-compra-votos-sucre-durante-elecciones-presidenciales-ID37160109</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 10:33 a. m.</t>
+          <t>31/05/2026 01:58 p. m.</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -6948,19 +6912,19 @@
       </c>
       <c r="D240" s="4" t="inlineStr">
         <is>
-          <t>¡Ojo! Caficultores de Bello tienen hasta este 31 de mayo para acceder a apoyos en cultivos</t>
+          <t>La verdadera razón del último partido de la Selección en Colombia antes del Mundial</t>
         </is>
       </c>
       <c r="E240" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/antioquia/plazo-caficultores-de-bello-antioquia-apoyos-cafetales-FG37138973</t>
+          <t>https://www.elcolombiano.com/especiales/mundial-2026/por-que-seleccion-colombia-juega-con-costa-rica-despedida-al-mundial-estadio-el-campin-hora-donde-ver-MD37166093</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 10:33 a. m.</t>
+          <t>31/05/2026 01:58 p. m.</t>
         </is>
       </c>
       <c r="B241" s="6" t="inlineStr">
@@ -6975,19 +6939,19 @@
       </c>
       <c r="D241" s="7" t="inlineStr">
         <is>
-          <t>Más de 100 exalcaldes de Antioquia anuncian su respaldo a Paloma Valencia y Juan Daniel Oviedo</t>
+          <t>Nacional viaja a Barranquilla para iniciar una final con cuentas pendientes entre los Arias, Diego y Alfredo</t>
         </is>
       </c>
       <c r="E241" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/antioquia/exalcaldes-antioquia-apoyan-paloma-valencia-HG37138834</t>
+          <t>https://www.elcolombiano.com/deportes/futbol/nacional-junior-final-diego-arias-alfredo-arias-rueda-de-prensa-barranquilla-liga-betplay-BD37168018</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 09:33 a. m.</t>
+          <t>31/05/2026 01:58 p. m.</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -7002,19 +6966,19 @@
       </c>
       <c r="D242" s="4" t="inlineStr">
         <is>
-          <t>Gobierno rechaza acuerdo entre Noboa y De la Espriella para eliminar aranceles: “es un injerencia deliberada” en elecciones</t>
+          <t>Procuraduría abrió investigación al ministro Sanguino por posible participación en política a favor de Cepeda</t>
         </is>
       </c>
       <c r="E242" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/petro-arremete-contra-daniel-noboa-bernie-moreno-aranceles-elecciones-PG37137769</t>
+          <t>https://www.elcolombiano.com/colombia/procuraduria-abre-investigacion-mintrabajo-antonio-sanguino-participacion-politica-GD37166220</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 09:33 a. m.</t>
+          <t>31/05/2026 01:58 p. m.</t>
         </is>
       </c>
       <c r="B243" s="6" t="inlineStr">
@@ -7029,19 +6993,19 @@
       </c>
       <c r="D243" s="7" t="inlineStr">
         <is>
-          <t>La exigencia física le pasó factura a David Alonso en Italia que correrá este domingo, ¿cómo y dónde ver la carrera?</t>
+          <t>Alcaldesa de El Paujil, Caquetá, salió con poncho de Cepeda y la Procuraduría la suspendió</t>
         </is>
       </c>
       <c r="E243" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/deportes/david-alonso-moto2-gp-italia-clasificacion-motogp-BG37137644</t>
+          <t>https://www.elcolombiano.com/especiales/elecciones-2026/alcaldesa-el-paujil-suspendida-por-presunta-participacion-politica-ED37166310</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:33 a. m.</t>
+          <t>31/05/2026 12:58 p. m.</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -7056,19 +7020,19 @@
       </c>
       <c r="D244" s="4" t="inlineStr">
         <is>
-          <t>Candidato Santiago Botero fue desalojado de su casa tras impedir el ingreso de su esposa e hijo; tiene una denuncia por violencia intrafamiliar</t>
+          <t>¿Podían Petro, Benedetti y Char mostrar su voto? Expertos explican límites legales para funcionarios públicos y qué les podría pasar</t>
         </is>
       </c>
       <c r="E244" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/santiago-botero-desalojo-casa-cartagena-IG37136842</t>
+          <t>https://www.elcolombiano.com/colombia/podian-petro-benedetti-char-voto-expertos-explican-limites-legales-funcionarios-publicos-MD37165933</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 06:33 a. m.</t>
+          <t>31/05/2026 12:58 p. m.</t>
         </is>
       </c>
       <c r="B245" s="6" t="inlineStr">
@@ -7083,19 +7047,19 @@
       </c>
       <c r="D245" s="7" t="inlineStr">
         <is>
-          <t>A lomo de mula y cruzando ríos: así logró reducir el hambre Antioquia</t>
+          <t>Autoridades reportaron una captura y una sanción contra un testigo electoral durante las votaciones en Medellín</t>
         </is>
       </c>
       <c r="E245" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/antioquia/estrategia-contra-el-hambre-y-la-desnutricion-en-antioquia-JG37134638</t>
+          <t>https://www.elcolombiano.com/medellin/autoridades-reportan-captura-y-sancion-testigo-electoral-votaciones-medellin-GD37164828</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 06:33 a. m.</t>
+          <t>31/05/2026 11:58 a. m.</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -7110,19 +7074,19 @@
       </c>
       <c r="D246" s="4" t="inlineStr">
         <is>
-          <t>Lo que debe saber para votar este domingo: ¿alguno podría ganar en primera vuelta?</t>
+          <t>Kvaratskhelia es elegido como el mejor jugador de la Champions League 25/26</t>
         </is>
       </c>
       <c r="E246" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/especiales/elecciones-2026/elecciones-2026-consulta-puesto-votacion-horarios-primera-vuelta-PG37135864</t>
+          <t>https://www.elcolombiano.com/deportes/futbol/khvicha-kvartaskhelia-psg-paris-champions-mvp-liga-de-campeones-ND37162069</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 05:33 a. m.</t>
+          <t>31/05/2026 10:58 a. m.</t>
         </is>
       </c>
       <c r="B247" s="6" t="inlineStr">
@@ -7137,17 +7101,21 @@
       </c>
       <c r="D247" s="7" t="inlineStr">
         <is>
-          <t>Calor dispara en más de 50% la venta de ventiladores en El Hueco, en Medellín: estos son los más vendidos</t>
+          <t>MinTIC monitorea fallas en redes de telecomunicaciones en 18 departamentos durante las elecciones</t>
         </is>
       </c>
       <c r="E247" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/medellin/calor-medellin-ventas-ventiladores-hueco-KG37131092</t>
+          <t>https://www.elcolombiano.com/colombia/elecciones-hoy-mintic-falla-redes-telecomunicaciones-18-departamentos-LD37160597</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="3" t="inlineStr"/>
+      <c r="A248" s="3" t="inlineStr">
+        <is>
+          <t>31/05/2026 07:58 a. m.</t>
+        </is>
+      </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7160,12 +7128,12 @@
       </c>
       <c r="D248" s="4" t="inlineStr">
         <is>
-          <t>21 municipios en riesgo electoral y récord en testigos: así llega Antioquia a las elecciones</t>
+          <t>Minuto a minuto | Así transcurrió la jornada de elecciones en la que De la Espriella y Cepeda ganaron el paso a segunda vuelta</t>
         </is>
       </c>
       <c r="E248" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/antioquia/antioquia-riesgo-electoral-testigos-preparacion-elecciones-presidenciales-2026-PG37135846</t>
+          <t>https://www.elcolombiano.com/especiales/elecciones-2026/en-vivo-colombia-elecciones-hoy-presidente-minuto-a-minuto-31-de-mayo-CA37156037</t>
         </is>
       </c>
     </row>
@@ -7183,12 +7151,12 @@
       </c>
       <c r="D249" s="7" t="inlineStr">
         <is>
-          <t>Así se enriqueció la novia de Petro</t>
+          <t>Operativo destapa helicóptero con pasado oscuro y motor Rolls-Royce</t>
         </is>
       </c>
       <c r="E249" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/multimedia/videos/asi-se-enriquecio-la-novia-de-petro-IH37120899</t>
+          <t>https://www.elcolombiano.com/colombia/ejercito-incauta-helicoptero-de-la-mafia-NG33717192</t>
         </is>
       </c>
     </row>
@@ -7206,17 +7174,21 @@
       </c>
       <c r="D250" s="4" t="inlineStr">
         <is>
-          <t>Operativo destapa helicóptero con pasado oscuro y motor Rolls-Royce</t>
+          <t>Cuerpos de disidentes muertos en Guaviare tenían explosivos para atentar contra la Fuerza Pública</t>
         </is>
       </c>
       <c r="E250" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/ejercito-incauta-helicoptero-de-la-mafia-NG33717192</t>
+          <t>https://www.elcolombiano.com/colombia/explosivos-en-cuerpos-evacuados-tras-combates-guaviare-farc-JB37145950</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="6" t="inlineStr"/>
+      <c r="A251" s="6" t="inlineStr">
+        <is>
+          <t>31/05/2026 07:44 p. m.</t>
+        </is>
+      </c>
       <c r="B251" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7224,22 +7196,26 @@
       </c>
       <c r="C251" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D251" s="7" t="inlineStr">
         <is>
-          <t>Voraz incendio consumió vivienda en Itagüí y dejó a una familia sin nada</t>
+          <t>Iván Cepeda denuncia injerencia extranjera tras resultados de primera vuelta</t>
         </is>
       </c>
       <c r="E251" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/antioquia/incendio-vivienda-itagui-el-guayabo-una-familia-sin-nada-AG37135775</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/31/ivan-cepeda-denuncia-injerencia-extranjera-tras-resultados-de-primera-vuelta/</t>
         </is>
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="3" t="inlineStr"/>
+      <c r="A252" s="3" t="inlineStr">
+        <is>
+          <t>31/05/2026 07:37 p. m.</t>
+        </is>
+      </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7247,22 +7223,26 @@
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D252" s="4" t="inlineStr">
         <is>
-          <t>¡Le interesa! Este domingo habrá café gratis y descuentos en 120 marcas en Antioquia presentando el certificado de votación</t>
+          <t>Eduardo Verano destacó tranquilidad de la jornada electoral en el Atlántico</t>
         </is>
       </c>
       <c r="E252" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/medellin/descuentos-y-beneficios-en-medellin-por-votar-elecciones-2026-IF37102578</t>
+          <t>https://www.eluniversal.com.co/regional/atlantico/2026/05/31/eduardo-verano-destaco-tranquilidad-de-la-jornada-electoral-en-el-atlantico/</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="6" t="inlineStr"/>
+      <c r="A253" s="6" t="inlineStr">
+        <is>
+          <t>31/05/2026 07:37 p. m.</t>
+        </is>
+      </c>
       <c r="B253" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7270,22 +7250,26 @@
       </c>
       <c r="C253" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D253" s="7" t="inlineStr">
         <is>
-          <t>Maluma habló de las elecciones en Colombia y lanzó inesperada propuesta para llevar votantes</t>
+          <t>Atlántico</t>
         </is>
       </c>
       <c r="E253" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/entretenimiento/maluma-hablo-elecciones-colombia-lanzo-inesperada-propuesta-votantes-IF37100945</t>
+          <t>https://www.eluniversal.com.co/regional/atlantico/</t>
         </is>
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="3" t="inlineStr"/>
+      <c r="A254" s="3" t="inlineStr">
+        <is>
+          <t>31/05/2026 07:23 p. m.</t>
+        </is>
+      </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7293,24 +7277,24 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D254" s="4" t="inlineStr">
         <is>
-          <t>¿Qué proponen en materia de impuestos los candidatos presidenciales punteros?</t>
+          <t>Policía reporta balance de primera vuelta presidencial: 89 capturas y sin alteraciones</t>
         </is>
       </c>
       <c r="E254" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/especiales/elecciones-2026/yo-cuido-la-democracia/propuestas-de-los-candidatos-presidenciales-GB37052040</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/31/policia-reporta-balance-de-primera-vuelta-presidencial-89-capturas-y-sin-alteraciones/</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 08:33 p. m.</t>
+          <t>31/05/2026 07:18 p. m.</t>
         </is>
       </c>
       <c r="B255" s="6" t="inlineStr">
@@ -7320,24 +7304,24 @@
       </c>
       <c r="C255" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D255" s="7" t="inlineStr">
         <is>
-          <t>Elecciones Colombia este domingo 31 de mayo: horarios de votación y recomendaciones para la jornada electoral</t>
+          <t>“Como presidente no acepto los resultados”: Petro reacciona tras la primera vuelta</t>
         </is>
       </c>
       <c r="E255" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/elecciones-colombia-este-domingo-31-de-mayo-horarios-de-votacion-y-recomendaciones-para-la-jornada-electoral/202636/</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/31/como-presidente-no-acepto-los-resultados-petro-reacciona-tras-la-primera-vuelta/</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 08:33 p. m.</t>
+          <t>31/05/2026 07:01 p. m.</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -7347,24 +7331,24 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr">
         <is>
-          <t>Cómo consultar el puesto de votación para las elecciones de 2026; link de consulta</t>
+          <t>Así fue la votación del Atlántico para la primera vuelta presidencial 2026</t>
         </is>
       </c>
       <c r="E256" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/articulo/como-consultar-el-puesto-de-votacion-para-las-elecciones-de-2026-link-de-consulta/202639/</t>
+          <t>https://www.eluniversal.com.co/regional/atlantico/2026/05/31/asi-fue-la-votacion-del-atlantico-para-la-primera-vuelta-presidencial-2026/</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 07:33 p. m.</t>
+          <t>31/05/2026 06:30 p. m.</t>
         </is>
       </c>
       <c r="B257" s="6" t="inlineStr">
@@ -7374,24 +7358,24 @@
       </c>
       <c r="C257" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D257" s="7" t="inlineStr">
         <is>
-          <t>Abelardo de la Espriella habla con Westcol en Barranquilla: “Yo nunca he defendido narcotraficantes, eso es una leyenda urbana”</t>
+          <t>Tras derrota en primer vuelta, Paloma Valencia anunció su apoyo a Abelardo</t>
         </is>
       </c>
       <c r="E257" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/abelardo-de-la-espriella-habla-con-westcol-en-barranquilla-yo-nunca-he-defendido-narcotraficantes-eso-es-una-leyenda-urbana/202659/</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/31/tras-derrota-en-primer-vuelta-paloma-valencia-anuncio-su-apoyo-a-abelardo/</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 06:33 p. m.</t>
+          <t>31/05/2026 06:17 p. m.</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -7401,24 +7385,24 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D258" s="4" t="inlineStr">
         <is>
-          <t>🔴 Elecciones Colombia 2026 EN VIVO | Siga en directo las últimas noticias: horarios de votación de la jornada electoral</t>
+          <t>¿Qué día será la segunda vuelta para elegir al presidente en Colombia?</t>
         </is>
       </c>
       <c r="E258" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/articulo/elecciones-colombia-2026-en-vivo-siga-en-directo-las-ultimas-noticias-horarios-de-votacion-de-la-jornada-electoral/202656/</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/31/que-dia-sera-la-segunda-vuelta-para-elegir-al-presidente-en-colombia/</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 03:33 p. m.</t>
+          <t>31/05/2026 06:16 p. m.</t>
         </is>
       </c>
       <c r="B259" s="6" t="inlineStr">
@@ -7428,24 +7412,24 @@
       </c>
       <c r="C259" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D259" s="7" t="inlineStr">
         <is>
-          <t>VIDEO | Así fue la vibrante tanda de penaltis en la final de la Champions League que dejó al PSG campeón</t>
+          <t>Abelardo de la Espriella se pronuncia tras arrasar en la primera vuelta presidencial de Colombia 2026</t>
         </is>
       </c>
       <c r="E259" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/video-asi-fue-la-vibrante-tanda-de-penaltis-en-la-final-de-la-champions-league-que-dejo-al-psg-campeon/202641/</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/31/abelardo-de-la-espriella-se-pronuncia-tras-arrasar-en-la-primera-vuelta-presidencial-de-colombia-2026/</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 02:33 p. m.</t>
+          <t>31/05/2026 06:05 p. m.</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
@@ -7455,24 +7439,24 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t>PSG retiene su corona de la Champions League: bicampeón ante Arsenal por penales</t>
+          <t>Autoridades revelan cómo transcurrió la jornada electoral en Bolívar</t>
         </is>
       </c>
       <c r="E260" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/psg-retiene-su-corona-de-la-champions-league-bicampeon-ante-arsenal-por-penales/202608/</t>
+          <t>https://www.eluniversal.com.co/regional/bolivar/2026/05/31/autoridades-revelan-como-transcurrio-la-jornada-electoral-en-bolivar/</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 03:33 a. m.</t>
+          <t>31/05/2026 05:02 p. m.</t>
         </is>
       </c>
       <c r="B261" s="6" t="inlineStr">
@@ -7482,24 +7466,24 @@
       </c>
       <c r="C261" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D261" s="7" t="inlineStr">
         <is>
-          <t>“Respetaremos los resultados”: Armando Benedetti explica el blindaje de seguridad del Gobierno Petro para las elecciones del domingo</t>
+          <t>Abelardo de la Espriella e Iván Cepeda disputarán la segunda vuelta presidencial en Colombia</t>
         </is>
       </c>
       <c r="E261" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/respetaremos-los-resultados-armando-benedetti-explica-el-blindaje-de-seguridad-del-gobierno-petro-para-las-elecciones-del-domingo/202659/</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/31/abelardo-de-la-espriella-e-ivan-cepeda-disputaran-la-segunda-vuelta-presidencial-en-colombia/</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 03:33 a. m.</t>
+          <t>31/05/2026 05:02 p. m.</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
@@ -7509,24 +7493,24 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D262" s="4" t="inlineStr">
         <is>
-          <t>“La gente podrá salir libre y en paz”: presidente del CNE, Cristian Quiroz, sobre las elecciones presidenciales</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E262" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/mejor-colombia/elecciones/articulo/la-gente-podra-salir-a-votar-libre-y-en-paz-presidente-del-cne-da-parte-de-tranquilidad-para-las-elecciones-del-domingo/202600/</t>
+          <t>https://www.eluniversal.com.co/colombia/</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 03:33 a. m.</t>
+          <t>31/05/2026 04:37 p. m.</t>
         </is>
       </c>
       <c r="B263" s="6" t="inlineStr">
@@ -7536,24 +7520,24 @@
       </c>
       <c r="C263" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D263" s="7" t="inlineStr">
         <is>
-          <t>La última elección de Sergio Fajardo: el profesor busca la Presidencia reivindicando una forma diferente de hacer política</t>
+          <t>Hallaron sin vida a Marliez Genz, la turista neerlandesa que desapareció en Quindío</t>
         </is>
       </c>
       <c r="E263" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/la-ultima-eleccion-de-sergio-fajardo-el-profesor-busca-la-presidencia-reivindicando-una-forma-diferente-de-hacer-politica/202654/</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/31/hallaron-sin-vida-a-marliez-genz-la-turista-neerlandesa-que-desaparecio-en-quindio/</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 03:33 a. m.</t>
+          <t>31/05/2026 04:33 p. m.</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
@@ -7563,24 +7547,24 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D264" s="4" t="inlineStr">
         <is>
-          <t>Los días difíciles de Paloma Valencia: con un cambio de estrategia, que la llevó a atacar a Abelardo de la Espriella, así llega a las elecciones la candidata del Centro Democrático</t>
+          <t>A ‘Yayo’ lo arrolló una tractomula y murió tras 2 días de estar hospitalizado</t>
         </is>
       </c>
       <c r="E264" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/los-dias-dificiles-de-paloma-valencia-con-un-cambio-de-estrategia-que-la-llevo-a-atacar-a-abelardo-de-la-espriella-asi-llega-a-las-elecciones-la-candidata-del-centro-democratico/202608/</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/31/a-yayo-lo-arrollo-una-tractomula-y-fallecio-tras-2-dias-de-estar-hospitalizad/</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 03:33 a. m.</t>
+          <t>31/05/2026 04:25 p. m.</t>
         </is>
       </c>
       <c r="B265" s="6" t="inlineStr">
@@ -7590,24 +7574,24 @@
       </c>
       <c r="C265" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D265" s="7" t="inlineStr">
         <is>
-          <t>Los contrastes de Aida Quilcué y José Manuel Restrepo: estos son los perfiles de los candidatos a la Vicepresidencia más opcionados</t>
+          <t>FIFA reveló cuál será la prioridad de los árbitros en el Mundial</t>
         </is>
       </c>
       <c r="E265" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/los-contrastes-de-aida-quilcue-y-jose-manuel-restrepo-estos-son-los-perfiles-de-los-candidatos-a-la-vicepresidencia-mas-opcionados/202625/</t>
+          <t>https://www.eluniversal.com.co/deportes/2026/05/31/fifa-revelo-cual-sera-la-prioridad-de-los-arbitros-en-el-mundial/</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 03:33 a. m.</t>
+          <t>31/05/2026 04:25 p. m.</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -7617,24 +7601,24 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D266" s="4" t="inlineStr">
         <is>
-          <t>Abelardo de la Espriella e Iván Cepeda buscan ganar la Presidencia, en primera vuelta, este domingo 31 de mayo: ¿esto se puede resolver ya?</t>
+          <t>Deportes</t>
         </is>
       </c>
       <c r="E266" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/abelardo-de-la-espriella-e-ivan-cepeda-buscan-ganar-la-presidencia-en-primera-vuelta-este-domingo-31-de-mayo-esto-se-puede-resolver-ya/202655/</t>
+          <t>https://www.eluniversal.com.co/deportes/</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 01:33 a. m.</t>
+          <t>31/05/2026 04:11 p. m.</t>
         </is>
       </c>
       <c r="B267" s="6" t="inlineStr">
@@ -7644,24 +7628,24 @@
       </c>
       <c r="C267" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D267" s="7" t="inlineStr">
         <is>
-          <t>“Mi papá estaría orgulloso”, la historia de los 70 años de Pajares Salinas</t>
+          <t>¿Qué le pasó a Diego Guauque? El periodista deberá someterse a una nueva cirugía</t>
         </is>
       </c>
       <c r="E267" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/cultura/articulo/mi-papa-estaria-orgulloso-la-historia-de-los-70-anos-de-pajares-salinas/202601/</t>
+          <t>https://www.eluniversal.com.co/farandula/2026/05/31/que-le-paso-a-diego-guauque-el-periodista-debera-someterse-a-una-nueva-cirugia/</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 01:33 a. m.</t>
+          <t>31/05/2026 03:36 p. m.</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
@@ -7671,24 +7655,24 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr">
         <is>
-          <t>Esta es la lista de urgencias económicas que recibirá el nuevo Gobierno. Diagnóstico de 13 gremios claves</t>
+          <t>Chris Rodríguez llegó de Puerto Rico para operarse y murió en el quirófano</t>
         </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/economia/empresas/articulo/esta-es-la-lista-de-urgencias-economicas-que-recibira-el-nuevo-gobierno-diagnostico-de-13-gremios-claves/202652/</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/31/chris-rodriguez-llego-de-puerto-rico-para-operarse-y-murio-en-el-quirofano/</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 12:33 a. m.</t>
+          <t>31/05/2026 02:33 p. m.</t>
         </is>
       </c>
       <c r="B269" s="6" t="inlineStr">
@@ -7698,22 +7682,26 @@
       </c>
       <c r="C269" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D269" s="7" t="inlineStr">
         <is>
-          <t>El sistema de salud llega enfermo al próximo cuatrienio. ¿Aún tiene remedio?</t>
+          <t>Elian Hernández, el barbero informal que sicario le quitó la vida a balazos</t>
         </is>
       </c>
       <c r="E269" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/articulo/el-sistema-de-salud-llega-enfermo-al-proximo-cuatrienio-aun-tiene-remedio/202650/</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/31/elian-hernandez-el-barbero-informal-que-sicario-le-quito-la-vida-a-balazos/</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="3" t="inlineStr"/>
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t>31/05/2026 02:00 p. m.</t>
+        </is>
+      </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7721,22 +7709,26 @@
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D270" s="4" t="inlineStr">
         <is>
-          <t>Mercados votan antes que las urnas: dólar, deuda y acciones en alerta</t>
+          <t>Él era Virgilio Bueno, el reconocido comerciante que mataron en un ataque de sicarios</t>
         </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/economia/inversionistas/articulo/mercados-votan-antes-que-las-urnas-dolar-deuda-y-acciones-en-alerta/202600/</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/31/el-era-virgilio-bueno-el-reconocido-comerciante-que-murio-en-un-ataque-de-sicarios/</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="6" t="inlineStr"/>
+      <c r="A271" s="6" t="inlineStr">
+        <is>
+          <t>31/05/2026 01:25 p. m.</t>
+        </is>
+      </c>
       <c r="B271" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7744,22 +7736,26 @@
       </c>
       <c r="C271" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D271" s="7" t="inlineStr">
         <is>
-          <t>Julia Loktev habla con Arcadia sobre documentar en tiempo real la tiranía que apagó la prensa libre</t>
+          <t>Video: ¿Qué ocasionó incendio en bodega de reciclaje en el barrio 13 de Junio?</t>
         </is>
       </c>
       <c r="E271" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/cultura/articulo/julia-loktev-habla-con-arcadia-sobre-documentar-la-tirania-y-como-apago-la-prensa-libre-en-tiempo-real/202600/</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/31/video-que-ocasiono-incendio-en-bodega-de-reciclaje-en-el-barrio-13-de-junio/</t>
         </is>
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="3" t="inlineStr"/>
+      <c r="A272" s="3" t="inlineStr">
+        <is>
+          <t>31/05/2026 11:54 a. m.</t>
+        </is>
+      </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7767,22 +7763,26 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D272" s="4" t="inlineStr">
         <is>
-          <t>Balón de letras: diez libros sobre balompié a menos de dos semanas de la cita mundialista</t>
+          <t>‘Quilla’ no votará: cayó con prendas de oro y celulares robados en el Pie de La Popa</t>
         </is>
       </c>
       <c r="E272" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/cultura/articulo/balon-de-letras-diez-libros-sobre-balompie-a-menos-de-dos-semanas-de-la-cita-mundialista/202600/</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/31/quilla-no-votara-cayo-con-prendas-de-oro-y-celulares-robados-en-el-pie-de-la-popa/</t>
         </is>
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="6" t="inlineStr"/>
+      <c r="A273" s="6" t="inlineStr">
+        <is>
+          <t>31/05/2026 11:33 a. m.</t>
+        </is>
+      </c>
       <c r="B273" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7790,17 +7790,17 @@
       </c>
       <c r="C273" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D273" s="7" t="inlineStr">
         <is>
-          <t>‘Marginalia’, de Juan Andrés Arango: Los márgenes como destino</t>
+          <t>Así mataron a alias ‘Chupi’ en Calamar: intentaron linchar a su expareja</t>
         </is>
       </c>
       <c r="E273" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/cultura/libros/articulo/marginalia-de-juan-andres-arango-los-margenes-como-destino/202600/</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/31/asi-mataron-a-alias-chupi-en-calamar-intentaron-lichar-a-su-expareja/</t>
         </is>
       </c>
     </row>
@@ -7813,17 +7813,17 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D274" s="4" t="inlineStr">
         <is>
-          <t>Vitinha, tras el título de Champions League con el PSG, manda contundente mensaje a Colombia: ojo, Lorenzo</t>
+          <t>Premios Excelencia El Universal 2026: ya están abiertas las postulaciones</t>
         </is>
       </c>
       <c r="E274" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/vitinha-tras-el-titulo-de-champions-league-con-el-psg-manda-contundente-mensaje-a-colombia-ojo-lorenzo/202631/</t>
+          <t>https://www.eluniversal.com.co/cartagena/2026/05/26/premios-excelencia-el-universal-2026-ya-estan-abiertas-las-postulaciones/</t>
         </is>
       </c>
     </row>
@@ -7836,22 +7836,26 @@
       </c>
       <c r="C275" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D275" s="7" t="inlineStr">
         <is>
-          <t>El récord negativo que Messi tiene en la historia de los Mundiales: ni siquiera él lo puede cambiar</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="E275" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/el-record-negativo-que-messi-tiene-en-la-historia-de-los-mundiales-ni-siquiera-el-lo-puede-cambiar/202600/</t>
+          <t>https://www.eluniversal.com.co/cartagena/</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="3" t="inlineStr"/>
+      <c r="A276" s="3" t="inlineStr">
+        <is>
+          <t>31/05/2026 06:28 p. m.</t>
+        </is>
+      </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7859,22 +7863,26 @@
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D276" s="4" t="inlineStr">
         <is>
-          <t>Néstor Lorenzo responde si hubo o no dos listas de convocados de Colombia al Mundial: dio su versión</t>
+          <t>Paloma Valencia anuncia su unión a Abelardo de la Espriella: “Seguiré en la batalla para derrotar a Iván Cepeda»</t>
         </is>
       </c>
       <c r="E276" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/nestor-lorenzo-responde-si-hubo-o-no-dos-listas-de-convocados-de-colombia-al-mundial-dio-su-version/202650/</t>
+          <t>https://canaltrece.com.co/noticias/paloma-valencia-anuncia-su-union-a-abelardo-de-la-espriella-seguire-en-la-batalla-para-derrotar-a-ivan-cepeda/</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="6" t="inlineStr"/>
+      <c r="A277" s="6" t="inlineStr">
+        <is>
+          <t>31/05/2026 06:22 p. m.</t>
+        </is>
+      </c>
       <c r="B277" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7882,22 +7890,26 @@
       </c>
       <c r="C277" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D277" s="7" t="inlineStr">
         <is>
-          <t>Luis Díaz habló sobre la capitanía de la Selección Colombia en el Mundial 2026: claro mensaje a James Rodríguez</t>
+          <t>El factor Fajardo: Más de un millón de ciudadanos eligen el centro y definen las llaves del balotaje</t>
         </is>
       </c>
       <c r="E277" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/luis-diaz-hablo-sobre-la-capitania-de-la-seleccion-colombia-en-el-mundial-2026-claro-mensaje-a-james-rodriguez/202642/</t>
+          <t>https://canaltrece.com.co/noticias/el-factor-fajardo-mas-de-un-millon-de-ciudadanos-eligen-el-centro-y-definen-las-llaves-del-balotaje/</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="3" t="inlineStr"/>
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t>31/05/2026 06:16 p. m.</t>
+        </is>
+      </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7905,22 +7917,26 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D278" s="4" t="inlineStr">
         <is>
-          <t>Picante respuesta de Néstor Lorenzo hacia los duros críticos de la Selección Colombia: habló de frente</t>
+          <t>¿Qué regiones votaron por cada candidato?</t>
         </is>
       </c>
       <c r="E278" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/picante-respuesta-de-nestor-lorenzo-hacia-los-duros-criticos-de-la-seleccion-colombia-hablo-de-frente/202636/</t>
+          <t>https://canaltrece.com.co/noticias/que-regiones-votaron-por-cada-candidato/</t>
         </is>
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="6" t="inlineStr"/>
+      <c r="A279" s="6" t="inlineStr">
+        <is>
+          <t>31/05/2026 06:07 p. m.</t>
+        </is>
+      </c>
       <c r="B279" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7928,22 +7944,26 @@
       </c>
       <c r="C279" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D279" s="7" t="inlineStr">
         <is>
-          <t>El compromiso al que llegaron Abelardo de la Espriella y Westcol: “Vas a ver todo lo que muerde el tigre”</t>
+          <t>Fiesta en el Malecón del Río: Abelardo de la Espriella celebra el triunfo en primera vuelta y redefine a la derecha</t>
         </is>
       </c>
       <c r="E279" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/el-compromiso-al-que-llegaron-abelardo-de-la-espriella-y-westcol-vas-a-ver-todo-lo-que-muerde-el-tigre/202627/</t>
+          <t>https://canaltrece.com.co/noticias/fiesta-en-el-malecon-del-rio-abelardo-de-la-espriella-celebra-el-triunfo-en-primera-vuelta-y-redefine-a-la-derecha/</t>
         </is>
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="3" t="inlineStr"/>
+      <c r="A280" s="3" t="inlineStr">
+        <is>
+          <t>31/05/2026 05:59 p. m.</t>
+        </is>
+      </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7951,22 +7971,26 @@
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D280" s="4" t="inlineStr">
         <is>
-          <t>Bernie Moreno envió mensaje previo a las elecciones presidenciales: “El futuro de Colombia puede ser más brillante que nunca”</t>
+          <t>El ajedrez de la segunda vuelta: Las alianzas clave que definirán el futuro de De la Espriella y Cepeda</t>
         </is>
       </c>
       <c r="E280" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/bernie-moreno-envio-mensaje-previo-a-las-elecciones-presidenciales-el-futuro-de-colombia-puede-ser-mas-brillante-que-nunca/202641/</t>
+          <t>https://canaltrece.com.co/noticias/el-ajedrez-de-la-segunda-vuelta-las-alianzas-clave-que-definiran-el-futuro-de-de-la-espriella-y-cepeda/</t>
         </is>
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="6" t="inlineStr"/>
+      <c r="A281" s="6" t="inlineStr">
+        <is>
+          <t>31/05/2026 05:51 p. m.</t>
+        </is>
+      </c>
       <c r="B281" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7974,22 +7998,26 @@
       </c>
       <c r="C281" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D281" s="7" t="inlineStr">
         <is>
-          <t>Abelardo de la Espriella lanza dardo a Petro en entrevista con Westcol: “Es un costeño chimbo”</t>
+          <t>Tensión en el Hotel Tequendama: Campaña de Iván Cepeda suspende transmisión en vivo ante resultados adversos</t>
         </is>
       </c>
       <c r="E281" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/abelardo-de-la-espriella-lanza-dardo-a-petro-en-entrevista-con-westcol-es-un-costeno-chimbo/202633/</t>
+          <t>https://canaltrece.com.co/noticias/tension-en-el-hotel-tequendama-campana-de-ivan-cepeda-suspende-transmision-en-vivo-ante-resultados-adversos/</t>
         </is>
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="3" t="inlineStr"/>
+      <c r="A282" s="3" t="inlineStr">
+        <is>
+          <t>31/05/2026 05:19 p. m.</t>
+        </is>
+      </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7997,22 +8025,26 @@
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D282" s="4" t="inlineStr">
         <is>
-          <t>Alejandro Char respondió a los señalamientos de Gustavo Petro: “Es triste verlo salir de la Casa de Nariño destilando odio”</t>
+          <t>De la Espriella Y Cepeda pasan a segunda vuelta presidencial en Colombia</t>
         </is>
       </c>
       <c r="E282" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/alejandro-char-respondio-a-los-senalamientos-de-gustavo-petro-es-triste-verlo-salir-de-la-casa-de-narino-destilando-odio/202610/</t>
+          <t>https://canaltrece.com.co/noticias/de-la-espriella-y-cepeda-pasan-a-segunda-vuelta-presidencial-en-colombia/</t>
         </is>
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="6" t="inlineStr"/>
+      <c r="A283" s="6" t="inlineStr">
+        <is>
+          <t>31/05/2026 04:28 p. m.</t>
+        </is>
+      </c>
       <c r="B283" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -8020,22 +8052,26 @@
       </c>
       <c r="C283" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D283" s="7" t="inlineStr">
         <is>
-          <t>Así encontraron el cuerpo de joven que murió en aguas del embalse El Peñol-Guatapé: “Logramos la recuperación”</t>
+          <t>Primeros boletines de la Registraduría: Iván Cepeda y Abelardo de la Espriella lideran los resultados presidenciales</t>
         </is>
       </c>
       <c r="E283" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/medellin/articulo/asi-encontraron-el-cuerpo-de-joven-que-murio-en-aguas-del-embalse-el-penol-guatape-logramos-la-recuperacion/202605/</t>
+          <t>https://canaltrece.com.co/noticias/primeros-boletines-de-la-registraduria-ivan-cepeda-y-abelardo-de-la-espriella-lideran-los-resultados-presidenciales/</t>
         </is>
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="3" t="inlineStr"/>
+      <c r="A284" s="3" t="inlineStr">
+        <is>
+          <t>31/05/2026 04:17 p. m.</t>
+        </is>
+      </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -8043,24 +8079,24 @@
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>Procurador Gregorio Eljach entregó un parte de tranquilidad para las elecciones e invitó a los colombianos a votar temprano</t>
+          <t>Balance de la Registraduría a las 4:00 p.m.: Así avanza el preconteo y la digitalización de los formularios E-14</t>
         </is>
       </c>
       <c r="E284" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/articulo/procurador-gregorio-eljach-entrego-un-parte-de-tranquilidad-para-las-elecciones-e-invito-a-los-colombianos-a-votar-temprano/202652/</t>
+          <t>https://canaltrece.com.co/noticias/balance-de-la-registraduria-a-las-400-p-m-asi-avanza-el-preconteo-y-la-digitalizacion-de-los-formularios-e-14/</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 07:50 p. m.</t>
+          <t>31/05/2026 03:55 p. m.</t>
         </is>
       </c>
       <c r="B285" s="6" t="inlineStr">
@@ -8070,24 +8106,24 @@
       </c>
       <c r="C285" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D285" s="7" t="inlineStr">
         <is>
-          <t>Resultado Culona Noche: número ganador de hoy sábado 30 de mayo de 2026</t>
+          <t>Elecciones 2026 en vivo: resultados y minuto a minuto del preconteo</t>
         </is>
       </c>
       <c r="E285" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/loterias/2026/05/30/resultado-culona-noche-numero-ganador-de-hoy-sabado-30-de-mayo-de-2026/</t>
+          <t>https://canaltrece.com.co/noticias/elecciones-2026-en-vivo-resultados-y-minuto-a-minuto-del-preconteo/</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 07:50 p. m.</t>
+          <t>31/05/2026 02:40 p. m.</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
@@ -8097,24 +8133,24 @@
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>Loterias</t>
+          <t>El fenómeno ‘Polymarket’: Se disparan las apuestas que dan a Abelardo de la Espriella como favorito a la Presidencia</t>
         </is>
       </c>
       <c r="E286" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/loterias/</t>
+          <t>https://canaltrece.com.co/noticias/el-fenomeno-polymarket-se-disparan-las-apuestas-que-dan-a-abelardo-de-la-espriella-como-favorito-a-la-presidencia/</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 07:22 p. m.</t>
+          <t>31/05/2026 01:56 p. m.</t>
         </is>
       </c>
       <c r="B287" s="6" t="inlineStr">
@@ -8124,24 +8160,24 @@
       </c>
       <c r="C287" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D287" s="7" t="inlineStr">
         <is>
-          <t>OEA hará seguimiento a denuncias contra Petro por participación en política</t>
+          <t>Formulario E-14: cómo consultar las actas de las elecciones 2026</t>
         </is>
       </c>
       <c r="E287" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/30/oea-hara-seguimiento-a-denuncias-contra-petro-por-participacion-en-politica/</t>
+          <t>https://canaltrece.com.co/noticias/formulario-e-14-como-consultar-las-actas-de-las-elecciones-2026/</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 07:22 p. m.</t>
+          <t>31/05/2026 01:48 p. m.</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
@@ -8151,24 +8187,24 @@
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>¿Cuándo se posesiona el próximo presidente de Colombia en 2026?</t>
         </is>
       </c>
       <c r="E288" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/</t>
+          <t>https://canaltrece.com.co/noticias/cuando-se-posesiona-el-proximo-presidente-de-colombia-en-2026/</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 07:01 p. m.</t>
+          <t>31/05/2026 01:41 p. m.</t>
         </is>
       </c>
       <c r="B289" s="6" t="inlineStr">
@@ -8178,24 +8214,24 @@
       </c>
       <c r="C289" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D289" s="7" t="inlineStr">
         <is>
-          <t>“Nadie vende su voto”: el mensaje de Petro a horas de las elecciones presidenciales</t>
+          <t>Voto en blanco en Colombia: ¿qué pasa si gana en presidenciales?</t>
         </is>
       </c>
       <c r="E289" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/30/nadie-vende-su-voto-el-mensaje-de-petro-a-horas-de-las-elecciones-presidenciales/</t>
+          <t>https://canaltrece.com.co/noticias/voto-en-blanco-en-colombia-que-pasa-si-gana-en-presidenciales/</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 06:06 p. m.</t>
+          <t>31/05/2026 01:35 p. m.</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -8205,24 +8241,24 @@
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>Contratista de Ecopetrol resultó herido tras ataque a bala en Tibú, Norte de Santander</t>
+          <t>Certificado electoral 2026: beneficios y cómo pedir copia si lo pierde</t>
         </is>
       </c>
       <c r="E290" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/judicial/2026/05/30/contratista-de-ecopetrol-resulto-herido-tras-ataque-a-bala-en-tibu-norte-de-santander/</t>
+          <t>https://canaltrece.com.co/noticias/certificado-electoral-2026-beneficios-y-como-pedir-copia-si-lo-pierde/</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 06:06 p. m.</t>
+          <t>31/05/2026 11:49 a. m.</t>
         </is>
       </c>
       <c r="B291" s="6" t="inlineStr">
@@ -8232,24 +8268,24 @@
       </c>
       <c r="C291" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D291" s="7" t="inlineStr">
         <is>
-          <t>Judicial</t>
+          <t>Delitos electorales 2026: cómo denunciar compra de votos o presiones</t>
         </is>
       </c>
       <c r="E291" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/judicial/</t>
+          <t>https://canaltrece.com.co/noticias/delitos-electorales-2026-como-denunciar-compra-de-votos-o-presiones/</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 04:55 p. m.</t>
+          <t>31/05/2026 11:44 a. m.</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
@@ -8259,24 +8295,24 @@
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>Candidato Santiago Botero respondió luego de la orden de desalojo en su contra en caso de violencia intrafamiliar</t>
+          <t>Elecciones 2026: ¿qué hacer si no aparece en el puesto de votación?</t>
         </is>
       </c>
       <c r="E292" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/30/candidato-santiago-botero-respondio-luego-de-la-orden-de-desalojo-en-su-contra-en-caso-de-violencia-intrafamiliar/</t>
+          <t>https://canaltrece.com.co/editorial/elecciones-2026-que-hacer-si-no-aparece-en-el-puesto-de-votacion/</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 04:19 p. m.</t>
+          <t>31/05/2026 11:40 a. m.</t>
         </is>
       </c>
       <c r="B293" s="6" t="inlineStr">
@@ -8286,24 +8322,24 @@
       </c>
       <c r="C293" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D293" s="7" t="inlineStr">
         <is>
-          <t>Denuncian que equipos básicos de Minsalud le estarían haciendo campaña a Cepeda en La Guajira</t>
+          <t>Elecciones 2026: ¿se puede votar con contraseña en Colombia?</t>
         </is>
       </c>
       <c r="E293" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/30/denuncian-que-equipos-basicos-de-minsalud-le-estarian-haciendo-campana-a-cepeda-en-la-guajira/</t>
+          <t>https://canaltrece.com.co/noticias/elecciones-2026-se-puede-votar-con-contrasena-en-colombia/</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 04:03 p. m.</t>
+          <t>31/05/2026 11:36 a. m.</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
@@ -8313,24 +8349,24 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>Activan Puesto de Mando Unificado para vigilar las elecciones presidenciales</t>
+          <t>Elecciones 2026: ¿qué pasa si llega a votar después de las 4:00 p. m.?</t>
         </is>
       </c>
       <c r="E294" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/30/activan-puesto-de-mando-unificado-para-vigilar-las-elecciones-presidenciales/</t>
+          <t>https://canaltrece.com.co/editorial/elecciones-2026-que-pasa-si-llega-a-votar-despues-de-las-400-p-m/</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 02:54 p. m.</t>
+          <t>31/05/2026 11:33 a. m.</t>
         </is>
       </c>
       <c r="B295" s="6" t="inlineStr">
@@ -8340,24 +8376,24 @@
       </c>
       <c r="C295" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D295" s="7" t="inlineStr">
         <is>
-          <t>“Ahóguenlo” revelan video que muestra los últimos minutos de Alexander Avendaño</t>
+          <t>Elecciones 2026: ¿hasta qué hora se puede votar hoy en Colombia?</t>
         </is>
       </c>
       <c r="E295" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/30/ahoguenlo-revelan-video-que-muestra-los-ultimos-minutos-de-alexander-avendano/</t>
+          <t>https://canaltrece.com.co/noticias/elecciones-2026-hasta-que-hora-se-puede-votar-hoy-en-colombia/</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 02:19 p. m.</t>
+          <t>31/05/2026 11:27 a. m.</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
@@ -8367,24 +8403,24 @@
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>Mindefensa alerta que varios cadáveres recuperados tras combates en Guaviare tenían explosivos</t>
+          <t>Elecciones 2026: más de 41 millones de colombianos pueden votar</t>
         </is>
       </c>
       <c r="E296" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/30/mindefensa-alerta-que-varios-cadaveres-recuperados-tras-combates-en-guaviare-tenian-explosivos/</t>
+          <t>https://canaltrece.com.co/noticias/elecciones-2026-mas-de-41-millones-de-colombianos-pueden-votar/</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 01:27 p. m.</t>
+          <t>31/05/2026 10:55 a. m.</t>
         </is>
       </c>
       <c r="B297" s="6" t="inlineStr">
@@ -8394,24 +8430,24 @@
       </c>
       <c r="C297" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D297" s="7" t="inlineStr">
         <is>
-          <t>Cárcel para médico de Bogotá por presunto abuso de dos niñas en las consultas</t>
+          <t>Elecciones 2026: 408.000 uniformados custodian puestos de votación</t>
         </is>
       </c>
       <c r="E297" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/30/carcel-para-medico-de-bogota-por-presunto-abuso-de-dos-ninas-en-las-consultas/</t>
+          <t>https://canaltrece.com.co/noticias/elecciones-2026-408-000-uniformados-custodian-puestos-de-votacion/</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 01:23 p. m.</t>
+          <t>31/05/2026 10:08 a. m.</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
@@ -8421,24 +8457,24 @@
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D298" s="4" t="inlineStr">
         <is>
-          <t>Gobierno negocia con Calarcá desde 2023 pero no tiene forma de contactarlo</t>
+          <t>Presidente Petro pide voto libre y mayor control estatal en los escrutinios</t>
         </is>
       </c>
       <c r="E298" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/30/gobierno-negocia-con-calarca-desde-2023-pero-no-tiene-forma-de-contactarlo/</t>
+          <t>https://canaltrece.com.co/noticias/presidente-petro-pide-voto-libre-y-mayor-control-estatal-en-los-escrutinios/</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 10:43 a. m.</t>
+          <t>31/05/2026 09:30 a. m.</t>
         </is>
       </c>
       <c r="B299" s="6" t="inlineStr">
@@ -8448,24 +8484,24 @@
       </c>
       <c r="C299" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D299" s="7" t="inlineStr">
         <is>
-          <t>Cancillería desmiente a Noboa y afirma que CAN obligó retiro de aranceles a Colombia</t>
+          <t>Elecciones 2026: cierres viales y desvíos en Bogotá este 31 de mayo</t>
         </is>
       </c>
       <c r="E299" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/30/cancilleria-desmiente-a-noboa-y-afirma-que-can-obligo-retiro-de-aranceles-a-colombia/</t>
+          <t>https://canaltrece.com.co/noticias/elecciones-2026-cierres-viales-y-desvios-en-bogota-este-31-de-mayo/</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 05:26 p. m.</t>
+          <t>31/05/2026 08:28 a. m.</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
@@ -8475,26 +8511,22 @@
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D300" s="4" t="inlineStr">
         <is>
-          <t>Cepeda llega a primera vuelta sin revelar sus asesores económicos</t>
+          <t>Clima para votar en elecciones 2026: lluvias en varias regiones del país</t>
         </is>
       </c>
       <c r="E300" s="5" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/cepeda-llega-a-primera-vuelta-sin-revelar-sus-asesores-economicos/</t>
+          <t>https://canaltrece.com.co/noticias/clima-para-votar-en-elecciones-2026-lluvias-en-varias-regiones-del-pais/</t>
         </is>
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="6" t="inlineStr">
-        <is>
-          <t>30/05/2026 01:54 p. m.</t>
-        </is>
-      </c>
+      <c r="A301" s="6" t="inlineStr"/>
       <c r="B301" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -8502,26 +8534,22 @@
       </c>
       <c r="C301" s="6" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D301" s="7" t="inlineStr">
         <is>
-          <t>El último acto de campaña de Paloma será una entrevista con Mr Stiven TC</t>
+          <t>Abelardo de la Espriella responde desde un buque blindado: «No permitiremos que Petro y Cepeda se roben las elecciones»</t>
         </is>
       </c>
       <c r="E301" s="8" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/el-ultimo-acto-de-campana-de-paloma-sera-una-entrevista-con-mr-stiven-tc/</t>
+          <t>https://canaltrece.com.co/noticias/abelardo-de-la-espriella-responde-desde-un-buque-blindado-no-permitiremos-que-petro-y-cepeda-se-roben-las-elecciones/</t>
         </is>
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="3" t="inlineStr">
-        <is>
-          <t>30/05/2026 01:31 p. m.</t>
-        </is>
-      </c>
+      <c r="A302" s="3" t="inlineStr"/>
       <c r="B302" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -8529,26 +8557,22 @@
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D302" s="4" t="inlineStr">
         <is>
-          <t>Aumentó la violencia por conflicto armado antes de elecciones: Cerac</t>
+          <t>Iván Cepeda rompe el silencio: Congela aceptación de resultados, tilda a De la Espriella de «fascismo mafioso» y suma apoyos clave</t>
         </is>
       </c>
       <c r="E302" s="5" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/aumento-la-violencia-por-conflicto-armado-antes-de-elecciones-cerac/</t>
+          <t>https://canaltrece.com.co/noticias/ivan-cepeda-rompe-el-silencio-congela-aceptacion-de-resultados-tilda-a-de-la-espriella-de-fascismo-mafioso-y-suma-apoyos-clave/</t>
         </is>
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="6" t="inlineStr">
-        <is>
-          <t>30/05/2026 11:21 a. m.</t>
-        </is>
-      </c>
+      <c r="A303" s="6" t="inlineStr"/>
       <c r="B303" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -8556,26 +8580,22 @@
       </c>
       <c r="C303" s="6" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D303" s="7" t="inlineStr">
         <is>
-          <t>La Cancillería anuncia que derogará medidas económicas contra Ecuador</t>
+          <t>Presidente Petro no acepta el preconteo y denuncia graves irregularidades en el software electoral</t>
         </is>
       </c>
       <c r="E303" s="8" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/la-cancilleria-anuncia-que-derogara-medidas-economicas-contra-ecuador/</t>
+          <t>https://canaltrece.com.co/noticias/presidente-petro-no-acepta-el-preconteo-y-denuncia-graves-irregularidades-en-el-software-electoral/</t>
         </is>
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="3" t="inlineStr">
-        <is>
-          <t>30/05/2026 09:52 a. m.</t>
-        </is>
-      </c>
+      <c r="A304" s="3" t="inlineStr"/>
       <c r="B304" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -8583,26 +8603,22 @@
       </c>
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D304" s="4" t="inlineStr">
         <is>
-          <t>“No se trata de si yo tengo un jaguar y otro tiene un tigre”: Petro</t>
+          <t>Jornada histórica y pacífica en Colombia: Más de 24 millones de ciudadanos votaron y definieron el balotaje para el 21 de junio</t>
         </is>
       </c>
       <c r="E304" s="5" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/no-se-trata-de-si-yo-tengo-un-jaguar-y-otro-tiene-un-tigre-petro/</t>
+          <t>https://canaltrece.com.co/noticias/jornada-historica-y-pacifica-en-colombia-mas-de-24-millones-de-ciudadanos-votaron-y-definieron-el-balotaje-para-el-21-de-junio/</t>
         </is>
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="6" t="inlineStr">
-        <is>
-          <t>30/05/2026 09:00 a. m.</t>
-        </is>
-      </c>
+      <c r="A305" s="6" t="inlineStr"/>
       <c r="B305" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -8610,400 +8626,22 @@
       </c>
       <c r="C305" s="6" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>Canal Trece</t>
         </is>
       </c>
       <c r="D305" s="7" t="inlineStr">
         <is>
-          <t>Caquetá vota bajo presión armada y cansado de la extorsión y otras noticias</t>
+          <t>Claudia López rompe el silencio: Pide a Cepeda asumir el liderazgo de su campaña ante el temor de una presidencia de De la Espriella</t>
         </is>
       </c>
       <c r="E305" s="8" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/caqueta-vota-bajo-presion-armada-y-cansado-de-la-extorsion-y-otras-noticias/</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" s="3" t="inlineStr">
-        <is>
-          <t>29/05/2026 07:43 p. m.</t>
-        </is>
-      </c>
-      <c r="B306" s="3" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C306" s="3" t="inlineStr">
-        <is>
-          <t>La Silla Vacía</t>
-        </is>
-      </c>
-      <c r="D306" s="4" t="inlineStr">
-        <is>
-          <t>Duerma informado con las claves de este 29 de mayo de 2026</t>
-        </is>
-      </c>
-      <c r="E306" s="5" t="inlineStr">
-        <is>
-          <t>https://www.lasillavacia.com/en-vivo/duerma-informado-con-las-claves-de-este-29-de-mayo-de-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="6" t="inlineStr">
-        <is>
-          <t>29/05/2026 07:40 p. m.</t>
-        </is>
-      </c>
-      <c r="B307" s="6" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C307" s="6" t="inlineStr">
-        <is>
-          <t>La Silla Vacía</t>
-        </is>
-      </c>
-      <c r="D307" s="7" t="inlineStr">
-        <is>
-          <t>Noboa habla con Abelardo y anuncia que quitará aranceles el 1 de junio</t>
-        </is>
-      </c>
-      <c r="E307" s="8" t="inlineStr">
-        <is>
-          <t>https://www.lasillavacia.com/en-vivo/noboa-habla-con-abelardo-y-anuncia-que-quitara-aranceles-el-1-de-junio/</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="3" t="inlineStr">
-        <is>
-          <t>29/05/2026 06:48 p. m.</t>
-        </is>
-      </c>
-      <c r="B308" s="3" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C308" s="3" t="inlineStr">
-        <is>
-          <t>La Silla Vacía</t>
-        </is>
-      </c>
-      <c r="D308" s="4" t="inlineStr">
-        <is>
-          <t>Dane: Desempleo en Colombia se mantuvo en 8,8% en abril de 2026</t>
-        </is>
-      </c>
-      <c r="E308" s="5" t="inlineStr">
-        <is>
-          <t>https://www.lasillavacia.com/en-vivo/dane-desempleo-en-colombia-se-mantuvo-en-88-en-abril-de-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" s="6" t="inlineStr">
-        <is>
-          <t>29/05/2026 05:57 p. m.</t>
-        </is>
-      </c>
-      <c r="B309" s="6" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C309" s="6" t="inlineStr">
-        <is>
-          <t>La Silla Vacía</t>
-        </is>
-      </c>
-      <c r="D309" s="7" t="inlineStr">
-        <is>
-          <t>ELN liberó a Iván Alfredo Guzmán, hijo del exalcalde de Tame, Arauca</t>
-        </is>
-      </c>
-      <c r="E309" s="8" t="inlineStr">
-        <is>
-          <t>https://www.lasillavacia.com/en-vivo/eln-libero-a-ivan-alfredo-guzman-hijo-del-exalcalde-de-tame-arauca/</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="3" t="inlineStr">
-        <is>
-          <t>29/05/2026 05:19 p. m.</t>
-        </is>
-      </c>
-      <c r="B310" s="3" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C310" s="3" t="inlineStr">
-        <is>
-          <t>La Silla Vacía</t>
-        </is>
-      </c>
-      <c r="D310" s="4" t="inlineStr">
-        <is>
-          <t>Petro se reunirá con Zohran Mamdani, el alcalde de Nueva York</t>
-        </is>
-      </c>
-      <c r="E310" s="5" t="inlineStr">
-        <is>
-          <t>https://www.lasillavacia.com/en-vivo/petro-se-reunira-con-zohran-mamdani-el-alcalde-de-nueva-york/</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="6" t="inlineStr">
-        <is>
-          <t>29/05/2026 04:26 p. m.</t>
-        </is>
-      </c>
-      <c r="B311" s="6" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C311" s="6" t="inlineStr">
-        <is>
-          <t>La Silla Vacía</t>
-        </is>
-      </c>
-      <c r="D311" s="7" t="inlineStr">
-        <is>
-          <t>Recuperados 48 cuerpos tras combates entre Mordisco y Calarcá en Guaviare</t>
-        </is>
-      </c>
-      <c r="E311" s="8" t="inlineStr">
-        <is>
-          <t>https://www.lasillavacia.com/en-vivo/recuperados-48-cuerpos-tras-combates-entre-mordisco-y-calarca-en-guaviare/</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="3" t="inlineStr">
-        <is>
-          <t>29/05/2026 03:36 p. m.</t>
-        </is>
-      </c>
-      <c r="B312" s="3" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C312" s="3" t="inlineStr">
-        <is>
-          <t>La Silla Vacía</t>
-        </is>
-      </c>
-      <c r="D312" s="4" t="inlineStr">
-        <is>
-          <t>Polymarket paga publicaciones a favor de Abelardo y políticos de derecha</t>
-        </is>
-      </c>
-      <c r="E312" s="5" t="inlineStr">
-        <is>
-          <t>https://www.lasillavacia.com/en-vivo/polymarket-paga-publicaciones-a-favor-de-abelardo-y-politicos-de-derecha/</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="6" t="inlineStr">
-        <is>
-          <t>29/05/2026 02:23 p. m.</t>
-        </is>
-      </c>
-      <c r="B313" s="6" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C313" s="6" t="inlineStr">
-        <is>
-          <t>La Silla Vacía</t>
-        </is>
-      </c>
-      <c r="D313" s="7" t="inlineStr">
-        <is>
-          <t>Tras salida de El Tiempo, Jineth Bedoya denuncia a Gabriel Meluk por acoso</t>
-        </is>
-      </c>
-      <c r="E313" s="8" t="inlineStr">
-        <is>
-          <t>https://www.lasillavacia.com/en-vivo/tras-salida-de-el-tiempo-jineth-bedoya-denuncia-a-gabriel-meluk-por-acoso/</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="3" t="inlineStr">
-        <is>
-          <t>29/05/2026 01:50 p. m.</t>
-        </is>
-      </c>
-      <c r="B314" s="3" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C314" s="3" t="inlineStr">
-        <is>
-          <t>La Silla Vacía</t>
-        </is>
-      </c>
-      <c r="D314" s="4" t="inlineStr">
-        <is>
-          <t>Diario de Campaña: la recta final hacia primera vuelta</t>
-        </is>
-      </c>
-      <c r="E314" s="5" t="inlineStr">
-        <is>
-          <t>https://www.lasillavacia.com/en-vivo/diario-de-campana-asi-esta-la-recta-final-hacia-primera-vuelta/</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="6" t="inlineStr">
-        <is>
-          <t>29/05/2026 01:36 p. m.</t>
-        </is>
-      </c>
-      <c r="B315" s="6" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C315" s="6" t="inlineStr">
-        <is>
-          <t>La Silla Vacía</t>
-        </is>
-      </c>
-      <c r="D315" s="7" t="inlineStr">
-        <is>
-          <t>“Nos quitarán las oportunidades de vida”: Petro en el Caribe</t>
-        </is>
-      </c>
-      <c r="E315" s="8" t="inlineStr">
-        <is>
-          <t>https://www.lasillavacia.com/en-vivo/nos-quitaran-las-oportunidades-de-vida-petro-en-el-caribe/</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="3" t="inlineStr">
-        <is>
-          <t>29/05/2026 12:24 p. m.</t>
-        </is>
-      </c>
-      <c r="B316" s="3" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C316" s="3" t="inlineStr">
-        <is>
-          <t>La Silla Vacía</t>
-        </is>
-      </c>
-      <c r="D316" s="4" t="inlineStr">
-        <is>
-          <t>Termina inscripción de testigos con el Centro Democrático a la cabeza</t>
-        </is>
-      </c>
-      <c r="E316" s="5" t="inlineStr">
-        <is>
-          <t>https://www.lasillavacia.com/en-vivo/termina-inscripcion-de-testigos-con-el-centro-democratico-a-la-cabeza/</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="6" t="inlineStr">
-        <is>
-          <t>29/05/2026 11:06 a. m.</t>
-        </is>
-      </c>
-      <c r="B317" s="6" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C317" s="6" t="inlineStr">
-        <is>
-          <t>La Silla Vacía</t>
-        </is>
-      </c>
-      <c r="D317" s="7" t="inlineStr">
-        <is>
-          <t>Partidos reiteran a sus bases moverse por Paloma y Oviedo</t>
-        </is>
-      </c>
-      <c r="E317" s="8" t="inlineStr">
-        <is>
-          <t>https://www.lasillavacia.com/en-vivo/partidos-reiteran-a-sus-bases-moverse-por-paloma-y-oviedo/</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" s="3" t="inlineStr">
-        <is>
-          <t>29/05/2026 10:16 a. m.</t>
-        </is>
-      </c>
-      <c r="B318" s="3" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C318" s="3" t="inlineStr">
-        <is>
-          <t>La Silla Vacía</t>
-        </is>
-      </c>
-      <c r="D318" s="4" t="inlineStr">
-        <is>
-          <t>ABC de la Democracia: aprenda en 90 minutos</t>
-        </is>
-      </c>
-      <c r="E318" s="5" t="inlineStr">
-        <is>
-          <t>https://www.lasillavacia.com/en-vivo/abc-de-la-democracia-aprenda-en-90-minutos/</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="6" t="inlineStr">
-        <is>
-          <t>29/05/2026 09:48 a. m.</t>
-        </is>
-      </c>
-      <c r="B319" s="6" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C319" s="6" t="inlineStr">
-        <is>
-          <t>La Silla Vacía</t>
-        </is>
-      </c>
-      <c r="D319" s="7" t="inlineStr">
-        <is>
-          <t>Pese a orden de Petro, Óscar Muñoz sigue en la embajada de Guyana</t>
-        </is>
-      </c>
-      <c r="E319" s="8" t="inlineStr">
-        <is>
-          <t>https://www.lasillavacia.com/en-vivo/pese-a-orden-de-petro-oscar-munoz-sigue-en-la-embajada-de-guyana/</t>
+          <t>https://canaltrece.com.co/noticias/claudia-lopez-rompe-el-silencio-pide-a-cepeda-asumir-el-liderazgo-de-su-campana-ante-el-temor-de-una-presidencia-de-de-la-espriella/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E319"/>
+  <autoFilter ref="A1:E305"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -9309,20 +8947,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E303" r:id="rId302"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E304" r:id="rId303"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E305" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E306" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E307" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E308" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E309" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E310" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E311" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E312" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E313" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E314" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E315" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E316" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E317" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E318" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E319" r:id="rId318"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/ultimahora.xlsx
+++ b/public/ultimahora.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Todas las noticias" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Todas las noticias'!$A$1:$E$305</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Todas las noticias'!$A$1:$E$306</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E305"/>
+  <dimension ref="A1:E306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 08:56 p. m.</t>
+          <t>31/05/2026 09:55 p. m.</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -542,19 +542,19 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Colombia vs. Costa Rica: ¿saturar a Luis Díaz o aprovechar para buscar relevos?</t>
+          <t>Paloma Valencia, entre la decepción y el apoyo final a Abelardo de la Espriella: así se vivió la derrota de la senadora del Centro Democrático</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/deportes/futbol-internacional/colombia-vs-costa-rica-saturar-a-luis-diaz-o-aprovechar-para-buscar-relevos-3560980</t>
+          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/paloma-valencia-entre-la-decepcion-y-el-apoyo-final-a-abelardo-de-la-espriella-asi-se-vivio-la-derrota-de-la-senadora-del-centro-democratico-3561006</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 08:49 p. m.</t>
+          <t>31/05/2026 09:54 p. m.</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -569,19 +569,19 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Elecciones presidenciales 2026: los departamentos donde ganaron Abelardo de la Espriella e Iván Cepeda en primera vuelta</t>
+          <t>‘Vamos a ser protagonistas de lo que falta en estas elecciones’: Sergio Fajardo</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/resultados-presidenciales-2026-primera-vuelta/elecciones-presidenciales-2026-los-departamentos-donde-ganaron-abelardo-de-la-espriella-e-ivan-cepeda-en-primera-vuelta-3560985</t>
+          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/resultados-presidenciales-2026-primera-vuelta/vamos-a-ser-protagonistas-de-lo-que-falta-en-estas-elecciones-sergio-fajardo-3560999</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 08:49 p. m.</t>
+          <t>31/05/2026 09:43 p. m.</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -596,19 +596,19 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Elecciones presidenciales 2026: Miguel Uribe Londoño agradeció a todas las personas que lo acompañaron y dijo que la causa de su hijo seguirá vigente</t>
+          <t>International Board anuncia novedad de última hora en el protocolo VAR para el Mundial 2026</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/resultados-presidenciales-2026-primera-vuelta/elecciones-presidenciales-2026-miguel-uribe-londono-agradecio-a-todas-las-personas-que-lo-acompanaron-y-dijo-que-la-causa-de-su-hijo-seguira-vigente-3560986</t>
+          <t>https://www.eltiempo.com/deportes/futbol-internacional/international-board-anuncia-novedad-de-ultima-hora-en-el-protocolo-var-para-el-mundial-3560998</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 08:47 p. m.</t>
+          <t>31/05/2026 09:43 p. m.</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -623,19 +623,19 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Primera vuelta con sello nariñense: Iván Cepeda lidera, la abstención se debate y la seguridad se impone en sus 64 municipios</t>
+          <t>ONU y OEA se pronunciaron sobre la primera vuelta presidencial en Colombia: pidieron respetar el compromiso por unas elecciones 'libres y en paz'</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/colombia/cali/primera-vuelta-con-sello-narinense-ivan-cepeda-lidera-la-abstencion-se-debate-y-la-seguridad-se-impone-en-sus-64-municipios-3560984</t>
+          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/onu-y-oea-se-pronunciaron-sobre-la-primera-vuelta-presidencial-en-colombia-pidieron-respetar-el-compromiso-por-unas-elecciones-libres-y-en-paz-3561003</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 08:46 p. m.</t>
+          <t>31/05/2026 09:42 p. m.</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -650,19 +650,19 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Abelardo de la Espriella e Iván Cepeda son los candidatos más votados en una primera vuelta en las elecciones presidenciales de Colombia</t>
+          <t>En flagrancia: capturan a cinco personas por presunta compra de votos en Popayán mientras el país ejercía su derecho democrático</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/abelardo-de-la-espriella-e-ivan-cepeda-superaron-la-votacion-en-primera-vuelta-de-gustavo-petro-en-2022-en-las-elecciones-de-colombia-3560981</t>
+          <t>https://www.eltiempo.com/colombia/cali/en-flagrancia-capturan-a-cinco-personas-por-presunta-compra-de-votos-en-popayan-mientras-el-pais-ejercia-su-derecho-democratico-3560994</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 08:37 p. m.</t>
+          <t>31/05/2026 09:39 p. m.</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -677,19 +677,19 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Bogotá transforma escombros clandestinos en material de construcción para las vías: así funciona el plan de economía circular para salvar a Doña Juana</t>
+          <t>Elecciones presidenciales Colombia 2026: ¿cómo consultar las actas E-14 tras el cierre de votaciones?</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/bogota/bogota-transforma-escombros-clandestinos-en-material-de-construccion-para-las-vias-asi-funciona-el-plan-de-economia-circular-para-salvar-a-dona-juana-3556875</t>
+          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/elecciones-presidenciales-colombia-2026-como-consultar-las-actas-e-14-tras-el-cierre-de-votaciones-3561002</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 08:24 p. m.</t>
+          <t>31/05/2026 09:33 p. m.</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -704,19 +704,19 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Javier Milei, presidente de Argentina, felicitó a Abelardo de la Espriella por ganar primera vuelta: 'Este resultado refleja el anhelo de libertad'</t>
+          <t>¿Quién es Iván Cepeda Castro, el hombre que busca que la izquierda siga en la Casa de Nariño? Perfil</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/mundo/latinoamerica/javier-milei-presidente-de-argentina-felicito-a-abelardo-de-la-espriella-por-su-paso-a-segunda-vuelta-este-resultado-refleja-el-anhelo-de-libertad-3560975</t>
+          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/quien-es-ivan-cepeda-castro-el-hombre-que-busca-que-la-izquierda-siga-en-la-casa-de-narino-perfil-3560997</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 08:22 p. m.</t>
+          <t>31/05/2026 09:29 p. m.</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -731,19 +731,19 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>¿Qué hacer si perdió el certificado electoral y quiere reclamar sus beneficios?</t>
+          <t>¿Se pueden acumular los descansos por votar en primera y segunda vuelta? Esto dice la ley</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/que-hacer-si-perdio-el-certificado-electoral-y-quiere-reclamar-sus-beneficios-3560971</t>
+          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/se-pueden-acumular-los-descansos-por-votar-en-primera-y-segunda-vuelta-esto-dice-la-ley-3560983</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 08:20 p. m.</t>
+          <t>31/05/2026 09:22 p. m.</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -758,19 +758,19 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Fotos | Así celebraron los seguidores de Abelardo de la Espriella en Barranquilla, Bucaramanga, Cali y otras ciudades tras pasar a la segunda vuelta</t>
+          <t>Así fueron los resultados de la primera vuelta de las elecciones presidenciales en Cundinamarca: Abelardo de la Espriella obtuvo mayor votación</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/fotos-asi-celebraron-los-seguidores-de-abelardo-de-la-espriella-en-barranquilla-bucaramanga-cali-y-otras-ciudades-tras-pasar-a-la-segunda-vuelta-3560961</t>
+          <t>https://www.eltiempo.com/bogota/asi-fueron-los-resultados-de-la-primera-vuelta-de-las-elecciones-presidenciales-en-cundinamarca-abelardo-de-la-espriella-obtuvo-mayor-votacion-3560988</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 08:11 p. m.</t>
+          <t>31/05/2026 09:12 p. m.</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -785,19 +785,19 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>El país votó en paz: así se desarrolló la primera vuelta presidencial en materia de orden público</t>
+          <t>Alcalde de Bogotá, Carlos F. Galán, se pronunció tras resultados de elecciones presidenciales en Colombia 2026: 'La democracia la tenemos que cuidar'</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/justicia/investigacion/el-pais-voto-en-paz-asi-se-desarrollo-la-primera-vuelta-presidencial-en-materia-de-orden-publico-3560938</t>
+          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/alcalde-de-bogota-carlos-f-galan-se-pronuncio-tras-resultados-de-elecciones-presidenciales-en-colombia-2026-la-democracia-tenemos-que-cuidarla-3560989</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 08:10 p. m.</t>
+          <t>31/05/2026 09:07 p. m.</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,19 +812,19 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Roy Barreras reiteró su apoyo a Iván Cepeda y le pidió 'abrir la campaña' para que Abelardo de la Espriella no sea presidente</t>
+          <t>Abelardo de la Espriella gana el voto en el exterior en primera vuelta con el 53,4 % ante Iván Cepeda: ¿por quién se inclina el electorado en segunda?</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/resultados-presidenciales-2026-primera-vuelta/roy-barreras-anuncio-su-apoyo-a-ivan-cepeda-y-le-pidio-abrir-la-campana-para-que-abelardo-de-la-espriella-no-sea-presidente-3560974</t>
+          <t>https://www.eltiempo.com/mundo/mas-regiones/abelardo-de-la-espriella-gana-el-voto-en-el-exterior-en-primera-vuelta-con-el-53-4-ante-ivan-cepeda-por-quien-se-inclina-el-electorado-en-segunda-3560977</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 08:06 p. m.</t>
+          <t>31/05/2026 09:02 p. m.</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -839,19 +839,19 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Senador Bernie Moreno felicitó a Abelardo de la Espriella por obtener la mayor votación en la primera vuelta presidencial: 'La democracia ganó hoy'</t>
+          <t>En Santander el favoritismo fue para Abelardo De La Espriella: solo en dos municipios ganó Iván Cepeda, ¿cuáles fueron?</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/resultados-presidenciales-2026-primera-vuelta/senador-bernie-moreno-felicito-a-abelardo-de-la-espriella-por-obtener-la-mayor-votacion-en-la-primera-vuelta-presidencial-la-democracia-gano-hoy-3560976</t>
+          <t>https://www.eltiempo.com/colombia/santander/en-santander-el-favoritismo-fue-para-abelardo-de-la-espriella-solo-en-dos-municipios-gano-ivan-cepeda-cuales-fueron-3560979</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 08:03 p. m.</t>
+          <t>31/05/2026 08:59 p. m.</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -866,19 +866,19 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>FOTOS | Los rostros desde la sede de campaña de Iván Cepeda y Aida Quilcué tras pasar a segunda vuelta presidencial contra Abelardo de la Espriella</t>
+          <t>Dos jurados de votación en Antioquia llegaron ebrios a sus mesas; la Policía intervino: ¿qué sanciones podrían recibir?</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/fotos-los-rostros-desde-la-sede-de-campana-de-ivan-cepeda-y-aida-quilcue-tras-pasar-a-segunda-vuelta-presidencial-contra-abelardo-de-la-espriella-3560969</t>
+          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/dos-jurados-de-votacion-en-antioquia-llegaron-ebrios-a-sus-mesas-la-policia-intervino-que-sanciones-podrian-recibir-3560982</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 08:01 p. m.</t>
+          <t>31/05/2026 08:56 p. m.</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -893,19 +893,19 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>¿Se puede cambiar el puesto de votación para la segunda vuelta? Esto respondió la Registraduría Nacional del Estado Civil</t>
+          <t>Colombia vs. Costa Rica: ¿saturar a Luis Díaz o aprovechar para buscar relevos?</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/resultados-presidenciales-2026-primera-vuelta/se-puede-cambiar-el-puesto-de-votacion-para-la-segunda-vuelta-esto-respondio-la-registraduria-nacional-del-estado-civil-3560972</t>
+          <t>https://www.eltiempo.com/deportes/futbol-internacional/colombia-vs-costa-rica-saturar-a-luis-diaz-o-aprovechar-para-buscar-relevos-3560980</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 08:01 p. m.</t>
+          <t>31/05/2026 08:49 p. m.</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -920,19 +920,19 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Las reacciones de medios internacionales a la segunda vuelta entre Abelardo de la Espriella e Iván Cepeda por la Presidencia de Colombia</t>
+          <t>Elecciones presidenciales 2026: los departamentos donde ganaron Abelardo de la Espriella e Iván Cepeda en primera vuelta</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/las-reacciones-de-medios-internacionales-a-la-segunda-vuelta-entre-abelardo-de-la-espriella-e-ivan-cepeda-por-la-presidencia-de-colombia-3560965</t>
+          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/resultados-presidenciales-2026-primera-vuelta/elecciones-presidenciales-2026-los-departamentos-donde-ganaron-abelardo-de-la-espriella-e-ivan-cepeda-en-primera-vuelta-3560985</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 07:53 p. m.</t>
+          <t>31/05/2026 08:49 p. m.</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -947,19 +947,19 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Video | Neymar se roba el 'show' en victoria de Brasil: jugadores de Panamá hacen fila para tomarse una foto con él</t>
+          <t>Elecciones presidenciales 2026: Miguel Uribe Londoño agradeció a todas las personas que lo acompañaron y dijo que la causa de su hijo seguirá vigente</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/deportes/futbol-internacional/video-neymar-se-roba-el-show-en-victoria-de-brasil-jugadores-de-panama-hacen-fila-para-tomarse-una-foto-con-el-3560973</t>
+          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/resultados-presidenciales-2026-primera-vuelta/elecciones-presidenciales-2026-miguel-uribe-londono-agradecio-a-todas-las-personas-que-lo-acompanaron-y-dijo-que-la-causa-de-su-hijo-seguira-vigente-3560986</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 07:40 p. m.</t>
+          <t>31/05/2026 08:47 p. m.</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -974,19 +974,19 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Iván Cepeda dice que se pronunciará luego de los resultados de comisión escrutadora sobre la primera vuelta presidencial de Colombia 2026</t>
+          <t>Primera vuelta con sello nariñense: Iván Cepeda lidera, la abstención se debate y la seguridad se impone en sus 64 municipios</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/ivan-cepeda-dice-que-se-pronunciara-luego-de-los-resultados-de-comision-escrutadora-sobre-la-primera-vuelta-3560966</t>
+          <t>https://www.eltiempo.com/colombia/cali/primera-vuelta-con-sello-narinense-ivan-cepeda-lidera-la-abstencion-se-debate-y-la-seguridad-se-impone-en-sus-64-municipios-3560984</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 07:38 p. m.</t>
+          <t>31/05/2026 08:46 p. m.</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -1001,19 +1001,19 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Balance de la jornada electoral en el Valle del Cauca: participación masiva y orden público garantizado en 42 municipios</t>
+          <t>Abelardo de la Espriella e Iván Cepeda son los candidatos más votados en una primera vuelta en las elecciones presidenciales de Colombia</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/colombia/cali/balance-de-la-jornada-electoral-en-el-valle-del-cauca-participacion-masiva-y-orden-publico-garantizado-en-42-municipios-3560964</t>
+          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/abelardo-de-la-espriella-e-ivan-cepeda-superaron-la-votacion-en-primera-vuelta-de-gustavo-petro-en-2022-en-las-elecciones-de-colombia-3560981</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 07:37 p. m.</t>
+          <t>31/05/2026 08:37 p. m.</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1028,19 +1028,19 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Estos son los 9 candidatos que fueron superados por el voto en blanco en las elecciones presidenciales de este 31 de mayo</t>
+          <t>Bogotá transforma escombros clandestinos en material de construcción para las vías: así funciona el plan de economía circular para salvar a Doña Juana</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/estos-son-los-candidatos-que-fueron-superados-por-el-voto-en-blanco-en-las-elecciones-presidenciales-de-este-31-de-mayo-3560970</t>
+          <t>https://www.eltiempo.com/bogota/bogota-transforma-escombros-clandestinos-en-material-de-construccion-para-las-vias-asi-funciona-el-plan-de-economia-circular-para-salvar-a-dona-juana-3556875</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 07:31 p. m.</t>
+          <t>31/05/2026 08:24 p. m.</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -1055,19 +1055,19 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Gustavo Petro, Iván Duque, Juan Manuel Santos y los otros ganadores de la segunda vuelta en Colombia en los últimos años</t>
+          <t>Javier Milei, presidente de Argentina, felicitó a Abelardo de la Espriella por ganar primera vuelta: 'Este resultado refleja el anhelo de libertad'</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>https://www.eltiempo.com/politica/elecciones-colombia-2026/gustavo-petro-ivan-duque-juan-manuel-santos-y-los-otros-ganadores-de-la-segunda-vuelta-en-colombia-en-los-ultimos-anos-3560953</t>
+          <t>https://www.eltiempo.com/mundo/latinoamerica/javier-milei-presidente-de-argentina-felicito-a-abelardo-de-la-espriella-por-su-paso-a-segunda-vuelta-este-resultado-refleja-el-anhelo-de-libertad-3560975</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>01/06/2026 01:32 a. m.</t>
+          <t>01/06/2026 02:07 a. m.</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1082,19 +1082,19 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>“Ni se les ocurra desconocer la voluntad popular”: El mensaje de Abelardo de la Espriella camino a la segunda vuelta</t>
+          <t>Balance regional de la primera vuelta: así se repartieron los votos entre Abelardo de la Espriella e Iván Cepeda</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/politica/abelardo-de-la-espriella-discurso-segunda-vuelta-elecciones-presidenciales-mensaje-gustavo-petro-ivan-cepeda-400969</t>
+          <t>https://www.lafm.com.co/politica/elecciones-presidenciales-primera-vuelta-2026-balance-regiones-colombia-abelardo-de-la-espriella-ivan-cepeda-400970</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>01/06/2026 12:57 a. m.</t>
+          <t>01/06/2026 02:05 a. m.</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -1109,19 +1109,19 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>“No podemos volver a la muerte y a la exclusión”: el mensaje de Iván cepeda y Aida Quilcué tras la votación</t>
+          <t>¿Quién es Aída Quilcué? La senadora y defensora de Derechos Humanos que aspira a la vicepresidencia en la segunda vuelta</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/politica/ivan-cepeda-aida-quilcue-no-aceptan-votaciones-elecciones-presidenciales-400965</t>
+          <t>https://www.lafm.com.co/politica/quien-es-aida-quilcue-trayectoria-senado-formula-vicepresidencial-elecciones-colombia-400968</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>01/06/2026 12:39 a. m.</t>
+          <t>01/06/2026 01:32 a. m.</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1136,19 +1136,19 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>¿Cuántos votos sacaron Abelardo de la Espriella e Iván Cepeda y cómo pasan a segunda vuelta presidencial?</t>
+          <t>“Ni se les ocurra desconocer la voluntad popular”: El mensaje de Abelardo de la Espriella camino a la segunda vuelta</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/politica/segunda-vuelta-abelardo-de-la-espriella-ivan-cepeda-numero-total-de-votos-elecciones-colombia-400946</t>
+          <t>https://www.lafm.com.co/politica/abelardo-de-la-espriella-discurso-segunda-vuelta-elecciones-presidenciales-mensaje-gustavo-petro-ivan-cepeda-400969</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>01/06/2026 12:08 a. m.</t>
+          <t>01/06/2026 12:21 a. m.</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1163,19 +1163,19 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Álvaro Uribe se pronuncia tras derrota de Paloma Valencia y llama a elegir a Abelardo de la Espriella presidente</t>
+          <t>Cuántos votos necesitan Abelardo De la Espriella e Iván Cepeda para ganar la presidencia en segunda vuelta</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/politica/alvaro-uribe-llama-a-elegir-a-abelardo-de-la-espriella-como-presidente-de-colombia-400958</t>
+          <t>https://www.lafm.com.co/politica/segunda-vuelta-elecciones-colombia-2026-cuantos-votos-necesitan-de-la-espriella-cepeda-para-la-presidencia-400961</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>01/06/2026 12:03 a. m.</t>
+          <t>01/06/2026 12:08 a. m.</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1190,19 +1190,19 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>¿De dónde saldrán los votos de Abelardo de la Espriella e Iván Cepeda para ganar en segunda vuelta?</t>
+          <t>Álvaro Uribe se pronuncia tras derrota de Paloma Valencia y llama a elegir a Abelardo de la Espriella presidente</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/politica/abelardo-de-la-espriella-ivan-cepeda-segunda-vuelta-elecciones-presidenciales-2026-votos-400960</t>
+          <t>https://www.lafm.com.co/politica/alvaro-uribe-llama-a-elegir-a-abelardo-de-la-espriella-como-presidente-de-colombia-400958</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 11:40 p. m.</t>
+          <t>01/06/2026 12:03 a. m.</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -1217,19 +1217,19 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Sergio Fajardo tras un millón de votos: “vamos a ser protagonistas de la segunda vuelta presidencial”</t>
+          <t>¿De dónde saldrán los votos de Abelardo de la Espriella e Iván Cepeda para ganar en segunda vuelta?</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/politica/sergio-fajardo-cerca-millon-votos-anuncia-participacion-en-segunda-vuelta-400957</t>
+          <t>https://www.lafm.com.co/politica/abelardo-de-la-espriella-ivan-cepeda-segunda-vuelta-elecciones-presidenciales-2026-votos-400960</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 10:51 p. m.</t>
+          <t>31/05/2026 11:40 p. m.</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1244,12 +1244,12 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>¿Quién es José Manuel Restrepo? El exministro que acompaña a Abelardo de la Espriella como fórmula vicepresidencial</t>
+          <t>Sergio Fajardo tras un millón de votos: “vamos a ser protagonistas de la segunda vuelta presidencial”</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/politica/quien-es-jose-manuel-restrepo-fomula-vicepresidencial-abelardo-de-la-espriella-exministro-400947</t>
+          <t>https://www.lafm.com.co/politica/sergio-fajardo-cerca-millon-votos-anuncia-participacion-en-segunda-vuelta-400957</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>27/05/2026 11:55 a. m.</t>
+          <t>28/05/2026 11:28 a. m.</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>¿Quién es Iván Cepeda? El congresista que busca la Presidencia en segunda vuelta 2026</t>
+          <t>“No acepto los resultados”: Gustavo Petro denuncia irregularidades tras primera vuelta y señala presunto fraude electoral en Colombia</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/politica/ivan-cepeda-perfil-politico-rumbo-segunda-vuelta-elecciones-presidenciales-colombia2026-400891</t>
+          <t>https://www.lafm.com.co/politica/presidente-petro-no-acepto-los-resultados-de-la-primera-vuelta-presidencial-2026-400963</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>“No acepto los resultados”: Gustavo Petro denuncia irregularidades tras primera vuelta y señala presunto fraude electoral en Colombia</t>
+          <t>“No podemos volver a la muerte y a la exclusión”: el mensaje de Iván cepeda y Aida Quilcué tras la votación</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/politica/presidente-petro-no-acepto-los-resultados-de-la-primera-vuelta-presidencial-2026-400963</t>
+          <t>https://www.lafm.com.co/politica/ivan-cepeda-aida-quilcue-no-aceptan-votaciones-elecciones-presidenciales-400965</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Cuántos votos necesitan Abelardo De la Espriella e Iván Cepeda para ganar la presidencia en segunda vuelta</t>
+          <t>¿Cuántos votos sacaron Abelardo de la Espriella e Iván Cepeda y cómo pasan a segunda vuelta presidencial?</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>https://www.lafm.com.co/politica/segunda-vuelta-elecciones-colombia-2026-cuantos-votos-necesitan-de-la-espriella-cepeda-para-la-presidencia-400961</t>
+          <t>https://www.lafm.com.co/politica/segunda-vuelta-abelardo-de-la-espriella-ivan-cepeda-numero-total-de-votos-elecciones-colombia-400946</t>
         </is>
       </c>
     </row>
@@ -1610,12 +1610,12 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Así votaron los colombianos en el exterior: Abelardo de la Espriella e Iván Cepeda lideraron en las urnas</t>
+          <t>Tras los resultados de la primera vuelta presidencial, el empresario Mario Hernández pidió “recuperar a Colombia en segunda”</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/06/01/asi-votaron-los-colombianos-en-el-exterior-abelardo-de-la-espriella-e-ivan-cepeda-lideraron-en-las-urnas/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/tras-los-resultados-de-la-primera-vuelta-presidencial-el-empresario-mario-hernandez-pidio-recuperar-a-colombia-en-segunda/</t>
         </is>
       </c>
     </row>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Prensa internacional registró la victoria de Abelardo de la Espriella en las elecciones presidenciales: “Una Colombia partida en dos”</t>
+          <t>Segunda vuelta: cómo se repartirían los votos de Paloma Valencia y Sergio Fajardo tras derrota en la primera vuelta; expertos opinan</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/06/01/prensa-internacional-registro-la-victoria-de-abelardo-de-la-espriella-en-las-elecciones-presidenciales-una-colombia-partida-en-dos/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/segunda-vuelta-como-se-repartirian-los-votos-de-paloma-valencia-y-sergio-fajardo-tras-derrota-en-la-primera-vuelta-expertos-opinan/</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Canciller Rosa Villavicencio entregó el primer balance sobre el desarrollo de las elecciones presidenciales en el exterior: “Han existido alteraciones”</t>
+          <t>Caribeña Noche, resultado del último sorteo hoy domingo 31 de mayo</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/06/01/canciller-rosa-villavicencio-entrego-el-primer-balance-sobre-el-desarrollo-de-las-elecciones-presidenciales-en-el-exterior-han-existido-alteraciones/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/caribena-noche-resultado-del-ultimo-sorteo-hoy-lunes-1-de-junio/</t>
         </is>
       </c>
     </row>
@@ -1691,12 +1691,12 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>El resultado de la primera vuelta sacudió al país político: así reaccionaron a las elecciones entre De la Espriella e Iván Cepeda</t>
+          <t>¿Va al Mundial 2026? Esto pasa si quiere votar por De la Espriella o Iván Cepeda desde Estados Unidos, México o Canadá</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/06/01/el-resultado-de-la-primera-vuelta-sacudio-al-pais-politico-asi-reaccionaron-a-las-elecciones-entre-de-la-espriella-e-ivan-cepeda/</t>
+          <t>https://www.infobae.com/colombia/deportes/2026/06/01/va-al-mundial-2026-esto-pasa-si-quiere-votar-por-de-la-espriella-o-ivan-cepeda-desde-estados-unidos-mexico-o-canada/</t>
         </is>
       </c>
     </row>
@@ -1718,12 +1718,12 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Tomás Uribe reaccionó al avance de Abelardo de la Espriella y celebró la derrota de Cepeda en primera vuelta: “Es una gran ganancia para Colombia”</t>
+          <t>Así quedó el mapa político en Colombia tras la primera vuelta presidencial: estos departamentos apoyaron a Iván Cepeda y a Abelardo de la Espriella</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/06/01/tomas-uribe-reacciono-al-avance-de-abelardo-de-la-espriella-y-celebro-la-derrota-de-cepeda-en-primera-vuelta-es-una-gran-ganancia-para-colombia/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/asi-quedo-el-mapa-politico-en-colombia-tras-la-primera-vuelta-presidencial-estos-departamentos-apoyaron-a-ivan-cepeda-y-a-abelardo-de-la-espriella/</t>
         </is>
       </c>
     </row>
@@ -1745,12 +1745,12 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>El alcalde Federico Gutiérrez rechazó las declaraciones de Petro sobre resultados electorales: "Pasarás a la historia como el peor presidente de Colombia"</t>
+          <t>Mafe Carrascal le lanzó una pícara propuesta a Juan Daniel Oviedo tras perder las elecciones presidenciales: esto le dijo</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/06/01/el-alcalde-federico-gutierrez-rechazo-las-declaraciones-de-petro-sobre-resultados-electorales-pasaras-a-la-historia-como-el-peor-presidente-de-colombia/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/mafe-carrascal-le-lanzo-una-picara-propuesta-a-juan-daniel-oviedo-tras-perder-las-elecciones-presidenciales-esto-le-dijo/</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1772,12 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>De ‘Betty, la fea’ a series internacionales y darles nuevas caras a los candidatos, los  memes que dejaron las elecciones presidenciales</t>
+          <t>Resultado Super Astro Luna HOY: número ganador del domingo 31 de mayo</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/06/01/los-memes-que-causaron-furor-en-redes-y-marcaron-la-jornada-electoral-en-colombia-una-valeriana-o-algo/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/resultado-super-astro-luna-hoy-numero-ganador-del-domingo-31-de-mayo/</t>
         </is>
       </c>
     </row>
@@ -1799,12 +1799,12 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Resultado Chontico Noche: números ganadores del último sorteo hoy, domingo 31 de mayo de 2026</t>
+          <t>Gustavo Petro desató ola de críticas por rechazar los resultados de las elecciones presidenciales: “Qué peligro este señor”</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/06/01/resultado-chontico-noche-numeros-ganadores-del-ultimo-sorteo-hoy-domingo-31-de-mayo-de-2026/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/gustavo-petro-desato-ola-de-criticas-por-rechazar-los-resultados-de-las-elecciones-presidenciales-que-peligro-este-senor/</t>
         </is>
       </c>
     </row>
@@ -1826,12 +1826,12 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Claudia López explicó por qué Iván Cepeda quedó segundo en la primera vuelta de las elecciones presidenciales: “No te pueden hacer la campaña”</t>
+          <t>Paloma Valencia se convirtió en la cuarta mujer más votada para la Presidencia de Colombia: ranking completo del top seis</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/06/01/claudia-lopez-explico-por-que-ivan-cepeda-quedo-segundo-en-la-primera-vuelta-de-las-elecciones-presidenciales-no-te-pueden-hacer-la-campana/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/paloma-valencia-se-convirtio-en-la-cuarta-mujer-mas-votada-para-la-presidencia-de-colombia-ranking-completo-del-top-seis/</t>
         </is>
       </c>
     </row>
@@ -1853,12 +1853,12 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Juan Daniel Oviedo calificó a Abelardo de la Espriella como un “candidato machista y homofóbico”</t>
+          <t>Jornada electoral del 31 de mayo dejó más de 80 capturas y la votación de más de 70 personas reportadas como desaparecidas</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/06/01/juan-daniel-oviedo-califico-a-abelardo-de-la-espriella-como-un-candidato-machista-y-homofobico/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/jornada-electoral-del-31-de-mayo-dejo-mas-de-80-capturas-y-la-votacion-de-mas-de-70-personas-reportadas-como-desaparecidas/</t>
         </is>
       </c>
     </row>
@@ -1880,12 +1880,12 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Departamento de Estado se pronunció tras primera vuelta en Colombia: “EE. UU. apoya el derecho del pueblo colombiano a elegir libremente”</t>
+          <t>Resultado Sinuano Noche hoy 31 de mayo</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/06/01/departamento-de-estado-se-pronuncio-tras-primera-vuelta-en-colombia-ee-uu-apoya-el-derecho-del-pueblo-colombiano-a-elegir-libremente/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/resultado-sinuano-noche-hoy-31-de-mayo/</t>
         </is>
       </c>
     </row>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Bernie Moreno dio parte de tranquilidad en la primera vuelta y celebró victoria de Abelardo de la Espriella: “El trabajo no está terminado aún”</t>
+          <t>De la Espriella recibió apoyo de líderes internacionales de derecha tras su triunfo en primera vuelta: “La libertad avanza”</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/06/01/bernie-moreno-dio-parte-de-tranquilidad-en-la-primera-vuelta-y-celebro-victoria-de-abelardo-de-la-espriella-el-trabajo-no-esta-terminado-aun/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/de-la-espriella-recibio-apoyo-de-lideres-internacionales-de-derecha-tras-su-triunfo-en-primera-vuelta-la-libertad-avanza/</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Gustavo Petro no reconoció los resultados electorales de la primera vuelta en Colombia: “Como presidente no los acepto”</t>
+          <t>Abelardo de la Espriella e Iván Cepeda: de qué equipo serían hinchas los candidatos de la segunda vuelta presidencial</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/06/01/gustavo-petro-no-reconoce-los-resultados-electorales-de-la-primera-vuelta-como-presidente-no-los-acepto/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/abelardo-de-la-espriella-e-ivan-cepeda-de-que-equipo-serian-hinchas-los-candidatos-de-la-segunda-vuelta-presidencial/</t>
         </is>
       </c>
     </row>
@@ -1961,12 +1961,12 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Exministro de Defensa de Juan Manuel Santos también anunció su apoyo a Abelardo de la Espriella para la segunda vuelta presidencial: “Recuperemos a Colombia”</t>
+          <t>Elecciones presidenciales del 21 de junio: ¿se puede cambiar el puesto de votación para la segunda vuelta?</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/06/01/exministro-de-defensa-de-juan-manuel-santos-tambien-anuncio-su-apoyo-a-abelardo-de-la-espriella-para-la-segunda-vuelta-presidencial-recuperemos-a-colombia/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/elecciones-presidenciales-del-21-de-junio-se-puede-cambiar-el-puesto-de-votacion-para-la-segunda-vuelta/</t>
         </is>
       </c>
     </row>
@@ -1988,12 +1988,12 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Riña con arma blanca dejó un muerto en el sur de Bogotá, en plena ley seca: ocurrió a pocos metros de un CAI</t>
+          <t>Abelardo De La Espriella respondió al llamado de Roy Barreras de unir votos de Fajardo y López a favor de Iván Cepeda</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/06/01/rina-con-arma-blanca-dejo-un-muerto-en-el-sur-de-bogota-en-plena-ley-seca-ocurrio-a-pocos-metros-de-un-cai/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/abelardo-de-la-espriella-respondio-al-llamado-de-roy-barreras-de-unir-votos-de-fajardo-y-lopez-a-favor-de-ivan-cepeda/</t>
         </is>
       </c>
     </row>
@@ -2015,19 +2015,19 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Turista neerlandesa fue encontrada muerta en zona rural de Salento tras ser reportada como desaparecida</t>
+          <t>Mónica Rodríguez aseguró que Uribe sabía lo que pasaría con Abelardo de la Espriella: “Siempre ha sido su as bajo la manga”</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/06/01/turista-neerlandesa-fue-encontrada-muerta-en-zona-rural-de-salento-tras-ser-reportada-como-desaparecida/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/monica-rodriguez-aseguro-que-uribe-sabia-lo-que-pasaria-con-abelardo-de-la-espriella-siempre-ha-sido-su-as-bajo-la-manga/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 12:00 a. m.</t>
+          <t>01/06/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2042,19 +2042,19 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Elecciones en Colombia 2026, EN VIVO: De “abogado de paramiliatares” a “espía de las Farc”, las pullas entre De la Espriella y Cepeda ya iniciaron campaña</t>
+          <t>Presidente de VOX envió mensaje a Abelardo de la Espriella tras conocerse que ganó la primera vuelta en Colombia: “Enhorabuena”</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/elecciones-en-colombia-2026-en-vivo-reporte-de-orden-publico-apertura-de-mesas-y-noticias-relevantes-hoy-31-de-mayo/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/presidente-de-vox-envio-mensaje-a-abelardo-de-la-espriella-tras-conocerse-que-gano-la-primera-vuelta-en-colombia-enhorabuena/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 12:00 a. m.</t>
+          <t>01/06/2026 12:00 a. m.</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Elecciones presidenciales desde Bogotá: Iván Cepeda venció a Abelardo de la Espriella en la capital</t>
+          <t>Sergio Fajardo valoró el respaldo de un millón de votos tras la primera vuelta presidencial en Colombia: “Vamos a ser protagonistas”</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/elecciones-presidenciales-en-vivo-desde-bogota-hoy-31-de-mayo-siga-el-minuto-a-minuto-de-las-votaciones/</t>
+          <t>https://www.infobae.com/colombia/2026/06/01/sergio-fajardo-valoro-el-respaldo-de-un-millon-de-votos-tras-la-primera-vuelta-presidencial-en-colombia-vamos-a-ser-protagonistas/</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Sorpresa en las elecciones de Colombia: Abelardo de la Espriella gana la primera vuelta y disputará la presidencia con Iván Cepeda</t>
+          <t>Elecciones en Colombia 2026, EN VIVO: De “abogado de paramiliatares” a “espía de las Farc”, las pullas entre De la Espriella y Cepeda ya iniciaron campaña</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/sorpresa-en-las-elecciones-de-colombia-abelardo-de-la-espriella-gana-la-primera-vuelta-y-disputara-la-presidencia-con-ivan-cepeda/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/elecciones-en-colombia-2026-en-vivo-reporte-de-orden-publico-apertura-de-mesas-y-noticias-relevantes-hoy-31-de-mayo/</t>
         </is>
       </c>
     </row>
@@ -2123,19 +2123,19 @@
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Elecciones en Antioquia: Abelardo de la Espriella duplicó a Iván Cepeda</t>
+          <t>Elecciones 2026| Colombia rompe récords en votaciones: Registraduría resaltó los bajos niveles de abstención</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/05/31/elecciones-en-antioquia-en-vivo/</t>
+          <t>https://www.infobae.com/colombia/2026/05/31/elecciones-2026-colombia-registra-su-eleccion-presidencial-mas-votada-en-la-historia/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 08:55 p. m.</t>
+          <t>31/05/2026 09:49 p. m.</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2150,19 +2150,19 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Procurador general resalta la transparencia de las elecciones presidenciales en Colombia</t>
+          <t>Gilberto Rodríguez Orejuela: del control del 80% de la cocaína a estudiar filosofía en su celda</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/procurador-general-resalta-la-transparencia-de-las-elecciones-presidenciales-en-colombia-rg10</t>
+          <t>https://www.noticiascaracol.com/los-informantes/capitulos/gilberto-rodriguez-orejuela-del-control-del-80-de-la-cocaina-a-estudiar-filosofia-en-su-celda-pr30</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 08:52 p. m.</t>
+          <t>31/05/2026 09:31 p. m.</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -2177,19 +2177,19 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Abelardo de la Espriella pide veeduría internacional para segunda vuelta y lanza críticas a Cepeda</t>
+          <t>Cepeda y De la Espriella se lanzan duros ataques y hacen llamados para ganar en segunda vuelta</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/abelardo-de-la-espriella-pide-veeduria-internacional-para-segunda-vuelta-y-lanza-criticas-a-cepeda-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/cepeda-y-de-la-espriella-se-lanzan-duros-ataques-y-hacen-llamados-para-ganar-en-segunda-vuelta-rg10</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 08:21 p. m.</t>
+          <t>31/05/2026 09:28 p. m.</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2204,19 +2204,19 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Departamento de Estado de Estados Unidos se pronunció tras la jornada electoral en Colombia</t>
+          <t>¿Cómo votaron los colombianos en Estados Unidos para las elecciones presidenciales?</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/departamento-de-estado-de-estados-unidos-se-pronuncio-tras-la-jornada-electoral-en-colombia-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/como-votaron-los-colombianos-en-estados-unidos-para-las-elecciones-presidenciales-rg10</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 08:13 p. m.</t>
+          <t>31/05/2026 09:20 p. m.</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
@@ -2231,19 +2231,19 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Defensoría del Pueblo advierte riesgos en segunda vuelta e hizo llamado a De La Espriella y Cepeda</t>
+          <t>Así será la despedida de la Selección Colombia previo al Mundial 2026; fiesta en El Campín</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/defensoria-del-pueblo-advierte-riesgos-en-segunda-vuelta-e-hizo-llamado-a-de-la-espriella-y-cepeda-rg10</t>
+          <t>https://www.noticiascaracol.com/golcaracol/seleccion-colombia/asi-sera-la-despedida-de-la-seleccion-colombia-previo-al-mundial-2026-fiesta-en-el-campin-rg10</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 08:00 p. m.</t>
+          <t>31/05/2026 09:16 p. m.</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2258,19 +2258,19 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Resultados Sinuano Noche último sorteo del 31 de mayo de 2026: números ganadores</t>
+          <t>Elecciones permitieron ubicar a 77 personas que estaban en registros de desaparecidos</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/sinuano-noche-31-de-mayo-2026-resultados-numeros-ganadores-de-hoy-so35</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/elecciones-permitieron-ubicar-a-77-personas-que-estaban-en-registros-de-desaparecidos-cb20</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 08:00 p. m.</t>
+          <t>31/05/2026 08:55 p. m.</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -2285,19 +2285,19 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Resultados Caribeña Noche último sorteo del domingo 31 de mayo de 2026: números ganadores</t>
+          <t>Procurador general resalta la transparencia de las elecciones presidenciales en Colombia</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/caribena-noche-31-de-mayo-2026-resultados-numeros-ganadores-de-hoy-so35</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/procurador-general-resalta-la-transparencia-de-las-elecciones-presidenciales-en-colombia-rg10</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 08:00 p. m.</t>
+          <t>31/05/2026 08:52 p. m.</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2312,19 +2312,19 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Super Astro Luna resultados del domingo 31 de mayo de 2026: los números ganadores</t>
+          <t>Abelardo de la Espriella pide veeduría internacional para segunda vuelta y lanza críticas a Cepeda</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/super-astro-luna-31-de-mayo-de-2026-cuales-son-los-numeros-ganadores-so35</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/abelardo-de-la-espriella-pide-veeduria-internacional-para-segunda-vuelta-y-lanza-criticas-a-cepeda-rg10</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 07:55 p. m.</t>
+          <t>31/05/2026 08:21 p. m.</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -2339,19 +2339,19 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Iván Cepeda esperará a resultados de comisiones escrutadoras para pronunciarse tras elecciones</t>
+          <t>Departamento de Estado de Estados Unidos se pronunció tras la jornada electoral en Colombia</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/ivan-cepeda-esperara-a-resultados-de-comisiones-escrutadoras-para-pronunciarse-tras-elecciones-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/departamento-de-estado-de-estados-unidos-se-pronuncio-tras-la-jornada-electoral-en-colombia-rg10</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 07:49 p. m.</t>
+          <t>31/05/2026 08:13 p. m.</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2366,19 +2366,19 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>"A 'Cucho' Hernández se le ve mucho mejor jugando con otro '9', con un tanque al lado"</t>
+          <t>Defensoría del Pueblo advierte riesgos en segunda vuelta e hizo llamado a De La Espriella y Cepeda</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/golcaracol/seleccion-colombia/a-cucho-hernandez-se-le-ve-mucho-mejor-jugando-con-otro-9-con-un-tanque-al-lado-ex40</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/defensoria-del-pueblo-advierte-riesgos-en-segunda-vuelta-e-hizo-llamado-a-de-la-espriella-y-cepeda-rg10</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 07:37 p. m.</t>
+          <t>31/05/2026 08:00 p. m.</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -2393,19 +2393,19 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>¿Cómo votaron los departamentos con más municipios bajo riesgo por violencia en Colombia?</t>
+          <t>Resultados Sinuano Noche último sorteo del 31 de mayo de 2026: números ganadores</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/como-votaron-los-departamentos-con-mas-municipios-bajo-riesgo-por-violencia-en-colombia-rg10</t>
+          <t>https://www.noticiascaracol.com/economia/sinuano-noche-31-de-mayo-2026-resultados-numeros-ganadores-de-hoy-so35</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 07:12 p. m.</t>
+          <t>31/05/2026 08:00 p. m.</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2420,19 +2420,19 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>"Como presidente no acepto los resultados del preconteo": Petro tras las elecciones</t>
+          <t>Resultados Caribeña Noche último sorteo del domingo 31 de mayo de 2026: números ganadores</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/como-presidente-no-acepto-los-resultados-del-preconteo-petro-tras-las-elecciones-rg10</t>
+          <t>https://www.noticiascaracol.com/economia/caribena-noche-31-de-mayo-2026-resultados-numeros-ganadores-de-hoy-so35</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 07:03 p. m.</t>
+          <t>31/05/2026 08:00 p. m.</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
@@ -2447,19 +2447,19 @@
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Juan Daniel Oviedo tras primera vuelta: “Los resultados se debaten entre los extremos populistas”</t>
+          <t>Super Astro Luna resultados del domingo 31 de mayo de 2026: los números ganadores</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/oviedo-tras-resultados-elecciones-los-resultados-se-debatan-entre-los-extremos-populistas-rg10</t>
+          <t>https://www.noticiascaracol.com/economia/super-astro-luna-31-de-mayo-de-2026-cuales-son-los-numeros-ganadores-so35</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 07:00 p. m.</t>
+          <t>31/05/2026 07:55 p. m.</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2474,19 +2474,19 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Resultados Chontico Noche último sorteo hoy, domingo 31 de mayo de 2026: números ganadores</t>
+          <t>Iván Cepeda esperará a resultados de comisiones escrutadoras para pronunciarse tras elecciones</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/chontico-noche-31-mayo-2026-resultados-numeros-ganadores-de-hoy-so35</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/ivan-cepeda-esperara-a-resultados-de-comisiones-escrutadoras-para-pronunciarse-tras-elecciones-rg10</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 07:00 p. m.</t>
+          <t>31/05/2026 07:49 p. m.</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
@@ -2501,19 +2501,19 @@
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Resultados Dorado Noche, último sorteo hoy domingo 31 de mayo de 2026: números ganadores</t>
+          <t>"A 'Cucho' Hernández se le ve mucho mejor jugando con otro '9', con un tanque al lado"</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/economia/dorado-noche-31-de-mayo-de-2026-cuales-son-los-numeros-ganadores-so35</t>
+          <t>https://www.noticiascaracol.com/golcaracol/seleccion-colombia/a-cucho-hernandez-se-le-ve-mucho-mejor-jugando-con-otro-9-con-un-tanque-al-lado-ex40</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 06:46 p. m.</t>
+          <t>31/05/2026 07:37 p. m.</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2528,19 +2528,19 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>¿Cómo votaron los colombianos en España en las elecciones presidenciales? Resultados de preconteo</t>
+          <t>Así votaron los departamentos con más municipios bajo riesgo por violencia, según MOE, en Colombia</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/como-votaron-los-colombianos-en-espana-en-las-elecciones-presidenciales-de-2026-resultados-del-100-de-preconteo-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/como-votaron-los-departamentos-con-mas-municipios-bajo-riesgo-por-violencia-en-colombia-rg10</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 06:41 p. m.</t>
+          <t>31/05/2026 07:12 p. m.</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -2555,19 +2555,19 @@
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>"Colombianos, hemos perdido": Álvaro Uribe tras la primera vuelta de las elecciones presidenciales</t>
+          <t>"Como presidente no acepto los resultados del preconteo": Petro tras las elecciones</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/colombianos-hemos-perdido-alvaro-uribe-tras-la-primera-vuelta-presidencial-en-colombia-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/como-presidente-no-acepto-los-resultados-del-preconteo-petro-tras-las-elecciones-rg10</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 06:36 p. m.</t>
+          <t>31/05/2026 07:03 p. m.</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2582,19 +2582,19 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Elecciones en Colombia: voto en blanco vence a seis candidatos y supera los 400.000 sufragios</t>
+          <t>Juan Daniel Oviedo tras primera vuelta: “Los resultados se debaten entre los extremos populistas”</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/elecciones-en-colombia-voto-en-blanco-vence-a-seis-candidatos-y-supera-los-400-000-sufragios-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/oviedo-tras-resultados-elecciones-los-resultados-se-debatan-entre-los-extremos-populistas-rg10</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 06:32 p. m.</t>
+          <t>31/05/2026 07:00 p. m.</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
@@ -2609,19 +2609,19 @@
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Sergio Fajardo habla tras su derrota en las elecciones presidenciales: "No nos vamos a resignar"</t>
+          <t>Resultados Chontico Noche último sorteo hoy, domingo 31 de mayo de 2026: números ganadores</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/sergio-fajardo-habla-tras-su-derrota-en-las-elecciones-presidenciales-de-2026-no-nos-vamos-a-resignar-rg10</t>
+          <t>https://www.noticiascaracol.com/economia/chontico-noche-31-mayo-2026-resultados-numeros-ganadores-de-hoy-so35</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 06:30 p. m.</t>
+          <t>31/05/2026 07:00 p. m.</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2636,19 +2636,19 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>"Yo sé que Iván es un hombre decente": Claudia López tras finalizar la primera vuelta presidencial</t>
+          <t>Resultados Dorado Noche, último sorteo hoy domingo 31 de mayo de 2026: números ganadores</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/yo-se-que-ivan-es-un-hombre-decente-claudia-lopez-tras-finalizar-la-primera-vuelta-presidencial-rg10</t>
+          <t>https://www.noticiascaracol.com/economia/dorado-noche-31-de-mayo-de-2026-cuales-son-los-numeros-ganadores-so35</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 06:26 p. m.</t>
+          <t>31/05/2026 06:46 p. m.</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
@@ -2663,19 +2663,19 @@
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Paloma Valencia anuncia su apoyo a Abelardo de la Espriella para la segunda vuelta</t>
+          <t>¿Cómo votaron los colombianos en España en las elecciones presidenciales? Resultados de preconteo</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/paloma-valencia-anuncia-su-apoyo-a-abelardo-de-la-espriella-para-la-segunda-vuelta-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/como-votaron-los-colombianos-en-espana-en-las-elecciones-presidenciales-de-2026-resultados-del-100-de-preconteo-rg10</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 06:07 p. m.</t>
+          <t>31/05/2026 06:41 p. m.</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -2690,19 +2690,19 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Abelardo de la Espriella habla tras confirmarse segunda vuelta presidencial contra Iván Cepeda</t>
+          <t>"Colombianos, hemos perdido": Álvaro Uribe tras la primera vuelta de las elecciones presidenciales</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/abelardo-de-la-espriella-habla-tras-confirmarse-segunda-vuelta-presidencial-contra-ivan-cepeda-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/colombianos-hemos-perdido-alvaro-uribe-tras-la-primera-vuelta-presidencial-en-colombia-rg10</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 05:55 p. m.</t>
+          <t>31/05/2026 06:36 p. m.</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
@@ -2717,19 +2717,19 @@
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Resultados elecciones Colombia: De la Espriella ganó en Antioquia en primera vuelta; Cepeda, segundo</t>
+          <t>Elecciones en Colombia: voto en blanco vence a seis candidatos y supera los 400.000 sufragios</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/resultados-elecciones-colombia-de-la-espriella-gano-en-antioquia-en-primera-vuelta-cepeda-segundo-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/elecciones-en-colombia-voto-en-blanco-vence-a-seis-candidatos-y-supera-los-400-000-sufragios-rg10</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 05:44 p. m.</t>
+          <t>31/05/2026 06:32 p. m.</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -2744,19 +2744,19 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Elecciones en Colombia: así votó la región Caribe en la primera vuelta presidencial</t>
+          <t>Sergio Fajardo habla tras su derrota en las elecciones presidenciales: "No nos vamos a resignar"</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/elecciones-en-colombia-asi-voto-la-region-caribe-en-la-primera-vuelta-presidencial-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/sergio-fajardo-habla-tras-su-derrota-en-las-elecciones-presidenciales-de-2026-no-nos-vamos-a-resignar-rg10</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 05:42 p. m.</t>
+          <t>31/05/2026 06:30 p. m.</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
@@ -2771,19 +2771,19 @@
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Abelardo de la Espriella e Iván Cepeda pasan a segunda vuelta en elecciones Colombia 2026</t>
+          <t>"Yo sé que Iván es un hombre decente": Claudia López tras finalizar la primera vuelta presidencial</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/abelardo-de-la-espriella-e-ivan-cepeda-pasan-a-segunda-vuelta-en-elecciones-colombia-2026-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/yo-se-que-ivan-es-un-hombre-decente-claudia-lopez-tras-finalizar-la-primera-vuelta-presidencial-rg10</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 05:40 p. m.</t>
+          <t>31/05/2026 06:26 p. m.</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -2798,19 +2798,19 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Ministerio de Defensa entrega balance tras elecciones presidenciales: “La alerta se eleva aun más”</t>
+          <t>Paloma Valencia anuncia su apoyo a Abelardo de la Espriella para la segunda vuelta</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/colombia/ministerio-de-defensa-entrega-balance-tras-elecciones-presidenciales-la-alerta-se-eleva-aun-mas</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/paloma-valencia-anuncia-su-apoyo-a-abelardo-de-la-espriella-para-la-segunda-vuelta-rg10</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 05:40 p. m.</t>
+          <t>31/05/2026 06:07 p. m.</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
@@ -2825,19 +2825,19 @@
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>¿Cuándo será la segunda vuelta presidencial en Colombia? Esto dice el calendario electoral</t>
+          <t>Abelardo de la Espriella habla tras confirmarse segunda vuelta presidencial contra Iván Cepeda</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/cuando-sera-la-segunda-vuelta-presidencial-en-colombia-esto-dice-el-calendario-electoral-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/abelardo-de-la-espriella-habla-tras-confirmarse-segunda-vuelta-presidencial-contra-ivan-cepeda-rg10</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 05:35 p. m.</t>
+          <t>31/05/2026 05:55 p. m.</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -2852,19 +2852,19 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Así fue la votación en Bogotá: resultados de las elecciones presidenciales Colombia 2026</t>
+          <t>Resultados elecciones Colombia: De la Espriella ganó en Antioquia en primera vuelta; Cepeda, segundo</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/elecciones-presidenciales-colombia-2026-resultados-de-la-votacion-en-bogota-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/resultados-elecciones-colombia-de-la-espriella-gano-en-antioquia-en-primera-vuelta-cepeda-segundo-rg10</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 05:14 p. m.</t>
+          <t>31/05/2026 05:44 p. m.</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
@@ -2879,19 +2879,19 @@
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Jurados de votación llegaron ebrios a mesas electorales en Antioquia: serán sancionados</t>
+          <t>Elecciones en Colombia: así votó la región Caribe en la primera vuelta presidencial</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/jurados-de-votacion-llegaron-en-ebrios-a-mesas-electorales-en-antioquia-seran-sancionados-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/elecciones-en-colombia-asi-voto-la-region-caribe-en-la-primera-vuelta-presidencial-rg10</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 04:33 p. m.</t>
+          <t>31/05/2026 05:42 p. m.</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -2906,19 +2906,19 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Registrador Hernán Penagos da balance tras el cierre de urnas en las elecciones presidenciales</t>
+          <t>Abelardo de la Espriella e Iván Cepeda pasan a segunda vuelta en elecciones Colombia 2026</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/registrador-hernan-penagos-da-balance-tras-el-cierre-de-urnas-en-las-elecciones-presidenciales-rg10</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/abelardo-de-la-espriella-e-ivan-cepeda-pasan-a-segunda-vuelta-en-elecciones-colombia-2026-rg10</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 04:23 p. m.</t>
+          <t>31/05/2026 04:33 p. m.</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
@@ -2933,19 +2933,19 @@
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Gobierno de Ecuador oficializa el fin de los aranceles del 100 % a las importaciones de Colombia</t>
+          <t>Registrador Hernán Penagos da balance tras el cierre de urnas en las elecciones presidenciales</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiascaracol.com/mundo/gobierno-de-ecuador-oficializa-el-fin-de-los-aranceles-del-100-a-las-importaciones-de-colombia-cb20</t>
+          <t>https://www.noticiascaracol.com/politica/elecciones-colombia/registrador-hernan-penagos-da-balance-tras-el-cierre-de-urnas-en-las-elecciones-presidenciales-rg10</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 08:52 p. m.</t>
+          <t>31/05/2026 09:46 p. m.</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -2955,24 +2955,24 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Mapa Electoral 2026: así votó Colombia en las elecciones presidenciales del 31 de mayo</t>
+          <t>Presidente de Ecuador felicita a De La Espriella por "una gran victoria" en primera vuelta</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/politica/mapa-electoral-2026-que-candidato-gano-en-cada-departamento/</t>
+          <t>https://www.bluradio.com/nacion/elecciones/promesas-y-propuestas/presidente-de-ecuador-felicita-a-de-la-espriella-por-una-gran-victoria-en-primera-vuelta-cb20</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 08:36 p. m.</t>
+          <t>31/05/2026 09:42 p. m.</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
@@ -2982,24 +2982,24 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Cundinamarca nuevamente inclinó su voto por la derecha: así fue la jornada electoral</t>
+          <t>Municipios afectados por grupos armados marcaron fuerte votación por De la Espriella en el Caribe</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cundinamarca/cundinamarca-nuevamente-inclino-su-voto-por-la-derecha-asi-fue-la-jornada-electoral/</t>
+          <t>https://www.bluradio.com/regiones/caribe/municipios-afectados-por-grupos-armados-marcaron-fuerte-votacion-por-de-la-espriella-en-el-caribe-rg10</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 08:31 p. m.</t>
+          <t>31/05/2026 09:41 p. m.</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3009,24 +3009,24 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Resultados elecciones en Colombia 2026 EN VIVO: estas son las cifras finales del preconteo</t>
+          <t>El alcalde de Bogotá pide respetar los resultados de las presidenciales en Colombia</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/politica/elecciones-colombia-2026/resultados-elecciones-presidenciales-colombia-2026-en-vivo-quien-gano/</t>
+          <t>https://www.bluradio.com/nacion/elecciones/el-alcalde-de-bogota-pide-respetar-los-resultados-de-las-presidenciales-en-colombia-cb20</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 08:22 p. m.</t>
+          <t>31/05/2026 09:26 p. m.</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
@@ -3036,24 +3036,24 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>¿De la Espriella o Cepeda?: este sería la ruta de las fórmulas a la Vicepresidencia</t>
+          <t>No solo es caminar: la tecnología en prótesis que devuelve el deporte y la independencia a amputados</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/politica/elecciones-colombia-2026/juan-daniel-oviedo-edna-bonilla-y-leonardo-huerta-este-seria-su-camino-entre-abelardo-de-la-espriella-o-ivan-cepeda-noticias-hoy/</t>
+          <t>https://www.bluradio.com/tecnologia/ciencia/no-solo-es-caminar-la-tecnologia-en-protesis-que-devuelve-el-deporte-y-la-independencia-a-amputados-so35</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 08:19 p. m.</t>
+          <t>31/05/2026 09:25 p. m.</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3063,24 +3063,24 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Edgar Morin, el caminante (Homenaje)</t>
+          <t>"Hoy fue una jornada democrática impecable": Fedepartamentos rechaza declaraciones de Petro</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/el-magazin-cultural/edgar-morin-el-caminante-homenaje/</t>
+          <t>https://www.bluradio.com/nacion/elecciones/hoy-fue-una-jornada-democratica-impecable-fedepartamentos-rechaza-declaraciones-de-petro-rg10</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 08:12 p. m.</t>
+          <t>31/05/2026 09:16 p. m.</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
@@ -3090,24 +3090,24 @@
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Elecciones a la presidencia: en Cali y Valle, Cepeda obtuvo la mayoría de los votos</t>
+          <t>Iván Duque a De La Espriella: "La unidad de quienes creemos en la democracia"</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/elecciones-a-la-presidencia-los-resultados-en-cali-y-valle-del-cauca/</t>
+          <t>https://www.bluradio.com/nacion/elecciones/ivan-duque-a-de-la-espriella-la-unidad-de-quienes-creemos-en-la-democracia-cb20</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 08:12 p. m.</t>
+          <t>31/05/2026 09:06 p. m.</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3117,24 +3117,24 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Nicolás Maduro y su esposa “elevan oraciones” antes de su próxima audiencia en Nueva York</t>
+          <t>Hora y dónde ver EN VIVO el amistoso Colombia vs. Costa Rica previo al Mundial</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/mundo/venezuela/nicolas-maduro-y-su-esposa-dicen-tener-una-fe-inquebrantable-en-la-victoria-de-la-verdad/</t>
+          <t>https://www.bluradio.com/deportes/futbol/hora-y-donde-ver-en-vivo-el-amistoso-colombia-vs-costa-rica-previo-al-mundial-so35</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 08:08 p. m.</t>
+          <t>31/05/2026 09:04 p. m.</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
@@ -3144,24 +3144,24 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Iván Cepeda se pronuncia tras quedar segundo en las votaciones: negó resultados de preconteo</t>
+          <t>¿Puede cambiar el puesto de votación para elecciones de segunda vuelta? Esto dice la Registraduría</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/politica/elecciones-colombia-2026/ivan-cepeda-se-pronuncia-tras-quedar-segundo-en-las-votaciones-nego-resultados-de-preconteo/</t>
+          <t>https://www.bluradio.com/nacion/elecciones/puede-cambiar-el-puesto-de-votacion-para-elecciones-de-segunda-vuelta-esto-dice-la-registraduria-so35</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 08:01 p. m.</t>
+          <t>31/05/2026 09:01 p. m.</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3171,24 +3171,24 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Presunta participación en política y delitos electorales: el saldo judicial de la jornada</t>
+          <t>Juez deja en libertad a teniente y suboficial acusados de desobedecer orden militar en Nariño</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/judicial/presunta-participacion-en-politica-y-delitos-electorales-el-saldo-judicial-de-la-jornada/</t>
+          <t>https://www.bluradio.com/regiones/pacifico/juez-deja-en-libertad-a-teniente-y-suboficial-acusados-de-desobedecer-orden-militar-en-narino-rg10</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 08:00 p. m.</t>
+          <t>31/05/2026 08:35 p. m.</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
@@ -3198,24 +3198,24 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>El Mundial viene con instrucciones nuevas</t>
+          <t>Brasil no perdona y golea a Panamá como preparación para el Mundial</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/opinion/columnistas/antonio-casale/el-mundial-viene-con-instrucciones-nuevas-columna-de-antonio-casale/</t>
+          <t>https://www.bluradio.com/deportes/futbol/brasil-no-perdona-y-golea-a-panama-como-preparacion-para-el-mundial-cb20</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 08:43 p. m.</t>
+          <t>31/05/2026 08:26 p. m.</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3225,24 +3225,24 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>¿Cuántos votos sacó Petro en primera vuelta 2022? Diferencia de votos con De la Espriella y Cepeda</t>
+          <t>Se acorta diferencia de votos entre el Petrismo y el Charismo en Barranquilla: así quedó la cuenta</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/06/01/cuantos-votos-saco-petro-en-primera-vuelta-2022-diferencia-de-votos-con-de-la-espriella-y-cepeda/</t>
+          <t>https://www.bluradio.com/regiones/caribe/se-acorta-diferencia-de-votos-entre-el-petrismo-y-el-charismo-en-barranquilla-asi-quedo-la-cuenta-rg10</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 08:39 p. m.</t>
+          <t>31/05/2026 08:23 p. m.</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
@@ -3252,24 +3252,24 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>🔴 Boletín ELECCIONES 2026 EN VIVO: Confirmada segunda vuelta Abelardo de la Espriella e Iván Cepeda</t>
+          <t>De La Espriella ofrece su "respeto" a Paloma Valencia y señala a Cepeda de "impedido"</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/31/resultados-registraduria-en-vivo-ultimo-boletin-y-conteo-de-votos-en-directo-quien-lidera/</t>
+          <t>https://www.bluradio.com/nacion/elecciones/promesas-y-propuestas/de-la-espriella-ofrece-su-respeto-a-paloma-valencia-y-senala-a-cepeda-de-impedido-rs15</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 08:10 p. m.</t>
+          <t>31/05/2026 09:45 p. m.</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -3279,24 +3279,24 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Petro quiere perpetuarse en el poder desconociendo voluntad del pueblo colombiano: De La Espriella</t>
+          <t>El 21 de junio Colombia profundizará la polarización</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/06/01/petro-quiere-perpetuarse-en-el-poder-desconociendo-voluntad-del-pueblo-colombiano-de-la-espriella/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-06-01/el-21-de-junio-colombia-profundizara-la-polarizacion.html</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 07:59 p. m.</t>
+          <t>31/05/2026 09:30 p. m.</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
@@ -3306,24 +3306,24 @@
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Segunda vuelta presidencial: ¿Cuándo se posesiona el nuevo presidente de Colombia 2026?</t>
+          <t>“Creamos soluciones que afectan a la vida diaria de las personas”</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/06/01/segunda-vuelta-presidencial-cuando-se-posesiona-el-nuevo-presidente-de-colombia-2026/</t>
+          <t>https://elpais.com/aniversario/branded/un-futuro-por-escribir/2026-06-01/creamos-soluciones-que-afectan-a-la-vida-diaria-de-las-personas.html?autoplay=1</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 07:50 p. m.</t>
+          <t>31/05/2026 09:08 p. m.</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -3333,24 +3333,24 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Iván Cepeda aseguró que hay un desfase en los resultados preliminares: “son 885.000 personas”</t>
+          <t>Javier Aguirre elige a los 26 futbolistas de la selección mexicana para el Mundial de 2026</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/06/01/ivan-cepeda-desconoce-resultados-preliminares-y-asegura-que-hay-un-desfase-son-885000-votos/</t>
+          <t>https://elpais.com/mexico/2026-06-01/aguirre-elige-a-los-26-futbolistas-de-la-seleccion-mexicana-para-el-mundial-de-2026.html</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 07:50 p. m.</t>
+          <t>31/05/2026 08:01 p. m.</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
@@ -3360,24 +3360,24 @@
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>“Petro no sabe ni entiende lo que dice”: exregistrador Galindo por denuncia de fraude en elecciones</t>
+          <t>Petro se niega a aceptar los resultados de la primera vuelta</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/06/01/petro-no-sabe-ni-entiende-lo-que-dice-exregistrador-galindo-por-denuncia-de-fraude-en-elecciones/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-06-01/petro-se-niega-a-aceptar-el-conteo-provisional-de-la-primera-vuelta.html</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 07:30 p. m.</t>
+          <t>31/05/2026 07:54 p. m.</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3387,24 +3387,24 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>“Abelardo de la Espriella es un peligro para Colombia”: Claudia López</t>
+          <t>Las propuestas de Abelardo de la Espriella: seguridad de “mano dura”, reducción del Estado y libertades tributarias</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/06/01/abelardo-de-la-espriella-es-un-peligro-para-colombia-claudia-lopez/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-06-01/las-propuestas-de-abelardo-de-la-espriella-seguridad-de-mano-dura-reduccion-del-estado-y-libertades-tributarias.html</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 07:13 p. m.</t>
+          <t>31/05/2026 07:48 p. m.</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
@@ -3414,24 +3414,24 @@
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>El presidente Gustavo Petro no aceptó los resultados del preconteo electoral</t>
+          <t>Iván Cepeda cuestiona los resultados de la primera vuelta: “Solo nos pronunciaremos cuando las comisiones escrutadoras aclaren nuestras dudas”</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/06/01/el-presidente-gustavo-petro-no-acepto-los-resultados-del-preconteo-electoral/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-06-01/ivan-cepeda-pone-en-duda-los-datos-conocidos-de-la-primera-vuelta-solo-nos-pronunciaremos-sobre-los-resultados-cuando-las-comisiones-escrutadoras-aclaren-nuestras-dudas.html</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 07:10 p. m.</t>
+          <t>31/05/2026 07:45 p. m.</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3441,24 +3441,24 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Último boletín elecciones ATLÁNTICO: Registraduría confirma quién ganó en Barranquilla y la región</t>
+          <t>Las propuestas de Iván Cepeda: tres revoluciones, rechazo a la militarización y continuidad</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/31/elecciones-2026-en-vivo-barranquilla-asi-avanzan-las-votaciones-hoy-31-de-mayo-de-2026/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-06-01/las-propuestas-de-ivan-cepeda-tres-revoluciones-rechazo-a-la-militarizacion-y-continuidad.html</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 07:01 p. m.</t>
+          <t>31/05/2026 07:34 p. m.</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
@@ -3468,24 +3468,24 @@
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>Hemos perdido, asumo mi responsabilidad: Álvaro Uribe tras resultados de primera vuelta presidencial</t>
+          <t>Iván Cepeda, el candidato inalterable que promete continuidad</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/06/01/hemos-perdido-asumo-mi-responsabilidad-alvaro-uribe-tras-resultados-de-primera-vuelta-presidencial/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-06-01/ivan-cepeda-el-candidato-inalterable-que-promete-continuidad.html</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 07:01 p. m.</t>
+          <t>31/05/2026 07:22 p. m.</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -3495,24 +3495,24 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>¿Cómo votaron los departamentos en las elecciones 2026? Así quedó el mapa político de Colombia</t>
+          <t>Sergio Fajardo valoriza su millón de votos: “Vamos a ser protagonistas de estas elecciones”</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/06/01/como-votaron-los-departamentos-en-las-elecciones-2026-asi-quedo-el-mapa-politico-de-colombia/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-06-01/sergio-fajardo-valoriza-su-millon-de-votos-vamos-a-ser-protagonistas-de-estas-elecciones.html</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 07:00 p. m.</t>
+          <t>31/05/2026 07:18 p. m.</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
@@ -3522,24 +3522,24 @@
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>“Seremos protagonistas de lo que falta en estas elecciones”: Sergio Fajardo</t>
+          <t>Abelardo de la Espriella tras su victoria y los cuestionamientos de Petro: “Defenderemos la democracia por la razón o por la fuerza”</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/06/01/seremos-protagonistas-de-lo-que-falta-en-estas-elecciones-sergio-fajardo/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-06-01/abelardo-de-la-espriella-celebra-su-victoria-en-la-primera-vuelta-vamos-a-derrotar-la-tirania-y-el-absolutismo.html</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 06:48 p. m.</t>
+          <t>31/05/2026 07:06 p. m.</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -3549,24 +3549,24 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Así quedó el último boletín de la Registraduría: ¿Cuántos votos sacaron De la Espriella y Cepeda?</t>
+          <t>Paloma Valencia acepta su derrota y apoya a Abelardo de la Espriella</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/31/asi-quedo-el-ultimo-boletin-de-la-registraduria-cuantos-votos-sacaron-de-la-espriella-y-cepeda/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-06-01/paloma-valencia-acepta-su-derrota-y-apoya-a-abelardo-de-la-espriella.html</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 06:34 p. m.</t>
+          <t>31/05/2026 06:35 p. m.</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>“Yo, como proyecto político, me debo a Bogotá”: Juan Daniel Oviedo tras primera vuelta presidencial</t>
+          <t>El presidente Kast llama a la “esperanza” a horas de su primera Cuenta Pública, mientras la desaprobación aumenta a un 53%</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/31/yo-como-proyecto-politico-me-debo-a-bogota-juan-daniel-oviedo-tras-primera-vuelta-presidencial/</t>
+          <t>https://elpais.com/chile/2026-05-31/el-presidente-kast-llama-a-la-esperanza-a-horas-de-su-primera-cuenta-publica-mientras-la-desaprobacion-aumenta-a-un-53.html</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 06:32 p. m.</t>
+          <t>31/05/2026 06:23 p. m.</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -3603,24 +3603,24 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Así quedó la votación en Magdalena: Últimos resultados de la Registraduría</t>
+          <t>Abelardo de la Espriella, el abogado del diablo que quiere ser presidente de Colombia</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/31/asi-quedo-la-votacion-en-magdalena-ultimos-resultados-de-la-registraduria/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/abelardo-de-la-espriella-abogado-del-diablo-que-quiere-ser-presidente-de-colombia.html</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 06:26 p. m.</t>
+          <t>31/05/2026 06:15 p. m.</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
@@ -3630,24 +3630,24 @@
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>Jornada electoral transcurrió con total normalidad en Antioquia pese a denuncias de constreñimiento</t>
+          <t>Las claves de la primera vuelta en Colombia: el auge ultra, la unidad en la izquierda y la importancia de los votos del centro</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/31/jornada-electoral-transcurrio-con-total-normalidad-en-antioquia-pese-a-denuncias-de-constrenimiento/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/las-claves-de-la-primera-vuelta-en-colombia-el-auge-ultra-unidad-en-la-izquierda-y-los-votos-del-centro-claves.html</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 06:26 p. m.</t>
+          <t>31/05/2026 06:05 p. m.</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -3657,24 +3657,24 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Paloma Valencia anunció respaldo presidencial a Abelardo de la Espriella en la segunda vuelta</t>
+          <t>La izquierda de Iván Cepeda se ve obligada a remontar para asegurar un segundo Gobierno progresista</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/31/paloma-valencia-anuncio-respaldo-a-presidencial-abelardo-de-la-espriella-en-la-segunda-vuelta/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/la-izquierda-de-ivan-cepeda-se-ve-obligada-a-remontar-para-asegurar-un-segundo-gobierno-progresista.html</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 06:11 p. m.</t>
+          <t>31/05/2026 06:02 p. m.</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
@@ -3684,17 +3684,17 @@
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>Reacciones a la segunda vuelta presidencial entre de Abelardo de la Espriella e Iván Cepeda</t>
+          <t>De la Espriella y Cepeda se disputarán la presidencia de Colombia mientras Petro cuestiona los resultados</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/31/reacciones-a-la-segunda-vuelta-presidencial-entre-de-abelardo-de-la-espriella-e-ivan-cepeda/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/de-la-espriella-y-cepeda-se-disputaran-la-presidencia-de-colombia-con-un-pais-partido-en-dos.html</t>
         </is>
       </c>
     </row>
@@ -3711,24 +3711,24 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Capturaron a tres personas e impusieron 29 comparendos durante las elecciones en el Tolima</t>
+          <t>La derecha colombiana se vuelca con el ultra Abelardo de la Espriella y da la espalda a Álvaro Uribe</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/31/capturaron-a-tres-personas-e-impusieron-29-comparendos-durante-las-elecciones-en-el-tolima/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/la-derecha-colombiana-se-vuelca-con-el-ultra-abelardo-de-la-espriella-y-da-la-espalda-a-alvaro-uribe.html</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 05:35 p. m.</t>
+          <t>31/05/2026 05:00 p. m.</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
@@ -3738,24 +3738,24 @@
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>Elecciones Cúcuta HOY: ¿Quién ganó en el departamento Norte de Santander? Resultados Registraduría</t>
+          <t>Las gafas más icónicas de Ray-Ban bajan 80 euros en AliExpress: una oferta imbatible por tiempo limitado</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>https://caracol.com.co/2026/05/31/votaciones-en-cucuta-hoy-horario-para-votar-y-ultimas-noticias-de-elecciones-en-norte-de-santander/</t>
+          <t>https://elpais.com/hemeroteca/2026-06-01/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 08:40 p. m.</t>
+          <t>31/05/2026 04:29 p. m.</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -3765,24 +3765,24 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>La dura advertencia de Abelardo De la Espriella a Petro: “el pueblo lo va enfrentar”</t>
+          <t>Muere bajo custodia del régimen de Ortega el líder indígena nicaragüense Brooklyn Rivera tras casi tres años de arresto político</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/politica/elecciones/2026/05/31/la-dura-advertencia-de-abelardo-de-la-espriella-a-petro-el-pueblo-lo-va-enfrentar/</t>
+          <t>https://elpais.com/america/2026-05-31/muere-bajo-custodia-del-regimen-de-ortega-el-lider-indigena-nicaraguense-brooklyn-rivera-tras-casi-tres-anos-de-arresto-politico.html</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 08:40 p. m.</t>
+          <t>31/05/2026 04:09 p. m.</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
@@ -3792,24 +3792,24 @@
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>Elecciones</t>
+          <t>Almería-Castellón y Málaga-Las Palmas, las semifinales por el ascenso a Primera División</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/politica/elecciones/</t>
+          <t>https://elpais.com/deportes/futbol/2026-05-31/almeria-castellon-y-malaga-las-palmas-las-semifinales-por-el-ascenso-a-primera-division.html</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 08:21 p. m.</t>
+          <t>31/05/2026 03:59 p. m.</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -3819,24 +3819,24 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Iván Duque alerta sobre “amenaza” de Gustavo Petro a la democracia tras elecciones</t>
+          <t>Resultados de las elecciones en Colombia 2026, en vivo | Abelardo de la Espriella: “Petro y Cepeda son un par de bandidos que vamos a jubilar”</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/politica/elecciones/2026/05/31/ivan-duque-alerta-sobre-amenaza-de-gustavo-petro-a-la-democracia-tras-elecciones/</t>
+          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/resultados-de-las-elecciones-colombia-2026-en-vivo.html</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 08:21 p. m.</t>
+          <t>31/05/2026 12:14 p. m.</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
@@ -3846,24 +3846,24 @@
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>Super Astro Luna: número y signo ganador del sorteo del domingo 31 de mayo de 2026</t>
+          <t>Diez cosas que los correctores de la Selectividad aconsejan hacer (o evitar) en los exámenes de la PAU</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/loterias/2026/05/31/super-astro-luna-numero-y-signo-ganador-del-sorteo-del-domingo-31-de-mayo-de-2026/</t>
+          <t>https://elpais.com/educacion/2026-05-31/diez-cosas-que-los-correctores-de-la-selectividad-aconsejan-hacer-o-evitar-en-los-examenes-de-la-pau.html</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 08:21 p. m.</t>
+          <t>31/05/2026 10:33 a. m.</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -3873,24 +3873,24 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Loterias</t>
+          <t>Cabeza dura y puños de acero: Rafa Jódar remonta a Carreño y tiene derecho a soñar</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/loterias/</t>
+          <t>https://elpais.com/deportes/tenis/2026-05-31/rafa-jodar-remonta-a-carreno-y-se-endurece-rumbo-a-cuartos.html</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 08:21 p. m.</t>
+          <t>31/05/2026 08:58 a. m.</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
@@ -3900,24 +3900,24 @@
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>Resultado Caribeña Noche: qué cayó hoy domingo 31 de mayo de 2026</t>
+          <t>Marco Bezzecchi y Aprilia conquistan por primera vez el GP de Italia</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/loterias/2026/05/31/resultado-caribena-noche-que-cayo-hoy-domingo-31-de-mayo-de-2026/</t>
+          <t>https://elpais.com/deportes/motociclismo/2026-05-31/marco-bezzecchi-y-aprilia-conquistan-por-primera-vez-el-gp-de-italia.html</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 04:55 p. m.</t>
+          <t>31/05/2026 07:55 a. m.</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -3927,24 +3927,24 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Capturan a alias ‘Chalia’ en el Chocó</t>
+          <t>Miles de personas salen a la calle en Madrid contra la política sanitaria de Ayuso: “Ahoga la pública para engordar los seguros privados”</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/31/capturan-a-alias-chalia-en-el-choco/</t>
+          <t>https://elpais.com/espana/madrid/2026-05-31/miles-de-personas-salen-a-la-calle-en-madrid-contra-la-politica-sanitaria-de-ayuso-ahoga-la-publica-para-engordar-los-seguros-privados.html</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 04:55 p. m.</t>
+          <t>31/05/2026 07:39 a. m.</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
@@ -3954,24 +3954,24 @@
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sánchez pide tiempo frente a la oposición “marrullera” que quiere “derribar” al Gobierno con “malas artes”</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/</t>
+          <t>https://elpais.com/espana/2026-05-31/sanchez-cierra-el-congreso-de-las-juventudes-socialistas-en-madrid.html</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 04:14 p. m.</t>
+          <t>31/05/2026 07:01 a. m.</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -3981,24 +3981,24 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Elecciones transparente y tranquilas: balance de observadores de Unión Europea</t>
+          <t>Vuelta de tuerca en el tumor más letal: una terapia dirigida logra duplicar la supervivencia en el cáncer de páncreas</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/31/elecciones-transparente-y-tranquilas-balance-de-observadores-de-union-europea/</t>
+          <t>https://elpais.com/salud-y-bienestar/2026-05-31/vuelta-de-tuerca-en-el-tumor-mas-letal-una-terapia-dirigida-logra-duplicar-la-supervivencia-en-el-cancer-de-pancreas.html</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 03:38 p. m.</t>
+          <t>31/05/2026 06:46 a. m.</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
@@ -4008,24 +4008,24 @@
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>Habitantes de Islas del Rosario, en Cartagena, advierten que no participarán en votaciones por falta de energía</t>
+          <t>780 detenidos y más de 200 heridos durante las celebraciones de la victoria del PSG en la Champions</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/31/habitantes-de-islas-del-rosario-en-cartagena-advierten-que-no-participaran-en-votaciones-por-falta-de-energia/</t>
+          <t>https://elpais.com/deportes/futbol/2026-05-30/mas-de-un-centenar-de-detenidos-en-paris-en-los-incidentes-producidos-tras-la-victoria-del-psg-en-la-champions.html</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 03:26 p. m.</t>
+          <t>30/05/2026 10:30 p. m.</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -4035,24 +4035,24 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Emergencia en Quindío: vehículo choca contra una fonda en el sector de Barragán</t>
+          <t>‘Cape Fear’ en Apple TV, ‘La casa del dragón’ en HBO Max y otras series recomendadas para junio</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/31/emergencia-en-quindio-vehiculo-choca-contra-una-fonda-en-el-sector-de-barragan/</t>
+          <t>https://elpais.com/television/series/2026-05-31/cape-fear-en-apple-tv-la-casa-del-dragon-en-hbo-max-y-otras-series-recomendadas-para-junio.html</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 03:09 p. m.</t>
+          <t>30/05/2026 04:51 p. m.</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
@@ -4062,24 +4062,24 @@
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>Procuraduría abrió investigación al ministro Sanguino por posible participación en política</t>
+          <t>Bad Bunny en Madrid: el alucinante jolgorio del perreo y el amor</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/31/procuraduria-abrio-investigacion-al-ministro-sanguino-por-posible-participacion-en-politica/</t>
+          <t>https://elpais.com/cultura/2026-05-30/bad-bunny-en-madrid-el-alucinante-jolgorio-del-perreo-y-el-amor.html</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 02:28 p. m.</t>
+          <t>31/05/2026 09:43 p. m.</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -4089,24 +4089,24 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Medicina legal inicia proceso de identificación de los cuerpos de 48 disidentes</t>
+          <t>Ocho capturas y 10 noticias criminales por presuntos delitos electorales: Fiscalía</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/31/medicina-legal-inicia-proceso-de-identificacion-de-los-cuerpos-de-48-disidentes/</t>
+          <t>https://caracol.com.co/2026/06/01/ocho-capturas-10-noticias-criminales-por-presuntos-delitos-electorales-fiscalia/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 02:26 p. m.</t>
+          <t>31/05/2026 09:25 p. m.</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
@@ -4116,24 +4116,24 @@
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>Santander, entre los departamentos con fallas en redes de telecomunicaciones durante la jornada electoral</t>
+          <t>Human Rights Watch pide proteger Registraduría tras desconocimiento de resultado electoral de Petro</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/31/santander-entre-los-departamentos-con-fallas-en-redes-de-telecomunicaciones-durante-la-jornada-electoral/</t>
+          <t>https://caracol.com.co/2026/06/01/human-rights-watch-pide-proteger-registraduria-tras-desconocimiento-de-resultado-electoral-de-petro/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 02:01 p. m.</t>
+          <t>31/05/2026 09:21 p. m.</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -4143,24 +4143,24 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Elecciones presidenciales: incautan $110 millones y capturan a una persona en operativos de la Policía</t>
+          <t>¿Cuánto les pagan a candidatos por la reposición de votos en Colombia? No todos llegaron al umbral</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/31/elecciones-presidenciales-incautan-110-millones-y-capturan-a-una-persona-en-operativos-de-la-policia/</t>
+          <t>https://caracol.com.co/2026/06/01/cuanto-les-pagan-a-candidatos-por-la-reposicion-de-votos-en-colombia-no-todos-llegaron-al-umbral/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 01:40 p. m.</t>
+          <t>31/05/2026 08:43 p. m.</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
@@ -4170,24 +4170,24 @@
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>Identifican grupo de personas que presuntamente compraba votos en Popayán</t>
+          <t>¿Cuántos votos sacó Petro en primera vuelta 2022? Diferencia de votos con De la Espriella y Cepeda</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/31/identifican-grupo-de-personas-que-presuntamente-compraba-votos-en-popayan/</t>
+          <t>https://caracol.com.co/2026/06/01/cuantos-votos-saco-petro-en-primera-vuelta-2022-diferencia-de-votos-con-de-la-espriella-y-cepeda/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 11:52 a. m.</t>
+          <t>31/05/2026 08:39 p. m.</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -4197,24 +4197,24 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Vanguardia</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Cárcel para médico de Bogotá por presunto abuso de dos niñas en las consultas</t>
+          <t>🔴 Boletín ELECCIONES 2026 EN VIVO: Confirmada segunda vuelta Abelardo de la Espriella e Iván Cepeda</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardia.com/colombia/2026/05/30/carcel-para-medico-de-bogota-por-presunto-abuso-de-dos-ninas-en-las-consultas/</t>
+          <t>https://caracol.com.co/2026/05/31/resultados-registraduria-en-vivo-ultimo-boletin-y-conteo-de-votos-en-directo-quien-lidera/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 08:35 p. m.</t>
+          <t>31/05/2026 08:10 p. m.</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
@@ -4224,24 +4224,24 @@
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>Brasil no perdona y golea a Panamá como preparación para el Mundial</t>
+          <t>Petro quiere perpetuarse en el poder desconociendo voluntad del pueblo colombiano: De La Espriella</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/deportes/futbol/brasil-no-perdona-y-golea-a-panama-como-preparacion-para-el-mundial-cb20</t>
+          <t>https://caracol.com.co/2026/06/01/petro-quiere-perpetuarse-en-el-poder-desconociendo-voluntad-del-pueblo-colombiano-de-la-espriella/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 08:26 p. m.</t>
+          <t>31/05/2026 07:59 p. m.</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -4251,24 +4251,24 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Se acorta diferencia de votos entre el Petrismo y el Charismo en Barranquilla: así quedó la cuenta</t>
+          <t>Segunda vuelta presidencial: ¿Cuándo se posesiona el nuevo presidente de Colombia 2026?</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/regiones/caribe/se-acorta-diferencia-de-votos-entre-el-petrismo-y-el-charismo-en-barranquilla-asi-quedo-la-cuenta-rg10</t>
+          <t>https://caracol.com.co/2026/06/01/segunda-vuelta-presidencial-cuando-se-posesiona-el-nuevo-presidente-de-colombia-2026/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 08:23 p. m.</t>
+          <t>31/05/2026 07:50 p. m.</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
@@ -4278,24 +4278,24 @@
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>De La Espriella ofrece su "respeto" a Paloma Valencia y señala a Cepeda de "impedido"</t>
+          <t>Iván Cepeda aseguró que hay un desfase en los resultados preliminares: “son 885.000 personas”</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/elecciones/promesas-y-propuestas/de-la-espriella-ofrece-su-respeto-a-paloma-valencia-y-senala-a-cepeda-de-impedido-rs15</t>
+          <t>https://caracol.com.co/2026/06/01/ivan-cepeda-desconoce-resultados-preliminares-y-asegura-que-hay-un-desfase-son-885000-votos/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 07:58 p. m.</t>
+          <t>31/05/2026 07:50 p. m.</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -4305,24 +4305,24 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Cepeda llama a De La Espriella como “estafador de estafadores” y aún no reconoce resultados</t>
+          <t>“Petro no sabe ni entiende lo que dice”: exregistrador Galindo por denuncia de fraude en elecciones</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/elecciones/cepeda-llama-a-de-la-espriella-como-estafador-de-estafadores-y-aun-no-reconoce-resultados-rs15</t>
+          <t>https://caracol.com.co/2026/06/01/petro-no-sabe-ni-entiende-lo-que-dice-exregistrador-galindo-por-denuncia-de-fraude-en-elecciones/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 07:53 p. m.</t>
+          <t>31/05/2026 07:30 p. m.</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
@@ -4332,24 +4332,24 @@
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>Aida Quilcué, fórmula vicepresidencial de Cepeda: "Aún no aceptamos resultados; tenemos que revisar"</t>
+          <t>“Abelardo de la Espriella es un peligro para Colombia”: Claudia López</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/elecciones/promesas-y-propuestas/aida-quilcue-formula-vicepresidencial-de-cepeda-aun-no-aceptamos-resultados-tenemos-que-revisar-so35</t>
+          <t>https://caracol.com.co/2026/06/01/abelardo-de-la-espriella-es-un-peligro-para-colombia-claudia-lopez/</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 07:51 p. m.</t>
+          <t>31/05/2026 07:13 p. m.</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -4359,24 +4359,24 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Abelardo De la Espriella y movimiento Creemos, grandes ganadores de la primera vuelta en Medellín</t>
+          <t>El presidente Gustavo Petro no aceptó los resultados del preconteo electoral</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/regiones/antioquia/abelardo-de-la-espriella-y-movimiento-creemos-grandes-ganadores-de-la-primera-vuelta-en-medellin-rg10</t>
+          <t>https://caracol.com.co/2026/06/01/el-presidente-gustavo-petro-no-acepto-los-resultados-del-preconteo-electoral/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 07:45 p. m.</t>
+          <t>31/05/2026 07:10 p. m.</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
@@ -4386,24 +4386,24 @@
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>No hay paso entre Manizales y Murillo: deslizamiento cerca al Nevado del Ruiz genera bloqueo</t>
+          <t>Último boletín elecciones ATLÁNTICO: Registraduría confirma quién ganó en Barranquilla y la región</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/no-hay-paso-entre-manizales-y-murillo-deslizamiento-cerca-al-nevado-del-ruiz-genera-bloqueo-rg10</t>
+          <t>https://caracol.com.co/2026/05/31/elecciones-2026-en-vivo-barranquilla-asi-avanzan-las-votaciones-hoy-31-de-mayo-de-2026/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 07:33 p. m.</t>
+          <t>31/05/2026 07:01 p. m.</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -4413,24 +4413,24 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>El uribismo perdió en Antioquia: De la Espriella arrasó con la candidatura de Paloma Valencia</t>
+          <t>Hemos perdido, asumo mi responsabilidad: Álvaro Uribe tras resultados de primera vuelta presidencial</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/regiones/antioquia/el-uribismo-perdio-en-antioquia-de-la-espriella-arraso-con-la-candidatura-de-paloma-valencia-rg10</t>
+          <t>https://caracol.com.co/2026/06/01/hemos-perdido-asumo-mi-responsabilidad-alvaro-uribe-tras-resultados-de-primera-vuelta-presidencial/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 07:23 p. m.</t>
+          <t>31/05/2026 07:01 p. m.</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
@@ -4440,24 +4440,24 @@
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>Dorado Noche, resultado del último sorteo hoy domingo 31 de mayo de 2026</t>
+          <t>¿Cómo votaron los departamentos en las elecciones 2026? Así quedó el mapa político de Colombia</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/dorado-noche-resultado-del-ultimo-sorteo-hoy-domingo-31-de-mayo-de-2026-so35</t>
+          <t>https://caracol.com.co/2026/06/01/como-votaron-los-departamentos-en-las-elecciones-2026-asi-quedo-el-mapa-politico-de-colombia/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 07:22 p. m.</t>
+          <t>31/05/2026 07:00 p. m.</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -4467,24 +4467,24 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Caribeña Noche, resultado del último sorteo hoy domingo 31 de mayo de 2026</t>
+          <t>“Seremos protagonistas de lo que falta en estas elecciones”: Sergio Fajardo</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/caribena-noche-resultado-del-ultimo-sorteo-hoy-domingo-31-de-mayo-de-2026-so35</t>
+          <t>https://caracol.com.co/2026/06/01/seremos-protagonistas-de-lo-que-falta-en-estas-elecciones-sergio-fajardo/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 07:21 p. m.</t>
+          <t>31/05/2026 06:48 p. m.</t>
         </is>
       </c>
       <c r="B149" s="6" t="inlineStr">
@@ -4494,24 +4494,24 @@
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>Sinuano Noche, resultados del último sorteo hoy domingo 31 de mayo de 2026</t>
+          <t>Así quedó el último boletín de la Registraduría: ¿Cuántos votos sacaron De la Espriella y Cepeda?</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/economia/juegos-de-azar/sinuano-noche-resultados-del-ultimo-sorteo-hoy-domingo-31-de-mayo-de-2026-so35</t>
+          <t>https://caracol.com.co/2026/05/31/asi-quedo-el-ultimo-boletin-de-la-registraduria-cuantos-votos-sacaron-de-la-espriella-y-cepeda/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 07:15 p. m.</t>
+          <t>31/05/2026 06:34 p. m.</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Petro no acepta resultados del preconteo y asegura que solo reconocerá escrutinios oficiales</t>
+          <t>“Yo, como proyecto político, me debo a Bogotá”: Juan Daniel Oviedo tras primera vuelta presidencial</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/elecciones/petro-no-acepta-resultados-del-preconteo-y-asegura-que-solo-reconocera-escrutinios-rg10</t>
+          <t>https://caracol.com.co/2026/05/31/yo-como-proyecto-politico-me-debo-a-bogota-juan-daniel-oviedo-tras-primera-vuelta-presidencial/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 08:31 p. m.</t>
+          <t>31/05/2026 06:32 p. m.</t>
         </is>
       </c>
       <c r="B151" s="6" t="inlineStr">
@@ -4548,24 +4548,24 @@
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>Si va al Mundial 2026: ¿Puede votar desde allí por Abelardo de la Espriella o Iván Cepeda?</t>
+          <t>Así quedó la votación en Magdalena: Últimos resultados de la Registraduría</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/si-va-al-mundial-2026-puede-votar-desde-alli-por-abelardo-de-la-espriella-o-ivan-cepeda/202633/</t>
+          <t>https://caracol.com.co/2026/05/31/asi-quedo-la-votacion-en-magdalena-ultimos-resultados-de-la-registraduria/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 08:10 p. m.</t>
+          <t>31/05/2026 06:26 p. m.</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -4575,24 +4575,24 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>¿Cuántos votos se necesitan para ganar la segunda vuelta en Colombia? Estas son las cuentas</t>
+          <t>Jornada electoral transcurrió con total normalidad en Antioquia pese a denuncias de constreñimiento</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/cuantos-votos-se-necesitan-para-ganar-la-segunda-vuelta-en-colombia/202622/</t>
+          <t>https://caracol.com.co/2026/05/31/jornada-electoral-transcurrio-con-total-normalidad-en-antioquia-pese-a-denuncias-de-constrenimiento/</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 08:01 p. m.</t>
+          <t>31/05/2026 06:26 p. m.</t>
         </is>
       </c>
       <c r="B153" s="6" t="inlineStr">
@@ -4602,24 +4602,24 @@
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>Abelardo de la Espriella habla desde un planchón en Barranquilla, tras su triunfo: “Que Estados Unidos y otros países vigilen la segunda vuelta”</t>
+          <t>Paloma Valencia anunció respaldo presidencial a Abelardo de la Espriella en la segunda vuelta</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/abelardo-de-la-espriella-habla-desde-un-planchon-en-barranquilla-tras-su-triunfo-en-la-primera-vuelta/202652/</t>
+          <t>https://caracol.com.co/2026/05/31/paloma-valencia-anuncio-respaldo-a-presidencial-abelardo-de-la-espriella-en-la-segunda-vuelta/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 07:58 p. m.</t>
+          <t>31/05/2026 09:37 p. m.</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -4629,24 +4629,24 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Juan Daniel Oviedo se pronuncia tras su derrota: “Es increíble que Colombia se debata su futuro alrededor de la homofobia y el machismo”</t>
+          <t>Capturan a 5 personas en Funza cuando atacaron lugar que almacenaba material electoral</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/juan-daniel-oviedo-se-pronuncia-tras-su-derrota-es-increible-que-colombia-se-debata-su-futuro-alrededor-de-la-homofobia-y-el-machismo/202659/</t>
+          <t>https://www.elespectador.com/bogota/capturan-a-5-personas-en-funza-cuando-atacaron-lugar-que-almacenaba-material-electoral/</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 07:58 p. m.</t>
+          <t>31/05/2026 09:00 p. m.</t>
         </is>
       </c>
       <c r="B155" s="6" t="inlineStr">
@@ -4656,24 +4656,24 @@
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>Elecciones Colombia en el exterior: mapa de cómo votaron los colombianos este domingo, 31 de mayo</t>
+          <t>Abelardo De la Espriella arremete contra Petro y Cepeda por no reconocer los resultados</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/elecciones-colombia-en-el-exterior-mapa-de-como-votaron-los-colombianos-este-domingo-31-de-mayo/202601/</t>
+          <t>https://www.elespectador.com/politica/elecciones-colombia-2026/abelardo-de-la-espriella-habla-sobre-petro-y-cepeda-por-no-reconocer-los-resultados-de-primera-vuelta-noticias-hoy/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 07:58 p. m.</t>
+          <t>31/05/2026 09:00 p. m.</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -4683,24 +4683,24 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Iván Cepeda cuestiona los resultados de la primera vuelta presidencial: advierte sobre un “desfase” de 885.000 cédulas en el censo electoral</t>
+          <t>Iván Cepeda ganó la primera vuelta en Bogotá, pero la derecha obtuvo más votos</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/ivan-cepeda-cuestiona-los-resultados-de-la-primera-vuelta-presidencial-advierte-sobre-un-desfase-de-885000-cedulas-en-el-censo-electoral/202600/</t>
+          <t>https://www.elespectador.com/bogota/ivan-cepeda-gano-la-primera-vuelta-en-bogota-pero-la-derecha-obtuvo-mas-votos/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 07:58 p. m.</t>
+          <t>31/05/2026 09:00 p. m.</t>
         </is>
       </c>
       <c r="B157" s="6" t="inlineStr">
@@ -4710,24 +4710,24 @@
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>Gustavo Petro reacciona a la primera vuelta presidencial: “No acepto los resultados del preconteo”</t>
+          <t>Paz, tierras y justicia transicional, la apuesta de Cepeda para llegar a la Casa de Nariño</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/gustavo-petro-reacciona-a-la-primera-vuelta-presidencial-no-acepto-los-resultados-del-preconteo/202631/</t>
+          <t>https://www.elespectador.com/colombia-20/paz-y-memoria/ivan-cepeda-las-propuestas-sobre-seguridad-y-paz-dialogos-con-grupos-armados-acuerdo-de-paz-y-la-jep-elecciones-2026/</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 06:58 p. m.</t>
+          <t>31/05/2026 08:58 p. m.</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -4737,24 +4737,24 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Segunda vuelta presidencial Colombia 2026: Fecha oficial y lo que debe saber</t>
+          <t>“‘Outsider’ pro-Trump gana primera vuelta”: la prensa internacional sobre Colombia</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/cuando-es-la-segunda-vuelta-presidencial-de-las-elecciones-en-colombia-2026-fechas-claves/202657/</t>
+          <t>https://www.elespectador.com/mundo/america/outsider-pro-trump-gana-primera-vuelta-la-prensa-internacional-sobre-colombia/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 06:58 p. m.</t>
+          <t>31/05/2026 08:57 p. m.</t>
         </is>
       </c>
       <c r="B159" s="6" t="inlineStr">
@@ -4764,24 +4764,24 @@
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>“SEMANA merece reconocimiento por informar con veracidad a sus lectores y por su compromiso con la independencia”: Andrei Roman, CEO de AtlasIntel</t>
+          <t>Estos fueron los resultados de la primera vuelta: De la Espriella y Cepeda pasan a segunda</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/confidenciales/articulo/semana-merece-reconocimiento-por-informar-con-veracidad-a-sus-lectores-y-por-su-compromiso-con-la-independencia-andrei-roman-ceo-de-atlasintel/202623/</t>
+          <t>https://www.elespectador.com/politica/elecciones-colombia-2026/resultados-elecciones-presidenciales-colombia-2026-en-vivo-quien-gano/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 06:58 p. m.</t>
+          <t>31/05/2026 08:52 p. m.</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -4791,24 +4791,24 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>“Ganó el doctor Abelardo de la Espriella. Cumplimos la palabra, votaremos por él y pedimos que se vote por él”: Álvaro Uribe</t>
+          <t>Mapa Electoral 2026: así votó Colombia en las elecciones presidenciales del 31 de mayo</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/gano-el-doctor-abelardo-de-la-espriella-cumplimos-la-palabra-votaremos-por-el-y-pedimos-que-se-vote-por-el-alvaro-uribe/202627/</t>
+          <t>https://www.elespectador.com/politica/mapa-electoral-2026-que-candidato-gano-en-cada-departamento/</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 06:58 p. m.</t>
+          <t>31/05/2026 08:36 p. m.</t>
         </is>
       </c>
       <c r="B161" s="6" t="inlineStr">
@@ -4818,24 +4818,24 @@
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>Quién es Iván Cepeda, el candidato del Pacto Histórico que va a segunda vuelta</t>
+          <t>Cundinamarca nuevamente inclinó su voto por la derecha: así fue la jornada electoral</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/quien-es-ivan-cepeda-biografia-trayectoria-profesional-y-politica-del-candidato-a-la-presidencia-de-colombia/202620/</t>
+          <t>https://www.elespectador.com/colombia/cundinamarca/cundinamarca-nuevamente-inclino-su-voto-por-la-derecha-asi-fue-la-jornada-electoral/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 06:58 p. m.</t>
+          <t>31/05/2026 08:22 p. m.</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -4845,24 +4845,24 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Quién es Abelardo de la Espriella, el candidato que busca la Presidencia en segunda vuelta</t>
+          <t>¿De la Espriella o Cepeda?: este sería la ruta de las fórmulas a la Vicepresidencia</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/quien-es-abelardo-de-la-espriella-el-candidato-que-busca-la-presidencia-en-segunda-vuelta/202634/</t>
+          <t>https://www.elespectador.com/politica/elecciones-colombia-2026/juan-daniel-oviedo-edna-bonilla-y-leonardo-huerta-este-seria-su-camino-entre-abelardo-de-la-espriella-o-ivan-cepeda-noticias-hoy/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 06:58 p. m.</t>
+          <t>31/05/2026 08:19 p. m.</t>
         </is>
       </c>
       <c r="B163" s="6" t="inlineStr">
@@ -4872,24 +4872,24 @@
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>Paloma Valencia reconoce derrota y anuncia su apoyo a Abelardo de la Espriella</t>
+          <t>Edgar Morin, el caminante (Homenaje)</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/paloma-valencia-reconoce-derrota-y-anuncia-apoya-a-abelardo-de-al-espriella/202623/</t>
+          <t>https://www.elespectador.com/el-magazin-cultural/edgar-morin-el-caminante-homenaje/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 06:58 p. m.</t>
+          <t>31/05/2026 09:35 p. m.</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -4904,19 +4904,19 @@
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>¿Se puede cambiar el puesto de votación para segunda vuelta presidencial? Registraduría responde</t>
+          <t>¿Quién es José Manuel Restrepo, la fórmula vicepresidencial de Abelardo de la Espriella?</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/se-puede-cambiar-el-puesto-de-votacion-para-segunda-vuelta-presidencial-registraduria-responde/202646/</t>
+          <t>https://www.semana.com/politica/articulo/quien-es-jose-manuel-restrepo-la-formula-vicepresidencial-de-abelardo-de-la-espriella/202615/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 04:58 p. m.</t>
+          <t>31/05/2026 08:58 p. m.</t>
         </is>
       </c>
       <c r="B165" s="6" t="inlineStr">
@@ -4931,19 +4931,19 @@
       </c>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>La Champions League se pronunció y eligió al mejor jugador de la temporada: no irá al Mundial 2026</t>
+          <t>Si va al Mundial 2026: ¿Puede votar desde allí por Abelardo de la Espriella o Iván Cepeda?</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/la-champions-league-se-pronuncio-y-eligio-el-mejor-jugador-de-la-temporada-no-ira-al-mundial-2026/202601/</t>
+          <t>https://www.semana.com/deportes/articulo/si-va-al-mundial-2026-puede-votar-desde-alli-por-abelardo-de-la-espriella-o-ivan-cepeda/202633/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 04:58 p. m.</t>
+          <t>31/05/2026 08:58 p. m.</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -4958,19 +4958,19 @@
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>¿Quién es Pilar Rueda, la esposa de Iván Cepeda? Así es la familia del candidato del Pacto Histórico</t>
+          <t>¿Cuántos votos se necesitan para ganar la segunda vuelta en Colombia? Estas son las cuentas</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/pilar-rueda-la-esposa-de-ivan-cepeda-asi-es-la-familia-del-candidato-del-pacto-historico/202650/</t>
+          <t>https://www.semana.com/politica/articulo/cuantos-votos-se-necesitan-para-ganar-la-segunda-vuelta-en-colombia/202622/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 04:58 p. m.</t>
+          <t>31/05/2026 08:58 p. m.</t>
         </is>
       </c>
       <c r="B167" s="6" t="inlineStr">
@@ -4985,19 +4985,19 @@
       </c>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>¿Quién es Ana Lucía Pineda, la esposa de Abelardo de la Espriella, candidato por la presidencia en Colombia?</t>
+          <t>Abelardo de la Espriella habla desde un planchón en Barranquilla, tras su triunfo: “Que Estados Unidos y otros países vigilen la segunda vuelta”</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/quien-es-ana-lucia-pineda-la-esposa-de-abelardo-de-la-espriella-candidato-por-la-presidencia-en-colombia/202645/</t>
+          <t>https://www.semana.com/politica/articulo/abelardo-de-la-espriella-habla-desde-un-planchon-en-barranquilla-tras-su-triunfo-en-la-primera-vuelta/202652/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 03:58 p. m.</t>
+          <t>31/05/2026 07:58 p. m.</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -5012,19 +5012,19 @@
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Vingegaard es campeón del Giro de Italia; Egan, fenomenal: es top 10 y aumenta su historia en el ciclismo mundial</t>
+          <t>Juan Daniel Oviedo se pronuncia tras su derrota: “Es increíble que Colombia se debata su futuro alrededor de la homofobia y el machismo”</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/ciclismo/articulo/vingegaard-es-campeon-del-giro-de-italia-y-egan-fenomenal-top-10-y-aumenta-su-historia-en-el-ciclismo-mundial/202625/</t>
+          <t>https://www.semana.com/politica/articulo/juan-daniel-oviedo-se-pronuncia-tras-su-derrota-es-increible-que-colombia-se-debata-su-futuro-alrededor-de-la-homofobia-y-el-machismo/202659/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 12:58 p. m.</t>
+          <t>31/05/2026 07:58 p. m.</t>
         </is>
       </c>
       <c r="B169" s="6" t="inlineStr">
@@ -5039,17 +5039,21 @@
       </c>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>¿Hasta qué hora es la ley seca en Colombia? Conozca el momento exacto en que finaliza la restricción</t>
+          <t>Elecciones Colombia en el exterior: mapa de cómo votaron los colombianos este domingo, 31 de mayo</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/articulo/hasta-que-hora-es-la-ley-seca-en-colombia-conozca-el-momento-exacto-en-que-finaliza-la-restriccion/202622/</t>
+          <t>https://www.semana.com/politica/articulo/elecciones-colombia-en-el-exterior-mapa-de-como-votaron-los-colombianos-este-domingo-31-de-mayo/202601/</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="3" t="inlineStr"/>
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>31/05/2026 07:58 p. m.</t>
+        </is>
+      </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5062,17 +5066,21 @@
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Brasil y Ancelotti hablaron desde el Maracaná y advierten a sus máximos rivales en el Mundial 2026 con gran goleada</t>
+          <t>Iván Cepeda cuestiona los resultados de la primera vuelta presidencial: advierte sobre un “desfase” de 885.000 cédulas en el censo electoral</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/brasil-y-ancelotti-hablaron-desde-el-maracana-y-advierten-a-sus-maximos-rivales-en-el-mundial-2026-con-gran-goleada/202621/</t>
+          <t>https://www.semana.com/politica/articulo/ivan-cepeda-cuestiona-los-resultados-de-la-primera-vuelta-presidencial-advierte-sobre-un-desfase-de-885000-cedulas-en-el-censo-electoral/202600/</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="6" t="inlineStr"/>
+      <c r="A171" s="6" t="inlineStr">
+        <is>
+          <t>31/05/2026 07:58 p. m.</t>
+        </is>
+      </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5085,17 +5093,21 @@
       </c>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>Hijo de Zinedine Zidane se ilusiona con jugar el Mundial 2026: convocatoria oficial desde África resalta su nombre</t>
+          <t>Gustavo Petro reacciona a la primera vuelta presidencial: “No acepto los resultados del preconteo”</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/hijo-de-zinedine-zidane-se-ilusiona-con-jugar-el-mundial-2026-convocatoria-oficial-desde-africa-resalta-su-nombre/202626/</t>
+          <t>https://www.semana.com/politica/articulo/gustavo-petro-reacciona-a-la-primera-vuelta-presidencial-no-acepto-los-resultados-del-preconteo/202631/</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="3" t="inlineStr"/>
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>31/05/2026 06:58 p. m.</t>
+        </is>
+      </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5108,17 +5120,21 @@
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Los partidos del Mundial 2026 que se disputarán el 21 de junio, día de la segunda vuelta entre Abelardo de la Espriella e Iván Cepeda: ¿incidirá en las votaciones?</t>
+          <t>Segunda vuelta presidencial Colombia 2026: Fecha oficial y lo que debe saber</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/deportes/articulo/los-partidos-del-mundial-2026-que-se-disputaran-el-21-de-junio-dia-de-la-segunda-vuelta-entre-abelardo-de-la-espriella-e-ivan-cepeda-incidira-en-las-votaciones/202619/</t>
+          <t>https://www.semana.com/politica/articulo/cuando-es-la-segunda-vuelta-presidencial-de-las-elecciones-en-colombia-2026-fechas-claves/202657/</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="6" t="inlineStr"/>
+      <c r="A173" s="6" t="inlineStr">
+        <is>
+          <t>31/05/2026 06:58 p. m.</t>
+        </is>
+      </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5131,17 +5147,21 @@
       </c>
       <c r="D173" s="7" t="inlineStr">
         <is>
-          <t>Elecciones presidenciales 2026 EN VIVO | Abelardo de la Espriella e Iván Cepeda se enfrentarán en segunda vuelta: reacciones y últimas noticias</t>
+          <t>Quién es Iván Cepeda, el candidato del Pacto Histórico que va a segunda vuelta</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/articulo/resultados-elecciones-colombia-2026-en-vivo-habla-abelardo-de-la-espriella-y-anticipa-que-cambiara-la-historia/202622/</t>
+          <t>https://www.semana.com/politica/articulo/quien-es-ivan-cepeda-biografia-trayectoria-profesional-y-politica-del-candidato-a-la-presidencia-de-colombia/202620/</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="3" t="inlineStr"/>
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>31/05/2026 06:58 p. m.</t>
+        </is>
+      </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5154,17 +5174,21 @@
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Aída Quilcué no reconoce los resultados arrojados por el preconteo y habla de caminar en una “minga”</t>
+          <t>Quién es Abelardo de la Espriella, el candidato que busca la Presidencia en segunda vuelta</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/aida-quilcue-no-reconoce-los-resultados-arrojados-por-el-preconteo-y-habla-de-caminar-en-una-minga/202610/</t>
+          <t>https://www.semana.com/politica/articulo/quien-es-abelardo-de-la-espriella-el-candidato-que-busca-la-presidencia-en-segunda-vuelta/202634/</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="6" t="inlineStr"/>
+      <c r="A175" s="6" t="inlineStr">
+        <is>
+          <t>31/05/2026 06:58 p. m.</t>
+        </is>
+      </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5177,17 +5201,21 @@
       </c>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>¿Se le dañó el certificado electoral? Esto es lo que debe hacer para no perder sus beneficios</t>
+          <t>Paloma Valencia reconoce derrota y anuncia su apoyo a Abelardo de la Espriella</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/se-le-dano-el-certificado-electoral-esto-es-lo-que-debe-hacer-para-no-perder-sus-beneficios/202628/</t>
+          <t>https://www.semana.com/politica/articulo/paloma-valencia-reconoce-derrota-y-anuncia-apoya-a-abelardo-de-al-espriella/202623/</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="3" t="inlineStr"/>
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>31/05/2026 06:58 p. m.</t>
+        </is>
+      </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5200,17 +5228,21 @@
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>“¡Qué peligro! Gustavo Petro quiere quedarse en el poder”: reacciones porque el presidente no aceptó resultados electorales</t>
+          <t>¿Se puede cambiar el puesto de votación para segunda vuelta presidencial? Registraduría responde</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/que-peligro-gustavo-petro-quiere-quedarse-en-el-poder-reacciones-porque-el-presidente-no-acepto-resultados-electorales/202643/</t>
+          <t>https://www.semana.com/politica/articulo/se-puede-cambiar-el-puesto-de-votacion-para-segunda-vuelta-presidencial-registraduria-responde/202646/</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="6" t="inlineStr"/>
+      <c r="A177" s="6" t="inlineStr">
+        <is>
+          <t>31/05/2026 04:58 p. m.</t>
+        </is>
+      </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5223,17 +5255,21 @@
       </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>Roy Barreras se inclina por el Pacto Histórico en segunda vuelta y manda mensaje a Iván Cepeda: “Debe abrirse al centro”</t>
+          <t>La Champions League se pronunció y eligió al mejor jugador de la temporada: no irá al Mundial 2026</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/cali/articulo/roy-barreras-se-inclina-por-el-pacto-historico-en-segunda-vuelta-y-manda-mensaje-a-ivan-cepeda-debe-abrirse-al-centro/202645/</t>
+          <t>https://www.semana.com/deportes/articulo/la-champions-league-se-pronuncio-y-eligio-el-mejor-jugador-de-la-temporada-no-ira-al-mundial-2026/202601/</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="3" t="inlineStr"/>
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>31/05/2026 04:58 p. m.</t>
+        </is>
+      </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5246,17 +5282,21 @@
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Mapa de los resultados de la primera vuelta | Así votó Colombia este domingo, 31 de mayo</t>
+          <t>¿Quién es Pilar Rueda, la esposa de Iván Cepeda? Así es la familia del candidato del Pacto Histórico</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/cali/articulo/mapa-de-los-resultados-de-la-primera-vuelta-asi-voto-colombia-este-domingo-31-de-mayo/202635/</t>
+          <t>https://www.semana.com/politica/articulo/pilar-rueda-la-esposa-de-ivan-cepeda-asi-es-la-familia-del-candidato-del-pacto-historico/202650/</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="6" t="inlineStr"/>
+      <c r="A179" s="6" t="inlineStr">
+        <is>
+          <t>31/05/2026 04:58 p. m.</t>
+        </is>
+      </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5269,17 +5309,21 @@
       </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>Ministro de Defensa lanza advertencia tras votaciones: “La alerta se incrementa aún más”</t>
+          <t>¿Quién es Ana Lucía Pineda, la esposa de Abelardo de la Espriella, candidato por la presidencia en Colombia?</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>https://www.semana.com/politica/articulo/ministro-de-defensa-lanza-advertencia-tras-votaciones-la-alerta-se-incrementa-aun-mas/202622/</t>
+          <t>https://www.semana.com/politica/articulo/quien-es-ana-lucia-pineda-la-esposa-de-abelardo-de-la-espriella-candidato-por-la-presidencia-en-colombia/202645/</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="3" t="inlineStr"/>
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>31/05/2026 03:58 p. m.</t>
+        </is>
+      </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5292,19 +5336,19 @@
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>El Ideam entregó el pronóstico del clima para las primeras horas de junio: “Probabilidad de lluvias en distintos sectores”</t>
+          <t>Vingegaard es campeón del Giro de Italia; Egan, fenomenal: es top 10 y aumenta su historia en el ciclismo mundial</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>https://www.semana.com/nacion/bogota/articulo/el-ideam-entrego-el-pronostico-del-clima-para-las-primeras-horas-de-junio-probabilidad-de-lluvias-en-distintos-sectores/202647/</t>
+          <t>https://www.semana.com/deportes/ciclismo/articulo/vingegaard-es-campeon-del-giro-de-italia-y-egan-fenomenal-top-10-y-aumenta-su-historia-en-el-ciclismo-mundial/202625/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 08:05 p. m.</t>
+          <t>31/05/2026 03:58 p. m.</t>
         </is>
       </c>
       <c r="B181" s="6" t="inlineStr">
@@ -5314,24 +5358,24 @@
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D181" s="7" t="inlineStr">
         <is>
-          <t>¿Quién es Iván Cepeda, el líder de izquierda que llega a la segunda vuelta presidencial?</t>
+          <t>Exclusivo: Angie Rodríguez denunció a su exasesor en el Fondo Adaptación por intento de envenenamiento. “Vitaminas, pastas para el dolor de cabeza”</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/quien-es-ivan-cepeda-quien-llega-a-segunda-vuelta-presidencial-1026606</t>
+          <t>https://www.semana.com/politica/articulo/exclusivo-angie-rodriguez-denuncio-a-su-exasesor-en-el-fondo-adaptacion-por-intento-de-envenenamiento-vitaminas-pastas-para-el-dolor-de-cabeza/202635/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 07:59 p. m.</t>
+          <t>31/05/2026 12:58 p. m.</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -5341,26 +5385,22 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Juan Daniel Oviedo se aparta de la decisión de Paloma Valencia de sumarse a la campaña de la Espriella</t>
+          <t>¿Hasta qué hora es la ley seca en Colombia? Conozca el momento exacto en que finaliza la restricción</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/juan-daniel-oviedo-se-aparta-de-la-decision-de-paloma-valencia-de-sumarse-a-la-campana-de-la-espriella-1026587</t>
+          <t>https://www.semana.com/nacion/articulo/hasta-que-hora-es-la-ley-seca-en-colombia-conozca-el-momento-exacto-en-que-finaliza-la-restriccion/202622/</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="6" t="inlineStr">
-        <is>
-          <t>31/05/2026 07:47 p. m.</t>
-        </is>
-      </c>
+      <c r="A183" s="6" t="inlineStr"/>
       <c r="B183" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5368,26 +5408,22 @@
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D183" s="7" t="inlineStr">
         <is>
-          <t>“Obtuvimos 10 millones de votos mal contados”: Iván Cepeda tras preconteo electoral</t>
+          <t>Brasil y Ancelotti hablaron desde el Maracaná y advierten a sus máximos rivales en el Mundial 2026 con gran goleada</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/obtuvimos-10-millones-de-votos-mal-contados-ivan-cepeda-denuncio-irregularidades-en-elecciones-1026594</t>
+          <t>https://www.semana.com/deportes/articulo/brasil-y-ancelotti-hablaron-desde-el-maracana-y-advierten-a-sus-maximos-rivales-en-el-mundial-2026-con-gran-goleada/202621/</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="3" t="inlineStr">
-        <is>
-          <t>31/05/2026 07:41 p. m.</t>
-        </is>
-      </c>
+      <c r="A184" s="3" t="inlineStr"/>
       <c r="B184" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5395,26 +5431,22 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>8 capturas, 10 noticias criminales y 77 desaparecidos en las urnas: Fiscalía sobre su plan de acción durante las elecciones</t>
+          <t>Hijo de Zinedine Zidane se ilusiona con jugar el Mundial 2026: convocatoria oficial desde África resalta su nombre</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/fiscalia-mantiene-plan-de-accion-contra-delitos-en-las-elecciones-2026-1026569</t>
+          <t>https://www.semana.com/deportes/articulo/hijo-de-zinedine-zidane-se-ilusiona-con-jugar-el-mundial-2026-convocatoria-oficial-desde-africa-resalta-su-nombre/202626/</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="6" t="inlineStr">
-        <is>
-          <t>31/05/2026 07:37 p. m.</t>
-        </is>
-      </c>
+      <c r="A185" s="6" t="inlineStr"/>
       <c r="B185" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5422,26 +5454,22 @@
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D185" s="7" t="inlineStr">
         <is>
-          <t>¿Se puede modificar el puesto de votación para la segunda vuelta de las elecciones 2026?</t>
+          <t>Los partidos del Mundial 2026 que se disputarán el 21 de junio, día de la segunda vuelta entre Abelardo de la Espriella e Iván Cepeda: ¿incidirá en las votaciones?</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/no-se-puede-cambiar-el-puesto-de-votacion-para-la-segunda-vuelta-de-las-elecciones-1026588</t>
+          <t>https://www.semana.com/deportes/articulo/los-partidos-del-mundial-2026-que-se-disputaran-el-21-de-junio-dia-de-la-segunda-vuelta-entre-abelardo-de-la-espriella-e-ivan-cepeda-incidira-en-las-votaciones/202619/</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="3" t="inlineStr">
-        <is>
-          <t>31/05/2026 07:30 p. m.</t>
-        </is>
-      </c>
+      <c r="A186" s="3" t="inlineStr"/>
       <c r="B186" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5449,26 +5477,22 @@
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>Abelardo de la Espriella, el ‘outsider’ millonario que se disputa la Presidencia de Colombia</t>
+          <t>“Ganó el doctor Abelardo de la Espriella. Cumplimos la palabra, votaremos por él y pedimos que se vote por él”: Álvaro Uribe</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/quien-es-abelardo-de-la-espriella-el-tigre-candidato-a-la-presidencia-de-colombia-1026581</t>
+          <t>https://www.semana.com/politica/articulo/gano-el-doctor-abelardo-de-la-espriella-cumplimos-la-palabra-votaremos-por-el-y-pedimos-que-se-vote-por-el-alvaro-uribe/202627/</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="6" t="inlineStr">
-        <is>
-          <t>31/05/2026 07:21 p. m.</t>
-        </is>
-      </c>
+      <c r="A187" s="6" t="inlineStr"/>
       <c r="B187" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5476,26 +5500,22 @@
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D187" s="7" t="inlineStr">
         <is>
-          <t>Presidente Gustavo Petro no aceptó resultados del preconteo y denunció alteraciones en software</t>
+          <t>Elecciones presidenciales 2026 EN VIVO | Abelardo de la Espriella e Iván Cepeda se enfrentarán en segunda vuelta: reacciones y últimas noticias</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/gustavo-petro-no-acepto-resultados-en-primera-vuelta-y-denuncio-irregularidades-1026575</t>
+          <t>https://www.semana.com/nacion/articulo/resultados-elecciones-colombia-2026-en-vivo-habla-abelardo-de-la-espriella-y-anticipa-que-cambiara-la-historia/202622/</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="3" t="inlineStr">
-        <is>
-          <t>31/05/2026 07:14 p. m.</t>
-        </is>
-      </c>
+      <c r="A188" s="3" t="inlineStr"/>
       <c r="B188" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5503,26 +5523,22 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Así reaccionaron “los quemados” a los resultados de primera vuelta</t>
+          <t>Aída Quilcué no reconoce los resultados arrojados por el preconteo y habla de caminar en una “minga”</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/asi-reaccionaron-los-quemados-a-los-resultados-de-primera-vuelta-1026544</t>
+          <t>https://www.semana.com/politica/articulo/aida-quilcue-no-reconoce-los-resultados-arrojados-por-el-preconteo-y-habla-de-caminar-en-una-minga/202610/</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="6" t="inlineStr">
-        <is>
-          <t>31/05/2026 06:57 p. m.</t>
-        </is>
-      </c>
+      <c r="A189" s="6" t="inlineStr"/>
       <c r="B189" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5530,26 +5546,22 @@
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D189" s="7" t="inlineStr">
         <is>
-          <t>Así quedó el mapa político en primera vuelta: regiones que lideraron de la Espriella y Cepeda</t>
+          <t>¿Se le dañó el certificado electoral? Esto es lo que debe hacer para no perder sus beneficios</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/asi-quedo-el-mapa-politico-en-primera-vuelta-regiones-que-lideraron-de-la-espriella-y-cepeda-1026528</t>
+          <t>https://www.semana.com/politica/articulo/se-le-dano-el-certificado-electoral-esto-es-lo-que-debe-hacer-para-no-perder-sus-beneficios/202628/</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="3" t="inlineStr">
-        <is>
-          <t>31/05/2026 06:39 p. m.</t>
-        </is>
-      </c>
+      <c r="A190" s="3" t="inlineStr"/>
       <c r="B190" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5557,26 +5569,22 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>Noticias RCN</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>Sergio Fajardo habla sobre lo que le pedirá a sus votantes de cara a la segunda vuelta</t>
+          <t>Roy Barreras se inclina por el Pacto Histórico en segunda vuelta y manda mensaje a Iván Cepeda: “Debe abrirse al centro”</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>https://www.noticiasrcn.com/colombia/que-pasara-con-los-votos-de-sergio-fajardo-en-la-segunda-vuelta-presidencial-1026542</t>
+          <t>https://www.semana.com/nacion/cali/articulo/roy-barreras-se-inclina-por-el-pacto-historico-en-segunda-vuelta-y-manda-mensaje-a-ivan-cepeda-debe-abrirse-al-centro/202645/</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="6" t="inlineStr">
-        <is>
-          <t>31/05/2026 08:01 p. m.</t>
-        </is>
-      </c>
+      <c r="A191" s="6" t="inlineStr"/>
       <c r="B191" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5584,26 +5592,22 @@
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D191" s="7" t="inlineStr">
         <is>
-          <t>Petro se niega a aceptar los resultados de la primera vuelta</t>
+          <t>Mapa de los resultados de la primera vuelta | Así votó Colombia este domingo, 31 de mayo</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-06-01/petro-se-niega-a-aceptar-el-conteo-provisional-de-la-primera-vuelta.html</t>
+          <t>https://www.semana.com/nacion/cali/articulo/mapa-de-los-resultados-de-la-primera-vuelta-asi-voto-colombia-este-domingo-31-de-mayo/202635/</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="3" t="inlineStr">
-        <is>
-          <t>31/05/2026 07:54 p. m.</t>
-        </is>
-      </c>
+      <c r="A192" s="3" t="inlineStr"/>
       <c r="B192" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5611,26 +5615,22 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>Las propuestas de Abelardo de la Espriella: seguridad de “mano dura”, reducción del Estado y libertades tributarias</t>
+          <t>Ministro de Defensa lanza advertencia tras votaciones: “La alerta se incrementa aún más”</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-06-01/las-propuestas-de-abelardo-de-la-espriella-seguridad-de-mano-dura-reduccion-del-estado-y-libertades-tributarias.html</t>
+          <t>https://www.semana.com/politica/articulo/ministro-de-defensa-lanza-advertencia-tras-votaciones-la-alerta-se-incrementa-aun-mas/202622/</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="6" t="inlineStr">
-        <is>
-          <t>31/05/2026 07:48 p. m.</t>
-        </is>
-      </c>
+      <c r="A193" s="6" t="inlineStr"/>
       <c r="B193" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -5638,24 +5638,24 @@
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="D193" s="7" t="inlineStr">
         <is>
-          <t>Iván Cepeda pone en duda los resultados de la primera vuelta: “Solo nos pronunciaremos cuando las comisiones escrutadoras aclaren nuestras dudas”</t>
+          <t>El Ideam entregó el pronóstico del clima para las primeras horas de junio: “Probabilidad de lluvias en distintos sectores”</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-06-01/ivan-cepeda-pone-en-duda-los-datos-conocidos-de-la-primera-vuelta-solo-nos-pronunciaremos-sobre-los-resultados-cuando-las-comisiones-escrutadoras-aclaren-nuestras-dudas.html</t>
+          <t>https://www.semana.com/nacion/bogota/articulo/el-ideam-entrego-el-pronostico-del-clima-para-las-primeras-horas-de-junio-probabilidad-de-lluvias-en-distintos-sectores/202647/</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 07:45 p. m.</t>
+          <t>31/05/2026 09:29 p. m.</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -5665,24 +5665,24 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Las propuestas de Iván Cepeda: tres revoluciones, rechazo a la militarización y continuidad</t>
+          <t>Abelardo de la Espriella endurece su discurso tras ganar la primera vuelta</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-06-01/las-propuestas-de-ivan-cepeda-tres-revoluciones-rechazo-a-la-militarizacion-y-continuidad.html</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/31/abelardo-de-la-espriella-endurece-su-discurso-tras-ganar-la-primera-vuelta/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 07:34 p. m.</t>
+          <t>31/05/2026 07:44 p. m.</t>
         </is>
       </c>
       <c r="B195" s="6" t="inlineStr">
@@ -5692,24 +5692,24 @@
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D195" s="7" t="inlineStr">
         <is>
-          <t>Iván Cepeda, el candidato inalterable que promete continuidad</t>
+          <t>Iván Cepeda denuncia injerencia extranjera tras resultados de primera vuelta</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-06-01/ivan-cepeda-el-candidato-inalterable-que-promete-continuidad.html</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/31/ivan-cepeda-denuncia-injerencia-extranjera-tras-resultados-de-primera-vuelta/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 07:22 p. m.</t>
+          <t>31/05/2026 07:37 p. m.</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -5719,24 +5719,24 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>Sergio Fajardo valoriza su millón de votos: “Vamos a ser protagonistas de estas elecciones”</t>
+          <t>Eduardo Verano destacó tranquilidad de la jornada electoral en el Atlántico</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-06-01/sergio-fajardo-valoriza-su-millon-de-votos-vamos-a-ser-protagonistas-de-estas-elecciones.html</t>
+          <t>https://www.eluniversal.com.co/regional/atlantico/2026/05/31/eduardo-verano-destaco-tranquilidad-de-la-jornada-electoral-en-el-atlantico/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 07:18 p. m.</t>
+          <t>31/05/2026 07:37 p. m.</t>
         </is>
       </c>
       <c r="B197" s="6" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D197" s="7" t="inlineStr">
         <is>
-          <t>Abelardo de la Espriella celebra su victoria en la primera vuelta: “Petro y Cepeda son un par de bandidos que vamos a jubilar”</t>
+          <t>Atlántico</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-06-01/abelardo-de-la-espriella-celebra-su-victoria-en-la-primera-vuelta-vamos-a-derrotar-la-tirania-y-el-absolutismo.html</t>
+          <t>https://www.eluniversal.com.co/regional/atlantico/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 07:06 p. m.</t>
+          <t>31/05/2026 07:23 p. m.</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -5773,24 +5773,24 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>Paloma Valencia acepta su derrota y apoya a Abelardo de la Espriella</t>
+          <t>Policía reporta balance de primera vuelta presidencial: 89 capturas y sin alteraciones</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-06-01/paloma-valencia-acepta-su-derrota-y-apoya-a-abelardo-de-la-espriella.html</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/31/policia-reporta-balance-de-primera-vuelta-presidencial-89-capturas-y-sin-alteraciones/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 06:35 p. m.</t>
+          <t>31/05/2026 07:01 p. m.</t>
         </is>
       </c>
       <c r="B199" s="6" t="inlineStr">
@@ -5800,24 +5800,24 @@
       </c>
       <c r="C199" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D199" s="7" t="inlineStr">
         <is>
-          <t>El presidente Kast llama a la “esperanza” a horas de su primera Cuenta Pública, mientras la desaprobación aumenta a un 53%</t>
+          <t>Así fue la votación del Atlántico para la primera vuelta presidencial 2026</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/chile/2026-05-31/el-presidente-kast-llama-a-la-esperanza-a-horas-de-su-primera-cuenta-publica-mientras-la-desaprobacion-aumenta-a-un-53.html</t>
+          <t>https://www.eluniversal.com.co/regional/atlantico/2026/05/31/asi-fue-la-votacion-del-atlantico-para-la-primera-vuelta-presidencial-2026/</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 06:23 p. m.</t>
+          <t>31/05/2026 06:54 p. m.</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -5827,24 +5827,24 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>Abelardo de la Espriella, el abogado del diablo que quiere ser presidente de Colombia</t>
+          <t>Álvaro Uribe reconoce derrota de Valencia y anuncia respaldo a De la Espriella</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/abelardo-de-la-espriella-abogado-del-diablo-que-quiere-ser-presidente-de-colombia.html</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/31/alvaro-uribe-reconoce-derrota-de-valencia-y-anuncia-respaldo-a-de-la-espriella/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 06:15 p. m.</t>
+          <t>31/05/2026 06:30 p. m.</t>
         </is>
       </c>
       <c r="B201" s="6" t="inlineStr">
@@ -5854,24 +5854,24 @@
       </c>
       <c r="C201" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D201" s="7" t="inlineStr">
         <is>
-          <t>Las claves de la primera vuelta en Colombia: el auge ultra, la unidad en la izquierda y la importancia de los votos del centro</t>
+          <t>Tras derrota en primer vuelta, Paloma Valencia anunció su apoyo a Abelardo</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/las-claves-de-la-primera-vuelta-en-colombia-el-auge-ultra-unidad-en-la-izquierda-y-los-votos-del-centro-claves.html</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/31/tras-derrota-en-primer-vuelta-paloma-valencia-anuncio-su-apoyo-a-abelardo/</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 06:05 p. m.</t>
+          <t>31/05/2026 06:17 p. m.</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -5881,24 +5881,24 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>La izquierda de Iván Cepeda se ve obligada a remontar para asegurar un segundo Gobierno progresista</t>
+          <t>¿Qué día será la segunda vuelta para elegir al presidente en Colombia?</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/la-izquierda-de-ivan-cepeda-se-ve-obligada-a-remontar-para-asegurar-un-segundo-gobierno-progresista.html</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/31/que-dia-sera-la-segunda-vuelta-para-elegir-al-presidente-en-colombia/</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 06:02 p. m.</t>
+          <t>31/05/2026 06:16 p. m.</t>
         </is>
       </c>
       <c r="B203" s="6" t="inlineStr">
@@ -5908,24 +5908,24 @@
       </c>
       <c r="C203" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D203" s="7" t="inlineStr">
         <is>
-          <t>De la Espriella y Cepeda se disputarán la presidencia de Colombia mientras Petro cuestiona los resultados</t>
+          <t>Abelardo de la Espriella se pronuncia tras arrasar en la primera vuelta presidencial de Colombia 2026</t>
         </is>
       </c>
       <c r="E203" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/de-la-espriella-y-cepeda-se-disputaran-la-presidencia-de-colombia-con-un-pais-partido-en-dos.html</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/31/abelardo-de-la-espriella-se-pronuncia-tras-arrasar-en-la-primera-vuelta-presidencial-de-colombia-2026/</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 05:47 p. m.</t>
+          <t>31/05/2026 05:02 p. m.</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -5935,24 +5935,24 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>La derecha colombiana se vuelca con el ultra Abelardo de la Espriella y da la espalda a Álvaro Uribe</t>
+          <t>Abelardo de la Espriella e Iván Cepeda disputarán la segunda vuelta presidencial en Colombia</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/la-derecha-colombiana-se-vuelca-con-el-ultra-abelardo-de-la-espriella-y-da-la-espalda-a-alvaro-uribe.html</t>
+          <t>https://www.eluniversal.com.co/colombia/2026/05/31/abelardo-de-la-espriella-e-ivan-cepeda-disputaran-la-segunda-vuelta-presidencial-en-colombia/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 05:00 p. m.</t>
+          <t>31/05/2026 05:02 p. m.</t>
         </is>
       </c>
       <c r="B205" s="6" t="inlineStr">
@@ -5962,24 +5962,24 @@
       </c>
       <c r="C205" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D205" s="7" t="inlineStr">
         <is>
-          <t>Las gafas más icónicas de Ray-Ban bajan 80 euros en AliExpress: una oferta imbatible por tiempo limitado</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E205" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/hemeroteca/2026-06-01/</t>
+          <t>https://www.eluniversal.com.co/colombia/</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 04:29 p. m.</t>
+          <t>31/05/2026 04:37 p. m.</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -5989,24 +5989,24 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>Muere bajo custodia del régimen de Ortega el líder indígena nicaragüense Brooklyn Rivera tras casi tres años de arresto político</t>
+          <t>Hallaron sin vida a Marliez Genz, la turista neerlandesa que desapareció en Quindío</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/america/2026-05-31/muere-bajo-custodia-del-regimen-de-ortega-el-lider-indigena-nicaraguense-brooklyn-rivera-tras-casi-tres-anos-de-arresto-politico.html</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/31/hallaron-sin-vida-a-marliez-genz-la-turista-neerlandesa-que-desaparecio-en-quindio/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 04:09 p. m.</t>
+          <t>31/05/2026 04:33 p. m.</t>
         </is>
       </c>
       <c r="B207" s="6" t="inlineStr">
@@ -6016,24 +6016,24 @@
       </c>
       <c r="C207" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D207" s="7" t="inlineStr">
         <is>
-          <t>Almería-Castellón y Málaga-Las Palmas, las semifinales por el ascenso a Primera División</t>
+          <t>A ‘Yayo’ lo arrolló una tractomula y murió tras 2 días de estar hospitalizado</t>
         </is>
       </c>
       <c r="E207" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/deportes/futbol/2026-05-31/almeria-castellon-y-malaga-las-palmas-las-semifinales-por-el-ascenso-a-primera-division.html</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/31/a-yayo-lo-arrollo-una-tractomula-y-fallecio-tras-2-dias-de-estar-hospitalizad/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 03:59 p. m.</t>
+          <t>31/05/2026 04:25 p. m.</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -6043,24 +6043,24 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>Resultados de las elecciones en Colombia 2026, en vivo | Abelardo de la Espriella hace un llamado a defender la democracia “por la razón o por la fuerza”</t>
+          <t>FIFA reveló cuál será la prioridad de los árbitros en el Mundial</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/america-colombia/elecciones-presidenciales/2026-05-31/resultados-de-las-elecciones-colombia-2026-en-vivo.html</t>
+          <t>https://www.eluniversal.com.co/deportes/2026/05/31/fifa-revelo-cual-sera-la-prioridad-de-los-arbitros-en-el-mundial/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 03:51 p. m.</t>
+          <t>31/05/2026 04:25 p. m.</t>
         </is>
       </c>
       <c r="B209" s="6" t="inlineStr">
@@ -6070,24 +6070,24 @@
       </c>
       <c r="C209" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D209" s="7" t="inlineStr">
         <is>
-          <t>Los Javis y Judeline, invitados de La Casita de Bad Bunny en su segundo concierto en Madrid</t>
+          <t>Deportes</t>
         </is>
       </c>
       <c r="E209" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/cultura/2026-05-31/los-javis-y-judeline-invitados-de-la-casita-de-bad-bunny-en-su-segundo-concierto-en-madrid.html</t>
+          <t>https://www.eluniversal.com.co/deportes/</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 03:48 p. m.</t>
+          <t>31/05/2026 04:11 p. m.</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -6097,24 +6097,24 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>Antonio Ferrera, creativo e histriónico, por la Puerta Grande</t>
+          <t>¿Qué le pasó a Diego Guauque? El periodista deberá someterse a una nueva cirugía</t>
         </is>
       </c>
       <c r="E210" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/cultura/2026-05-31/antonio-ferrera-creativo-e-histrionico-por-la-puerta-grande.html</t>
+          <t>https://www.eluniversal.com.co/farandula/2026/05/31/que-le-paso-a-diego-guauque-el-periodista-debera-someterse-a-una-nueva-cirugia/</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 03:39 p. m.</t>
+          <t>31/05/2026 03:36 p. m.</t>
         </is>
       </c>
       <c r="B211" s="6" t="inlineStr">
@@ -6124,24 +6124,24 @@
       </c>
       <c r="C211" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D211" s="7" t="inlineStr">
         <is>
-          <t>La campaña de ataques de EE UU contra supuestas narcolanchas supera los 200 muertos</t>
+          <t>Chris Rodríguez llegó de Puerto Rico para operarse y murió en el quirófano</t>
         </is>
       </c>
       <c r="E211" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/america/2026-05-31/la-campana-de-ataques-de-ee-uu-contra-supuestas-narcolanchas-supera-los-200-muertos.html</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/31/chris-rodriguez-llego-de-puerto-rico-para-operarse-y-murio-en-el-quirofano/</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 12:14 p. m.</t>
+          <t>31/05/2026 02:33 p. m.</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -6151,24 +6151,24 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>Diez cosas que los correctores de la Selectividad aconsejan hacer (o evitar) en los exámenes de la PAU</t>
+          <t>Elian Hernández, el barbero informal que sicario le quitó la vida a balazos</t>
         </is>
       </c>
       <c r="E212" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/educacion/2026-05-31/diez-cosas-que-los-correctores-de-la-selectividad-aconsejan-hacer-o-evitar-en-los-examenes-de-la-pau.html</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/31/elian-hernandez-el-barbero-informal-que-sicario-le-quito-la-vida-a-balazos/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 10:33 a. m.</t>
+          <t>31/05/2026 02:00 p. m.</t>
         </is>
       </c>
       <c r="B213" s="6" t="inlineStr">
@@ -6178,24 +6178,24 @@
       </c>
       <c r="C213" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D213" s="7" t="inlineStr">
         <is>
-          <t>Cabeza dura y puños de acero: Rafa Jódar remonta a Carreño y tiene derecho a soñar</t>
+          <t>Él era Virgilio Bueno, el reconocido comerciante que mataron en un ataque de sicarios</t>
         </is>
       </c>
       <c r="E213" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/deportes/tenis/2026-05-31/rafa-jodar-remonta-a-carreno-y-se-endurece-rumbo-a-cuartos.html</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/31/el-era-virgilio-bueno-el-reconocido-comerciante-que-murio-en-un-ataque-de-sicarios/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 08:58 a. m.</t>
+          <t>31/05/2026 01:25 p. m.</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -6205,24 +6205,24 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>Marco Bezzecchi y Aprilia conquistan por primera vez el GP de Italia</t>
+          <t>Video: ¿Qué ocasionó incendio en bodega de reciclaje en el barrio 13 de Junio?</t>
         </is>
       </c>
       <c r="E214" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/deportes/motociclismo/2026-05-31/marco-bezzecchi-y-aprilia-conquistan-por-primera-vez-el-gp-de-italia.html</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/31/video-que-ocasiono-incendio-en-bodega-de-reciclaje-en-el-barrio-13-de-junio/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 07:55 a. m.</t>
+          <t>31/05/2026 11:54 a. m.</t>
         </is>
       </c>
       <c r="B215" s="6" t="inlineStr">
@@ -6232,24 +6232,24 @@
       </c>
       <c r="C215" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D215" s="7" t="inlineStr">
         <is>
-          <t>Miles de personas salen a la calle en Madrid contra la política sanitaria de Ayuso: “Ahoga la pública para engordar los seguros privados”</t>
+          <t>‘Quilla’ no votará: cayó con prendas de oro y celulares robados en el Pie de La Popa</t>
         </is>
       </c>
       <c r="E215" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/espana/madrid/2026-05-31/miles-de-personas-salen-a-la-calle-en-madrid-contra-la-politica-sanitaria-de-ayuso-ahoga-la-publica-para-engordar-los-seguros-privados.html</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/31/quilla-no-votara-cayo-con-prendas-de-oro-y-celulares-robados-en-el-pie-de-la-popa/</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 07:39 a. m.</t>
+          <t>31/05/2026 11:33 a. m.</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -6259,26 +6259,22 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t>Sánchez pide tiempo frente a la oposición “marrullera” que quiere “derribar” al Gobierno con “malas artes”</t>
+          <t>Así mataron a alias ‘Chupi’ en Calamar: intentaron linchar a su expareja</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/espana/2026-05-31/sanchez-cierra-el-congreso-de-las-juventudes-socialistas-en-madrid.html</t>
+          <t>https://www.eluniversal.com.co/sucesos/2026/05/31/asi-mataron-a-alias-chupi-en-calamar-intentaron-lichar-a-su-expareja/</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="6" t="inlineStr">
-        <is>
-          <t>31/05/2026 07:01 a. m.</t>
-        </is>
-      </c>
+      <c r="A217" s="6" t="inlineStr"/>
       <c r="B217" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -6286,26 +6282,22 @@
       </c>
       <c r="C217" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D217" s="7" t="inlineStr">
         <is>
-          <t>Vuelta de tuerca en el tumor más letal: una terapia dirigida logra duplicar la supervivencia en el cáncer de páncreas</t>
+          <t>Premios Excelencia El Universal 2026: ya están abiertas las postulaciones</t>
         </is>
       </c>
       <c r="E217" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/salud-y-bienestar/2026-05-31/vuelta-de-tuerca-en-el-tumor-mas-letal-una-terapia-dirigida-logra-duplicar-la-supervivencia-en-el-cancer-de-pancreas.html</t>
+          <t>https://www.eluniversal.com.co/cartagena/2026/05/26/premios-excelencia-el-universal-2026-ya-estan-abiertas-las-postulaciones/</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="3" t="inlineStr">
-        <is>
-          <t>31/05/2026 06:46 a. m.</t>
-        </is>
-      </c>
+      <c r="A218" s="3" t="inlineStr"/>
       <c r="B218" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -6313,24 +6305,24 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>780 detenidos y más de 200 heridos durante las celebraciones de la victoria del PSG en la Champions</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="E218" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/deportes/futbol/2026-05-30/mas-de-un-centenar-de-detenidos-en-paris-en-los-incidentes-producidos-tras-la-victoria-del-psg-en-la-champions.html</t>
+          <t>https://www.eluniversal.com.co/cartagena/</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
         <is>
-          <t>30/05/2026 10:30 p. m.</t>
+          <t>31/05/2026 09:25 p. m.</t>
         </is>
       </c>
       <c r="B219" s="6" t="inlineStr">
@@ -6340,24 +6332,24 @@
       </c>
       <c r="C219" s="6" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D219" s="7" t="inlineStr">
         <is>
-          <t>‘Cape Fear’ en Apple TV, ‘La casa del dragón’ en HBO Max y otras series recomendadas para junio</t>
+          <t>Así gobernaría Iván Cepeda si es elegido presidente de Colombia</t>
         </is>
       </c>
       <c r="E219" s="8" t="inlineStr">
         <is>
-          <t>https://elpais.com/television/series/2026-05-31/cape-fear-en-apple-tv-la-casa-del-dragon-en-hbo-max-y-otras-series-recomendadas-para-junio.html</t>
+          <t>https://www.vanguardia.com/politica/2026/05/31/asi-gobernaria-ivan-cepeda-si-es-elegido-presidente-de-colombia/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>30/05/2026 04:51 p. m.</t>
+          <t>31/05/2026 09:25 p. m.</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -6367,24 +6359,24 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D220" s="4" t="inlineStr">
         <is>
-          <t>Bad Bunny en Madrid: el alucinante jolgorio del perreo y el amor</t>
+          <t>Política</t>
         </is>
       </c>
       <c r="E220" s="5" t="inlineStr">
         <is>
-          <t>https://elpais.com/cultura/2026-05-30/bad-bunny-en-madrid-el-alucinante-jolgorio-del-perreo-y-el-amor.html</t>
+          <t>https://www.vanguardia.com/politica/</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 07:58 p. m.</t>
+          <t>31/05/2026 09:22 p. m.</t>
         </is>
       </c>
       <c r="B221" s="6" t="inlineStr">
@@ -6394,24 +6386,24 @@
       </c>
       <c r="C221" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D221" s="7" t="inlineStr">
         <is>
-          <t>Los totes de la primera vuelta presidencial</t>
+          <t>Abelardo De La Espriella, con boleto directo a la segunda vuelta presidencial</t>
         </is>
       </c>
       <c r="E221" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/multimedia/videos/los-totes-de-la-primera-vuelta-presidencial-FM37191105</t>
+          <t>https://www.vanguardia.com/politica/2026/05/31/abelardo-de-la-espriella-con-boleto-directo-a-la-segunda-vuelta-presidencial/</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 07:58 p. m.</t>
+          <t>31/05/2026 08:55 p. m.</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -6421,24 +6413,24 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t>“Hay un desfase que queremos verificar”: Cepeda no acepta la derrota y dice que esperará hasta el escrutinio</t>
+          <t>Horóscopo del 1 de junio 2026: Cómo influyen Júpiter y Urano en sus decisiones</t>
         </is>
       </c>
       <c r="E222" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/especiales/elecciones-2026/ivan-cepeda-no-acepta-derrota-resultados-elecciones-2026-OM37193379</t>
+          <t>https://www.vanguardia.com/entretenimiento/tendencias/2026/05/31/horoscopo-del-1-de-junio-2026-como-influyen-jupiter-y-urano-en-sus-decisiones/</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 06:58 p. m.</t>
+          <t>31/05/2026 08:55 p. m.</t>
         </is>
       </c>
       <c r="B223" s="6" t="inlineStr">
@@ -6448,24 +6440,24 @@
       </c>
       <c r="C223" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D223" s="7" t="inlineStr">
         <is>
-          <t>“Increíble que Colombia se debata su futuro alrededor de homofobia, machismo e irresponsabilidad”: Oviedo</t>
+          <t>Tendencias</t>
         </is>
       </c>
       <c r="E223" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/juan-daniel-oviedo-dice-a-quien-apoyar-elecciones-abelardo-cepeda-PN37189431</t>
+          <t>https://www.vanguardia.com/entretenimiento/tendencias/</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 06:58 p. m.</t>
+          <t>31/05/2026 08:55 p. m.</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -6475,24 +6467,24 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>Así votó Antioquia en primera vuelta: De la Espriella (54%) dobló a Cepeda (25,4%)</t>
+          <t>Resultado Motilón Noche: número ganador de hoy domingo 31 de mayo de 2026</t>
         </is>
       </c>
       <c r="E224" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/antioquia/antioquia-elecciones-presidenciales-colombia-2026-primera-vuelta-ON37188723</t>
+          <t>https://www.vanguardia.com/loterias/2026/05/31/resultado-motilon-noche-numero-ganador-de-hoy-domingo-31-de-mayo-de-2026/</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 06:58 p. m.</t>
+          <t>31/05/2026 08:55 p. m.</t>
         </is>
       </c>
       <c r="B225" s="6" t="inlineStr">
@@ -6502,24 +6494,24 @@
       </c>
       <c r="C225" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D225" s="7" t="inlineStr">
         <is>
-          <t>Uribe y su derrota en las presidenciales: se la juega ahora por De la Espriella</t>
+          <t>Loterias</t>
         </is>
       </c>
       <c r="E225" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/especiales/elecciones-2026/uribe-derrota-presidenciales-de-la-espriella-IM37190697</t>
+          <t>https://www.vanguardia.com/loterias/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 06:58 p. m.</t>
+          <t>31/05/2026 04:55 p. m.</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -6529,24 +6521,24 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t>Con más de 670.000 votos, De La Espriella barrió en Medellín en la primera vuelta</t>
+          <t>Capturan a alias ‘Chalia’ en el Chocó</t>
         </is>
       </c>
       <c r="E226" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/medellin/resultados-medellin-primera-vuelta-elecciones-presidenciales-2026-DN37188975</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/31/capturan-a-alias-chalia-en-el-choco/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 06:58 p. m.</t>
+          <t>31/05/2026 04:55 p. m.</t>
         </is>
       </c>
       <c r="B227" s="6" t="inlineStr">
@@ -6556,24 +6548,24 @@
       </c>
       <c r="C227" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D227" s="7" t="inlineStr">
         <is>
-          <t>“Anuncio mi apoyo a Abelardo e invito a que derrotemos a Cepeda”: Paloma Valencia reconoce resultados de primera vuelta</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E227" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/paloma-valencia-apoyo-abelardo-de-la-espriella-segunda-vuelta-junio-2026-ON37188701</t>
+          <t>https://www.vanguardia.com/colombia/</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 06:58 p. m.</t>
+          <t>31/05/2026 04:14 p. m.</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -6583,24 +6575,24 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t>Abelardo de la Espriella celebra su paso a segunda vuelta: “Vamos a derrotar la tiranía y el absolutismo”</t>
+          <t>Elecciones transparente y tranquilas: balance de observadores de Unión Europea</t>
         </is>
       </c>
       <c r="E228" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/abelardo-discurso-segunda-vuelta-elecciones-2026-celebracion-BN37189448</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/31/elecciones-transparente-y-tranquilas-balance-de-observadores-de-union-europea/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 05:58 p. m.</t>
+          <t>31/05/2026 03:38 p. m.</t>
         </is>
       </c>
       <c r="B229" s="6" t="inlineStr">
@@ -6610,24 +6602,24 @@
       </c>
       <c r="C229" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D229" s="7" t="inlineStr">
         <is>
-          <t>“Este millón de votos decidirá el futuro de nuestro país” ¿Sergio Fajardo tomará partido y anunciará apoyos?</t>
+          <t>Habitantes de Islas del Rosario, en Cartagena, advierten que no participarán en votaciones por falta de energía</t>
         </is>
       </c>
       <c r="E229" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/sergio-fajardo-elecciones-resultados-discurso-que-dijo-ON37187768</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/31/habitantes-de-islas-del-rosario-en-cartagena-advierten-que-no-participaran-en-votaciones-por-falta-de-energia/</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 05:58 p. m.</t>
+          <t>31/05/2026 03:26 p. m.</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -6637,24 +6629,24 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D230" s="4" t="inlineStr">
         <is>
-          <t>“¡Inés, una valeriana o algo!”: los divertidos memes que dejó la primera vuelta presidencial</t>
+          <t>Emergencia en Quindío: vehículo choca contra una fonda en el sector de Barragán</t>
         </is>
       </c>
       <c r="E230" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/tendencias/memes-primera-vuelta-presidencial-mayo-2026-ON37182862</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/31/emergencia-en-quindio-vehiculo-choca-contra-una-fonda-en-el-sector-de-barragan/</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 05:58 p. m.</t>
+          <t>31/05/2026 03:09 p. m.</t>
         </is>
       </c>
       <c r="B231" s="6" t="inlineStr">
@@ -6664,24 +6656,24 @@
       </c>
       <c r="C231" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D231" s="7" t="inlineStr">
         <is>
-          <t>Aunque encuestas mostraban a Cepeda ganando, Atlas Intel fue la que más se acercó al éxito de Abelardo</t>
+          <t>Procuraduría abrió investigación al ministro Sanguino por posible participación en política</t>
         </is>
       </c>
       <c r="E231" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/elecciones-2026-resultados-ivan-cepeda-departamentos-LN37183901</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/31/procuraduria-abrio-investigacion-al-ministro-sanguino-por-posible-participacion-en-politica/</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 05:58 p. m.</t>
+          <t>31/05/2026 02:28 p. m.</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -6691,24 +6683,24 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D232" s="4" t="inlineStr">
         <is>
-          <t>Hernán Penagos, otro de los grandes ganadores de la jornada electoral</t>
+          <t>Medicina legal inicia proceso de identificación de los cuerpos de 48 disidentes</t>
         </is>
       </c>
       <c r="E232" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/especiales/elecciones-2026/ciudadanos-consultar-actas-electorales-votacion-PN37183084</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/31/medicina-legal-inicia-proceso-de-identificacion-de-los-cuerpos-de-48-disidentes/</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 05:58 p. m.</t>
+          <t>31/05/2026 02:26 p. m.</t>
         </is>
       </c>
       <c r="B233" s="6" t="inlineStr">
@@ -6718,24 +6710,24 @@
       </c>
       <c r="C233" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D233" s="7" t="inlineStr">
         <is>
-          <t>El costo de la derrota: estos son los candidatos que no alcanzaron la reposición de votos en las presidenciales 2026</t>
+          <t>Santander, entre los departamentos con fallas en redes de telecomunicaciones durante la jornada electoral</t>
         </is>
       </c>
       <c r="E233" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/estos-son-candidatos-no-alcanzan-reposicion-votos-elecciones-2026-BN37184401</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/31/santander-entre-los-departamentos-con-fallas-en-redes-de-telecomunicaciones-durante-la-jornada-electoral/</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 04:58 p. m.</t>
+          <t>31/05/2026 02:01 p. m.</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -6745,24 +6737,24 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D234" s="4" t="inlineStr">
         <is>
-          <t>“Transparente y garantista”: la UE tumbó fantasma del fraude y dio balance de las elecciones presidenciales en Colombia</t>
+          <t>Elecciones presidenciales: incautan $110 millones y capturan a una persona en operativos de la Policía</t>
         </is>
       </c>
       <c r="E234" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/union-europea-balance-elecciones-presidenciales-colombia-CC37179865</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/31/elecciones-presidenciales-incautan-110-millones-y-capturan-a-una-persona-en-operativos-de-la-policia/</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 04:58 p. m.</t>
+          <t>31/05/2026 01:40 p. m.</t>
         </is>
       </c>
       <c r="B235" s="6" t="inlineStr">
@@ -6772,24 +6764,24 @@
       </c>
       <c r="C235" s="6" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D235" s="7" t="inlineStr">
         <is>
-          <t>Cinco capturas por presunta compra de votos y un joven con $110 millones en efectivo: los lunares de la jornada electoral de este 31 de mayo</t>
+          <t>Identifican grupo de personas que presuntamente compraba votos en Popayán</t>
         </is>
       </c>
       <c r="E235" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/cinco-capturas-compra-votos-joven-110-millones-lunares-jornada-electoral-31-mayo-GN37180688</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/31/identifican-grupo-de-personas-que-presuntamente-compraba-votos-en-popayan/</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 03:58 p. m.</t>
+          <t>31/05/2026 11:52 a. m.</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -6799,24 +6791,24 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Vanguardia</t>
         </is>
       </c>
       <c r="D236" s="4" t="inlineStr">
         <is>
-          <t>Conozca a los grandes “cerebros” detrás de las selecciones en el Mundial</t>
+          <t>Cárcel para médico de Bogotá por presunto abuso de dos niñas en las consultas</t>
         </is>
       </c>
       <c r="E236" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/especiales/mundial-2026/mejores-entrenadores-mundial-2026-ED37169287</t>
+          <t>https://www.vanguardia.com/colombia/2026/05/30/carcel-para-medico-de-bogota-por-presunto-abuso-de-dos-ninas-en-las-consultas/</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 03:58 p. m.</t>
+          <t>31/05/2026 08:58 p. m.</t>
         </is>
       </c>
       <c r="B237" s="6" t="inlineStr">
@@ -6831,19 +6823,19 @@
       </c>
       <c r="D237" s="7" t="inlineStr">
         <is>
-          <t>En video | Análisis de los resultados de las elecciones presidenciales de este 31 de mayo</t>
+          <t>Claudia López advirtió sobre el escenario político en la segunda vuelta tras los resultados: “Esa opción todavía no ha ganado...”</t>
         </is>
       </c>
       <c r="E237" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/en-vivo-elecciones-presidenciales-2026-transmision-especial-MC37173249</t>
+          <t>https://www.elcolombiano.com/especiales/elecciones-2026/claudia-lopez-llama-a-defender-la-democracia-PM37194290</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 02:58 p. m.</t>
+          <t>31/05/2026 07:58 p. m.</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -6858,19 +6850,19 @@
       </c>
       <c r="D238" s="4" t="inlineStr">
         <is>
-          <t>Europa se rinde ante Luis Díaz: top 10 de la Champions y figura absoluta</t>
+          <t>EE. UU. envió mensaje a Colombia e invitó a respaldar la voluntad popular en las elecciones</t>
         </is>
       </c>
       <c r="E238" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/deportes/futbol/luis-diaz-top-10-champions-bayern-munich-CC37172404</t>
+          <t>https://www.elcolombiano.com/internacional/ee-uu-respalda-a-colombia-primera-vuelta-elecciones-2026-BM37191123</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 01:58 p. m.</t>
+          <t>31/05/2026 07:58 p. m.</t>
         </is>
       </c>
       <c r="B239" s="6" t="inlineStr">
@@ -6885,19 +6877,19 @@
       </c>
       <c r="D239" s="7" t="inlineStr">
         <is>
-          <t>La MOE alerta por presunta compra de votos en Sucre durante las elecciones presidenciales</t>
+          <t>Los totes de la primera vuelta presidencial</t>
         </is>
       </c>
       <c r="E239" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/especiales/elecciones-2026/moe-alerta-presunta-compra-votos-sucre-durante-elecciones-presidenciales-ID37160109</t>
+          <t>https://www.elcolombiano.com/multimedia/videos/los-totes-de-la-primera-vuelta-presidencial-FM37191105</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 01:58 p. m.</t>
+          <t>31/05/2026 07:58 p. m.</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -6912,19 +6904,19 @@
       </c>
       <c r="D240" s="4" t="inlineStr">
         <is>
-          <t>La verdadera razón del último partido de la Selección en Colombia antes del Mundial</t>
+          <t>“Hay un desfase que queremos verificar”: Cepeda no acepta la derrota y dice que esperará hasta el escrutinio</t>
         </is>
       </c>
       <c r="E240" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/especiales/mundial-2026/por-que-seleccion-colombia-juega-con-costa-rica-despedida-al-mundial-estadio-el-campin-hora-donde-ver-MD37166093</t>
+          <t>https://www.elcolombiano.com/especiales/elecciones-2026/ivan-cepeda-no-acepta-derrota-resultados-elecciones-2026-OM37193379</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 01:58 p. m.</t>
+          <t>31/05/2026 06:58 p. m.</t>
         </is>
       </c>
       <c r="B241" s="6" t="inlineStr">
@@ -6939,19 +6931,19 @@
       </c>
       <c r="D241" s="7" t="inlineStr">
         <is>
-          <t>Nacional viaja a Barranquilla para iniciar una final con cuentas pendientes entre los Arias, Diego y Alfredo</t>
+          <t>Así votó Antioquia en primera vuelta: De la Espriella (54%) dobló a Cepeda (25,4%)</t>
         </is>
       </c>
       <c r="E241" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/deportes/futbol/nacional-junior-final-diego-arias-alfredo-arias-rueda-de-prensa-barranquilla-liga-betplay-BD37168018</t>
+          <t>https://www.elcolombiano.com/antioquia/antioquia-elecciones-presidenciales-colombia-2026-primera-vuelta-ON37188723</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 01:58 p. m.</t>
+          <t>31/05/2026 06:58 p. m.</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -6966,19 +6958,19 @@
       </c>
       <c r="D242" s="4" t="inlineStr">
         <is>
-          <t>Procuraduría abrió investigación al ministro Sanguino por posible participación en política a favor de Cepeda</t>
+          <t>Uribe y su derrota en las presidenciales: se la juega ahora por De la Espriella</t>
         </is>
       </c>
       <c r="E242" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/procuraduria-abre-investigacion-mintrabajo-antonio-sanguino-participacion-politica-GD37166220</t>
+          <t>https://www.elcolombiano.com/especiales/elecciones-2026/uribe-derrota-presidenciales-de-la-espriella-IM37190697</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 01:58 p. m.</t>
+          <t>31/05/2026 06:58 p. m.</t>
         </is>
       </c>
       <c r="B243" s="6" t="inlineStr">
@@ -6993,19 +6985,19 @@
       </c>
       <c r="D243" s="7" t="inlineStr">
         <is>
-          <t>Alcaldesa de El Paujil, Caquetá, salió con poncho de Cepeda y la Procuraduría la suspendió</t>
+          <t>Con más de 670.000 votos, De La Espriella barrió en Medellín en la primera vuelta</t>
         </is>
       </c>
       <c r="E243" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/especiales/elecciones-2026/alcaldesa-el-paujil-suspendida-por-presunta-participacion-politica-ED37166310</t>
+          <t>https://www.elcolombiano.com/medellin/resultados-medellin-primera-vuelta-elecciones-presidenciales-2026-DN37188975</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 12:58 p. m.</t>
+          <t>31/05/2026 06:58 p. m.</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -7020,19 +7012,19 @@
       </c>
       <c r="D244" s="4" t="inlineStr">
         <is>
-          <t>¿Podían Petro, Benedetti y Char mostrar su voto? Expertos explican límites legales para funcionarios públicos y qué les podría pasar</t>
+          <t>“Increíble que Colombia se debata su futuro alrededor de homofobia, machismo e irresponsabilidad”: Oviedo</t>
         </is>
       </c>
       <c r="E244" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/podian-petro-benedetti-char-voto-expertos-explican-limites-legales-funcionarios-publicos-MD37165933</t>
+          <t>https://www.elcolombiano.com/colombia/juan-daniel-oviedo-dice-a-quien-apoyar-elecciones-abelardo-cepeda-PN37189431</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 12:58 p. m.</t>
+          <t>31/05/2026 06:58 p. m.</t>
         </is>
       </c>
       <c r="B245" s="6" t="inlineStr">
@@ -7047,19 +7039,19 @@
       </c>
       <c r="D245" s="7" t="inlineStr">
         <is>
-          <t>Autoridades reportaron una captura y una sanción contra un testigo electoral durante las votaciones en Medellín</t>
+          <t>“Anuncio mi apoyo a Abelardo e invito a que derrotemos a Cepeda”: Paloma Valencia reconoce resultados de primera vuelta</t>
         </is>
       </c>
       <c r="E245" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/medellin/autoridades-reportan-captura-y-sancion-testigo-electoral-votaciones-medellin-GD37164828</t>
+          <t>https://www.elcolombiano.com/colombia/paloma-valencia-apoyo-abelardo-de-la-espriella-segunda-vuelta-junio-2026-ON37188701</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 11:58 a. m.</t>
+          <t>31/05/2026 06:58 p. m.</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -7074,19 +7066,19 @@
       </c>
       <c r="D246" s="4" t="inlineStr">
         <is>
-          <t>Kvaratskhelia es elegido como el mejor jugador de la Champions League 25/26</t>
+          <t>Abelardo de la Espriella celebra su paso a segunda vuelta: “Vamos a derrotar la tiranía y el absolutismo”</t>
         </is>
       </c>
       <c r="E246" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/deportes/futbol/khvicha-kvartaskhelia-psg-paris-champions-mvp-liga-de-campeones-ND37162069</t>
+          <t>https://www.elcolombiano.com/colombia/abelardo-discurso-segunda-vuelta-elecciones-2026-celebracion-BN37189448</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 10:58 a. m.</t>
+          <t>31/05/2026 05:58 p. m.</t>
         </is>
       </c>
       <c r="B247" s="6" t="inlineStr">
@@ -7101,19 +7093,19 @@
       </c>
       <c r="D247" s="7" t="inlineStr">
         <is>
-          <t>MinTIC monitorea fallas en redes de telecomunicaciones en 18 departamentos durante las elecciones</t>
+          <t>“Este millón de votos decidirá el futuro de nuestro país” ¿Sergio Fajardo tomará partido y anunciará apoyos?</t>
         </is>
       </c>
       <c r="E247" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/elecciones-hoy-mintic-falla-redes-telecomunicaciones-18-departamentos-LD37160597</t>
+          <t>https://www.elcolombiano.com/colombia/sergio-fajardo-elecciones-resultados-discurso-que-dijo-ON37187768</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 07:58 a. m.</t>
+          <t>31/05/2026 05:58 p. m.</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -7128,17 +7120,21 @@
       </c>
       <c r="D248" s="4" t="inlineStr">
         <is>
-          <t>Minuto a minuto | Así transcurrió la jornada de elecciones en la que De la Espriella y Cepeda ganaron el paso a segunda vuelta</t>
+          <t>“¡Inés, una valeriana o algo!”: los divertidos memes que dejó la primera vuelta presidencial</t>
         </is>
       </c>
       <c r="E248" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/especiales/elecciones-2026/en-vivo-colombia-elecciones-hoy-presidente-minuto-a-minuto-31-de-mayo-CA37156037</t>
+          <t>https://www.elcolombiano.com/tendencias/memes-primera-vuelta-presidencial-mayo-2026-ON37182862</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="6" t="inlineStr"/>
+      <c r="A249" s="6" t="inlineStr">
+        <is>
+          <t>31/05/2026 05:58 p. m.</t>
+        </is>
+      </c>
       <c r="B249" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7151,17 +7147,21 @@
       </c>
       <c r="D249" s="7" t="inlineStr">
         <is>
-          <t>Operativo destapa helicóptero con pasado oscuro y motor Rolls-Royce</t>
+          <t>Aunque encuestas mostraban a Cepeda ganando, Atlas Intel fue la que más se acercó al éxito de Abelardo</t>
         </is>
       </c>
       <c r="E249" s="8" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/ejercito-incauta-helicoptero-de-la-mafia-NG33717192</t>
+          <t>https://www.elcolombiano.com/colombia/elecciones-2026-resultados-ivan-cepeda-departamentos-LN37183901</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="3" t="inlineStr"/>
+      <c r="A250" s="3" t="inlineStr">
+        <is>
+          <t>31/05/2026 05:58 p. m.</t>
+        </is>
+      </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7174,19 +7174,19 @@
       </c>
       <c r="D250" s="4" t="inlineStr">
         <is>
-          <t>Cuerpos de disidentes muertos en Guaviare tenían explosivos para atentar contra la Fuerza Pública</t>
+          <t>Hernán Penagos, otro de los grandes ganadores de la jornada electoral</t>
         </is>
       </c>
       <c r="E250" s="5" t="inlineStr">
         <is>
-          <t>https://www.elcolombiano.com/colombia/explosivos-en-cuerpos-evacuados-tras-combates-guaviare-farc-JB37145950</t>
+          <t>https://www.elcolombiano.com/especiales/elecciones-2026/ciudadanos-consultar-actas-electorales-votacion-PN37183084</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 07:44 p. m.</t>
+          <t>31/05/2026 05:58 p. m.</t>
         </is>
       </c>
       <c r="B251" s="6" t="inlineStr">
@@ -7196,24 +7196,24 @@
       </c>
       <c r="C251" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D251" s="7" t="inlineStr">
         <is>
-          <t>Iván Cepeda denuncia injerencia extranjera tras resultados de primera vuelta</t>
+          <t>El costo de la derrota: estos son los candidatos que no alcanzaron la reposición de votos en las presidenciales 2026</t>
         </is>
       </c>
       <c r="E251" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/2026/05/31/ivan-cepeda-denuncia-injerencia-extranjera-tras-resultados-de-primera-vuelta/</t>
+          <t>https://www.elcolombiano.com/colombia/estos-son-candidatos-no-alcanzan-reposicion-votos-elecciones-2026-BN37184401</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 07:37 p. m.</t>
+          <t>31/05/2026 04:58 p. m.</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -7223,24 +7223,24 @@
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D252" s="4" t="inlineStr">
         <is>
-          <t>Eduardo Verano destacó tranquilidad de la jornada electoral en el Atlántico</t>
+          <t>“Transparente y garantista”: la UE tumbó fantasma del fraude y dio balance de las elecciones presidenciales en Colombia</t>
         </is>
       </c>
       <c r="E252" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/regional/atlantico/2026/05/31/eduardo-verano-destaco-tranquilidad-de-la-jornada-electoral-en-el-atlantico/</t>
+          <t>https://www.elcolombiano.com/colombia/union-europea-balance-elecciones-presidenciales-colombia-CC37179865</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 07:37 p. m.</t>
+          <t>31/05/2026 04:58 p. m.</t>
         </is>
       </c>
       <c r="B253" s="6" t="inlineStr">
@@ -7250,24 +7250,24 @@
       </c>
       <c r="C253" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D253" s="7" t="inlineStr">
         <is>
-          <t>Atlántico</t>
+          <t>Cinco capturas por presunta compra de votos y un joven con $110 millones en efectivo: los lunares de la jornada electoral de este 31 de mayo</t>
         </is>
       </c>
       <c r="E253" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/regional/atlantico/</t>
+          <t>https://www.elcolombiano.com/colombia/cinco-capturas-compra-votos-joven-110-millones-lunares-jornada-electoral-31-mayo-GN37180688</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 07:23 p. m.</t>
+          <t>31/05/2026 03:58 p. m.</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -7277,24 +7277,24 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D254" s="4" t="inlineStr">
         <is>
-          <t>Policía reporta balance de primera vuelta presidencial: 89 capturas y sin alteraciones</t>
+          <t>Conozca a los grandes “cerebros” detrás de las selecciones en el Mundial</t>
         </is>
       </c>
       <c r="E254" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/2026/05/31/policia-reporta-balance-de-primera-vuelta-presidencial-89-capturas-y-sin-alteraciones/</t>
+          <t>https://www.elcolombiano.com/especiales/mundial-2026/mejores-entrenadores-mundial-2026-ED37169287</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 07:18 p. m.</t>
+          <t>31/05/2026 03:58 p. m.</t>
         </is>
       </c>
       <c r="B255" s="6" t="inlineStr">
@@ -7304,24 +7304,24 @@
       </c>
       <c r="C255" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D255" s="7" t="inlineStr">
         <is>
-          <t>“Como presidente no acepto los resultados”: Petro reacciona tras la primera vuelta</t>
+          <t>En video | Análisis de los resultados de las elecciones presidenciales de este 31 de mayo</t>
         </is>
       </c>
       <c r="E255" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/2026/05/31/como-presidente-no-acepto-los-resultados-petro-reacciona-tras-la-primera-vuelta/</t>
+          <t>https://www.elcolombiano.com/colombia/en-vivo-elecciones-presidenciales-2026-transmision-especial-MC37173249</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 07:01 p. m.</t>
+          <t>31/05/2026 02:58 p. m.</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -7331,24 +7331,24 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr">
         <is>
-          <t>Así fue la votación del Atlántico para la primera vuelta presidencial 2026</t>
+          <t>Europa se rinde ante Luis Díaz: top 10 de la Champions y figura absoluta</t>
         </is>
       </c>
       <c r="E256" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/regional/atlantico/2026/05/31/asi-fue-la-votacion-del-atlantico-para-la-primera-vuelta-presidencial-2026/</t>
+          <t>https://www.elcolombiano.com/deportes/futbol/luis-diaz-top-10-champions-bayern-munich-CC37172404</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 06:30 p. m.</t>
+          <t>31/05/2026 01:58 p. m.</t>
         </is>
       </c>
       <c r="B257" s="6" t="inlineStr">
@@ -7358,24 +7358,24 @@
       </c>
       <c r="C257" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D257" s="7" t="inlineStr">
         <is>
-          <t>Tras derrota en primer vuelta, Paloma Valencia anunció su apoyo a Abelardo</t>
+          <t>La verdadera razón del último partido de la Selección en Colombia antes del Mundial</t>
         </is>
       </c>
       <c r="E257" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/2026/05/31/tras-derrota-en-primer-vuelta-paloma-valencia-anuncio-su-apoyo-a-abelardo/</t>
+          <t>https://www.elcolombiano.com/especiales/mundial-2026/por-que-seleccion-colombia-juega-con-costa-rica-despedida-al-mundial-estadio-el-campin-hora-donde-ver-MD37166093</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 06:17 p. m.</t>
+          <t>31/05/2026 01:58 p. m.</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -7385,24 +7385,24 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D258" s="4" t="inlineStr">
         <is>
-          <t>¿Qué día será la segunda vuelta para elegir al presidente en Colombia?</t>
+          <t>Nacional viaja a Barranquilla para iniciar una final con cuentas pendientes entre los Arias, Diego y Alfredo</t>
         </is>
       </c>
       <c r="E258" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/2026/05/31/que-dia-sera-la-segunda-vuelta-para-elegir-al-presidente-en-colombia/</t>
+          <t>https://www.elcolombiano.com/deportes/futbol/nacional-junior-final-diego-arias-alfredo-arias-rueda-de-prensa-barranquilla-liga-betplay-BD37168018</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 06:16 p. m.</t>
+          <t>31/05/2026 01:58 p. m.</t>
         </is>
       </c>
       <c r="B259" s="6" t="inlineStr">
@@ -7412,24 +7412,24 @@
       </c>
       <c r="C259" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D259" s="7" t="inlineStr">
         <is>
-          <t>Abelardo de la Espriella se pronuncia tras arrasar en la primera vuelta presidencial de Colombia 2026</t>
+          <t>Procuraduría abrió investigación al ministro Sanguino por posible participación en política a favor de Cepeda</t>
         </is>
       </c>
       <c r="E259" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/2026/05/31/abelardo-de-la-espriella-se-pronuncia-tras-arrasar-en-la-primera-vuelta-presidencial-de-colombia-2026/</t>
+          <t>https://www.elcolombiano.com/colombia/procuraduria-abre-investigacion-mintrabajo-antonio-sanguino-participacion-politica-GD37166220</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 06:05 p. m.</t>
+          <t>31/05/2026 01:58 p. m.</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
@@ -7439,24 +7439,24 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t>Autoridades revelan cómo transcurrió la jornada electoral en Bolívar</t>
+          <t>Alcaldesa de El Paujil, Caquetá, salió con poncho de Cepeda y la Procuraduría la suspendió</t>
         </is>
       </c>
       <c r="E260" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/regional/bolivar/2026/05/31/autoridades-revelan-como-transcurrio-la-jornada-electoral-en-bolivar/</t>
+          <t>https://www.elcolombiano.com/especiales/elecciones-2026/alcaldesa-el-paujil-suspendida-por-presunta-participacion-politica-ED37166310</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 05:02 p. m.</t>
+          <t>31/05/2026 01:58 p. m.</t>
         </is>
       </c>
       <c r="B261" s="6" t="inlineStr">
@@ -7466,24 +7466,24 @@
       </c>
       <c r="C261" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D261" s="7" t="inlineStr">
         <is>
-          <t>Abelardo de la Espriella e Iván Cepeda disputarán la segunda vuelta presidencial en Colombia</t>
+          <t>La MOE alerta por presunta compra de votos en Sucre durante las elecciones presidenciales</t>
         </is>
       </c>
       <c r="E261" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/2026/05/31/abelardo-de-la-espriella-e-ivan-cepeda-disputaran-la-segunda-vuelta-presidencial-en-colombia/</t>
+          <t>https://www.elcolombiano.com/especiales/elecciones-2026/moe-alerta-presunta-compra-votos-sucre-durante-elecciones-presidenciales-ID37160109</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 05:02 p. m.</t>
+          <t>31/05/2026 12:58 p. m.</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
@@ -7493,24 +7493,24 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D262" s="4" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Autoridades reportaron una captura y una sanción contra un testigo electoral durante las votaciones en Medellín</t>
         </is>
       </c>
       <c r="E262" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/colombia/</t>
+          <t>https://www.elcolombiano.com/medellin/autoridades-reportan-captura-y-sancion-testigo-electoral-votaciones-medellin-GD37164828</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 04:37 p. m.</t>
+          <t>31/05/2026 11:58 a. m.</t>
         </is>
       </c>
       <c r="B263" s="6" t="inlineStr">
@@ -7520,24 +7520,24 @@
       </c>
       <c r="C263" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D263" s="7" t="inlineStr">
         <is>
-          <t>Hallaron sin vida a Marliez Genz, la turista neerlandesa que desapareció en Quindío</t>
+          <t>Kvaratskhelia es elegido como el mejor jugador de la Champions League 25/26</t>
         </is>
       </c>
       <c r="E263" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/31/hallaron-sin-vida-a-marliez-genz-la-turista-neerlandesa-que-desaparecio-en-quindio/</t>
+          <t>https://www.elcolombiano.com/deportes/futbol/khvicha-kvartaskhelia-psg-paris-champions-mvp-liga-de-campeones-ND37162069</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 04:33 p. m.</t>
+          <t>31/05/2026 10:58 a. m.</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
@@ -7547,24 +7547,24 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D264" s="4" t="inlineStr">
         <is>
-          <t>A ‘Yayo’ lo arrolló una tractomula y murió tras 2 días de estar hospitalizado</t>
+          <t>MinTIC monitorea fallas en redes de telecomunicaciones en 18 departamentos durante las elecciones</t>
         </is>
       </c>
       <c r="E264" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/31/a-yayo-lo-arrollo-una-tractomula-y-fallecio-tras-2-dias-de-estar-hospitalizad/</t>
+          <t>https://www.elcolombiano.com/colombia/elecciones-hoy-mintic-falla-redes-telecomunicaciones-18-departamentos-LD37160597</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 04:25 p. m.</t>
+          <t>31/05/2026 07:58 a. m.</t>
         </is>
       </c>
       <c r="B265" s="6" t="inlineStr">
@@ -7574,26 +7574,22 @@
       </c>
       <c r="C265" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D265" s="7" t="inlineStr">
         <is>
-          <t>FIFA reveló cuál será la prioridad de los árbitros en el Mundial</t>
+          <t>Minuto a minuto | Así transcurrió la jornada de elecciones en la que De la Espriella y Cepeda ganaron el paso a segunda vuelta</t>
         </is>
       </c>
       <c r="E265" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/deportes/2026/05/31/fifa-revelo-cual-sera-la-prioridad-de-los-arbitros-en-el-mundial/</t>
+          <t>https://www.elcolombiano.com/especiales/elecciones-2026/en-vivo-colombia-elecciones-hoy-presidente-minuto-a-minuto-31-de-mayo-CA37156037</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="3" t="inlineStr">
-        <is>
-          <t>31/05/2026 04:25 p. m.</t>
-        </is>
-      </c>
+      <c r="A266" s="3" t="inlineStr"/>
       <c r="B266" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7601,24 +7597,24 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D266" s="4" t="inlineStr">
         <is>
-          <t>Deportes</t>
+          <t>Operativo destapa helicóptero con pasado oscuro y motor Rolls-Royce</t>
         </is>
       </c>
       <c r="E266" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/deportes/</t>
+          <t>https://www.elcolombiano.com/colombia/ejercito-incauta-helicoptero-de-la-mafia-NG33717192</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 04:11 p. m.</t>
+          <t>31/05/2026 08:05 p. m.</t>
         </is>
       </c>
       <c r="B267" s="6" t="inlineStr">
@@ -7628,24 +7624,24 @@
       </c>
       <c r="C267" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D267" s="7" t="inlineStr">
         <is>
-          <t>¿Qué le pasó a Diego Guauque? El periodista deberá someterse a una nueva cirugía</t>
+          <t>¿Quién es Iván Cepeda, el líder de izquierda que llega a la segunda vuelta presidencial?</t>
         </is>
       </c>
       <c r="E267" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/farandula/2026/05/31/que-le-paso-a-diego-guauque-el-periodista-debera-someterse-a-una-nueva-cirugia/</t>
+          <t>https://www.noticiasrcn.com/colombia/quien-es-ivan-cepeda-quien-llega-a-segunda-vuelta-presidencial-1026606</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 03:36 p. m.</t>
+          <t>31/05/2026 07:59 p. m.</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
@@ -7655,24 +7651,24 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr">
         <is>
-          <t>Chris Rodríguez llegó de Puerto Rico para operarse y murió en el quirófano</t>
+          <t>Juan Daniel Oviedo se aparta de la decisión de Paloma Valencia de sumarse a la campaña de la Espriella</t>
         </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/31/chris-rodriguez-llego-de-puerto-rico-para-operarse-y-murio-en-el-quirofano/</t>
+          <t>https://www.noticiasrcn.com/colombia/juan-daniel-oviedo-se-aparta-de-la-decision-de-paloma-valencia-de-sumarse-a-la-campana-de-la-espriella-1026587</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 02:33 p. m.</t>
+          <t>31/05/2026 07:47 p. m.</t>
         </is>
       </c>
       <c r="B269" s="6" t="inlineStr">
@@ -7682,24 +7678,24 @@
       </c>
       <c r="C269" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D269" s="7" t="inlineStr">
         <is>
-          <t>Elian Hernández, el barbero informal que sicario le quitó la vida a balazos</t>
+          <t>“Obtuvimos 10 millones de votos mal contados”: Iván Cepeda tras preconteo electoral</t>
         </is>
       </c>
       <c r="E269" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/31/elian-hernandez-el-barbero-informal-que-sicario-le-quito-la-vida-a-balazos/</t>
+          <t>https://www.noticiasrcn.com/colombia/obtuvimos-10-millones-de-votos-mal-contados-ivan-cepeda-denuncio-irregularidades-en-elecciones-1026594</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 02:00 p. m.</t>
+          <t>31/05/2026 07:41 p. m.</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
@@ -7709,24 +7705,24 @@
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D270" s="4" t="inlineStr">
         <is>
-          <t>Él era Virgilio Bueno, el reconocido comerciante que mataron en un ataque de sicarios</t>
+          <t>8 capturas, 10 noticias criminales y 77 desaparecidos en las urnas: Fiscalía sobre su plan de acción durante las elecciones</t>
         </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/31/el-era-virgilio-bueno-el-reconocido-comerciante-que-murio-en-un-ataque-de-sicarios/</t>
+          <t>https://www.noticiasrcn.com/colombia/fiscalia-mantiene-plan-de-accion-contra-delitos-en-las-elecciones-2026-1026569</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 01:25 p. m.</t>
+          <t>31/05/2026 07:37 p. m.</t>
         </is>
       </c>
       <c r="B271" s="6" t="inlineStr">
@@ -7736,24 +7732,24 @@
       </c>
       <c r="C271" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D271" s="7" t="inlineStr">
         <is>
-          <t>Video: ¿Qué ocasionó incendio en bodega de reciclaje en el barrio 13 de Junio?</t>
+          <t>¿Se puede modificar el puesto de votación para la segunda vuelta de las elecciones 2026?</t>
         </is>
       </c>
       <c r="E271" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/31/video-que-ocasiono-incendio-en-bodega-de-reciclaje-en-el-barrio-13-de-junio/</t>
+          <t>https://www.noticiasrcn.com/colombia/no-se-puede-cambiar-el-puesto-de-votacion-para-la-segunda-vuelta-de-las-elecciones-1026588</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 11:54 a. m.</t>
+          <t>31/05/2026 07:30 p. m.</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
@@ -7763,24 +7759,24 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D272" s="4" t="inlineStr">
         <is>
-          <t>‘Quilla’ no votará: cayó con prendas de oro y celulares robados en el Pie de La Popa</t>
+          <t>Abelardo de la Espriella, el ‘outsider’ millonario que se disputa la Presidencia de Colombia</t>
         </is>
       </c>
       <c r="E272" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/31/quilla-no-votara-cayo-con-prendas-de-oro-y-celulares-robados-en-el-pie-de-la-popa/</t>
+          <t>https://www.noticiasrcn.com/colombia/quien-es-abelardo-de-la-espriella-el-tigre-candidato-a-la-presidencia-de-colombia-1026581</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 11:33 a. m.</t>
+          <t>31/05/2026 07:21 p. m.</t>
         </is>
       </c>
       <c r="B273" s="6" t="inlineStr">
@@ -7790,22 +7786,26 @@
       </c>
       <c r="C273" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D273" s="7" t="inlineStr">
         <is>
-          <t>Así mataron a alias ‘Chupi’ en Calamar: intentaron linchar a su expareja</t>
+          <t>Presidente Gustavo Petro no aceptó resultados del preconteo y denunció alteraciones en software</t>
         </is>
       </c>
       <c r="E273" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/sucesos/2026/05/31/asi-mataron-a-alias-chupi-en-calamar-intentaron-lichar-a-su-expareja/</t>
+          <t>https://www.noticiasrcn.com/colombia/gustavo-petro-no-acepto-resultados-en-primera-vuelta-y-denuncio-irregularidades-1026575</t>
         </is>
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="3" t="inlineStr"/>
+      <c r="A274" s="3" t="inlineStr">
+        <is>
+          <t>31/05/2026 07:14 p. m.</t>
+        </is>
+      </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7813,22 +7813,26 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D274" s="4" t="inlineStr">
         <is>
-          <t>Premios Excelencia El Universal 2026: ya están abiertas las postulaciones</t>
+          <t>Así reaccionaron “los quemados” a los resultados de primera vuelta</t>
         </is>
       </c>
       <c r="E274" s="5" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/cartagena/2026/05/26/premios-excelencia-el-universal-2026-ya-estan-abiertas-las-postulaciones/</t>
+          <t>https://www.noticiasrcn.com/colombia/asi-reaccionaron-los-quemados-a-los-resultados-de-primera-vuelta-1026544</t>
         </is>
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="6" t="inlineStr"/>
+      <c r="A275" s="6" t="inlineStr">
+        <is>
+          <t>31/05/2026 06:57 p. m.</t>
+        </is>
+      </c>
       <c r="B275" s="6" t="inlineStr">
         <is>
           <t>Medio de Comunicación</t>
@@ -7836,24 +7840,24 @@
       </c>
       <c r="C275" s="6" t="inlineStr">
         <is>
-          <t>El Universal</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D275" s="7" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Así quedó el mapa político en primera vuelta: regiones que lideraron de la Espriella y Cepeda</t>
         </is>
       </c>
       <c r="E275" s="8" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.co/cartagena/</t>
+          <t>https://www.noticiasrcn.com/colombia/asi-quedo-el-mapa-politico-en-primera-vuelta-regiones-que-lideraron-de-la-espriella-y-cepeda-1026528</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 06:28 p. m.</t>
+          <t>31/05/2026 06:39 p. m.</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
@@ -7863,24 +7867,24 @@
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>Canal Trece</t>
+          <t>Noticias RCN</t>
         </is>
       </c>
       <c r="D276" s="4" t="inlineStr">
         <is>
-          <t>Paloma Valencia anuncia su unión a Abelardo de la Espriella: “Seguiré en la batalla para derrotar a Iván Cepeda»</t>
+          <t>Sergio Fajardo habla sobre lo que le pedirá a sus votantes de cara a la segunda vuelta</t>
         </is>
       </c>
       <c r="E276" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/paloma-valencia-anuncia-su-union-a-abelardo-de-la-espriella-seguire-en-la-batalla-para-derrotar-a-ivan-cepeda/</t>
+          <t>https://www.noticiasrcn.com/colombia/que-pasara-con-los-votos-de-sergio-fajardo-en-la-segunda-vuelta-presidencial-1026542</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 06:22 p. m.</t>
+          <t>31/05/2026 06:28 p. m.</t>
         </is>
       </c>
       <c r="B277" s="6" t="inlineStr">
@@ -7895,19 +7899,19 @@
       </c>
       <c r="D277" s="7" t="inlineStr">
         <is>
-          <t>El factor Fajardo: Más de un millón de ciudadanos eligen el centro y definen las llaves del balotaje</t>
+          <t>Paloma Valencia anuncia su unión a Abelardo de la Espriella: “Seguiré en la batalla para derrotar a Iván Cepeda»</t>
         </is>
       </c>
       <c r="E277" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/el-factor-fajardo-mas-de-un-millon-de-ciudadanos-eligen-el-centro-y-definen-las-llaves-del-balotaje/</t>
+          <t>https://canaltrece.com.co/noticias/paloma-valencia-anuncia-su-union-a-abelardo-de-la-espriella-seguire-en-la-batalla-para-derrotar-a-ivan-cepeda/</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 06:16 p. m.</t>
+          <t>31/05/2026 06:22 p. m.</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
@@ -7922,19 +7926,19 @@
       </c>
       <c r="D278" s="4" t="inlineStr">
         <is>
-          <t>¿Qué regiones votaron por cada candidato?</t>
+          <t>El factor Fajardo: Más de un millón de ciudadanos eligen el centro y definen las llaves del balotaje</t>
         </is>
       </c>
       <c r="E278" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/que-regiones-votaron-por-cada-candidato/</t>
+          <t>https://canaltrece.com.co/noticias/el-factor-fajardo-mas-de-un-millon-de-ciudadanos-eligen-el-centro-y-definen-las-llaves-del-balotaje/</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 06:07 p. m.</t>
+          <t>31/05/2026 06:16 p. m.</t>
         </is>
       </c>
       <c r="B279" s="6" t="inlineStr">
@@ -7949,19 +7953,19 @@
       </c>
       <c r="D279" s="7" t="inlineStr">
         <is>
-          <t>Fiesta en el Malecón del Río: Abelardo de la Espriella celebra el triunfo en primera vuelta y redefine a la derecha</t>
+          <t>¿Qué regiones votaron por cada candidato?</t>
         </is>
       </c>
       <c r="E279" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/fiesta-en-el-malecon-del-rio-abelardo-de-la-espriella-celebra-el-triunfo-en-primera-vuelta-y-redefine-a-la-derecha/</t>
+          <t>https://canaltrece.com.co/noticias/que-regiones-votaron-por-cada-candidato/</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 05:59 p. m.</t>
+          <t>31/05/2026 06:07 p. m.</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -7976,19 +7980,19 @@
       </c>
       <c r="D280" s="4" t="inlineStr">
         <is>
-          <t>El ajedrez de la segunda vuelta: Las alianzas clave que definirán el futuro de De la Espriella y Cepeda</t>
+          <t>Fiesta en el Malecón del Río: Abelardo de la Espriella celebra el triunfo en primera vuelta y redefine a la derecha</t>
         </is>
       </c>
       <c r="E280" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/el-ajedrez-de-la-segunda-vuelta-las-alianzas-clave-que-definiran-el-futuro-de-de-la-espriella-y-cepeda/</t>
+          <t>https://canaltrece.com.co/noticias/fiesta-en-el-malecon-del-rio-abelardo-de-la-espriella-celebra-el-triunfo-en-primera-vuelta-y-redefine-a-la-derecha/</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 05:51 p. m.</t>
+          <t>31/05/2026 05:59 p. m.</t>
         </is>
       </c>
       <c r="B281" s="6" t="inlineStr">
@@ -8003,19 +8007,19 @@
       </c>
       <c r="D281" s="7" t="inlineStr">
         <is>
-          <t>Tensión en el Hotel Tequendama: Campaña de Iván Cepeda suspende transmisión en vivo ante resultados adversos</t>
+          <t>El ajedrez de la segunda vuelta: Las alianzas clave que definirán el futuro de De la Espriella y Cepeda</t>
         </is>
       </c>
       <c r="E281" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/tension-en-el-hotel-tequendama-campana-de-ivan-cepeda-suspende-transmision-en-vivo-ante-resultados-adversos/</t>
+          <t>https://canaltrece.com.co/noticias/el-ajedrez-de-la-segunda-vuelta-las-alianzas-clave-que-definiran-el-futuro-de-de-la-espriella-y-cepeda/</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 05:19 p. m.</t>
+          <t>31/05/2026 05:51 p. m.</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
@@ -8030,19 +8034,19 @@
       </c>
       <c r="D282" s="4" t="inlineStr">
         <is>
-          <t>De la Espriella Y Cepeda pasan a segunda vuelta presidencial en Colombia</t>
+          <t>Tensión en el Hotel Tequendama: Campaña de Iván Cepeda suspende transmisión en vivo ante resultados adversos</t>
         </is>
       </c>
       <c r="E282" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/de-la-espriella-y-cepeda-pasan-a-segunda-vuelta-presidencial-en-colombia/</t>
+          <t>https://canaltrece.com.co/noticias/tension-en-el-hotel-tequendama-campana-de-ivan-cepeda-suspende-transmision-en-vivo-ante-resultados-adversos/</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 04:28 p. m.</t>
+          <t>31/05/2026 05:19 p. m.</t>
         </is>
       </c>
       <c r="B283" s="6" t="inlineStr">
@@ -8057,19 +8061,19 @@
       </c>
       <c r="D283" s="7" t="inlineStr">
         <is>
-          <t>Primeros boletines de la Registraduría: Iván Cepeda y Abelardo de la Espriella lideran los resultados presidenciales</t>
+          <t>De la Espriella Y Cepeda pasan a segunda vuelta presidencial en Colombia</t>
         </is>
       </c>
       <c r="E283" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/primeros-boletines-de-la-registraduria-ivan-cepeda-y-abelardo-de-la-espriella-lideran-los-resultados-presidenciales/</t>
+          <t>https://canaltrece.com.co/noticias/de-la-espriella-y-cepeda-pasan-a-segunda-vuelta-presidencial-en-colombia/</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 04:17 p. m.</t>
+          <t>31/05/2026 04:28 p. m.</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
@@ -8084,19 +8088,19 @@
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>Balance de la Registraduría a las 4:00 p.m.: Así avanza el preconteo y la digitalización de los formularios E-14</t>
+          <t>Primeros boletines de la Registraduría: Iván Cepeda y Abelardo de la Espriella lideran los resultados presidenciales</t>
         </is>
       </c>
       <c r="E284" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/balance-de-la-registraduria-a-las-400-p-m-asi-avanza-el-preconteo-y-la-digitalizacion-de-los-formularios-e-14/</t>
+          <t>https://canaltrece.com.co/noticias/primeros-boletines-de-la-registraduria-ivan-cepeda-y-abelardo-de-la-espriella-lideran-los-resultados-presidenciales/</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 03:55 p. m.</t>
+          <t>31/05/2026 04:17 p. m.</t>
         </is>
       </c>
       <c r="B285" s="6" t="inlineStr">
@@ -8111,19 +8115,19 @@
       </c>
       <c r="D285" s="7" t="inlineStr">
         <is>
-          <t>Elecciones 2026 en vivo: resultados y minuto a minuto del preconteo</t>
+          <t>Balance de la Registraduría a las 4:00 p.m.: Así avanza el preconteo y la digitalización de los formularios E-14</t>
         </is>
       </c>
       <c r="E285" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/elecciones-2026-en-vivo-resultados-y-minuto-a-minuto-del-preconteo/</t>
+          <t>https://canaltrece.com.co/noticias/balance-de-la-registraduria-a-las-400-p-m-asi-avanza-el-preconteo-y-la-digitalizacion-de-los-formularios-e-14/</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 02:40 p. m.</t>
+          <t>31/05/2026 03:55 p. m.</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
@@ -8138,19 +8142,19 @@
       </c>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>El fenómeno ‘Polymarket’: Se disparan las apuestas que dan a Abelardo de la Espriella como favorito a la Presidencia</t>
+          <t>Elecciones 2026 en vivo: resultados y minuto a minuto del preconteo</t>
         </is>
       </c>
       <c r="E286" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/el-fenomeno-polymarket-se-disparan-las-apuestas-que-dan-a-abelardo-de-la-espriella-como-favorito-a-la-presidencia/</t>
+          <t>https://canaltrece.com.co/noticias/elecciones-2026-en-vivo-resultados-y-minuto-a-minuto-del-preconteo/</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 01:56 p. m.</t>
+          <t>31/05/2026 02:40 p. m.</t>
         </is>
       </c>
       <c r="B287" s="6" t="inlineStr">
@@ -8165,19 +8169,19 @@
       </c>
       <c r="D287" s="7" t="inlineStr">
         <is>
-          <t>Formulario E-14: cómo consultar las actas de las elecciones 2026</t>
+          <t>El fenómeno ‘Polymarket’: Se disparan las apuestas que dan a Abelardo de la Espriella como favorito a la Presidencia</t>
         </is>
       </c>
       <c r="E287" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/formulario-e-14-como-consultar-las-actas-de-las-elecciones-2026/</t>
+          <t>https://canaltrece.com.co/noticias/el-fenomeno-polymarket-se-disparan-las-apuestas-que-dan-a-abelardo-de-la-espriella-como-favorito-a-la-presidencia/</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 01:48 p. m.</t>
+          <t>31/05/2026 01:56 p. m.</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
@@ -8192,19 +8196,19 @@
       </c>
       <c r="D288" s="4" t="inlineStr">
         <is>
-          <t>¿Cuándo se posesiona el próximo presidente de Colombia en 2026?</t>
+          <t>Formulario E-14: cómo consultar las actas de las elecciones 2026</t>
         </is>
       </c>
       <c r="E288" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/cuando-se-posesiona-el-proximo-presidente-de-colombia-en-2026/</t>
+          <t>https://canaltrece.com.co/noticias/formulario-e-14-como-consultar-las-actas-de-las-elecciones-2026/</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 01:41 p. m.</t>
+          <t>31/05/2026 01:48 p. m.</t>
         </is>
       </c>
       <c r="B289" s="6" t="inlineStr">
@@ -8219,19 +8223,19 @@
       </c>
       <c r="D289" s="7" t="inlineStr">
         <is>
-          <t>Voto en blanco en Colombia: ¿qué pasa si gana en presidenciales?</t>
+          <t>¿Cuándo se posesiona el próximo presidente de Colombia en 2026?</t>
         </is>
       </c>
       <c r="E289" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/voto-en-blanco-en-colombia-que-pasa-si-gana-en-presidenciales/</t>
+          <t>https://canaltrece.com.co/noticias/cuando-se-posesiona-el-proximo-presidente-de-colombia-en-2026/</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 01:35 p. m.</t>
+          <t>31/05/2026 01:41 p. m.</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -8246,19 +8250,19 @@
       </c>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>Certificado electoral 2026: beneficios y cómo pedir copia si lo pierde</t>
+          <t>Voto en blanco en Colombia: ¿qué pasa si gana en presidenciales?</t>
         </is>
       </c>
       <c r="E290" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/certificado-electoral-2026-beneficios-y-como-pedir-copia-si-lo-pierde/</t>
+          <t>https://canaltrece.com.co/noticias/voto-en-blanco-en-colombia-que-pasa-si-gana-en-presidenciales/</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 11:49 a. m.</t>
+          <t>31/05/2026 01:35 p. m.</t>
         </is>
       </c>
       <c r="B291" s="6" t="inlineStr">
@@ -8273,19 +8277,19 @@
       </c>
       <c r="D291" s="7" t="inlineStr">
         <is>
-          <t>Delitos electorales 2026: cómo denunciar compra de votos o presiones</t>
+          <t>Certificado electoral 2026: beneficios y cómo pedir copia si lo pierde</t>
         </is>
       </c>
       <c r="E291" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/delitos-electorales-2026-como-denunciar-compra-de-votos-o-presiones/</t>
+          <t>https://canaltrece.com.co/noticias/certificado-electoral-2026-beneficios-y-como-pedir-copia-si-lo-pierde/</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 11:44 a. m.</t>
+          <t>31/05/2026 11:49 a. m.</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
@@ -8300,19 +8304,19 @@
       </c>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>Elecciones 2026: ¿qué hacer si no aparece en el puesto de votación?</t>
+          <t>Delitos electorales 2026: cómo denunciar compra de votos o presiones</t>
         </is>
       </c>
       <c r="E292" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/editorial/elecciones-2026-que-hacer-si-no-aparece-en-el-puesto-de-votacion/</t>
+          <t>https://canaltrece.com.co/noticias/delitos-electorales-2026-como-denunciar-compra-de-votos-o-presiones/</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 11:40 a. m.</t>
+          <t>31/05/2026 11:44 a. m.</t>
         </is>
       </c>
       <c r="B293" s="6" t="inlineStr">
@@ -8327,19 +8331,19 @@
       </c>
       <c r="D293" s="7" t="inlineStr">
         <is>
-          <t>Elecciones 2026: ¿se puede votar con contraseña en Colombia?</t>
+          <t>Elecciones 2026: ¿qué hacer si no aparece en el puesto de votación?</t>
         </is>
       </c>
       <c r="E293" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/elecciones-2026-se-puede-votar-con-contrasena-en-colombia/</t>
+          <t>https://canaltrece.com.co/editorial/elecciones-2026-que-hacer-si-no-aparece-en-el-puesto-de-votacion/</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 11:36 a. m.</t>
+          <t>31/05/2026 11:40 a. m.</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
@@ -8354,19 +8358,19 @@
       </c>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>Elecciones 2026: ¿qué pasa si llega a votar después de las 4:00 p. m.?</t>
+          <t>Elecciones 2026: ¿se puede votar con contraseña en Colombia?</t>
         </is>
       </c>
       <c r="E294" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/editorial/elecciones-2026-que-pasa-si-llega-a-votar-despues-de-las-400-p-m/</t>
+          <t>https://canaltrece.com.co/noticias/elecciones-2026-se-puede-votar-con-contrasena-en-colombia/</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 11:33 a. m.</t>
+          <t>31/05/2026 11:36 a. m.</t>
         </is>
       </c>
       <c r="B295" s="6" t="inlineStr">
@@ -8381,19 +8385,19 @@
       </c>
       <c r="D295" s="7" t="inlineStr">
         <is>
-          <t>Elecciones 2026: ¿hasta qué hora se puede votar hoy en Colombia?</t>
+          <t>Elecciones 2026: ¿qué pasa si llega a votar después de las 4:00 p. m.?</t>
         </is>
       </c>
       <c r="E295" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/elecciones-2026-hasta-que-hora-se-puede-votar-hoy-en-colombia/</t>
+          <t>https://canaltrece.com.co/editorial/elecciones-2026-que-pasa-si-llega-a-votar-despues-de-las-400-p-m/</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 11:27 a. m.</t>
+          <t>31/05/2026 11:33 a. m.</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
@@ -8408,19 +8412,19 @@
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>Elecciones 2026: más de 41 millones de colombianos pueden votar</t>
+          <t>Elecciones 2026: ¿hasta qué hora se puede votar hoy en Colombia?</t>
         </is>
       </c>
       <c r="E296" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/elecciones-2026-mas-de-41-millones-de-colombianos-pueden-votar/</t>
+          <t>https://canaltrece.com.co/noticias/elecciones-2026-hasta-que-hora-se-puede-votar-hoy-en-colombia/</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 10:55 a. m.</t>
+          <t>31/05/2026 11:27 a. m.</t>
         </is>
       </c>
       <c r="B297" s="6" t="inlineStr">
@@ -8435,19 +8439,19 @@
       </c>
       <c r="D297" s="7" t="inlineStr">
         <is>
-          <t>Elecciones 2026: 408.000 uniformados custodian puestos de votación</t>
+          <t>Elecciones 2026: más de 41 millones de colombianos pueden votar</t>
         </is>
       </c>
       <c r="E297" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/elecciones-2026-408-000-uniformados-custodian-puestos-de-votacion/</t>
+          <t>https://canaltrece.com.co/noticias/elecciones-2026-mas-de-41-millones-de-colombianos-pueden-votar/</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>31/05/2026 10:08 a. m.</t>
+          <t>31/05/2026 10:55 a. m.</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
@@ -8462,19 +8466,19 @@
       </c>
       <c r="D298" s="4" t="inlineStr">
         <is>
-          <t>Presidente Petro pide voto libre y mayor control estatal en los escrutinios</t>
+          <t>Elecciones 2026: 408.000 uniformados custodian puestos de votación</t>
         </is>
       </c>
       <c r="E298" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/presidente-petro-pide-voto-libre-y-mayor-control-estatal-en-los-escrutinios/</t>
+          <t>https://canaltrece.com.co/noticias/elecciones-2026-408-000-uniformados-custodian-puestos-de-votacion/</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026 09:30 a. m.</t>
+          <t>31/05/2026 10:08 a. m.</t>
         </is>
       </c>
       <c r="B299" s="6" t="inlineStr">
@@ -8489,62 +8493,66 @@
       </c>
       <c r="D299" s="7" t="inlineStr">
         <is>
-          <t>Elecciones 2026: cierres viales y desvíos en Bogotá este 31 de mayo</t>
+          <t>Presidente Petro pide voto libre y mayor control estatal en los escrutinios</t>
         </is>
       </c>
       <c r="E299" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/elecciones-2026-cierres-viales-y-desvios-en-bogota-este-31-de-mayo/</t>
+          <t>https://canaltrece.com.co/noticias/presidente-petro-pide-voto-libre-y-mayor-control-estatal-en-los-escrutinios/</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
+          <t>31/05/2026 09:30 a. m.</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
+        <is>
+          <t>Medio de Comunicación</t>
+        </is>
+      </c>
+      <c r="C300" s="3" t="inlineStr">
+        <is>
+          <t>Canal Trece</t>
+        </is>
+      </c>
+      <c r="D300" s="4" t="inlineStr">
+        <is>
+          <t>Elecciones 2026: cierres viales y desvíos en Bogotá este 31 de mayo</t>
+        </is>
+      </c>
+      <c r="E300" s="5" t="inlineStr">
+        <is>
+          <t>https://canaltrece.com.co/noticias/elecciones-2026-cierres-viales-y-desvios-en-bogota-este-31-de-mayo/</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="6" t="inlineStr">
+        <is>
           <t>31/05/2026 08:28 a. m.</t>
         </is>
       </c>
-      <c r="B300" s="3" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C300" s="3" t="inlineStr">
+      <c r="B301" s="6" t="inlineStr">
+        <is>
+          <t>Medio de Comunicación</t>
+        </is>
+      </c>
+      <c r="C301" s="6" t="inlineStr">
         <is>
           <t>Canal Trece</t>
         </is>
       </c>
-      <c r="D300" s="4" t="inlineStr">
+      <c r="D301" s="7" t="inlineStr">
         <is>
           <t>Clima para votar en elecciones 2026: lluvias en varias regiones del país</t>
         </is>
       </c>
-      <c r="E300" s="5" t="inlineStr">
+      <c r="E301" s="8" t="inlineStr">
         <is>
           <t>https://canaltrece.com.co/noticias/clima-para-votar-en-elecciones-2026-lluvias-en-varias-regiones-del-pais/</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="6" t="inlineStr"/>
-      <c r="B301" s="6" t="inlineStr">
-        <is>
-          <t>Medio de Comunicación</t>
-        </is>
-      </c>
-      <c r="C301" s="6" t="inlineStr">
-        <is>
-          <t>Canal Trece</t>
-        </is>
-      </c>
-      <c r="D301" s="7" t="inlineStr">
-        <is>
-          <t>Abelardo de la Espriella responde desde un buque blindado: «No permitiremos que Petro y Cepeda se roben las elecciones»</t>
-        </is>
-      </c>
-      <c r="E301" s="8" t="inlineStr">
-        <is>
-          <t>https://canaltrece.com.co/noticias/abelardo-de-la-espriella-responde-desde-un-buque-blindado-no-permitiremos-que-petro-y-cepeda-se-roben-las-elecciones/</t>
         </is>
       </c>
     </row>
@@ -8562,12 +8570,12 @@
       </c>
       <c r="D302" s="4" t="inlineStr">
         <is>
-          <t>Iván Cepeda rompe el silencio: Congela aceptación de resultados, tilda a De la Espriella de «fascismo mafioso» y suma apoyos clave</t>
+          <t>Abelardo de la Espriella responde desde un buque blindado: «No permitiremos que Petro y Cepeda se roben las elecciones»</t>
         </is>
       </c>
       <c r="E302" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/ivan-cepeda-rompe-el-silencio-congela-aceptacion-de-resultados-tilda-a-de-la-espriella-de-fascismo-mafioso-y-suma-apoyos-clave/</t>
+          <t>https://canaltrece.com.co/noticias/abelardo-de-la-espriella-responde-desde-un-buque-blindado-no-permitiremos-que-petro-y-cepeda-se-roben-las-elecciones/</t>
         </is>
       </c>
     </row>
@@ -8585,12 +8593,12 @@
       </c>
       <c r="D303" s="7" t="inlineStr">
         <is>
-          <t>Presidente Petro no acepta el preconteo y denuncia graves irregularidades en el software electoral</t>
+          <t>Iván Cepeda rompe el silencio: Congela aceptación de resultados, tilda a De la Espriella de «fascismo mafioso» y suma apoyos clave</t>
         </is>
       </c>
       <c r="E303" s="8" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/presidente-petro-no-acepta-el-preconteo-y-denuncia-graves-irregularidades-en-el-software-electoral/</t>
+          <t>https://canaltrece.com.co/noticias/ivan-cepeda-rompe-el-silencio-congela-aceptacion-de-resultados-tilda-a-de-la-espriella-de-fascismo-mafioso-y-suma-apoyos-clave/</t>
         </is>
       </c>
     </row>
@@ -8608,12 +8616,12 @@
       </c>
       <c r="D304" s="4" t="inlineStr">
         <is>
-          <t>Jornada histórica y pacífica en Colombia: Más de 24 millones de ciudadanos votaron y definieron el balotaje para el 21 de junio</t>
+          <t>Presidente Petro no acepta el preconteo y denuncia graves irregularidades en el software electoral</t>
         </is>
       </c>
       <c r="E304" s="5" t="inlineStr">
         <is>
-          <t>https://canaltrece.com.co/noticias/jornada-historica-y-pacifica-en-colombia-mas-de-24-millones-de-ciudadanos-votaron-y-definieron-el-balotaje-para-el-21-de-junio/</t>
+          <t>https://canaltrece.com.co/noticias/presidente-petro-no-acepta-el-preconteo-y-denuncia-graves-irregularidades-en-el-software-electoral/</t>
         </is>
       </c>
     </row>
@@ -8631,17 +8639,40 @@
       </c>
       <c r="D305" s="7" t="inlineStr">
         <is>
+          <t>Jornada histórica y pacífica en Colombia: Más de 24 millones de ciudadanos votaron y definieron el balotaje para el 21 de junio</t>
+        </is>
+      </c>
+      <c r="E305" s="8" t="inlineStr">
+        <is>
+          <t>https://canaltrece.com.co/noticias/jornada-historica-y-pacifica-en-colombia-mas-de-24-millones-de-ciudadanos-votaron-y-definieron-el-balotaje-para-el-21-de-junio/</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="3" t="inlineStr"/>
+      <c r="B306" s="3" t="inlineStr">
+        <is>
+          <t>Medio de Comunicación</t>
+        </is>
+      </c>
+      <c r="C306" s="3" t="inlineStr">
+        <is>
+          <t>Canal Trece</t>
+        </is>
+      </c>
+      <c r="D306" s="4" t="inlineStr">
+        <is>
           <t>Claudia López rompe el silencio: Pide a Cepeda asumir el liderazgo de su campaña ante el temor de una presidencia de De la Espriella</t>
         </is>
       </c>
-      <c r="E305" s="8" t="inlineStr">
+      <c r="E306" s="5" t="inlineStr">
         <is>
           <t>https://canaltrece.com.co/noticias/claudia-lopez-rompe-el-silencio-pide-a-cepeda-asumir-el-liderazgo-de-su-campana-ante-el-temor-de-una-presidencia-de-de-la-espriella/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E305"/>
+  <autoFilter ref="A1:E306"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -8947,6 +8978,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E303" r:id="rId302"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E304" r:id="rId303"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E306" r:id="rId305"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
